--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -65,7 +65,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="Microsoft YaHei UI"/>
       <charset val="134"/>
       <family val="2"/>
       <color theme="1"/>
@@ -73,13 +73,13 @@
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="128"/>
       <family val="3"/>
-      <sz val="9"/>
+      <sz val="6"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Microsoft YaHei UI"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
       <family val="2"/>
       <color theme="1"/>
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,11 +260,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1802,8 +1807,8 @@
     <col width="5.265625" bestFit="1" customWidth="1" style="19" min="26" max="26"/>
     <col width="4.73046875" bestFit="1" customWidth="1" style="19" min="27" max="28"/>
     <col width="5.1328125" bestFit="1" customWidth="1" style="19" min="29" max="29"/>
-    <col width="9" customWidth="1" style="14" min="30" max="30"/>
-    <col width="9" customWidth="1" style="14" min="31" max="16384"/>
+    <col width="9" customWidth="1" style="14" min="30" max="31"/>
+    <col width="9" customWidth="1" style="14" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -4395,7 +4400,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>niu_bang</t>
+          <t>niu_bang_zi</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
@@ -4479,7 +4484,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>dou_chi</t>
+          <t>dan_dou_chi</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -4731,7 +4736,7 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>dou_chi</t>
+          <t>dan_dou_chi</t>
         </is>
       </c>
       <c r="C40" s="35" t="inlineStr">
@@ -4759,7 +4764,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>zhi_pi</t>
+          <t>zhi_zi</t>
         </is>
       </c>
       <c r="C41" s="35" t="inlineStr">
@@ -6467,7 +6472,7 @@
       </c>
       <c r="B102" s="27" t="inlineStr">
         <is>
-          <t>mai_dong</t>
+          <t>mai_men_dong</t>
         </is>
       </c>
       <c r="C102" s="28" t="inlineStr">
@@ -6719,7 +6724,7 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>tian_dong</t>
+          <t>tian_men_dong</t>
         </is>
       </c>
       <c r="C111" s="29" t="inlineStr">
@@ -6747,7 +6752,7 @@
       </c>
       <c r="B112" s="27" t="inlineStr">
         <is>
-          <t>mai_dong</t>
+          <t>mai_men_dong</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
@@ -8231,7 +8236,7 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>tong_cao</t>
+          <t>mu_tong</t>
         </is>
       </c>
       <c r="C165" s="30" t="inlineStr">
@@ -9211,7 +9216,7 @@
       </c>
       <c r="B200" s="27" t="inlineStr">
         <is>
-          <t>mai_dong</t>
+          <t>mai_men_dong</t>
         </is>
       </c>
       <c r="C200" s="29" t="inlineStr">
@@ -11707,7 +11712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
@@ -11803,7 +11808,7 @@
         <is>
           <t>生姜
 【气味】
-辛，温
+味辛，性温
 【毒性】
 无毒
 【归经】
@@ -11868,9 +11873,9 @@
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>葱白
+          <t>葱白（葱）
 【气味】
-辛，温
+味辛，性温
 【毒性】
 无毒
 【归经】
@@ -11996,9 +12001,9 @@
       </c>
       <c r="H5" s="39" t="inlineStr">
         <is>
-          <t>桂枝
+          <t>桂枝（桂）
 【气味】
-辛、甘，温
+味辛、甘，性温
 【毒性】
 无毒
 【归经】
@@ -12061,9 +12066,9 @@
       </c>
       <c r="H6" s="39" t="inlineStr">
         <is>
-          <t>杏仁
+          <t>杏仁（杏）
 【气味】
-苦，温
+味苦，性温
 【毒性】
 有小毒
 【归经】
@@ -12127,7 +12132,7 @@
         <is>
           <t>甘草
 【气味】
-甘，平
+味甘，性平
 【毒性】
 无毒
 【归经】
@@ -12269,9 +12274,9 @@
       </c>
       <c r="H9" s="39" t="inlineStr">
         <is>
-          <t>大枣
+          <t>大枣（枣）
 【气味】
-甘，温
+味甘，性温
 【毒性】
 无毒
 【归经】
@@ -12336,9 +12341,9 @@
       </c>
       <c r="H10" s="39" t="inlineStr">
         <is>
-          <t>葛根
+          <t>葛根（葛）
 【气味】
-甘、辛、凉
+味甘、辛，性凉
 【毒性】
 无毒
 【归经】
@@ -12407,9 +12412,9 @@
       </c>
       <c r="H11" s="39" t="inlineStr">
         <is>
-          <t>桑叶
+          <t>桑叶（桑）
 【气味】
-甘、苦，寒
+味甘、苦，性寒
 【毒性】
 无毒
 【归经】
@@ -12474,9 +12479,9 @@
       </c>
       <c r="H12" s="39" t="inlineStr">
         <is>
-          <t>菊花
+          <t>菊花（菊）
 【气味】
-甘、苦，微寒
+味甘、苦，性微寒
 【毒性】
 无毒
 【归经】
@@ -12494,12 +12499,7 @@
 《抱朴子》云︰仙方所谓日精、更生、周盈，皆一菊而根、茎、花、实之名异也。
 【发明】
 震亨曰︰黄菊花属土与金，有水与火，能补阴血，故养目。
-时珍曰︰菊春生夏茂，秋花冬实，备受四气，饱经露霜，叶枯不落，花槁不零，味兼甘苦，性禀平和。昔人谓其能除风热，益肝补阴，盖不知其得金水之精英尤多，能益金水二脏也。补水所以制火，益金所以平木，木平则风息，火降则热除，用治诸风头目，其旨深微。黄者入金水阴分；白者，入金水阳分；红者，行妇人血分。皆可入药，神而明之，存乎其人。其苗可蔬，叶可啜，花可饵，根实可药，囊之可枕，酿之可饮，自本至末，罔不有功。宜乎前贤比之君子，神农列之上品，隐士采入酒饵，骚人餐其落英。
-费长房言︰九日饮菊酒，可以辟不祥。
-《神仙传》言︰康风子、朱孺子皆以服菊花成仙。
-《荆州记》言︰胡广久病风羸，饮菊潭水多寿。菊之贵重如此，是岂群芳可伍哉？
-钟会《菊有五美赞》云︰圆花高悬，准天极也。纯黄不杂，后土色也。早植晚发，君子德也；冒霜吐颖，象贞质也；杯中体轻，神仙 食也。
-《西京杂记》言︰采菊花茎叶，杂秫米酿酒，至次年九月始熟，用之</t>
+时珍曰︰菊春生夏茂，秋花冬实，备受四气，饱经露霜，叶枯不落，花槁不零，味兼甘苦，性禀平和。昔人谓其能除风热，益肝补阴，盖不知其得金水之精英尤多，能益金水二脏也。补水所以制火，益金所以平木，木平则风息，火降则热除，用治诸风头目，其旨深微。黄者入金水阴分；白者，入金水阳分；红者，行妇人血分。皆可入药，神而明之，存乎其人。其苗可蔬，叶可啜，花可饵，根实可药，囊之可枕，酿之可饮，自本至末，罔不有功。宜乎前贤比之君子，神农列之上品，隐士采入酒饵，骚人餐其落英。费长房言︰九日饮菊酒，可以辟不祥。《神仙传》言︰康风子、朱孺子皆以服菊花成仙。《荆州记》言︰胡广久病风羸，饮菊潭水多寿。菊之贵重如此，是岂群芳可伍哉？钟会《菊有五美赞》云︰圆花高悬，准天极也。纯黄不杂，后土色也。早植晚发，君子德也；冒霜吐颖，象贞质也；杯中体轻，神仙 食也。《西京杂记》言︰采菊花茎叶，杂秫米酿酒，至次年九月始熟，用之</t>
         </is>
       </c>
       <c r="I12" s="38" t="inlineStr">
@@ -12617,7 +12617,7 @@
         <is>
           <t>桔梗
 【气味】
-苦、辛，平
+味苦、辛，性平
 【毒性】
 小毒
 【归经】
@@ -12679,9 +12679,9 @@
       </c>
       <c r="H15" s="39" t="inlineStr">
         <is>
-          <t>芦根
+          <t>芦根（芦）
 【气味】
-甘，寒
+味甘，性寒
 【毒性】
 无毒
 【归经】
@@ -12745,7 +12745,7 @@
         <is>
           <t>金银花（忍冬）
 【气味】
-甘，寒
+味甘，性寒
 【毒性】
 无毒
 【归经】
@@ -12808,7 +12808,7 @@
         <is>
           <t>连翘
 【气味】
-苦，微寒
+味苦，性微寒
 【毒性】
 无毒
 【归经】
@@ -12836,1838 +12836,3149 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>niu_bang</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>牛蒡</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>niu_bang_zi</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>牛蒡子</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>寒</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>牛蒡子（恶实）
+【气味】
+味辛、苦，性寒
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+疏散风热
+宣肺透疹
+解毒利咽
+滑肠通便
+【释名】
+鼠粘（《别录》）、牛蒡（《别录》）、大力子（《纲目》）、蒡翁菜（《纲目》）、便牵牛（《纲目》）、蝙蝠刺。
+时珍曰︰其实状恶而多刺钩，故名也。其根叶皆可食，人呼为牛菜，术人隐之呼为大力也。俚人谓之便牵牛。河南人呼为夜叉头。
+颂曰︰实壳多刺，鼠过之则缀惹不可脱，故谓之鼠粘子，亦如羊负来之比。
+【发明】
+杲曰︰鼠粘子其用有四︰治风湿瘾疹，咽喉风热，散诸肿疮疡之毒，利凝滞腰 膝之气，是也。</t>
+        </is>
+      </c>
+      <c r="I18" s="38" t="inlineStr">
+        <is>
+          <t>草之四</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>jing_jie</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>荆芥</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>辛</t>
+        </is>
+      </c>
+      <c r="E19" s="39" t="inlineStr">
+        <is>
+          <t>肝|肺</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G19" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H19" s="39" t="inlineStr">
+        <is>
+          <t>荆芥（假苏）
+【气味】
+味辛，性微温
+【毒性】
+无毒
+【归经】
+归肺、肝经
+【主治】
+解表散风
+透疹
+利咽消肿
+止血
+【释名】
+姜芥（《别录》）、荆芥（《吴普》）、鼠 （《本经》）。
+弘景曰︰假苏方药不复用。
+恭曰︰此即菜中荆芥也，姜芥声讹尔。先居草部，今录入菜部。
+士良曰︰荆芥本草呼为假苏。假苏又别是一物。叶锐圆，多野生，以香气似苏，故呼为苏。
+颂曰︰医官陈巽言︰江左人谓假苏、荆芥实两物。苏恭以本草一名姜芥，荆姜声讹，谓为荆芥，非矣。
+时珍曰︰按《吴普本草》云︰假苏一名荆芥，叶似落藜而细，蜀中生啖之。普乃东汉末 人，去《别录》时未远，其言当不谬，故唐人苏恭祖其说。而陈士良、苏颂复启为两物之疑，亦臆说尔。曰苏、曰姜、曰芥，皆因气味辛香，如苏、如姜、如芥也。
+【发明】
+元素曰︰荆芥辛苦，气味俱薄，浮而升，阳也。
+好古曰︰肝经气分药也。能搜肝气。
+时珍曰︰荆芥入足厥阴经气分，其功长于祛风邪，散瘀血，破结气，消疮毒。盖厥阴乃风木也，主血，而相火寄之，故风病血病疮病为要药。其治风也，贾丞相称为再生丹，许学 士谓有神圣功，戴院使许为产后要药，萧存敬呼为一捻金，陈无择隐为举卿古拜散，夫岂无故而得此隆誉哉？按《唐韵》︰荆字，举卿切，芥字古拜切。盖二字之反切，隐语以秘其方也。
+又曰︰荆芥反鱼蟹河豚之说，本草医方并未言及，而稗官小说往往载之。按李廷飞《延 寿书》云︰凡食一切无鳞鱼，忌荆芥。食黄 鱼后食之，令人吐血，惟地浆可解。与蟹同食，动风。又《蔡絛铁围山丛话》云︰予居岭峤，见食黄颡鱼犯姜芥者立死，甚于钩吻。洪 迈《夷坚志》云︰吴人魏几道，啖黄颡鱼羹，后采荆芥和茶饮。少顷足痒，上彻心肺，狂走，足皮欲裂。急服药，两日乃解。陶九成《辍耕录》云︰凡食河豚，不可服荆芥药，大相反。 予在江阴见一儒者，因此丧命。《苇航纪谈》云︰凡服荆芥风药，忌食鱼。杨诚斋曾见一人，立致于死也。时珍按︰荆芥乃日用之药，其相反如此，故详录之，以为警戒。又按《物类相感志》言︰河豚用荆芥同煮，三五次换水，则无毒。其说与诸书不同，何哉？大抵养生者，宁守前说为戒可也。</t>
+        </is>
+      </c>
+      <c r="I19" s="38" t="inlineStr">
+        <is>
+          <t>草之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>dan_dou_chi</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>淡豆豉</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>凉</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>苦|辛</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>脾|肺</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="38" t="inlineStr">
-        <is>
-          <t>草之四</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>jing_jie</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>荆芥</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t>淡豆豉（大豆豉）
+【气味】
+味苦、辛，性凉
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+解表除烦
+宣发郁热
+【释名】
+时珍曰︰按︰刘熙《释名》云︰豉，嗜也。调和五味，可甘嗜也。许慎《说文》谓豉为配盐幽菽者，乃咸豉也。
+【发明】
+弘景曰︰豉，食中常用。春夏之气不和，蒸炒以酒渍服之至佳。依康伯法，先以醋、酒溲蒸曝燥，麻油和，再蒸曝之，凡三过，末椒、姜治和进食，大胜今时油豉也。患脚人，常将渍酒饮之，以滓敷脚，皆瘥。
+颂曰︰古今方书用豉治病最多，江南人善作豉，凡得时气，即先用葱豉汤服之取汗，往往便瘥也。
+时珍曰︰陶说康伯豉法，见《博物志》，云原出外国，中国谓之康伯，乃传此法之姓名耳。其豉调中下气最妙。黑豆性平，作豉则温。既经蒸 ，故能升能散。得葱则发汗，得盐则能吐，得酒则治风，得薤则治痢，得蒜则止血，炒熟则又能止汗，亦麻黄根节之义也。</t>
+        </is>
+      </c>
+      <c r="I20" s="38" t="inlineStr">
+        <is>
+          <t>谷之四</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>zhu_ye</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>竹叶</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>甘|淡</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t>心|脾</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G21" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H21" s="39" t="inlineStr">
+        <is>
+          <t>竹叶（竹）
+【气味】
+味甘、淡，性寒
+【毒性】
+无毒
+【归经】
+归心、胃、小肠经
+【主治】
+清热泻火
+除烦
+生津利尿
+【释名】
+时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。
+故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+【发明】
+弘景曰︰甘竹叶最胜。
+诜曰︰竹叶︰ 、苦、淡、甘之外，馀皆不堪入药，不宜人。淡竹为上，甘竹次之。
+宗奭曰︰诸竹笋性皆微寒，故知其叶一致也。张仲景竹叶汤，惟用淡竹。
+元素曰︰竹叶苦平，阴中微阳。
+杲曰︰竹叶辛苦寒，可升可降，阳中阴也。其用有二︰除新久风邪之烦热，止喘促气胜</t>
+        </is>
+      </c>
+      <c r="I21" s="38" t="inlineStr">
+        <is>
+          <t>木之五</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>sha_shen</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>沙参</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G22" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H22" s="39" t="inlineStr">
+        <is>
+          <t>沙参
+【气味】
+味甘，性微寒
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+养阴清肺
+益胃生津
+化痰益气
+【释名】
+白参（《吴普》）、知母（《别录》）、羊乳（《别录》）、羊婆奶（《纲目》）、铃儿草（《别录》）、虎须（《别录》）、苦心（《别录》，又名文希，一名识美，一名志取。）
+弘景曰︰此与人参、玄参、丹参、苦参是为五参，其形不尽相类，而主疗颇同，故皆有参名。又有紫参，乃牡蒙也。
+时珍曰︰沙参白色，宜于沙地，故名。其根多白汁，俚人呼为羊婆奶。《别录》有名未用，羊乳即此也。此物无心味淡，而《别录》一名苦心，又与知母同名，不知所谓也。铃儿草，象花形也。
+【发明】
+元素曰︰肺寒者，用人参；肺热者，用沙参代之，取其味甘也。好古曰︰沙参味甘微苦，厥阴本经之药，又为脾经气分药。微苦补阴，甘则补阳，故洁古取沙参代人参。盖人参性温，补五脏之阳；沙参性寒，补五脏之阴。虽云补五脏，亦须各用本脏药相佐，使随所引而相辅之可也。
+时珍曰︰人参甘苦温，其体重实，专补脾胃元气，因而益肺与肾，故内伤元气者宜之。沙参甘淡而寒，其体轻虚，专补肺气，因而益脾与肾，故金能受火克者宜之。一补阳而生阴，一补阴而制阳，不可不辨之也。</t>
+        </is>
+      </c>
+      <c r="I22" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>bei_mu</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>贝母</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E23" s="39" t="inlineStr">
+        <is>
+          <t>心|肺</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G23" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H23" s="39" t="inlineStr">
+        <is>
+          <t>贝母
+【气味】
+味甘、苦，性微寒
+【毒性】
+无毒
+【归经】
+归肺、心经
+【主治】
+清热润肺
+化痰止咳
+散结消痈
+【释名】
+（《尔雅》，音萌）、勤母（《别录》）、苦菜（《别录》）、苦花（《别录》）、空草（《本经》）、药实。
+弘景曰：形似聚贝子，故名贝母。
+时珍曰：《诗》云言采其 ，即此。一作虻，谓根状如虻也。苦菜、药实，与野苦 、黄药子同名。
+【发明】
+承曰：贝母能散心胸郁结之气，故《诗》云言：采其 ，是也。作诗者，本以不得志而言。今用治心中气不快、多愁郁者，殊有功。信矣。
+好古曰：贝母乃肺经气分药也。 仲景治寒实结胸、外无热证者，三物小陷胸汤主之，白散亦可，以其内有贝母也。
+成无己云： 辛散而苦泄，桔梗、贝母之苦辛，用以下气。
+机曰：俗以半夏有毒，用贝母代之。夫贝母乃太阴肺经之药，半夏乃太阴脾经、阳明胃经之药，何可以代？若虚劳咳嗽、吐血咯血、肺痿 肺痈、妇人乳痈、痈疽及诸郁之证，半夏乃禁忌，皆贝母为向导，犹可代也；至于脾胃湿热，涎化为痰，久则生火，痰火上攻，昏愦僵仆蹇涩诸证，生死旦夕，亦岂贝母可代乎？颂曰： 贝母治恶疮。
+唐人记其事云：江左尝有商人，左膊上有疮如人面，亦无他苦。商人戏以酒滴 口中，其面赤色。以物食之，亦能食，多则膊内肉胀起。或不食，则一臂痹焉。有名医教其历试诸药，金石草木之类，悉无所苦，至贝母，其疮乃聚眉闭口。商人喜，因以小苇筒毁其口灌之，数日成痂遂愈，然不知何疾也。
+《本经》言主金疮，此岂金疮之类欤？</t>
+        </is>
+      </c>
+      <c r="I23" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>zhi_zi</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>栀子</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>苦</t>
+        </is>
+      </c>
+      <c r="E24" s="39" t="inlineStr">
+        <is>
+          <t>心|肺</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G24" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H24" s="39" t="inlineStr">
+        <is>
+          <t>栀子
+【气味】
+味苦，性寒
+【毒性】
+无毒
+【归经】
+心、肺、三焦经
+【主治】
+清泄肺热
+疏散肌表湿热
+凉血解毒
+【释名】
+木丹（《本经》）、越桃（《别录》）
+时珍曰︰卮，酒器也。栀子象之，故名。俗作栀。
+司马相如赋云︰鲜支黄砾。注云︰鲜支即支子也。佛书称其花为卜，谢灵运谓之林兰，曾端伯呼为禅友。
+或曰︰卜金色，非栀子也。
+【发明】
+元素曰︰栀子轻飘而象肺，色赤而象火，故能泻肺中之火。
+其用有四︰心经客热一也，除烦躁二也，去上焦虚热三也，治风四也。
+震亨曰︰栀子泻三焦之火，及痞块中火邪，最清胃脘之血。其性屈曲下行，能降火从小便中泄去。凡心痛稍久，不宜温散，反助火邪。故古方多用栀子以导热药，则邪易伏而病易退。
+好古曰︰本草不言栀子能吐，仲景用为吐药。栀子本非吐药，为邪气在上，拒而不纳，食令上吐，则邪因以出，所谓“其高者因而越之”也。或用为利小便药，实非利小便，乃清肺也。肺清则化行，而膀胱津液之府，得此气化而出也。本草言治大小肠热，乃辛与庚合，又与丙合，又能泄戊，先入中州故也。仲景治烦躁用栀子豉汤，烦者气也，躁者血也。气主肺，血主肾。故用栀子以治肺烦，香杲曰︰仲景以栀子色赤味苦，入心而治烦；香豉色黑味咸，入肾而治躁。
+宗奭曰︰仲景治伤寒发汗吐下后，虚烦不得眠；若剧者，必反复颠倒，心中懊 ，栀子豉汤治之。因其虚，故不用大黄，有寒毒故也。栀子虽寒而无毒，治胃中热气，既亡血亡津液，腑脏无润养，内生虚热，非此物不可去也。又治心经留热，小便赤涩，用去皮栀子（火煨）、大黄、连翘、炙甘草等分末之，水煎三钱服，无不利也。
+发黄，皆用栀子、茵陈、甘草、香豉四物作汤饮。又治大病后劳复，皆用栀子、鼠矢等汤，利小便而愈。其方极多，不可悉载。</t>
+        </is>
+      </c>
+      <c r="I24" s="38" t="inlineStr">
+        <is>
+          <t>木之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>li_pi</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>梨皮</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>凉</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>甘|涩</t>
+        </is>
+      </c>
+      <c r="E25" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G25" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H25" s="39" t="inlineStr">
+        <is>
+          <t>梨皮（梨）
+【气味】
+味甘、微涩，性凉
+【毒性】
+无毒
+【归经】
+归肺、心、肾经
+【主治】
+清心润肺
+降火生津
+止咳化痰
+【释名】
+快果、果宗、玉乳、蜜父。
+震亨曰︰梨者，利也。其性下行流利也。
+弘景曰︰梨种殊多，并皆冷利，多食损人，故俗人谓之快果，不入药用。
+【发明】
+宗奭曰︰梨，多食动脾，少则不及病，用梨者当斟酌之。惟病酒烦渴人食之甚佳，终不能却疾。
+慎微曰︰孙光宪《北梦琐言》云︰有一朝士见奉御梁新诊之，曰︰风疾已深，请速归去。复见 州马医赵鄂诊之，言与梁同，但请多吃消梨，咀 不及，绞汁而饮。到家旬日，唯吃消梨，顿爽也。
+时珍曰︰《别录》著梨，只言其害，不著其功。陶隐居言梨不入药。盖古人论病多主风寒，用药皆是桂、附，故不知梨有治风热、润肺凉心、消痰降火、解毒之功也。今人痰病、火病，十居六、七。梨之有益，盖不为少，但不宜过食尔。按︰《类编》云︰一士人状若有疾，厌厌无聊，往谒杨吉老诊之。杨曰︰君热症已极，气血消铄，此去三年，当以疽死。士人不乐而去。闻茅山有道士医术通神，而不欲自鸣。乃衣仆衣，诣山拜之，愿执薪水之役。道士留置弟子中。久之以实白道士。道士诊之，笑曰︰汝便下山，但日日吃好梨一颗。如生梨已尽，则取干者泡汤，食滓饮汁，疾自当平。士人如其戒，经一岁复见吉老。见其颜貌腴泽，脉息和平，惊曰︰君必遇异人，不然岂有痊理？士人备告吉老。吉老具衣冠望茅山设拜，自咎其学之未至。此与琐言之说仿佛。观夫二条，则梨之功岂小补哉？然惟乳梨、鹅梨、消梨可食，余梨则亦不能去病也。</t>
+        </is>
+      </c>
+      <c r="I25" s="38" t="inlineStr">
+        <is>
+          <t>果之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>su_ye</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>苏叶</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>辛</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G26" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H26" s="39" t="inlineStr">
+        <is>
+          <t>苏叶（苏）
+【气味】
+味辛，性温
+【毒性】
+无毒
+【归经】
+归肺、脾经
+【主治】
+解表散寒
+行气和胃
+【释名】
+紫苏（《食疗》）、赤苏（《肘后方》）
+桂荏时珍曰︰苏从酥，音酥，舒畅也。苏性舒畅，行气和血，故谓之苏。曰紫苏者，以别白苏也。苏乃荏类，而味更辛如桂，故《尔 雅》谓之桂荏。
+【发明】
+颂曰︰若宣通风毒，则单用茎，去节尤良。
+时珍曰︰紫苏，近世要药也。其味辛，入气分；其色紫，入血分。故同橘皮，砂仁，则行气安胎；同藿香、乌药，则温中止痛；同香附、麻黄，则发汗解肌；同芎 、当归则和血散血；同木瓜、浓朴，则散湿解暑，治霍乱、脚气；同桔梗、枳壳，则利膈宽肠；同杏仁、莱菔子，则消痰定喘也。 久则泄人真气焉。
+宗奭曰︰紫苏其气香，其味微辛甘能散。今人朝暮饮紫苏汤，甚无益。医家谓芳草致豪贵之疾者，此有一焉。若脾胃寒人，多致滑泄，往往不觉。</t>
+        </is>
+      </c>
+      <c r="I26" s="38" t="inlineStr">
+        <is>
+          <t>草之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>ban_xia</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>辛</t>
+        </is>
+      </c>
+      <c r="E27" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F27" s="39" t="inlineStr">
+        <is>
+          <t>有毒</t>
+        </is>
+      </c>
+      <c r="G27" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H27" s="39" t="inlineStr">
+        <is>
+          <t>半夏
+【气味】
+味辛，性温
+【毒性】
+有毒
+【归经】
+归脾、胃、肺经
+【主治】
+燥湿化痰
+降逆止呕
+消痞散结
+【释名】
+守田（《别录》）、水玉（《本经》）
+时珍曰︰《礼记‧月令》︰五月半夏生。盖当夏之半也，故名。守田会意，水玉因形。
+【发明】
+权曰︰半夏使也。虚而有痰气，宜加用之。
+颂曰︰胃冷呕哕，方药之最要。
+成无己曰︰辛者散也，润也。半夏之辛，以散逆气结气，除烦呕，发音声，行水气，而润肾燥。
+好古曰︰《经》云︰肾主五液，化为五湿。自入为唾，入肝为泣，入心为汗，入脾为痰，入肺为涕。有痰曰嗽，无痰曰咳。痰者，因咳而动脾之湿也。 半夏能泄痰之标，不能泄痰之本。泄本者，泄肾也。咳无形，痰有形；无形则润，有形 则燥，所以为流湿润燥也。俗以半夏为肺药，非也。止呕吐为足阳明，除痰为足太阴。柴胡为之使，故今柴胡汤中用之，虽为止呕，亦助柴胡、黄芩主往来寒热，是又为足少阳、阳明也。
+宗奭曰︰今人惟知半夏去痰，不言益脾，盖能分水故也。脾恶湿，湿则濡困，困则不能治水。《经》云︰湿胜则泻。一男子夜数如厕，或教以生姜一两，半夏、大枣各三十枚，水一升，瓷瓶中慢火烧为熟水，时呷之，便已也。 赵继宗曰︰丹溪言︰二陈汤治一身之痰，世医执之，凡有痰者皆用。夫二陈内有半夏，其性燥烈，若风痰、寒痰、湿痰、食痰则相宜；至于劳痰、失血诸痰，用之反能燥血液而加 病，不可不知。 
+机曰︰俗以半夏性燥有毒，多以贝母代之。贝母乃太阴肺经之药，半夏乃太阴脾经、阳 明胃经之药，何可代也？夫咳嗽吐痰，虚劳吐血，或痰中见血，诸郁，咽痛喉痹，肺痈肺痿，痈疽，妇人乳难，此皆贝母为向导，半夏乃禁用之药。若涎者脾之液，美味膏粱炙爆，皆能生脾胃湿热，故涎化为痰，久则痰火上攻，令人昏愦口噤，偏废僵仆，蹇涩不语，生死旦夕，自非半夏、南星，曷可治乎？若以贝母代之，则翘首待毙矣。
+时珍曰︰脾无留湿不生痰，故脾为生痰之源，肺为贮痰之器。半夏能主痰饮及腹胀者，为其体滑而味辛性温也。涎滑能润，辛温能散亦能润，故行湿而通大便，利窍而泄小便。所谓辛走气，能化液，辛以润之是矣。洁古张氏云︰半夏、南星治其痰，而咳嗽自愈。丹溪朱氏云︰二陈汤能使大便润而小便长。聊摄成氏云︰半夏辛而散，行水气而润肾燥。又《和剂 局方》，用半硫丸治老人虚秘，皆取其滑润也。世俗皆以南星、半夏为性燥，误矣。湿去则土燥，痰涎不生，非二物之性燥也。古方治咽痛喉痹，吐血下血，多用二物，非禁剂也。二物亦能散血，故破伤打扑皆主之。惟阴虚劳损，则非湿热之邪，而用利窍行湿之药，是乃重 竭其津液，医之罪也，岂药之咎哉？《甲乙经》用治夜不眠，是果性燥者乎？岐伯云︰卫气行于阳，阳气满，不得入于阴，阴气虚，故目不得瞑。治法︰饮以半夏汤一剂，阴阳既通，其卧立至。方用流水千里者八升，扬之万遍，取清五升，煮之，炊以苇薪，大沸，入秫米一升，半夏五合，煮一升半，饮汁一杯，日三，以知为度。病新发者，覆杯则卧，汗出则已。久者，三饮而已。</t>
+        </is>
+      </c>
+      <c r="I27" s="38" t="inlineStr">
+        <is>
+          <t>草之六</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>qian_hu</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>前胡</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>苦|辛</t>
+        </is>
+      </c>
+      <c r="E28" s="39" t="inlineStr">
+        <is>
+          <t>肺</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G28" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H28" s="39" t="inlineStr">
+        <is>
+          <t>前胡
+【气味】
+味苦、辛，性微寒
+【毒性】
+无毒
+【归经】
+归肺经
+【主治】
+降气化痰
+散风清热
+【释名】
+时珍曰：按：孙 《唐韵》作湔胡，名义未解。
+【发明】
+时珍曰：前胡味甘、辛，气微平，阳中之阴，降也。乃手足太阴、阳明之药，与柴胡纯阳上升入少阳、厥阴者不同也。其功长于下气，故能治痰热喘嗽、痞膈呕逆诸疾，气下则火降，痰亦降矣。所以有推陈致新之绩，为痰气要药。陶弘景言其与柴胡同功，非矣。治证虽同，而所入所主则异。</t>
+        </is>
+      </c>
+      <c r="I28" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>chen_pi</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D29" s="39" t="inlineStr">
+        <is>
+          <t>苦|辛</t>
+        </is>
+      </c>
+      <c r="E29" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G29" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H29" s="39" t="inlineStr">
+        <is>
+          <t>陈皮（橘）
+【气味】
+味苦、辛，性温
+【毒性】
+无毒
+【归经】
+归脾、肺经
+【主治】
+理气健脾
+燥湿化痰
+【释名】
+红皮（《汤液》）、陈皮（《食疗》）。
+弘景曰︰橘皮疗气大胜。以东橘为好，西江者不如。须陈久者为良。
+好古曰︰橘皮以色红日久者为佳，故曰红皮、陈皮。去白者曰橘红也。
+【发明】
+杲曰︰橘皮，气薄味浓，阳中之阴也。可升可降，为脾、肺二经气分药。留白则补脾胃，去白则理肺气；同白术则补脾胃，同甘草则补肺，独用则泻肺损脾。其体轻浮，一能导胸中寒邪，二破滞气，三益脾胃。加青皮减半用之，去滞气，推陈致新。但多用久服，能损元气也。
+原曰︰橘皮，能散、能泻、能温、能补、能和，化痰治嗽，顺气理中，调脾快膈，通五淋，疗酒病，其功当在诸药之上。
+时珍曰︰橘皮，苦能泄、能燥，辛能散，温能和。其治百病，总是取其理气燥湿之功。
+同补药则补，同泻药则泻，同升药则升，同降药则降。脾乃元气之母，肺乃摄气之 ，故橘皮为二经气分之药，但随所配而补泻升降也。洁古张氏云︰陈皮、枳壳利其气而痰自下，盖此义也。同杏仁治大肠气秘，同桃仁治大肠血秘，皆取其通滞也。详见杏仁下。按方勺《泊宅编》云︰橘皮宽膈降气，消痰饮，极有殊功。他药贵新，惟此贵陈。外舅莫强中令丰城时得疾，凡食已辄胸满不下，百方不效。偶家人合橘红汤，因取尝之，似相宜，连日饮之。一日忽觉胸中有物坠下，大惊目瞪，自汗如雨。须臾腹痛，下数块如铁弹子，臭不可闻。自此胸次廓然，其疾顿愈，盖脾之冷积也。其方︰用橘皮（去穰）一斤，甘草、盐花各四两。水五碗，慢火煮干，焙研为末，白汤点服。名二贤散，治一切痰气特验。世医徒知半夏、南星之属，何足以语此哉？珍按︰二贤散，丹溪变之为润下丸，用治痰气有效。惟气实人服之相宜，气不足者不宜用之也。</t>
+        </is>
+      </c>
+      <c r="I29" s="38" t="inlineStr">
+        <is>
+          <t>果之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>fu_ling</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>茯苓</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>甘|淡</t>
+        </is>
+      </c>
+      <c r="E30" s="39" t="inlineStr">
+        <is>
+          <t>心|脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G30" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H30" s="39" t="inlineStr">
+        <is>
+          <t>茯苓
+【气味】
+味甘、淡，性平
+【毒性】
+无毒
+【归经】
+归心、肺、脾、肾经
+【主治】
+利水渗湿
+健脾宁心
+【释名】
+伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
+宗奭曰︰多年樵斫之松根之气味，抑郁未绝，精英未沦。其精气盛者，发泄于外，结为茯苓，故不抱根，离其本体，有零之义也。津气不盛，只能附结本根，既不离本，故曰伏神。
+时珍曰︰茯苓，《史记•龟策传》作伏灵。盖松之神灵之气，伏结而成，故谓之伏灵、伏神也。《仙经》言︰伏灵大如拳者，佩之令百鬼消灭，则神灵之气，亦可征矣。俗作苓者，传写之讹尔。下有伏灵，上有菟丝，故又名伏莬。或云“其形如兔，故名”，亦通。
+【发明】
+弘景曰︰茯苓白色者补，赤色者利。俗用甚多，仙方服食亦为至要。云其通神而致灵，和魂而炼魄，利窍而益肌，浓肠而开心，调营而理卫，上品仙药也。善能断谷不饥。
+宗奭曰︰茯苓行水之功多，益心脾不可缺也。
+元素曰︰茯苓赤泻白补，上古无此说。气味俱薄，性浮而升。其用有五︰利小便也；开腠理也，生津液也，除虚热也，止泻也。如小便利或数者，多服则损人目。汗多人服之，亦损元气，夭人寿，为其淡而渗也。又云︰淡为天之阳，阳当上行，何以利水而泻下？气薄者阳中之阴，所以茯苓利水泻下。不离阳之体，故入手太阳。
+杲曰︰白者入壬癸，赤者入丙丁。味甘而淡，降也，阳中阴也。其用有六︰利窍而除湿，益气而和中，治惊悸，生津液，小便多者能止，小便结者能通。又云︰湿淫所胜，小便不利。淡以利窍，甘以助阳。甘平能益脾逐水，乃除湿之圣药也。
+好古曰︰白者入手太阴、足太阳、少阳经气分，赤者入足太阴、手少阴、太阳气分。伐肾邪。小便多，能止之；小便涩，能利之。与车前子相似，虽利小便而不走气。酒浸与光明朱砂同用，能秘真元。味甘而平，如何是利小便耶？
+震亨曰︰茯苓，得松之馀气而成，属金，仲景利小便多用之，此暴新病之要药也。若阴虚者，恐未为宜。此物有行水之功，久服损人。八味丸用之者，亦不过接引他药归就肾经，去胞中久陈积垢，为搬运之功尔。
+时珍曰︰茯苓本草又言利小便，伐肾邪。至李东垣、王海藏乃言小便多者能止，涩者能通，同朱砂能秘真元。而朱丹溪又言阴虚者不宜用，义似相反，何哉？茯苓气味淡而渗，其性上行，生津液，开腠理，滋水之源而下降，利小便。故张洁古谓其属阳，浮而升，言其性也；东垣谓其为阳中之阴，降而下，言其功也。《素问》云︰饮食入胃，游溢精气，上输于肺，通调水道，下输膀胱。观此，则知淡渗之药，俱皆上行而后下降，非直下行也。小便多，其源亦异。《素问》云︰肺气盛则小便数而欠；虚则欠欬、小便遗数。心虚则少气遗溺。下焦虚则遗溺。胞移热于膀胱则遗溺。膀胱不利为癃，不约为遗溺。厥阴病则遗溺闭癃。所谓肺气盛者，实热也。其人必气壮脉强，宜用茯苓甘淡以渗其热，故曰︰小便多者能止也。若夫肺虚、心虚、胞热、厥阴病者，皆虚热也。其人必上热下寒，脉虚而弱。法当用升阳之药，以升水降火。膀胱不约、下焦虚者，乃火投于水，水泉不藏，脱阳之症。其人必肢冷脉迟。法当用温热之药，峻补其下，交济坎离。二症皆非茯苓辈淡渗之药所可治，故曰︰阴虚者不宜用也。仙家虽有服食之法，亦当因人而用焉。</t>
+        </is>
+      </c>
+      <c r="I30" s="38" t="inlineStr">
+        <is>
+          <t>木之四</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>zhi_ke</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>枳壳</t>
+        </is>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="inlineStr">
+        <is>
+          <t>苦|辛|酸</t>
+        </is>
+      </c>
+      <c r="E31" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G31" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H31" s="39" t="inlineStr">
+        <is>
+          <t>枳壳（枳）
+【气味】
+味苦、辛、酸，性微寒
+【毒性】
+无毒
+【归经】
+归脾、胃、大肠经
+【主治】
+行气消胀
+宽中除痞
+化痰消积
+【释名】
+子名枳实（《本经》）、枳壳（宋《开宝》）。
+宗奭曰：枳实、枳壳，一物也。小则其性酷而速，大则其性详而缓。故张仲景治伤寒仓猝之病，承气汤中用枳实，皆取其疏通、决泄、破结实之义。他方但导败风壅之气，可常服者，故用枳壳，其义如此。
+恭曰：既称枳实，须合核瓤，今殊不然。
+时珍曰：枳乃木名，从只，谐声也。实乃其子，故曰枳实。后人因小者性速，又呼老者为枳壳。生则皮厚而实，熟则壳薄而虚，正如青橘皮、陈橘皮之义。宋人复出枳壳一条，非矣。寇氏以为破结实而名，亦未必然。
+【发明】
+元素曰︰枳壳破气，胜湿化痰，泄肺走大肠，多用损胸中至高之气，只可二、三服而已。禀受素壮而气刺痛者，看在何杲曰︰气血弱者不可服，以其损气也。
+好古曰︰枳壳主高，枳实主下；高者主气，下者主血。故壳主胸膈皮毛之病，实主心腹脾胃之病，大同小异。朱肱《活人书》言︰治痞宜先用桔梗枳壳汤，非用此治心下痞也。果知能消分别。魏、晋以来，始分实、壳之用。
+皆能利气。气下则痰喘止，气行则痞胀消，气通则痛刺止，气利则后重除。故以枳壳利胸膈，枳实利肠胃。然张仲景治胸痹痞满，以枳实为要药；诸方治下血痔痢、大肠秘塞、里急后重，又以枳壳为通用。则枳实不独治下，而壳不独治高也。盖自飞门至魄门，皆肺主之，三焦相通，一气而已。则二物分之可也，不分亦无伤。杜壬方载湖阳公方。用枳壳四两，甘草二两，为末。每服一钱，白汤点服。自五月后一日一服，至临月，不惟易产，仍无胎中恶病也。张洁古《活法机要》改以枳术丸日服，令胎瘦易生，谓之束胎丸。
+而寇宗奭《衍义》言︰胎壮则子有力易生，令服枳壳药反致无力，兼胎易产者，大不然也。以理思之，寇氏之说似觉为优。或胎前气盛壅滞者宜用之，所谓八、九月胎必用枳壳、苏梗以顺气，胎前无滞，则产后无虚也。若气禀弱者，即大非所宜矣。
+震享曰︰难产多见于郁闷安逸之人，富贵奉养之家。古方瘦胎饮，为湖阳公主作也。予妹苦于难产，其形肥而好坐，予思此与公主正相反也。彼奉养之人，其气必实，故耗其气使平则易产。今形肥则气虚，久坐则气不运，当补其母之气。以紫苏饮加补气药，与十数贴服之，遂快产。</t>
+        </is>
+      </c>
+      <c r="I31" s="38" t="inlineStr">
+        <is>
+          <t>木之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>fang_feng</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>防风</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="inlineStr">
+        <is>
+          <t>辛|甘</t>
+        </is>
+      </c>
+      <c r="E32" s="39" t="inlineStr">
+        <is>
+          <t>肝|脾|肾</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G32" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H32" s="39" t="inlineStr">
+        <is>
+          <t>防风
+【气味】
+味辛、甘，性微温
+【毒性】
+无毒
+【归经】
+归膀胱、肝、脾经
+【主治】
+祛风解表
+胜湿止痛
+止痉
+【释名】
+铜芸（《本经》）、茴芸（《吴普》）、茴草（《别录》）、屏风（《别录》）、 根（《别录》）、百枝（《别录》）、百蜚（《吴普》）
+时珍曰：防者，御也。其功疗风最要，故名
+【发明】
+元素曰：防风，治风通用。身半以上风邪用身，身半以下风邪，用梢，治风去湿之仙药也，风能胜湿故尔。能泻肺实，误服泻人上焦元气。杲曰：防风治一身尽痛，乃猝 伍卑贱之职，随所引而至，乃风药中润剂也。若补脾胃，非此引用不能行。凡脊痛项强，不可回顾，腰似折，项似拔者，乃手足太阳证，正当用防风。凡疮在胸膈以上，虽无手足太阳 证，亦当用之，为能散结，去上部风。病患身体拘倦者，风也，诸疮见此证，亦须用之。钱 仲阳泻黄散中倍用防风者，乃于土中泻木也。</t>
+        </is>
+      </c>
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>qin_jiao</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>秦艽</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E33" s="39" t="inlineStr">
+        <is>
+          <t>肝|脾</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G33" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H33" s="39" t="inlineStr">
+        <is>
+          <t>秦艽
+【气味】
+味辛、苦，性平
+【毒性】
+无毒
+【归经】
+归胃、肝、胆经
+【主治】
+祛风湿
+清湿热
+止痹痛
+退虚热
+【释名】
+秦糺（《唐本》）、秦爪（萧炳）
+恭曰：秦艽，俗作秦胶，本名秦糺，与纠同。
+时珍曰：秦艽出秦中，以根作罗纹交纠者佳，故名秦艽、秦糺。
+【发明】
+时珍曰：秦艽，手足阳明经药也，兼入肝胆，故手足不遂、黄胆烦渴之病须之，取其去阳明之湿热也。阳明有湿，则身体酸疼烦热；有热，则日晡潮热骨蒸。所以《圣惠方》治急劳烦热，身体酸疼。用秦艽、柴胡各一两，甘草五钱。为末，每服三钱，白汤调下。治小儿骨蒸潮热，减食瘦弱。用秦艽、炙甘草各一两。每用一、二钱，水煎服之。钱乙加 薄荷叶五钱。</t>
+        </is>
+      </c>
+      <c r="I33" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>dang_gui</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>当归</t>
+        </is>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>甘|辛</t>
+        </is>
+      </c>
+      <c r="E34" s="39" t="inlineStr">
+        <is>
+          <t>心|肝|脾</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G34" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H34" s="39" t="inlineStr">
+        <is>
+          <t>当归
+【气味】
+味甘、辛，性温
+【毒性】
+无毒
+【归经】
+归肝、心、脾经
+【主治】
+补血活血
+调经止痛
+润肠通便
+【释名】
+干归（《本经》）、山蕲（《尔雅》）、白蕲（《尔雅》）、文无（《纲目》）
+颂曰︰按而粗大。许慎《说文》云︰生山中者，名薜，一名山蕲。然则当归，芹类也。在平地者名芹，生山中粗大者，名当归也。宗奭曰︰今川蜀皆以畦种，尤肥好多脂，不以平地、山中为等差也。
+时珍曰︰当归本非芹类，特以花叶似芹，故得芹名。古人娶妻为嗣续也，当归调血为女人要药，有思夫之意，故有当归之名，正与唐诗胡麻好种无人种，正是归时又不归之旨相同。崔豹《古今注》云，古人相赠以芍药，相招以文无。文无一名当归，芍药一名将离，故也。
+承曰︰当归治妊妇产后恶血上冲，仓猝取效。气血昏乱者，服之即定。能使气血各有所归，恐当归之名必因此出也。
+【发明】
+权曰︰患人虚冷者，加而用之。
+承曰︰世俗多谓惟能治血，而《金匮》、《外台》、《千金》诸方皆为大补不足、决取立效之药。古方用治妇人产后恶血上冲，取效无急于此。凡气血昏乱者，服之即定。可以补虚，备产后要药也。
+宗奭曰︰《药性论》补女子诸不足一说，尽当归之用矣。成无己曰︰脉者血之府，诸血皆属心。凡通脉者，必先补心益血。故张仲景治手足厥寒、脉细欲绝者，用当归之苦温以助心血。
+元素曰︰其用有三︰一，心经本药；二，和血；三，治诸病夜甚。凡血受病，必须用之。血壅而不流则痛，当归之甘温能和血，辛温能散内寒，苦温能助心散寒，使气血各有所归。
+好古曰︰入手少阴，以其心生血也。入足太阴，以其脾裹血也。入足厥阴，以其肝藏血也。头，能破血；身，能养血，尾能行血。全用，同人参、黄耆，则补气而生血；同牵牛、大治头痛，诸痛皆属木，故以血药主之。
+机曰︰治头痛，酒煮服清，取其浮而上也。治心痛，酒调末服，取其浊而半沉半浮也。治小便出血，用酒煎服，取其沉入下极也。自有高低之分如此。王海藏言当归血药，如何治胸中咳逆上气？按当归其味辛散，乃血中气药也。况咳逆上气，有阴虚阳无所附者，故用血药补阴，则血和而气降矣。
+韩𢘅曰︰当归主血分之病。川产力刚可攻，秦产力柔宜补。凡用，本病宜酒制，有痰以姜制，导血归源之理。血虚以人参、石脂为佐，血热以生地黄、条芩为佐，不绝生化之源。血积配以大黄。要之，血药不容舍当归。故古方四物汤以为君，芍药为臣，地黄为佐，芎为使也。</t>
+        </is>
+      </c>
+      <c r="I34" s="38" t="inlineStr">
+        <is>
+          <t>草之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>chuan_xiong</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>川芎</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="inlineStr">
+        <is>
+          <t>辛</t>
+        </is>
+      </c>
+      <c r="E35" s="39" t="inlineStr">
+        <is>
+          <t>肝</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G35" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H35" s="39" t="inlineStr">
+        <is>
+          <t>川芎（芎䓖）
+【气味】
+味辛，性温
+【毒性】
+无毒
+【归经】
+归肝、胆、心包经
+【主治】
+活血行气
+祛风止痛
+【释名】
+胡䓖（《别录》）、川芎（《纲目》）、香果（《别录》）、山鞠穷（《纲目》）
+时珍曰︰芎本作营，名义未详。或云︰人头穹窿穷高，天之象也。此药上行，专治头脑 诸疾，故有芎 之名。以胡戎者为佳，故曰胡芎。古人因其根节状如马衔，谓之马衔芎 。 后世因其状如雀脑，谓之雀脑芎。其出关中者，呼为京芎，亦曰西芎；出蜀中者，为川芎；出天台者，为台芎；出江南者，为抚芎，皆因地而名也。《左传》︰楚人谓萧人曰︰有麦曲乎？ 有山鞠穷乎？河鱼腹疾柰何？二物皆御湿，故以谕之。丹溪朱氏治六郁越鞠丸中用越桃、鞠 穷，故以命名。《金光明经》谓之 莫迦。
+【发明】
+宗奭曰︰今人用此最多，头面风不可缺也，然须以他药佐之。
+元素曰︰川芎上行头目，下行血海，故清神及四物汤皆用之。能散肝经之风，治少阳厥 阴经头痛，及血虚头痛之圣药也。其用有四︰为少阳引经，一也；诸经头痛，二也；助清阳 之气，三也；去湿气在头，四也。
+杲曰︰头痛必用川芎。如不愈，加各引经药︰太阳羌活，阳明白芷，少阳柴胡，太阴苍术，厥阴吴茱萸，少阴细辛，是也。
+震亨曰︰郁在中焦，须抚芎开提其气以升之，气升则郁自降。故抚芎总解诸郁，直达三焦，为通阴阳气血之使。
+时珍曰︰芎 ，血中气药也。肝苦急，以辛补之，故血虚者宜之。辛以散之，故气郁者宜之。《左传》言︰麦曲鞠穷御湿，治河鱼腹疾。予治湿泻每加二味，其应如响也。血痢已 通而痛不止者，乃阴亏气郁，药中加芎为佐，气行血调，其病立止。此皆医学妙旨，圆机之士，始可语之。
+宗奭曰︰沈括《笔谈》云︰一族子旧服芎 ，医郑叔熊见之云︰芎 不可久服，多令人暴死。后族子果无疾而卒。又朝士张子通之妻，病脑风，服芎 甚久，一旦暴亡。皆目见者。 此皆单服既久，则走散真气。若使他药佐使，又不久服，中病便已，则焉能至此哉？ 虞搏曰︰骨蒸多汗，及气弱之人，不可久服。其性辛散，令真气走泄，而阴愈虚也。
+时珍曰︰五味入胃，各归其本脏。久服则增气偏胜，必有偏绝，故有暴夭之患。若药具 五味，备四气，君臣佐使配合得宜，岂有此害哉？如芎 ，肝经药也。若单服既久，则辛喜 归肺，肺气偏胜，金来贼木，肝必受邪，久则偏绝，岂不夭亡？故医者贵在格物也。</t>
+        </is>
+      </c>
+      <c r="I35" s="38" t="inlineStr">
+        <is>
+          <t>草之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>wu_tou</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>乌头</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>热</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>心|肝|脾|肾</t>
+        </is>
+      </c>
+      <c r="F36" s="39" t="inlineStr">
+        <is>
+          <t>大毒</t>
+        </is>
+      </c>
+      <c r="G36" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H36" s="39" t="inlineStr">
+        <is>
+          <t>乌头
+【气味】
+味辛、苦，性热
+【毒性】
+大毒
+【归经】
+归心、肝、肾、脾经
+【主治】
+祛风除湿
+温经止痛
+【释名】
+乌喙（《本经》，即两头尖）、草乌头（《纲目》）、土附子（《日华》）、奚毒（《本经》）、耿子（《吴普》）、毒公（《吴普》。又名帝秋)、金鸦（《纲目》）、苗名茛（音艮）、芨（音及）、堇（音近）、独白草（《拾遗》）、鸳鸯菊（《纲目》）、汁煎名射罔
+普曰︰乌头，形如乌之头也。有两歧相合如乌之喙者，名曰乌喙。喙即乌之口也。
+恭曰︰乌喙，即乌头异名也。此有三歧者，然两歧者少。若乌头两歧名乌喙，则天雄、附子之两歧者，复何以名之？
+时珍曰︰此即乌头之野生于他处者，俗谓之草乌头，亦曰竹节乌头，出江北者曰淮乌头，《日华子》所谓土附子者是也。乌喙，即偶生两歧者，今俗呼为两头尖，因形而名，其实乃一物也。附子、天雄之偶生两歧者，亦谓之乌喙，功亦同于天雄，非此乌头也。苏恭不知此义，故反疑之。草乌头取汁，晒为毒药，射禽兽，故有射罔之称。《后魏书》言︰辽东塞外秋收乌头为毒药射禽兽，陈藏器所引《续汉五行志》，言西国生独白草，煎为药，敷箭射人即死者，皆此乌头，非川乌头也。
+《菊谱》云︰鸳鸯菊，即乌喙苗也。
+【发明】
+时珍曰︰草乌头、射罔，乃至毒之药。非若川乌头、附子，人所栽种，加以酿 制，杀其毒性之比。自非风顽急疾，不可轻投。甄权《药性论》言其益阳事，治男子肾气衰弱者，未可遽然也。此类止能搜风胜湿，开顽痰，治顽疮，以毒攻毒而已，岂有川乌头、附子补右肾命门之功哉？吾蕲郝知府自负知医，因病风癣，服草乌头、木鳖子药过多，甫入腹而麻痹，遂至不救，可不慎乎？ 机曰︰乌喙形如乌嘴，其气锋锐。宜其通经络，利关节，寻蹊达径，而直抵病所。煎为射罔，能杀禽兽。非气之锋锐捷利，能如是乎？ 杨清叟曰︰凡风寒湿痹，骨内冷痛，及损伤入骨，年久发痛，或一切阴疽肿毒。并宜草乌头、南星等分，少加肉桂为末，姜汁热酒调涂。未破者能内消，久溃者能去黑烂。二药性味辛烈，能破恶块，逐寒热，遇冷即消，遇热即溃。</t>
+        </is>
+      </c>
+      <c r="I36" s="38" t="inlineStr">
+        <is>
+          <t>草之六</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>huang_qi</t>
+        </is>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>黄芪</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D37" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E37" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G37" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H37" s="39" t="inlineStr">
+        <is>
+          <t>黄芪（黄耆）
+【气味】
+味甘，性微温
+【毒性】
+无毒
+【归经】
+归脾、肺经
+【主治】
+补气升阳
+固表止汗
+利水消肿
+生津养血
+行滞通痹
+托毒排脓
+敛疮生肌
+【释名】
+黄耆（《纲目》）、戴糁（《本经》）、戴椹（《别录》，又名独椹）、芰草（《别录》，又名蜀脂）、百本（《别录》）、王孙（《药性论》）。
+时珍曰︰耆，长也。黄耆色黄，为补药之长，故名。今俗通作黄芪。或作蓍者，非矣。蓍，乃蓍龟之蓍，音尸。王孙与牡蒙同名异物。
+【发明】
+弘景曰︰出陇西者，温补；出白水者，冷补。又有赤色者，可作膏，用消痈肿。
+藏器曰︰虚而客热，用白水黄耆；虚而客冷，用陇西黄耆。
+大明曰︰黄耆，药中补益，呼为羊肉；白水耆，凉，无毒，排脓治血，及烦闷热毒骨蒸劳；赤水耆，凉，无毒，治血退热毒，馀功并同；木耆，凉，无毒，治烦排脓之力，微于黄，遇阙即倍用之。
+元素曰︰黄耆甘温纯阳，其用有五︰补诸虚不足，一也；益元气，二也；壮脾胃，三也；去肌热，四也；排脓止痛，活血生血，内托阴疽，为疮家圣药，五也。又曰︰补五脏诸虚，治脉弦自汗，泻阴火，去虚热，无汗，则发之；有汗，则止之。
+好古曰︰黄耆，治气虚盗汗，并自汗及肤痛，是皮表之药；治咯血，柔脾胃，是中州之药；治伤寒尺脉不至，补肾脏元气，是里药。乃上、中、下、内、外、三焦之药也。
+杲曰︰《灵枢》云卫气者，所以温分肉而充皮肤，肥腠理而司开阖。黄耆既补三焦，实卫气，与桂同功；特比桂甘平，不辛热为异耳。但桂则通血脉，能破血而实卫气， 则益气也。又黄耆与人参、甘草三味，为除躁热肌热之圣药。脾胃一虚，肺气先绝，必用黄耆温分肉，益皮毛，实腠理，不令汗出，以益元气而补三焦。
+震亨曰︰黄耆补元气，肥白而多汗者，为宜；若面黑形实而瘦者，服之，令人胸满，宜以三拗汤泻之。
+宗奭曰︰防风、黄耆，世多相须而用。唐许胤宗初仕陈为新蔡王外兵参军时，柳太后病风不能言，脉沉而口噤。
+胤宗曰︰既不能下药，宜汤气蒸之，药入腠理，周时可瘥。乃造黄耆防风汤数斛，置于床下，气如烟雾，其夕便得语也。
+杲曰︰防风能制黄耆，黄耆得防风其功愈大，乃相畏而相使也。
+震亨曰︰人之口通乎地，鼻通乎天。口以养阴，鼻以养阳。天主清，故鼻不受有形而受无形；地主浊，故口受有形而兼乎无形。柳太后之病不言，若以有形之汤，缓不及事；今投以二物，汤气满室，则口鼻俱受。非智者通神，不可回生也。
+杲曰︰小儿外物惊，宜用黄连安神丸镇心药。若脾胃寒湿，呕吐腹痛，泻痢青白，宜用益黄散药。如脾胃伏火，劳役不足之证，及服巴豆之类，胃虚而成慢惊者，用益黄、理中之药，必伤人命。当于心经中，以甘温补土之源，更于脾土中，以甘寒泻火，以酸凉补金，使金旺火衰，风木自平矣。今立黄耆汤泻火补金益土，为神治之法。用炙黄耆二钱，人参一钱，炙甘草五分，白芍药五分，水一大盏，煎半盏，温服。
+机曰︰萧山魏直著《博爱心鉴》三卷，言小儿痘疮，惟有顺、逆、险三证。顺者为吉，不用药。逆者为凶，不必用药。惟险乃悔吝之象，当以药转危为安，宜用保元东加减主之。
+此方原出东垣，治慢惊土衰火旺之法。今借而治痘，以其内固营血，外护卫气，滋助阴阳，作为脓血，其证虽异，其理则同。去白芍药，加生姜，改名曰保元汤。炙黄耆三钱，人参二钱，炙甘草一钱，生姜一片，水煎服之。险证者，初出圆晕干红少润也，浆长光泽，顶陷不起也；既出虽起惨色不明也，浆行色灰不荣也，浆定光润不消也，浆老湿润不敛也，结痂而胃弱内虚也，痂落而口渴不食也，痂后生痈肿也，痈肿溃而敛迟也。凡有诸症，并宜此汤。或加芎 ，加官桂，加糯米以助之。详见本书。
+嘉谟曰︰人参补中，黄耆实表。凡内伤脾胃，发热恶寒，吐泄怠卧，胀满痞塞，神短脉微者，当以人参为君，黄耆为臣；若表虚自汗亡阳，溃疡痘疹阴疮者，当以黄耆为君，人参为臣，不可执一也。</t>
+        </is>
+      </c>
+      <c r="I37" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>feng_mi</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>蜂蜜</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G38" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H38" s="39" t="inlineStr">
+        <is>
+          <t>蜂蜜
+【气味】
+味甘，性平
+【毒性】
+无毒
+【归经】
+归肺、脾、大肠经
+【主治】
+补中润燥
+止痛解毒
+外用生肌敛疮
+【释名】
+蜂糖（俗名）生岩石者名石蜜（《本经》）、石饴（同上）、岩蜜。
+时珍曰︰蜜以密成，故谓之蜜。《本经》原作石蜜，盖以生岩石者为良耳，而诸家反致疑辩。今直题曰蜂蜜，正名也。
+【发明】
+弘景曰︰石蜜道家丸饵，莫不须之。仙方亦单炼服食，云致长生不老也。
+时珍曰︰蜂采无毒之花，酿以小便而成蜜，所谓臭腐生神奇也。其入药之功有五︰清热也，补中也，解毒也，润燥也，止痛也。生则性凉，故能清热；熟则性温，故能补中。甘而和平，故能解毒；柔而濡泽，故能润燥。缓可以去急，故能止心腹、肌肉、疮疡之痛；和可以致中，故能调和百药，而与甘草同功。张仲景治阳明结燥，大便不通，蜜煎导法，诚千古神方也。
+诜曰︰但凡觉有热，四肢不和，即服蜜浆一碗，甚良。又点目中热膜，以家养白蜜为上，木蜜次之，崖蜜更次之也。与姜汁熬炼，治癞甚效。</t>
+        </is>
+      </c>
+      <c r="I38" s="38" t="inlineStr">
+        <is>
+          <t>虫之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>yi_yi_ren</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>薏苡仁</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="inlineStr">
+        <is>
+          <t>凉</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="inlineStr">
+        <is>
+          <t>甘|淡</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G39" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H39" s="39" t="inlineStr">
+        <is>
+          <t>薏苡仁
+【气味】
+味甘、淡，性凉
+【毒性】
+无毒
+【归经】
+归脾、胃、肺经
+【主治】
+利水渗湿
+健脾止泻
+除痹排脓
+解毒散结
+【释名】
+解蠡（音礼。《本经》）、芑实（音起。《别录》）、赣米（《别录》。音感。陶氏作珠，雷氏作 米）、回回米（《救荒本草》）、薏珠子（《图经》）。
+时珍曰︰薏苡名义未详。其叶似蠡实叶而解散，又似芑黍之苗，故有解蠡、芑实之名。 赣米乃其坚硬者，有赣强之意。苗名屋 。《救荒本草》云︰回回米又呼西番蜀秫。俗名草珠儿。
+【发明】
+宗奭曰︰薏苡仁《本经》云︰微寒，主筋急拘挛。拘挛有两等︰《素问》注中，大筋受热，则缩而短，故挛急不伸，此是因热而拘挛也，故可用薏苡；若《素问》言因寒则筋急者，不可更用此也。 盖受寒使人筋急；寒热使人筋挛；若但受热不曾受寒，亦使人筋缓；受湿则又引长无力 也。此药力势和缓，凡用须加倍即见效。
+震亨曰︰寒则筋急，热则筋缩。急因于坚强，缩因于短促。若受湿则弛，弛则引长。然寒与湿未尝不挟热。三者皆因于湿，然外湿非内湿启之不能成病。故湿之为病，因酒而鱼肉继之。甘滑、陈久、烧炙并辛香，皆致湿之因也。
+时珍曰︰薏苡仁属土，阳明药也，故能健脾益胃。虚则补其母，故肺痿、肺痈用之。筋骨之病，以治阳明为本，故拘挛筋急风痹者用之。土能胜水除湿，故泄痢水肿用之。按︰古方小续命汤注云︰中风筋急拘挛，语迟脉弦者，加薏苡仁。亦扶脾抑肝之义。又《后汉书》云︰马援在交趾常饵薏苡实，云能轻身省欲以胜瘴气也。又张师正《倦游录》云︰辛稼轩忽患疝疾，重坠大如杯。一道人教以薏珠用东壁黄土炒过，水煮为膏服，数服即消。程沙随病此，稼轩授之亦效。《本草》薏苡乃上品养心药，故此有功。
+颂曰︰薏苡仁，心肺之药多用之。故范汪治肺痈，张仲景治风湿、胸痹，并有方法。《济生方》治肺损咯血，以熟猪肺切，蘸薏苡仁末，空心食之。薏苡补肺，猪肺引经也。赵君猷言屡用有效。</t>
+        </is>
+      </c>
+      <c r="I39" s="38" t="inlineStr">
+        <is>
+          <t>谷之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>qiang_huo</t>
+        </is>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>羌活</t>
+        </is>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D40" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E40" s="39" t="inlineStr">
+        <is>
+          <t>肾</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G40" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H40" s="39" t="inlineStr">
+        <is>
+          <t>羌活（独活羌活）
+【气味】
+味辛、苦，性温
+【毒性】
+无毒
+【归经】
+归膀胱、肾经
+【主治】
+解表散寒
+祛风除湿
+止痛
+【释名】
+羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草
+弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
+时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
+【发明】
+恭曰：疗风，宜用独活；兼水，宜用羌活。
+刘完素曰：独活不摇风而治风，浮萍不沉水而利水，因其所胜而为制也。张元素曰：风能胜湿，故羌活能治水湿。独活与细辛同用，治少阴头痛，头运目眩，非此不能除；羌活与川芎同用，治太阳、少阴头痛，透关利节，治督脉为病，脊强而厥。好古曰：羌活乃足太阳、厥阴、少阴药，与独活不分二种。后人因羌活气雄，独活气细。故雄者，治足太阳风湿相搏，头痛、肢节痛、一身尽痛者，非此不能除，乃却乱反正之主君药也。细者，治足少阴伏风，头痛、两足湿痹、不能动止者，非此不能治，而不治太阳之证。时珍曰：羌活、独活皆能逐 风胜湿，透关利节，但气有刚、劣不同尔。《素问》云：从下上者，引而去之。二味苦辛而温，味之薄者，阴中之阳，故能引气上升，通达周身，而散风胜湿。按文系曰：唐刘师贞之兄病风，梦神人曰：但取胡王使者浸酒服，便愈。师贞访问，皆不晓。复梦其母曰：胡王使 者，即羌活也。求而用之，兄疾遂愈。嘉谟曰：羌活，本手足太阳表里引经之药，又入足少阴、厥阴。名列君部之中，非比柔懦之主。小无不入，大无不通。故能散肌表八风之邪，利周身百节之痛。</t>
+        </is>
+      </c>
+      <c r="I40" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>du_huo</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>独活</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="inlineStr">
+        <is>
+          <t>肾</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G41" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H41" s="39" t="inlineStr">
+        <is>
+          <t>独活（独活羌活）
+【气味】
+味辛、苦，性温
+【毒性】
+无毒
+【归经】
+归膀胱、肾经
+【主治】
+解表散寒
+祛风除湿
+止痛
+【释名】
+羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草
+弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
+时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
+【发明】
+恭曰：疗风，宜用独活；兼水，宜用羌活。
+刘完素曰：独活不摇风而治风，浮萍不沉水而利水，因其所胜而为制也。张元素曰：风能胜湿，故羌活能治水湿。独活与细辛同用，治少阴头痛，头运目眩，非此不能除；羌活与川芎同用，治太阳、少阴头痛，透关利节，治督脉为病，脊强而厥。好古曰：羌活乃足太阳、厥阴、少阴药，与独活不分二种。后人因羌活气雄，独活气细。故雄者，治足太阳风湿相搏，头痛、肢节痛、一身尽痛者，非此不能除，乃却乱反正之主君药也。细者，治足少阴伏风，头痛、两足湿痹、不能动止者，非此不能治，而不治太阳之证。时珍曰：羌活、独活皆能逐 风胜湿，透关利节，但气有刚、劣不同尔。《素问》云：从下上者，引而去之。二味苦辛而温，味之薄者，阴中之阳，故能引气上升，通达周身，而散风胜湿。按文系曰：唐刘师贞之兄病风，梦神人曰：但取胡王使者浸酒服，便愈。师贞访问，皆不晓。复梦其母曰：胡王使 者，即羌活也。求而用之，兄疾遂愈。嘉谟曰：羌活，本手足太阳表里引经之药，又入足少阴、厥阴。名列君部之中，非比柔懦之主。小无不入，大无不通。故能散肌表八风之邪，利周身百节之痛。</t>
+        </is>
+      </c>
+      <c r="I41" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>shi_gao</t>
+        </is>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>石膏</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="inlineStr">
+        <is>
+          <t>甘|辛</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G42" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H42" s="39" t="inlineStr">
+        <is>
+          <t>石膏
+【气味】
+味甘、辛，性大寒
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+清热泻火
+除烦止渴
+【释名】
+细理石（《别录》）、寒水石（《纲目》）
+震享曰︰火 细研醋调，封丹灶，其固密甚于脂膏。此盖兼质与能而得名，正与石脂同意。
+时珍曰︰其纹理细密，故名细理石。其性大寒如水，故名寒水石，与凝水石同名异物。
+【发明】
+成无己曰︰风，阳邪也；寒，阴邪也。风喜伤阳，寒喜伤阴。营卫阴阳，为风寒所伤，则非轻剂所能独散，必须轻重之剂同散之，乃得阴阳之邪俱去，营卫之气俱和。是以大青龙汤，以石膏为使。石膏乃重剂，而又专达肌表也。又云︰热淫所胜，佐以苦甘。知母、石膏之苦甘以散热。
+元素曰︰石膏性寒，味辛而淡，气味俱薄，体重而沉，降也，阴也，乃阳明经大寒之药。善治本经头痛牙痛，止消渴中暑潮热。然能寒胃，令人不食，非腹有极热者，不宜轻用。又阳明经中热，发热恶寒燥热，日晡潮热，肌肉壮热，小便浊赤，大渴引饮，自汗，苦头痛之药，仲景用白虎汤是也。若无以上诸证，勿服之。多有血虚发热象白虎证，及脾胃虚劳，形体病证，初得之时，与此证同。医者不识而误用之，不可胜救也。
+杲曰︰石膏，足阳明药也。故仲景治伤寒阳明证，身热、目痛、鼻干、不得卧。身以前，胃之经也；胸前，肺之室也；邪在阳明，肺受火制，故用辛寒以清肺气，所以有白虎之名。又治三焦皮肤大热，入手少阳也。凡病脉数不退者，宜用之；胃弱者，不可用。
+宗奭曰︰孙兆言︰四月以后天气热时，宜用白虎。但四方气候不齐，岁中运气不一，亦宜两审。其说甚雅。
+时珍曰︰东垣李氏云︰立夏前多服白虎汤者，令人小便不禁，此乃降令太过也。阳明津液不能上输于肺，肺之清气亦复下降故尔。甄立言《古今录验方》︰治诸蒸病有五蒸汤，亦是白虎加人参、茯苓、地黄、葛根，因病加减。王焘《外台秘要》︰治骨蒸劳热久嗽，用石膏（纹如束针者）一斤，粉甘草一两。细研如面，日以水调三、四服。言其无毒有大益，乃养命上药，不可忽其贱而疑其寒。《名医录》言︰睦州杨士丞女，病骨蒸内热外寒，众医不瘥，处州吴医用此方而体遂凉。愚谓此皆少壮肺胃火盛，能食而病者言也。若衰暮及气虚、血虚、胃弱者，恐非所宜。
+广济林训导年五十，病痰嗽发热。或令单服石膏药至一斤许，遂不能食，而咳益频，病益甚，遂至不起。此盖用药者之瞀瞀也，石膏何与焉。杨士瀛云︰石膏 过，最能收疮晕，不至烂肌。按︰刘 《钱乙传》云︰宗室子病呕泄，医用温药加喘。乙曰︰病本中热，奈何以刚剂燥之，将不得前后溲，宜与石膏汤。宗室与医皆不信。后二日果来召。乙曰︰仍石膏汤证也。竟如言而愈。又按︰古方所用寒水石，是凝水石；唐宋以来诸方所用寒水石，即今之石膏也。故寒水石诸方多附于后。近人又以长石、方解石为寒水石，不可不辨之。</t>
+        </is>
+      </c>
+      <c r="I42" s="38" t="inlineStr">
+        <is>
+          <t>金石之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>zhi_mu</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>知母</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="inlineStr">
+        <is>
+          <t>苦|甘</t>
+        </is>
+      </c>
+      <c r="E43" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G43" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H43" s="39" t="inlineStr">
+        <is>
+          <t>知母
+【气味】
+味苦、甘，性寒
+【毒性】
+无毒
+【归经】
+归肺、胃、肾经
+【主治】
+清热泻火
+滋阴润燥
+【释名】
+母（《本经》音迟。《说文》作 ）、连母（《本经》）、 母（ 音匙，又音提，或作 ）、货母（《本经》）、地参（《本经》）、水参（又名水须、水浚）、 （《尔雅》，音覃）、 藩（音沉烦）、苦心（《别录》）、儿草（《别录》，又名儿踵草、女雷、女理、鹿列、韭逢、东根、野蓼、昌支）
+时珍曰︰宿根之旁，初生子根，状如 虻之状，故谓之 母，讹为知母、 母也。馀多未详。
+【发明】
+权曰︰知母治诸热劳，患人虚而口干者，加用之。
+杲曰︰知母入足阳明、手太阴。其用有四︰泻无根之肾火，疗有汗之骨蒸，止虚劳之热，滋化源之阴。仲景用此入白虎汤治不得眠者，烦躁也。烦出于肺，躁出于肾。君以石膏，佐以知母之苦寒，以清肾之源；缓以甘草、粳米，使不速下也。又凡病小便 塞而渴者，热在上焦气分，肺中伏热不能生水，膀胱绝其化源，宜用气薄、味薄、淡渗之药，以泻肺火、清肺金而滋水之化源。若热在下焦血分而不渴者，乃真水不足，膀胱干涸，乃无阴则阳无以化，法当用黄柏、知母大苦寒之药，以补肾与膀胱，使阴气行而阳自化，小便自通。方法详载木部黄柏下。
+时珍曰︰肾苦燥，宜食辛以润之。肺苦逆，宜食苦以泻之。知母之辛苦寒凉，下则润肾燥而滋阴，上则清肺金而泻火，乃二经气分药也。黄柏则是肾经血分药。故二药必相须而行，昔人譬之虾与水母，必相依附。补阴之说，详黄柏条。</t>
+        </is>
+      </c>
+      <c r="I43" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>jing_mi</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>粳米</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D44" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E44" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G44" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H44" s="39" t="inlineStr">
+        <is>
+          <t>粳米（粳）
+【气味】
+味甘，性平
+【毒性】
+无毒
+【归经】
+归脾、胃、肺经
+【主治】
+补中益气
+健脾和胃
+除烦渴
+止泻痢
+【释名】
+（与粳同）
+时珍曰︰粳乃谷稻之总名也，有早、中、晚三收。诸本草独以晚稻为粳者，非矣。粘者为糯，不粘者为粳。糯者懦也，粳者硬也。但入解热药，以晚粳为良尔。
+【发明】
+诜曰︰粳米赤者粒大而香，水渍之有味益人。大抵新熟者动气，经再年者亦发病。惟江南人多收火稻贮仓，烧去毛，至春舂米食之，即不发病宜人，温中益气，补下元也。
+宗奭曰︰粳以白晚米为第一，早熟米不及也。平和五脏，补益胃气，其功莫逮。然稍生则复不益脾，过熟乃佳。
+颖曰︰粳有早、中、晚三收，以晚白米为第一。各处所产，种类甚多，气味不能无少异，而亦不大相远也。天生五谷，所以养人，得之则生，不得则死。惟此谷得天地中和之气，同造化生育之功，故非他物可比。入药之功在所略尔。
+好古曰︰《本草》言粳米益脾胃，而张仲景白虎汤用之入肺。以味甘为阳明之经，色白为西方之象，而气寒入手太阴也。少阴证桃花汤，用之以补正气。竹叶石膏汤，用之以益不足。
+时珍曰︰粳稻六、七月收者为早粳（止可充食），八、九月收者为迟粳，十月收者为晚粳。北方气寒，粳性多凉，八、九月收者即可入药。南方气热，粳性多温，惟十月晚稻气凉乃可入药。迟粳、晚粳得金气多，故色白者入肺而解热也。早粳得土气多，故赤者益脾而白者益胃。若滇、岭之粳则性热，惟彼土宜之耳。</t>
+        </is>
+      </c>
+      <c r="I44" s="38" t="inlineStr">
+        <is>
+          <t>谷之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>dan_nan_xing</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>胆南星</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="inlineStr">
+        <is>
+          <t>凉</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="inlineStr">
+        <is>
+          <t>苦|辛</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="inlineStr">
         <is>
           <t>肝|肺</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="F45" s="39" t="inlineStr">
+        <is>
+          <t>有毒</t>
+        </is>
+      </c>
+      <c r="G45" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>dou_chi</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>豆豉</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>凉</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="H45" s="39" t="inlineStr">
+        <is>
+          <t>胆南星（虎掌）
+【气味】
+味苦、微辛，性凉
+【毒性】
+有毒
+【归经】
+归肺、肝、脾经
+【主治】
+清热化痰
+息风定惊
+【释名】
+虎膏（《纲目》）、鬼蒟蒻（《日华》）
+恭曰︰其根四畔有圆牙，看如虎掌，故有此名。
+颂曰︰天南星即本草虎掌也，小者名由跋。古方多用虎掌，不言天南星。南星近出唐人中风痰毒方中用之，乃后人采用，别立此名尔。
+时珍曰︰虎掌因叶形似之，非根也。南星因根圆白，形如老人星状，故名南星，即虎掌也。苏颂说甚明白。宋《开宝》不当重出南星条，今并入。
+【发明】
+时珍曰︰虎掌、天南星，乃手足太阴脾肺之药。味辛而麻，故能治风散血；气温而燥，故能胜湿除涎；性紧而毒，故能攻积拔肿而治口 舌糜。
+杨士瀛《直指方》云︰诸风口噤，宜用南星，更以人参、石菖蒲佐之。</t>
+        </is>
+      </c>
+      <c r="I45" s="38" t="inlineStr">
+        <is>
+          <t>草之六</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>gua_lou_ren</t>
+        </is>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>瓜蒌仁</t>
+        </is>
+      </c>
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D46" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E46" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G46" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H46" s="39" t="inlineStr">
+        <is>
+          <t>瓜蒌仁（栝蒌）
+【气味】
+味甘，性寒
+【毒性】
+无毒
+【归经】
+归肺、胃、大肠经
+【主治】
+润肺化痰
+滑肠通便
+【释名】
+果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
+根名白药（《图经》）、天花粉（《图经》）、瑞雪
+时珍曰︰裸，与蓏同。
+许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
+【发明】
+震亨曰︰栝蒌实治胸痹者，以其味甘性润。甘能补肺，润能降气。胸中有痰者，乃肺受火逼，失其降下之令。今得甘缓润下之助，则痰自降，宜其为治嗽之要药也。且又能洗涤胸膈中垢腻郁热，为治消渴之神药。
+时珍曰︰张仲景治胸痹痛引心背，咳唾喘息，及结胸满痛，皆用栝蒌实。乃取其甘寒不犯胃气，能降上焦之火，使痰气下降也。成无己不知此意，乃云苦寒以泻热。盖不尝其味原不苦，而随文傅会尔。</t>
+        </is>
+      </c>
+      <c r="I46" s="38" t="inlineStr">
+        <is>
+          <t>草之七</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>huang_qin</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>黄芩</t>
+        </is>
+      </c>
+      <c r="C47" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>苦</t>
+        </is>
+      </c>
+      <c r="E47" s="39" t="inlineStr">
+        <is>
+          <t>肝|脾|肺</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G47" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H47" s="39" t="inlineStr">
+        <is>
+          <t>黄芩
+【气味】
+味苦，性寒
+【毒性】
+无毒
+【归经】
+归肺、胆、脾、大肠、小肠经
+【主治】
+清热燥湿
+泻火解毒
+止血
+安胎
+【释名】
+腐肠（《本经》）、空肠（《别录》）、内虚（《别录》）、妒妇（《吴普》）、经芩 （《别录》）、黄文（《别录》）、印头（《吴普》）、苦督邮（《记事》），内实者名子芩（弘景）、条芩（《纲目》）、 尾芩（《唐本》）、鼠尾芩。
+弘景曰：圆者，名子芩；破者，名宿芩，其腹中皆烂，故名腐肠。
+时珍曰：芩，《说文》作 ，谓其色黄也。或云芩者，黔也，黔乃黄黑之色也。宿芩乃旧根，多中空，外黄内黑，即今所谓片芩，故又有腐肠、妒妇诸名。妒 妇心黯，故以比之。子芩乃新根，多内实，即今所谓条芩。或云西芩多中空而色黔，北芩多内实而深黄。
+【发明】
+杲曰：黄芩之中枯而飘者，泻肺火，利气，消痰，除风热，清肌表之热；细实而坚者，泻大肠火，养阴退阳，补膀胱寒水，滋其化源。高下之分与枳实、枳壳同例。
+元素曰：黄芩之用有九：泻肺热，一也；上焦皮肤风热风湿，二也；去诸热，三也；利胸中气，四也；消痰膈，五也；除脾经诸湿，六也；夏月须用，七也；妇人产后养阴退阳，八也；安胎，九也。酒炒上行，主上部积血，非此不能除。下痢脓血，腹痛后重，身热久不能止者，与芍药、甘草同用之。凡诸疮痛不可忍者，宜芩、连苦寒之药，详上下，分身、梢及引经药用之。
+震亨曰：黄芩降痰，假其降火也。凡去上焦湿热，须以酒洗过用。片芩泻肺火，须用桑白皮佐之。若肺虚者，多用则伤肺，必先以天门冬保定肺气而后用之。黄芩、白术乃安胎圣药，俗以黄芩为寒而不敢用，盖不知胎孕宜清热凉血，血不妄行，乃能养胎。黄芩乃上、中二焦药，能降火下行，白术能补脾也。
+罗天益曰：肺主气，热伤气，故身体麻木。又五臭入肺为腥，故黄芩之苦寒，能泻火、补气而利肺，治喉中腥臭。颂曰：张仲景治伤寒心下痞满，泻心汤。凡四方皆用黄芩，以其主诸热、利小肠故也。又太阳病下之利不止，喘而汗出者，有葛根黄芩黄连汤，及主妊娠安胎散，亦多用之。
+时珍曰：洁古张氏言：黄芩泻肺火，治脾湿；东垣李氏言：片芩治肺火，条芩治大肠火；丹溪朱氏言：黄芩治上中二焦火；而张仲景治少阳证小柴胡汤，太阳少阳合病下利黄芩汤，少阳证下后心下满而不痛泻心汤，并用之；成无己言黄芩苦而入心，泄痞热。是黄芩能入手少阴阳明、手足太阴少阳六经矣。盖黄芩气寒味苦，色黄带绿，苦入心，寒胜热，泻心火，治脾之湿热，一则金不受刑，一则胃火不流入肺，即所以救肺也。肺虚不宜者，苦寒伤脾胃，损其母也。少阳之证，寒热胸胁痞满，默默不欲饮食，心烦呕，或渴或痞，或小便不利。虽曰病在半表半里，而胸胁痞满，实兼心肺上焦之邪。心烦喜呕，默默不欲饮食，又兼脾胃中焦之证。故用黄芩以治手足少阳相火，黄芩亦少阳本经药也。成无己《注伤寒论》，但云柴胡、黄芩之苦，以发传邪之热；芍药、黄芩之苦，以坚敛肠胃之气，殊昧其治火之妙。杨士瀛《直指方》云：柴胡退热，不及黄芩。盖亦不知柴胡之退热，乃苦以发之，散火之标也；黄芩之退热，乃寒能胜热，折火之本也。仲景又云：少阳证腹中痛者，去黄芩，加芍药。心下悸，小便不利者，去黄芩，加茯苓。似与《别录》治少腹绞痛、利小肠之文不合。成氏言黄芩寒中，苦能坚肾，故去之，盖亦不然。至此当以意逆之，辨以脉证可也。若因饮寒受寒，腹中痛，及饮水心下悸，小便不利，而脉不数者，是里无热证，则黄芩不可用也。若热厥腹痛，肺热而小便不利者，黄芩其可不用乎？故善观书者，先求之理，毋徒泥其文。昔有人素多酒欲，病少腹绞痛不可忍，小便如淋，诸药不效。偶用黄芩、木通、甘草三味煎服，遂止。王海藏言有人因虚服附子药多，病小便秘，服芩、连药而愈。此皆热厥之痛也，学人其可拘乎？予年二十时，因感冒咳嗽既久，且犯戒，遂病骨蒸发热，肤如火燎，每日吐痰碗许，暑月烦渴，寝食几废，六脉浮洪。遍服柴胡、麦门冬、荆沥诸药，月馀益剧，皆以为必死矣。先君偶思李东垣治肺热如火燎，烦躁引饮而昼盛者，气分热也。宜一味黄芩汤，以泻肺经气分之火。遂按方用片芩一两，水二钟，煎一钟，顿服。次日身热尽退，而痰嗽皆愈。药中肯綮，如鼓应桴，医中之妙，有如此哉。</t>
+        </is>
+      </c>
+      <c r="I47" s="38" t="inlineStr">
+        <is>
+          <t>草之二</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>zhi_shi</t>
+        </is>
+      </c>
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>枳实</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D48" s="39" t="inlineStr">
+        <is>
+          <t>苦|辛|酸</t>
+        </is>
+      </c>
+      <c r="E48" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G48" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H48" s="39" t="inlineStr">
+        <is>
+          <t>枳实（枳）
+【气味】
+味苦、辛、酸，性微寒
+【毒性】
+无毒
+【归经】
+归脾、胃、大肠经
+【主治】
+破气消积
+化痰散痞
+【释名】
+子名枳实（《本经》）、枳壳（宋《开宝》）。
+宗奭曰：枳实、枳壳，一物也。小则其性酷而速，大则其性详而缓。故张仲景治伤寒仓猝之病，承气汤中用枳实，皆取其疏通、决泄、破结实之义。他方但导败风壅之气，可常服者，故用枳壳，其义如此。
+恭曰：既称枳实，须合核瓤，今殊不然。
+时珍曰：枳乃木名，从只，谐声也。实乃其子，故曰枳实。后人因小者性速，又呼老者为枳壳。生则皮厚而实，熟则壳薄而虚，正如青橘皮、陈橘皮之义。宋人复出枳壳一条，非矣。寇氏以为破结实而名，亦未必然。
+【发明】
+震亨曰：枳实泻痰，能冲墙倒壁，滑窍破气之药也。
+元素曰：心下痞及宿食不消，并宜枳实、黄连。
+杲曰：以蜜炙用，则破水积以泄气，除内热。洁古用去脾经积血。脾无积血，则心下不痞也。
+好古曰：益气则佐之以人参、白术、干姜，破气则佐之以大黄、牵牛、芒硝，此《本经》所以言益气而复言消痞也。非白术不能去湿，非枳实不能除痞。故洁古制枳术丸方，以调胃脾；张仲景治心下坚大如盘，水饮所作，枳实白术汤，用枳实七枚，术三两，水一斗，煎三升，分三服，腹中软，即消也。余见枳壳下。</t>
+        </is>
+      </c>
+      <c r="I48" s="38" t="inlineStr">
+        <is>
+          <t>木之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>ren_shen</t>
+        </is>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>人参</t>
+        </is>
+      </c>
+      <c r="C49" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D49" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E49" s="39" t="inlineStr">
+        <is>
+          <t>心|脾|肺</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G49" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H49" s="39" t="inlineStr">
+        <is>
+          <t>人参
+【气味】
+味甘、微苦，性微温
+【毒性】
+无毒
+【归经】
+归脾、肺、心经
+【主治】
+大补元气
+复脉固脱
+益气摄血
+生津安神
+【释名】
+人薓（音参。或省作参）、黄参（《吴普》）、血参（《别录》）、人衔（《本经》）、鬼盖（《本经》）、神草（《别录》）、土精（《别录》）、地精（《广雅》）、海腴、皱面还丹（《广雅》）。
+时珍曰︰人薓年深，浸渐长成者，根如人形，有神，故谓之人薓、神草。薓字，从𣹰，亦浸渐之义。𣹰，即浸字，后世因字文繁，遂以参星之字代之，从简便尔。然承误日久，亦不能变矣，惟张仲景《伤寒论》尚作薓字。《别录》一名人微，微乃薓字之讹也。其成有阶级，故曰人衔。其草背阳向阴，故曰鬼盖。其在五参，色黄属土，而补脾胃，生阴血，故有黄参、血参之名。得地之精灵，故有土精、地精之名。
+《广五行记》云︰隋文帝时，上党有人宅后每夜闻人呼声，求之不得。去宅一里许，见人参枝叶异常，掘之入地五尺，得人参，一如人体，四肢毕备，呼声遂绝。观此，则土精之名，尤可证也。《礼斗威仪》云︰下有人参，上有紫气。
+《春秋运斗枢》云︰摇光星散而为人参。人君废山渎之利，则摇光不明，人参不生。观此，则神草之名，又可证矣。
+【发明】
+弘景曰︰人参为药切要，与甘草同功。
+杲曰︰人参甘温，能补肺中元气，肺气旺则四脏之气皆旺，精自生而形自盛，肺主诸气故也。张仲景云︰病患汗后身热、亡血、脉沉迟者，下痢身凉、脉微、血虚者，并加人参。
+古人血脱者益气，盖血不自生，须得生阳气之药乃生，阳生则阴长，血乃旺也。若单用补血药，血无由而生矣。《素问》言︰无阳则阴无以生，无阴则阳无以化。故补气须用人参，血虚者亦须用之。本草十剂云︰补可去弱，人参、羊肉之属是也。盖人参补气，羊肉补形，形气者，有无之象也。
+好古曰︰洁古老人言︰以沙参代人参，取其味甘也。然人参补五脏之阳，沙参补五脏之阴，安得无异？虽云补五脏，亦须各用本脏药相佐使引之。
+言闻曰︰人参生用气凉，熟用气温；味甘补阳，微苦补阴。气主生物，本呼天；味主成物，本呼地。气味生成，阴阳之造化也。凉者，高秋清肃之气，天之阴也，其性降；温者，阳春生发之气，天之阳也，其性升。甘者，湿土化成之味，地之阳也，其性浮；微苦者，火土相生之味，地之阴也，其性沉。人参气味俱薄。气之薄者，生降熟升；味之薄者，生升熟降。如土虚火旺之病，则宜生参，凉薄之气，以泻火而补土，是纯用其气也；脾虚肺怯之病，则宜熟参，甘温之味，以补土而生金，是纯用其味也。东垣以相火乘脾，身热而烦，气高而喘，头痛而渴，脉洪而大者，用黄柏佐人参。孙真人治夏月热伤元气，人汗大泄，欲成痿厥，用生脉散，以泻热火而救金水。君以人参之甘寒，泻火而补元气；臣以麦门冬之苦甘寒，清金而滋水源，佐以五味子之酸温，生肾精而收耗气。此皆补天元之真气，非补热火也。白飞霞云︰人参炼膏服，回元气于无何有之乡。凡病后气虚及肺虚嗽者，并宜之。若气虚有火者，合天门冬膏对服之。</t>
+        </is>
+      </c>
+      <c r="I49" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>shu_di_huang</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>熟地黄</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D50" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E50" s="39" t="inlineStr">
+        <is>
+          <t>肝|肾</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G50" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H50" s="39" t="inlineStr">
+        <is>
+          <t>熟地黄（地黄）
+【气味】
+味甘，性微温
+【毒性】
+无毒
+【归经】
+归肝、肾经
+【主治】
+补血滋阴
+益精填髓
+【释名】
+ 芐（音户）、芑（音起）、地髓（本经）
+大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
+时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
+【发明】
+元素曰︰地黄生则大寒而凉血，血热者须用之；熟则微温而补肾，血衰者须用之。又脐下痛属肾经，非熟地黄不能除，乃通肾之药也。
+好古曰︰生地黄治心热、手足心热，入手足少阴厥阴，能益肾水，凉心血，其脉洪实者宜之。若脉虚者，则宜熟地黄，假火力蒸九数，故能补肾中元气。仲景八味丸以之为诸药之首，天一所生之源也。汤液四物汤治藏血之脏，以之为君者，癸乙同归一治也。
+时珍曰︰按王硕《易简方》云︰男子多阴虚，宜用熟地黄；女子多血热，宜用生地黄。
+又云︰生地黄能生精血，天门冬引入所生之处；熟地黄能补精血，用麦门冬引入所补之处。
+虞搏《医学正传》云︰生地黄生血，而胃气弱者服之，恐妨食；熟地黄补血，而痰饮多者服之，恐泥膈。或云︰生地黄酒炒则不妨胃，熟地黄姜汁炒则不泥膈。此皆得用地黄之精微者也。
+颂曰︰崔元亮《海上方》︰治一切心痛，无问新久。以生地黄一味，随人所食多少，捣绞取汁，搜面作患此病二年，深以为恨，临终戒其家人，吾死后当剖去病本。从其言果得虫，置于竹节中，每所食皆饲之。因食地黄 亦与之，随即坏烂。由此得方。刘禹锡《传信方》亦纪其事云︰贞元十年，通事舍人崔抗女，患心痛垂绝，遂作地黄冷淘食，便吐一物，可方寸匕，状如蛤蟆，无足目，似有口，遂愈。冷淘勿著</t>
+        </is>
+      </c>
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>草之五</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>wu_wei_zi</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>五味子</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>酸|甘</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="inlineStr">
+        <is>
+          <t>心|肺|肾</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G51" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H51" s="39" t="inlineStr">
+        <is>
+          <t>五味子
+【气味】
+味酸、甘，性温
+【毒性】
+无毒
+【归经】
+归肺、心、肾经
+【主治】
+收敛固涩
+益气生津
+补肾宁心
+【释名】
+荎藸 （《尔雅》，音知除）
+恭曰︰五味，皮、肉甘、酸，核中辛、苦，都有咸味，此则五味具也。《本经》但云味酸，当以木为五行之先也。
+【发明】
+成无己曰︰肺欲收，急食酸以收之，以酸补之。芍药、五味之酸，以收逆气而安肺。
+杲曰︰收肺气，补气不足，升也。酸以收逆气，肺寒气逆，则宜此与干姜同治之。又五味子收肺气，乃火热必用之药，故治嗽以之为君。但有外邪者不可骤用，恐闭其邪气，必先发散而后用之乃良。有痰者，以半夏为佐；喘者，阿胶为佐，但分两少不同耳。
+宗奭曰︰今华州以西至秦州多产之。方红熟时，彼人采得，蒸烂，研滤汁，熬成稀膏，量酸甘入蜜炼匀，待冷收器中。肺虚寒人，作汤时时饮之。作果可以寄远。《本经》言其性温，今食之多致虚热，小儿益甚。《药性论》谓其除热气，《日华子》谓其暖水脏、除烦热，后学至此多惑。今既用治肺虚寒，则更不取其除热之说。
+震亨曰︰五味大能收肺气，宜其有补肾之功。收肺气，非除热乎？补肾，非暖水脏乎？乃火热嗽必用之药。寇氏所谓食之多致虚热者，盖收补之骤也，何惑之有？又黄昏嗽乃火气浮入肺中，不宜用凉药，宜五味子、五倍子敛而降之。
+思邈曰︰五、六月宜常服五味子汤，以益肺金之气，在上则滋源，在下则补肾。其法︰以五味子一大合，木臼捣细，瓷瓶中，以百沸汤投之，入少蜜，封置火边良久，汤成任饮。
+元素曰︰孙真人《千金月令》言︰五月常服五味，以补五脏之气。遇夏月季夏之间，困乏无力，无气以动。与黄 、人参、麦门冬，少加黄柏，煎汤服之。使人精神顿加，两足筋力涌出也。盖五味子之酸，辅人参，能泻丙火而补庚金，收敛耗散之气。
+好古曰︰张仲景八味丸，用此补肾，亦兼述类象形也。
+机曰︰五味治喘嗽，须分南北。生津止渴，润肺补肾，劳嗽，宜用北者；风寒在肺，宜用南者。
+慎微曰︰《抱朴子》云︰五味者，五行之精，其子有五味。淮南公羡门子服之十六年，面色如玉女，入水不沾，入火不灼。</t>
+        </is>
+      </c>
+      <c r="I51" s="38" t="inlineStr">
+        <is>
+          <t>草之七</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>zi_wan</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
+        <is>
+          <t>紫菀</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>肺</t>
+        </is>
+      </c>
+      <c r="F52" s="45" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G52" s="43" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H52" s="43" t="inlineStr">
+        <is>
+          <t>紫菀
+【气味】
+味辛、苦，性温
+【毒性】
+无毒
+【归经】
+归肺经
+【主治】
+润肺下气
+化痰止咳
+【释名】
+青菀（《别录》）、紫蒨（《别录》）、返魂草（《纲目》）、夜牵牛
+时珍曰︰其根色紫而柔宛，故名许慎《说文》作茈菀。《斗门方》谓之返魂草。
+【发明】</t>
+        </is>
+      </c>
+      <c r="I52" s="38" t="inlineStr">
+        <is>
+          <t>草之五</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>sang_bai_pi</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>桑白皮</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D53" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E53" s="39" t="inlineStr">
+        <is>
+          <t>肺</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G53" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H53" s="39" t="inlineStr">
+        <is>
+          <t>桑白皮（桑）
+【气味】
+味甘，性寒
+【毒性】
+无毒
+【归经】
+归肺经
+【主治】
+泻肺平喘
+利水消肿
+【释名】
+子名椹。
+时珍曰︰徐锴《说文解字》云︰桑，音若，东方自然神木之名，其字象形。桑乃蚕所食，异于东方自然之神木，故加木于桑下而别之。《典术》云︰桑乃箕星之精。
+【发明】
+杲曰︰桑白皮，甘以固元气之不足而补虚，辛以泻肺气之有馀而止嗽。又云︰桑白皮泻肺，然性不纯良，不宜多用。
+时珍曰︰桑白皮长于利小水，乃实则泻其子也，故肺中有水气及肺火有馀者宜之。十剂云︰燥可去湿，桑白皮、赤小豆之属是矣。宋医钱乙治肺气热盛，咳嗽而后喘，面肿身热，泻白散︰用桑白皮（炒）一两，地骨皮（焙）一两，甘草（炒）半两。每服一、二钱，入粳米百粒，水煎，食后温服。桑白皮、地骨皮皆能泻火从小便去，甘草泻火而缓中，粳米清肺而养血，此乃泻肺诸方之准绳也。元医罗天益言其泻肺中伏火而补正气，泻邪所以补正也。若肺虚而小便利者，不宜用之。
+颂曰︰桑白皮作线缝金疮肠出，更以热鸡血涂之。唐‧安金藏剖腹，用此法而愈。</t>
+        </is>
+      </c>
+      <c r="I53" s="38" t="inlineStr">
+        <is>
+          <t>木之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>mai_men_dong</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>麦门冬</t>
+        </is>
+      </c>
+      <c r="C54" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D54" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E54" s="39" t="inlineStr">
+        <is>
+          <t>心|脾|肺</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G54" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H54" s="39" t="inlineStr">
+        <is>
+          <t>麦门冬
+【气味】
+味甘、微苦，性微寒
+【毒性】
+无毒
+【归经】
+归心、肺、胃经
+【主治】
+养阴生津
+润肺清心
+【释名】
+冬（音门），韭（《吴普》）阶前草
+时珍曰︰麦须曰 ，此草根似麦而有须，其叶如韭，凌冬不凋，故谓之麦 冬，及有诸韭、忍冬诸名。俗作门冬，便于字也。可以服食断谷，一名仆垒，一名随脂。
+【发明】
+宗奭曰︰麦门冬治肺热之功为多，其味苦，但专泄而不专收，寒多人禁服。治心肺虚热及虚劳。与地黄、阿胶、麻仁，同为润经益血、复脉通心之剂；与五味子、枸杞子，同为生脉之剂。
+元素曰︰麦门冬治肺中伏火、脉气欲绝者，加五味子、人参二味为生脉散，补肺中元气不足。
+杲曰︰六七月间湿热方旺，人病骨乏无力，身重气短，头旋眼黑，甚则痿软。故孙真人以生脉散补其天元真气。脉者，人之元气也。人参之甘寒，泻热火而益元气。麦门冬之苦寒，滋燥金而清水源。五味子之酸温，泻丙火而补庚金，兼益五脏之气也。
+时珍曰︰按︰赵继宗《儒医精要》云︰麦门冬以地黄为使，服之令人头不白，补髓，通肾气，定喘促，令人肌体滑泽，除身上一切恶气不洁之疾，盖有君而有使也。若有君无使，是独行无功矣。此方惟火盛气壮之人服之相宜。若气弱胃寒者，必不可饵也。</t>
+        </is>
+      </c>
+      <c r="I54" s="38" t="inlineStr">
+        <is>
+          <t>草之五</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>yu_zhu</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>玉竹</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D55" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E55" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G55" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H55" s="39" t="inlineStr">
+        <is>
+          <t>玉竹（萎蕤）
+【气味】
+味甘，性微寒
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+养阴润燥
+生津止渴
+【释名】
+女萎（《本经》）、葳蕤（《吴普》）、萎 （音威移）、委萎（《尔雅》）、萎香（《纲目》）、荧（《尔雅》，音行）、玉竹（《别录》）、地节（《别录》）。
+时珍曰︰按︰黄公绍《古今韵会》云︰葳蕤，草木叶垂之貌。此草根长多须，如冠缨下垂之 而有威仪，故以名之。凡羽盖旌旗之缨 ，皆象葳蕤，是矣。张氏《瑞应图》云︰王者礼备，则葳蕤生于殿前。一名萎香。则威仪之义，于此可见。《别录》作葳蕤，省文也。《说文》作萎 ，音相近也。《尔雅》作委萎，字相近也。其叶光莹而象竹，其根多节，故有荧及玉竹、地节诸名。《吴普本草》又有乌女、虫蝉之名。宋本一名马熏，即乌萎之讹者也。
+【发明】
+杲曰︰葳蕤能升能降，阳中阴也。其用有四︰主风淫四末，两目泪烂，男子湿注腰痛，女子面生黑 。
+时珍曰︰葳蕤性平味甘，柔润可食。故朱肱《南阳活人书》，治风温自汗身重，语言难出，用葳蕤汤，以之为君药。予每用治虚劳寒热 疟，及一切不足之证，用代参、 ，不寒不燥，大有殊功，不只于去风热湿毒而已，此昔人所未阐者也。
+藏器曰︰陈寿《魏志‧樊阿传》云︰青粘，一名黄芝，一名地节。此即葳蕤，极似偏精。
+本功外，主聪明，调血气，令人强壮。和漆叶为散服，主五脏益精，去三虫，轻身不老，变白，润肌肤，暖腰脚惟有热不可服。晋嵇绍有胸中寒疾，每酒后苦唾，服之得愈。草似竹，取根花叶阴干用。昔华佗入山见仙人所服，以告樊阿，服之寿百岁也。颂曰︰陈藏器以青粘即葳蕤。世无识者，未敢以为信然。
+时珍曰︰苏颂注黄精，疑青粘是黄精，与此说不同。今考黄精、葳蕤性味功用大抵相近，而葳蕤之功更胜。故青粘，一名黄芝，与黄精同名；一名地节，与葳蕤同名，则二物虽通用亦可。</t>
+        </is>
+      </c>
+      <c r="I55" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>tian_hua_fen</t>
+        </is>
+      </c>
+      <c r="B56" s="39" t="inlineStr">
+        <is>
+          <t>天花粉</t>
+        </is>
+      </c>
+      <c r="C56" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D56" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E56" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F56" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G56" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H56" s="39" t="inlineStr">
+        <is>
+          <t>天花粉（栝蒌）
+【气味】
+味甘、微苦，性微寒
+【毒性】
+无毒
+【归经】
+归肺、胃经
+【主治】
+清热泻火
+生津止渴
+消肿排脓
+【释名】
+果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
+根名白药（《图经》）、天花粉（《图经》）、瑞雪
+时珍曰︰裸，与蓏同。
+许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
+【发明】
+恭曰︰用根作粉，洁白美好，食之大宜虚热人。
+杲曰︰栝蒌根纯阴，解烦渴，行津液。心中枯涸者，非此不能除。与辛酸同用，导肿气成无己曰︰津液不足则为渴。栝蒌根味苦微寒，润枯燥而通行津液，是为渴所宜也。
+时珍曰︰栝蒌根味甘微苦酸。其茎叶味酸。酸能生津，感召之理，故能止渴润枯。微苦降火，甘不伤胃。昔人只言其苦寒，似未深察。</t>
+        </is>
+      </c>
+      <c r="I56" s="38" t="inlineStr">
+        <is>
+          <t>草之七</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>bian_dou</t>
+        </is>
+      </c>
+      <c r="B57" s="39" t="inlineStr">
+        <is>
+          <t>扁豆</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D57" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E57" s="39" t="inlineStr">
+        <is>
+          <t>脾</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G57" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H57" s="39" t="inlineStr">
+        <is>
+          <t>扁豆（藊豆）
+【气味】
+味甘，性微温
+【毒性】
+无毒
+【归经】
+归脾、胃经
+【主治】
+健脾化湿
+和中消暑
+【释名】
+沿篱豆（俗）、蛾眉豆
+时珍曰︰ ，本作扁，荚形扁也。沿篱，蔓延也。蛾眉，象豆脊白路之形也。
+【发明】
+时珍曰︰硬壳白扁豆，其子充实，白而微黄，其气腥香，其性温平，得乎中和，脾之谷也。入太阴气分，通利三焦，能化清降浊，故专治中宫之病，消暑除湿而解毒也。其软壳及黑鹊色者，其性微凉，但可供食，亦调脾胃。</t>
+        </is>
+      </c>
+      <c r="I57" s="38" t="inlineStr">
+        <is>
+          <t>谷之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>sheng_di_huang</t>
+        </is>
+      </c>
+      <c r="B58" s="39" t="inlineStr">
+        <is>
+          <t>生地黄</t>
+        </is>
+      </c>
+      <c r="C58" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D58" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E58" s="39" t="inlineStr">
+        <is>
+          <t>心|肝|肾</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G58" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H58" s="39" t="inlineStr">
+        <is>
+          <t>生地黄（地黄）
+【气味】
+味甘、苦，性寒
+【毒性】
+无毒
+【归经】
+归心、肝、肾经
+【主治】
+清热凉血
+养阴生津
+【释名】
+芐（音户）、芑（音起）、地髓（本经）
+大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
+时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
+【发明】
+好古曰︰生地黄入手少阴，又为手太阳之剂，故钱仲阳泻丙火与木通同用以导赤也。诸经之血热，与他药相随，亦能治之。溺血、便血皆同。
+权曰︰病患虚而多热者，宜加用之。
+戴原礼曰︰阴微阳盛，相火炽强，来乘阴位，日渐煎熬，为虚火之证者，宜地黄之属，以滋阴退阳。
+宗奭曰︰《本经》只言干、生二种，不言熟者。如血虚劳热，产后虚热，老人中虚燥热者，若与生干，当虑太寒，故后世改用蒸曝熟者。生熟之功殊别，不可不详。
+时珍曰︰《本经》所谓干地黄者，乃阴干、日干、火干者，故又云生者尤良。《别录》复云生地黄者，乃新掘鲜者，故其性大寒。其熟地黄乃后人复蒸晒者。诸家本草皆指干地黄为熟地黄，虽主治证同，而凉血、补血之功稍异，故今别出熟地黄一条于下。</t>
+        </is>
+      </c>
+      <c r="I58" s="38" t="inlineStr">
+        <is>
+          <t>草之五</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>tian_men_dong</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>天门冬</t>
+        </is>
+      </c>
+      <c r="C59" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D59" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦</t>
+        </is>
+      </c>
+      <c r="E59" s="39" t="inlineStr">
+        <is>
+          <t>肺|肾</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G59" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H59" s="39" t="inlineStr">
+        <is>
+          <t>天门冬
+【气味】
+味甘、苦，性寒
+【毒性】
+无毒
+【归经】
+归肺、肾经
+【主治】
+养阴润燥
+清肺生津
+【释名】
+冬（音门）、颠勒
+禹锡曰︰按︰《尔雅》云︰蔷蘼， 冬。注云︰门冬也，一名满冬。《抱朴子》云︰一名颠棘，或名地门冬，或名筵门冬。在东岳名淫羊藿；在中岳名天门冬；在西岳名管松；在北岳，名无不愈；在南岳名百部；在京陆山阜名颠棘；在越人，名浣草。虽处处有之，其名不同，其实一也。别有百部草，其根有百许如一，而苗小异，其苗似菝 ，惟可治咳，不中服食，须分别之。
+时珍曰︰草之茂者为 ，俗作门。此草蔓茂，而功同麦门冬，故曰天门冬，或曰天棘。
+《尔雅》云︰髦，颠棘也。因其细叶如髦，有细棘也。颠、天，音相近也。按︰《救荒本草》云︰俗名万岁藤，又名娑萝树。其形与治肺之功颇同百部，故亦名百部也。蔷蘼乃营实苗，而《尔雅》指为 冬，盖古书错
+【发明】
+权曰︰天门冬冷而能补，患人体虚而热者，宜加用之。和地黄为使，服之耐老头不白。
+宗奭曰︰治肺热之功为多。其味苦，专泄而不专收，寒多人禁服之。
+元素曰︰苦以泄滞血，甘以助元气，及治血妄行，此天门冬之功也。保定肺气，治血热侵肺，上气喘促，宜加人参、黄耆为主，用之神效。
+嘉谟曰︰天、麦门冬并入手太阴，祛烦解渴，止咳消痰。而麦门冬兼行手少阴，清心降火，使肺不犯邪，故止咳立效。天门冬复走足少阴，滋肾助元，全其母气，故消痰殊功。盖肾主津液，燥则凝而为痰，得润剂则化，所谓治痰之本也。
+好古曰︰入手太阴、足少阴经。营卫枯涸，宜以湿剂润之。二门冬、人参、五味、枸杞子同为生脉之剂，此上焦独取寸口之意。
+赵继宗曰︰五药虽为生脉之剂，然生地黄、贝母为天门冬之使；地黄、车前，为麦门冬之使；茯苓，为人参之使。若有君无使，是独行无功也。故张三丰与胡KT 尚书长生不方，用天门冬三斤，地黄一斤， 乃有君而有使也。
+禹锡曰︰《抱朴子》言︰入山便可以天门冬蒸煮，啖之，取足以断谷。若有力可饵之，或作散、酒服，或捣汁作液、膏服。至百日丁壮兼倍，快于术及黄精也。二百日强筋髓，驻颜色。与炼成松脂同蜜丸服，尤善。杜紫微服之，御八十外家，一百四十岁，日行三百里。
+慎微曰︰《列仙传》云︰赤须子食天门冬，齿落更生，细发复出。太原甘始服天门冬，在人间三百馀年。《圣化经》云︰以天门冬、茯苓等分，为末，日服方寸匕。则不畏寒，大寒时单衣汗出也。
+时珍曰︰天门冬清金降火，益水之上源，故能下通肾气，入滋补方，合群药用之有效。若脾胃虚寒人，单饵既久，必病肠滑，反成痼疾。此物性寒而润，能利大肠故也。</t>
+        </is>
+      </c>
+      <c r="I59" s="38" t="inlineStr">
+        <is>
+          <t>草之七</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>xuan_shen</t>
+        </is>
+      </c>
+      <c r="B60" s="39" t="inlineStr">
+        <is>
+          <t>玄参</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D60" s="39" t="inlineStr">
+        <is>
+          <t>甘|苦|咸</t>
+        </is>
+      </c>
+      <c r="E60" s="39" t="inlineStr">
+        <is>
+          <t>脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G60" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H60" s="39" t="inlineStr">
+        <is>
+          <t>玄参
+【气味】
+味甘、苦、咸，性微寒
+【毒性】
+无毒
+【归经】
+归肺、胃、肾经
+【主治】
+清热凉血
+滋阴降火
+解毒散结
+【释名】
+黑参（《纲目》）、玄台（《吴普》）、重台（《本经》）、鹿肠（《吴普》）、正马（《别录》）、逐马（《药性》）、馥草（《开宝》）、野脂麻（《纲目》）、鬼藏（《吴普》）。时珍曰︰玄，黑色也。《别录》一名端，一名咸，多未详。
+弘景曰︰其茎微似人参，故得参名。志曰︰合香家用之，故俗呼馥草。
+【发明】
+元素曰︰玄参乃枢机之剂，管领诸气上下，清肃而不浊，风药中多用之。故《活人书》治伤寒阳毒，汗下后毒不散，及心下懊 ，烦不得眠，心神颠倒欲绝者，俱用玄参。以此论之，治胸中氤氲之气，无根之火，当以玄参为圣剂也。
+时珍曰︰肾水受伤，真阴失守，孤阳无根，发为火病。法宜壮水以制火，故玄参与地黄同功。其消瘰 亦是散火，刘守真言︰结核是火病。</t>
+        </is>
+      </c>
+      <c r="I60" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>dan_shen</t>
+        </is>
+      </c>
+      <c r="B61" s="39" t="inlineStr">
+        <is>
+          <t>丹参</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D61" s="39" t="inlineStr">
+        <is>
+          <t>苦</t>
+        </is>
+      </c>
+      <c r="E61" s="39" t="inlineStr">
+        <is>
+          <t>心|肝</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G61" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H61" s="39" t="inlineStr">
+        <is>
+          <t>丹参
+【气味】
+味苦，性微寒
+【毒性】
+无毒
+【归经】
+归心、肝经
+【主治】
+活血祛瘀
+通经止痛
+清心除烦
+凉血消痈
+【释名】
+赤参（《别录》）、山参（《日华》）、 蝉草（《本经》）、木羊乳（《吴普》）、逐马（弘景）、奔马草。
+时珍曰︰五参五色配五脏。故人参入脾，曰黄参；沙参入肺，曰白参；玄参入肾，曰黑参；牡蒙入肝，曰紫参；丹参入心，曰赤参。其苦参，则右肾命门之药也。古人舍紫参而称苦参，未达此义尔。炳曰︰丹参治风软脚，可逐奔马，故名奔马草。曾用，实有效。
+【发明】
+时珍曰︰丹参色赤味苦，气平而降，阴中之阳也。入手少阴、厥阴之经，心与包络血分药也。按︰《妇人明理论》云︰四物汤治妇人病，不问产前、产后，经水多少，皆可通用。惟一味丹参散，主治与之相同。盖丹参能破宿血，补新血，安生胎，落死胎，止崩中带下，调经脉，其功大类当归、地黄、芎 、芍药故也。</t>
+        </is>
+      </c>
+      <c r="I61" s="38" t="inlineStr">
+        <is>
+          <t>草之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>fu_shen</t>
+        </is>
+      </c>
+      <c r="B62" s="39" t="inlineStr">
+        <is>
+          <t>茯神</t>
+        </is>
+      </c>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D62" s="39" t="inlineStr">
+        <is>
+          <t>甘|淡</t>
+        </is>
+      </c>
+      <c r="E62" s="39" t="inlineStr">
+        <is>
+          <t>心|脾</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G62" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H62" s="39" t="inlineStr">
+        <is>
+          <t>茯神（茯苓）
+【气味】
+味甘、淡，性平
+【毒性】
+无毒
+【归经】
+归心、脾经
+【主治】
+宁心安神
+利水渗湿
+【释名】
+伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
+宗奭曰︰多年樵斫之松根之气味，抑郁未绝，精英未沦。其精气盛者，发泄于外，结为茯苓，故不抱根，离其本体，有零之义也。津气不盛，只能附结本根，既不离本，故曰伏神。
+时珍曰︰茯苓，《史记•龟策传》作伏灵。盖松之神灵之气，伏结而成，故谓之伏灵、伏神也。《仙经》言︰伏灵大如拳者，佩之令百鬼消灭，则神灵之气，亦可征矣。俗作苓者，传写之讹尔。下有伏灵，上有菟丝，故又名伏莬。或云“其形如兔，故名”，亦通。
+【发明】
+弘景曰︰仙方只云茯苓而无茯神，为疗既同，用应无嫌。
+时珍曰︰《神农本草》只言茯苓，《名医别录》始添茯神，而主治皆同。后人治心病必用茯神。故洁古张氏云︰风眩心虚，非茯神不能除。然茯苓亦未尝不治心病也。陶弘景始言茯苓赤泻白补。
+李杲复分赤入丙丁、白入壬癸。此其发前人之秘者。时珍则谓茯苓、茯神，只当云赤入血分，则白茯神不能治心病，赤茯苓不能入膀胱矣。张元素不分赤白之说，于理欠通。
+《圣济录》松节散︰用茯神心中木一两，乳香一钱，石器炒，研为末。每服二钱，木瓜酒下。治风寒冷湿搏于筋骨，足筋挛痛，行步艰难，但是诸筋挛缩疼痛并主之。</t>
+        </is>
+      </c>
+      <c r="I62" s="38" t="inlineStr">
+        <is>
+          <t>木之四</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>suan_zao_ren</t>
+        </is>
+      </c>
+      <c r="B63" s="39" t="inlineStr">
+        <is>
+          <t>酸枣仁</t>
+        </is>
+      </c>
+      <c r="C63" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D63" s="39" t="inlineStr">
+        <is>
+          <t>甘|酸</t>
+        </is>
+      </c>
+      <c r="E63" s="39" t="inlineStr">
+        <is>
+          <t>心|肝</t>
+        </is>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G63" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H63" s="39" t="inlineStr">
+        <is>
+          <t>酸枣仁（酸枣）
+【气味】
+味甘、酸，性平
+【毒性】
+无毒
+【归经】
+归肝、胆、心经
+【主治】
+养心补肝
+宁心安神
+敛汗生津
+【释名】
+（《尔雅》）、山枣。
+【发明】
+恭曰︰《本经》用实疗不得眠，不言用仁。今方皆用仁。补中益肝，坚筋骨，助阴气，皆酸枣仁之功也。
+宗奭曰︰酸枣，《经》不言用仁，而今天下皆用之。
+志曰︰按︰《五代史‧后唐》刊石药验云︰酸枣仁，睡多生使，不得睡炒熟。陶云食之醒睡，而《经》云疗不得眠。盖其子肉味酸，食之使不思睡；核中仁服之，疗不得眠。正如麻黄发汗，根节止汗也。
+时珍曰︰酸枣实，味酸性收，故主肝病，寒热结气，酸痹久泄，脐下满痛之症。其仁甘而润，故熟用疗胆虚不得眠、烦渴虚汗之症，生用疗胆热好眠，皆足厥阴、少阳药也。今人专以为心家药，殊昧此理。</t>
+        </is>
+      </c>
+      <c r="I63" s="38" t="inlineStr">
+        <is>
+          <t>木之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>bai_zi_ren</t>
+        </is>
+      </c>
+      <c r="B64" s="39" t="inlineStr">
+        <is>
+          <t>柏子仁</t>
+        </is>
+      </c>
+      <c r="C64" s="39" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="D64" s="39" t="inlineStr">
+        <is>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E64" s="39" t="inlineStr">
+        <is>
+          <t>心|肺|肾</t>
+        </is>
+      </c>
+      <c r="F64" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G64" s="39" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H64" s="39" t="inlineStr">
+        <is>
+          <t>柏子仁（柏）
+【气味】
+味甘，性平
+【毒性】
+无毒
+【归经】
+归心、肾、大肠经
+【主治】
+养心安神
+润肠通便
+止汗
+【释名】
+（音菊）、侧柏。
+李时珍曰︰按︰魏子才《六书精蕴》云︰万木皆向阳，而柏独西指，盖阴木而有贞德者，故字从白。白者，西方也。陆佃《埤雅》云︰柏之指西，犹针之指南也。柏有数种，入药惟取叶扁而侧生者，故曰侧柏。
+寇宗奭曰︰予官陕西，登高望柏，千万株皆一一西指。盖此木至坚，不畏霜雪，得木之正气，他木不及。所以受金之正气所制，一一西指也。
+【发明】
+王好古曰︰柏子仁，肝经气分药也。又润肾，古方十精丸用之。
+时珍曰︰柏子仁性平而不寒不燥，味甘而补，辛而能润，其气清香，能透心肾，益脾盖仙家上品药也，宜乎滋养之剂用之。
+《列仙传》云︰赤松子食柏实，齿落更生，行及奔马。谅非虚语也。</t>
+        </is>
+      </c>
+      <c r="I64" s="38" t="inlineStr">
+        <is>
+          <t>木之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>yuan_zhi</t>
+        </is>
+      </c>
+      <c r="B65" s="39" t="inlineStr">
+        <is>
+          <t>远志</t>
+        </is>
+      </c>
+      <c r="C65" s="39" t="inlineStr">
+        <is>
+          <t>温</t>
+        </is>
+      </c>
+      <c r="D65" s="39" t="inlineStr">
         <is>
           <t>苦|辛</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="E65" s="39" t="inlineStr">
+        <is>
+          <t>心|肺|肾</t>
+        </is>
+      </c>
+      <c r="F65" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G65" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="38" t="inlineStr">
-        <is>
-          <t>谷之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>zhu_ye</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>竹叶</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>心|脾</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="38" t="inlineStr">
-        <is>
-          <t>木之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>sha_shen</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>沙参</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="38" t="inlineStr">
-        <is>
-          <t>草之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>bei_mu</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>贝母</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>心|肺</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="38" t="inlineStr">
-        <is>
-          <t>草之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>zhi_pi</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>栀皮</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>苦</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|脾|肺</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="38" t="inlineStr">
-        <is>
-          <t>木之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>li_pi</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>梨皮</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>凉</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="38" t="inlineStr">
-        <is>
-          <t>果之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>su_ye</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>苏叶</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>辛</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>ban_xia</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>辛</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>有毒</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="38" t="inlineStr">
-        <is>
-          <t>草之六</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>qian_hu</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>前胡</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>肺</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>chen_pi</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="38" t="inlineStr">
-        <is>
-          <t>果之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>fu_ling</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>茯苓</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="38" t="inlineStr">
-        <is>
-          <t>木之四</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>zhi_ke</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>枳壳</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>酸|苦|辛</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="38" t="inlineStr">
-        <is>
-          <t>木之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>fang_feng</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>防风</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>甘|辛</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>肝|脾|肾</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>qin_jiao</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>秦艽</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>肝|脾</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="38" t="inlineStr">
-        <is>
-          <t>草之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>dang_gui</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>当归</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>甘|辛</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|脾</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>chuan_xiong</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>川芎</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>辛</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>肝</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="38" t="inlineStr">
-        <is>
-          <t>草之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>wu_tou</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>乌头</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>热</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|脾|肾</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>大毒</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="38" t="inlineStr">
-        <is>
-          <t>草之六</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>huang_qi</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>黄芪</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="38" t="inlineStr">
-        <is>
-          <t>草之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>feng_mi</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>蜂蜜</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="38" t="inlineStr">
-        <is>
-          <t>虫之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>yi_yi_ren</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>薏苡仁</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>凉</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="38" t="inlineStr">
-        <is>
-          <t>谷之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>qiang_huo</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>羌活</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>肾</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="38" t="inlineStr">
-        <is>
-          <t>草之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>du_huo</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>独活</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>肾</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="38" t="inlineStr">
-        <is>
-          <t>草之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>shi_gao</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>石膏</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>大寒</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>甘|辛</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="38" t="inlineStr">
-        <is>
-          <t>石之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>zhi_mu</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>知母</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="38" t="inlineStr">
-        <is>
-          <t>草之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>jing_mi</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>粳米</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="38" t="inlineStr">
-        <is>
-          <t>谷之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>dan_nan_xing</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>胆南星</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>凉</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>肝|肺</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>有毒</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="38" t="inlineStr">
-        <is>
-          <t>草之六</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>gua_lou_ren</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>瓜蒌仁</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="38" t="inlineStr">
-        <is>
-          <t>草之七</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>huang_qin</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>黄芩</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>苦</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="38" t="inlineStr">
-        <is>
-          <t>草之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>zhi_shi</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>枳实</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>酸|苦|辛</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="38" t="inlineStr">
-        <is>
-          <t>木之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>ren_shen</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>人参</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肺</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="38" t="inlineStr">
-        <is>
-          <t>草之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>shu_di_huang</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>熟地黄</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>肝|肾</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>wu_wei_zi</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>五味子</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>酸|甘</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>心|肺|肾</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="38" t="inlineStr">
-        <is>
-          <t>草之七</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>zi_wan</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>紫菀</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>肺</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>sang_bai_pi</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>桑白皮</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>肺</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="38" t="inlineStr">
-        <is>
-          <t>木之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>mai_dong</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>麦冬</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肺</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>yu_zhu</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>玉竹</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>tian_hua_fen</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>天花粉</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="38" t="inlineStr">
-        <is>
-          <t>草之七</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t>bian_dou</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>扁豆</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>脾</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="38" t="inlineStr">
-        <is>
-          <t>谷之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
-        <is>
-          <t>sheng_di_huang</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>生地黄</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|肾</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>tian_dong</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>天冬</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>寒</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>肺|肾</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>xuan_shen</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>玄参</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>甘|苦|咸</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t>dan_shen</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>丹参</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>苦</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>心|肝</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="38" t="inlineStr">
-        <is>
-          <t>草之五</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t>fu_shen</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>茯神</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="38" t="inlineStr">
-        <is>
-          <t>木之四</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>suan_zao_ren</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>酸枣仁</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>酸|甘</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>心|肝</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="38" t="inlineStr">
-        <is>
-          <t>果之二</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t>bai_zi_ren</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>柏子仁</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>心|肺|肾</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="38" t="inlineStr">
-        <is>
-          <t>木之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t>yuan_zhi</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>远志</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>温</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>心|肺|肾</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="n"/>
+      <c r="H65" s="39" t="inlineStr">
+        <is>
+          <t>远志
+【气味】
+味苦、辛，性温
+【毒性】
+无毒
+【归经】
+归心、肾、肺经
+【主治】
+安神益智
+交通心肾
+祛痰
+消肿
+【释名】
+苗名小草（《本经》）、细草（《本经》）、棘菀（《本经》）、 绕（《本经》）。
+时珍曰︰此草服之能益智强志，故有远志之称。《世说》载郝隆讥谢安云︰处则为远志，出则为小草。《记事珠》谓之醒心杖。
+【发明】
+好古曰︰远志，肾经气分药也。
+时珍曰︰远志，入足少阴肾经，非心经药也。其功专于强志益精，治善忘。盖精与志，皆肾经之所藏也。肾经不足，则志气衰，不能上通于心，故迷惑善忘。《灵枢经》云︰肾藏精，精合志。肾盛怒而不止则伤志，志伤则喜忘其前言，腰脊不可以俯仰屈伸，毛悴色夭。又云︰人之善忘者，上气不足，下气有馀，肠胃实而心肺虚，虚则营卫留于下，久之不以时上，故善忘也。陈言《三因方》远志酒，治痈疽，云有奇功，盖亦补肾之力尔。葛洪《抱朴子》云：陵阳子仲服远志二十年，有子三十七人，能开书所视不忘，坐在立亡。</t>
+        </is>
+      </c>
       <c r="I65" s="38" t="inlineStr">
         <is>
           <t>草之一</t>
@@ -14700,7 +16011,11 @@
           <t>心|肝|脾|肾</t>
         </is>
       </c>
-      <c r="F66" s="39" t="n"/>
+      <c r="F66" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
       <c r="G66" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
@@ -14708,9 +16023,9 @@
       </c>
       <c r="H66" s="39" t="inlineStr">
         <is>
-          <t>肉桂
+          <t>肉桂（桂）
 【气味】
-辛、甘，大热
+味辛、甘，性大热
 【毒性】
 无毒
 【归经】
@@ -14738,37 +16053,62 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>mu_tong</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>木通</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="39" t="inlineStr">
         <is>
           <t>寒</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="39" t="inlineStr">
         <is>
           <t>苦</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>心|肾</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="E67" s="39" t="inlineStr">
+        <is>
+          <t>心|脾|肾</t>
+        </is>
+      </c>
+      <c r="F67" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G67" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="39" t="inlineStr">
+        <is>
+          <t>木通（通草）
+【气味】
+味苦，性寒
+【毒性】
+无毒
+【归经】
+归心、小肠、膀胱经
+【主治】
+利尿通淋
+清心除烦
+通经下乳
+【释名】
+木通（士良）、附支（《本经》）
+时珍曰︰有细细孔，两头皆通，故名通草，即今所谓木通也。今之通草，乃古之通脱木也。宋本草混注为一，名实相乱，今分出之。
+【发明】
+杲曰︰本草十剂︰通可去滞，通草、防己之属是也。夫防己大苦寒，能泻血中湿热之滞，又通大便。通草甘淡，能助西方秋气下降，利小便，专泻气滞也。肺受热邪，津液气化之原绝，则寒水断流，膀胱受湿热，癃闭约缩，小便不通，宜此治之。其症胸中烦热，口燥舌干，咽干，大渴引饮，小便淋沥，或闭塞不通，胫酸脚热，并宜通草主之。凡气味与之同者，茯苓、泽泻、灯草、猪苓、琥珀、瞿麦、车前子之类，皆可以渗湿利小便，泄其滞气也。又曰︰木通下行，泄小肠火，利小便，与琥珀同功，无他药可比。
+时珍曰︰木通手厥阴心包络、手足太阳小肠、膀胱之药也。故上能通心清肺，治头痛，利九窍；下能泄湿热，利小便，通大肠，治遍身拘痛。《本经》及《别录》皆不言及利小便治淋之功，甄权、日华子辈始发扬之。盖其能泄丙丁之火，则肺不受邪，能通水道。水源既清，则津液自化，而诸经之湿与热，皆由小便泄去。故古方导赤散用之，亦泻南补北、扶西抑东之意。杨仁斋《直指方》言︰人遍身胸腹隐热，疼痛拘急，足冷，皆是伏热伤血。血属于心，宜木通以通心窍，则经络流行也。</t>
+        </is>
+      </c>
       <c r="I67" s="38" t="inlineStr">
         <is>
           <t>草之七</t>
@@ -14776,37 +16116,59 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>zhu_ru</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>竹茹</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>微寒</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="C68" s="39" t="inlineStr">
+        <is>
+          <t>寒</t>
+        </is>
+      </c>
+      <c r="D68" s="39" t="inlineStr">
         <is>
           <t>甘</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="39" t="inlineStr">
         <is>
           <t>心|肝|脾|肺</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="F68" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G68" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="39" t="inlineStr">
+        <is>
+          <t>竹茹（竹）
+【气味】
+味甘，性微寒
+【毒性】
+无毒
+【归经】
+归肺、胃、心、胆经
+【主治】
+清热化痰
+除烦止呕
+【释名】
+时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。
+故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+【发明】</t>
+        </is>
+      </c>
       <c r="I68" s="38" t="inlineStr">
         <is>
           <t>木之五</t>
@@ -14814,37 +16176,64 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="41" t="inlineStr">
         <is>
           <t>shi_chang_pu</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="39" t="inlineStr">
         <is>
           <t>石菖蒲</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="39" t="inlineStr">
         <is>
           <t>温</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>苦|辛</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="D69" s="39" t="inlineStr">
+        <is>
+          <t>辛|苦</t>
+        </is>
+      </c>
+      <c r="E69" s="39" t="inlineStr">
         <is>
           <t>心|脾</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="F69" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G69" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H69" s="7" t="n"/>
+      <c r="H69" s="39" t="inlineStr">
+        <is>
+          <t>石菖蒲（菖蒲）
+【气味】
+味辛、苦，性温
+【毒性】
+无毒
+【归经】
+归心、胃经
+【主治】
+开窍豁痰
+醒神益智
+化湿开胃
+【释名】
+昌阳（《本经》）、尧韭（普）、水剑草。
+时珍曰︰菖蒲，乃蒲类之昌盛者，故曰菖蒲。又《吕氏春秋》云︰冬至后五十七日，菖始生。菖者百草之先生者，于是始耕。则菖蒲、昌阳又取此义也。《典术》云︰尧时天降精于庭为韭，感百阴之气为菖蒲。故曰尧韭。方士隐为水剑，因叶形也。
+【发明】
+颂曰︰古方有单服菖蒲法。蜀人治心腹冷气 痛者，取一、二寸捶碎，同吴茱萸煎汤饮之。亦将随行，卒患心痛，嚼一、二寸，热汤或酒送下，亦效。
+时珍曰︰国初周颠仙对太祖高皇帝常嚼菖蒲饮水。问其故。云服之无腹痛之疾。高皇御制碑中载之。菖蒲气温味辛，乃手少阴、足厥阴之药。心气不足者用之，虚则补其母也。肝苦急以辛补之，是矣。《道藏经》有《菖蒲传》一卷，其语粗陋。今略节其要云︰菖蒲者，水草之精英，神仙之灵药也。其法采紧小似鱼鳞者一斤，以水及米泔浸各一宿，刮去皮切，曝干捣筛，以糯米粥和匀，更入熟蜜搜和，丸如梧子大，稀葛袋盛，置当风处令干。每旦酒、饮任下三十丸，临卧更服三十丸。服至一月，消食；二月，痰除；服至五年，骨髓充，颜色泽，白发黑，落齿更生。其药以五德配五行︰叶青，花赤，节白，心黄，根黑。能治一切诸风，手足顽痹，瘫缓不遂，五劳七伤，填血补脑，坚骨髓，长精神，润五脏，裨六腑，开胃口，和血脉，益口齿，明耳目，泽皮肤，去寒热，除三尸九虫，天行时疾，瘴疫瘦病，泻痢痔漏，妇人带下，产后血运。并以酒服。河内叶敬母中风，服之一年而百病愈。寇天师服之得道，至今庙前犹生菖蒲。郑鱼、曾原等，皆以服此得道也。
+又按︰葛洪《抱朴子》云︰韩众服菖蒲十三年，身上生毛，冬袒不寒，日记万言。商丘子不娶，惟食菖蒲根，不饥不老，不知所终。《神仙传》云︰咸阳王典食菖蒲得长生。安期生采一寸九节菖蒲服，仙去。又按︰ 仙《神隐书》云︰石菖蒲置一盆于几上，夜间观书，则收烟无害目之患。或置星露之下，至旦取叶尖露水洗目，大能明视，久则白昼见星。端午日以酒服，尤妙。苏东坡云︰凡草生石上，必须微土以附其根。惟石菖蒲濯去泥土，渍以清水，置盆中，可数十年不枯。节叶坚瘦，根须连络，苍然于几案间，久更可喜。其延年轻身之功，既非昌阳可比；至于忍寒淡泊，不待泥土而生，又岂昌阳所能仿佛哉？
+杨士瀛曰︰下痢噤口，虽是脾虚，亦热气闭隔心胸所致。俗用木香失之温，用山药失之闭。惟参苓白术散加石菖蒲，粳米饮调下。或用参、苓、石莲肉，少入菖蒲服。胸次一开，自然思食。</t>
+        </is>
+      </c>
       <c r="I69" s="38" t="inlineStr">
         <is>
           <t>草之八</t>
@@ -14852,37 +16241,73 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="15" t="inlineStr">
+      <c r="A70" s="41" t="inlineStr">
         <is>
           <t>huang_lian</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>黄连</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="39" t="inlineStr">
         <is>
           <t>寒</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="39" t="inlineStr">
         <is>
           <t>苦</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>心|肝|脾|肺</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="E70" s="39" t="inlineStr">
+        <is>
+          <t>心|肝|脾</t>
+        </is>
+      </c>
+      <c r="F70" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G70" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H70" s="7" t="n"/>
+      <c r="H70" s="39" t="inlineStr">
+        <is>
+          <t>黄连
+【气味】
+味苦，大寒
+【毒性】
+无毒
+【归经】
+归心、脾、胃、肝、胆、大肠经
+【主治】
+清热燥湿
+泻火解毒
+【释名】
+王连（《本经》）、支连（《药性》）
+时珍曰：其根连珠而色黄，故名。
+【发明】
+元素曰：黄连性寒味苦，气味俱浓，可升可降，阴中阳也，入手少阴经。其用有六：泻心脏火，一也；去中焦湿热，二也；诸疮必用，三也；去风湿，四也；赤眼暴发，五也；止中部见血，六也。张仲景治九种心下痞，五等泻心汤，皆用之。
+成无己曰：苦入心，寒胜热，黄连、大黄之苦寒，以导心下之虚热。蛔得甘则动，得苦 则安，黄连、黄柏之苦，以安蛔也。
+好古曰：黄连苦燥，苦入心，火就燥。泻心者，其实泻脾也，实则泻其子也。
+震亨曰：黄连，去中焦湿热而泻心火。若脾胃气虚，不能转运者，则以茯苓、黄芩代之。以猪胆汁拌炒，佐以龙胆草，则大泻肝胆之火。下痢胃口热禁口者，用黄连、人参煎汤，终日呷之，如吐再强饮，但得一呷下咽便好。
+刘完素曰：古方以黄连为治痢之最。盖治痢惟宜辛苦寒药，辛能发散开通郁结，苦能燥 湿，寒能胜热，使气宣平而已。诸苦寒药多泄，惟黄连、黄柏性冷而燥，能降火去湿而止泻痢，故治痢以之为君。
+宗奭曰：今人多用黄连治痢，盖执以苦燥之义。下俚但见肠虚渗泄，微似有血，便即用之，又罔顾寒热多少，惟欲尽剂，由是多致危困。若气实初病，热多血痢，服之便止，不必 尽剂。虚而冷者，慎勿轻用。
+杲曰：诸痛痒疮疡，皆属心火。凡诸疮宜以黄连、当归为君，甘草、黄芩为佐。凡眼暴 发赤肿，痛不可忍者，宜黄连、当归以酒浸煎之。宿食不消，心下痞满者，须用黄连、枳实。
+颂曰：黄连治目方多，而羊肝丸尤奇异。今医家洗眼，以黄连、当归、芍药等分，用雪 水或甜水煎汤热洗之，冷即再温，甚益眼目。但是风毒赤目花翳，用之无不神效。盖眼目之病，皆是血脉凝滞使然，故以行血药合黄连治之。血得热则行，故乘热洗也。
+韩 曰：火分之病，黄连为主，不但泻心火，而与芩、柏诸苦药例称者比也。目疾，入以人乳浸蒸，或点或服之。生用为君，佐以官桂少许，煎百沸，入蜜空心服之，能使心肾 交于顷刻。入五苓、滑石，大治梦遗。以黄土、姜汁、酒、蜜四炒为君，以使君子为臣，白芍药酒煮为佐，广木香为使，治小儿五疳。以茱萸炒者，加木香等分，生大黄倍之，水丸，治五痢。此皆得制方之法也。
+时珍曰：黄连，治目及痢为要药。古方治痢：香连丸，用黄连、木香；姜连散，用干姜、黄连；变通丸，用黄连、茱萸；姜黄散，用黄连、生姜。治消渴，用酒蒸黄连；治伏暑，用酒煮黄连；治下血，用黄连、大蒜；治肝火，用黄连、茱萸；治口疮，用黄连、细辛。皆是一冷一热，一阴一阳，寒因热用，热因寒用，君臣相佐，阴阳相济，最得制方之妙，所以有成功而无偏胜之害也。
+弘景曰：俗方多用黄连治痢及渴，道方服食长生。
+慎微曰：刘宋王微《黄连赞》云：黄连味苦，左右相因。断凉涤暑，阐命轻身。缙云昔御，飞跸上 。不行而至，吾闻其人。又梁江淹《黄连颂》云：黄连上草，丹砂之次。御孽 辟妖，长灵久视。骖龙行天，驯马匝地。鸿飞以仪，顺道则利。
+时珍曰：《本经》、《别录》并无黄连久服长生之说，惟陶弘景言道方久服长生。
+《神仙传》载封君达、黑穴公，并服黄连五十年得仙。窃谓黄连大苦大寒之药，用之降火燥 湿，中病即当止。岂可久服，使肃杀之令常行，而伐其生发冲和之气乎？《素问》载岐伯言 ：五味入胃，各归所喜攻。久而增气，物化之常也。气增而久，夭之由也。王冰注云：酸入肝为温，苦入心为热，辛入肺为清，咸入肾为寒，甘入脾为至阴而四气兼之，皆增其味而益其气，故各从本脏之气为用。所以久服黄连、苦参反热，从火化也，余味皆然。久则脏气偏 胜，即有偏绝，则有暴夭之道。是以绝粒服饵之人不暴亡者，无五味偏助也。又秦观与乔希 圣论黄连书云：闻公以眼疾饵黄连，至十数两犹不巳，殆不可也。医经有久服黄连、苦参反 热之说。此虽大寒，其味至苦，入胃则先归于心，久而不己，心火偏胜则热，乃其理也。况 眼疾本于肝热，肝与心为子母。心火也，肝亦火也，肾孤脏也，人患一水不胜二火。岂可久 服苦药，使心有所偏胜，是以火救火，其可乎？秦公此书，盖因王公之说而推详之也。我明荆端王素多火病，医令服金花丸，乃芩、连、栀、柏四味，饵至数年，其火愈炽，遂至内障 丧明。观此，则寒苦之药，不但使人不能长生，久则气增偏胜，速夭之由矣。当以《素问》 之言为法，陶氏道书之说，皆谬谈也。杨士瀛云：黄连能去心窍恶血。</t>
+        </is>
+      </c>
       <c r="I70" s="38" t="inlineStr">
         <is>
           <t>草之二</t>
@@ -14890,42 +16315,68 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="41" t="inlineStr">
         <is>
           <t>xi_xin</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="39" t="inlineStr">
         <is>
           <t>细辛</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="39" t="inlineStr">
         <is>
           <t>温</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="39" t="inlineStr">
         <is>
           <t>辛</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E71" s="39" t="inlineStr">
         <is>
           <t>心|肺|肾</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="39" t="inlineStr">
         <is>
           <t>小毒</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G71" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H71" s="7" t="n"/>
+      <c r="H71" s="39" t="inlineStr">
+        <is>
+          <t>细辛
+【气味】
+味辛，性温
+【毒性】
+小毒
+【归经】
+归肺、肾、心经
+【主治】
+解表散寒
+祛风止痛
+通窍
+温肺化饮
+【释名】
+小辛（《本经》）、少辛。
+颂曰：华州真细辛，根细而味极辛，故名之曰细辛。
+时珍曰：小辛、少辛，皆此义也。按《山海经》云，浮戏之山多少辛。《管子》云，五沃之土，群药生少辛，是矣。
+【发明】
+宗奭曰：治头面风痛，不可缺此。
+元素曰：细辛气温，味大辛，气浓于味，阳也，升也，入足厥阴、少阴血分，为手少阴引经之药。香味俱细，故入少阴，与独活相类。以独活为使，治少阴头痛如神。亦止诸阳头痛，诸风通用之。味辛而热，温少阴之经，散水气以去内寒。
+成无己曰：水停心下不行，则肾气燥，宜辛以润之。细辛之辛，以行水气而润燥。
+杲曰：胆气不足，细辛补之。又治邪气自里之表，故仲景少阴证，用麻黄附子细辛汤。
+时珍曰：气之浓者能发热，阳中之阳也。辛温能散，故诸风寒、风湿头痛、痰饮、胸中滞气、惊痫者，宜用之。口疮、喉痹、 齿诸病用之者，取其能散浮热，亦火郁则发之之义也。辛能泄肺，故风寒咳嗽上气者，宜用之。辛能补肝，故胆气不足，惊痫眼目诸病，宜用之。辛能润燥，故通少阴及耳窍，便涩者宜用之。
+承曰：细辛非华阴者不得为真。若单用末，不可过一钱。多则气闷塞不通者死，虽死无伤。近年开平狱中尝治此，不可不记。非本有毒，但不识多寡耳。</t>
+        </is>
+      </c>
       <c r="I71" s="38" t="inlineStr">
         <is>
           <t>草之二</t>
@@ -14935,12 +16386,12 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>tong_cao</t>
+          <t>chai_hu</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>通草</t>
+          <t>柴胡</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -14950,12 +16401,17 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>甘</t>
+          <t>苦|辛</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>脾|肺</t>
+          <t>肝</t>
+        </is>
+      </c>
+      <c r="F72" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -14966,34 +16422,39 @@
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="38" t="inlineStr">
         <is>
-          <t>木之五</t>
+          <t>草之二</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>chai_hu</t>
+          <t>xiang_fu</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>柴胡</t>
+          <t>香附</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>微寒</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>苦|辛</t>
+          <t>甜|苦|辛</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>肝</t>
+          <t>肝|脾</t>
+        </is>
+      </c>
+      <c r="F73" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -15004,34 +16465,39 @@
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="38" t="inlineStr">
         <is>
-          <t>草之二</t>
+          <t>草之八</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>xiang_fu</t>
+          <t>long_dan_cao</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>香附</t>
+          <t>龙胆草</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>寒</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>甜|苦|辛</t>
+          <t>苦</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>肝|脾</t>
+          <t>肝</t>
+        </is>
+      </c>
+      <c r="F74" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -15042,19 +16508,19 @@
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="38" t="inlineStr">
         <is>
-          <t>草之八</t>
+          <t>草之二</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>long_dan_cao</t>
+          <t>ze_xie</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>龙胆草</t>
+          <t>泽泻</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -15064,12 +16530,17 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>苦</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>肝</t>
+          <t>甘</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>肾</t>
+        </is>
+      </c>
+      <c r="F75" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -15080,34 +16551,39 @@
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="38" t="inlineStr">
         <is>
-          <t>草之二</t>
+          <t>草之八</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>zhi_zi</t>
+          <t>che_qian_zi</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>栀子</t>
+          <t>车前子</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>寒</t>
+          <t>微寒</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>苦</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>心|肺</t>
+          <t>心|肝|肺|肾</t>
+        </is>
+      </c>
+      <c r="F76" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -15118,34 +16594,39 @@
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="38" t="inlineStr">
         <is>
-          <t>木之三</t>
+          <t>草之八</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>ze_xie</t>
+          <t>hui_xiang</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>泽泻</t>
+          <t>茴香</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>寒</t>
+          <t>温</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>肾</t>
+          <t>辛</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>肝|脾|肾</t>
+        </is>
+      </c>
+      <c r="F77" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -15156,24 +16637,24 @@
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="38" t="inlineStr">
         <is>
-          <t>草之八</t>
+          <t>菜之二</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t>che_qian_zi</t>
+          <t>gou_qi_zi</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>车前子</t>
+          <t>枸杞子</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>微寒</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -15183,7 +16664,12 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>心|肝|肺|肾</t>
+          <t>肝|肾</t>
+        </is>
+      </c>
+      <c r="F78" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -15194,19 +16680,19 @@
       <c r="H78" s="7" t="n"/>
       <c r="I78" s="38" t="inlineStr">
         <is>
-          <t>草之八</t>
+          <t>木之三</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>hui_xiang</t>
+          <t>wu_yao</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>茴香</t>
+          <t>乌药</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -15221,7 +16707,12 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>肝|脾|肾</t>
+          <t>脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F79" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -15232,34 +16723,39 @@
       <c r="H79" s="7" t="n"/>
       <c r="I79" s="38" t="inlineStr">
         <is>
-          <t>菜之二</t>
+          <t>木之三</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t>gou_qi_zi</t>
+          <t>chen_xiang</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>枸杞子</t>
+          <t>沉香</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>微温</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>甘</t>
+          <t>苦|辛</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>肝|肾</t>
+          <t>脾|肾</t>
+        </is>
+      </c>
+      <c r="F80" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -15270,34 +16766,39 @@
       <c r="H80" s="7" t="n"/>
       <c r="I80" s="38" t="inlineStr">
         <is>
-          <t>木之三</t>
+          <t>木之一</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>wu_yao</t>
+          <t>chuan_lian_zi</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>乌药</t>
+          <t>川楝子</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>温</t>
+          <t>寒</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>辛</t>
+          <t>苦</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>脾|肺|肾</t>
+          <t>心|肝|肾</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>小毒</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -15315,27 +16816,32 @@
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t>chen_xiang</t>
+          <t>gou_teng</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>沉香</t>
+          <t>钩藤</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>微温</t>
+          <t>凉</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>苦|辛</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>脾|肾</t>
+          <t>肝</t>
+        </is>
+      </c>
+      <c r="F82" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -15346,39 +16852,39 @@
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="38" t="inlineStr">
         <is>
-          <t>木之一</t>
+          <t>草之七</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>chuan_lian_zi</t>
+          <t>bai_zhu</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>川楝子</t>
+          <t>白术</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>寒</t>
+          <t>温</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>苦</t>
+          <t>甘|苦</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>心|肝|肾</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>小毒</t>
+          <t>脾</t>
+        </is>
+      </c>
+      <c r="F83" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -15389,34 +16895,39 @@
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="38" t="inlineStr">
         <is>
-          <t>木之三</t>
+          <t>草之二</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>gou_teng</t>
+          <t>huo_xiang</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>钩藤</t>
+          <t>藿香</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>凉</t>
+          <t>微温</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>甘</t>
+          <t>辛</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>肝</t>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -15427,19 +16938,19 @@
       <c r="H84" s="7" t="n"/>
       <c r="I84" s="38" t="inlineStr">
         <is>
-          <t>草之七</t>
+          <t>草之三</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>bai_zhu</t>
+          <t>hou_po</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>白术</t>
+          <t>厚朴</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -15449,12 +16960,17 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>甘|苦</t>
+          <t>苦|辛</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>脾</t>
+          <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F85" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -15465,19 +16981,19 @@
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="38" t="inlineStr">
         <is>
-          <t>草之二</t>
+          <t>木之二</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>huo_xiang</t>
+          <t>da_fu_pi</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>藿香</t>
+          <t>大腹皮</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
@@ -15492,7 +17008,12 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>脾|肺</t>
+          <t>心|脾|肺</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
@@ -15503,19 +17024,19 @@
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="38" t="inlineStr">
         <is>
-          <t>草之三</t>
+          <t>木之三</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>hou_po</t>
+          <t>bai_zhi</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>厚朴</t>
+          <t>白芷</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -15525,12 +17046,17 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>苦|辛</t>
+          <t>辛</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
           <t>脾|肺</t>
+        </is>
+      </c>
+      <c r="F87" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -15541,34 +17067,39 @@
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="38" t="inlineStr">
         <is>
-          <t>木之二</t>
+          <t>草之三</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t>da_fu_pi</t>
+          <t>shan_yao</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>大腹皮</t>
+          <t>山药</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>微温</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>辛</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>心|脾|肺</t>
+          <t>脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -15579,34 +17110,39 @@
       <c r="H88" s="7" t="n"/>
       <c r="I88" s="38" t="inlineStr">
         <is>
-          <t>木之三</t>
+          <t>草之一</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>bai_zhi</t>
+          <t>lian_zi</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>白芷</t>
+          <t>莲子</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>温</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>辛</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>脾|肺</t>
+          <t>心|脾|肾</t>
+        </is>
+      </c>
+      <c r="F89" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -15617,24 +17153,24 @@
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="38" t="inlineStr">
         <is>
-          <t>草之三</t>
+          <t>果之六</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>shan_yao</t>
+          <t>sha_ren</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>山药</t>
+          <t>扁豆</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>微温</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -15644,7 +17180,12 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>脾|肺|肾</t>
+          <t>脾</t>
+        </is>
+      </c>
+      <c r="F90" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
@@ -15652,126 +17193,72 @@
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H90" s="7" t="n"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>扁豆（藊豆）
+【气味】
+味甘，性微温
+【毒性】
+无毒
+【归经】
+归脾、胃经
+【主治】
+健脾化湿
+和中消暑
+【释名】
+沿篱豆（俗）、蛾眉豆
+时珍曰︰ ，本作扁，荚形扁也。沿篱，蔓延也。蛾眉，象豆脊白路之形也。
+【发明】
+时珍曰︰硬壳白扁豆，其子充实，白而微黄，其气腥香，其性温平，得乎中和，脾之谷也。入太阴气分，通利三焦，能化清降浊，故专治中宫之病，消暑除湿而解毒也。其软壳及黑鹊色者，其性微凉，但可供食，亦调脾胃。</t>
+        </is>
+      </c>
       <c r="I90" s="38" t="inlineStr">
         <is>
-          <t>草之一</t>
+          <t>谷之三</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>lian_zi</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>莲子</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肾</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="A91" s="41" t="inlineStr">
+        <is>
+          <t>gan_jiang</t>
+        </is>
+      </c>
+      <c r="B91" s="39" t="inlineStr">
+        <is>
+          <t>干姜</t>
+        </is>
+      </c>
+      <c r="C91" s="39" t="inlineStr">
+        <is>
+          <t>热</t>
+        </is>
+      </c>
+      <c r="D91" s="39" t="inlineStr">
+        <is>
+          <t>辛</t>
+        </is>
+      </c>
+      <c r="E91" s="39" t="inlineStr">
+        <is>
+          <t>心|脾|肺|肾</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G91" s="39" t="inlineStr">
         <is>
           <t>shen_nong_bai_cao_jing</t>
         </is>
       </c>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="38" t="inlineStr">
-        <is>
-          <t>果之六</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>sha_ren</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>扁豆</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>微温</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>脾</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="38" t="inlineStr">
-        <is>
-          <t>谷之三</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="41" t="inlineStr">
-        <is>
-          <t>gan_jiang</t>
-        </is>
-      </c>
-      <c r="B93" s="39" t="inlineStr">
-        <is>
-          <t>干姜</t>
-        </is>
-      </c>
-      <c r="C93" s="39" t="inlineStr">
-        <is>
-          <t>热</t>
-        </is>
-      </c>
-      <c r="D93" s="39" t="inlineStr">
-        <is>
-          <t>辛</t>
-        </is>
-      </c>
-      <c r="E93" s="39" t="inlineStr">
-        <is>
-          <t>心|脾|肺|肾</t>
-        </is>
-      </c>
-      <c r="F93" s="39" t="n"/>
-      <c r="G93" s="39" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H93" s="39" t="inlineStr">
+      <c r="H91" s="39" t="inlineStr">
         <is>
           <t>干姜
 【气味】
-辛，热
+味辛，性热
 【毒性】
 无毒
 【归经】
@@ -15790,36 +17277,127 @@
 时珍曰：干姜，能引血药入血分，气药入气分，又能去恶养新，有阳生阴长之意，故血虚者用之；而人吐血、衄血、下血，有阴无阳者，亦宜用之。乃热因热用，从治之法也。</t>
         </is>
       </c>
+      <c r="I91" s="38" t="inlineStr">
+        <is>
+          <t>菜之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>shan_zhu_yu</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>山茱萸</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>微温</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>酸</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>肝|肾</t>
+        </is>
+      </c>
+      <c r="F92" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="38" t="inlineStr">
+        <is>
+          <t>果之三</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>dan_pi</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>丹皮</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>微寒</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>苦|辛</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>心|肝|肾</t>
+        </is>
+      </c>
+      <c r="F93" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>shen_nong_bai_cao_jing</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="n"/>
       <c r="I93" s="38" t="inlineStr">
         <is>
-          <t>菜之一</t>
+          <t>木之三</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>shan_zhu_yu</t>
+          <t>fu_zi</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>山茱萸</t>
+          <t>附子</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>微温</t>
+          <t>大热</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>酸</t>
+          <t>甘|辛</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>肝|肾</t>
+          <t>心|脾|肾</t>
+        </is>
+      </c>
+      <c r="F94" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
@@ -15830,34 +17408,39 @@
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="38" t="inlineStr">
         <is>
-          <t>果之三</t>
+          <t>草之六</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>dan_pi</t>
+          <t>long_yan</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>丹皮</t>
+          <t>龙眼</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>微寒</t>
+          <t>温</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>苦|辛</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>心|肝|肾</t>
+          <t>心|脾</t>
+        </is>
+      </c>
+      <c r="F95" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -15868,34 +17451,39 @@
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="38" t="inlineStr">
         <is>
-          <t>木之三</t>
+          <t>果之三</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t>fu_zi</t>
+          <t>mu_xiang</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>附子</t>
+          <t>木香</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>大热</t>
+          <t>温</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>甘|辛</t>
+          <t>苦|辛</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>心|脾|肾</t>
+          <t>肝|脾|肺</t>
+        </is>
+      </c>
+      <c r="F96" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
@@ -15906,24 +17494,24 @@
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="38" t="inlineStr">
         <is>
-          <t>草之六</t>
+          <t>草之三</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>long_yan</t>
+          <t>e_jiao</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>龙眼</t>
+          <t>阿胶</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>温</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -15933,7 +17521,12 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>心|脾</t>
+          <t>肝|肺|肾</t>
+        </is>
+      </c>
+      <c r="F97" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -15944,34 +17537,39 @@
       <c r="H97" s="7" t="n"/>
       <c r="I97" s="38" t="inlineStr">
         <is>
-          <t>果之三</t>
+          <t>兽之一</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>mu_xiang</t>
+          <t>ji_zi_huang</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>木香</t>
+          <t>鸡子黄</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>温</t>
+          <t>平</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>苦|辛</t>
+          <t>甘</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>肝|脾|肺</t>
+          <t>心|脾|肾</t>
+        </is>
+      </c>
+      <c r="F98" s="40" t="inlineStr">
+        <is>
+          <t>无毒</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -15982,85 +17580,15 @@
       <c r="H98" s="7" t="n"/>
       <c r="I98" s="38" t="inlineStr">
         <is>
-          <t>草之三</t>
+          <t>禽之一</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>e_jiao</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>阿胶</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>肝|肺|肾</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="n"/>
-      <c r="I99" s="38" t="inlineStr">
-        <is>
-          <t>兽之一</t>
-        </is>
-      </c>
+      <c r="A99" s="15" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>ji_zi_huang</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>鸡子黄</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>平</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>甘</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>心|脾|肾</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>shen_nong_bai_cao_jing</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="38" t="inlineStr">
-        <is>
-          <t>禽之一</t>
-        </is>
-      </c>
+      <c r="A100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="15" t="n"/>
@@ -16088,12 +17616,6 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="15" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A1048576">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Disease" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Book" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,7 +23,7 @@
   <numFmts count="0"/>
   <fonts count="10">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -86,7 +86,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <charset val="134"/>
       <family val="3"/>
       <sz val="9"/>
@@ -272,7 +272,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -626,13 +626,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="37.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="37.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="19" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="20.75" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26.59765625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="20.73046875" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -1994,10 +1994,10 @@
 【症状】
 大热：全身壮热、不恶寒反恶热；大汗：热迫津泄、大汗出；大渴：口大渴、喜冷饮；脉洪大
 【脉象】
-浮脉（表）：波峰高（轻微），波速快（轻微）
-左寸（心）：波峰高（轻微），波速快（轻微）
-右寸（肺）：波峰高（剧烈），波速快（剧烈），波宽窄（轻微）
-右关（脾胃，大小肠）：波峰高（剧烈），波速快（剧烈），波宽窄（轻微）
+浮脉（表）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
+左寸（心）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
+右寸（肺）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
+右关（脾胃，大小肠）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
 【标准方】
 白虎汤</t>
         </is>
@@ -2197,33 +2197,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="38" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="38" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="38" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="33" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="39" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="39" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="39" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="38" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="38" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="38" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="39" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="39" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="39" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="40" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="40" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="40" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="40" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="40" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="40" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="38" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="38" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="38" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="41" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="38" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="38" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="38" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="41" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="41" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="41" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="41" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="41" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="41" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="41" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="41" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="41" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="41" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="41" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="41" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="38"/>
-    <col width="9" customWidth="1" style="9" min="39" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="41" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="39"/>
+    <col width="9" customWidth="1" style="9" min="40" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -2849,17 +2849,23 @@
         </is>
       </c>
       <c r="B39" s="38" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D39" s="38" t="n">
         <v>1.3</v>
       </c>
+      <c r="E39" s="38" t="n">
+        <v>0.7</v>
+      </c>
       <c r="F39" s="33" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H39" s="33" t="n">
         <v>1.3</v>
       </c>
+      <c r="I39" s="33" t="n">
+        <v>0.7</v>
+      </c>
       <c r="N39" s="40" t="n">
         <v>1.5</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>1.5</v>
       </c>
       <c r="Q39" s="40" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R39" s="38" t="n">
         <v>1.5</v>
@@ -2876,7 +2882,7 @@
         <v>1.5</v>
       </c>
       <c r="U39" s="38" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -2966,12 +2972,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="45.75" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="45.73046875" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -4918,14 +4924,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F306"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13513,17 +13519,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20501,14 +20507,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -686,14 +686,11 @@
       <c r="E2" s="26" t="inlineStr">
         <is>
           <t>风寒表实证
-【病机】
-寒邪束表、腠理闭塞、卫阳被遏
-【症状】
-恶寒发热，头身酸疼，无汗而喘
+【病机】寒邪束表、腠理闭塞、卫阳被遏
+【症状】恶寒发热，头身酸疼，无汗而喘
 【脉象】
 浮脉（表）：波峰高，波速慢
-【标准方】
-麻黄汤</t>
+【标准方】麻黄汤</t>
         </is>
       </c>
     </row>
@@ -721,14 +718,11 @@
       <c r="E3" s="26" t="inlineStr">
         <is>
           <t>风寒表虚证
-【病机】
-风寒袭表，卫气不固，营阴外泄
-【症状】
-恶风发热，头痛流清涕，出汗
+【病机】风寒袭表，卫气不固，营阴外泄
+【症状】恶风发热，头痛流清涕，出汗
 【脉象】
 浮脉（表）：波峰低，波速慢
-【标准方】
-桂枝汤</t>
+【标准方】桂枝汤</t>
         </is>
       </c>
     </row>
@@ -756,14 +750,11 @@
       <c r="E4" s="26" t="inlineStr">
         <is>
           <t>风热表证
-【病机】
-风热之邪侵袭肺卫，卫气失和，肺失清肃
-【症状】
-发热重，咽喉红肿，痰涕黄稠
+【病机】风热之邪侵袭肺卫，卫气失和，肺失清肃
+【症状】发热重，咽喉红肿，痰涕黄稠
 【脉象】
 浮脉（表）：波速快
-【标准方】
-银翘散</t>
+【标准方】银翘散</t>
         </is>
       </c>
     </row>
@@ -791,14 +782,11 @@
       <c r="E5" s="26" t="inlineStr">
         <is>
           <t>温燥证
-【病机】
-初秋燥热之邪侵袭肺卫，肺失清润
-【症状】
-发热恶风，口鼻干燥、咽干口渴、干咳少痰，痰涕黄稠
+【病机】初秋燥热之邪侵袭肺卫，肺失清润
+【症状】发热恶风，口鼻干燥、咽干口渴、干咳少痰，痰涕黄稠
 【脉象】
 浮脉（表）：波速快，波宽窄
-【标准方】
-桑杏汤</t>
+【标准方】桑杏汤</t>
         </is>
       </c>
     </row>
@@ -826,14 +814,11 @@
       <c r="E6" s="26" t="inlineStr">
         <is>
           <t>凉燥证
-【病机】
-深秋寒气渐生，燥邪兼风寒侵袭肺卫
-【症状】
-恶寒发热、鼻塞流清涕、干咳少痰、咽干唇燥、皮肤干燥
+【病机】深秋寒气渐生，燥邪兼风寒侵袭肺卫
+【症状】恶寒发热、鼻塞流清涕、干咳少痰、咽干唇燥、皮肤干燥
 【脉象】
 浮脉（表）：波速慢，波宽窄
-【标准方】
-杏苏散</t>
+【标准方】杏苏散</t>
         </is>
       </c>
     </row>
@@ -861,14 +846,11 @@
       <c r="E7" s="26" t="inlineStr">
         <is>
           <t>行痹（风痹）
-【病机】
-风寒湿邪侵袭经络，以风邪偏盛为主。风性善行、走窜不定。
-【症状】
-肢体关节酸痛，疼痛游走不定，窜走周身。
+【病机】风寒湿邪侵袭经络，以风邪偏盛为主。风性善行、走窜不定。
+【症状】肢体关节酸痛，疼痛游走不定，窜走周身。
 【脉象】
 浮脉（表）：波峰高（剧烈），波速慢（轻微），波宽宽（轻微）
-【标准方】
-防风汤</t>
+【标准方】防风汤</t>
         </is>
       </c>
     </row>
@@ -896,14 +878,11 @@
       <c r="E8" s="26" t="inlineStr">
         <is>
           <t>痛痹（寒痹）
-【病机】
-风寒湿邪痹阻经络，寒邪偏盛。寒主收引、凝滞，气血不通则疼痛剧烈。
-【症状】
-肢体关节疼痛剧烈、固定不移；遇寒加重、得温痛减；关节屈伸不利，局部怕冷
+【病机】风寒湿邪痹阻经络，寒邪偏盛。寒主收引、凝滞，气血不通则疼痛剧烈。
+【症状】肢体关节疼痛剧烈、固定不移；遇寒加重、得温痛减；关节屈伸不利，局部怕冷
 【脉象】
 浮脉（表）：波峰高（轻微），波速慢（剧烈），波宽宽（轻微）
-【标准方】
-乌头汤</t>
+【标准方】乌头汤</t>
         </is>
       </c>
     </row>
@@ -931,15 +910,12 @@
       <c r="E9" s="26" t="inlineStr">
         <is>
           <t>着痹（湿痹）
-【病机】
-风寒湿邪侵袭，湿邪偏盛；湿性重浊、黏滞，阻滞经络、困遏气机。
-【症状】
-关节沉重酸痛、重着如裹；痛处固定，肌肤麻木、肢体困重；关节肿胀、屈伸不利
+【病机】风寒湿邪侵袭，湿邪偏盛；湿性重浊、黏滞，阻滞经络、困遏气机。
+【症状】关节沉重酸痛、重着如裹；痛处固定，肌肤麻木、肢体困重；关节肿胀、屈伸不利
 阴雨潮湿天气加重
 【脉象】
 浮脉（表）：波峰高（轻微），波速慢（轻微），波宽宽（剧烈）
-【标准方】
-薏苡仁汤</t>
+【标准方】薏苡仁汤</t>
         </is>
       </c>
     </row>
@@ -967,14 +943,11 @@
       <c r="E10" s="26" t="inlineStr">
         <is>
           <t>热痹
-【病机】
-风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
-【症状】
-关节红肿灼热、疼痛剧烈；触之发热、拒按，得冷稍舒；发热、口渴、烦躁；肢体屈伸不利。
+【病机】风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
+【症状】关节红肿灼热、疼痛剧烈；触之发热、拒按，得冷稍舒；发热、口渴、烦躁；肢体屈伸不利。
 【脉象】
 浮脉（表）：波峰高（轻微），波速快（剧烈），波宽宽（轻微）
-【标准方】
-白虎桂枝汤</t>
+【标准方】白虎桂枝汤</t>
         </is>
       </c>
     </row>
@@ -1002,14 +975,11 @@
       <c r="E11" s="26" t="inlineStr">
         <is>
           <t>卫气虚
-【病机】
-素体虚弱、久病耗伤肺气，卫气不固、腠理疏松、防御固摄功能减退。
-【症状】
-自汗：不活动也出汗，动则更甚；易感冒：怕风畏冷、不耐风寒，稍受凉即感冒；面色㿠白、气短乏力、神疲懒言；皮肤腠理疏松、常畏风
+【病机】素体虚弱、久病耗伤肺气，卫气不固、腠理疏松、防御固摄功能减退。
+【症状】自汗：不活动也出汗，动则更甚；易感冒：怕风畏冷、不耐风寒，稍受凉即感冒；面色㿠白、气短乏力、神疲懒言；皮肤腠理疏松、常畏风
 【脉象】
 浮脉（表）：波峰低
-【标准方】
-玉屏风散</t>
+【标准方】玉屏风散</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1007,11 @@
       <c r="E12" s="26" t="inlineStr">
         <is>
           <t>肺热壅盛
-【病机】
-邪热壅滞于肺，肺失宣降，气机闭塞，热盛气逆
-【症状】
-咳嗽气粗、喘促胸闷；痰黄黏稠、不易咳出；发热、口渴咽痛；鼻翼煽动，大便偏干，小便黄。
+【病机】邪热壅滞于肺，肺失宣降，气机闭塞，热盛气逆
+【症状】咳嗽气粗、喘促胸闷；痰黄黏稠、不易咳出；发热、口渴咽痛；鼻翼煽动，大便偏干，小便黄。
 【脉象】
 右寸（肺）：波速快
-【标准方】
-麻杏石甘汤</t>
+【标准方】麻杏石甘汤</t>
         </is>
       </c>
     </row>
@@ -1072,14 +1039,11 @@
       <c r="E13" s="26" t="inlineStr">
         <is>
           <t>痰湿阻肺
-【病机】
-脾失健运，痰湿内生，上壅于肺，肺失宣降。
-【症状】
-咳嗽痰多，色白黏稠、量多易咯；胸闷、气喘、喉间痰鸣；肢体困重，口淡不渴
+【病机】脾失健运，痰湿内生，上壅于肺，肺失宣降。
+【症状】咳嗽痰多，色白黏稠、量多易咯；胸闷、气喘、喉间痰鸣；肢体困重，口淡不渴
 【脉象】
 右寸（肺）：波宽宽
-【标准方】
-二陈汤</t>
+【标准方】二陈汤</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1071,11 @@
       <c r="E14" s="26" t="inlineStr">
         <is>
           <t>痰热壅肺
-【病机】
-邪热入里，灼津成痰、痰热互结，壅遏肺气，肺失宣降。
-【症状】
-咳嗽气喘，痰多黄稠、黏稠难咯；胸闷胸痛，甚则鼻翼煽动；发热口渴、烦躁、大便干结、小便黄
+【病机】邪热入里，灼津成痰、痰热互结，壅遏肺气，肺失宣降。
+【症状】咳嗽气喘，痰多黄稠、黏稠难咯；胸闷胸痛，甚则鼻翼煽动；发热口渴、烦躁、大便干结、小便黄
 【脉象】
 右寸（肺）：波速快，波宽宽
-【标准方】
-清气化痰丸</t>
+【标准方】清气化痰丸</t>
         </is>
       </c>
     </row>
@@ -1142,14 +1103,11 @@
       <c r="E15" s="26" t="inlineStr">
         <is>
           <t>肺气虚
-【病机】
-肺气不足，宣降无力，卫外不固。
-【症状】
-咳喘无力，气短懒言，动则加重；语声低微、少气乏力；自汗、怕风、易感冒；痰液清稀、量少
+【病机】肺气不足，宣降无力，卫外不固。
+【症状】咳喘无力，气短懒言，动则加重；语声低微、少气乏力；自汗、怕风、易感冒；痰液清稀、量少
 【脉象】
 右寸（肺）：波峰低
-【标准方】
-补肺汤</t>
+【标准方】补肺汤</t>
         </is>
       </c>
     </row>
@@ -1177,14 +1135,11 @@
       <c r="E16" s="26" t="inlineStr">
         <is>
           <t>肺阴虚
-【病机】
-肺阴亏虚，虚火内生，肺失滋润、清肃无权。
-【症状】
-干咳无痰，或痰少黏稠难咯；咽干口燥、声音嘶哑；潮热盗汗、五心烦热；颧红、形体消瘦
+【病机】肺阴亏虚，虚火内生，肺失滋润、清肃无权。
+【症状】干咳无痰，或痰少黏稠难咯；咽干口燥、声音嘶哑；潮热盗汗、五心烦热；颧红、形体消瘦
 【脉象】
 右寸（肺）：波速快，波宽窄，
-【标准方】
-沙参麦冬汤</t>
+【标准方】沙参麦冬汤</t>
         </is>
       </c>
     </row>
@@ -1212,14 +1167,11 @@
       <c r="E17" s="26" t="inlineStr">
         <is>
           <t>心阳虚
-【病机】
-心阳不足，温煦、鼓动无力，虚寒内生。
-【症状】
-心悸怔忡，心慌不安；胸闷气短、遇寒加重；畏寒怕冷、四肢不温；面色㿠白，精神疲乏，自汗
+【病机】心阳不足，温煦、鼓动无力，虚寒内生。
+【症状】心悸怔忡，心慌不安；胸闷气短、遇寒加重；畏寒怕冷、四肢不温；面色㿠白，精神疲乏，自汗
 【脉象】
 左寸（心）：波峰低，波速慢
-【标准方】
-桂枝甘草汤</t>
+【标准方】桂枝甘草汤</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1199,11 @@
       <c r="E18" s="26" t="inlineStr">
         <is>
           <t>心阴虚
-【病机】
-心阴亏虚，心神失养，虚火内扰。
-【症状】
-心悸怔忡，心慌不安；心烦失眠、多梦易醒；五心烦热、潮热盗汗；口干咽燥、面色颧红；
+【病机】心阴亏虚，心神失养，虚火内扰。
+【症状】心悸怔忡，心慌不安；心烦失眠、多梦易醒；五心烦热、潮热盗汗；口干咽燥、面色颧红；
 【脉象】
 左寸（心）：波线细，波速快，波宽窄
-【标准方】
-天王补心丹</t>
+【标准方】天王补心丹</t>
         </is>
       </c>
     </row>
@@ -1282,14 +1231,11 @@
       <c r="E19" s="26" t="inlineStr">
         <is>
           <t>心气虚
-【病机】
-心气不足，鼓动无力，心神失养。
-【症状】
-心悸怔忡，活动后加重；气短、胸闷、精神疲倦；自汗，面色淡白；
+【病机】心气不足，鼓动无力，心神失养。
+【症状】心悸怔忡，活动后加重；气短、胸闷、精神疲倦；自汗，面色淡白；
 【脉象】
 左寸（心）：波峰低
-【标准方】
-养心汤</t>
+【标准方】养心汤</t>
         </is>
       </c>
     </row>
@@ -1317,14 +1263,11 @@
       <c r="E20" s="26" t="inlineStr">
         <is>
           <t>心火亢盛
-【病机】
-心火内炽，火热扰心、灼伤脉络、下移小肠。
-【症状】
-心胸烦热、心悸失眠、烦躁易怒；口舌生疮、舌尖红赤疼痛；口干口苦、面红目赤；小便短赤、灼热涩痛；
+【病机】心火内炽，火热扰心、灼伤脉络、下移小肠。
+【症状】心胸烦热、心悸失眠、烦躁易怒；口舌生疮、舌尖红赤疼痛；口干口苦、面红目赤；小便短赤、灼热涩痛；
 【脉象】
 左寸（心）：波速快
-【标准方】
-导赤散</t>
+【标准方】导赤散</t>
         </is>
       </c>
     </row>
@@ -1352,14 +1295,11 @@
       <c r="E21" s="26" t="inlineStr">
         <is>
           <t>痰迷心窍
-【病机】
-痰湿浊邪蒙蔽心窍，神明失主，多由情志郁结、脾失健运、痰浊内生，上蒙心神所致。
-【症状】
-神志痴呆、精神抑郁、表情淡漠；喃喃自语、举止失常、昏不知人；喉中痰鸣、胸闷痰多、意识模糊；甚则突然昏仆、不省人事；
+【病机】痰湿浊邪蒙蔽心窍，神明失主，多由情志郁结、脾失健运、痰浊内生，上蒙心神所致。
+【症状】神志痴呆、精神抑郁、表情淡漠；喃喃自语、举止失常、昏不知人；喉中痰鸣、胸闷痰多、意识模糊；甚则突然昏仆、不省人事；
 【脉象】
 左寸（心）：波宽宽
-【标准方】
-涤痰汤</t>
+【标准方】涤痰汤</t>
         </is>
       </c>
     </row>
@@ -1387,14 +1327,11 @@
       <c r="E22" s="26" t="inlineStr">
         <is>
           <t>痰火扰心
-【病机】
-痰浊郁而化火，痰火互结、上扰心神，神明躁动不宁。
-【症状】
-心烦失眠、躁扰不宁、狂躁易怒；多梦易惊、甚至胡言乱语、哭笑无常；胸闷痞满、口苦、痰多黄稠；
+【病机】痰浊郁而化火，痰火互结、上扰心神，神明躁动不宁。
+【症状】心烦失眠、躁扰不宁、狂躁易怒；多梦易惊、甚至胡言乱语、哭笑无常；胸闷痞满、口苦、痰多黄稠；
 【脉象】
 左寸（心）：波速快，波宽宽
-【标准方】
-黄连温胆汤</t>
+【标准方】黄连温胆汤</t>
         </is>
       </c>
     </row>
@@ -1422,14 +1359,11 @@
       <c r="E23" s="26" t="inlineStr">
         <is>
           <t>寒凝心脉
-【病机】
-素体阳虚，阴寒凝滞，寒邪痹阻心脉、胸阳不振，心脉拘急不通而痛。
-【症状】
-猝然胸痛、痛势剧烈、遇寒加重、得温痛减；胸闷气短、心悸怔忡；畏寒肢冷、面色苍白、唇甲青紫；
+【病机】素体阳虚，阴寒凝滞，寒邪痹阻心脉、胸阳不振，心脉拘急不通而痛。
+【症状】猝然胸痛、痛势剧烈、遇寒加重、得温痛减；胸闷气短、心悸怔忡；畏寒肢冷、面色苍白、唇甲青紫；
 【脉象】
 左寸（心）：波速慢
-【标准方】
-当归四逆汤</t>
+【标准方】当归四逆汤</t>
         </is>
       </c>
     </row>
@@ -1457,14 +1391,11 @@
       <c r="E24" s="26" t="inlineStr">
         <is>
           <t>肝气郁结
-【病机】
-情志不遂，肝失疏泄，气机郁滞、经脉不畅。
-【症状】
-胸胁、乳房、少腹胀痛走窜；情绪抑郁、易怒、善太息；咽部异物感（梅核气）、胸闷嗳气；女子月经不调、痛经；
+【病机】情志不遂，肝失疏泄，气机郁滞、经脉不畅。
+【症状】胸胁、乳房、少腹胀痛走窜；情绪抑郁、易怒、善太息；咽部异物感（梅核气）、胸闷嗳气；女子月经不调、痛经；
 【脉象】
 左关（肝胆）：波峰高
-【标准方】
-柴胡疏肝散</t>
+【标准方】柴胡疏肝散</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1423,11 @@
       <c r="E25" s="26" t="inlineStr">
         <is>
           <t>肝血虚
-【病机】
-肝血不足，筋脉、目、爪甲、心神失于濡养。
-【症状】
-头晕眼花、视力减退、视物模糊；爪甲干枯脆薄，肢体麻木、筋脉拘挛；面色淡白或萎黄，唇舌色淡；女子月经量少、色淡，甚则闭经；失眠多梦、易惊
+【病机】肝血不足，筋脉、目、爪甲、心神失于濡养。
+【症状】头晕眼花、视力减退、视物模糊；爪甲干枯脆薄，肢体麻木、筋脉拘挛；面色淡白或萎黄，唇舌色淡；女子月经量少、色淡，甚则闭经；失眠多梦、易惊
 【脉象】
 左关（肝胆）：波线细
-【标准方】
-四物汤</t>
+【标准方】四物汤</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1455,11 @@
       <c r="E26" s="26" t="inlineStr">
         <is>
           <t>肝火上炎
-【病机】
-肝郁化火、暴怒伤肝，肝火炽盛、气火上逆，属实热证。
-【症状】
-头晕胀痛、面红目赤、急躁易怒；口苦口干、耳鸣耳聋、胁肋灼痛；失眠多梦、甚至狂躁；吐血、衄血；
+【病机】肝郁化火、暴怒伤肝，肝火炽盛、气火上逆，属实热证。
+【症状】头晕胀痛、面红目赤、急躁易怒；口苦口干、耳鸣耳聋、胁肋灼痛；失眠多梦、甚至狂躁；吐血、衄血；
 【脉象】
 左关（肝胆）：波速快
-【标准方】
-龙胆泻肝汤</t>
+【标准方】龙胆泻肝汤</t>
         </is>
       </c>
     </row>
@@ -1562,14 +1487,11 @@
       <c r="E27" s="26" t="inlineStr">
         <is>
           <t>寒滞肝脉
-【病机】
-外感寒邪、凝滞肝经，肝脉拘急、气血阻滞、阳气被遏，属实寒证。
-【症状】
-少腹冷痛、睾丸坠胀冷痛、疝气痛；巅顶头痛、畏寒喜暖、得温痛减、遇寒加重；四肢厥冷、面色青白；
+【病机】外感寒邪、凝滞肝经，肝脉拘急、气血阻滞、阳气被遏，属实寒证。
+【症状】少腹冷痛、睾丸坠胀冷痛、疝气痛；巅顶头痛、畏寒喜暖、得温痛减、遇寒加重；四肢厥冷、面色青白；
 【脉象】
 左关（肝胆）：波速慢
-【标准方】
-暖肝煎</t>
+【标准方】暖肝煎</t>
         </is>
       </c>
     </row>
@@ -1597,14 +1519,11 @@
       <c r="E28" s="26" t="inlineStr">
         <is>
           <t>肝阴虚
-【病机】
-情志化火、久病耗伤，肝阴不足、虚火内生、头目筋脉失养。
-【症状】
-头晕耳鸣、两目干涩、视物昏花；胁肋隐隐灼痛、五心烦热；潮热盗汗、口燥咽干、面部烘热；手足蠕动、筋脉拘急；
+【病机】情志化火、久病耗伤，肝阴不足、虚火内生、头目筋脉失养。
+【症状】头晕耳鸣、两目干涩、视物昏花；胁肋隐隐灼痛、五心烦热；潮热盗汗、口燥咽干、面部烘热；手足蠕动、筋脉拘急；
 【脉象】
 左关（肝胆）：波线细，波速快，波宽窄
-【标准方】
-一贯煎</t>
+【标准方】一贯煎</t>
         </is>
       </c>
     </row>
@@ -1632,14 +1551,11 @@
       <c r="E29" s="26" t="inlineStr">
         <is>
           <t>肝阳上亢
-【病机】
-肝肾阴虚，阴不制阳、肝阳升发太过、上扰头目，属本虚标实。
-【症状】
-眩晕耳鸣、头目胀痛、面红目赤；急躁易怒、失眠多梦、腰膝酸软；头重脚轻、步履不稳
+【病机】肝肾阴虚，阴不制阳、肝阳升发太过、上扰头目，属本虚标实。
+【症状】眩晕耳鸣、头目胀痛、面红目赤；急躁易怒、失眠多梦、腰膝酸软；头重脚轻、步履不稳
 【脉象】
 左关（肝胆）：波峰高，波速快
-【标准方】
-钩藤散</t>
+【标准方】钩藤散</t>
         </is>
       </c>
     </row>
@@ -1667,14 +1583,11 @@
       <c r="E30" s="26" t="inlineStr">
         <is>
           <t>脾气虚
-【病机】
-饮食劳倦、久病耗伤，脾失健运、中气不足、运化失职。
-【症状】
-食少纳呆、脘腹胀满，饭后尤甚；神疲乏力、少气懒言、肢体倦怠；面色萎黄、形体消瘦或浮肿；大便溏薄
+【病机】饮食劳倦、久病耗伤，脾失健运、中气不足、运化失职。
+【症状】食少纳呆、脘腹胀满，饭后尤甚；神疲乏力、少气懒言、肢体倦怠；面色萎黄、形体消瘦或浮肿；大便溏薄
 【脉象】
 右关（脾胃，大小肠）：波峰低
-【标准方】
-四君子汤</t>
+【标准方】四君子汤</t>
         </is>
       </c>
     </row>
@@ -1702,14 +1615,11 @@
       <c r="E31" s="26" t="inlineStr">
         <is>
           <t>湿盛困脾
-【病机】
-外感湿邪、或嗜食生冷肥甘，湿邪壅滞、脾阳被困、运化失司，属实证。
-【症状】
-脘腹痞闷、食少纳呆；恶心欲呕、口中黏腻、口淡不渴；头身困重、四肢酸楚、困倦嗜睡；大便溏稀不爽
+【病机】外感湿邪、或嗜食生冷肥甘，湿邪壅滞、脾阳被困、运化失司，属实证。
+【症状】脘腹痞闷、食少纳呆；恶心欲呕、口中黏腻、口淡不渴；头身困重、四肢酸楚、困倦嗜睡；大便溏稀不爽
 【脉象】
 右关（脾胃，大小肠）：波宽宽
-【标准方】
-平胃散</t>
+【标准方】平胃散</t>
         </is>
       </c>
     </row>
@@ -1737,14 +1647,11 @@
       <c r="E32" s="26" t="inlineStr">
         <is>
           <t>脾虚湿盛
-【病机】
-脾气本虚，运化无力，水湿内生，湿浊内停
-【症状】
-食少纳呆，脘腹痞闷，饭后胀甚；神疲乏力、少气懒言、四肢困重；大便溏薄、或泄泻、黏滞不爽；面色萎黄，或肢体浮肿、带下量多清稀
+【病机】脾气本虚，运化无力，水湿内生，湿浊内停
+【症状】食少纳呆，脘腹痞闷，饭后胀甚；神疲乏力、少气懒言、四肢困重；大便溏薄、或泄泻、黏滞不爽；面色萎黄，或肢体浮肿、带下量多清稀
 【脉象】
 右关（脾胃，大小肠）：波峰低，波宽宽
-【标准方】
-参苓白术散</t>
+【标准方】参苓白术散</t>
         </is>
       </c>
     </row>
@@ -1772,14 +1679,11 @@
       <c r="E33" s="26" t="inlineStr">
         <is>
           <t>脾阳虚
-【病机】
-脾气久虚，脾阳不足、虚寒内生、运化腐熟无权。
-【症状】
-食少纳呆、脘腹冷痛，喜温喜按；大便清稀溏薄，甚至完谷不化；畏寒肢冷、四肢不温、神疲乏力；口淡不渴、面色㿠白或萎黄；或肢体浮肿、白带清稀量多
+【病机】脾气久虚，脾阳不足、虚寒内生、运化腐熟无权。
+【症状】食少纳呆、脘腹冷痛，喜温喜按；大便清稀溏薄，甚至完谷不化；畏寒肢冷、四肢不温、神疲乏力；口淡不渴、面色㿠白或萎黄；或肢体浮肿、白带清稀量多
 【脉象】
 右关（脾胃，大小肠）：波峰低，波速慢，波宽宽
-【标准方】
-理中丸</t>
+【标准方】理中丸</t>
         </is>
       </c>
     </row>
@@ -1807,15 +1711,12 @@
       <c r="E34" s="26" t="inlineStr">
         <is>
           <t>肾阴虚
-【病机】
-久病耗伤、房劳过度、过服温燥，肾阴亏虚、虚火内生、失于滋养。
-【症状】
-腰膝酸痛、眩晕耳鸣、健忘；潮热盗汗、五心烦热、口燥咽干；男子遗精早泄，女子经少、闭经或崩漏；形体消瘦、失眠多梦
+【病机】久病耗伤、房劳过度、过服温燥，肾阴亏虚、虚火内生、失于滋养。
+【症状】腰膝酸痛、眩晕耳鸣、健忘；潮热盗汗、五心烦热、口燥咽干；男子遗精早泄，女子经少、闭经或崩漏；形体消瘦、失眠多梦
 【脉象】
 左尺（肾阴）：波线细，波宽窄
 右尺（肾阳）：波速快
-【标准方】
-六味地黄丸</t>
+【标准方】六味地黄丸</t>
         </is>
       </c>
     </row>
@@ -1843,15 +1744,12 @@
       <c r="E35" s="26" t="inlineStr">
         <is>
           <t>肾阳虚
-【病机】
-年老肾亏、久病伤阳、房劳耗损，肾阳亏虚、命门火衰、温煦气化无权。
-【症状】
-腰膝冷痛、酸软无力；畏寒肢冷，尤以下肢为甚；精神萎靡、面色㿠白或黧黑；小便清长、夜尿多、遗尿；男子阳痿早泄，女子宫寒不孕、带下清稀；大便久泄不止、完谷不化、五更泄泻
+【病机】年老肾亏、久病伤阳、房劳耗损，肾阳亏虚、命门火衰、温煦气化无权。
+【症状】腰膝冷痛、酸软无力；畏寒肢冷，尤以下肢为甚；精神萎靡、面色㿠白或黧黑；小便清长、夜尿多、遗尿；男子阳痿早泄，女子宫寒不孕、带下清稀；大便久泄不止、完谷不化、五更泄泻
 【脉象】
 左尺（肾阴）：波宽宽
 右尺（肾阳）：波峰低，波速慢
-【标准方】
-金匮肾气丸</t>
+【标准方】金匮肾气丸</t>
         </is>
       </c>
     </row>
@@ -1879,15 +1777,12 @@
       <c r="E36" s="26" t="inlineStr">
         <is>
           <t>肾气不固
-【病机】
-久病劳损、年老体弱、房事不节，肾气亏虚、封藏固摄无权，偏虚证、无明显寒热。
-【症状】
-腰膝酸软、神疲乏力，耳鸣；小便频数清长、夜尿多、遗尿、小便失禁；男子：滑精、早泄；女子：带下清稀量多、胎动易滑；
+【病机】久病劳损、年老体弱、房事不节，肾气亏虚、封藏固摄无权，偏虚证、无明显寒热。
+【症状】腰膝酸软、神疲乏力，耳鸣；小便频数清长、夜尿多、遗尿、小便失禁；男子：滑精、早泄；女子：带下清稀量多、胎动易滑；
 【脉象】
 左尺（肾阴）：波宽宽
 右尺（肾阳）：波峰低
-【标准方】
-金锁固精丸</t>
+【标准方】金锁固精丸</t>
         </is>
       </c>
     </row>
@@ -1915,16 +1810,13 @@
       <c r="E37" s="26" t="inlineStr">
         <is>
           <t>肾精不足
-【病机】
-先天禀赋不足、后天耗伤太过、久病及肾、房劳过度，肾精亏少，不能充养骨骼、脑髓、生殖之本。
-【症状】
-小儿五迟五软：立迟、行迟、语迟、发迟、齿迟；囟门迟闭、智力低下、身材矮小
+【病机】先天禀赋不足、后天耗伤太过、久病及肾、房劳过度，肾精亏少，不能充养骨骼、脑髓、生殖之本。
+【症状】小儿五迟五软：立迟、行迟、语迟、发迟、齿迟；囟门迟闭、智力低下、身材矮小
 成人脑髓失养：头晕耳鸣、健忘失眠、精神迟钝；早衰特征：发脱齿摇、须发早白；骨骼失养：腰膝酸软、足痿无力生殖亏虚：男子精少不育；女子经闭、不孕
 【脉象】
 左尺（肾阴）：波线细
 右尺（肾阳）：波峰低
-【标准方】
-左归丸</t>
+【标准方】左归丸</t>
         </is>
       </c>
     </row>
@@ -1952,16 +1844,13 @@
       <c r="E38" s="26" t="inlineStr">
         <is>
           <t>肾虚水泛
-【病机】
-肾阳虚衰，气化无权，水湿内停，泛溢肌肤
-【症状】
-周身浮肿，腰以下肿甚，按之凹陷不起；腰膝酸软冷痛，畏寒肢冷；小便短少，或小便不利；心悸气短、喘咳痰稀如水；面色㿠白或灰黯
+【病机】肾阳虚衰，气化无权，水湿内停，泛溢肌肤
+【症状】周身浮肿，腰以下肿甚，按之凹陷不起；腰膝酸软冷痛，畏寒肢冷；小便短少，或小便不利；心悸气短、喘咳痰稀如水；面色㿠白或灰黯
 【脉象】
 左尺（肾阴）：波宽宽
 右尺（肾阳）：波峰低，波速慢
 右关（脾胃，大小肠）：波宽宽
-【标准方】
-真武汤</t>
+【标准方】真武汤</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1878,14 @@
       <c r="E39" s="26" t="inlineStr">
         <is>
           <t>气分热盛
-【病机】
-外感温热病邪入里，邪热炽盛、入居气分、里热蒸腾、正邪剧争，属实热证。
-【症状】
-大热：全身壮热、不恶寒反恶热；大汗：热迫津泄、大汗出；大渴：口大渴、喜冷饮；脉洪大
+【病机】外感温热病邪入里，邪热炽盛、入居气分、里热蒸腾、正邪剧争，属实热证。
+【症状】大热：全身壮热、不恶寒反恶热；大汗：热迫津泄、大汗出；大渴：口大渴、喜冷饮；脉洪大
 【脉象】
 浮脉（表）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
 左寸（心）：波峰高（轻微），波速快（轻微），波宽窄（轻微）
 右寸（肺）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
 右关（脾胃，大小肠）：波峰高（剧烈），波速快（剧烈），波宽窄（剧烈）
-【标准方】
-白虎汤</t>
+【标准方】白虎汤</t>
         </is>
       </c>
     </row>
@@ -2027,15 +1913,12 @@
       <c r="E40" s="26" t="inlineStr">
         <is>
           <t>心脾两虚
-【病机】
-思虑过度、劳倦伤脾、久病体虚、失血过多；脾气虚弱，气血生化不足，心血亏虚、心神失养，属气血两虚、虚证。
-【症状】
-心悸怔忡、失眠多梦、健忘头晕；食欲不振、腹胀便溏、神疲乏力；面色萎黄或苍白、肢体倦怠；女子月经量少色淡、淋漓不尽
+【病机】思虑过度、劳倦伤脾、久病体虚、失血过多；脾气虚弱，气血生化不足，心血亏虚、心神失养，属气血两虚、虚证。
+【症状】心悸怔忡、失眠多梦、健忘头晕；食欲不振、腹胀便溏、神疲乏力；面色萎黄或苍白、肢体倦怠；女子月经量少色淡、淋漓不尽
 【脉象】
 左寸（心）：波线细
 右关（脾胃，大小肠）：波峰低
-【标准方】
-归脾汤</t>
+【标准方】归脾汤</t>
         </is>
       </c>
     </row>
@@ -2063,16 +1946,13 @@
       <c r="E41" s="26" t="inlineStr">
         <is>
           <t>心肾不交
-【病机】
-肾阴不足，不能上滋心火；心火偏亢，不能下温肾水，水火失济、阴阳失调。多由劳神过度、久病耗阴、情志郁而化火所致，多属阴虚火旺。
-【症状】
-心火亢于上：心烦失眠、多梦易醒、心悸怔忡、口舌生疮；肾阴亏于下：腰膝酸软、眩晕耳鸣、潮热盗汗、五心烦热；失眠多梦 ， 腰膝酸软 ， 夜寐不安
+【病机】肾阴不足，不能上滋心火；心火偏亢，不能下温肾水，水火失济、阴阳失调。多由劳神过度、久病耗阴、情志郁而化火所致，多属阴虚火旺。
+【症状】心火亢于上：心烦失眠、多梦易醒、心悸怔忡、口舌生疮；肾阴亏于下：腰膝酸软、眩晕耳鸣、潮热盗汗、五心烦热；失眠多梦 ， 腰膝酸软 ， 夜寐不安
 【脉象】
 左寸（心）：波速快
 左尺（肾阴）：波线细，波宽窄
 右尺（肾阳）：波速快
-【标准方】
-黄连阿胶汤</t>
+【标准方】黄连阿胶汤</t>
         </is>
       </c>
     </row>
@@ -2100,15 +1980,12 @@
       <c r="E42" s="26" t="inlineStr">
         <is>
           <t>肝脾不和（肝郁脾虚）
-【病机】
-情志不舒、肝气郁结，木旺克土；脾虚失运、肝气乘脾。
-【症状】
-胸胁胀痛、善太息、情绪抑郁易怒；脘腹胀满、嗳气食少；腹痛泄泻、泻后痛减；食欲不振、肠鸣矢气多
+【病机】情志不舒、肝气郁结，木旺克土；脾虚失运、肝气乘脾。
+【症状】胸胁胀痛、善太息、情绪抑郁易怒；脘腹胀满、嗳气食少；腹痛泄泻、泻后痛减；食欲不振、肠鸣矢气多
 【脉象】
 左关（肝胆）：波峰高
 右关（脾胃，大小肠）：波峰低
-【标准方】
-逍遥散</t>
+【标准方】逍遥散</t>
         </is>
       </c>
     </row>
@@ -2136,15 +2013,12 @@
       <c r="E43" s="26" t="inlineStr">
         <is>
           <t>肾不纳气
-【病机】
-久病咳喘、年老肾虚、劳伤肾气；肾气亏虚，下元不固，不能摄纳肺气，气浮于上。属虚喘、肺肾两虚，无明显实邪。
-【症状】
-喘促日久、呼多吸少、动则喘甚；气短不足以息、吸气浅表；腰膝酸软、神疲乏力；或自汗、语声低怯
+【病机】久病咳喘、年老肾虚、劳伤肾气；肾气亏虚，下元不固，不能摄纳肺气，气浮于上。属虚喘、肺肾两虚，无明显实邪。
+【症状】喘促日久、呼多吸少、动则喘甚；气短不足以息、吸气浅表；腰膝酸软、神疲乏力；或自汗、语声低怯
 【脉象】
 右寸（肺）：波峰低
 右尺（肾阳）：波峰低
-【标准方】
-人参蛤蚧散</t>
+【标准方】人参蛤蚧散</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2046,12 @@
       <c r="E44" s="26" t="inlineStr">
         <is>
           <t>外感风寒，内伤湿滞
-【病机】
-外感风寒之邪束表，内伤饮食湿浊阻滞中焦；表有风寒、里有湿滞
-【症状】
-外感风寒：恶寒发热、头痛身重、无汗、鼻塞流清涕；内伤湿滞：胸膈满闷、脘腹胀痛、恶心呕吐、肠鸣泄泻；怕冷发热 + 又吐又泻、身重胸闷
+【病机】外感风寒之邪束表，内伤饮食湿浊阻滞中焦；表有风寒、里有湿滞
+【症状】外感风寒：恶寒发热、头痛身重、无汗、鼻塞流清涕；内伤湿滞：胸膈满闷、脘腹胀痛、恶心呕吐、肠鸣泄泻；怕冷发热 + 又吐又泻、身重胸闷
 【脉象】
 浮脉（表）：波速慢
 右关（脾胃，大小肠）：波宽宽
-【标准方】
-藿香正气散</t>
+【标准方】藿香正气散</t>
         </is>
       </c>
     </row>
@@ -3032,12 +2903,9 @@
       <c r="E2" s="25" t="inlineStr">
         <is>
           <t>麻黄汤
-【出处】
-《伤寒论》
-【功效】
-发汗解表，宣肺平喘
-【主治】
-风寒表实证
+【出处】《伤寒论》
+【功效】发汗解表，宣肺平喘
+【主治】风寒表实证
 【组成】
 君：麻黄 三钱
 臣：桂枝 二钱
@@ -3074,12 +2942,9 @@
       <c r="E3" s="25" t="inlineStr">
         <is>
           <t>桂枝汤
-【出处】
-《伤寒论》
-【功效】
-解肌发表，调和营卫
-【主治】
-风寒表虚证
+【出处】《伤寒论》
+【功效】解肌发表，调和营卫
+【主治】风寒表虚证
 【组成】
 君：桂枝 三钱
 臣：白芍 三钱
@@ -3115,12 +2980,9 @@
       <c r="E4" s="25" t="inlineStr">
         <is>
           <t>银翘散
-【出处】
-《温病条辩》
-【功效】
-辛凉透表，清热解毒
-【主治】
-风热表证
+【出处】《温病条辩》
+【功效】辛凉透表，清热解毒
+【主治】风热表证
 【组成】
 君：金银花 一两，连翘 一两
 臣：牛蒡子 六钱，荆芥四钱，薄荷 六钱，淡豆豉 五钱
@@ -3160,12 +3022,9 @@
       <c r="E5" s="25" t="inlineStr">
         <is>
           <t>桑杏汤
-【出处】
-《温病条辨》
-【功效】
-清宣温燥，润肺止咳
-【主治】
-温燥证
+【出处】《温病条辨》
+【功效】清宣温燥，润肺止咳
+【主治】温燥证
 【组成】
 君：桑叶 一钱五分，杏仁 二钱
 臣：沙参 一钱
@@ -3206,12 +3065,9 @@
       <c r="E6" s="25" t="inlineStr">
         <is>
           <t>杏苏散
-【出处】
-《温病条辨》
-【功效】
-轻宣凉燥，理肺化痰
-【主治】
-凉燥证
+【出处】《温病条辨》
+【功效】轻宣凉燥，理肺化痰
+【主治】凉燥证
 【组成】
 君：杏仁 三钱，苏叶 三钱
 臣：半夏 三钱，前胡 三钱，陈皮 三钱
@@ -3251,12 +3107,9 @@
       <c r="E7" s="25" t="inlineStr">
         <is>
           <t>防风汤
-【出处】
-《太平惠民和剂局方》
-【功效】
-祛风通络，散寒除湿
-【主治】
-行痹（风痹）
+【出处】《太平惠民和剂局方》
+【功效】祛风通络，散寒除湿
+【主治】行痹（风痹）
 【组成】
 君：防风 五钱
 臣：桂枝 三钱，秦艽 三钱
@@ -3297,12 +3150,9 @@
       <c r="E8" s="25" t="inlineStr">
         <is>
           <t>乌头汤
-【出处】
-《金匮要略》
-【功效】
-温经散寒，除湿止痛
-【主治】
-痛痹（寒痹）
+【出处】《金匮要略》
+【功效】温经散寒，除湿止痛
+【主治】痛痹（寒痹）
 【组成】
 君：乌头 二钱
 臣：麻黄 三钱
@@ -3341,12 +3191,9 @@
       <c r="E9" s="25" t="inlineStr">
         <is>
           <t>薏苡仁汤
-【出处】
-《太医院经验奇效良方大全》
-【功效】
-除湿通络，祛风散寒
-【主治】
-着痹（湿痹）
+【出处】《太医院经验奇效良方大全》
+【功效】除湿通络，祛风散寒
+【主治】着痹（湿痹）
 【组成】
 君：薏苡仁 一两
 臣：羌活 三钱，独活 三钱，麻黄 三钱，桂枝 三钱
@@ -3385,12 +3232,9 @@
       <c r="E10" s="25" t="inlineStr">
         <is>
           <t>白虎桂枝汤
-【出处】
-《金匮要略》
-【功效】
-清热通络，和营祛风
-【主治】
-热痹
+【出处】《金匮要略》
+【功效】清热通络，和营祛风
+【主治】热痹
 【组成】
 君：石膏 二两
 臣：知母 六钱
@@ -3428,12 +3272,9 @@
       <c r="E11" s="25" t="inlineStr">
         <is>
           <t>玉屏风散
-【出处】
-《究原方》
-【功效】
-益气固表，止汗御风
-【主治】
-卫气虚
+【出处】《究原方》
+【功效】益气固表，止汗御风
+【主治】卫气虚
 【组成】
 君：黄芪  一两
 臣：白术 一两
@@ -3470,12 +3311,9 @@
       <c r="E12" s="25" t="inlineStr">
         <is>
           <t>麻杏石甘汤
-【出处】
-《伤寒论》
-【功效】
-辛凉疏表，清肺平喘
-【主治】
-肺热壅盛
+【出处】《伤寒论》
+【功效】辛凉疏表，清肺平喘
+【主治】肺热壅盛
 【组成】
 君：麻黄 三钱
 臣：石膏 八钱
@@ -3513,12 +3351,9 @@
       <c r="E13" s="25" t="inlineStr">
         <is>
           <t>二陈汤
-【出处】
-《太平惠民和剂局方》
-【功效】
-燥湿化痰，理气和中
-【主治】
-痰湿阻肺
+【出处】《太平惠民和剂局方》
+【功效】燥湿化痰，理气和中
+【主治】痰湿阻肺
 【组成】
 君：半夏 五钱
 臣：陈皮 五钱
@@ -3556,12 +3391,9 @@
       <c r="E14" s="25" t="inlineStr">
         <is>
           <t>清气化痰丸
-【出处】
-《医方考》
-【功效】
-清热化痰，理气止咳
-【主治】
-痰热壅肺
+【出处】《医方考》
+【功效】清热化痰，理气止咳
+【主治】痰热壅肺
 【组成】
 君：胆南星 一两五钱
 臣：半夏 一两五钱，瓜蒌仁 一两，黄芩 一两
@@ -3602,12 +3434,9 @@
       <c r="E15" s="25" t="inlineStr">
         <is>
           <t>补肺汤
-【出处】
-《备急千金要方》
-【功效】
-补肺益气，止咳平喘
-【主治】
-肺气虚
+【出处】《备急千金要方》
+【功效】补肺益气，止咳平喘
+【主治】肺气虚
 【组成】
 君：人参 三钱，黄芪 五钱
 臣：熟地黄 五钱
@@ -3645,12 +3474,9 @@
       <c r="E16" s="25" t="inlineStr">
         <is>
           <t>沙参麦冬汤
-【出处】
-《温病条辩》
-【功效】
-清养肺胃，生津润燥
-【主治】
-肺阴虚
+【出处】《温病条辩》
+【功效】清养肺胃，生津润燥
+【主治】肺阴虚
 【组成】
 君：沙参 三钱，麦门冬 三钱
 臣：玉竹 二钱，天花粉 一钱五分
@@ -3689,12 +3515,9 @@
       <c r="E17" s="25" t="inlineStr">
         <is>
           <t>桂枝甘草汤
-【出处】
-《伤寒论》
-【功效】
-温补心阳，益气定悸
-【主治】
-心阳虚
+【出处】《伤寒论》
+【功效】温补心阳，益气定悸
+【主治】心阳虚
 【组成】
 君：桂枝 四钱
 臣：甘草 二钱
@@ -3730,12 +3553,9 @@
       <c r="E18" s="25" t="inlineStr">
         <is>
           <t>天王补心丹
-【出处】
-《金匮要略》
-【功效】
-滋阴养血，补心安神
-【主治】
-心阴虚
+【出处】《金匮要略》
+【功效】滋阴养血，补心安神
+【主治】心阴虚
 【组成】
 君：生地黄 四两
 臣：天门冬 一两，麦门冬 一两，酸枣仁 一两，柏子仁 一两，当归一两
@@ -3776,12 +3596,9 @@
       <c r="E19" s="25" t="inlineStr">
         <is>
           <t>养心汤
-【出处】
-《仁斋直指方论》
-【功效】
-益气补血，养心安神
-【主治】
-心气虚
+【出处】《仁斋直指方论》
+【功效】益气补血，养心安神
+【主治】心气虚
 【组成】
 君：黄芪 五钱，人参 三钱
 臣：当归 五钱，茯神 五钱，茯苓 五钱
@@ -3822,12 +3639,9 @@
       <c r="E20" s="25" t="inlineStr">
         <is>
           <t>导赤散
-【出处】
-《小儿药证直决》
-【功效】
-清心利水养阴
-【主治】
-心火亢盛
+【出处】《小儿药证直决》
+【功效】清心利水养阴
+【主治】心火亢盛
 【组成】
 君：生地黄 二钱，木通 二钱
 臣：竹叶 二钱
@@ -3865,12 +3679,9 @@
       <c r="E21" s="25" t="inlineStr">
         <is>
           <t>涤痰汤
-【出处】
-《太医院经验奇效良方大全》
-【功效】
-涤痰开窍，益气扶正
-【主治】
-痰迷心窍
+【出处】《太医院经验奇效良方大全》
+【功效】涤痰开窍，益气扶正
+【主治】痰迷心窍
 【组成】
 君：半夏 二钱五分，胆南星 二钱五分
 臣：枳实 二钱，陈皮 一分五钱
@@ -3911,12 +3722,9 @@
       <c r="E22" s="25" t="inlineStr">
         <is>
           <t>黄连温胆汤
-【出处】
-《备急千金要方》
-【功效】
-清热化痰，和中安神
-【主治】
-痰火扰心
+【出处】《备急千金要方》
+【功效】清热化痰，和中安神
+【主治】痰火扰心
 【组成】
 君：黄连 三钱
 臣：半夏 四钱，竹茹 五钱
@@ -3959,12 +3767,9 @@
       <c r="E23" s="25" t="inlineStr">
         <is>
           <t>当归四逆汤
-【出处】
-《伤寒论》
-【功效】
-温经散寒，养血通脉
-【主治】
-寒凝心脉
+【出处】《伤寒论》
+【功效】温经散寒，养血通脉
+【主治】寒凝心脉
 【组成】
 君：当归 四钱
 臣：桂枝 三钱，白芍 三钱
@@ -4004,14 +3809,10 @@
       <c r="E24" s="25" t="inlineStr">
         <is>
           <t>柴胡疏肝散
-【出处】
-《景岳全书》
-【功效】
-疏肝解郁，行气止痛
-【主治】
-肝气郁结
-【组成】
-君：柴胡 二钱
+【出处】《景岳全书》
+【功效】疏肝解郁，行气止痛
+【主治】肝气郁结
+【组成】君：柴胡 二钱
 臣：香附 一钱五分钱，川芎 一钱五分
 佐：陈皮 二钱，枳壳 一钱五分，白芍 一钱五分
 使：甘草 五分
@@ -4049,12 +3850,9 @@
       <c r="E25" s="25" t="inlineStr">
         <is>
           <t>四物汤
-【出处】
-《太平惠民和剂局方》
-【功效】
-补血调血
-【主治】
-肝血虚
+【出处】《太平惠民和剂局方》
+【功效】补血调血
+【主治】肝血虚
 【组成】
 君：熟地黄 四钱
 臣：当归 三钱
@@ -4092,12 +3890,9 @@
       <c r="E26" s="25" t="inlineStr">
         <is>
           <t>龙胆泻肝汤
-【出处】
-《兰室秘藏》
-【功效】
-清泻肝胆实火，清利肝经湿热
-【主治】
-肝火上炎
+【出处】《兰室秘藏》
+【功效】清泻肝胆实火，清利肝经湿热
+【主治】肝火上炎
 【组成】
 君：龙胆草 二钱
 臣：黄芩 三钱，栀子 三钱
@@ -4137,12 +3932,9 @@
       <c r="E27" s="25" t="inlineStr">
         <is>
           <t>暖肝煎
-【出处】
-《景岳全书》
-【功效】
-温补肝肾，行气散寒
-【主治】
-寒滞肝脉
+【出处】《景岳全书》
+【功效】温补肝肾，行气散寒
+【主治】寒滞肝脉
 【组成】
 君：肉桂 一钱，茴香 二钱
 臣：当归 二钱，枸杞子 三钱
@@ -4183,12 +3975,9 @@
       <c r="E28" s="25" t="inlineStr">
         <is>
           <t>一贯煎
-【出处】
-《柳州医话》
-【功效】
-滋阴疏肝
-【主治】
-肝阴虚
+【出处】《柳州医话》
+【功效】滋阴疏肝
+【主治】肝阴虚
 【组成】
 君：生地黄 一两
 臣：枸杞子 六钱，沙参 三钱，麦门冬 三钱，当归 三钱
@@ -4227,12 +4016,9 @@
       <c r="E29" s="25" t="inlineStr">
         <is>
           <t>钩藤散
-【出处】
-《普济本事方》
-【功效】
-平肝息风，清热化痰，益气养阴
-【主治】
-肝阳上亢
+【出处】《普济本事方》
+【功效】平肝息风，清热化痰，益气养阴
+【主治】肝阳上亢
 【组成】
 君：钩藤 三钱，菊花 三钱
 臣：防风 三钱，石膏 三钱
@@ -4273,12 +4059,9 @@
       <c r="E30" s="25" t="inlineStr">
         <is>
           <t>四君子汤
-【出处】
-《太平惠民和剂局方》
-【功效】
-益气健脾
-【主治】
-脾气虚
+【出处】《太平惠民和剂局方》
+【功效】益气健脾
+【主治】脾气虚
 【组成】
 君：人参 四钱
 臣：白术 三钱
@@ -4316,12 +4099,9 @@
       <c r="E31" s="25" t="inlineStr">
         <is>
           <t>平胃散
-【出处】
-《太平惠民和剂局方》
-【功效】
-燥湿运脾，行气和胃
-【主治】
-湿盛困脾
+【出处】《太平惠民和剂局方》
+【功效】燥湿运脾，行气和胃
+【主治】湿盛困脾
 【组成】
 君：苍术 三钱
 臣：厚朴 二钱
@@ -4359,12 +4139,9 @@
       <c r="E32" s="25" t="inlineStr">
         <is>
           <t>参苓白术散
-【出处】
-《太平惠民和剂局方》
-【功效】
-益气健脾，渗湿止泻
-【主治】
-脾虚湿盛
+【出处】《太平惠民和剂局方》
+【功效】益气健脾，渗湿止泻
+【主治】脾虚湿盛
 【组成】
 君：人参 五钱，茯苓 五钱，白术 五钱
 臣：山药 五钱，莲子 三钱，扁豆 三钱，薏苡仁 七钱
@@ -4403,12 +4180,9 @@
       <c r="E33" s="25" t="inlineStr">
         <is>
           <t>理中丸
-【出处】
-《伤寒论》
-【功效】
-温中祛寒，补气健脾
-【主治】
-脾阳虚
+【出处】《伤寒论》
+【功效】温中祛寒，补气健脾
+【主治】脾阳虚
 【组成】
 君：干姜 五钱
 臣：人参 五钱
@@ -4446,12 +4220,9 @@
       <c r="E34" s="25" t="inlineStr">
         <is>
           <t>六味地黄丸
-【出处】
-《金匮要略》
-【功效】
-滋阴补肾
-【主治】
-肾阴虚
+【出处】《金匮要略》
+【功效】滋阴补肾
+【主治】肾阴虚
 【组成】
 君：熟地黄 八钱
 臣：山茱萸 四钱，山药 四钱
@@ -4491,12 +4262,9 @@
       <c r="E35" s="25" t="inlineStr">
         <is>
           <t>金匮肾气丸
-【出处】
-《金匮要略》
-【功效】
-温补肾阳，化气行水
-【主治】
-肾阳虚
+【出处】《金匮要略》
+【功效】温补肾阳，化气行水
+【主治】肾阳虚
 【组成】
 君：附子 二钱，桂枝 三钱
 臣：熟地黄 一钱，山茱萸 四钱，山药 五钱
@@ -4533,12 +4301,9 @@
       <c r="E36" s="25" t="inlineStr">
         <is>
           <t>金锁固精丸
-【出处】
-《医方集解》
-【功效】
-补肾涩精，固摄肾气
-【主治】
-肾气不固
+【出处】《医方集解》
+【功效】补肾涩精，固摄肾气
+【主治】肾气不固
 【组成】
 君：蒺藜 五钱
 臣：芡实 五钱
@@ -4577,12 +4342,9 @@
       <c r="E37" s="25" t="inlineStr">
         <is>
           <t>左归丸
-【出处】
-《景岳全书》
-【功效】
-滋阴补肾，填精益髓
-【主治】
-肾精不足
+【出处】《景岳全书》
+【功效】滋阴补肾，填精益髓
+【主治】肾精不足
 【组成】
 君：熟地黄 八钱
 臣：龟板胶 四钱，鹿角胶 四钱，枸杞子 四钱，菟丝子 四钱
@@ -4620,13 +4382,10 @@
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>真武汤.txt
-【出处】
-《伤寒论》
-【功效】
-温阳利水
-【主治】
-肾虚水泛
+          <t>真武汤
+【出处】《伤寒论》
+【功效】温阳利水
+【主治】肾虚水泛
 【组成】
 君：附子 三钱
 臣：茯苓 三钱，白术 三钱
@@ -4665,12 +4424,9 @@
       <c r="E39" s="25" t="inlineStr">
         <is>
           <t>白虎汤
-【出处】
-《伤寒论》
-【功效】
-清热生津，辛寒清气
-【主治】
-气分热盛
+【出处】《伤寒论》
+【功效】清热生津，辛寒清气
+【主治】气分热盛
 【组成】
 君：石膏 二两
 臣：知母 六钱
@@ -4707,12 +4463,9 @@
       <c r="E40" s="25" t="inlineStr">
         <is>
           <t>归脾汤
-【出处】
-《严氏济生方》
-【功效】
-益气补血，健脾养心
-【主治】
-心脾两虚
+【出处】《严氏济生方》
+【功效】益气补血，健脾养心
+【主治】心脾两虚
 【组成】
 君：黄芪 一两，人参 五钱
 臣：龙眼 五钱，白术 五钱，当归 五钱，酸枣仁 六钱
@@ -4753,12 +4506,9 @@
       <c r="E41" s="25" t="inlineStr">
         <is>
           <t>黄连阿胶汤
-【出处】
-《伤寒论》
-【功效】
-滋阴降火，交通心肾
-【主治】
-心肾不交
+【出处】《伤寒论》
+【功效】滋阴降火，交通心肾
+【主治】心肾不交
 【组成】
 君：黄连 四钱
 臣：黄芩 三钱，白芍 三钱
@@ -4797,12 +4547,9 @@
       <c r="E42" s="25" t="inlineStr">
         <is>
           <t>逍遥散
-【出处】
-《太平惠民和剂局方》
-【功效】
-疏肝解郁，养血健脾
-【主治】
-肝脾不和（肝郁脾虚）
+【出处】《太平惠民和剂局方》
+【功效】疏肝解郁，养血健脾
+【主治】肝脾不和（肝郁脾虚）
 【组成】
 君：柴胡 三钱
 臣：当归 三钱，白芍 三钱
@@ -4842,12 +4589,9 @@
       <c r="E43" s="25" t="inlineStr">
         <is>
           <t>人参蛤蚧散
-【出处】
-《博济方》
-【功效】
-补肺益肾，纳气定喘，止咳化痰
-【主治】
-肾不纳气
+【出处】《博济方》
+【功效】补肺益肾，纳气定喘，止咳化痰
+【主治】肾不纳气
 【组成】
 君：蛤蚧 五钱，人参 四钱
 臣：知母 三钱，贝母 三钱，桑白皮 三钱
@@ -4887,12 +4631,9 @@
       <c r="E44" s="25" t="inlineStr">
         <is>
           <t>藿香正气散
-【出处】
-《太平惠民和剂局方》
-【功效】
-解表散寒，化湿和中，理气止呕
-【主治】
-外感风寒，内伤湿滞
+【出处】《太平惠民和剂局方》
+【功效】解表散寒，化湿和中，理气止呕
+【主治】外感风寒，内伤湿滞
 【组成】
 君：藿香 五钱
 臣：苏叶 三钱，白芷 三钱，半夏 四钱，厚朴 四钱
@@ -13613,16 +13354,11 @@
       <c r="H2" s="31" t="inlineStr">
         <is>
           <t>生姜
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归肺、脾、胃经
-【主治】
-解表散寒，温中止呕，解鱼蟹毒
-【释名】
-时珍曰：按：许慎《说文》：姜作䕬，云御湿之菜也。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归肺、脾、胃经。
+【主治】解表散寒，温中止呕，解鱼蟹毒。
+【释名】时珍曰：按：许慎《说文》：姜作䕬，云御湿之菜也。
 王安石《字说》云：姜能强御百邪，故谓之姜。初生嫩者，其尖微紫，名紫姜，或作子姜；宿根谓之母姜也。
 【发明】
 成无己曰︰姜、枣味辛、甘，专行脾之津液而和营卫。药中用之，不独专于发散也。
@@ -13677,19 +13413,13 @@
       <c r="H3" s="7" t="inlineStr">
         <is>
           <t>麻黄
-【气味】
-辛苦，温
-【毒性】
-无毒
-【归经】
-归肺、膀胱经
-【主治】
-发汗解表，宣肺平喘，利水消肿
-【释名】
-龙沙（《本经》）、卑相（《别录》）、卑盐（《别录》）。
+【气味】辛苦，温。
+【毒性】无毒。
+【归经】归肺、膀胱经。
+【主治】发汗解表，宣肺平喘，利水消肿。
+【释名】龙沙（《本经》）、卑相（《别录》）、卑盐（《别录》）。
 时珍曰：诸名殊不可解。或云其味麻，其色黄，未审然否？张揖《广雅》云：龙沙，麻黄也。狗骨，麻黄根也。不知何以分别如此？
-【发明】
-弘景曰︰麻黄疗伤寒，解肌第一药。
+【发明】弘景曰︰麻黄疗伤寒，解肌第一药。
 颂曰︰张仲景治伤寒，有麻黄汤及葛根汤、大小青龙汤，皆用麻黄。治肺痿上气，有射干麻黄汤、浓朴麻黄汤，皆大方也。
 杲曰︰轻可去实，麻黄、葛根之属是也。六淫有馀之邪，客于阳分皮毛之间，腠理闭拒，营卫气血不行，故谓之实。二药轻清成象，故可去之。麻黄微苦，其形中空，阴中之阳，入足太阳寒水之经。其经循背下行，本寒而又受外寒，故宜发汗，去皮毛气分寒邪，以泄表实。若过发则汗多亡阳，或饮食劳倦及杂病自汗表虚之证用之，则脱人元气，不可不禁。
 好古曰︰麻黄治卫实之药，桂枝治卫虚之药，二物虽为太阳证药，其实营卫药也。心主营为血，肺主卫为气。故麻黄为手太阴肺之剂，桂枝为手少阴心之剂。伤寒伤风而咳嗽，用麻黄、桂枝，即汤液之源也。
@@ -13741,16 +13471,11 @@
       <c r="H4" s="7" t="inlineStr">
         <is>
           <t>桂枝（桂）
-【气味】
-味辛、甘，性温
-【毒性】
-无毒
-【归经】
-归心、肺、膀胱经
-【主治】
-发汗解肌，温通经脉，助阳化气
-【释名】
-时珍曰︰按︰范成大《桂海志》云︰凡木叶心皆一纵理，独桂有两道如圭形，故字从圭。
+【气味】味辛、甘，性温。
+【毒性】无毒。
+【归经】归心、肺、膀胱经。
+【主治】发汗解肌，温通经脉，助阳化气。
+【释名】时珍曰︰按︰范成大《桂海志》云︰凡木叶心皆一纵理，独桂有两道如圭形，故字从圭。
 陆佃《埤雅》云︰桂犹圭也。宣导百药，为之先聘通使，如执圭之使也。《尔雅》谓之梫者，能侵害他木也。故《吕氏春秋》云︰桂枝之下无杂木。《雷公炮炙论》云︰桂钉木根，其木即死，是也。桂即牡桂之浓而辛烈者，牡桂即桂之薄而味淡者，《别录》不当重出，今并为一，而分目于下。
 【发明】
 宗奭曰︰桂甘、辛，大热。《素问》云︰辛甘发散为阳。故汉张仲景桂枝汤治伤寒表虚，皆须此药，正合辛甘发散之意。本草三种之桂，不用牡桂、菌桂者，此二种性只于温，不可以治风寒之病也。然《本经》只言桂，仲景又言桂枝者，取枝上皮也。
@@ -13804,16 +13529,11 @@
       <c r="H5" s="7" t="inlineStr">
         <is>
           <t>杏仁（杏）
-【气味】
-味苦，性温
-【毒性】
-有小毒
-【归经】
-归肺、大肠经
-【主治】
-止咳平喘，润肠通便
-【释名】
-时珍曰︰杏字篆文象子在木枝之形。或云从口及从可者，并非也。《江南录》云︰杨行密改杏名甜梅。
+【气味】味苦，性温。
+【毒性】有小毒。
+【归经】归肺、大肠经。
+【主治】止咳平喘，润肠通便。
+【释名】时珍曰︰杏字篆文象子在木枝之形。或云从口及从可者，并非也。《江南录》云︰杨行密改杏名甜梅。
 【发明】
 元素曰︰杏仁气薄味浓，浊而沉坠，降也、阴也。入手太阴经。其用有三︰润肺也，消食积也，散滞气也。
 杲曰︰杏仁散结润燥，除肺中风热咳嗽。杏仁下喘，治气也；桃仁疗狂，治血也。俱治大便秘，当分气、血。昼则便难，行阳气也；夜则便难，行阴血也。故虚人便闭，不可过泄。脉浮者属气，用杏仁、陈皮；脉沉者属血，用桃仁、陈皮。手阳明与手太阴为表里，贲门主往来，魄门主收闭，为气之通道，故并用陈皮佐之。
@@ -13866,16 +13586,11 @@
       <c r="H6" s="7" t="inlineStr">
         <is>
           <t>甘草
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归心、肺、脾、胃经
-【主治】
-益气补中，清热解毒，祛痰止咳，缓急止痛，调和诸药
-【释名】
-密甘（《别录》）、密草（《别录》）、美草（《别录》）、蕗草（《别录》）、灵通（《记事珠》）、国老（《别录》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归心、肺、脾、胃经。
+【主治】益气补中，清热解毒，祛痰止咳，缓急止痛，调和诸药。
+【释名】密甘（《别录》）、密草（《别录》）、美草（《别录》）、蕗草（《别录》）、灵通（《记事珠》）、国老（《别录》）。
 弘景曰︰此草最为众药之主，经方少有不用者，犹如香中有沉香也。国老即帝师之称，虽非君而为君所宗，是以能安和草石而解诸毒也。
 甄权曰︰诸药中甘草为君，治七十二种乳石毒，解一千二百般草木毒，调和众药有功故有国老之号。
 【发明】
@@ -13931,16 +13646,11 @@
       <c r="H7" s="7" t="inlineStr">
         <is>
           <t>白芍（芍药）
-【气味】
-苦、酸，微寒
-【毒性】
-无毒
-【归经】
-归肝、脾经
-【主治】
-养血调经，敛阴止汗，柔肝止痛，平抑肝阳
-【释名】
-将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
+【气味】苦、酸，微寒。
+【毒性】无毒。
+【归经】归肝、脾经。
+【主治】养血调经，敛阴止汗，柔肝止痛，平抑肝阳。
+【释名】将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
 时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。
 郑风诗云：伊其相谑，赠之以芍药。
 《韩诗外传》云：芍药，离草也。董子云：芍药一名将离，故将别赠之。俗呼其花之千叶者，为小牡丹；赤者为木芍药，与牡丹同名也。
@@ -14000,21 +13710,15 @@
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>赤芍（芍药）
-【气味】
-苦，微寒
-【毒性】
-无毒
-【归经】
-归肝经
-【主治】
-清热凉血，散瘀止痛，清肝泻火
-【释名】
-将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
+【气味】苦，微寒。
+【毒性】无毒。
+【归经】归肝经。
+【主治】清热凉血，散瘀止痛，清肝泻火。
+【释名】将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
 时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。
 郑风诗云：伊其相谑，赠之以芍药。
 《韩诗外传》云：芍药，离草也。董子云：芍药一名将离，故将别赠之。俗呼其花之千叶者，为小牡丹；赤者为木芍药，与牡丹同名也。
-【发明】
-志曰：赤者，利小便下气；白者，止痛散血。
+【发明】志曰：赤者，利小便下气；白者，止痛散血。
 大明曰：赤者补气，白者补血。
 弘景曰：赤者小利，俗方以止痛不减当归。白者道家亦服食之，及煮石用。
 成无己曰：**白补而赤泻，白收而赤散。酸以收之，甘以缓之，故酸甘相合，用补阴血。收逆气而除肺燥。**又云：芍药之酸，敛津液而益营血，收阴气而泄邪热。
@@ -14069,16 +13773,11 @@
       <c r="H9" s="7" t="inlineStr">
         <is>
           <t>大枣（枣）
-【气味】
-味甘，性温
-【毒性】
-无毒
-【归经】
-归脾、胃、心经
-【主治】
-补中益气，养血安神，缓和药性
-【释名】
-干枣（《别录》）、美枣（《别录》）、良枣（《别录》）。
+【气味】味甘，性温。
+【毒性】无毒。
+【归经】归脾、胃、心经。
+【主治】补中益气，养血安神，缓和药性。
+【释名】干枣（《别录》）、美枣（《别录》）、良枣（《别录》）。
 《别录》曰︰八月采，曝干。
 瑞曰︰此即晒干大枣也。味最良美，故宜入药。今人亦有用胶枣之肥大者。
 【发明】
@@ -14134,19 +13833,13 @@
       <c r="H10" s="7" t="inlineStr">
         <is>
           <t>葛根（葛）
-【气味】
-味甘、辛，性凉
-【毒性】
-无毒
-【归经】
-归脾、胃、肺经
-【主治】
-解肌退热，透发麻疹，生津止渴，升阳止泻，通经活络，解酒毒
-【释名】
-鸡齐（《本经》）、鹿藿（《别录》）、黄斤（《别录》）。
+【气味】味甘、辛，性凉。
+【毒性】无毒。
+【归经】归脾、胃、肺经。
+【主治】解肌退热，透发麻疹，生津止渴，升阳止泻，通经活络，解酒毒。
+【释名】鸡齐（《本经》）、鹿藿（《别录》）、黄斤（《别录》）。
 时珍曰︰葛从曷，谐声也。鹿食九草，此其一种，故曰鹿藿。黄斤未详。
-【发明】
-弘景曰︰生葛捣汁饮，解温病发热。五月五日日中时，取根为屑，熬令黄黑，屑末水服方寸匕，疗疟及疮，至良。
+【发明】弘景曰︰生葛捣汁饮，解温病发热。五月五日日中时，取根为屑，熬令黄黑，屑末水服方寸匕，疗疟及疮，至良。
 颂曰︰张仲景治伤寒有葛根汤，以其主大热、解肌、发腠理故也。
 元素曰︰升阳生津。脾虚作渴者，非此不除。勿多用，恐伤胃气。张仲景治太阳阳明合病，桂枝汤内加麻黄、葛根，又有葛根黄芩黄连解肌汤，是用此以断太阳入阳明之路，非即太阳药也。头颅痛如破，乃阳明中风，可用葛根葱白汤，为阳明仙药。若太阳初病，未入阳明而头痛者，不可便服升麻、葛根发之，是反引邪气入阳明，为引贼破家也。
 震亨曰︰凡痘已见红点，不可用葛根升麻汤，恐表虚反增斑烂也。
@@ -14200,16 +13893,11 @@
       <c r="H11" s="7" t="inlineStr">
         <is>
           <t>桑叶（桑）
-【气味】
-味甘、苦，性寒
-【毒性】
-无毒
-【归经】
-归肺、肝经
-【主治】
-疏散风热，清肺润燥，平抑肝阳，清肝明目，凉血止血
-【释名】
-子名椹（《集韵》）。
+【气味】味甘、苦，性寒。
+【毒性】无毒。
+【归经】归肺、肝经。
+【主治】疏散风热，清肺润燥，平抑肝阳，清肝明目，凉血止血。
+【释名】子名椹（《集韵》）。
 时珍曰︰徐锴《说文解字》云︰桑，音若，东方自然神木之名，其字象形。桑乃蚕所食，异于东方自然之神木，故加木于桑下而别之。
 《典术》云︰桑乃箕星之精。
 【发明】
@@ -14263,22 +13951,16 @@
       <c r="H12" s="7" t="inlineStr">
         <is>
           <t>菊花（菊）
-【气味】
-味甘、苦，性微寒
-【毒性】
-无毒
-【归经】
-归肺、肝经
-【主治】
-疏散风热，平抑肝阳，清肝明目，清热解毒
-【释名】
-节华（《本经》）、女节（《别录》）、女华（《别录》）、女茎（《别录》）、日精（《别录》）、更生（《别录》）、傅延年（《别录》）、治蔷（《尔雅》）、金蕊（《纲目》）、阴成（《别录》）、周盈（《别录》）。
+【气味】味甘、苦，性微寒。
+【毒性】无毒。
+【归经】归肺、肝经。
+【主治】疏散风热，平抑肝阳，清肝明目，清热解毒。
+【释名】节华（《本经》）、女节（《别录》）、女华（《别录》）、女茎（《别录》）、日精（《别录》）、更生（《别录》）、傅延年（《别录》）、治蔷（《尔雅》）、金蕊（《纲目》）、阴成（《别录》）、周盈（《别录》）。
 时珍曰︰按陆佃《埤雅》云︰菊本作蘜，从鞠。鞠，穷也。
 《月令》︰九月，菊有黄华。华事至此而穷尽，故谓之蘜。节华之名，亦取其应节候也。
 崔实《月令》云︰女节、女华，菊华之名也。治蔷、日精，菊根之名也。
 《抱朴子》云︰仙方所谓日精、更生、周盈，皆一菊而根、茎、花、实之名异也。
-【发明】
-震亨曰︰黄菊花属土与金，有水与火，能补阴血，故养目。
+【发明】震亨曰︰黄菊花属土与金，有水与火，能补阴血，故养目。
 时珍曰︰菊春生夏茂，秋花冬实，备受四气，饱经露霜，叶枯不落，花槁不零，味兼甘苦，性禀平和。昔人谓其能除风热，益肝补阴，盖不知其得金水之精英尤多，能益金水二脏也。补水所以制火，益金所以平木，木平则风息，火降则热除，用治诸风头目，其旨深微。黄者入金水阴分；白者，入金水阳分；红者，行妇人血分。皆可入药，神而明之，存乎其人。其苗可蔬，叶可啜，花可饵，根实可药，囊之可枕，酿之可饮，自本至末，罔不有功。宜乎前贤比之君子，神农列之上品，隐士采入酒饵，骚人餐其落英。费长房言︰九日饮菊酒，可以辟不祥。《神仙传》言︰康风子、朱孺子皆以服菊花成仙。《荆州记》言︰胡广久病风羸，饮菊潭水多寿。菊之贵重如此，是岂群芳可伍哉？钟会《菊有五美赞》云︰圆花高悬，准天极也。纯黄不杂，后土色也。早植晚发，君子德也；冒霜吐颖，象贞质也；杯中体轻，神仙 食也。《西京杂记》言︰采菊花茎叶，杂秫米酿酒，至次年九月始熟，用之</t>
         </is>
       </c>
@@ -14327,21 +14009,15 @@
       <c r="H13" s="7" t="inlineStr">
         <is>
           <t>薄荷
-【气味】
-辛，凉
-【毒性】
-无毒
-【归经】
-归肺、肝经
-【主治】
-疏散风热，清利头目，利咽透疹，疏肝行气
-【释名】
-菝（《食性》）、蕃荷菜（《千金》）、吴菝（《食性》）、南薄荷（《衍义》）、金钱薄荷（《会编》）。
+【气味】辛，凉。
+【毒性】无毒。
+【归经】归肺、肝经。
+【主治】疏散风热，清利头目，利咽透疹，疏肝行气。
+【释名】菝（《食性》）、蕃荷菜（《千金》）、吴菝（《食性》）、南薄荷（《衍义》）、金钱薄荷（《会编》）。
 时珍曰：薄荷，俗称也。陈士良《食性本草》作菝，扬雄《甘泉赋》作茇，吕忱《字林》作茇，则薄荷之为讹称可知矣。
 孙思邈《千金方》作蕃荷，又方音之讹也。今人药用，多以苏州者为胜，故陈士良谓之吴菝，以别胡菝也。
 宗奭曰：世称此为南薄荷，为有一种龙脑薄荷，所以别之。机曰：小儿方多用金钱薄荷，谓其叶小颇圆如钱也，书作金银误矣。
-【发明】
-元素曰：薄荷辛凉，气味俱薄，浮而升，阳也。故能去高巅及皮肤风热。
+【发明】元素曰：薄荷辛凉，气味俱薄，浮而升，阳也。故能去高巅及皮肤风热。
 士良曰：薄荷能引诸药入营卫，故能发散风寒。
 宗奭曰：小儿惊狂壮热，须此引药。又治骨蒸热劳，用其汁与众药熬为膏。猫食薄荷则醉，物相感尔。
 好古曰：薄荷，手、足厥阴气分药也。能搜肝气，又主肺盛有余肩背痛，及风寒汗出。
@@ -14393,16 +14069,11 @@
       <c r="H14" s="7" t="inlineStr">
         <is>
           <t>桔梗
-【气味】
-味苦、辛，性平
-【毒性】
-小毒
-【归经】
-归肺经
-【主治】
-宣肺利咽，祛痰排脓
-【释名】
-白药（《别录》）、梗草（《别录》）、荠 （《本经》）。
+【气味】味苦、辛，性平。
+【毒性】小毒。
+【归经】归肺经。
+【主治】宣肺利咽，祛痰排脓。
+【释名】白药（《别录》）、梗草（《别录》）、荠 （《本经》）。
 时珍曰︰此草之根结实而梗直，故名。《吴普本草》一名利如，一名符扈，一名房图，方书并无见，盖亦瘦辞尔。桔梗、荠 乃一类，有甜、苦二种，故《本经》桔梗一名荠 ，而今俗呼荠 为甜桔梗也。至《别录》始出荠 条，分为二物，然其性味功用皆不同，当以《别录》为是。
 【发明】
 好古曰︰桔梗气微温，味苦辛，味浓气轻，阳中之阴，升也。入手太阴肺经气分及足少阴经。
@@ -14456,16 +14127,11 @@
       <c r="H15" s="7" t="inlineStr">
         <is>
           <t>芦根（芦）
-【气味】
-味甘，性寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-清热泻火，生津止渴，除烦止呕，利尿
-【释名】
-苇（音伟《尔雅》）、葭（音加《尔雅》），花名蓬蕽（《唐本》）、笋名虇（音拳《尔雅》）。
+【气味】味甘，性寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】清热泻火，生津止渴，除烦止呕，利尿。
+【释名】苇（音伟《尔雅》）、葭（音加《尔雅》），花名蓬蕽（《唐本》）、笋名虇（音拳《尔雅》）。
 时珍曰︰按毛苌《诗疏》云︰苇之初生曰葭；未秀曰芦；长成曰苇。苇者，伟大也。芦者，色卢黑也。葭者，嘉美也。
 【发明】
 时珍曰︰按《雷公炮炙论》序云︰益食加觞，须煎芦、朴。注云︰用逆水芦根并浓朴二味等分，煎汤服。盖芦根甘能益胃，寒能降火故也。</t>
@@ -14516,20 +14182,14 @@
       <c r="H16" s="7" t="inlineStr">
         <is>
           <t>金银花（忍冬）
-【气味】
-味甘，性寒
-【毒性】
-无毒
-【归经】
-归肺、心、胃经
-【主治】
-清热解毒，疏散风热
-【释名】
-金银藤（《纲目》）、鸳鸯藤（《纲目》）、鹭鸶藤（《纲目》）、老翁须（《纲目》）、左缠藤（《纲目》）、金钗股（《纲目》）、通灵草（《土宿》）、蜜桶藤（《土宿》）。
+【气味】味甘，性寒。
+【毒性】无毒。
+【归经】归肺、心、胃经。
+【主治】清热解毒，疏散风热。
+【释名】金银藤（《纲目》）、鸳鸯藤（《纲目》）、鹭鸶藤（《纲目》）、老翁须（《纲目》）、左缠藤（《纲目》）、金钗股（《纲目》）、通灵草（《土宿》）、蜜桶藤（《土宿》）。
 弘景曰︰处处有之。藤生，凌冬不凋，故名忍冬。
 时珍曰︰其花长瓣垂须，黄白相半，而藤左缠，故有金银、鸳鸯以下诸名。金钗股，贵其功也。土宿真君云︰蜜桶藤，阴草也。取汁能伏硫制汞，故有通灵之称。
-【发明】
-弘景曰︰忍冬，煮汁酿酒饮，补虚疗风。此既长年益寿，可常采服，而《仙经》少用。凡易得之草，人多不肯为之，更求难得者，贵远贱近，庸人之情也。
+【发明】弘景曰︰忍冬，煮汁酿酒饮，补虚疗风。此既长年益寿，可常采服，而《仙经》少用。凡易得之草，人多不肯为之，更求难得者，贵远贱近，庸人之情也。
 时珍曰︰忍冬，茎叶及花，功用皆同。昔人称其治风除胀，解痢逐尸为要药，而后世不复知用，后世称其消肿散毒治疮为要药，而昔人并未言及。乃知古今之理，万变不同，未可一辙论也。按︰陈自明《外科精要》云︰忍冬酒，治痈疽发背，初发便当服此，其效甚奇，胜于红内消。洪内翰迈、沈内翰括诸方，所载甚详。如疡医丹阳僧、江西僧鉴清、金陵王琪、王尉子骏、海州刘秀才纯臣等，所载疗痈疽发背经效奇方，皆是此物。故张相公云︰谁知至贱之中，乃有殊常之效，正此类也。</t>
         </is>
       </c>
@@ -14578,16 +14238,11 @@
       <c r="H17" s="7" t="inlineStr">
         <is>
           <t>连翘
-【气味】
-味苦，性微寒
-【毒性】
-无毒
-【归经】
-归肺、心、小肠经
-【主治】
-清热解毒，消肿散结，疏散风热
-【释名】
-连（《尔雅》）、异翘（《尔雅》）、旱莲子（《药性》）、兰华（《吴普》）、三廉（别录）、根名连轺（仲景）、折根（别录）。 
+【气味】味苦，性微寒。
+【毒性】无毒。
+【归经】归肺、心、小肠经。
+【主治】清热解毒，消肿散结，疏散风热。
+【释名】连（《尔雅》）、异翘（《尔雅》）、旱莲子（《药性》）、兰华（《吴普》）、三廉（别录）、根名连轺（仲景）、折根（别录）。 
 恭曰︰其实似莲作房，翘出众草，故名。
 宗奭曰︰连翘亦不翘出众草。太山山谷间甚多。其子折之，片片相比如翘，应以此得名耳。
 时珍曰︰按《尔雅》云︰连，异翘。则是本名连，又名异翘，人因合称为连翘矣。连轺亦作连苕，即《本经》下品翘根是也。唐苏恭《修本草》退入有名未用中，今并为一。旱莲乃小翘，人以为鳢肠者，故同名。
@@ -14643,16 +14298,11 @@
       <c r="H18" s="7" t="inlineStr">
         <is>
           <t>牛蒡子（恶实）
-【气味】
-味辛、苦，性寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-疏散风热，宣肺透疹，解毒利咽，滑肠通便
-【释名】
-鼠粘（《别录》）、牛蒡（《别录》）、大力子（《纲目》）、蒡翁菜（《纲目》）、便牵牛（《纲目》）、蝙蝠刺（《斗门方》）。
+【气味】味辛、苦，性寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】疏散风热，宣肺透疹，解毒利咽，滑肠通便。
+【释名】鼠粘（《别录》）、牛蒡（《别录》）、大力子（《纲目》）、蒡翁菜（《纲目》）、便牵牛（《纲目》）、蝙蝠刺（《斗门方》）。
 时珍曰︰其实状恶而多刺钩，故名也。其根叶皆可食，人呼为牛菜，术人隐之呼为大力也。俚人谓之便牵牛。河南人呼为夜叉头。
 颂曰︰实壳多刺，鼠过之则缀惹不可脱，故谓之鼠粘子，亦如羊负来之比。
 【发明】
@@ -14704,16 +14354,11 @@
       <c r="H19" s="7" t="inlineStr">
         <is>
           <t>荆芥（假苏）
-【气味】
-味辛，性微温
-【毒性】
-无毒
-【归经】
-归肺、肝经
-【主治】
-解表散风，透疹，利咽消肿，止血
-【释名】
-姜芥（《别录》）、荆芥（《吴普》）、鼠蓂（《本经》）。
+【气味】味辛，性微温。
+【毒性】无毒。
+【归经】归肺、肝经。
+【主治】解表散风，透疹，利咽消肿，止血。
+【释名】姜芥（《别录》）、荆芥（《吴普》）、鼠蓂（《本经》）。
 弘景曰︰假苏方药不复用。
 恭曰︰此即菜中荆芥也，姜芥声讹尔。先居草部，今录入菜部。
 士良曰︰荆芥本草呼为假苏。假苏又别是一物。叶锐圆，多野生，以香气似苏，故呼为苏。
@@ -14771,16 +14416,11 @@
       <c r="H20" s="7" t="inlineStr">
         <is>
           <t>淡豆豉（大豆豉）
-【气味】
-味苦、辛，性凉
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-解表除烦，宣发郁热
-【释名】
-时珍曰︰按︰刘熙《释名》云︰豉，嗜也。调和五味，可甘嗜也。许慎《说文》谓豉为配盐幽菽者，乃咸豉也。
+【气味】味苦、辛，性凉。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】解表除烦，宣发郁热。
+【释名】时珍曰︰按︰刘熙《释名》云︰豉，嗜也。调和五味，可甘嗜也。许慎《说文》谓豉为配盐幽菽者，乃咸豉也。
 【发明】
 弘景曰︰豉，食中常用。春夏之气不和，蒸炒以酒渍服之至佳。依康伯法，先以醋、酒溲蒸曝燥，麻油和，再蒸曝之，凡三过，末椒、姜治和进食，大胜今时油豉也。患脚人，常将渍酒饮之，以滓敷脚，皆瘥。
 颂曰︰古今方书用豉治病最多，江南人善作豉，凡得时气，即先用葱豉汤服之取汗，往往便瘥也。
@@ -14832,16 +14472,11 @@
       <c r="H21" s="7" t="inlineStr">
         <is>
           <t>竹叶（竹）
-【气味】
-味甘、淡，性寒
-【毒性】
-无毒
-【归经】
-归心、胃、小肠经
-【主治】
-清热泻火，除烦，生津利尿
-【释名】
-时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+【气味】味甘、淡，性寒。
+【毒性】无毒。
+【归经】归心、胃、小肠经。
+【主治】清热泻火，除烦，生津利尿。
+【释名】时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
 【发明】
 弘景曰︰甘竹叶最胜。
 诜曰︰竹叶︰ 、苦、淡、甘之外，馀皆不堪入药，不宜人。淡竹为上，甘竹次之。
@@ -14895,16 +14530,11 @@
       <c r="H22" s="7" t="inlineStr">
         <is>
           <t>沙参
-【气味】
-味甘，性微寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-养阴清肺，益胃生津，化痰益气
-【释名】
-白参（《吴普》）、知母（《别录》）、羊乳（《别录》）、羊婆奶（《纲目》）、铃儿草（《别录》）、虎须（《别录》）、苦心（《别录》，又名文希，一名识美，一名志取。）
+【气味】味甘，性微寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】养阴清肺，益胃生津，化痰益气。
+【释名】白参（《吴普》）、知母（《别录》）、羊乳（《别录》）、羊婆奶（《纲目》）、铃儿草（《别录》）、虎须（《别录》）、苦心（《别录》，又名文希，一名识美，一名志取。）
 弘景曰︰此与人参、玄参、丹参、苦参是为五参，其形不尽相类，而主疗颇同，故皆有参名。又有紫参，乃牡蒙也。
 时珍曰︰沙参白色，宜于沙地，故名。其根多白汁，俚人呼为羊婆奶。《别录》有名未用，羊乳即此也。此物无心味淡，而《别录》一名苦心，又与知母同名，不知所谓也。铃儿草，象花形也。
 【发明】
@@ -14957,16 +14587,11 @@
       <c r="H23" s="7" t="inlineStr">
         <is>
           <t>贝母
-【气味】
-味甘、苦，性微寒
-【毒性】
-无毒
-【归经】
-归肺、心经
-【主治】
-清热润肺，化痰止咳，散结消痈
-【释名】
-（《尔雅》，音萌）、勤母（《别录》）、苦菜（《别录》）、苦花（《别录》）、空草（《本经》）、药实（《别录》）。
+【气味】味甘、苦，性微寒。
+【毒性】无毒。
+【归经】归肺、心经。
+【主治】清热润肺，化痰止咳，散结消痈。
+【释名】（《尔雅》，音萌）、勤母（《别录》）、苦菜（《别录》）、苦花（《别录》）、空草（《本经》）、药实（《别录》）。
 弘景曰：形似聚贝子，故名贝母。
 时珍曰：《诗》云言采其 ，即此。一作虻，谓根状如虻也。苦菜、药实，与野苦 、黄药子同名。
 【发明】
@@ -15023,16 +14648,11 @@
       <c r="H24" s="7" t="inlineStr">
         <is>
           <t>栀子
-【气味】
-味苦，性寒
-【毒性】
-无毒
-【归经】
-心、肺、三焦经
-【主治】
-清泄肺热，疏散肌表湿热，凉血解毒
-【释名】
-木丹（《本经》）、越桃（《别录》）、鲜支（《纲目》），花名薝蔔（《酉阳杂俎》）。
+【气味】味苦，性寒。
+【毒性】无毒。
+【归经】心、肺、三焦经。
+【主治】清泄肺热，疏散肌表湿热，凉血解毒。
+【释名】木丹（《本经》）、越桃（《别录》）、鲜支（《纲目》），花名薝蔔（《酉阳杂俎》）。
 时珍曰︰卮，酒器也。栀子象之，故名。俗作栀。司马相如赋云︰鲜支黄砾。注云︰鲜支即支子也。佛书称其花为卜，谢灵运谓之林兰，曾端伯呼为禅友。或曰︰卜金色，非栀子也。
 【发明】
 元素曰︰栀子轻飘而象肺，色赤而象火，故能泻肺中之火。
@@ -15088,16 +14708,11 @@
       <c r="H25" s="7" t="inlineStr">
         <is>
           <t>梨皮（梨）
-【气味】
-味甘、微涩，性凉
-【毒性】
-无毒
-【归经】
-归肺、心、肾经
-【主治】
-清心润肺，降火生津，止咳化痰
-【释名】
-快果（《弘景》）、果宗（《纲目》）、玉乳（《纲目》）、蜜父（《清异录》）。
+【气味】味甘、微涩，性凉。
+【毒性】无毒。
+【归经】归肺、心、肾经。
+【主治】清心润肺，降火生津，止咳化痰。
+【释名】快果（《弘景》）、果宗（《纲目》）、玉乳（《纲目》）、蜜父（《清异录》）。
 震亨曰︰梨者，利也。其性下行流利也。
 弘景曰︰梨种殊多，并皆冷利，多食损人，故俗人谓之快果，不入药用。
 【发明】
@@ -15151,16 +14766,11 @@
       <c r="H26" s="7" t="inlineStr">
         <is>
           <t>苏叶（苏）
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归肺、脾经
-【主治】
-解表散寒，行气和胃
-【释名】
-紫苏（《食疗》）、赤苏（《肘后方》）、桂荏（《尔雅》）。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归肺、脾经。
+【主治】解表散寒，行气和胃。
+【释名】紫苏（《食疗》）、赤苏（《肘后方》）、桂荏（《尔雅》）。
 时珍曰︰苏从酥，音酥，舒畅也。苏性舒畅，行气和血，故谓之苏。曰紫苏者，以别白苏也。苏乃荏类，而味更辛如桂，故《尔 雅》谓之桂荏。
 【发明】
 颂曰︰若宣通风毒，则单用茎，去节尤良。
@@ -15213,16 +14823,11 @@
       <c r="H27" s="7" t="inlineStr">
         <is>
           <t>半夏
-【气味】
-味辛，性温
-【毒性】
-有毒
-【归经】
-归脾、胃、肺经
-【主治】
-燥湿化痰，降逆止呕，消痞散结
-【释名】
-守田（《别录》）、水玉（《本经》）、地文（《本经》）、和姑（《吴普》）。
+【气味】味辛，性温。
+【毒性】有毒。
+【归经】归脾、胃、肺经。
+【主治】燥湿化痰，降逆止呕，消痞散结。
+【释名】守田（《别录》）、水玉（《本经》）、地文（《本经》）、和姑（《吴普》）。
 时珍曰︰《礼记‧月令》︰五月半夏生。盖当夏之半也，故名。守田会意，水玉因形。
 【发明】
 权曰︰半夏使也。虚而有痰气，宜加用之。
@@ -15279,16 +14884,11 @@
       <c r="H28" s="7" t="inlineStr">
         <is>
           <t>前胡
-【气味】
-味苦、辛，性微寒
-【毒性】
-无毒
-【归经】
-归肺经
-【主治】
-降气化痰，散风清热
-【释名】
-时珍曰：按：孙 《唐韵》作湔胡，名义未解。
+【气味】味苦、辛，性微寒。
+【毒性】无毒。
+【归经】归肺经。
+【主治】降气化痰，散风清热。
+【释名】时珍曰：按：孙 《唐韵》作湔胡，名义未解。
 【发明】
 时珍曰：前胡味甘、辛，气微平，阳中之阴，降也。乃手足太阴、阳明之药，与柴胡纯阳上升入少阳、厥阴者不同也。其功长于下气，故能治痰热喘嗽、痞膈呕逆诸疾，气下则火降，痰亦降矣。所以有推陈致新之绩，为痰气要药。陶弘景言其与柴胡同功，非矣。治证虽同，而所入所主则异。</t>
         </is>
@@ -15338,16 +14938,11 @@
       <c r="H29" s="7" t="inlineStr">
         <is>
           <t>陈皮（橘）
-【气味】
-味苦、辛，性温
-【毒性】
-无毒
-【归经】
-归脾、肺经
-【主治】
-理气健脾，燥湿化痰
-【释名】
-红皮（《汤液》）、陈皮（《食疗》）。
+【气味】味苦、辛，性温。
+【毒性】无毒。
+【归经】归脾、肺经。
+【主治】理气健脾，燥湿化痰。
+【释名】红皮（《汤液》）、陈皮（《食疗》）。
 弘景曰︰橘皮疗气大胜。以东橘为好，西江者不如。须陈久者为良。
 好古曰︰橘皮以色红日久者为佳，故曰红皮、陈皮。去白者曰橘红也。
 【发明】
@@ -15402,20 +14997,14 @@
       <c r="H30" s="7" t="inlineStr">
         <is>
           <t>茯苓
-【气味】
-味甘、淡，性平
-【毒性】
-无毒
-【归经】
-归心、肺、脾、肾经
-【主治】
-利水渗湿，健脾宁心
-【释名】
-伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
+【气味】味甘、淡，性平。
+【毒性】无毒。
+【归经】归心、肺、脾、肾经。
+【主治】利水渗湿，健脾宁心。
+【释名】伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
 宗奭曰︰多年樵斫之松根之气味，抑郁未绝，精英未沦。其精气盛者，发泄于外，结为茯苓，故不抱根，离其本体，有零之义也。津气不盛，只能附结本根，既不离本，故曰伏神。
 时珍曰︰茯苓，《史记•龟策传》作伏灵。盖松之神灵之气，伏结而成，故谓之伏灵、伏神也。《仙经》言︰伏灵大如拳者，佩之令百鬼消灭，则神灵之气，亦可征矣。俗作苓者，传写之讹尔。下有伏灵，上有菟丝，故又名伏莬。或云“其形如兔，故名”，亦通。
-【发明】
-弘景曰︰茯苓白色者补，赤色者利。俗用甚多，仙方服食亦为至要。云其通神而致灵，和魂而炼魄，利窍而益肌，浓肠而开心，调营而理卫，上品仙药也。善能断谷不饥。
+【发明】弘景曰︰茯苓白色者补，赤色者利。俗用甚多，仙方服食亦为至要。云其通神而致灵，和魂而炼魄，利窍而益肌，浓肠而开心，调营而理卫，上品仙药也。善能断谷不饥。
 宗奭曰︰茯苓行水之功多，益心脾不可缺也。
 元素曰︰茯苓赤泻白补，上古无此说。气味俱薄，性浮而升。其用有五︰利小便也；开腠理也，生津液也，除虚热也，止泻也。如小便利或数者，多服则损人目。汗多人服之，亦损元气，夭人寿，为其淡而渗也。又云︰淡为天之阳，阳当上行，何以利水而泻下？气薄者阳中之阴，所以茯苓利水泻下。不离阳之体，故入手太阳。
 杲曰︰白者入壬癸，赤者入丙丁。味甘而淡，降也，阳中阴也。其用有六︰利窍而除湿，益气而和中，治惊悸，生津液，小便多者能止，小便结者能通。又云︰湿淫所胜，小便不利。淡以利窍，甘以助阳。甘平能益脾逐水，乃除湿之圣药也。
@@ -15469,16 +15058,11 @@
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>枳壳（枳）
-【气味】
-味苦、辛、酸，性微寒
-【毒性】
-无毒
-【归经】
-归脾、胃、大肠经
-【主治】
-行气消胀，宽中除痞，化痰消积
-【释名】
-子名枳实（《本经》）、枳壳（宋《开宝》）。
+【气味】味苦、辛、酸，性微寒。
+【毒性】无毒。
+【归经】归脾、胃、大肠经。
+【主治】行气消胀，宽中除痞，化痰消积。
+【释名】子名枳实（《本经》）、枳壳（宋《开宝》）。
 宗奭曰：枳实、枳壳，一物也。小则其性酷而速，大则其性详而缓。故张仲景治伤寒仓猝之病，承气汤中用枳实，皆取其疏通、决泄、破结实之义。他方但导败风壅之气，可常服者，故用枳壳，其义如此。
 恭曰：既称枳实，须合核瓤，今殊不然。
 时珍曰：枳乃木名，从只，谐声也。实乃其子，故曰枳实。后人因小者性速，又呼老者为枳壳。生则皮厚而实，熟则壳薄而虚，正如青橘皮、陈橘皮之义。宋人复出枳壳一条，非矣。寇氏以为破结实而名，亦未必然。
@@ -15535,19 +15119,13 @@
       <c r="H32" s="7" t="inlineStr">
         <is>
           <t>防风
-【气味】
-味辛、甘，性微温
-【毒性】
-无毒
-【归经】
-归膀胱、肝、脾经
-【主治】
-祛风解表，胜湿止痛，止痉
-【释名】
-铜芸（《本经》）、茴芸（《吴普》）、茴草（《别录》）、屏风（《别录》）、 根（《别录》）、百枝（《别录》）、百蜚（《吴普》）。
+【气味】味辛、甘，性微温。
+【毒性】无毒。
+【归经】归膀胱、肝、脾经。
+【主治】祛风解表，胜湿止痛，止痉。
+【释名】铜芸（《本经》）、茴芸（《吴普》）、茴草（《别录》）、屏风（《别录》）、 根（《别录》）、百枝（《别录》）、百蜚（《吴普》）。
 时珍曰：防者，御也。其功疗风最要，故名。屏风者，防风隐语也。曰芸、曰茴、曰蕳者，其花如茴香，其气如芸蒿、蕳兰也。
-【发明】
-元素曰：防风，治风通用。身半以上风邪用身，身半以下风邪，用梢，治风去湿之仙药也，风能胜湿故尔。能泻肺实，误服泻人上焦元气。杲曰：防风治一身尽痛，乃猝 伍卑贱之职，随所引而至，乃风药中润剂也。若补脾胃，非此引用不能行。凡脊痛项强，不可回顾，腰似折，项似拔者，乃手足太阳证，正当用防风。凡疮在胸膈以上，虽无手足太阳 证，亦当用之，为能散结，去上部风。病患身体拘倦者，风也，诸疮见此证，亦须用之。钱 仲阳泻黄散中倍用防风者，乃于土中泻木也。</t>
+【发明】元素曰：防风，治风通用。身半以上风邪用身，身半以下风邪，用梢，治风去湿之仙药也，风能胜湿故尔。能泻肺实，误服泻人上焦元气。杲曰：防风治一身尽痛，乃猝 伍卑贱之职，随所引而至，乃风药中润剂也。若补脾胃，非此引用不能行。凡脊痛项强，不可回顾，腰似折，项似拔者，乃手足太阳证，正当用防风。凡疮在胸膈以上，虽无手足太阳 证，亦当用之，为能散结，去上部风。病患身体拘倦者，风也，诸疮见此证，亦须用之。钱 仲阳泻黄散中倍用防风者，乃于土中泻木也。</t>
         </is>
       </c>
       <c r="I32" s="24" t="inlineStr">
@@ -15595,16 +15173,11 @@
       <c r="H33" s="7" t="inlineStr">
         <is>
           <t>秦艽
-【气味】
-味辛、苦，性平
-【毒性】
-无毒
-【归经】
-归胃、肝、胆经
-【主治】
-祛风湿，清湿热，止痹痛，退虚热
-【释名】
-秦糺（《唐本》）、秦爪（萧炳）。
+【气味】味辛、苦，性平。
+【毒性】无毒。
+【归经】归胃、肝、胆经。
+【主治】祛风湿，清湿热，止痹痛，退虚热。
+【释名】秦糺（《唐本》）、秦爪（萧炳）。
 恭曰：秦艽，俗作秦胶，本名秦糺，与纠同。
 时珍曰：秦艽出秦中，以根作罗纹交纠者佳，故名秦艽、秦糺。
 【发明】
@@ -15656,16 +15229,11 @@
       <c r="H34" s="7" t="inlineStr">
         <is>
           <t>当归
-【气味】
-味甘、辛，性温
-【毒性】
-无毒
-【归经】
-归肝、心、脾经
-【主治】
-补血活血，调经止痛，润肠通便
-【释名】
-乾归（《本经》）、山蕲（《尔雅》）、白蕲（《尔雅》）、文无（《纲目》）。
+【气味】味甘、辛，性温。
+【毒性】无毒。
+【归经】归肝、心、脾经。
+【主治】补血活血，调经止痛，润肠通便。
+【释名】乾归（《本经》）、山蕲（《尔雅》）、白蕲（《尔雅》）、文无（《纲目》）。
 颂曰︰按而粗大。许慎《说文》云︰生山中者，名薜，一名山蕲。然则当归，芹类也。在平地者名芹，生山中粗大者，名当归也。
 宗奭曰︰今川蜀皆以畦种，尤肥好多脂，不以平地、山中为等差也。
 时珍曰︰当归本非芹类，特以花叶似芹，故得芹名。古人娶妻为嗣续也，当归调血为女人要药，有思夫之意，故有当归之名，正与唐诗胡麻好种无人种，正是归时又不归之旨相同。崔豹《古今注》云，古人相赠以芍药，相招以文无。文无一名当归，芍药一名将离，故也。
@@ -15725,16 +15293,11 @@
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>川芎（芎䓖）
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归肝、胆、心包经
-【主治】
-活血行气，祛风止痛
-【释名】
-胡䓖（《别录》）、川芎（《纲目》）、香果（《别录》）、山鞠穷（《纲目》）。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归肝、胆、心包经。
+【主治】活血行气，祛风止痛。
+【释名】胡䓖（《别录》）、川芎（《纲目》）、香果（《别录》）、山鞠穷（《纲目》）。
 时珍曰︰芎本作营，名义未详。或云︰人头穹窿穷高，天之象也。此药上行，专治头脑 诸疾，故有芎 之名。以胡戎者为佳，故曰胡芎。古人因其根节状如马衔，谓之马衔芎 。 后世因其状如雀脑，谓之雀脑芎。其出关中者，呼为京芎，亦曰西芎；出蜀中者，为川芎；出天台者，为台芎；出江南者，为抚芎，皆因地而名也。《左传》︰楚人谓萧人曰︰有麦曲乎？ 有山鞠穷乎？河鱼腹疾柰何？二物皆御湿，故以谕之。丹溪朱氏治六郁越鞠丸中用越桃、鞠 穷，故以命名。《金光明经》谓之 莫迦。
 【发明】
 宗奭曰︰今人用此最多，头面风不可缺也，然须以他药佐之。
@@ -15791,14 +15354,10 @@
       <c r="H36" s="7" t="inlineStr">
         <is>
           <t>乌头（川乌，草乌）
-【气味】
-味辛、苦，性热
-【毒性】
-大毒（草乌毒烈更甚）
-【归经】
-归心、肝、肾、脾经
-【主治】
-祛风除湿，温经止痛
+【气味】味辛、苦，性热。
+【毒性】大毒（草乌毒烈更甚）。
+【归经】归心、肝、肾、脾经。
+【主治】祛风除湿，温经止痛。
 【释名】
 [川乌]
 时珍曰︰初种为乌头，象乌之头也。附乌头而生者为附子，如子附母也。乌头如芋魁，附子如芋子，盖一物也。别有草乌头、白附子，故俗呼此为黑附子，川乌头以别之。诸家不分乌头有川、草两种，皆混杂注解，今悉正之。
@@ -15864,19 +15423,13 @@
       <c r="H37" s="7" t="inlineStr">
         <is>
           <t>黄芪（黄耆）
-【气味】
-味甘，性微温
-【毒性】
-无毒
-【归经】
-归脾、肺经
-【主治】
-补气升阳，固表止汗，利水消肿，生津养血，行滞通痹，托毒排脓，敛疮生肌
-【释名】
-黄耆（《纲目》）、戴糁（《本经》）、戴椹（《别录》，又名独椹）、芰草（《别录》，又名蜀脂）、百本（《别录》）、王孙（《药性论》）。
+【气味】味甘，性微温。
+【毒性】无毒。
+【归经】归脾、肺经。
+【主治】补气升阳，固表止汗，利水消肿，生津养血，行滞通痹，托毒排脓，敛疮生肌。
+【释名】黄耆（《纲目》）、戴糁（《本经》）、戴椹（《别录》，又名独椹）、芰草（《别录》，又名蜀脂）、百本（《别录》）、王孙（《药性论》）。
 时珍曰︰耆，长也。黄耆色黄，为补药之长，故名。今俗通作黄芪。或作蓍者，非矣。蓍，乃蓍龟之蓍，音尸。王孙与牡蒙同名异物。
-【发明】
-弘景曰︰出陇西者，温补；出白水者，冷补。又有赤色者，可作膏，用消痈肿。
+【发明】弘景曰︰出陇西者，温补；出白水者，冷补。又有赤色者，可作膏，用消痈肿。
 藏器曰︰虚而客热，用白水黄耆；虚而客冷，用陇西黄耆。
 大明曰︰黄耆，药中补益，呼为羊肉；白水耆，凉，无毒，排脓治血，及烦闷热毒骨蒸劳；赤水耆，凉，无毒，治血退热毒，馀功并同；木耆，凉，无毒，治烦排脓之力，微于黄，遇阙即倍用之。
 元素曰︰黄耆甘温纯阳，其用有五︰补诸虚不足，一也；益元气，二也；壮脾胃，三也；去肌热，四也；排脓止痛，活血生血，内托阴疽，为疮家圣药，五也。又曰︰补五脏诸虚，治脉弦自汗，泻阴火，去虚热，无汗，则发之；有汗，则止之。
@@ -15938,19 +15491,13 @@
       <c r="H38" s="7" t="inlineStr">
         <is>
           <t>蜂蜜
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归肺、脾、大肠经
-【主治】
-补中润燥，止痛解毒，外用生肌敛疮
-【释名】
-蜂糖（俗名）生岩石者名石蜜（《本经》）、石饴（同上）、岩蜜（《拾遗》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归肺、脾、大肠经。
+【主治】补中润燥，止痛解毒，外用生肌敛疮。
+【释名】蜂糖（俗名）生岩石者名石蜜（《本经》）、石饴（同上）、岩蜜（《拾遗》）。
 时珍曰︰蜜以密成，故谓之蜜。《本经》原作石蜜，盖以生岩石者为良耳，而诸家反致疑辩。今直题曰蜂蜜，正名也。
-【发明】
-弘景曰︰石蜜道家丸饵，莫不须之。仙方亦单炼服食，云致长生不老也。
+【发明】弘景曰︰石蜜道家丸饵，莫不须之。仙方亦单炼服食，云致长生不老也。
 时珍曰︰蜂采无毒之花，酿以小便而成蜜，所谓臭腐生神奇也。其入药之功有五︰清热也，补中也，解毒也，润燥也，止痛也。生则性凉，故能清热；熟则性温，故能补中。甘而和平，故能解毒；柔而濡泽，故能润燥。缓可以去急，故能止心腹、肌肉、疮疡之痛；和可以致中，故能调和百药，而与甘草同功。张仲景治阳明结燥，大便不通，蜜煎导法，诚千古神方也。
 诜曰︰但凡觉有热，四肢不和，即服蜜浆一碗，甚良。又点目中热膜，以家养白蜜为上，木蜜次之，崖蜜更次之也。与姜汁熬炼，治癞甚效。</t>
         </is>
@@ -16000,16 +15547,11 @@
       <c r="H39" s="7" t="inlineStr">
         <is>
           <t>薏苡仁
-【气味】
-味甘、淡，性凉
-【毒性】
-无毒
-【归经】
-归脾、胃、肺经
-【主治】
-利水渗湿，健脾止泻，除痹排脓，解毒散结
-【释名】
-解蠡（音礼。《本经》）、芑实（音起。《别录》）、赣米（《别录》。音感。陶氏作珠，雷氏作 米）、回回米（《救荒本草》）、薏珠子（《图经》）。
+【气味】味甘、淡，性凉。
+【毒性】无毒。
+【归经】归脾、胃、肺经。
+【主治】利水渗湿，健脾止泻，除痹排脓，解毒散结。
+【释名】解蠡（音礼。《本经》）、芑实（音起。《别录》）、赣米（《别录》。音感。陶氏作珠，雷氏作 米）、回回米（《救荒本草》）、薏珠子（《图经》）。
 时珍曰︰薏苡名义未详。其叶似蠡实叶而解散，又似芑黍之苗，故有解蠡、芑实之名。 赣米乃其坚硬者，有赣强之意。苗名屋 。《救荒本草》云︰回回米又呼西番蜀秫。俗名草珠儿。
 【发明】
 宗奭曰︰薏苡仁《本经》云︰微寒，主筋急拘挛。拘挛有两等︰《素问》注中，大筋受热，则缩而短，故挛急不伸，此是因热而拘挛也，故可用薏苡；若《素问》言因寒则筋急者，不可更用此也。 盖受寒使人筋急；寒热使人筋挛；若但受热不曾受寒，亦使人筋缓；受湿则又引长无力 也。此药力势和缓，凡用须加倍即见效。
@@ -16063,16 +15605,11 @@
       <c r="H40" s="7" t="inlineStr">
         <is>
           <t>羌活（独活羌活）
-【气味】
-味辛、苦，性温
-【毒性】
-无毒
-【归经】
-归膀胱、肾经
-【主治】
-解表散寒，祛风除湿，止痛
-【释名】
-羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
+【气味】味辛、苦，性温。
+【毒性】无毒。
+【归经】归膀胱、肾经。
+【主治】解表散寒，祛风除湿，止痛。
+【释名】羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
 弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
 时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
 【发明】
@@ -16125,16 +15662,11 @@
       <c r="H41" s="7" t="inlineStr">
         <is>
           <t>独活（独活羌活）
-【气味】
-味辛、苦，性温
-【毒性】
-无毒
-【归经】
-归膀胱、肾经
-【主治】
-解表散寒，祛风除湿，止痛
-【释名】
-羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
+【气味】味辛、苦，性温。
+【毒性】无毒。
+【归经】归膀胱、肾经。
+【主治】解表散寒，祛风除湿，止痛。
+【释名】羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
 弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
 时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
 【发明】
@@ -16187,16 +15719,11 @@
       <c r="H42" s="7" t="inlineStr">
         <is>
           <t>石膏
-【气味】
-味甘、辛，性大寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-清热泻火，除烦止渴
-【释名】
-细理石（《别录》）、寒水石（《纲目》）。
+【气味】味甘、辛，性大寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】清热泻火，除烦止渴。
+【释名】细理石（《别录》）、寒水石（《纲目》）。
 震享曰︰火煅细研醋调，封丹灶，其固密甚于脂膏。此盖兼质与能而得名，正与石脂同意。
 时珍曰︰其纹理细密，故名细理石。其性大寒如水，故名寒水石，与凝水石同名异物。
 【发明】
@@ -16253,16 +15780,11 @@
       <c r="H43" s="7" t="inlineStr">
         <is>
           <t>知母
-【气味】
-味苦、甘，性寒
-【毒性】
-无毒
-【归经】
-归肺、胃、肾经
-【主治】
-清热泻火，滋阴润燥
-【释名】
-母（《本经》音迟。《说文》作 ）、连母（《本经》）、 母（ 音匙，又音提，或作 ）、货母（《本经》）、地参（《本经》）、水参（又名水须、水浚）、 （《尔雅》，音覃）、 藩（音沉烦）、苦心（《别录》）、儿草（《别录》，又名儿踵草、女雷、女理、鹿列、韭逢、东根、野蓼、昌支）
+【气味】味苦、甘，性寒。
+【毒性】无毒。
+【归经】归肺、胃、肾经。
+【主治】清热泻火，滋阴润燥。
+【释名】母（《本经》音迟。《说文》作 ）、连母（《本经》）、 母（ 音匙，又音提，或作 ）、货母（《本经》）、地参（《本经》）、水参（又名水须、水浚）、 （《尔雅》，音覃）、 藩（音沉烦）、苦心（《别录》）、儿草（《别录》，又名儿踵草、女雷、女理、鹿列、韭逢、东根、野蓼、昌支）
 时珍曰︰宿根之旁，初生子根，状如 虻之状，故谓之 母，讹为知母、 母也。馀多未详。
 【发明】
 权曰︰知母治诸热劳，患人虚而口干者，加用之。
@@ -16315,16 +15837,11 @@
       <c r="H44" s="7" t="inlineStr">
         <is>
           <t>粳米（粳）
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归脾、胃、肺经
-【主治】
-补中益气，健脾和胃，除烦渴，止泻痢
-【释名】
-秔（《说文》与粳同）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归脾、胃、肺经。
+【主治】补中益气，健脾和胃，除烦渴，止泻痢。
+【释名】秔（《说文》与粳同）。
 时珍曰︰粳乃谷稻之总名也，有早、中、晚三收。诸本草独以晚稻为粳者，非矣。粘者为糯，不粘者为粳。糯者懦也，粳者硬也。但入解热药，以晚粳为良尔。
 【发明】
 诜曰︰粳米赤者粒大而香，水渍之有味益人。大抵新熟者动气，经再年者亦发病。惟江南人多收火稻贮仓，烧去毛，至春舂米食之，即不发病宜人，温中益气，补下元也。
@@ -16379,16 +15896,11 @@
       <c r="H45" s="7" t="inlineStr">
         <is>
           <t>胆南星（虎掌）
-【气味】
-味苦、微辛，性凉
-【毒性】
-有毒
-【归经】
-归肺、肝、脾经
-【主治】
-清热化痰，息风定惊
-【释名】
-虎膏（《纲目》）、鬼蒟蒻（《日华》）。
+【气味】味苦、微辛，性凉。
+【毒性】有毒。
+【归经】归肺、肝、脾经。
+【主治】清热化痰，息风定惊。
+【释名】虎膏（《纲目》）、鬼蒟蒻（《日华》）。
 恭曰︰其根四畔有圆牙，看如虎掌，故有此名。
 颂曰︰天南星即本草虎掌也，小者名由跋。古方多用虎掌，不言天南星。南星近出唐人中风痰毒方中用之，乃后人采用，别立此名尔。
 时珍曰︰虎掌因叶形似之，非根也。南星因根圆白，形如老人星状，故名南星，即虎掌也。苏颂说甚明白。宋《开宝》不当重出南星条，今并入。
@@ -16442,16 +15954,11 @@
       <c r="H46" s="7" t="inlineStr">
         <is>
           <t>瓜蒌仁（栝蒌）
-【气味】
-味甘，性寒
-【毒性】
-无毒
-【归经】
-归肺、胃、大肠经
-【主治】
-润肺化痰，滑肠通便
-【释名】
-果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
+【气味】味甘，性寒。
+【毒性】无毒。
+【归经】归肺、胃、大肠经。
+【主治】润肺化痰，滑肠通便。
+【释名】果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
 根名白药（《图经》）、天花粉（《图经》）、瑞雪（《赵宜真》）。
 时珍曰︰裸，与蓏同。
 许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
@@ -16505,20 +16012,14 @@
       <c r="H47" s="7" t="inlineStr">
         <is>
           <t>黄芩
-【气味】
-味苦，性寒
-【毒性】
-无毒
-【归经】
-归肺、胆、脾、大肠、小肠经
-【主治】
-清热燥湿，泻火解毒，止血，安胎
-【释名】
-腐肠（《本经》）、空肠（《别录》）、内虚（《别录》）、妒妇（《吴普》）、经芩 （《别录》）、黄文（《别录》）、印头（《吴普》）、苦督邮（《记事》），内实者名子芩（弘景）、条芩（《纲目》）、 尾芩（《唐本》）、鼠尾芩（《纲目》）。
+【气味】味苦，性寒。
+【毒性】无毒。
+【归经】归肺、胆、脾、大肠、小肠经。
+【主治】清热燥湿，泻火解毒，止血，安胎。
+【释名】腐肠（《本经》）、空肠（《别录》）、内虚（《别录》）、妒妇（《吴普》）、经芩 （《别录》）、黄文（《别录》）、印头（《吴普》）、苦督邮（《记事》），内实者名子芩（弘景）、条芩（《纲目》）、 尾芩（《唐本》）、鼠尾芩（《纲目》）。
 弘景曰：圆者，名子芩；破者，名宿芩，其腹中皆烂，故名腐肠。
 时珍曰：芩，《说文》作 ，谓其色黄也。或云芩者，黔也，黔乃黄黑之色也。宿芩乃旧根，多中空，外黄内黑，即今所谓片芩，故又有腐肠、妒妇诸名。妒 妇心黯，故以比之。子芩乃新根，多内实，即今所谓条芩。或云西芩多中空而色黔，北芩多内实而深黄。
-【发明】
-杲曰：黄芩之中枯而飘者，泻肺火，利气，消痰，除风热，清肌表之热；细实而坚者，泻大肠火，养阴退阳，补膀胱寒水，滋其化源。高下之分与枳实、枳壳同例。
+【发明】杲曰：黄芩之中枯而飘者，泻肺火，利气，消痰，除风热，清肌表之热；细实而坚者，泻大肠火，养阴退阳，补膀胱寒水，滋其化源。高下之分与枳实、枳壳同例。
 元素曰：黄芩之用有九：泻肺热，一也；上焦皮肤风热风湿，二也；去诸热，三也；利胸中气，四也；消痰膈，五也；除脾经诸湿，六也；夏月须用，七也；妇人产后养阴退阳，八也；安胎，九也。酒炒上行，主上部积血，非此不能除。下痢脓血，腹痛后重，身热久不能止者，与芍药、甘草同用之。凡诸疮痛不可忍者，宜芩、连苦寒之药，详上下，分身、梢及引经药用之。
 震亨曰：黄芩降痰，假其降火也。凡去上焦湿热，须以酒洗过用。片芩泻肺火，须用桑白皮佐之。若肺虚者，多用则伤肺，必先以天门冬保定肺气而后用之。黄芩、白术乃安胎圣药，俗以黄芩为寒而不敢用，盖不知胎孕宜清热凉血，血不妄行，乃能养胎。黄芩乃上、中二焦药，能降火下行，白术能补脾也。
 罗天益曰：肺主气，热伤气，故身体麻木。又五臭入肺为腥，故黄芩之苦寒，能泻火、补气而利肺，治喉中腥臭。颂曰：张仲景治伤寒心下痞满，泻心汤。凡四方皆用黄芩，以其主诸热、利小肠故也。又太阳病下之利不止，喘而汗出者，有葛根黄芩黄连汤，及主妊娠安胎散，亦多用之。
@@ -16570,16 +16071,11 @@
       <c r="H48" s="7" t="inlineStr">
         <is>
           <t>枳实（枳）
-【气味】
-味苦、辛、酸，性微寒
-【毒性】
-无毒
-【归经】
-归脾、胃、大肠经
-【主治】
-破气消积，化痰散痞
-【释名】
-子名枳实（《本经》）、枳壳（宋《开宝》）。
+【气味】味苦、辛、酸，性微寒。
+【毒性】无毒。
+【归经】归脾、胃、大肠经。
+【主治】破气消积，化痰散痞。
+【释名】子名枳实（《本经》）、枳壳（宋《开宝》）。
 宗奭曰：枳实、枳壳，一物也。小则其性酷而速，大则其性详而缓。故张仲景治伤寒仓猝之病，承气汤中用枳实，皆取其疏通、决泄、破结实之义。他方但导败风壅之气，可常服者，故用枳壳，其义如此。
 恭曰：既称枳实，须合核瓤，今殊不然。
 时珍曰：枳乃木名，从只，谐声也。实乃其子，故曰枳实。后人因小者性速，又呼老者为枳壳。生则皮厚而实，熟则壳薄而虚，正如青橘皮、陈橘皮之义。宋人复出枳壳一条，非矣。寇氏以为破结实而名，亦未必然。
@@ -16635,16 +16131,11 @@
       <c r="H49" s="7" t="inlineStr">
         <is>
           <t>人参
-【气味】
-味甘、微苦，性微温
-【毒性】
-无毒
-【归经】
-归脾、肺、心经
-【主治】
-大补元气，复脉固脱，益气摄血，生津安神
-【释名】
-人薓（音参。或省作参）、黄参（《吴普》）、血参（《别录》）、人衔（《本经》）、鬼盖（《本经》）、神草（《别录》）、土精（《别录》）、地精（《广雅》）、海腴、皱面还丹（《广雅》）。
+【气味】味甘、微苦，性微温。
+【毒性】无毒。
+【归经】归脾、肺、心经。
+【主治】大补元气，复脉固脱，益气摄血，生津安神。
+【释名】人薓（音参。或省作参）、黄参（《吴普》）、血参（《别录》）、人衔（《本经》）、鬼盖（《本经》）、神草（《别录》）、土精（《别录》）、地精（《广雅》）、海腴、皱面还丹（《广雅》）。
 时珍曰︰人薓年深，浸渐长成者，根如人形，有神，故谓之人薓、神草。薓字，从𣹰，亦浸渐之义。𣹰，即浸字，后世因字文繁，遂以参星之字代之，从简便尔。然承误日久，亦不能变矣，惟张仲景《伤寒论》尚作薓字。《别录》一名人微，微乃薓字之讹也。其成有阶级，故曰人衔。其草背阳向阴，故曰鬼盖。其在五参，色黄属土，而补脾胃，生阴血，故有黄参、血参之名。得地之精灵，故有土精、地精之名。《广五行记》云︰隋文帝时，上党有人宅后每夜闻人呼声，求之不得。去宅一里许，见人参枝叶异常，掘之入地五尺，得人参，一如人体，四肢毕备，呼声遂绝。观此，则土精之名，尤可证也。《礼斗威仪》云︰下有人参，上有紫气。《春秋运斗枢》云︰摇光星散而为人参。人君废山渎之利，则摇光不明，人参不生。观此，则神草之名，又可证矣。
 【发明】
 弘景曰︰人参为药切要，与甘草同功。
@@ -16699,16 +16190,11 @@
       <c r="H50" s="7" t="inlineStr">
         <is>
           <t>熟地黄（地黄）
-【气味】
-味甘，性微温
-【毒性】
-无毒
-【归经】
-归肝、肾经
-【主治】
-补血滋阴，益精填髓
-【释名】
-芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
+【气味】味甘，性微温。
+【毒性】无毒。
+【归经】归肝、肾经。
+【主治】补血滋阴，益精填髓。
+【释名】芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
 大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
 时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
 【发明】
@@ -16765,16 +16251,11 @@
       <c r="H51" s="7" t="inlineStr">
         <is>
           <t>五味子
-【气味】
-味酸、甘，性温
-【毒性】
-无毒
-【归经】
-归肺、心、肾经
-【主治】
-收敛固涩，益气生津，补肾宁心
-【释名】
-荎藸 （《尔雅》，音知除）、玄及（《别录》）、会及（《别录》）。
+【气味】味酸、甘，性温。
+【毒性】无毒。
+【归经】归肺、心、肾经。
+【主治】收敛固涩，益气生津，补肾宁心。
+【释名】荎藸 （《尔雅》，音知除）、玄及（《别录》）、会及（《别录》）。
 恭曰︰五味，皮、肉甘、酸，核中辛、苦，都有咸味，此则五味具也。《本经》但云味酸，当以木为五行之先也。
 【发明】
 成无己曰︰肺欲收，急食酸以收之，以酸补之。芍药、五味之酸，以收逆气而安肺。
@@ -16833,16 +16314,11 @@
       <c r="H52" s="27" t="inlineStr">
         <is>
           <t>紫菀
-【气味】
-味辛、苦，性温
-【毒性】
-无毒
-【归经】
-归肺经
-【主治】
-润肺下气，化痰止咳
-【释名】
-青菀（《别录》）、紫蒨（《别录》）、返魂草（《纲目》）、夜牵牛（《斗门方》）。
+【气味】味辛、苦，性温。
+【毒性】无毒。
+【归经】归肺经。
+【主治】润肺下气，化痰止咳。
+【释名】青菀（《别录》）、紫蒨（《别录》）、返魂草（《纲目》）、夜牵牛（《斗门方》）。
 时珍曰︰其根色紫而柔宛，故名许慎《说文》作茈菀。《斗门方》谓之返魂草。
 【发明】</t>
         </is>
@@ -16892,16 +16368,11 @@
       <c r="H53" s="7" t="inlineStr">
         <is>
           <t>桑白皮（桑）
-【气味】
-味甘，性寒
-【毒性】
-无毒
-【归经】
-归肺经
-【主治】
-泻肺平喘，利水消肿
-【释名】
-子名椹（《集韵》）。
+【气味】味甘，性寒。
+【毒性】无毒。
+【归经】归肺经。
+【主治】泻肺平喘，利水消肿。
+【释名】子名椹（《集韵》）。
 时珍曰︰徐锴《说文解字》云︰桑，音若，东方自然神木之名，其字象形。桑乃蚕所食，异于东方自然之神木，故加木于桑下而别之。《典术》云︰桑乃箕星之精。
 【发明】
 杲曰︰桑白皮，甘以固元气之不足而补虚，辛以泻肺气之有馀而止嗽。又云︰桑白皮泻肺，然性不纯良，不宜多用。
@@ -16954,20 +16425,14 @@
       <c r="H54" s="7" t="inlineStr">
         <is>
           <t>麦门冬
-【气味】
-味甘、微苦，性微寒
-【毒性】
-无毒
-【归经】
-归心、肺、胃经
-【主治】
-养阴生津，润肺清心
-【释名】
-虋冬（音门《尔雅》），秦名羊韭、齐名爱韭、楚名马韭、越名羊耆（并《别录》）。禹韭（《吴普》）、禹余粮（《别录》）、忍冬（《吴普》）、忍凌（《吴普》）、不死药（《吴普》）、阶前草（《梅尧臣诗》）。
+【气味】味甘、微苦，性微寒。
+【毒性】无毒。
+【归经】归心、肺、胃经。
+【主治】养阴生津，润肺清心。
+【释名】虋冬（音门《尔雅》），秦名羊韭、齐名爱韭、楚名马韭、越名羊耆（并《别录》）。禹韭（《吴普》）、禹余粮（《别录》）、忍冬（《吴普》）、忍凌（《吴普》）、不死药（《吴普》）、阶前草（《梅尧臣诗》）。
 弘景曰：根似穬麦，故谓之麦门冬。
 时珍曰︰麦须曰虋，此草根似麦而有须，其叶如韭，凌冬不凋，故谓之麦 冬，及有诸韭、忍冬诸名。俗作门冬，便于字也。可以服食断谷，一名仆垒，一名随脂。
-【发明】
-宗奭曰︰麦门冬治肺热之功为多，其味苦，但专泄而不专收，寒多人禁服。治心肺虚热及虚劳。与地黄、阿胶、麻仁，同为润经益血、复脉通心之剂；与五味子、枸杞子，同为生脉之剂。
+【发明】宗奭曰︰麦门冬治肺热之功为多，其味苦，但专泄而不专收，寒多人禁服。治心肺虚热及虚劳。与地黄、阿胶、麻仁，同为润经益血、复脉通心之剂；与五味子、枸杞子，同为生脉之剂。
 元素曰︰麦门冬治肺中伏火、脉气欲绝者，加五味子、人参二味为生脉散，补肺中元气不足。
 杲曰︰六七月间湿热方旺，人病骨乏无力，身重气短，头旋眼黑，甚则痿软。故孙真人以生脉散补其天元真气。脉者，人之元气也。人参之甘寒，泻热火而益元气。麦门冬之苦寒，滋燥金而清水源。五味子之酸温，泻丙火而补庚金，兼益五脏之气也。
 时珍曰︰按︰赵继宗《儒医精要》云︰麦门冬以地黄为使，服之令人头不白，补髓，通肾气，定喘促，令人肌体滑泽，除身上一切恶气不洁之疾，盖有君而有使也。若有君无使，是独行无功矣。此方惟火盛气壮之人服之相宜。若气弱胃寒者，必不可饵也。</t>
@@ -17018,16 +16483,11 @@
       <c r="H55" s="7" t="inlineStr">
         <is>
           <t>玉竹（萎蕤）
-【气味】
-味甘，性微寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-养阴润燥，生津止渴
-【释名】
-女萎（《本经》）、葳蕤（《吴普》）、萎 （音威移）、委萎（《尔雅》）、萎香（《纲目》）、荧（《尔雅》，音行）、玉竹（《别录》）、地节（《别录》）。
+【气味】味甘，性微寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】养阴润燥，生津止渴。
+【释名】女萎（《本经》）、葳蕤（《吴普》）、萎 （音威移）、委萎（《尔雅》）、萎香（《纲目》）、荧（《尔雅》，音行）、玉竹（《别录》）、地节（《别录》）。
 时珍曰︰按︰黄公绍《古今韵会》云︰葳蕤，草木叶垂之貌。此草根长多须，如冠缨下垂之 而有威仪，故以名之。凡羽盖旌旗之缨 ，皆象葳蕤，是矣。张氏《瑞应图》云︰王者礼备，则葳蕤生于殿前。一名萎香。则威仪之义，于此可见。《别录》作葳蕤，省文也。《说文》作萎 ，音相近也。《尔雅》作委萎，字相近也。其叶光莹而象竹，其根多节，故有荧及玉竹、地节诸名。《吴普本草》又有乌女、虫蝉之名。宋本一名马熏，即乌萎之讹者也。
 【发明】
 杲曰︰葳蕤能升能降，阳中阴也。其用有四︰主风淫四末，两目泪烂，男子湿注腰痛，女子面生黑 。
@@ -17082,16 +16542,11 @@
       <c r="H56" s="7" t="inlineStr">
         <is>
           <t>天花粉（栝蒌）
-【气味】
-味甘、微苦，性微寒
-【毒性】
-无毒
-【归经】
-归肺、胃经
-【主治】
-清热泻火，生津止渴，消肿排脓
-【释名】
-果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
+【气味】味甘、微苦，性微寒。
+【毒性】无毒。
+【归经】归肺、胃经。
+【主治】清热泻火，生津止渴，消肿排脓。
+【释名】果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
 根名白药（《图经》）、天花粉（《图经》）、瑞雪（《赵宜真》）。
 时珍曰︰裸，与蓏同。
 许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
@@ -17146,16 +16601,11 @@
       <c r="H57" s="7" t="inlineStr">
         <is>
           <t>扁豆（藊豆）
-【气味】
-味甘，性微温
-【毒性】
-无毒
-【归经】
-归脾、胃经
-【主治】
-健脾化湿，和中消暑
-【释名】
-沿篱豆（俗）、蛾眉豆（《纲目》）。
+【气味】味甘，性微温。
+【毒性】无毒。
+【归经】归脾、胃经。
+【主治】健脾化湿，和中消暑。
+【释名】沿篱豆（俗）、蛾眉豆（《纲目》）。
 时珍曰︰ 藊本作扁，荚形扁也。沿篱，蔓延也。蛾眉，象豆脊白路之形也。
 【发明】
 时珍曰︰硬壳白扁豆，其子充实，白而微黄，其气腥香，其性温平，得乎中和，脾之谷也。入太阴气分，通利三焦，能化清降浊，故专治中宫之病，消暑除湿而解毒也。其软壳及黑鹊色者，其性微凉，但可供食，亦调脾胃。</t>
@@ -17206,16 +16656,11 @@
       <c r="H58" s="7" t="inlineStr">
         <is>
           <t>生地黄（地黄）
-【气味】
-味甘、苦，性寒
-【毒性】
-无毒
-【归经】
-归心、肝、肾经
-【主治】
-清热凉血，养阴生津
-【释名】
-芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
+【气味】味甘、苦，性寒。
+【毒性】无毒。
+【归经】归心、肝、肾经。
+【主治】清热凉血，养阴生津。
+【释名】芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
 大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
 时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
 【发明】
@@ -17271,16 +16716,11 @@
       <c r="H59" s="7" t="inlineStr">
         <is>
           <t>天门冬
-【气味】
-味甘、苦，性寒
-【毒性】
-无毒
-【归经】
-归肺、肾经
-【主治】
-养阴润燥，清肺生津
-【释名】
-虋冬（音门《尔雅》）、颠勒（《本经》）、天棘（《纲目》）、万岁藤（《救荒》）。
+【气味】味甘、苦，性寒。
+【毒性】无毒。
+【归经】归肺、肾经。
+【主治】养阴润燥，清肺生津。
+【释名】虋冬（音门《尔雅》）、颠勒（《本经》）、天棘（《纲目》）、万岁藤（《救荒》）。
 禹锡曰︰按︰《尔雅》云︰蔷蘼，虋冬。注云︰门冬也，一名满冬。《抱朴子》云︰一名颠棘，或名地门冬，或名筵门冬。在东岳名淫羊藿；在中岳名天门冬；在西岳名管松；在北岳，名无不愈；在南岳名百部；在京陆山阜名颠棘；在越人，名浣草。虽处处有之，其名不同，其实一也。别有百部草，其根有百许如一，而苗小异，其苗似菝 ，惟可治咳，不中服食，须分别之。
 时珍曰︰草之茂者为 ，俗作门。此草蔓茂，而功同麦门冬，故曰天门冬，或曰天棘。《尔雅》云︰髦，颠棘也。因其细叶如髦，有细棘也。颠、天，音相近也。按︰《救荒本草》云︰俗名万岁藤，又名娑萝树。其形与治肺之功颇同百部，故亦名百部也。蔷蘼乃营实苗，而《尔雅》指为虋冬，盖古书错简也。
 【发明】
@@ -17340,16 +16780,11 @@
       <c r="H60" s="7" t="inlineStr">
         <is>
           <t>玄参
-【气味】
-味甘、苦、咸，性微寒
-【毒性】
-无毒
-【归经】
-归肺、胃、肾经
-【主治】
-清热凉血，滋阴降火，解毒散结
-【释名】
-黑参（《纲目》）、玄台（《吴普》）、重台（《本经》）、鹿肠（《吴普》）、正马（《别录》）、逐马（《药性》）、馥草（《开宝》）、野脂麻（《纲目》）、鬼藏（《吴普》）。时珍曰︰玄，黑色也。《别录》一名端，一名咸，多未详。
+【气味】味甘、苦、咸，性微寒。
+【毒性】无毒。
+【归经】归肺、胃、肾经。
+【主治】清热凉血，滋阴降火，解毒散结。
+【释名】黑参（《纲目》）、玄台（《吴普》）、重台（《本经》）、鹿肠（《吴普》）、正马（《别录》）、逐马（《药性》）、馥草（《开宝》）、野脂麻（《纲目》）、鬼藏（《吴普》）。时珍曰︰玄，黑色也。《别录》一名端，一名咸，多未详。
 弘景曰︰其茎微似人参，故得参名。志曰︰合香家用之，故俗呼馥草。
 【发明】
 元素曰︰玄参乃枢机之剂，管领诸气上下，清肃而不浊，风药中多用之。故《活人书》治伤寒阳毒，汗下后毒不散，及心下懊 ，烦不得眠，心神颠倒欲绝者，俱用玄参。以此论之，治胸中氤氲之气，无根之火，当以玄参为圣剂也。
@@ -17401,16 +16836,11 @@
       <c r="H61" s="7" t="inlineStr">
         <is>
           <t>丹参
-【气味】
-味苦，性微寒
-【毒性】
-无毒
-【归经】
-归心、肝经
-【主治】
-活血祛瘀，通经止痛，清心除烦，凉血消痈
-【释名】
-赤参（《别录》）、山参（《日华》）、 蝉草（《本经》）、木羊乳（《吴普》）、逐马（弘景）、奔马草（《四声》）。
+【气味】味苦，性微寒。
+【毒性】无毒。
+【归经】归心、肝经。
+【主治】活血祛瘀，通经止痛，清心除烦，凉血消痈。
+【释名】赤参（《别录》）、山参（《日华》）、 蝉草（《本经》）、木羊乳（《吴普》）、逐马（弘景）、奔马草（《四声》）。
 时珍曰︰五参五色配五脏。故人参入脾，曰黄参；沙参入肺，曰白参；玄参入肾，曰黑参；牡蒙入肝，曰紫参；丹参入心，曰赤参。其苦参，则右肾命门之药也。古人舍紫参而称苦参，未达此义尔。炳曰︰丹参治风软脚，可逐奔马，故名奔马草。曾用，实有效。
 【发明】
 时珍曰︰丹参色赤味苦，气平而降，阴中之阳也。入手少阴、厥阴之经，心与包络血分药也。按︰《妇人明理论》云︰四物汤治妇人病，不问产前、产后，经水多少，皆可通用。惟一味丹参散，主治与之相同。盖丹参能破宿血，补新血，安生胎，落死胎，止崩中带下，调经脉，其功大类当归、地黄、芎 、芍药故也。</t>
@@ -17461,16 +16891,11 @@
       <c r="H62" s="7" t="inlineStr">
         <is>
           <t>茯神（茯苓）
-【气味】
-味甘、淡，性平
-【毒性】
-无毒
-【归经】
-归心、脾经
-【主治】
-宁心安神，利水渗湿
-【释名】
-伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
+【气味】味甘、淡，性平。
+【毒性】无毒。
+【归经】归心、脾经。
+【主治】宁心安神，利水渗湿。
+【释名】伏灵（《纲目》）、伏菟（《本经》）、松腴、不死面（《记事珠》），抱根者名伏神（《别录》）。
 宗奭曰︰多年樵斫之松根之气味，抑郁未绝，精英未沦。其精气盛者，发泄于外，结为茯苓，故不抱根，离其本体，有零之义也。津气不盛，只能附结本根，既不离本，故曰伏神。
 时珍曰︰茯苓，《史记•龟策传》作伏灵。盖松之神灵之气，伏结而成，故谓之伏灵、伏神也。《仙经》言︰伏灵大如拳者，佩之令百鬼消灭，则神灵之气，亦可征矣。俗作苓者，传写之讹尔。下有伏灵，上有菟丝，故又名伏莬。或云“其形如兔，故名”，亦通。
 【发明】
@@ -17525,18 +16950,12 @@
       <c r="H63" s="7" t="inlineStr">
         <is>
           <t>酸枣仁（酸枣）
-【气味】
-味甘、酸，性平
-【毒性】
-无毒
-【归经】
-归肝、胆、心经
-【主治】
-养心补肝，宁心安神，敛汗生津
-【释名】
-樲（《尔雅》）、山枣（《弘景》）。
-【发明】
-恭曰︰《本经》用实疗不得眠，不言用仁。今方皆用仁。补中益肝，坚筋骨，助阴气，皆酸枣仁之功也。
+【气味】味甘、酸，性平。
+【毒性】无毒。
+【归经】归肝、胆、心经。
+【主治】养心补肝，宁心安神，敛汗生津。
+【释名】樲（《尔雅》）、山枣（《弘景》）。
+【发明】恭曰︰《本经》用实疗不得眠，不言用仁。今方皆用仁。补中益肝，坚筋骨，助阴气，皆酸枣仁之功也。
 宗奭曰︰酸枣，《经》不言用仁，而今天下皆用之。
 志曰︰按︰《五代史‧后唐》刊石药验云︰酸枣仁，睡多生使，不得睡炒熟。陶云食之醒睡，而《经》云疗不得眠。盖其子肉味酸，食之使不思睡；核中仁服之，疗不得眠。正如麻黄发汗，根节止汗也。
 时珍曰︰酸枣实，味酸性收，故主肝病，寒热结气，酸痹久泄，脐下满痛之症。其仁甘而润，故熟用疗胆虚不得眠、烦渴虚汗之症，生用疗胆热好眠，皆足厥阴、少阳药也。今人专以为心家药，殊昧此理。</t>
@@ -17587,16 +17006,11 @@
       <c r="H64" s="7" t="inlineStr">
         <is>
           <t>柏子仁（柏）
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归心、肾、大肠经
-【主治】
-养心安神，润肠通便，止汗
-【释名】
-椈（音菊《尔雅》）、侧柏（《尔雅翼》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归心、肾、大肠经。
+【主治】养心安神，润肠通便，止汗。
+【释名】椈（音菊《尔雅》）、侧柏（《尔雅翼》）。
 李时珍曰︰按︰魏子才《六书精蕴》云︰万木皆向阳，而柏独西指，盖阴木而有贞德者，故字从白。白者，西方也。陆佃《埤雅》云︰柏之指西，犹针之指南也。柏有数种，入药惟取叶扁而侧生者，故曰侧柏。
 寇宗奭曰︰予官陕西，登高望柏，千万株皆一一西指。盖此木至坚，不畏霜雪，得木之正气，他木不及。所以受金之正气所制，一一西指也。
 【发明】
@@ -17650,16 +17064,11 @@
       <c r="H65" s="7" t="inlineStr">
         <is>
           <t>远志
-【气味】
-味苦、辛，性温
-【毒性】
-无毒
-【归经】
-归心、肾、肺经
-【主治】
-安神益智，交通心肾，祛痰，消肿
-【释名】
-苗名小草（《本经》）、细草（《本经》）、棘菀（《本经》）、 绕（《本经》）。
+【气味】味苦、辛，性温。
+【毒性】无毒。
+【归经】归心、肾、肺经。
+【主治】安神益智，交通心肾，祛痰，消肿。
+【释名】苗名小草（《本经》）、细草（《本经》）、棘菀（《本经》）、 绕（《本经》）。
 时珍曰︰此草服之能益智强志，故有远志之称。《世说》载郝隆讥谢安云︰处则为远志，出则为小草。《记事珠》谓之醒心杖。
 【发明】
 好古曰︰远志，肾经气分药也。
@@ -17711,16 +17120,11 @@
       <c r="H66" s="7" t="inlineStr">
         <is>
           <t>肉桂（桂）
-【气味】
-味辛、甘，性大热
-【毒性】
-无毒
-【归经】
-归肾、脾、心、肝经。
-【主治】
-补火助阳，引火归元，散寒止痛，温通经脉
-【释名】
-时珍曰︰按︰范成大《桂海志》云︰凡木叶心皆一纵理，独桂有两道如圭形，故字从圭。
+【气味】味辛、甘，性大热。
+【毒性】无毒。
+【归经】归肾、脾、心、肝经。
+【主治】补火助阳，引火归元，散寒止痛，温通经脉。
+【释名】时珍曰︰按︰范成大《桂海志》云︰凡木叶心皆一纵理，独桂有两道如圭形，故字从圭。
 陆佃《埤雅》云︰桂犹圭也。宣导百药，为之先聘通使，如执圭之使也。《尔雅》谓之梫者，能侵害他木也。故《吕氏春秋》云︰桂枝之下无杂木。《雷公炮炙论》云︰桂钉木根，其木即死，是也。桂即牡桂之浓而辛烈者，牡桂即桂之薄而味淡者，《别录》不当重出，今并为一，而分目于下。
 【发明】
 承曰︰凡桂之浓实气味重者，宜入治水脏及下焦药；轻薄气味淡者，宜入治头目发散药。故《本经》以菌桂养精神，牡桂利关节。仲景发汗用桂枝，乃枝条，非身干也，取其轻薄能发散。又有一种柳桂，乃桂之嫩小枝条，尤宜入上焦药用。
@@ -17775,16 +17179,11 @@
       <c r="H67" s="7" t="inlineStr">
         <is>
           <t>木通（通草）
-【气味】
-味苦，性寒
-【毒性】
-无毒
-【归经】
-归心、小肠、膀胱经
-【主治】
-利尿通淋，清心除烦，通经下乳
-【释名】
-木通（士良）、附支（《本经》）、丁翁（《吴普》）、万年藤（甄权），子名燕覆（《唐本》）。
+【气味】味苦，性寒。
+【毒性】无毒。
+【归经】归心、小肠、膀胱经。
+【主治】利尿通淋，清心除烦，通经下乳。
+【释名】木通（士良）、附支（《本经》）、丁翁（《吴普》）、万年藤（甄权），子名燕覆（《唐本》）。
 时珍曰︰有细细孔，两头皆通，故名通草，即今所谓木通也。今之通草，乃古之通脱木也。宋本草混注为一，名实相乱，今分出之。
 【发明】
 杲曰︰本草十剂︰通可去滞，通草、防己之属是也。夫防己大苦寒，能泻血中湿热之滞，又通大便。通草甘淡，能助西方秋气下降，利小便，专泻气滞也。肺受热邪，津液气化之原绝，则寒水断流，膀胱受湿热，癃闭约缩，小便不通，宜此治之。其症胸中烦热，口燥舌干，咽干，大渴引饮，小便淋沥，或闭塞不通，胫酸脚热，并宜通草主之。凡气味与之同者，茯苓、泽泻、灯草、猪苓、琥珀、瞿麦、车前子之类，皆可以渗湿利小便，泄其滞气也。又曰︰木通下行，泄小肠火，利小便，与琥珀同功，无他药可比。
@@ -17836,16 +17235,11 @@
       <c r="H68" s="27" t="inlineStr">
         <is>
           <t>竹茹（竹）
-【气味】
-味甘，性微寒
-【毒性】
-无毒
-【归经】
-归肺、胃、心、胆经
-【主治】
-清热化痰，除烦止呕
-【释名】
-时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+【气味】味甘，性微寒。
+【毒性】无毒。
+【归经】归肺、胃、心、胆经。
+【主治】清热化痰，除烦止呕。
+【释名】时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
 【发明】</t>
         </is>
       </c>
@@ -17894,16 +17288,11 @@
       <c r="H69" s="7" t="inlineStr">
         <is>
           <t>石菖蒲（菖蒲）
-【气味】
-味辛、苦，性温
-【毒性】
-无毒
-【归经】
-归心、胃经
-【主治】
-开窍豁痰，醒神益智，化湿开胃
-【释名】
-昌阳（《本经》）、尧韭（普）、水剑草（《纲目》）。
+【气味】味辛、苦，性温。
+【毒性】无毒。
+【归经】归心、胃经。
+【主治】开窍豁痰，醒神益智，化湿开胃。
+【释名】昌阳（《本经》）、尧韭（普）、水剑草（《纲目》）。
 时珍曰︰菖蒲，乃蒲类之昌盛者，故曰菖蒲。又《吕氏春秋》云︰冬至后五十七日，菖始生。菖者百草之先生者，于是始耕。则菖蒲、昌阳又取此义也。《典术》云︰尧时天降精于庭为韭，感百阴之气为菖蒲。故曰尧韭。方士隐为水剑，因叶形也。
 【发明】
 颂曰︰古方有单服菖蒲法。蜀人治心腹冷气 痛者，取一、二寸捶碎，同吴茱萸煎汤饮之。亦将随行，卒患心痛，嚼一、二寸，热汤或酒送下，亦效。
@@ -17957,19 +17346,13 @@
       <c r="H70" s="7" t="inlineStr">
         <is>
           <t>黄连
-【气味】
-味苦，大寒
-【毒性】
-无毒
-【归经】
-归心、脾、胃、肝、胆、大肠经
-【主治】
-清热燥湿，泻火解毒
-【释名】
-王连（《本经》）、支连（《药性》）。
+【气味】味苦，大寒。
+【毒性】无毒。
+【归经】归心、脾、胃、肝、胆、大肠经。
+【主治】清热燥湿，泻火解毒。
+【释名】王连（《本经》）、支连（《药性》）。
 时珍曰：其根连珠而色黄，故名。
-【发明】
-元素曰：黄连性寒味苦，气味俱浓，可升可降，阴中阳也，入手少阴经。其用有六：泻心脏火，一也；去中焦湿热，二也；诸疮必用，三也；去风湿，四也；赤眼暴发，五也；止中部见血，六也。张仲景治九种心下痞，五等泻心汤，皆用之。
+【发明】元素曰：黄连性寒味苦，气味俱浓，可升可降，阴中阳也，入手少阴经。其用有六：泻心脏火，一也；去中焦湿热，二也；诸疮必用，三也；去风湿，四也；赤眼暴发，五也；止中部见血，六也。张仲景治九种心下痞，五等泻心汤，皆用之。
 成无己曰：苦入心，寒胜热，黄连、大黄之苦寒，以导心下之虚热。蛔得甘则动，得苦 则安，黄连、黄柏之苦，以安蛔也。
 好古曰：黄连苦燥，苦入心，火就燥。泻心者，其实泻脾也，实则泻其子也。
 震亨曰：黄连，去中焦湿热而泻心火。若脾胃气虚，不能转运者，则以茯苓、黄芩代之。以猪胆汁拌炒，佐以龙胆草，则大泻肝胆之火。下痢胃口热禁口者，用黄连、人参煎汤，终日呷之，如吐再强饮，但得一呷下咽便好。
@@ -18030,16 +17413,11 @@
       <c r="H71" s="7" t="inlineStr">
         <is>
           <t>细辛
-【气味】
-味辛，性温
-【毒性】
-小毒
-【归经】
-归肺、肾、心经
-【主治】
-解表散寒，祛风止痛，通窍，温肺化饮
-【释名】
-小辛（《本经》）、少辛（《山海经》）。
+【气味】味辛，性温。
+【毒性】小毒。
+【归经】归肺、肾、心经。
+【主治】解表散寒，祛风止痛，通窍，温肺化饮。
+【释名】小辛（《本经》）、少辛（《山海经》）。
 颂曰：华州真细辛，根细而味极辛，故名之曰细辛。
 时珍曰：小辛、少辛，皆此义也。按《山海经》云，浮戏之山多少辛。《管子》云，五沃之土，群药生少辛，是矣。
 【发明】
@@ -18096,16 +17474,11 @@
       <c r="H72" s="7" t="inlineStr">
         <is>
           <t>柴胡（茈胡）
-【气味】
-味苦、辛，性微寒
-【毒性】
-无毒
-【归经】
-归肝、胆、肺经
-【主治】
-疏散退热，疏肝解郁，升举阳气
-【释名】
-地熏（《本经》）、芸蒿（《别录》）、山菜（《吴普》）、茹草（《吴普》）。
+【气味】味苦、辛，性微寒。
+【毒性】无毒。
+【归经】归肝、胆、肺经。
+【主治】疏散退热，疏肝解郁，升举阳气。
+【释名】地熏（《本经》）、芸蒿（《别录》）、山菜（《吴普》）、茹草（《吴普》）。
 恭曰：茈，是古柴字。《上林赋》云茈姜，及《尔雅》云茈草，并作此茈字。此草根紫色，今太常用茈胡是也。又以木代系，相承呼为柴胡。且检诸本草无名此者。
 时珍曰：茈字，有柴、紫二音。茈姜、茈草之茈，皆音紫；茈胡之茈，音柴。茈胡生山中，嫩则可茹，老则采而为柴，故苗有芸蒿、山菜、茹草之名，而根名柴胡也。苏恭之说殊欠明。古本张仲景《伤寒论》，尚作茈字也
 【发明】
@@ -18162,19 +17535,13 @@
       <c r="H73" s="7" t="inlineStr">
         <is>
           <t>香附（莎根，香附子）
-【气味】
-味辛、微苦、微甘，性平
-【毒性】
-无毒
-【归经】
-归肝、脾、三焦经
-【主治】
-疏肝解郁，理气宽中，调经止痛
-【释名】
-雀头香（《唐本》）、草附子（《图经》）、水香棱（《图经》）、水巴戟（《图经》）、水莎（《图经》）、侯莎（《尔雅》）、莎结（《图经》）、夫须（《别录》）、续根草（《图经》）、地毛（《广雅》）。
+【气味】味辛、微苦、微甘，性平。
+【毒性】无毒。
+【归经】归肝、脾、三焦经。
+【主治】疏肝解郁，理气宽中，调经止痛。
+【释名】雀头香（《唐本》）、草附子（《图经》）、水香棱（《图经》）、水巴戟（《图经》）、水莎（《图经》）、侯莎（《尔雅》）、莎结（《图经》）、夫须（《别录》）、续根草（《图经》）、地毛（《广雅》）。
 时珍曰︰《别录》止云莎草，不言用苗用根。后世皆用其根，名香附子，而不知莎草之名也。其草可为笠及雨衣，疏而不沾，故字从草从沙。亦作蓑字，因其为衣垂 ，如孝子衰衣之状，故又从苔乃笠名，贱夫所须也。其根相附连续而生，可以合香，故谓之香附子。上古谓之雀头香。 按《江表传》云︰魏文帝遣使于吴求雀头香，即此。其叶似三棱及巴戟，而生下湿地，故有水三棱、水巴戟之名。俗人呼为雷公头。《金光明经》谓之月萃哆。《记事珠》谓之抱灵居士。
-【发明】
-好古曰︰香附治膀胱两胁气妨，心忪少气，是能益气，乃血中之气药也。本草不言治崩漏，而方中用治崩漏，是能益气而止血也。又能逐去瘀血，是推陈也。正如巴豆治大便不通而又止泄泻同意。又云︰香附阳中之阴，血中之气药，凡气郁血气必用之。炒黑能止血治崩漏，此妇人之仙药也。多服亦能走气。
+【发明】好古曰︰香附治膀胱两胁气妨，心忪少气，是能益气，乃血中之气药也。本草不言治崩漏，而方中用治崩漏，是能益气而止血也。又能逐去瘀血，是推陈也。正如巴豆治大便不通而又止泄泻同意。又云︰香附阳中之阴，血中之气药，凡气郁血气必用之。炒黑能止血治崩漏，此妇人之仙药也。多服亦能走气。
 震亨曰︰香附须用童子小便浸过，能总解诸郁，凡血气必用之药，引至气分而生血，此正阴生阳长之义。本草不言补，而方家言于老人有益，意有存焉。盖于行中有补理。天之所以为天者，健而有常也。健运不息，所以生生无穷，即此理尔。今即香中亦用之。
 时珍曰︰香附之气平而不寒，香而能窜。其味多辛能散，微苦能降，微甘能和。乃足厥 阴肝、手少阳三焦气分主药，而兼通十二经气分。生则上行胸膈，外达皮肤；熟则下走肝肾，外彻腰足。炒黑则止血，得童溲浸炒则入血分而补虚，盐水浸炒则入血分而润燥，青盐炒则补肾气，酒浸炒则行经络，醋浸炒则消积聚，姜汁炒则化痰饮。得参、术，则补气；得归、，则补血；得木香，则疏滞和中；得檀香则理气醒脾，得沉香则升降诸气，得芎 、苍术 则总解诸郁，得栀子、黄连则能降火热，得茯神则交济心肾，得茴香、破故纸则引气归元，得浓朴、半夏则决壅消胀，得紫苏、葱白则解散邪气，得三棱、莪术则消磨积块，得艾叶则治血气暖子宫，乃气病之总司，女科之主帅也。飞霞子韩 云︰香附能推陈致新，故诸书皆云益气。而俗有耗气之说，宜于女人不宜于男子者，非矣。盖妇人以血用事，气行则无疾。 老人精枯血闭，惟气是资。小儿气日充，则形乃日固。大凡病则气滞而馁，故香附于气分为君药，世所罕知。臣以参、 ，佐以甘草，治虚怯甚速也。 游方外时，悬壶轻赉，治百病黄鹤丹，治妇人青囊丸，随宜用引，辄有小效。人索不已，用者当思法外意可也。黄鹤丹乃铢衣翁在黄鹤楼所授之方，故名。其方用香附一斤，黄连半斤，洗晒为末，水糊丸梧子大。 假如外感，葱姜汤下；内伤，米饮下；气病，木香汤下；血病，酒下；痰病，姜汤下；火病，白汤下。余可类推。青囊丸乃邵应节真人祷母病，感方士所授者。方用香附（略炒）一斤，乌药（略炮）五两三钱，为末，水醋煮面糊为丸。随证用引，如头痛，茶下；痰气，姜汤下；多用酒下，为妙。</t>
         </is>
@@ -18224,16 +17591,11 @@
       <c r="H74" s="7" t="inlineStr">
         <is>
           <t>龙胆草（龙胆）
-【气味】
-味苦，性寒
-【毒性】
-无毒
-【归经】
-归肝、胆经
-【主治】
-清热燥湿，泻肝胆火
-【释名】
-陵游（《本经》）。
+【气味】味苦，性寒。
+【毒性】无毒。
+【归经】归肝、胆经。
+【主治】清热燥湿，泻肝胆火。
+【释名】陵游（《本经》）。
 志曰：叶如龙葵，味苦如胆，因以为名。
 【发明】
 元素曰：龙胆味苦性寒，气味俱浓，沉而降，阴也，足厥阴、少阳经气分药也。其用有四：除下部风湿，一也；及湿热，二也；脐下至足肿痛，三也；寒湿脚气，四也。 下行之功与防己同，酒浸则能上行，外行以柴胡为主，龙胆为使治眼中疾必用之药。好古曰：益肝胆之气而泄火。
@@ -18285,16 +17647,11 @@
       <c r="H75" s="7" t="inlineStr">
         <is>
           <t>泽泻
-【气味】
-味甘、淡，性寒
-【毒性】
-无毒
-【归经】
-归肾、膀胱经
-【主治】
-利小便，清湿热，泄肾浊
-【释名】
-水泻（《本经》）、鹄泻（《本经》）、及泻（《别录》）、蕍（音俞）、芒芋（《本经》）、禹孙（《侯氏药谱》）。
+【气味】味甘、淡，性寒。
+【毒性】无毒。
+【归经】归肾、膀胱经。
+【主治】利小便，清湿热，泄肾浊。
+【释名】水泻（《本经》）、鹄泻（《本经》）、及泻（《别录》）、蕍（音俞）、芒芋（《本经》）、禹孙（《侯氏药谱》）。
 时珍曰︰去水曰泻，如泽水之泻也。禹能治水，故曰禹孙。馀未详。
 【发明】
 颂曰︰《素问》治酒风身热汗出，用泽泻、术；《深师方》治支饮，亦用泽泻、术，但煮法小别尔。张仲景治杂病，心下有支饮苦冒，有泽泻汤，治伤寒有大小泽泻汤、五苓散辈，皆用泽泻，行利停水，为最要药。元素曰︰泽泻乃除湿之圣药，入肾经，治小便淋沥，去阴间汗。无此疾服之，令人目
@@ -18349,16 +17706,11 @@
       <c r="H76" s="7" t="inlineStr">
         <is>
           <t>车前子（车前）
-【气味】
-味甘，性寒
-【毒性】
-无毒
-【归经】
-归肝、肾、肺、小肠经
-【主治】
-清热利尿，渗湿止泻，明目，清肺化痰
-【释名】
-当道（《本经》）、芣苡（音浮以）、马舄（音昔）、牛遗（并《别录》）、牛舌（《诗疏》）、车轮菜（《救荒》）、地衣（《纲目》）、蛤蟆衣（《别录》）。
+【气味】味甘，性寒。
+【毒性】无毒。
+【归经】归肝、肾、肺、小肠经。
+【主治】清热利尿，渗湿止泻，明目，清肺化痰。
+【释名】当道（《本经》）、芣苡（音浮以）、马舄（音昔）、牛遗（并《别录》）、牛舌（《诗疏》）、车轮菜（《救荒》）、地衣（《纲目》）、蛤蟆衣（《别录》）。
 时珍曰︰按《尔雅》云︰芣苡，马舄。马舄，车前。陆玑《诗疏》云︰此草牛马迹中，故有车前、当道、马舄、牛遗之名。舄，足履也。幽州人谓之牛舌草。虾蟆喜藏伏于下，故江东称为虾蟆衣。又《韩诗外传》言︰直曰车前；瞿曰芣苡，恐亦强说也生于两旁者。
 【发明】
 弘景曰︰车前子性冷利，仙经亦服饵之，云令人身轻，能跳越岸谷，不老长生也。
@@ -18412,21 +17764,15 @@
       <c r="H77" s="7" t="inlineStr">
         <is>
           <t>茴香
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归肝、肾、脾、胃经
-【主治】
-散寒止痛，理气和胃
-【释名】
-茴香（《图经》），八月珠（《侯氏药谱》）。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归肝、肾、脾、胃经。
+【主治】散寒止痛，理气和胃。
+【释名】茴香（《图经》），八月珠（《侯氏药谱》）。
 颂曰： 香，北人呼为茴香，声相近也。
 思邈曰：煮臭肉，下少许，即无臭气，臭酱入末亦香，故曰茴香。
 时珍曰：俚俗多怀之衿衽咀嚼，恐 香之名，或以此也。
-【发明】
-诜曰：茴香，国人重之，云有助阳道，未得其方法也。
+【发明】诜曰：茴香，国人重之，云有助阳道，未得其方法也。
 好古曰：茴香，本治膀胱药，以其先丙，故曰小肠也，能润丙燥；以其先戊，故从丙至壬，又手、足少阴二药，以开上下经之通道，所以壬与丙交也。
 时珍曰：小茴香性平，理气开胃，夏月祛蝇辟臭，食料宜之。大茴香性热，多食伤目发疮，食料不宜过用。古方有去铃丸：用茴香二两，连皮生姜四两，同入坩器内腌一伏时，慢火炒之，入盐一两，为末，糊丸梧子大。每服三、五十丸，空心盐酒下。此方本治脾胃虚弱病。茴香得盐则引入肾经，发出邪气。肾不受邪，病自不生也。亦治小肠疝气有效。</t>
         </is>
@@ -18476,16 +17822,11 @@
       <c r="H78" s="7" t="inlineStr">
         <is>
           <t>枸杞子（枸杞地骨皮）
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归肝、肾经
-【主治】
-滋补肝肾，益精明目
-【释名】
-枸 （《尔雅》。音计。《本经》作枸忌）、枸棘（《衍义》）、苦杞（《诗疏》）、红菜头（《图经》）、天精（《抱朴》）、地骨（《本经》）、地辅（《本经》）、地仙（《日华》）、却暑（《别录》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归肝、肾经。
+【主治】滋补肝肾，益精明目。
+【释名】枸 （《尔雅》。音计。《本经》作枸忌）、枸棘（《衍义》）、苦杞（《诗疏》）、红菜头（《图经》）、天精（《抱朴》）、地骨（《本经》）、地辅（《本经》）、地仙（《日华》）、却暑（《别录》）。
 时珍曰︰枸、杞二树名。此物棘如枸之刺，茎如杞之条，故兼名之。道书言︰千载枸杞，其形如犬，故得枸名，未审然否？
 颂曰︰仙人杖有三种︰一是枸杞；一是菜类，叶似苦苣；一是枯死竹竿之色黑者也。
 【发明】
@@ -18542,16 +17883,11 @@
       <c r="H79" s="7" t="inlineStr">
         <is>
           <t>乌药
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归肺、脾、肾、膀胱经
-【主治】
-行气止痛，温肾散寒
-【释名】
-旁其（《拾遗》）、鳑魮（《纲目》）、矮樟（《纲目》）。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归肺、脾、肾、膀胱经。
+【主治】行气止痛，温肾散寒。
+【释名】旁其（《拾遗》）、鳑魮（《纲目》）、矮樟（《纲目》）。
 时珍曰︰乌以色名。其叶状似 鲫鱼，故俗呼为 树。《拾遗》作旁其，方音讹也。南人亦呼为矮樟，其气似樟也。
 【发明】
 宗奭曰︰乌药性和，来气少，走泄多，但不甚刚猛。与沉香同磨作汤点服，治胸腹冷气甚稳当。
@@ -18604,16 +17940,11 @@
       <c r="H80" s="27" t="inlineStr">
         <is>
           <t>沉香
-【气味】
-味辛、苦，性微温
-【毒性】
-无毒
-【归经】
-归脾、胃、肾经
-【主治】
-行气止痛，温中止呕，纳气平喘
-【释名】
-沉水香（《纲目》）、蜜香（《南越志》）。
+【气味】味辛、苦，性微温。
+【毒性】无毒。
+【归经】归脾、胃、肾经。
+【主治】行气止痛，温中止呕，纳气平喘。
+【释名】沉水香（《纲目》）、蜜香（《南越志》）。
 时珍曰︰木之心节置水则沉，故名沉水，亦曰水沉。半沉者为栈香，不沉者为黄熟香。
 《南越志》言︰交州人称为蜜香，谓其气如蜜脾也。梵书名阿迦香。
 【发明】</t>
@@ -18664,16 +17995,11 @@
       <c r="H81" s="7" t="inlineStr">
         <is>
           <t>川楝子（楝）
-【气味】
-味苦，性寒
-【毒性】
-小毒
-【归经】
-归肝、小肠、膀胱经
-【主治】
-疏肝泄热，行气止痛，杀虫
-【释名】
-苦楝（《图经》），实名金铃子（《侯氏药谱》）。
+【气味】味苦，性寒。
+【毒性】小毒。
+【归经】归肝、小肠、膀胱经。
+【主治】疏肝泄热，行气止痛，杀虫。
+【释名】苦楝（《图经》），实名金铃子（《侯氏药谱》）。
 时珍曰︰按︰罗愿《尔雅翼》云︰楝叶可以练物，故谓之楝。其子如小铃，熟则黄色。名金铃，象形也。
 【发明】
 元素曰︰热厥暴痛，非此不能除。
@@ -18725,16 +18051,11 @@
       <c r="H82" s="7" t="inlineStr">
         <is>
           <t>钩藤（钓藤）
-【气味】
-味甘，性凉
-【毒性】
-无毒
-【归经】
-归肝、心包经
-【主治】
-息风定惊，清热平肝
-【释名】
-弘景曰︰出建平。亦作吊藤。疗小儿，不入余方。
+【气味】味甘，性凉。
+【毒性】无毒。
+【归经】归肝、心包经。
+【主治】息风定惊，清热平肝。
+【释名】弘景曰︰出建平。亦作吊藤。疗小儿，不入余方。
 时珍曰︰其刺曲如钓钩，故名。或作吊，从简耳。
 【发明】
 时珍曰︰钓藤，手足厥阴药也。足厥阴主风，手厥阴主火。 惊痫眩晕，皆肝风相火之病。钓藤通心包于肝木，风静火息，则诸证自除。或云︰入数寸</t>
@@ -18785,16 +18106,11 @@
       <c r="H83" s="7" t="inlineStr">
         <is>
           <t>白术（术）
-【气味】
-味苦、甘，性温
-【毒性】
-无毒
-【归经】
-归脾、胃经
-【主治】
-健脾益气，燥湿利水，止汗，安胎
-【释名】
-山蓟（《本经》）、杨桴（音孚）、桴蓟（《尔雅》）、马蓟（《纲目》）、山姜（《别录》）、山连（《别录》）、吃力伽（《日华》）。
+【气味】味苦、甘，性温。
+【毒性】无毒。
+【归经】归脾、胃经。
+【主治】健脾益气，燥湿利水，止汗，安胎。
+【释名】山蓟（《本经》）、杨桴（音孚）、桴蓟（《尔雅》）、马蓟（《纲目》）、山姜（《别录》）、山连（《别录》）、吃力伽（《日华》）。
 时珍曰︰按《六书本义》，术字篆文，象其根干枝叶之形。《吴普本草》一名山芥，一名天蓟。因其叶似蓟，而味似姜、芥也。西域谓之吃力伽，故《外台秘要》有吃力伽散。扬州之域多种白术，其状如桴，故有杨桴及桴蓟之名，今人谓之吴术是也。桴乃鼓槌之名。古方二术通用。后人始有苍、白之分，详见下。
 【发明】
 好古曰︰本草无苍、白术之名。近世多用白术，治皮间风，止汗消痞，补胃和发，有汗则止，与黄耆同功。
@@ -18847,16 +18163,11 @@
       <c r="H84" s="7" t="inlineStr">
         <is>
           <t>苍术
-【气味】
-辛、苦，温
-【毒性】
-无毒
-【归经】
-归脾、胃、肝经
-【主治】
-燥湿健脾，祛风散寒，明目
-【释名】
-赤术（《别录》）、山精（《抱朴》）、仙术（《纲目》）、山蓟（《本经》）。
+【气味】辛、苦，温。
+【毒性】无毒。
+【归经】归脾、胃、肝经。
+【主治】燥湿健脾，祛风散寒，明目。
+【释名】赤术（《别录》）、山精（《抱朴》）、仙术（《纲目》）、山蓟（《本经》）。
 时珍曰︰《异术》言︰术者山之精也，服之令人长生辟谷，致神仙，故有山精、仙术之号。术有赤、白二种，主治虽近，而性味止发不同。本草不分苍、白，亦未可据。今将《本经》并《别录》、甄权、大明四家所说功用，参考分别，各自附方，庶使用者有所依凭。
 【发明】
 宗 曰︰苍术，气味辛烈；白术，微辛苦而不烈。古方及《本经》止言术，未分苍、白。只缘陶隐居言术有两种，自此人多贵白者，往往将苍术置而不用。如古方平胃散之类，苍术为最要药，功效尤速。殊不详本草原无白术之名。嵇康曰︰闻道人遗言，饵术、黄精，令人久寿。亦无白字，用宜两审。
@@ -18913,16 +18224,11 @@
       <c r="H85" s="7" t="inlineStr">
         <is>
           <t>藿香
-【气味】
-味辛，性微温
-【毒性】
-无毒
-【归经】
-归脾、胃、肺经
-【主治】
-芳香化湿，和中止呕，发表解暑
-【释名】
-兜娄婆香（《楞严经》）。
+【气味】味辛，性微温。
+【毒性】无毒。
+【归经】归脾、胃、肺经。
+【主治】芳香化湿，和中止呕，发表解暑。
+【释名】兜娄婆香（《楞严经》）。
 时珍曰︰豆叶曰藿，其叶似之，故名。《楞严经》云︰坛前以兜娄婆香煎水洗浴。即此。《法华经》谓之多摩罗跋香，《金光明经》谓之钵怛罗香，皆兜娄二字梵言也。《涅槃》又谓之迦算香。
 【发明】
 杲曰︰芳香之气助脾胃，故藿香能止呕逆，进饮食。
@@ -18974,16 +18280,11 @@
       <c r="H86" s="7" t="inlineStr">
         <is>
           <t>厚朴（浓朴）
-【气味】
-味苦、辛，性温
-【毒性】
-无毒
-【归经】
-归脾、胃、肺、大肠经
-【主治】
-燥湿消痰，下气除满
-【释名】
-烈朴（《日华》）、赤朴（《别录》）、浓皮（同）、重皮（《广雅》），树名榛（《别录》），子名逐折（《别录》）。
+【气味】味苦、辛，性温。
+【毒性】无毒。
+【归经】归脾、胃、肺、大肠经。
+【主治】燥湿消痰，下气除满。
+【释名】烈朴（《日华》）、赤朴（《别录》）、浓皮（同）、重皮（《广雅》），树名榛（《别录》），子名逐折（《别录》）。
 时珍曰︰其木质朴而皮浓，味辛烈而色紫赤，故有浓朴、烈、赤诸名。
 颂曰︰《广雅》谓之重皮，方书或作浓皮也。
 【发明】
@@ -19039,16 +18340,11 @@
       <c r="H87" s="27" t="inlineStr">
         <is>
           <t>大腹皮（槟榔）
-【气味】
-味辛，性微温
-【毒性】
-无毒
-【归经】
-归脾、胃、大肠、小肠经
-【主治】
-行气宽中，行水消肿
-【释名】
-宾门（李当之《药对》）、仁频（《上林赋》）、洗瘴丹（《候氏药谱》）。
+【气味】味辛，性微温。
+【毒性】无毒。
+【归经】归脾、胃、大肠、小肠经。
+【主治】行气宽中，行水消肿。
+【释名】宾门（李当之《药对》）、仁频（《上林赋》）、洗瘴丹（《候氏药谱》）。
 时珍曰︰宾与郎皆贵客之称。稽含《南方草木状》言︰交广人凡贵胜族客，必先呈此果。若邂逅不设，用相嫌恨。则槟榔名义，盖取于此。雷《炮炙论》谓尖者为槟，圆者为榔，亦似强说。又颜师古注《上林赋》云︰仁频即槟榔也。诜曰︰闽中呼为橄榄子。
 【发明】</t>
         </is>
@@ -19098,16 +18394,11 @@
       <c r="H88" s="7" t="inlineStr">
         <is>
           <t>白芷
-【气味】
-辛，温
-【毒性】
-无毒
-【归经】
-归肺、胃、大肠经
-【主治】
-解表散寒，祛风止痛，宣通鼻窍，燥湿止带，消肿排脓
-【释名】
-白茝（音止，又昌海切《别录》）、芳香（《本经》）、泽芬（《别录》）、苻蓠（《别录》）、䖀（许骄切《吴普》）、莞（音官《别录》）；叶名蒚麻（音力《别录》）、药（音约《图经》）。
+【气味】辛，温。
+【毒性】无毒。
+【归经】归肺、胃、大肠经。
+【主治】解表散寒，祛风止痛，宣通鼻窍，燥湿止带，消肿排脓。
+【释名】白茝（音止，又昌海切《别录》）、芳香（《本经》）、泽芬（《别录》）、苻蓠（《别录》）、䖀（许骄切《吴普》）、莞（音官《别录》）；叶名蒚麻（音力《别录》）、药（音约《图经》）。
 时珍曰︰徐锴云︰初生根干为芷，则白芷之义取乎此也。
 王安石《字说》云︰ 香可以养鼻，又可养体，故 字从臣。臣音怡，养也。
 许慎《说文》云︰晋谓之 ，齐谓之 ，楚谓之蓠，又谓之药。生于下泽，芬芳与兰同德，故骚人以兰 为咏，而本草有芬香、泽芬之名，古人谓之香白芷云。
@@ -19164,16 +18455,11 @@
       <c r="H89" s="7" t="inlineStr">
         <is>
           <t>山药（薯蓣）
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归脾、肺、肾经
-【主治】
-益气养阴，补脾肺肾，固精止带
-【释名】
-藷藇（音诸预《山海经》）、土藷（音除《别录》）、山藷（《图经》）、山芋（《吴普》）、山药（《衍义》）、玉延（《吴普》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归脾、肺、肾经。
+【主治】益气养阴，补脾肺肾，固精止带。
+【释名】藷藇（音诸预《山海经》）、土藷（音除《别录》）、山藷（《图经》）、山芋（《吴普》）、山药（《衍义》）、玉延（《吴普》）。
 吴普曰︰薯蓣，一名薯薯，一名儿草，一名修脆。齐、鲁名山芋，郑、越名土薯，秦、楚名玉延。
 颂曰︰江、闽人单呼为薯（音若殊及韶），亦曰山薯。《山海经》云︰景山北望少泽，其草多薯藇（音同薯蓣）。则是一种，但字（或音殊，或音诸）不一，或语有轻重，或相传之讹耳。
 宗奭曰︰薯蓣，因唐代宗名预，避讳改为薯药；又因宋英宗讳署，改为山药。尽失当日本名。恐岁久以山药为别物，故详著之。
@@ -19229,16 +18515,11 @@
       <c r="H90" s="7" t="inlineStr">
         <is>
           <t>莲子（莲藕）
-【气味】
-味甘、涩，性平
-【毒性】
-无毒
-【归经】
-归脾、肾、心经
-【主治】
-补脾止泻，止带，益肾涩精，养心安神
-【释名】
-其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
+【气味】味甘、涩，性平。
+【毒性】无毒。
+【归经】归脾、肾、心经。
+【主治】补脾止泻，止带，益肾涩精，养心安神。
+【释名】其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
 韩保升曰︰藕生水中，其叶名荷。按︰《尔雅》云︰荷，芙蕖。其茎茄，其叶蕸，其本蔤，其华菡萏，其实莲，其根藕，其中菂，菂中薏。邢昺注云︰芙蕖，总名也，别名芙蓉，江东人呼为荷。菡萏，莲花也。菂，莲实也。薏，菂中青心也。郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
 时珍曰︰《尔雅》以荷为根名，韩氏以荷为叶名，陆机以荷为茎名。按︰茎乃负叶者也，有负荷之义，当从陆说。蔤乃嫩蒻，如竹之行鞭者。节生二茎，一为叶，一为花，尽处乃生藕，为花、叶、根、实之本。显仁藏用，功成不居，可谓退藏于密矣，故谓之蔤。花叶常偶生，不偶不生，故根曰藕。或云藕善耕泥，故字从耦，耦者耕也。茄音加，加于蔤上也。蕸音遐，远于密也。菡萏，函合未发之意。芙蓉，敷布容艳之意。莲者连也，花实相连而出也。菂者的也，子在房中点点如的也。的乃凡物点注之名。薏，犹意也，含苦在内也。古诗云︰食子心无弃，苦心生意存是矣。
 【发明】
@@ -19292,16 +18573,11 @@
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>砂仁
-【气味】
-味辛，性温
-【毒性】
-无毒
-【归经】
-归脾、胃、肾经
-【主治】
-化湿开胃，温脾止泻，理气安胎
-【释名】
-时珍曰︰名义未详。藕下白 多密，取其密藏之意。此物实在根下，仁藏壳内，亦或此意欤。
+【气味】味辛，性温。
+【毒性】无毒。
+【归经】归脾、胃、肾经。
+【主治】化湿开胃，温脾止泻，理气安胎。
+【释名】时珍曰︰名义未详。藕下白 多密，取其密藏之意。此物实在根下，仁藏壳内，亦或此意欤。
 【发明】
 时珍曰︰按韩 《医通》云︰肾恶燥，以辛润之。缩砂仁之辛，以润肾燥。又云︰缩砂属土，主醒脾调胃，引诸药归宿丹田。香而能窜，和合五脏冲和之气，如天地以土 为冲和之气，故补肾药用同地黄丸蒸，取其达下之旨也。又化骨，食草木药及方士炼三黄皆用之，不知其性何以能制此物也？</t>
         </is>
@@ -19351,16 +18627,11 @@
       <c r="H92" s="7" t="inlineStr">
         <is>
           <t>干姜
-【气味】
-味辛，性热
-【毒性】
-无毒
-【归经】
-归脾、胃、肾、心、肺经
-【主治】
-温中散寒，回阳通脉，温肺化饮
-【释名】
-时珍曰：以姜之干者故名，干姜以母姜造之。以白净结实者为良，故人呼为白姜，又曰均姜。凡入药并宜炮用。
+【气味】味辛，性热。
+【毒性】无毒。
+【归经】归脾、胃、肾、心、肺经。
+【主治】温中散寒，回阳通脉，温肺化饮。
+【释名】时珍曰：以姜之干者故名，干姜以母姜造之。以白净结实者为良，故人呼为白姜，又曰均姜。凡入药并宜炮用。
 【发明】
 元素曰：干姜气薄味厚，半沉半浮，可升可降，阳中之阴也。又曰：大辛大热，阳中之阳。其用有四：通心助阳，一也；去脏腑沉寒痼冷，二也；发诸经之寒气，三也；治感寒腹痛，四也。肾中无阳，脉气欲绝，黑附子为引，水煎服之，名姜附汤。亦治中焦寒邪，寒淫所胜，以辛散之也。又能补下焦，故四逆汤用之。干姜本辛，炮之稍苦，故止而不移，所以能治里寒，非若附子行而不止也。理中汤用之者，以其回阳也。
 李杲曰：干姜生辛炮苦，阳也。生则逐寒邪而发表，炮则除胃冷而守中。多用则耗散元气，辛以散之，是壮火食气故也，须以生甘草缓之。辛热以散里寒，同五味子用以温肺，同入参用以温胃也。
@@ -19414,16 +18685,11 @@
       <c r="H93" s="7" t="inlineStr">
         <is>
           <t>山茱萸
-【气味】
-味酸、涩，性微温
-【毒性】
-无毒
-【归经】
-归肝、肾经
-【主治】
-补益肝肾，收涩固脱
-【释名】
-蜀酸枣（《本经》）、肉枣（《纲目》）、鬾实（《别录》）、鸡足（《吴普》）、鼠矢（《吴普》）。
+【气味】味酸、涩，性微温。
+【毒性】无毒。
+【归经】归肝、肾经。
+【主治】补益肝肾，收涩固脱。
+【释名】蜀酸枣（《本经》）、肉枣（《纲目》）、鬾实（《别录》）、鸡足（《吴普》）、鼠矢（《吴普》）。
 宗奭曰︰山茱萸与吴茱萸甚不相类，治疗大不同，未审何缘命此名也？
 时珍曰︰《本经》一名蜀酸枣，今人呼为肉枣，皆象形也。
 【发明】
@@ -19475,16 +18741,11 @@
       <c r="H94" s="7" t="inlineStr">
         <is>
           <t>丹皮（牡丹）
-【气味】
-味苦、辛，性微寒
-【毒性】
-无毒
-【归经】
-归心、肝、肾经
-【主治】
-清热凉血，活血化瘀，退虚热
-【释名】
-鼠姑（《本经》）、鹿韭（《本经》）、百两金（《唐本》）、木芍药（《纲目》）、花王（《洛阳名园记》）。
+【气味】味苦、辛，性微寒。
+【毒性】无毒。
+【归经】归心、肝、肾经。
+【主治】清热凉血，活血化瘀，退虚热。
+【释名】鼠姑（《本经》）、鹿韭（《本经》）、百两金（《唐本》）、木芍药（《纲目》）、花王（《洛阳名园记》）。
 时珍曰︰牡丹，以色丹者为上，虽结子而根上生苗，故谓之牡丹。唐人谓之木芍药，以其花似芍药，而宿干似木也。群花品中，以牡丹第一，芍药第二，故世谓牡丹为花王，芍药为花相。欧阳修《花谱》所载，凡三十馀种。其名或以地，或以人，或以色，或以异，详见本书。
 【发明】
 元素曰︰牡丹乃天地之精，为群花之首。叶为阳，发生也；花为阴，成实也。 丹者赤色，火也。故能泻阴胞中之火。四物东加之，治妇人骨蒸。又曰︰牡丹皮入手厥阴、足少阴，故治无汗之骨蒸；地骨皮入足少阴、手少阳，故治有汗之骨蒸。神不足者手少阴，志不足者足少阴，故仲景肾气丸用之，治神志不足也。又能治肠胃积血，及吐血、衄血，必用之药，故犀角地黄汤用之。
@@ -19537,19 +18798,13 @@
       <c r="H95" s="7" t="inlineStr">
         <is>
           <t>附子
-【气味】
-味辛、甘，性大热
-【毒性】
-有毒
-【归经】
-归心、肾、脾经
-【主治】
-回阳救逆，补火助阳，散寒止痛
-【释名】
-其母名乌头（《本经》）。
+【气味】味辛、甘，性大热。
+【毒性】有毒。
+【归经】归心、肾、脾经。
+【主治】回阳救逆，补火助阳，散寒止痛。
+【释名】其母名乌头（《本经》）。
 时珍曰︰初种为乌头，象乌之头也。附乌头而生者为附子，如子附母也。乌头如芋魁，附子如芋子，盖一物也。别有草乌头、白附子，故俗呼此为黑附子，川乌头以别之。诸家不分乌头有川、草两种，皆混杂注解，今悉正之。
-【发明】
-宗奭曰︰补虚寒须用附子，风家即多用天雄，大略如此。其乌头、乌喙、附子，则量其材而用之。时珍曰︰按王氏《究原方》云︰附子性重滞，温脾逐寒。川乌头性轻疏，温脾去风。若是寒疾即用附子；风疾即用川乌头。一云︰凡人中风，不可先用风药及乌附。 若先用气药，后用乌附乃宜也。又凡用乌、附药，并宜冷服者，热因寒用也。盖阴寒在下，虚阳上浮。治之以寒，则阴气益甚而病增；治之以热，则拒格而不纳。热药冷冻饮料，下嗌之后，冷体既消，热性便发，而病气随愈。不违其情，而致大益，此反治之妙也。昔张仲景治寒疝 内结，用蜜煎乌头。《近效方》治喉痹，用蜜炙附子，含之咽汁。朱丹溪治疝气，用乌头、栀子。并热因寒用也。李东垣治冯翰林侄阴盛格阳伤寒，面赤目赤，烦渴引饮，脉来七、八至，但按之则散。用姜附东加人参，投半斤服之，得汗而愈。此则神圣之妙也。 吴绶曰︰附子乃阴证要药。凡伤寒传变三阴，及中寒夹阴，虽身大热而脉沉者，必用之。或厥冷腹痛，脉沉细，甚则唇青囊缩者，急须用之，有退阴回阳之力，起死回生之功。近 世阴证伤寒，往往疑似，不敢用附子，直待阴极阳竭而用之，已迟矣。且夹阴伤寒，内外皆阴，阳气顿衰。必须急用人参，健脉以益其原；佐以附子，温经散寒。舍此不用，将何以救 之？
+【发明】宗奭曰︰补虚寒须用附子，风家即多用天雄，大略如此。其乌头、乌喙、附子，则量其材而用之。时珍曰︰按王氏《究原方》云︰附子性重滞，温脾逐寒。川乌头性轻疏，温脾去风。若是寒疾即用附子；风疾即用川乌头。一云︰凡人中风，不可先用风药及乌附。 若先用气药，后用乌附乃宜也。又凡用乌、附药，并宜冷服者，热因寒用也。盖阴寒在下，虚阳上浮。治之以寒，则阴气益甚而病增；治之以热，则拒格而不纳。热药冷冻饮料，下嗌之后，冷体既消，热性便发，而病气随愈。不违其情，而致大益，此反治之妙也。昔张仲景治寒疝 内结，用蜜煎乌头。《近效方》治喉痹，用蜜炙附子，含之咽汁。朱丹溪治疝气，用乌头、栀子。并热因寒用也。李东垣治冯翰林侄阴盛格阳伤寒，面赤目赤，烦渴引饮，脉来七、八至，但按之则散。用姜附东加人参，投半斤服之，得汗而愈。此则神圣之妙也。 吴绶曰︰附子乃阴证要药。凡伤寒传变三阴，及中寒夹阴，虽身大热而脉沉者，必用之。或厥冷腹痛，脉沉细，甚则唇青囊缩者，急须用之，有退阴回阳之力，起死回生之功。近 世阴证伤寒，往往疑似，不敢用附子，直待阴极阳竭而用之，已迟矣。且夹阴伤寒，内外皆阴，阳气顿衰。必须急用人参，健脉以益其原；佐以附子，温经散寒。舍此不用，将何以救 之？
 刘完素曰︰俗方治麻痹多用乌附，其气暴能冲开道路，故气愈麻；及药气尽而正气行，则麻病愈矣。
 张元素曰︰附子以白术为佐，乃除寒湿之圣药。湿药宜少加之引经。又益火之原，以消阴翳，则便溺有节，乌、附是也。 虞抟曰︰附子禀雄壮之质，有斩关夺将之气。能引补气药行十二经，以追复散失之元阳；引 补血药入血分，以滋养不足之真阴；引发散药开腠理，以驱逐在表之风寒；引温暖药达下焦，以祛除在里之冷湿。
 震亨曰︰气虚热甚者，宜少用附子，以行参 。肥人多湿，亦宜少加乌、附行经。仲景八味丸，用为少阴响导，其补自是地黄，后世因以附子为补药，误矣。附子走而不守，取其健悍 走下之性，以行地黄之滞，可致远尔。乌头、天雄皆气壮形伟，可为下部药之佐；无人表其害人之祸，相习用为治风之药及补药，杀人多矣。 王履曰︰仲景八味丸，盖兼阴火不足者设。钱仲阳六味地黄丸，为阴虚者设。附子乃补阳之药，非为行滞也。
@@ -19602,16 +18857,11 @@
       <c r="H96" s="7" t="inlineStr">
         <is>
           <t>龙眼
-【气味】
-味甘，性温
-【毒性】
-无毒
-【归经】
-归心、脾经
-【主治】
-补益心脾，养血安神
-【释名】
-龙目（《吴普》）、圆眼（俗名）、益智（《本经》）、亚荔枝（《开宝》）、荔枝奴、骊珠、燕卵、蜜脾、鲛泪、时珍曰︰龙眼、龙目，象形也。《吴普本草》谓之龙目，又曰比目。曹宪《博雅》谓之益智。
+【气味】味甘，性温。
+【毒性】无毒。
+【归经】归心、脾经。
+【主治】补益心脾，养血安神。
+【释名】龙目（《吴普》）、圆眼（俗名）、益智（《本经》）、亚荔枝（《开宝》）、荔枝奴、骊珠、燕卵、蜜脾、鲛泪、时珍曰︰龙眼、龙目，象形也。《吴普本草》谓之龙目，又曰比目。曹宪《博雅》谓之益智。
 弘景曰︰广州有龙眼，非益智也，恐彼人别名耳。
 志曰︰甘味归脾，能益人智，故名益智，非今之益智子也。
 颂曰︰荔枝才过，龙眼即熟，故南人目为荔枝奴。又名木弹。晒干寄远，北人以为佳果，目为亚荔枝。
@@ -19664,16 +18914,11 @@
       <c r="H97" s="7" t="inlineStr">
         <is>
           <t>木香
-【气味】
-味辛、苦，性温
-【毒性】
-无毒
-【归经】
-归脾、胃、大肠、三焦、胆经
-【主治】
-行气止痛，健脾消食
-【释名】
-蜜香（《别录》）、青木香（弘景）、五木香（《图经》）、南木香（《纲目》）。
+【气味】味辛、苦，性温。
+【毒性】无毒。
+【归经】归脾、胃、大肠、三焦、胆经。
+【主治】行气止痛，健脾消食。
+【释名】蜜香（《别录》）、青木香（弘景）、五木香（《图经》）、南木香（《纲目》）。
 时珍曰︰木香，草类也。本名蜜香，因其香气如蜜也。缘沉香中有蜜香，遂讹此为木香尔。昔人谓之青木香。后人因呼马兜铃根为青木香，乃呼此为南木香、广木香以别之。今人又呼一种蔷薇为木香，愈乱真矣。《三洞珠囊》云︰五香者，即青木香也。一株五根，一茎五枝，一枝五叶，叶间五节，故名五香，烧之能上彻九天也。古方治痈疽有五香连翘汤，内用青木香。《古乐府》云︰氍毹 五木香，皆指此也。
 颂曰︰《修养书》云︰正月一日取五木煮汤以浴，令人至老须发黑。徐锴注云︰道家谓青木香为五香，亦云五木，多以为浴是矣。《金光明经》谓之矩琵佗香。
 【发明】
@@ -19732,21 +18977,15 @@
       <c r="H98" s="7" t="inlineStr">
         <is>
           <t>阿胶
-【气味】
-甘，平
-【毒性】
-无毒
-【归经】
-归肺、肝、肾经
-【主治】
-补血滋阴，润燥，止血
-【释名】
-傅致胶（《本经》）
+【气味】甘，平。
+【毒性】无毒。
+【归经】归肺、肝、肾经。
+【主治】补血滋阴，润燥，止血。
+【释名】傅致胶（《本经》）。
 弘景曰︰出东阿，故名阿胶。
 时珍曰︰阿井，在今山东兖州府阳谷县东北六十里，即古之东阿县也。有官舍禁之。
 郦道元《水经注》云︰东阿有井大如轮，深六七丈，岁常煮胶以贡天府者，即此也。其井乃济水所注，取井水煮胶，用搅浊水则清。故人服之，下膈疏痰止吐。盖济水清而重，其性趋下，故治淤浊及逆上之痰也。
-【发明】
-藏器曰︰诸胶皆主风、止泄、补虚，而驴皮主风为最。
+【发明】藏器曰︰诸胶皆主风、止泄、补虚，而驴皮主风为最。
 宗奭曰︰驴皮煎胶，取其发散皮肤之外也。用乌者，取乌色属水，以制热则生风之义，如乌蛇、乌鸦、乌鸡之类皆然。时珍曰︰阿胶大要只是补血与液，故能清肺益阴而治诸证。按陈自明云︰补虚用牛皮胶，去风用驴皮胶。
 成无己云︰阴不足者补之以味，阿胶之甘以补阴血。，不论肺虚肺实，可下可温，须用阿胶以安肺润肺。其性和平，为肺经要药。小儿惊风后瞳仁不正者，以阿胶倍人参煎服最良。阿胶育神，人参益气也。又痢疾多因伤暑伏热而成，阿胶乃大肠之要药。有热毒留滞者，则能疏导；无热毒留滞者，则能平安。数说足以发明阿胶之蕴矣。</t>
         </is>
@@ -19796,16 +19035,11 @@
       <c r="H99" s="7" t="inlineStr">
         <is>
           <t>鸡子黄
-【气味】
-味甘，性平
-【毒性】
-无毒
-【归经】
-归心、肾、脾经
-【主治】
-滋阴养血，润燥息风，清心安神，养胃止渴
-【释名】
-烛夜（《古今志》）。
+【气味】味甘，性平。
+【毒性】无毒。
+【归经】归心、肾、脾经。
+【主治】滋阴养血，润燥息风，清心安神，养胃止渴。
+【释名】烛夜（《古今志》）。
 时珍曰︰按徐铉云︰“鸡者稽也，能稽时也。”
 《广志》云︰“大曰蜀，小曰荆，雏曰𪇗 。
 《梵书》曰︰“鸡曰鸠七咤 。”
@@ -19858,16 +19092,11 @@
       <c r="H100" s="7" t="inlineStr">
         <is>
           <t>沙苑子 （白蒺藜）
-【气味】
-甘，温
-【毒性】
-无毒
-【归经】
-归肝、肾经
-【主治】
-补肾固精，养肝明目
-【释名】
-茨（《尔雅》）、旁通（《本经》）、屈人（《本经》）、止行（《本经》）、豺羽（《本经》）、升推（《本经》）。
+【气味】甘，温。
+【毒性】无毒。
+【归经】归肝、肾经。
+【主治】补肾固精，养肝明目。
+【释名】茨（《尔雅》）、旁通（《本经》）、屈人（《本经》）、止行（《本经》）、豺羽（《本经》）、升推（《本经》）。
 弘景曰︰多生道上及墙上，叶布地，子有刺，状如菱而小。长安最饶，人行多著木履。今军家乃铸铁作之，以布敌路，名铁蒺藜。
 《易》云︰据于蒺藜，言其凶伤；
 《诗》云︰墙有茨，不可扫也，以刺梗秽。方用甚稀。
@@ -19922,16 +19151,11 @@
       <c r="H101" s="7" t="inlineStr">
         <is>
           <t>芡实
-【气味】
-甘、涩，平
-【毒性】
-无毒
-【归经】
-归脾、肾经
-【主治】
-补肾固精，养肝明目
-【释名】
-鸡头（《本经》）、雁喙（同）、雁头（《古今注》）、鸿头（韩退之）、鸡雍（《庄子》）、卯菱（《管子》）、 子（音唯《弘景》）、水流黄（《谈圃》）。
+【气味】甘、涩，平。
+【毒性】无毒。
+【归经】归脾、肾经。
+【主治】补肾固精，养肝明目。
+【释名】鸡头（《本经》）、雁喙（同）、雁头（《古今注》）、鸿头（韩退之）、鸡雍（《庄子》）、卯菱（《管子》）、 子（音唯《弘景》）、水流黄（《谈圃》）。
 弘景曰︰此即今 子也。茎上花似鸡冠，故名鸡头。
 颂曰︰其苞形类鸡、雁头，故有诸名。
 时珍曰︰芡可济俭歉，故谓之芡。鸡雍见《庄子‧徐无鬼篇》。卯菱见《管子‧五行篇》。扬雄《方言》云︰南楚谓之鸡头，幽燕谓之雁头，徐、青、淮、泗谓之芡子。其茎谓之 ，亦曰 。郑樵《通志》以钩 为芡，误矣。钩 ，陆生草也，其茎可食。水流黄见下。
@@ -19987,16 +19211,11 @@
       <c r="H102" s="7" t="inlineStr">
         <is>
           <t>龙骨
-【气味】
-甘、涩，平
-【毒性】
-无毒
-【归经】
-归心、肝、肾经
-【主治】
-镇惊安神，平肝潜阳，收敛固涩，收湿敛疮
-【释名】
-时珍曰︰按许慎《说文》︰龙字篆文象形。《生肖论》云︰龙耳亏聪，故谓之龙。梵书名那伽。
+【气味】甘、涩，平。
+【毒性】无毒。
+【归经】归心、肝、肾经。
+【主治】镇惊安神，平肝潜阳，收敛固涩，收湿敛疮。
+【释名】时珍曰︰按许慎《说文》︰龙字篆文象形。《生肖论》云︰龙耳亏聪，故谓之龙。梵书名那伽。
 【发明】
 敩曰︰气入丈夫肾脏中，故益肾药宜用之。
 时珍曰︰涩可去脱。故成氏云︰龙骨能收敛浮越之正气，固大肠而镇惊。又主带脉为病。</t>
@@ -20047,16 +19266,11 @@
       <c r="H103" s="7" t="inlineStr">
         <is>
           <t>牡蛎
-【气味】
-咸，微寒
-【毒性】
-无毒
-【归经】
-归肝、胆、肾经
-【主治】
-重镇安神，潜阳补阴，软坚散结，收敛固涩，制酸止痛
-【释名】
-牡蛤（《别录》）、蛎蛤（《本经》）、古贲（《异物志》）、蚝。
+【气味】咸，微寒。
+【毒性】无毒。
+【归经】归肝、胆、肾经。
+【主治】重镇安神，潜阳补阴，软坚散结，收敛固涩，制酸止痛。
+【释名】牡蛤（《别录》）、蛎蛤（《本经》）、古贲（《异物志》）、蚝。
 弘景曰︰道家方以左顾是雄，故名牡蛎，右顾则牝蛎也。或以尖头为左顾，未详孰是。
 藏器曰︰天生万物皆有牡牝。惟蛎是咸水结成，块然不动，阴阳之道，何从而生？《经》言牡者，应是雄耳。
 宗奭曰︰《本经》不言左顾，止从陶说。而段成式亦云︰牡蛎言牡，非谓雄也。且如牡丹，岂有牝丹乎？此物无目，更何顾盻？
@@ -20113,16 +19327,11 @@
       <c r="H104" s="7" t="inlineStr">
         <is>
           <t>莲须（莲藕）
-【气味】
-甘、涩，平
-【毒性】
-无毒
-【归经】
-归心、肾经
-【主治】
-清心益肾，涩精止血
-【释名】
-其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
+【气味】甘、涩，平。
+【毒性】无毒。
+【归经】归心、肾经。
+【主治】清心益肾，涩精止血。
+【释名】其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
 韩保升曰︰藕生水中，其叶名荷。按︰《尔雅》云︰荷，芙蕖。其茎茄，其叶蕸，其本蔤，其华菡萏，其实莲，其根藕，其中菂，菂中薏。邢昺注云︰芙蕖，总名也，别名芙蓉，江东人呼为荷。菡萏，莲花也。菂，莲实也。薏，菂中青心也。
 郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
 时珍曰︰《尔雅》以荷为根名，韩氏以荷为叶名，陆机以荷为茎名。按︰茎乃负叶者也，有负荷之义，当从陆说。蔤乃嫩蒻，如竹之行鞭者。节生二茎，一为叶，一为花，尽处乃生藕，为花、叶、根、实之本。显仁藏用，功成不居，可谓退藏于密矣，故谓之蔤。花叶常偶生，不偶不生，故根曰藕。或云藕善耕泥，故字从耦，耦者耕也。茄音加，加于蔤上也。蕸音遐，远于密也。菡萏，函合未发之意。芙蓉，敷布容艳之意。莲者连也，花实相连而出也。菂者的也，子在房中点点如的也。的乃凡物点注之名。薏，犹意也，含苦在内也。古诗云︰食子心无弃，苦心生意存是矣。
@@ -20175,16 +19384,11 @@
       <c r="H105" s="7" t="inlineStr">
         <is>
           <t>龟板胶（水龟）
-【气味】
-甘、咸，凉
-【毒性】
-无毒
-【归经】
-归 肝、肾、心经
-【主治】
-滋阴潜阳，益肾健骨，养血补心，凉血止血
-【释名】
-神屋（《本经》）、败龟版（《日华》）、败将（《日华》）、漏天机（《图经》）。
+【气味】甘、咸，凉。
+【毒性】无毒。
+【归经】归 肝、肾、心经。
+【主治】滋阴潜阳，益肾健骨，养血补心，凉血止血。
+【释名】神屋（《本经》）、败龟版（《日华》）、败将（《日华》）、漏天机（《图经》）。
 时珍曰︰并隐名也。
 【发明】
 阴之物，禀北方之气而生，故能补阴、治血、治劳也。
@@ -20237,20 +19441,14 @@
       <c r="H106" s="7" t="inlineStr">
         <is>
           <t>鹿角胶
-【气味】
-甘、咸，温
-【毒性】
-无毒
-【归经】
-归 肝、肾经
-【主治】
-温补肝肾，益精养血，止血
-【释名】
-一名鹿角胶（《本经》）、粉名鹿角霜。
+【气味】甘、咸，温。
+【毒性】无毒。
+【归经】归 肝、肾经。
+【主治】温补肝肾，益精养血，止血。
+【释名】一名鹿角胶（《本经》）、粉名鹿角霜。
 甄权曰︰白胶一名黄明胶。
 时珍︰正误见黄明胶。
-【发明】
-𢽾曰︰凡使，鹿角胜于麋角。
+【发明】𢽾曰︰凡使，鹿角胜于麋角。
 颂曰︰今医家多用麋茸、麋角，云力紧于鹿也。
 时珍曰︰苏东坡《良方》云︰鹿阳兽，见阴而角解；麋阴兽，见阳而角解。故补阳以鹿角为胜，补阴以麋角为胜。其不同如此，但云鹿胜麋，麋胜鹿，疏矣。按此说与沈存中“鹿茸利补阴，麋茸利补阳”之说相反。以理与功推之，苏说为是。详见茸下。</t>
         </is>
@@ -20300,23 +19498,17 @@
       <c r="H107" s="7" t="inlineStr">
         <is>
           <t>菟丝子
-【气味】
-甘，温
-【毒性】
-无毒
-【归经】
-归 肝、肾、脾经
-【主治】
-补肾益精，养肝明目，止泻，安胎
-【释名】
-菟缕（《别录》）、菟蔂（《别录》）、菟芦（《本经》）、菟丘（《广雅》）、赤网（《别录》）、玉女（《尔雅》）、唐蒙（《尔雅》）、火焰草（《纲目》）、野狐丝（《纲目》）、金线草（《纲目》）。
+【气味】甘，温。
+【毒性】无毒。
+【归经】归 肝、肾、脾经。
+【主治】补肾益精，养肝明目，止泻，安胎。
+【释名】菟缕（《别录》）、菟蔂（《别录》）、菟芦（《本经》）、菟丘（《广雅》）、赤网（《别录》）、玉女（《尔雅》）、唐蒙（《尔雅》）、火焰草（《纲目》）、野狐丝（《纲目》）、金线草（《纲目》）。
 禹锡曰︰按《吕氏春秋》云︰或谓菟丝无根也。其根不属地，茯苓是也。《抱朴子》云︰菟丝之草，下有伏菟之根。无此菟，则丝不得生于上，然实不属也。伏菟抽则菟丝死。又云︰菟丝初生之根，其形似兔握，故割其血以和丹服，立能变化。则菟丝之名因此也。
 弘景曰︰旧言下有茯苓，上有菟丝，不必尔也。
 颂曰︰《抱朴》所说今未见，岂别一类乎？孙炎释《尔雅》云︰唐也，蒙也，女萝也，菟丝也，一物四名，而本草唐蒙为一名。《诗》云︰茑与女萝。毛苌云︰女萝，菟丝也。而本草菟丝无女萝之名，惟松萝一名女萝。岂二物皆是寄生同名，而本草脱漏乎？
 震亨曰︰菟丝未尝与茯苓共类，女萝附松而生，不相关涉，皆承讹而言也。
 时珍曰︰《毛诗》注女萝即菟丝。《吴普本草》菟丝一名松萝。陆佃言︰在木为女萝，在草为菟丝，二物殊别，皆由《尔雅》释《诗》误以为一物故也。张揖《广雅》云︰菟丘，菟丝也。女萝，松萝也。陆玑《诗疏》言︰菟丝蔓草上，黄赤如金；松萝蔓松上，生枝正青，无杂蔓者，皆得之。详见木部松萝下。又菟丝茯苓说，见茯苓下。
-【发明】
-𢽾曰︰菟丝子禀中和凝正阳气，一茎从树感枝而成，从中春上阳结实，故偏补人卫气，助人筋脉。
+【发明】𢽾曰︰菟丝子禀中和凝正阳气，一茎从树感枝而成，从中春上阳结实，故偏补人卫气，助人筋脉。
 颂曰︰《抱朴子》仙方单服法︰取实一斗，酒一斗浸，曝干再浸又曝，令酒尽乃止，捣筛。每酒服二钱，日二服。此药治腰膝去风，兼能明目。久服令人光泽，老变为少。十日外，饮啖如汤沃雪也。</t>
         </is>
       </c>
@@ -20365,16 +19557,11 @@
       <c r="H108" s="7" t="inlineStr">
         <is>
           <t>牛膝
-【气味】
-苦、甘、酸，平
-【毒性】
-无毒
-【归经】
-归 肝、肾经
-【主治】
-逐瘀通经，补肝肾，强筋骨，利尿通淋，引血下行
-【释名】
-牛荎（《广雅》）、百倍（《本经》）。
+【气味】苦、甘、酸，平。
+【毒性】无毒。
+【归经】归 肝、肾经。
+【主治】逐瘀通经，补肝肾，强筋骨，利尿通淋，引血下行。
+【释名】牛荎（《广雅》）、百倍（《本经》）。
 弘景曰︰其茎有节，似牛膝，故以为名。
 时珍曰︰《本经》又名百倍，隐语也，言其滋补之功，如牛之多力也。其叶似苋，其节对生，故俗有山苋、对节之称。
 【发明】
@@ -20428,20 +19615,14 @@
       <c r="H109" s="7" t="inlineStr">
         <is>
           <t>蛤蚧
-【气味】
-咸，平
-【毒性】
-小毒
-【归经】
-归 肺、肾经
-【主治】
-补肺益肾，纳气定喘，助阳益精
-【释名】
-蛤蟹（《日华》）、仙蟾（《纲目》）。
+【气味】咸，平。
+【毒性】小毒。
+【归经】归 肺、肾经。
+【主治】补肺益肾，纳气定喘，助阳益精。
+【释名】蛤蟹（《日华》）、仙蟾（《纲目》）。
 志曰︰一雌一雄，常自呼其名。
 时珍曰︰蛤蚧，因声而名，仙蟾，因形而名；岭南人呼蛙为蛤，又因其首如蛙、蟾也。雷𢽾以雄为蛤，以雌为蚧，亦通。
-【发明】
-宗奭曰︰补肺虚劳嗽有功。
+【发明】宗奭曰︰补肺虚劳嗽有功。
 时珍曰︰昔人言补可去弱，人参羊肉之属。蛤蚧补肺气，定喘止渴，功同人参。益阴血，助精扶羸，功同羊肉。近世治劳损痿弱，许叔微治消渴，皆用之，俱取其滋补也。刘纯云︰气液衰、阴血竭者，宜用之。何大英云︰定喘止嗽，莫佳于此。</t>
         </is>
       </c>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="2" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Disease" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,20 +13,22 @@
     <sheet name="Herb" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Book" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Theory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Story" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="StoryLine" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disease'!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -82,10 +84,25 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="Noto Sans JP"/>
       <charset val="128"/>
       <family val="3"/>
-      <sz val="6"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -172,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,9 +274,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="163">
     <dxf>
@@ -2233,13 +2277,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="37.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="37.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="19" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="20.75" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26.59765625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="20.73046875" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -3676,33 +3720,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="40"/>
-    <col width="9" customWidth="1" style="9" min="41" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="44"/>
+    <col width="9" customWidth="1" style="9" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -4451,12 +4495,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="45.75" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="45.73046875" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -6280,14 +6324,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F306"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14875,17 +14919,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14963,7 +15007,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -15021,7 +15065,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -15079,7 +15123,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -15136,7 +15180,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -15196,7 +15240,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -15260,7 +15304,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H7" s="28" t="inlineStr">
@@ -15319,7 +15363,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -15379,7 +15423,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -15440,7 +15484,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -15504,7 +15548,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -15565,7 +15609,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -15621,7 +15665,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -15679,7 +15723,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -15738,7 +15782,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -15795,7 +15839,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -15854,7 +15898,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -15915,7 +15959,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -15972,7 +16016,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -16031,7 +16075,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -16098,7 +16142,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -16157,7 +16201,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -16215,7 +16259,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -16272,7 +16316,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -16328,7 +16372,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -16388,7 +16432,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -16444,7 +16488,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -16506,7 +16550,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -16566,7 +16610,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -16622,7 +16666,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -16680,7 +16724,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -16735,7 +16779,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -16793,7 +16837,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -16851,7 +16895,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -16908,7 +16952,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -16969,7 +17013,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -17029,7 +17073,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -17087,7 +17131,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -17144,7 +17188,7 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -17205,7 +17249,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -17259,7 +17303,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -17318,7 +17362,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -17379,7 +17423,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -17437,7 +17481,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -17496,7 +17540,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -17555,7 +17599,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -17610,7 +17654,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -17679,7 +17723,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -17747,7 +17791,7 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -17803,7 +17847,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -17863,7 +17907,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -17927,7 +17971,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -17983,7 +18027,7 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -18041,7 +18085,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -18097,7 +18141,7 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -18152,7 +18196,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -18208,7 +18252,7 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -18271,7 +18315,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -18332,7 +18376,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -18388,7 +18432,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -18448,7 +18492,7 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -18507,7 +18551,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -18564,7 +18608,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -18618,7 +18662,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -18674,7 +18718,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -18735,7 +18779,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -18795,7 +18839,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -18856,7 +18900,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -18916,7 +18960,7 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -18974,7 +19018,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -19032,7 +19076,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -19086,7 +19130,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -19147,7 +19191,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -19203,7 +19247,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -19264,7 +19308,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -19318,7 +19362,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -19372,7 +19416,7 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -19429,7 +19473,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -19482,7 +19526,7 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -19542,7 +19586,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -19599,7 +19643,7 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -19656,7 +19700,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -19714,7 +19758,7 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -19772,7 +19816,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -19828,7 +19872,7 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -19887,7 +19931,7 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -19945,7 +19989,7 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -20006,7 +20050,7 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -20063,7 +20107,7 @@
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -20118,7 +20162,7 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -20175,7 +20219,7 @@
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -20232,7 +20276,7 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -20291,7 +20335,7 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -20349,7 +20393,7 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -20407,7 +20451,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -20462,7 +20506,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -20520,7 +20564,7 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -20576,7 +20620,7 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -20634,7 +20678,7 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -20690,7 +20734,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -20747,7 +20791,7 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -20806,7 +20850,7 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -20869,7 +20913,7 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -20928,7 +20972,7 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -20988,7 +21032,7 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -21043,7 +21087,7 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -21104,7 +21148,7 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -21161,7 +21205,7 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -21217,7 +21261,7 @@
       </c>
       <c r="G109" s="25" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="H109" s="25" t="inlineStr">
@@ -21312,306 +21356,6 @@
   <conditionalFormatting sqref="A1:A78 A110:A1048576">
     <cfRule type="duplicateValues" priority="413" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A102 A110:A1048576">
-    <cfRule type="duplicateValues" priority="7" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="8" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A5">
-    <cfRule type="duplicateValues" priority="162" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" priority="161" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" priority="160" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" priority="159" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" priority="156" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="157" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" priority="152" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="153" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" priority="150" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="151" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" priority="144" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="145" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" priority="140" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="141" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A19">
-    <cfRule type="duplicateValues" priority="137" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="138" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A23">
-    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24:A26">
-    <cfRule type="duplicateValues" priority="129" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="130" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" priority="127" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="128" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" priority="125" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="126" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30:A31">
-    <cfRule type="duplicateValues" priority="121" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="122" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A32">
-    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33">
-    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34:A35">
-    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A36:A37">
-    <cfRule type="duplicateValues" priority="112" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="113" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A38:A41">
-    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A42">
-    <cfRule type="duplicateValues" priority="108" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="109" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A43:A46">
-    <cfRule type="duplicateValues" priority="106" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="107" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:A49">
-    <cfRule type="duplicateValues" priority="104" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="105" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50:A51">
-    <cfRule type="duplicateValues" priority="101" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="102" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52:A53">
-    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54:A55">
-    <cfRule type="duplicateValues" priority="97" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="98" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" priority="95" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="96" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" priority="93" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="94" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
-    <cfRule type="duplicateValues" priority="90" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="91" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" priority="86" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="87" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" priority="82" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="83" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A63:A64">
-    <cfRule type="duplicateValues" priority="80" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="81" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65">
-    <cfRule type="duplicateValues" priority="78" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="79" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A67">
-    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A68">
-    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" priority="69" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="70" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70">
-    <cfRule type="duplicateValues" priority="67" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="68" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71">
-    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A72">
-    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A73">
-    <cfRule type="duplicateValues" priority="60" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="61" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A74">
-    <cfRule type="duplicateValues" priority="58" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="59" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
-    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A76:A77">
-    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A79">
-    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A80:A81">
-    <cfRule type="duplicateValues" priority="47" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="48" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A82">
-    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="45" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A83">
-    <cfRule type="duplicateValues" priority="42" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="43" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" priority="40" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="41" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A85">
-    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A86:A89">
-    <cfRule type="duplicateValues" priority="36" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="37" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A90:A91">
-    <cfRule type="duplicateValues" priority="34" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="35" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A92:A93">
-    <cfRule type="duplicateValues" priority="31" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="32" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A94">
-    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A95">
-    <cfRule type="duplicateValues" priority="26" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="27" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" priority="24" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="25" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A97">
-    <cfRule type="duplicateValues" priority="21" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="22" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" priority="19" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="20" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A99">
-    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A100">
-    <cfRule type="duplicateValues" priority="13" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="14" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A101">
-    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="10" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" priority="11" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="12" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A103:A107">
-    <cfRule type="duplicateValues" priority="5" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A108">
-    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A81 A110:A1048576">
     <cfRule type="duplicateValues" priority="386" dxfId="0"/>
   </conditionalFormatting>
@@ -21630,6 +21374,306 @@
   <conditionalFormatting sqref="A1:A99 A110:A1048576">
     <cfRule type="duplicateValues" priority="15" dxfId="0"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A102 A110:A1048576">
+    <cfRule type="duplicateValues" priority="7" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="8" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A5">
+    <cfRule type="duplicateValues" priority="162" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" priority="161" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="duplicateValues" priority="160" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="duplicateValues" priority="159" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" priority="157" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="156" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" priority="153" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="152" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="duplicateValues" priority="151" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="150" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="duplicateValues" priority="145" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="144" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="141" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="140" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A19">
+    <cfRule type="duplicateValues" priority="138" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="137" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:A23">
+    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A26">
+    <cfRule type="duplicateValues" priority="130" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="129" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="duplicateValues" priority="128" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="127" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28">
+    <cfRule type="duplicateValues" priority="126" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="125" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:A31">
+    <cfRule type="duplicateValues" priority="122" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="121" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:A35">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36:A37">
+    <cfRule type="duplicateValues" priority="113" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="112" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38:A41">
+    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="duplicateValues" priority="109" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="108" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43:A46">
+    <cfRule type="duplicateValues" priority="107" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="106" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47:A49">
+    <cfRule type="duplicateValues" priority="105" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="104" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50:A51">
+    <cfRule type="duplicateValues" priority="102" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="101" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52:A53">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:A55">
+    <cfRule type="duplicateValues" priority="98" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="97" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="96" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="95" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="94" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="93" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" priority="91" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="90" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="87" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="86" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" priority="83" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="82" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A63:A64">
+    <cfRule type="duplicateValues" priority="81" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="80" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" priority="79" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="78" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A67">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="70" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="69" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" priority="67" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="68" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A71">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A73">
+    <cfRule type="duplicateValues" priority="61" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="60" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74">
+    <cfRule type="duplicateValues" priority="59" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="58" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A76:A77">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80:A81">
+    <cfRule type="duplicateValues" priority="48" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="47" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A82">
+    <cfRule type="duplicateValues" priority="45" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A83">
+    <cfRule type="duplicateValues" priority="42" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="43" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="41" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="40" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A85">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:A89">
+    <cfRule type="duplicateValues" priority="37" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="36" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A90:A91">
+    <cfRule type="duplicateValues" priority="35" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="34" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A92:A93">
+    <cfRule type="duplicateValues" priority="32" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="31" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A94">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A95">
+    <cfRule type="duplicateValues" priority="27" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="26" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="25" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="24" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A97">
+    <cfRule type="duplicateValues" priority="22" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="21" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="20" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="19" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A99">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A100">
+    <cfRule type="duplicateValues" priority="14" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="13" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A101">
+    <cfRule type="duplicateValues" priority="10" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="12" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="11" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A103:A107">
+    <cfRule type="duplicateValues" priority="6" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A108">
+    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A109">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A111:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
   </conditionalFormatting>
@@ -21645,14 +21689,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -21738,12 +21782,12 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>shen_nong_bai_cao_jing</t>
+          <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>神农百草经</t>
+          <t>神农本草经</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -22246,15 +22290,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="18" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TheoryID</t>
@@ -22276,7 +22320,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ba_mai</t>
@@ -22294,8 +22338,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>打开脉象窗口后，按ASD，WSX可以分别显示左右手脉象图。
-游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
+          <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
 【寸关尺】
 寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
 【对应脏腑区域】
@@ -22308,14 +22351,18 @@
 右尺：肾阳
 【脉象】
 游戏中脉象由波形图表示。
-波峰的高低反应气的强弱，波峰越高气滞程度越高，波峰越低气虚程度越高。
-波线的粗细反应血的状态，波线越粗血瘀程度越高，波线越细血虚程度越高。
-波宽的宽窄反应湿燥程度，波宽越宽越湿，波宽越窄越燥。
-波速的快慢反应寒热程度，波速越快越热，波速越慢越寒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+波峰的高低反应气的强弱；
+波峰越高气滞程度越高，波峰越低气虚程度越高。
+波线的粗细反应血的状态；
+波线越粗血瘀程度越高，波线越细血虚程度越高。
+波宽的宽窄反应湿燥程度；
+波宽越宽越湿，波宽越窄越燥。
+波速的快慢反应寒热程度；
+波速越快越热，波速越慢越寒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>kai_fang</t>
@@ -22343,7 +22390,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>xing_yi_ji_kao</t>
@@ -22366,61 +22413,61 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -22429,4 +22476,699 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <cols>
+    <col width="20" bestFit="1" customWidth="1" style="49" min="1" max="1"/>
+    <col width="20" customWidth="1" style="43" min="2" max="2"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
+    <col width="12.1328125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
+    <col width="34" bestFit="1" customWidth="1" style="43" min="7" max="7"/>
+    <col width="11" customWidth="1" style="43" min="8" max="8"/>
+    <col width="9" customWidth="1" style="43" min="9" max="11"/>
+    <col width="9" customWidth="1" style="43" min="12" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>StoryID</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>StoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>TriggerScene</t>
+        </is>
+      </c>
+      <c r="D1" s="42" t="inlineStr">
+        <is>
+          <t>TriggerDay</t>
+        </is>
+      </c>
+      <c r="E1" s="42" t="inlineStr">
+        <is>
+          <t>PlayOnce</t>
+        </is>
+      </c>
+      <c r="F1" s="42" t="inlineStr">
+        <is>
+          <t>ReturnScene</t>
+        </is>
+      </c>
+      <c r="G1" s="42" t="inlineStr">
+        <is>
+          <t>BackgroundPath</t>
+        </is>
+      </c>
+      <c r="H1" s="42" t="inlineStr">
+        <is>
+          <t>SortIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="D2" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="44" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="G2" s="44" t="n"/>
+      <c r="H2" s="44" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+      <c r="F3" s="44" t="n"/>
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="n"/>
+      <c r="B4" s="44" t="n"/>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+      <c r="F4" s="44" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="44" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="n"/>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="44" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="n"/>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="44" t="n"/>
+      <c r="H19" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="n"/>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <cols>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
+    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
+    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
+    <col width="9" customWidth="1" style="43" min="9" max="10"/>
+    <col width="9" customWidth="1" style="43" min="11" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>StoryID</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>StoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>LineIndex</t>
+        </is>
+      </c>
+      <c r="D1" s="42" t="inlineStr">
+        <is>
+          <t>LineType</t>
+        </is>
+      </c>
+      <c r="E1" s="42" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="F1" s="46" t="inlineStr">
+        <is>
+          <t>PortraitSide</t>
+        </is>
+      </c>
+      <c r="G1" s="46" t="inlineStr">
+        <is>
+          <t>PortraitPath</t>
+        </is>
+      </c>
+      <c r="H1" s="42" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>明嘉靖十一年，蕲州州衙放榜处</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>…..........</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>嘶...... 又没中......</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>你再仔细看看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>爹，我看了好几遍了，确实没有我的名字…...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>考了三次童试都没中，看来我不是读书的材料啊爹</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>这说的是什么话，你看隔壁村那个老范，考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>我看我还是跟您学医吧，科举八股什么的，太难了</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,22 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="2" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Disease" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pulse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Formula" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FormulaIngredient" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Herb" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Book" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Theory" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Story" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="StoryLine" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Story" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="StoryLine" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Disease" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pulse" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Formula" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FormulaIngredient" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Herb" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Book" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Theory" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disease'!$A$1:$E$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="等线"/>
       <family val="2"/>
@@ -93,6 +92,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Noto Sans JP"/>
       <charset val="134"/>
       <family val="3"/>
       <color theme="1"/>
@@ -189,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -301,6 +307,7 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2272,18 +2279,981 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <cols>
+    <col width="7.3984375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.265625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>NpcID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NpcName</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="D1" s="51" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>BookID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <cols>
+    <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="6.86328125" customWidth="1" min="3" max="3"/>
+    <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>TheoryID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>TheoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>unlock required experie</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>BookID</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>DetailText</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ba_mai</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>把脉</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>huang_di_nei_jing</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
+【寸关尺】
+寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
+【对应脏腑区域】
+浮脉：表
+左寸：心
+左关：肝
+左尺：肾阴
+右寸：肺
+右关：脾
+右尺：肾阳
+【脉象】
+游戏中脉象由波形图表示。
+波峰的高低反应气的强弱；
+波峰越高气滞程度越高，波峰越低气虚程度越高。
+波线的粗细反应血的状态；
+波线越粗血瘀程度越高，波线越细血虚程度越高。
+波宽的宽窄反应湿燥程度；
+波宽越宽越湿，波宽越窄越燥。
+波速的快慢反应寒热程度；
+波速越快越热，波速越慢越寒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>kai_fang</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>开方</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>huang_di_nei_jing</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>点击选中君臣佐使区域，药材栏选取添加药材和药量，左键点击增加，右键减少。可以在搜索栏输入药材名或拼音，拼音首字母快速查找药材。
+【君臣佐使】
+方剂配伍的基本原则，指一个药方里不同药材扮演的不同角色，就像一只分工明确的团队。
+君药：针对主要病症的核心药材，力量最强，用量最大。
+臣药：辅助君药增强疗效，治疗兼带症状。
+佐药：制约君臣药的毒性或烈性，治疗次要症状。
+使药：调和诸药，引导药物直达病位，解毒缓解副作用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>xing_yi_ji_kao</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>行医记考</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>huang_di_nei_jing</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>李东壁在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材，方剂，疾病。
+在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <cols>
+    <col width="20" bestFit="1" customWidth="1" style="49" min="1" max="1"/>
+    <col width="20" customWidth="1" style="43" min="2" max="2"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
+    <col width="12.1328125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
+    <col width="34" bestFit="1" customWidth="1" style="43" min="7" max="7"/>
+    <col width="11" customWidth="1" style="43" min="8" max="8"/>
+    <col width="9" customWidth="1" style="43" min="9" max="13"/>
+    <col width="9" customWidth="1" style="43" min="14" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>StoryID</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>StoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>TriggerScene</t>
+        </is>
+      </c>
+      <c r="D1" s="42" t="inlineStr">
+        <is>
+          <t>TriggerDay</t>
+        </is>
+      </c>
+      <c r="E1" s="42" t="inlineStr">
+        <is>
+          <t>PlayOnce</t>
+        </is>
+      </c>
+      <c r="F1" s="42" t="inlineStr">
+        <is>
+          <t>ReturnScene</t>
+        </is>
+      </c>
+      <c r="G1" s="42" t="inlineStr">
+        <is>
+          <t>BackgroundPath</t>
+        </is>
+      </c>
+      <c r="H1" s="42" t="inlineStr">
+        <is>
+          <t>SortIndex</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="D2" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="44" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="G2" s="44" t="n"/>
+      <c r="H2" s="44" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+      <c r="F3" s="44" t="n"/>
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="n"/>
+      <c r="B4" s="44" t="n"/>
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+      <c r="F4" s="44" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="44" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="n"/>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="44" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="n"/>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="44" t="n"/>
+      <c r="H19" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="n"/>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <cols>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
+    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
+    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
+    <col width="9" customWidth="1" style="43" min="9" max="12"/>
+    <col width="9" customWidth="1" style="43" min="13" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>StoryID</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>StoryName</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>LineIndex</t>
+        </is>
+      </c>
+      <c r="D1" s="42" t="inlineStr">
+        <is>
+          <t>LineType</t>
+        </is>
+      </c>
+      <c r="E1" s="42" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="F1" s="46" t="inlineStr">
+        <is>
+          <t>PortraitSide</t>
+        </is>
+      </c>
+      <c r="G1" s="46" t="inlineStr">
+        <is>
+          <t>PortraitPath</t>
+        </is>
+      </c>
+      <c r="H1" s="42" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>明嘉靖十一年，蕲州州衙放榜处</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>…..........</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>嘶...... 又没中......</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>你再仔细看看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>爹，我看了好几遍了，确实没有我的名字…...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>考了三次童试都没中，看来我不是读书的材料啊爹</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>这说的是什么话，你看隔壁村那个老范，考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>res://Assets/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>我看我还是跟您学医吧，科举八股什么的，太难了</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>res://Assets/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="19" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
     <col width="26.59765625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="20.73046875" customWidth="1" style="3" min="5" max="5"/>
+    <col width="6.86328125" customWidth="1" style="7" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -2302,12 +3272,17 @@
           <t>RecommendedFormulaID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>unlock required experie</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>BookID</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>DetailText</t>
         </is>
@@ -2329,12 +3304,15 @@
           <t>ma_huang_tang</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>风寒表实证
 【病机】寒邪束表、腠理闭塞、卫阳被遏
@@ -2361,12 +3339,15 @@
           <t>gui_zhi_tang</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>风寒表虚证
 【病机】风寒袭表，卫气不固，营阴外泄
@@ -2393,12 +3374,15 @@
           <t>ma_xing_shi_gan_tang</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>肺热壅盛
 【病机】邪热壅滞于肺，肺失宣降，气机闭塞，热盛气逆
@@ -2425,12 +3409,15 @@
           <t>gui_zhi_gan_cao_tang</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>心阳虚
 【病机】心阳不足，温煦、鼓动无力，虚寒内生。
@@ -2457,12 +3444,15 @@
           <t>dang_gui_si_ni_tang</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>寒凝心脉
 【病机】素体阳虚，阴寒凝滞，寒邪痹阻心脉、胸阳不振，心脉拘急不通而痛。
@@ -2489,12 +3479,15 @@
           <t>li_zhong_wan</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>脾阳虚
 【病机】脾气久虚，脾阳不足、虚寒内生、运化腐熟无权。
@@ -2521,12 +3514,15 @@
           <t>zhen_wu_tang</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>肾虚水泛
 【病机】肾阳虚衰，气化无权，水湿内停，泛溢肌肤
@@ -2555,12 +3551,15 @@
           <t>bai_hu_tang</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>气分热盛
 【病机】外感温热病邪入里，邪热炽盛、入居气分、里热蒸腾、正邪剧争，属实热证。
@@ -2590,12 +3589,15 @@
           <t>huang_lian_e_jiao_tang</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>心肾不交
 【病机】肾阴不足，不能上滋心火；心火偏亢，不能下温肾水，水火失济、阴阳失调。多由劳神过度、久病耗阴、情志郁而化火所致，多属阴虚火旺。
@@ -2624,12 +3626,15 @@
           <t>yin_qiao_san</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>风热表证
 【病机】风热之邪侵袭肺卫，卫气失和，肺失清肃
@@ -2656,12 +3661,15 @@
           <t>sang_xing_tang</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>温燥证
 【病机】初秋燥热之邪侵袭肺卫，肺失清润
@@ -2688,12 +3696,15 @@
           <t>xing_su_san</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>凉燥证
 【病机】深秋寒气渐生，燥邪兼风寒侵袭肺卫
@@ -2720,12 +3731,15 @@
           <t>sha_shen_mai_dong_tang</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>肺阴虚
 【病机】肺阴亏虚，虚火内生，肺失滋润、清肃无权。
@@ -2752,12 +3766,15 @@
           <t>wu_tou_tang</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>痛痹（寒痹）
 【病机】风寒湿邪痹阻经络，寒邪偏盛。寒主收引、凝滞，气血不通则疼痛剧烈。
@@ -2784,12 +3801,15 @@
           <t>bai_hu_gui_zhi_tang</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>热痹
 【病机】风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
@@ -2816,12 +3836,15 @@
           <t>tian_wang_bu_xin_dan</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>心阴虚
 【病机】心阴亏虚，心神失养，虚火内扰。
@@ -2848,12 +3871,15 @@
           <t>jin_gui_shen_qi_wan</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>肾阳虚
 【病机】年老肾亏、久病伤阳、房劳耗损，肾阳亏虚、命门火衰、温煦气化无权。
@@ -2881,12 +3907,15 @@
           <t>fang_feng_tang</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>行痹（风痹）
 【病机】风寒湿邪侵袭经络，以风邪偏盛为主。风性善行、走窜不定。
@@ -2913,12 +3942,15 @@
           <t>er_chen_tang</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>痰湿阻肺
 【病机】脾失健运，痰湿内生，上壅于肺，肺失宣降。
@@ -2945,12 +3977,15 @@
           <t>si_wu_tang</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>肝血虚
 【病机】肝血不足，筋脉、目、爪甲、心神失于濡养。
@@ -2977,12 +4012,15 @@
           <t>si_jun_zi_tang</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>脾气虚
 【病机】饮食劳倦、久病耗伤，脾失健运、中气不足、运化失职。
@@ -3009,12 +4047,15 @@
           <t>ping_wei_san</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>湿盛困脾
 【病机】外感湿邪、或嗜食生冷肥甘，湿邪壅滞、脾阳被困、运化失司，属实证。
@@ -3041,12 +4082,15 @@
           <t>shen_ling_bai_zhu_san</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>脾虚湿盛
 【病机】脾气本虚，运化无力，水湿内生，湿浊内停
@@ -3073,12 +4117,15 @@
           <t>xiao_yao_san</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>肝脾不和（肝郁脾虚）
 【病机】情志不舒、肝气郁结，木旺克土；脾虚失运、肝气乘脾。
@@ -3106,12 +4153,15 @@
           <t>huo_xiang_zheng_qi_san</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>外感风寒，内伤湿滞
 【病机】外感风寒之邪束表，内伤饮食湿浊阻滞中焦；表有风寒、里有湿滞
@@ -3139,12 +4189,15 @@
           <t>bu_fei_tang</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>肺气虚
 【病机】肺气不足，宣降无力，卫外不固。
@@ -3171,12 +4224,15 @@
           <t>huang_lian_wen_dan_tang</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>痰火扰心
 【病机】痰浊郁而化火，痰火互结、上扰心神，神明躁动不宁。
@@ -3203,12 +4259,15 @@
           <t>yi_yi_ren_tang</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>着痹（湿痹）
 【病机】风寒湿邪侵袭，湿邪偏盛；湿性重浊、黏滞，阻滞经络、困遏气机。
@@ -3236,12 +4295,15 @@
           <t>di_tan_tang</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>痰迷心窍
 【病机】痰湿浊邪蒙蔽心窍，神明失主，多由情志郁结、脾失健运、痰浊内生，上蒙心神所致。
@@ -3268,12 +4330,15 @@
           <t>chai_hu_shu_gan_san</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>肝气郁结
 【病机】情志不遂，肝失疏泄，气机郁滞、经脉不畅。
@@ -3300,12 +4365,15 @@
           <t>nuan_gan_jian</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>寒滞肝脉
 【病机】外感寒邪、凝滞肝经，肝脉拘急、气血阻滞、阳气被遏，属实寒证。
@@ -3332,12 +4400,15 @@
           <t>zuo_gui_wan</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>肾精不足
 【病机】先天禀赋不足、后天耗伤太过、久病及肾、房劳过度，肾精亏少，不能充养骨骼、脑髓、生殖之本。
@@ -3366,12 +4437,15 @@
           <t>dao_chi_san</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>心火亢盛
 【病机】心火内炽，火热扰心、灼伤脉络、下移小肠。
@@ -3398,12 +4472,15 @@
           <t>liu_wei_di_huang_wan</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>肾阴虚
 【病机】久病耗伤、房劳过度、过服温燥，肾阴亏虚、虚火内生、失于滋养。
@@ -3431,12 +4508,15 @@
           <t>qing_qi_hua_tan_wan</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>痰热壅肺
 【病机】邪热入里，灼津成痰、痰热互结，壅遏肺气，肺失宣降。
@@ -3463,12 +4543,15 @@
           <t>gou_teng_san</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>肝阳上亢
 【病机】肝肾阴虚，阴不制阳、肝阳升发太过、上扰头目，属本虚标实。
@@ -3495,12 +4578,15 @@
           <t>long_dan_xie_gan_tang</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>肝火上炎
 【病机】肝郁化火、暴怒伤肝，肝火炽盛、气火上逆，属实热证。
@@ -3527,12 +4613,15 @@
           <t>yi_guan_jian</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>肝阴虚
 【病机】情志化火、久病耗伤，肝阴不足、虚火内生、头目筋脉失养。
@@ -3559,12 +4648,15 @@
           <t>gui_pi_tang</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>心脾两虚
 【病机】思虑过度、劳倦伤脾、久病体虚、失血过多；脾气虚弱，气血生化不足，心血亏虚、心神失养，属气血两虚、虚证。
@@ -3592,12 +4684,15 @@
           <t>yang_xin_tang</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>心气虚
 【病机】心气不足，鼓动无力，心神失养。
@@ -3624,12 +4719,15 @@
           <t>yu_ping_feng_san</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>卫气虚
 【病机】素体虚弱、久病耗伤肺气，卫气不固、腠理疏松、防御固摄功能减退。
@@ -3656,12 +4754,15 @@
           <t>jin_suo_gu_jing_wan</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>肾气不固
 【病机】久病劳损、年老体弱、房事不节，肾气亏虚、封藏固摄无权，偏虚证、无明显寒热。
@@ -3689,12 +4790,15 @@
           <t>ren_shen_ge_jie_san</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>肾不纳气
 【病机】久病咳喘、年老肾虚、劳伤肾气；肾气亏虚，下元不固，不能摄纳肺气，气浮于上。属虚喘、肺肾两虚，无明显实邪。
@@ -3706,14 +4810,200 @@
         </is>
       </c>
     </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="D45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="D46" s="28" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="15" customHeight="1">
+      <c r="D48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="D49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="D50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="D51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="D52" s="28" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="D53" s="28" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="D54" s="28" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="D55" s="28" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="D56" s="28" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="D57" s="28" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="D58" s="28" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="D59" s="28" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="D60" s="28" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="D61" s="28" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="D62" s="28" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="D63" s="28" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="D64" s="28" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="D65" s="28" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="D66" s="28" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="D67" s="28" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="D68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="D69" s="28" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="D70" s="28" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="D71" s="28" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="D72" s="28" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="D73" s="28" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="D74" s="28" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="D75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="D76" s="28" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="D77" s="28" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="D78" s="28" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="D79" s="28" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="D80" s="28" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="D81" s="28" t="n"/>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="15" customHeight="1">
+      <c r="D83" s="28" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="D84" s="28" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="D85" s="28" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="D86" s="28" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="D87" s="28" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="D88" s="28" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="D89" s="28" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="D90" s="28" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="D91" s="28" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="D92" s="28" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="D93" s="28" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="D94" s="28" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="D95" s="28" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="D96" s="28" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="D97" s="28" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="D98" s="28" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100" ht="15" customHeight="1">
+      <c r="D100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="D101" s="28" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="D102" s="28" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="D103" s="28" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="D104" s="28" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="D105" s="28" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="D106" s="28" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="D107" s="28" t="n"/>
+    </row>
+    <row r="108"/>
+    <row r="109" ht="15" customHeight="1">
+      <c r="D109" s="26" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3745,8 +5035,8 @@
     <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
     <col width="5.265625" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="44"/>
-    <col width="9" customWidth="1" style="9" min="45" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="46"/>
+    <col width="9" customWidth="1" style="9" min="47" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -4488,20 +5778,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
     <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="45.73046875" customWidth="1" style="3" min="4" max="4"/>
-    <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="6.86328125" customWidth="1" style="7" min="4" max="4"/>
+    <col width="45.73046875" customWidth="1" style="3" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -4520,12 +5811,17 @@
           <t>TargetDiseaseName</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>unlock required experie</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>BookID</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>DetailText</t>
         </is>
@@ -4547,12 +5843,15 @@
           <t>风寒表实证</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>麻黄汤
 【出处】《伤寒论》
@@ -4586,12 +5885,15 @@
           <t>风寒表虚证</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>桂枝汤
 【出处】《伤寒论》
@@ -4624,12 +5926,15 @@
           <t>肺热壅盛</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>麻杏石甘汤
 【出处】《伤寒论》
@@ -4664,12 +5969,15 @@
           <t>心阳虚</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>桂枝甘草汤
 【出处】《伤寒论》
@@ -4702,12 +6010,15 @@
           <t>寒凝心脉</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>当归四逆汤
 【出处】《伤寒论》
@@ -4744,12 +6055,15 @@
           <t>脾阳虚</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>理中丸
 【出处】《伤寒论》
@@ -4784,12 +6098,15 @@
           <t>肾虚水泛</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>真武汤
 【出处】《伤寒论》
@@ -4825,12 +6142,15 @@
           <t>气分热盛</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>白虎汤
 【出处】《伤寒论》
@@ -4864,12 +6184,15 @@
           <t>心肾不交</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>黄连阿胶汤
 【出处】《伤寒论》
@@ -4905,12 +6228,15 @@
           <t>风热表证</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>银翘散
 【出处】《温病条辩》
@@ -4947,12 +6273,15 @@
           <t>温燥证</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>桑杏汤
 【出处】《温病条辨》
@@ -4990,12 +6319,15 @@
           <t>温燥证</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>杏苏散
 【出处】《温病条辨》
@@ -5032,12 +6364,15 @@
           <t>肺阴虚</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>沙参麦冬汤
 【出处】《温病条辩》
@@ -5073,12 +6408,15 @@
           <t>痛痹</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>乌头汤
 【出处】《金匮要略》
@@ -5114,12 +6452,15 @@
           <t>热痹</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>白虎桂枝汤
 【出处】《金匮要略》
@@ -5154,12 +6495,15 @@
           <t>心阴虚</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>天王补心丹
 【出处】《金匮要略》
@@ -5197,12 +6541,15 @@
           <t>肾阳虚</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>金匮肾气丸
 【出处】《金匮要略》
@@ -5236,12 +6583,15 @@
           <t>行痹</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>防风汤
 【出处】《太平惠民和剂局方》
@@ -5279,12 +6629,15 @@
           <t>痰湿阻肺</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>二陈汤
 【出处】《太平惠民和剂局方》
@@ -5319,12 +6672,15 @@
           <t>肝血虚</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>四物汤
 【出处】《太平惠民和剂局方》
@@ -5359,12 +6715,15 @@
           <t>脾气虚</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>四君子汤
 【出处】《太平惠民和剂局方》
@@ -5399,12 +6758,15 @@
           <t>湿盛困脾</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>平胃散
 【出处】《太平惠民和剂局方》
@@ -5439,12 +6801,15 @@
           <t>脾虚湿盛</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>参苓白术散
 【出处】《太平惠民和剂局方》
@@ -5480,12 +6845,15 @@
           <t>肝脾不和</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>逍遥散
 【出处】《太平惠民和剂局方》
@@ -5522,12 +6890,15 @@
           <t>外感风寒，内伤湿滞</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>藿香正气散
 【出处】《太平惠民和剂局方》
@@ -5564,12 +6935,15 @@
           <t>肺气虚</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>bei_ji_qian_jin_yao_fang</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>补肺汤
 【出处】《备急千金要方》
@@ -5604,12 +6978,15 @@
           <t>痰火扰心</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>bei_ji_qian_jin_yao_fang</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>黄连温胆汤
 【出处】《备急千金要方》
@@ -5649,12 +7026,15 @@
           <t>着痹</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>薏苡仁汤
 【出处】《太医院经验奇效良方大全》
@@ -5690,12 +7070,15 @@
           <t>痰迷心窍</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>涤痰汤
 【出处】《太医院经验奇效良方大全》
@@ -5733,12 +7116,15 @@
           <t>肝气郁结</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>柴胡疏肝散
 【出处】《景岳全书》
@@ -5774,12 +7160,15 @@
           <t>寒滞肝脉</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>暖肝煎
 【出处】《景岳全书》
@@ -5817,12 +7206,15 @@
           <t>肾精不足</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>左归丸
 【出处】《景岳全书》
@@ -5858,12 +7250,15 @@
           <t>心火亢盛</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>xiao_er_yao_zheng_zhi_jue</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>导赤散
 【出处】《小儿药证直决》
@@ -5898,12 +7293,15 @@
           <t>肾阴虚</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>xiao_er_yao_zheng_zhi_jue</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>六味地黄丸
 【出处】《金匮要略》
@@ -5940,12 +7338,15 @@
           <t>痰热壅肺</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>yi_fang_kao</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>清气化痰丸
 【出处】《医方考》
@@ -5983,12 +7384,15 @@
           <t>肝阳上亢</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>pu_ji_ben_shi_fang</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>钩藤散
 【出处】《普济本事方》
@@ -6026,12 +7430,15 @@
           <t>肝火上炎</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>lan_shi_mi_cang</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>龙胆泻肝汤
 【出处】《兰室秘藏》
@@ -6068,12 +7475,15 @@
           <t>肝阴虚</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>liu_zhou_yi_hua</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>一贯煎
 【出处】《柳州医话》
@@ -6109,12 +7519,15 @@
           <t>心脾两虚</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>yan_shi_ji_sheng_fang</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>归脾汤
 【出处】《严氏济生方》
@@ -6152,12 +7565,15 @@
           <t>心气虚</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>ren_zhai_zhi_zhi_fang_lun</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>养心汤
 【出处】《仁斋直指方论》
@@ -6195,12 +7611,15 @@
           <t>卫气虚</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>jiu_yuan_fang</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>玉屏风散
 【出处】《究原方》
@@ -6234,12 +7653,15 @@
           <t>肾气不固</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>yi_fang_ji_jie</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>金锁固精丸
 【出处】《医方集解》
@@ -6275,12 +7697,15 @@
           <t>肾不纳气</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>wang_shi_bo_ji_fang</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>人参蛤蚧散
 【出处】《博济方》
@@ -6305,11 +7730,194 @@
       <c r="A45" s="7" t="n"/>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="28" t="n"/>
       <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="C46" s="7" t="n"/>
+      <c r="D46" s="28" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="15" customHeight="1">
+      <c r="D48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="D49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="D50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="D51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="D52" s="28" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="D53" s="28" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="D54" s="28" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="D55" s="28" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="D56" s="28" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="D57" s="28" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="D58" s="28" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="D59" s="28" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="D60" s="28" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="D61" s="28" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="D62" s="28" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="D63" s="28" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="D64" s="28" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="D65" s="28" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="D66" s="28" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="D67" s="28" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="D68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="D69" s="28" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="D70" s="28" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="D71" s="28" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="D72" s="28" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="D73" s="28" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="D74" s="28" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="D75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="D76" s="28" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="D77" s="28" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="D78" s="28" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="D79" s="28" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="D80" s="28" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="D81" s="28" t="n"/>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="15" customHeight="1">
+      <c r="D83" s="28" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="D84" s="28" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="D85" s="28" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="D86" s="28" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="D87" s="28" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="D88" s="28" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="D89" s="28" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="D90" s="28" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="D91" s="28" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="D92" s="28" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="D93" s="28" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="D94" s="28" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="D95" s="28" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="D96" s="28" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="D97" s="28" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="D98" s="28" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100" ht="15" customHeight="1">
+      <c r="D100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="D101" s="28" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="D102" s="28" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="D103" s="28" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="D104" s="28" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="D105" s="28" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="D106" s="28" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="D107" s="28" t="n"/>
+    </row>
+    <row r="108"/>
+    <row r="109" ht="15" customHeight="1">
+      <c r="D109" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6317,7 +7925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14912,13 +16520,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
@@ -14927,9 +16535,10 @@
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
     <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
     <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
-    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
+    <col width="6.59765625" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14963,12 +16572,17 @@
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>unlock required experie</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>BookID</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>DetailText</t>
         </is>
@@ -15005,12 +16619,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>麻黄
 【气味】辛苦，温。
@@ -15026,7 +16643,7 @@
 时珍曰︰麻黄乃肺经专药，故治肺病多用之。张仲景治伤寒无汗用麻黄，有汗用桂枝。历代明医解释，皆随文傅会，未有究其精微者。时珍常绎思之，似有一得，与昔人所解不同云。津液为汗，汗即血也。在营则为血，在卫则为汗。夫寒伤营，营血内涩，不能外通于卫，卫气闭固，津液不行，故无汗发热而憎寒。夫风伤卫，卫气外泄，不能内护于营，营气虚弱，津液不固，故有汗发热而恶风。然风寒之邪，皆由皮毛而入。皮毛者，肺之合也。肺主卫气，包罗一身，天之象也。是证虽属乎太阳，而肺实受邪气。其证时兼面赤怫郁，咳嗽有痰，喘而胸满诸证者，非肺病乎？盖皮毛外闭，则邪热内攻，而肺气郁。故用麻黄、甘引出营分之邪，达之肌表，佐以杏仁泄肺而利气。汗后无大热而喘者，加以石膏。朱肱《活人书》，夏至后加石膏、知母，皆是泄肺火之药。是则麻黄汤虽太阳发汗重剂，实为发散肺经火郁之药也。腠理不密，则津液外泄，而肺气自虚。虚则补其母。故用桂枝同甘草，外散风邪以救表，内伐肝木以防脾。佐以芍药，泄木而固脾，泄东所以补西也。使以姜枣，行脾之津液而和营卫也。下后微喘者加浓朴、杏仁，以利肺气也。汗后脉沉迟者加人参，以益肺气也。朱肱加黄芩为阳旦汤，以泻肺热也。皆是脾肺之药。是则桂枝虽太阳解肌轻剂，实为理脾救肺之药也。此千古未发之秘旨，愚因表而出之。又少阴病发热脉沉，有麻黄附子细辛汤、麻黄附子甘草汤。少阴与太阳为表里，乃赵嗣真所谓熟附配麻黄，补中有发也。一锦衣夏月饮酒达旦，病水泄，数日不止，水谷直出。服分利消导升提诸药则反剧。时珍诊之，脉浮而缓，大肠下弩，复发痔血。此因肉食生冷茶水过杂，抑遏阳气在下，木盛土衰，《素问》所谓久风成飧泄也。法当升之扬之。遂以小续命汤投之，一服而愈。昔仲景治伤寒六七日，大下后，脉沉迟，手足厥逆，咽喉不利，唾脓血，泄利不止者，用麻黄汤平其肝肺，兼升发之，即斯理也。神而明之，此类是矣。</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
+      <c r="J2" s="24" t="inlineStr">
         <is>
           <t>草之四</t>
         </is>
@@ -15063,12 +16680,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>桂枝（桂）
 【气味】味辛、甘，性温。
@@ -15084,7 +16704,7 @@
 时珍曰︰麻黄遍彻皮毛，故专于发汗而寒邪散，肺主皮毛，辛走肺也。桂枝透达营卫，故能解肌而风邪去，脾主营，肺主卫，甘走脾，辛走肺也。肉桂下行，益火之原，此东垣所谓肾苦燥，急食辛以润之，开腠理，致津液，通其气者也。《圣惠方》言︰桂心入心，引血化汗化脓。盖手少阴君火、厥阴相火，与命门同气者也。《别录》云桂通血脉是矣。</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>木之一</t>
         </is>
@@ -15121,12 +16741,15 @@
           <t>小毒</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>杏仁（杏）
 【气味】味苦，性温。
@@ -15141,7 +16764,7 @@
 时珍曰︰杏仁能散能降，故解肌散风、降气润燥、消积治伤损药中用之。治疮杀虫，用其毒也。按《医余》云︰凡索面、豆粉近杏仁则烂。顷一兵官食粉成积，医师以积气丸、杏仁相半研为丸，熟水下，数服愈。又《野人闲话》云︰翰林学士辛士逊，在青城山道院中，梦皇姑谓曰︰可服杏仁，令汝聪明，老而健壮，心力不倦。求其方，则用杏仁一味，每盥漱毕，以七枚纳口中，良久脱去皮，细嚼和津液顿咽。日日食之，一年必换血，令人轻健。此申天师方也。又杨士瀛《直指方》云︰凡人以水浸杏仁五枚，五更端坐，逐粒细嚼至尽，和津吞下。久则能润五脏，去尘滓，驱风明目，治肝肾风虚，瞳人带青，眼翳风痒之病。珍按杏仁性热降气，亦非久服之药。此特其咀嚼吞纳津液，以消积秽则可耳。古有服杏丹法，云是左慈之方。唐慎微收入本草，云久服寿至千万。其说妄诞可鄙，今删其纰谬之辞，存之于下，使读者毋信其诳也。</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>果之一</t>
         </is>
@@ -15178,12 +16801,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>甘草
 【气味】味甘，性平。
@@ -15201,7 +16827,7 @@
 颂曰︰按孙思邈《千金方论》云：甘草解百药毒，如汤沃雪。有中乌头、巴豆毒，甘草入腹即定，验如反掌。方称大豆汁解百药毒，予每试之不效。加入甘草为甘豆汤，其验乃奇也。又葛洪《肘后备急方》云：席辩刺史尝言岭南俚人解蛊毒药，并是常用之物，畏人得其法，乃言三百头牛药，或言三百两银药。久与亲狎，乃得其详。凡饮食时，先取炙熟甘草一寸，嚼之咽汁，若中毒，随即吐出。仍以炙甘草三两、生姜四两，水六升，煮二升，日三服。或用都淋藤、黄藤二物，酒煎温常服，则毒随大小溲出。又常带甘草数寸，随身备急。若经含甘草而食物不吐者，非毒物也。三百头牛药，即土常山也；三百两银药，即马兜铃藤也。详见各条。</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -15238,12 +16864,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>白芍（芍药）
 【气味】苦、酸，微寒。
@@ -15265,7 +16894,7 @@
 时珍曰：白芍药益脾，能于土中泻木。赤芍药散邪，能行血中之滞。《日华子》言：赤补气，白治血，欠审矣。产后肝血已虚，不可更泻，故禁之。酸寒之药多矣，何独避芍药耶？以此杲曰：或言古人以酸涩为收，《本经》何以言利小便？曰：芍药能益阴滋湿而停津液，故小便自行，非因通利也。曰：又言缓中何也？曰：损其肝者缓其中，即调血也，故四物汤用芍药。大抵酸涩者为收敛停湿之剂，故主手足太阴经收敛之体，又能治血海而入于九地之下，后至厥阴经。白者色在西方，故补；赤者色在南方，故泻。</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -15302,12 +16931,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>生姜
 【气味】味辛，性温。
@@ -15324,7 +16956,7 @@
 杨士瀛曰︰姜能助阳，茶能助阴，二物皆消散恶气，调和阴阳，且解湿热及酒食暑气之毒，不问赤、白通宜用之。苏东坡治文潞公有效。</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t>菜之一</t>
         </is>
@@ -15361,12 +16993,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>大枣（枣）
 【气味】味甘，性温。
@@ -15384,7 +17019,7 @@
 时珍曰︰《素问》言枣为脾之果，脾病宜食之。谓治病和药，枣为脾经血分药也。若无故频食，则生虫损齿，贻害多矣。按王好古云︰中满者勿食甘，甘令人满。故张仲景建中汤心下痞者，减饧、枣，与甘草同例，此得用枣之方矣。又按许叔微《本事方》云︰一妇病脏燥悲泣不止，祈祷备至。予忆古方治此证用大枣汤，遂治，与服尽剂而愈。古人识病治方，妙绝如此。又陈自明《妇人良方》云︰程虎卿内人妊娠四、五个月，遇昼则惨戚悲伤，泪下数欠，如有所凭，医巫兼治皆无益。管伯周说︰先人曾语此，治须大枣汤乃愈。虎卿借方治药，一投而愈。方见下条。又《摘玄方》治此证，用红枣烧存性，酒服三钱，亦大枣汤变法也。</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
         <is>
           <t>果之一</t>
         </is>
@@ -15421,12 +17056,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>石膏
 【气味】味甘、辛，性大寒。
@@ -15445,7 +17083,7 @@
 广济林训导年五十，病痰嗽发热。或令单服石膏药至一斤许，遂不能食，而咳益频，病益甚，遂至不起。此盖用药者之瞀瞀也，石膏何与焉。杨士瀛云︰石膏 过，最能收疮晕，不至烂肌。按︰刘 《钱乙传》云︰宗室子病呕泄，医用温药加喘。乙曰︰病本中热，奈何以刚剂燥之，将不得前后溲，宜与石膏汤。宗室与医皆不信。后二日果来召。乙曰︰仍石膏汤证也。竟如言而愈。又按︰古方所用寒水石，是凝水石；唐宋以来诸方所用寒水石，即今之石膏也。故寒水石诸方多附于后。近人又以长石、方解石为寒水石，不可不辨之。</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>金石之三</t>
         </is>
@@ -15482,12 +17120,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>当归
 【气味】味甘、辛，性温。
@@ -15509,7 +17150,7 @@
 韩𢘅曰︰当归主血分之病。川产力刚可攻，秦产力柔宜补。凡用，本病宜酒制，有痰以姜制，导血归源之理。血虚以人参、石脂为佐，血热以生地黄、条芩为佐，不绝生化之源。血积配以大黄。要之，血药不容舍当归。故古方四物汤以为君，芍药为臣，地黄为佐，芎为使也。</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="J10" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -15546,12 +17187,15 @@
           <t>小毒</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>细辛
 【气味】味辛，性温。
@@ -15570,7 +17214,7 @@
 承曰：细辛非华阴者不得为真。若单用末，不可过一钱。多则气闷塞不通者死，虽死无伤。近年开平狱中尝治此，不可不记。非本有毒，但不识多寡耳。</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -15607,12 +17251,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>木通（通草）
 【气味】味苦，性寒。
@@ -15626,7 +17273,7 @@
 时珍曰︰木通手厥阴心包络、手足太阳小肠、膀胱之药也。故上能通心清肺，治头痛，利九窍；下能泄湿热，利小便，通大肠，治遍身拘痛。《本经》及《别录》皆不言及利小便治淋之功，甄权、日华子辈始发扬之。盖其能泄丙丁之火，则肺不受邪，能通水道。水源既清，则津液自化，而诸经之湿与热，皆由小便泄去。故古方导赤散用之，亦泻南补北、扶西抑东之意。杨仁斋《直指方》言︰人遍身胸腹隐热，疼痛拘急，足冷，皆是伏热伤血。血属于心，宜木通以通心窍，则经络流行也。</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="J12" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -15663,12 +17310,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>干姜
 【气味】味辛，性热。
@@ -15684,7 +17334,7 @@
 时珍曰：干姜，能引血药入血分，气药入气分，又能去恶养新，有阳生阴长之意，故血虚者用之；而人吐血、衄血、下血，有阴无阳者，亦宜用之。乃热因热用，从治之法也。</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>菜之一</t>
         </is>
@@ -15721,12 +17371,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>人参
 【气味】味甘、微苦，性微温。
@@ -15743,7 +17396,7 @@
 言闻曰︰人参生用气凉，熟用气温；味甘补阳，微苦补阴。气主生物，本呼天；味主成物，本呼地。气味生成，阴阳之造化也。凉者，高秋清肃之气，天之阴也，其性降；温者，阳春生发之气，天之阳也，其性升。甘者，湿土化成之味，地之阳也，其性浮；微苦者，火土相生之味，地之阴也，其性沉。人参气味俱薄。气之薄者，生降熟升；味之薄者，生升熟降。如土虚火旺之病，则宜生参，凉薄之气，以泻火而补土，是纯用其气也；脾虚肺怯之病，则宜熟参，甘温之味，以补土而生金，是纯用其味也。东垣以相火乘脾，身热而烦，气高而喘，头痛而渴，脉洪而大者，用黄柏佐人参。孙真人治夏月热伤元气，人汗大泄，欲成痿厥，用生脉散，以泻热火而救金水。君以人参之甘寒，泻火而补元气；臣以麦门冬之苦甘寒，清金而滋水源，佐以五味子之酸温，生肾精而收耗气。此皆补天元之真气，非补热火也。白飞霞云︰人参炼膏服，回元气于无何有之乡。凡病后气虚及肺虚嗽者，并宜之。若气虚有火者，合天门冬膏对服之。</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -15780,12 +17433,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>白术（术）
 【气味】味苦、甘，性温。
@@ -15800,7 +17456,7 @@
 机曰︰脾恶湿，湿胜则气不得施化，津何由生？故曰︰膀胱者津液之府，气化则能出焉。用白术以除其湿，则气得周流而津液生矣。</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -15837,12 +17493,15 @@
           <t>大毒</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>附子
 【气味】味辛、甘，性大热。
@@ -15859,7 +17518,7 @@
 时珍曰︰乌、附毒药，非危病不用，而补药中少加引导，其功甚捷。有人才服钱匕，即发燥不堪，而昔人补剂用为常药，岂古今运气不同耶？荆府都昌王，体瘦而冷，无他病。日以附子煎汤饮，兼嚼硫黄，如此数岁。蕲州卫张百户，平生服鹿茸、附子药，至八十馀，康 健倍常。宋张杲《医说》载︰赵知府耽酒色，每日煎干姜熟附汤，吞硫黄金液丹百粒，乃能健啖，否则倦弱不支，寿至九十。他人服一粒即为害。若此数人，皆其脏腑禀赋之偏，服之有益无害，不可以常理概论也。又《琐碎录》言︰滑台风土极寒，民啖附子如啖芋栗。此则地气使然尔。</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="J16" s="24" t="inlineStr">
         <is>
           <t>草之六</t>
         </is>
@@ -15896,12 +17555,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>茯苓
 【气味】味甘、淡，性平。
@@ -15920,7 +17582,7 @@
 时珍曰︰茯苓本草又言利小便，伐肾邪。至李东垣、王海藏乃言小便多者能止，涩者能通，同朱砂能秘真元。而朱丹溪又言阴虚者不宜用，义似相反，何哉？茯苓气味淡而渗，其性上行，生津液，开腠理，滋水之源而下降，利小便。故张洁古谓其属阳，浮而升，言其性也；东垣谓其为阳中之阴，降而下，言其功也。《素问》云︰饮食入胃，游溢精气，上输于肺，通调水道，下输膀胱。观此，则知淡渗之药，俱皆上行而后下降，非直下行也。小便多，其源亦异。《素问》云︰肺气盛则小便数而欠；虚则欠欬、小便遗数。心虚则少气遗溺。下焦虚则遗溺。胞移热于膀胱则遗溺。膀胱不利为癃，不约为遗溺。厥阴病则遗溺闭癃。所谓肺气盛者，实热也。其人必气壮脉强，宜用茯苓甘淡以渗其热，故曰︰小便多者能止也。若夫肺虚、心虚、胞热、厥阴病者，皆虚热也。其人必上热下寒，脉虚而弱。法当用升阳之药，以升水降火。膀胱不约、下焦虚者，乃火投于水，水泉不藏，脱阳之症。其人必肢冷脉迟。法当用温热之药，峻补其下，交济坎离。二症皆非茯苓辈淡渗之药所可治，故曰︰阴虚者不宜用也。仙家虽有服食之法，亦当因人而用焉。</t>
         </is>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>木之四</t>
         </is>
@@ -15957,12 +17619,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>知母
 【气味】味苦、甘，性寒。
@@ -15977,7 +17642,7 @@
 时珍曰︰肾苦燥，宜食辛以润之。肺苦逆，宜食苦以泻之。知母之辛苦寒凉，下则润肾燥而滋阴，上则清肺金而泻火，乃二经气分药也。黄柏则是肾经血分药。故二药必相须而行，昔人譬之虾与水母，必相依附。补阴之说，详黄柏条。</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="J18" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -16014,12 +17679,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>粳米（粳）
 【气味】味甘，性平。
@@ -16036,7 +17704,7 @@
 时珍曰︰粳稻六、七月收者为早粳（止可充食），八、九月收者为迟粳，十月收者为晚粳。北方气寒，粳性多凉，八、九月收者即可入药。南方气热，粳性多温，惟十月晚稻气凉乃可入药。迟粳、晚粳得金气多，故色白者入肺而解热也。早粳得土气多，故赤者益脾而白者益胃。若滇、岭之粳则性热，惟彼土宜之耳。</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="J19" s="24" t="inlineStr">
         <is>
           <t>谷之一</t>
         </is>
@@ -16073,12 +17741,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>黄连
 【气味】味苦，大寒。
@@ -16103,7 +17774,7 @@
 《神仙传》载封君达、黑穴公，并服黄连五十年得仙。窃谓黄连大苦大寒之药，用之降火燥 湿，中病即当止。岂可久服，使肃杀之令常行，而伐其生发冲和之气乎？《素问》载岐伯言 ：五味入胃，各归所喜攻。久而增气，物化之常也。气增而久，夭之由也。王冰注云：酸入肝为温，苦入心为热，辛入肺为清，咸入肾为寒，甘入脾为至阴而四气兼之，皆增其味而益其气，故各从本脏之气为用。所以久服黄连、苦参反热，从火化也，余味皆然。久则脏气偏 胜，即有偏绝，则有暴夭之道。是以绝粒服饵之人不暴亡者，无五味偏助也。又秦观与乔希 圣论黄连书云：闻公以眼疾饵黄连，至十数两犹不巳，殆不可也。医经有久服黄连、苦参反 热之说。此虽大寒，其味至苦，入胃则先归于心，久而不己，心火偏胜则热，乃其理也。况 眼疾本于肝热，肝与心为子母。心火也，肝亦火也，肾孤脏也，人患一水不胜二火。岂可久 服苦药，使心有所偏胜，是以火救火，其可乎？秦公此书，盖因王公之说而推详之也。我明荆端王素多火病，医令服金花丸，乃芩、连、栀、柏四味，饵至数年，其火愈炽，遂至内障 丧明。观此，则寒苦之药，不但使人不能长生，久则气增偏胜，速夭之由矣。当以《素问》 之言为法，陶氏道书之说，皆谬谈也。杨士瀛云：黄连能去心窍恶血。</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="J20" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -16140,12 +17811,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>黄芩
 【气味】味苦，性寒。
@@ -16162,7 +17836,7 @@
 时珍曰：洁古张氏言：黄芩泻肺火，治脾湿；东垣李氏言：片芩治肺火，条芩治大肠火；丹溪朱氏言：黄芩治上中二焦火；而张仲景治少阳证小柴胡汤，太阳少阳合病下利黄芩汤，少阳证下后心下满而不痛泻心汤，并用之；成无己言黄芩苦而入心，泄痞热。是黄芩能入手少阴阳明、手足太阴少阳六经矣。盖黄芩气寒味苦，色黄带绿，苦入心，寒胜热，泻心火，治脾之湿热，一则金不受刑，一则胃火不流入肺，即所以救肺也。肺虚不宜者，苦寒伤脾胃，损其母也。少阳之证，寒热胸胁痞满，默默不欲饮食，心烦呕，或渴或痞，或小便不利。虽曰病在半表半里，而胸胁痞满，实兼心肺上焦之邪。心烦喜呕，默默不欲饮食，又兼脾胃中焦之证。故用黄芩以治手足少阳相火，黄芩亦少阳本经药也。成无己《注伤寒论》，但云柴胡、黄芩之苦，以发传邪之热；芍药、黄芩之苦，以坚敛肠胃之气，殊昧其治火之妙。杨士瀛《直指方》云：柴胡退热，不及黄芩。盖亦不知柴胡之退热，乃苦以发之，散火之标也；黄芩之退热，乃寒能胜热，折火之本也。仲景又云：少阳证腹中痛者，去黄芩，加芍药。心下悸，小便不利者，去黄芩，加茯苓。似与《别录》治少腹绞痛、利小肠之文不合。成氏言黄芩寒中，苦能坚肾，故去之，盖亦不然。至此当以意逆之，辨以脉证可也。若因饮寒受寒，腹中痛，及饮水心下悸，小便不利，而脉不数者，是里无热证，则黄芩不可用也。若热厥腹痛，肺热而小便不利者，黄芩其可不用乎？故善观书者，先求之理，毋徒泥其文。昔有人素多酒欲，病少腹绞痛不可忍，小便如淋，诸药不效。偶用黄芩、木通、甘草三味煎服，遂止。王海藏言有人因虚服附子药多，病小便秘，服芩、连药而愈。此皆热厥之痛也，学人其可拘乎？予年二十时，因感冒咳嗽既久，且犯戒，遂病骨蒸发热，肤如火燎，每日吐痰碗许，暑月烦渴，寝食几废，六脉浮洪。遍服柴胡、麦门冬、荆沥诸药，月馀益剧，皆以为必死矣。先君偶思李东垣治肺热如火燎，烦躁引饮而昼盛者，气分热也。宜一味黄芩汤，以泻肺经气分之火。遂按方用片芩一两，水二钟，煎一钟，顿服。次日身热尽退，而痰嗽皆愈。药中肯綮，如鼓应桴，医中之妙，有如此哉。</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -16199,12 +17873,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>阿胶
 【气味】甘，平。
@@ -16220,7 +17897,7 @@
 成无己云︰阴不足者补之以味，阿胶之甘以补阴血。，不论肺虚肺实，可下可温，须用阿胶以安肺润肺。其性和平，为肺经要药。小儿惊风后瞳仁不正者，以阿胶倍人参煎服最良。阿胶育神，人参益气也。又痢疾多因伤暑伏热而成，阿胶乃大肠之要药。有热毒留滞者，则能疏导；无热毒留滞者，则能平安。数说足以发明阿胶之蕴矣。</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="J22" s="24" t="inlineStr">
         <is>
           <t>兽之一</t>
         </is>
@@ -16257,12 +17934,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>鸡子黄
 【气味】味甘，性平。
@@ -16277,7 +17957,7 @@
 时珍曰︰鸡子黄，气味俱浓，阴中之阴，故能补形。昔人谓其与阿胶同功，正此意也。其治呕逆诸疮，则取其除热引虫而已。颂曰︰鸡子入药最多，而发煎方特奇。刘禹锡《传信方》云︰乱发鸡子膏，治孩子热疮。用鸡子五枚，去白取黄，乱发如鸡子大，相和，于铁铫中炭火熬之。初甚干，少顷即发焦，乃有液出。旋取置碗中，以液尽为度。取涂疮上，即以苦参末粉之。顷在武陵生子，蓐内便有热疮，涂诸药无益，而日益剧，蔓延半身，昼夜号啼，不乳不睡。因阅本草发 条云︰合鸡子黄煎之，消为水，疗小儿惊热、下痢。注云︰俗中妪母为小儿作鸡子煎，用发杂熬之，良久得汁，与小儿服，去痰热，主百病。又鸡子条云︰疗火疮。因是用之，果如神效也。</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>禽之二</t>
         </is>
@@ -16314,12 +17994,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>金银花（忍冬）
 【气味】味甘，性寒。
@@ -16333,7 +18016,7 @@
 时珍曰︰忍冬，茎叶及花，功用皆同。昔人称其治风除胀，解痢逐尸为要药，而后世不复知用，后世称其消肿散毒治疮为要药，而昔人并未言及。乃知古今之理，万变不同，未可一辙论也。按︰陈自明《外科精要》云︰忍冬酒，治痈疽发背，初发便当服此，其效甚奇，胜于红内消。洪内翰迈、沈内翰括诸方，所载甚详。如疡医丹阳僧、江西僧鉴清、金陵王琪、王尉子骏、海州刘秀才纯臣等，所载疗痈疽发背经效奇方，皆是此物。故张相公云︰谁知至贱之中，乃有殊常之效，正此类也。</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -16370,12 +18053,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>连翘
 【气味】味苦，性微寒。
@@ -16393,7 +18079,7 @@
 时珍曰︰连翘状似人心，两片合成，其中有仁甚香，乃少阴心经、厥阴包络气分主药也。诸痛痒疮疡皆属心火，故为十二经疮家圣药，而兼治手足少阳手阳明三经气分之热也。</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="J25" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -16430,12 +18116,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>牛蒡子（恶实）
 【气味】味辛、苦，性寒。
@@ -16449,7 +18138,7 @@
 杲曰︰鼠粘子其用有四︰治风湿瘾疹，咽喉风热，散诸肿疮疡之毒，利凝滞腰 膝之气，是也。</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="J26" s="24" t="inlineStr">
         <is>
           <t>草之四</t>
         </is>
@@ -16486,12 +18175,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>荆芥（假苏）
 【气味】味辛，性微温。
@@ -16511,7 +18203,7 @@
 又曰︰荆芥反鱼蟹河豚之说，本草医方并未言及，而稗官小说往往载之。按李廷飞《延 寿书》云︰凡食一切无鳞鱼，忌荆芥。食黄 鱼后食之，令人吐血，惟地浆可解。与蟹同食，动风。又《蔡絛铁围山丛话》云︰予居岭峤，见食黄颡鱼犯姜芥者立死，甚于钩吻。洪 迈《夷坚志》云︰吴人魏几道，啖黄颡鱼羹，后采荆芥和茶饮。少顷足痒，上彻心肺，狂走，足皮欲裂。急服药，两日乃解。陶九成《辍耕录》云︰凡食河豚，不可服荆芥药，大相反。 予在江阴见一儒者，因此丧命。《苇航纪谈》云︰凡服荆芥风药，忌食鱼。杨诚斋曾见一人，立致于死也。时珍按︰荆芥乃日用之药，其相反如此，故详录之，以为警戒。又按《物类相感志》言︰河豚用荆芥同煮，三五次换水，则无毒。其说与诸书不同，何哉？大抵养生者，宁守前说为戒可也。</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
+      <c r="J27" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -16548,12 +18240,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>薄荷
 【气味】辛，凉。
@@ -16571,7 +18266,7 @@
 时珍曰：薄荷入手太阴、足厥阴，辛能发散，凉能清利，专于消风散热，故头痛头风眼目咽喉口齿诸病，小儿惊热及瘰疬疮疥，为要药。戴原礼氏治猫咬，取其汁涂之有效，盖取其相制也。陆农师曰：薄荷，猫之酒也。犬，虎之酒也。桑椹，鸠之酒也。草，鱼之酒也。昝殷</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
+      <c r="J28" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -16608,12 +18303,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>淡豆豉（大豆豉）
 【气味】味苦、辛，性凉。
@@ -16627,7 +18325,7 @@
 时珍曰︰陶说康伯豉法，见《博物志》，云原出外国，中国谓之康伯，乃传此法之姓名耳。其豉调中下气最妙。黑豆性平，作豉则温。既经蒸 ，故能升能散。得葱则发汗，得盐则能吐，得酒则治风，得薤则治痢，得蒜则止血，炒熟则又能止汗，亦麻黄根节之义也。</t>
         </is>
       </c>
-      <c r="I29" s="24" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr">
         <is>
           <t>谷之四</t>
         </is>
@@ -16664,12 +18362,15 @@
           <t>小毒</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>桔梗
 【气味】味苦、辛，性平。
@@ -16685,7 +18386,7 @@
 时珍曰︰朱肱《活人书》治胸中痞满不痛，用桔梗、枳壳，取其通肺利膈下气也。张仲景《伤寒论》治寒实结胸，用桔梗、贝母、巴豆，取其温中消谷破积也。又治肺痈唾脓，用桔梗、甘草，取其苦辛清肺，甘温泻火，又能排脓血、补内漏也。其治少阴证二、三日咽痛，亦用桔梗、甘草，取其苦辛散寒，甘平除热，合而用之，能调寒热也。后人易名甘桔汤，通治咽喉口舌诸病。宋仁宗加荆芥、防风、连翘，遂名如圣汤，极言其验也。按︰王好古《医垒元戎》载之颇详，云失音，加诃子；声不出，加半夏；上气，加陈皮；涎嗽，加知母、贝母；咳渴，加五味子；酒毒，加葛根；少气，加人参；呕，加半夏、生姜；唾脓血，加紫菀；肺痿，加阿胶；胸膈不利，加枳壳；心胸痞满，加枳实；目赤，加栀子、大黄；面肿，加茯苓；肤痛，加黄耆；发斑，加防风、荆芥；疫毒，加鼠粘子、大黄；不得眠，加栀子。震亨曰︰干咳嗽，乃痰火之邪郁在肺中，宜苦梗以开之；痢疾腹痛，乃肺金之气郁在大肠，亦宜苦梗开之，后用痢药。此药能开提气血，故气药中宜用之。</t>
         </is>
       </c>
-      <c r="I30" s="24" t="inlineStr">
+      <c r="J30" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -16722,12 +18423,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>芦根（芦）
 【气味】味甘，性寒。
@@ -16740,7 +18444,7 @@
 时珍曰︰按《雷公炮炙论》序云︰益食加觞，须煎芦、朴。注云︰用逆水芦根并浓朴二味等分，煎汤服。盖芦根甘能益胃，寒能降火故也。</t>
         </is>
       </c>
-      <c r="I31" s="24" t="inlineStr">
+      <c r="J31" s="24" t="inlineStr">
         <is>
           <t>草之四</t>
         </is>
@@ -16777,12 +18481,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>竹叶（竹）
 【气味】味甘、淡，性寒。
@@ -16798,7 +18505,7 @@
 杲曰︰竹叶辛苦寒，可升可降，阳中阴也。其用有二︰除新久风邪之烦热，止喘促气胜</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
+      <c r="J32" s="24" t="inlineStr">
         <is>
           <t>木之五</t>
         </is>
@@ -16835,12 +18542,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>桑叶（桑）
 【气味】味甘、苦，性寒。
@@ -16856,7 +18566,7 @@
 时珍曰︰桑叶乃手、足阳明之药，汁煎代茗，能止消渴。</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr">
+      <c r="J33" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -16893,12 +18603,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>沙参
 【气味】味甘，性微寒。
@@ -16913,7 +18626,7 @@
 时珍曰︰人参甘苦温，其体重实，专补脾胃元气，因而益肺与肾，故内伤元气者宜之。沙参甘淡而寒，其体轻虚，专补肺气，因而益脾与肾，故金能受火克者宜之。一补阳而生阴，一补阴而制阳，不可不辨之也。</t>
         </is>
       </c>
-      <c r="I34" s="24" t="inlineStr">
+      <c r="J34" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -16950,12 +18663,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>贝母
 【气味】味甘、苦，性微寒。
@@ -16974,7 +18690,7 @@
 《本经》言主金疮，此岂金疮之类欤？</t>
         </is>
       </c>
-      <c r="I35" s="24" t="inlineStr">
+      <c r="J35" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -17011,12 +18727,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>栀子
 【气味】味苦，性寒。
@@ -17034,7 +18753,7 @@
 发黄，皆用栀子、茵陈、甘草、香豉四物作汤饮。又治大病后劳复，皆用栀子、鼠矢等汤，利小便而愈。其方极多，不可悉载。</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr">
+      <c r="J36" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -17071,12 +18790,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>梨皮（梨）
 【气味】味甘、微涩，性凉。
@@ -17092,7 +18814,7 @@
 时珍曰︰《别录》著梨，只言其害，不著其功。陶隐居言梨不入药。盖古人论病多主风寒，用药皆是桂、附，故不知梨有治风热、润肺凉心、消痰降火、解毒之功也。今人痰病、火病，十居六、七。梨之有益，盖不为少，但不宜过食尔。按︰《类编》云︰一士人状若有疾，厌厌无聊，往谒杨吉老诊之。杨曰︰君热症已极，气血消铄，此去三年，当以疽死。士人不乐而去。闻茅山有道士医术通神，而不欲自鸣。乃衣仆衣，诣山拜之，愿执薪水之役。道士留置弟子中。久之以实白道士。道士诊之，笑曰︰汝便下山，但日日吃好梨一颗。如生梨已尽，则取干者泡汤，食滓饮汁，疾自当平。士人如其戒，经一岁复见吉老。见其颜貌腴泽，脉息和平，惊曰︰君必遇异人，不然岂有痊理？士人备告吉老。吉老具衣冠望茅山设拜，自咎其学之未至。此与琐言之说仿佛。观夫二条，则梨之功岂小补哉？然惟乳梨、鹅梨、消梨可食，余梨则亦不能去病也。</t>
         </is>
       </c>
-      <c r="I37" s="24" t="inlineStr">
+      <c r="J37" s="24" t="inlineStr">
         <is>
           <t>果之二</t>
         </is>
@@ -17129,12 +18851,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>苏叶（苏）
 【气味】味辛，性温。
@@ -17149,7 +18874,7 @@
 宗奭曰︰紫苏其气香，其味微辛甘能散。今人朝暮饮紫苏汤，甚无益。医家谓芳草致豪贵之疾者，此有一焉。若脾胃寒人，多致滑泄，往往不觉。</t>
         </is>
       </c>
-      <c r="I38" s="24" t="inlineStr">
+      <c r="J38" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -17186,12 +18911,15 @@
           <t>有毒</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>半夏
 【气味】味辛，性温。
@@ -17210,7 +18938,7 @@
 时珍曰︰脾无留湿不生痰，故脾为生痰之源，肺为贮痰之器。半夏能主痰饮及腹胀者，为其体滑而味辛性温也。涎滑能润，辛温能散亦能润，故行湿而通大便，利窍而泄小便。所谓辛走气，能化液，辛以润之是矣。洁古张氏云︰半夏、南星治其痰，而咳嗽自愈。丹溪朱氏云︰二陈汤能使大便润而小便长。聊摄成氏云︰半夏辛而散，行水气而润肾燥。又《和剂 局方》，用半硫丸治老人虚秘，皆取其滑润也。世俗皆以南星、半夏为性燥，误矣。湿去则土燥，痰涎不生，非二物之性燥也。古方治咽痛喉痹，吐血下血，多用二物，非禁剂也。二物亦能散血，故破伤打扑皆主之。惟阴虚劳损，则非湿热之邪，而用利窍行湿之药，是乃重 竭其津液，医之罪也，岂药之咎哉？《甲乙经》用治夜不眠，是果性燥者乎？岐伯云︰卫气行于阳，阳气满，不得入于阴，阴气虚，故目不得瞑。治法︰饮以半夏汤一剂，阴阳既通，其卧立至。方用流水千里者八升，扬之万遍，取清五升，煮之，炊以苇薪，大沸，入秫米一升，半夏五合，煮一升半，饮汁一杯，日三，以知为度。病新发者，覆杯则卧，汗出则已。久者，三饮而已。</t>
         </is>
       </c>
-      <c r="I39" s="24" t="inlineStr">
+      <c r="J39" s="24" t="inlineStr">
         <is>
           <t>草之六</t>
         </is>
@@ -17247,12 +18975,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>前胡
 【气味】味苦、辛，性微寒。
@@ -17264,7 +18995,7 @@
 时珍曰：前胡味甘、辛，气微平，阳中之阴，降也。乃手足太阴、阳明之药，与柴胡纯阳上升入少阳、厥阴者不同也。其功长于下气，故能治痰热喘嗽、痞膈呕逆诸疾，气下则火降，痰亦降矣。所以有推陈致新之绩，为痰气要药。陶弘景言其与柴胡同功，非矣。治证虽同，而所入所主则异。</t>
         </is>
       </c>
-      <c r="I40" s="24" t="inlineStr">
+      <c r="J40" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -17301,12 +19032,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>陈皮（橘）
 【气味】味苦、辛，性温。
@@ -17323,7 +19057,7 @@
 同补药则补，同泻药则泻，同升药则升，同降药则降。脾乃元气之母，肺乃摄气之 ，故橘皮为二经气分之药，但随所配而补泻升降也。洁古张氏云︰陈皮、枳壳利其气而痰自下，盖此义也。同杏仁治大肠气秘，同桃仁治大肠血秘，皆取其通滞也。详见杏仁下。按方勺《泊宅编》云︰橘皮宽膈降气，消痰饮，极有殊功。他药贵新，惟此贵陈。外舅莫强中令丰城时得疾，凡食已辄胸满不下，百方不效。偶家人合橘红汤，因取尝之，似相宜，连日饮之。一日忽觉胸中有物坠下，大惊目瞪，自汗如雨。须臾腹痛，下数块如铁弹子，臭不可闻。自此胸次廓然，其疾顿愈，盖脾之冷积也。其方︰用橘皮（去穰）一斤，甘草、盐花各四两。水五碗，慢火煮干，焙研为末，白汤点服。名二贤散，治一切痰气特验。世医徒知半夏、南星之属，何足以语此哉？珍按︰二贤散，丹溪变之为润下丸，用治痰气有效。惟气实人服之相宜，气不足者不宜用之也。</t>
         </is>
       </c>
-      <c r="I41" s="24" t="inlineStr">
+      <c r="J41" s="24" t="inlineStr">
         <is>
           <t>果之二</t>
         </is>
@@ -17360,12 +19094,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>枳壳（枳）
 【气味】味苦、辛、酸，性微寒。
@@ -17384,7 +19121,7 @@
 震享曰︰难产多见于郁闷安逸之人，富贵奉养之家。古方瘦胎饮，为湖阳公主作也。予妹苦于难产，其形肥而好坐，予思此与公主正相反也。彼奉养之人，其气必实，故耗其气使平则易产。今形肥则气虚，久坐则气不运，当补其母之气。以紫苏饮加补气药，与十数贴服之，遂快产。</t>
         </is>
       </c>
-      <c r="I42" s="24" t="inlineStr">
+      <c r="J42" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -17421,12 +19158,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>麦门冬
 【气味】味甘、微苦，性微寒。
@@ -17442,7 +19182,7 @@
 时珍曰︰按︰赵继宗《儒医精要》云︰麦门冬以地黄为使，服之令人头不白，补髓，通肾气，定喘促，令人肌体滑泽，除身上一切恶气不洁之疾，盖有君而有使也。若有君无使，是独行无功矣。此方惟火盛气壮之人服之相宜。若气弱胃寒者，必不可饵也。</t>
         </is>
       </c>
-      <c r="I43" s="24" t="inlineStr">
+      <c r="J43" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -17479,12 +19219,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>玉竹（萎蕤）
 【气味】味甘，性微寒。
@@ -17501,7 +19244,7 @@
 时珍曰︰苏颂注黄精，疑青粘是黄精，与此说不同。今考黄精、葳蕤性味功用大抵相近，而葳蕤之功更胜。故青粘，一名黄芝，与黄精同名；一名地节，与葳蕤同名，则二物虽通用亦可。</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
+      <c r="J44" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -17538,12 +19281,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>天花粉（栝蒌）
 【气味】味甘、微苦，性微寒。
@@ -17560,7 +19306,7 @@
 时珍曰︰栝蒌根味甘微苦酸。其茎叶味酸。酸能生津，感召之理，故能止渴润枯。微苦降火，甘不伤胃。昔人只言其苦寒，似未深察。</t>
         </is>
       </c>
-      <c r="I45" s="24" t="inlineStr">
+      <c r="J45" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -17597,12 +19343,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>扁豆（藊豆）
 【气味】味甘，性微温。
@@ -17615,7 +19364,7 @@
 时珍曰︰硬壳白扁豆，其子充实，白而微黄，其气腥香，其性温平，得乎中和，脾之谷也。入太阴气分，通利三焦，能化清降浊，故专治中宫之病，消暑除湿而解毒也。其软壳及黑鹊色者，其性微凉，但可供食，亦调脾胃。</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
+      <c r="J46" s="24" t="inlineStr">
         <is>
           <t>谷之三</t>
         </is>
@@ -17652,12 +19401,15 @@
           <t>大毒</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>乌头（川乌，草乌）
 【气味】味辛、苦，性热。
@@ -17684,7 +19436,7 @@
 时珍曰︰草乌头、射罔，乃至毒之药。非若川乌头、附子，人所栽种，加以酿 制，杀其毒性之比。自非风顽急疾，不可轻投。甄权《药性论》言其益阳事，治男子肾气衰弱者，未可遽然也。此类止能搜风胜湿，开顽痰，治顽疮，以毒攻毒而已，岂有川乌头、附子补右肾命门之功哉？吾蕲郝知府自负知医，因病风癣，服草乌头、木鳖子药过多，甫入腹而麻痹，遂至不救，可不慎乎？ 机曰︰乌喙形如乌嘴，其气锋锐。宜其通经络，利关节，寻蹊达径，而直抵病所。煎为射罔，能杀禽兽。非气之锋锐捷利，能如是乎？ 杨清叟曰︰凡风寒湿痹，骨内冷痛，及损伤入骨，年久发痛，或一切阴疽肿毒。并宜草乌头、南星等分，少加肉桂为末，姜汁热酒调涂。未破者能内消，久溃者能去黑烂。二药性味辛烈，能破恶块，逐寒热，遇冷即消，遇热即溃。</t>
         </is>
       </c>
-      <c r="I47" s="24" t="inlineStr">
+      <c r="J47" s="24" t="inlineStr">
         <is>
           <t>草之六</t>
         </is>
@@ -17721,12 +19473,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>黄芪（黄耆）
 【气味】味甘，性微温。
@@ -17752,7 +19507,7 @@
 嘉谟曰︰人参补中，黄耆实表。凡内伤脾胃，发热恶寒，吐泄怠卧，胀满痞塞，神短脉微者，当以人参为君，黄耆为臣；若表虚自汗亡阳，溃疡痘疹阴疮者，当以黄耆为君，人参为臣，不可执一也。</t>
         </is>
       </c>
-      <c r="I48" s="24" t="inlineStr">
+      <c r="J48" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -17789,12 +19544,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>蜂蜜
 【气味】味甘，性平。
@@ -17808,7 +19566,7 @@
 诜曰︰但凡觉有热，四肢不和，即服蜜浆一碗，甚良。又点目中热膜，以家养白蜜为上，木蜜次之，崖蜜更次之也。与姜汁熬炼，治癞甚效。</t>
         </is>
       </c>
-      <c r="I49" s="24" t="inlineStr">
+      <c r="J49" s="24" t="inlineStr">
         <is>
           <t>虫之一</t>
         </is>
@@ -17845,12 +19603,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>生地黄（地黄）
 【气味】味甘、苦，性寒。
@@ -17868,7 +19629,7 @@
 时珍曰︰《本经》所谓干地黄者，乃阴干、日干、火干者，故又云生者尤良。《别录》复云生地黄者，乃新掘鲜者，故其性大寒。其熟地黄乃后人复蒸晒者。诸家本草皆指干地黄为熟地黄，虽主治证同，而凉血、补血之功稍异，故今别出熟地黄一条于下。</t>
         </is>
       </c>
-      <c r="I50" s="24" t="inlineStr">
+      <c r="J50" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -17905,12 +19666,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>天门冬
 【气味】味甘、苦，性寒。
@@ -17932,7 +19696,7 @@
 时珍曰︰天门冬清金降火，益水之上源，故能下通肾气，入滋补方，合群药用之有效。若脾胃虚寒人，单饵既久，必病肠滑，反成痼疾。此物性寒而润，能利大肠故也。</t>
         </is>
       </c>
-      <c r="I51" s="24" t="inlineStr">
+      <c r="J51" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -17969,12 +19733,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>酸枣仁（酸枣）
 【气味】味甘、酸，性平。
@@ -17988,7 +19755,7 @@
 时珍曰︰酸枣实，味酸性收，故主肝病，寒热结气，酸痹久泄，脐下满痛之症。其仁甘而润，故熟用疗胆虚不得眠、烦渴虚汗之症，生用疗胆热好眠，皆足厥阴、少阳药也。今人专以为心家药，殊昧此理。</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
+      <c r="J52" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -18025,12 +19792,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>柏子仁（柏）
 【气味】味甘，性平。
@@ -18046,7 +19816,7 @@
 《列仙传》云︰赤松子食柏实，齿落更生，行及奔马。谅非虚语也。</t>
         </is>
       </c>
-      <c r="I53" s="24" t="inlineStr">
+      <c r="J53" s="24" t="inlineStr">
         <is>
           <t>木之一</t>
         </is>
@@ -18083,12 +19853,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>玄参
 【气味】味甘、苦、咸，性微寒。
@@ -18102,7 +19875,7 @@
 时珍曰︰肾水受伤，真阴失守，孤阳无根，发为火病。法宜壮水以制火，故玄参与地黄同功。其消瘰 亦是散火，刘守真言︰结核是火病。</t>
         </is>
       </c>
-      <c r="I54" s="24" t="inlineStr">
+      <c r="J54" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -18139,12 +19912,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>丹参
 【气味】味苦，性微寒。
@@ -18157,7 +19933,7 @@
 时珍曰︰丹参色赤味苦，气平而降，阴中之阳也。入手少阴、厥阴之经，心与包络血分药也。按︰《妇人明理论》云︰四物汤治妇人病，不问产前、产后，经水多少，皆可通用。惟一味丹参散，主治与之相同。盖丹参能破宿血，补新血，安生胎，落死胎，止崩中带下，调经脉，其功大类当归、地黄、芎 、芍药故也。</t>
         </is>
       </c>
-      <c r="I55" s="24" t="inlineStr">
+      <c r="J55" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -18194,12 +19970,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="G56" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>远志
 【气味】味苦、辛，性温。
@@ -18213,7 +19992,7 @@
 时珍曰︰远志，入足少阴肾经，非心经药也。其功专于强志益精，治善忘。盖精与志，皆肾经之所藏也。肾经不足，则志气衰，不能上通于心，故迷惑善忘。《灵枢经》云︰肾藏精，精合志。肾盛怒而不止则伤志，志伤则喜忘其前言，腰脊不可以俯仰屈伸，毛悴色夭。又云︰人之善忘者，上气不足，下气有馀，肠胃实而心肺虚，虚则营卫留于下，久之不以时上，故善忘也。陈言《三因方》远志酒，治痈疽，云有奇功，盖亦补肾之力尔。葛洪《抱朴子》云：陵阳子仲服远志二十年，有子三十七人，能开书所视不忘，坐在立亡。</t>
         </is>
       </c>
-      <c r="I56" s="24" t="inlineStr">
+      <c r="J56" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -18250,12 +20029,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G57" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>五味子
 【气味】味酸、甘，性温。
@@ -18276,7 +20058,7 @@
 慎微曰︰《抱朴子》云︰五味者，五行之精，其子有五味。淮南公羡门子服之十六年，面色如玉女，入水不沾，入火不灼。</t>
         </is>
       </c>
-      <c r="I57" s="24" t="inlineStr">
+      <c r="J57" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -18313,12 +20095,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G58" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>熟地黄（地黄）
 【气味】味甘，性微温。
@@ -18337,7 +20122,7 @@
 颂曰︰崔元亮《海上方》︰治一切心痛，无问新久。以生地黄一味，随人所食多少，捣绞取汁，搜面作患此病二年，深以为恨，临终戒其家人，吾死后当剖去病本。从其言果得虫，置于竹节中，每所食皆饲之。因食地黄 亦与之，随即坏烂。由此得方。刘禹锡《传信方》亦纪其事云︰贞元十年，通事舍人崔抗女，患心痛垂绝，遂作地黄冷淘食，便吐一物，可方寸匕，状如蛤蟆，无足目，似有口，遂愈。冷淘勿著</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
+      <c r="J58" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -18374,12 +20159,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>山茱萸
 【气味】味酸、涩，性微温。
@@ -18393,7 +20181,7 @@
 好古曰︰滑则气脱，涩剂所以收之。山茱萸止小便利，秘精气，取其味酸涩以收滑也。仲景八味丸用之为君，其性味可知矣。</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
+      <c r="J59" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -18430,12 +20218,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G60" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>山药（薯蓣）
 【气味】味甘，性平。
@@ -18453,7 +20244,7 @@
 时珍曰︰按吴绶云︰山药入手、足太阴二经，补其不足，清其虚热。又按︰王履《溯洄集》云︰山药虽入手太阴，然肺为肾之上源，源既有滋，流岂无益，此八味丸所以用其强阴也。又按曹毗《杜兰香传》云︰食薯蓣可以辟雾露。</t>
         </is>
       </c>
-      <c r="I60" s="27" t="inlineStr">
+      <c r="J60" s="27" t="inlineStr">
         <is>
           <t>菜之二</t>
         </is>
@@ -18490,12 +20281,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G61" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>泽泻
 【气味】味甘、淡，性寒。
@@ -18512,7 +20306,7 @@
 时珍曰︰泽泻气平，味甘而淡。淡能渗泄，气味俱薄，所以利水而泄下。脾胃有湿热，则头重而目昏耳鸣。泽泻渗去其湿，则热亦随去，而土气得令，清气上行，天气明爽，故泽泻有养五脏、益气力、治头旋、聪明耳目之功。若久服，则降令太过，清气不升，真阴潜耗，安得不目昏耶？仲景地黄丸用茯苓、泽泻者，乃取其泻膀胱之邪气，非引接也。古人用补药必兼泻邪，邪去则补药得力，一辟一阖，此乃玄妙。后世不知此理，专一于补，所以久服必致偏胜之害也﹗</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
+      <c r="J61" s="24" t="inlineStr">
         <is>
           <t>草之八</t>
         </is>
@@ -18549,12 +20343,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G62" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>丹皮（牡丹）
 【气味】味苦、辛，性微寒。
@@ -18569,7 +20366,7 @@
 时珍曰︰牡丹皮治手、足少阴、厥阴四经血分伏火。盖伏火即阴火也，阴火即相火也。 古方惟以此治相火，故仲景肾气丸用之。后人乃专以黄柏治相火，不知牡丹之功更胜也。此乃千载秘奥，人所不知，今为拈出。赤花者利，白花者补，人亦罕悟，宜分别之。</t>
         </is>
       </c>
-      <c r="I62" s="24" t="inlineStr">
+      <c r="J62" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -18606,12 +20403,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G63" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>防风
 【气味】味辛、甘，性微温。
@@ -18623,7 +20423,7 @@
 【发明】元素曰：防风，治风通用。身半以上风邪用身，身半以下风邪，用梢，治风去湿之仙药也，风能胜湿故尔。能泻肺实，误服泻人上焦元气。杲曰：防风治一身尽痛，乃猝 伍卑贱之职，随所引而至，乃风药中润剂也。若补脾胃，非此引用不能行。凡脊痛项强，不可回顾，腰似折，项似拔者，乃手足太阳证，正当用防风。凡疮在胸膈以上，虽无手足太阳 证，亦当用之，为能散结，去上部风。病患身体拘倦者，风也，诸疮见此证，亦须用之。钱 仲阳泻黄散中倍用防风者，乃于土中泻木也。</t>
         </is>
       </c>
-      <c r="I63" s="24" t="inlineStr">
+      <c r="J63" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -18660,12 +20460,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="G64" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>秦艽
 【气味】味辛、苦，性平。
@@ -18679,7 +20482,7 @@
 时珍曰：秦艽，手足阳明经药也，兼入肝胆，故手足不遂、黄胆烦渴之病须之，取其去阳明之湿热也。阳明有湿，则身体酸疼烦热；有热，则日晡潮热骨蒸。所以《圣惠方》治急劳烦热，身体酸疼。用秦艽、柴胡各一两，甘草五钱。为末，每服三钱，白汤调下。治小儿骨蒸潮热，减食瘦弱。用秦艽、炙甘草各一两。每用一、二钱，水煎服之。钱乙加 薄荷叶五钱。</t>
         </is>
       </c>
-      <c r="I64" s="24" t="inlineStr">
+      <c r="J64" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -18716,12 +20519,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G65" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>川芎（芎䓖）
 【气味】味辛，性温。
@@ -18740,7 +20546,7 @@
 时珍曰︰五味入胃，各归其本脏。久服则增气偏胜，必有偏绝，故有暴夭之患。若药具 五味，备四气，君臣佐使配合得宜，岂有此害哉？如芎 ，肝经药也。若单服既久，则辛喜 归肺，肺气偏胜，金来贼木，肝必受邪，久则偏绝，岂不夭亡？故医者贵在格物也。</t>
         </is>
       </c>
-      <c r="I65" s="24" t="inlineStr">
+      <c r="J65" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -18777,12 +20583,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G66" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>葛根（葛）
 【气味】味甘、辛，性凉。
@@ -18800,7 +20609,7 @@
 时珍曰︰本草十剂云︰轻可去实，麻黄、葛根之属。盖麻黄乃太阳经药，兼入肺经，肺主皮毛；葛根乃阳明经药，兼入脾经，脾主肌肉。所以二味药皆轻扬发散，而所入迥然不同也。</t>
         </is>
       </c>
-      <c r="I66" s="24" t="inlineStr">
+      <c r="J66" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -18837,12 +20646,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G67" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>苍术
 【气味】辛、苦，温。
@@ -18861,7 +20673,7 @@
 时珍曰︰按︰《吐纳经》云︰紫微夫人术序云︰吾察草木之胜速益于己者，并不及术之多验也。可以长生久视，远而更灵。山林隐逸，得服术者，五岳比肩。又《神仙传》云︰陈子皇得饵术要方，其妻姜氏得疲病，服之自愈，颜色气力如二十时也。时珍谨按︰以上诸说，皆似苍术，不独白术。今服食家亦呼苍术为仙术，故皆列于苍术之后。又张仲景辟一切恶气，用赤术同猪蹄甲烧烟。陶隐居亦言术能除恶气，弭灾 。故今病疫及岁旦，人家往往烧苍术以辟邪气。《类编》载越民高氏妻，病恍惚谵语，亡夫之鬼凭之。其家烧苍术烟，鬼遽求去。《夷坚志》载江西一士人，为女妖所染。其鬼将别曰︰君为阴气所浸，必当暴泄，但多服平胃散为良。中有苍术能去邪也。许叔微《本事方》云︰微患饮癖三十年。始因少年夜坐写文，左向伏几，是以饮食多坠左边。中夜必饮酒数杯，又向左卧。壮时不觉，三、五年后，觉酒止从左下有声，胁痛食减嘈杂，饮酒半杯即止。十数日，必呕酸水数升。暑月止右边有汗，左边绝无。遍访名医及海上方，间或中病，止得月馀复作。其补，如天雄、附子、矾石辈；利，如牵牛、甘遂、大戟，备尝之矣。自揣必有癖囊，如潦水之有科臼，不盈科不行。但清者可行，而浊者停滞，无路以决之，故积至五、七日必呕而去。脾土恶湿，而水则流湿，莫若燥脾以去湿，崇土以填科臼。乃悉屏诸药，只以苍术一斤（去皮，切片，为末），生油麻（半两）（水二盏，研，滤汁），大枣（五十枚）（煮，去皮核）。捣和丸梧子大。每日空腹温服五十丸，增至一、二百丸。忌桃、李、雀肉。服三月而疾除。自此常服，不呕不痛，胸膈宽利，饮啖如故，暑月汗亦周身，灯下能书细字，皆术之力也。初服时必觉微燥，以山栀子末，沸汤点服解之，久服亦自不燥矣。</t>
         </is>
       </c>
-      <c r="I67" s="24" t="inlineStr">
+      <c r="J67" s="24" t="inlineStr">
         <is>
           <t>草之一</t>
         </is>
@@ -18898,12 +20710,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="G68" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>厚朴（浓朴）
 【气味】味苦、辛，性温。
@@ -18921,7 +20736,7 @@
 杲曰：苦能下气，故泄实满；温能益气，故散湿满。</t>
         </is>
       </c>
-      <c r="I68" s="24" t="inlineStr">
+      <c r="J68" s="24" t="inlineStr">
         <is>
           <t>木之二</t>
         </is>
@@ -18958,12 +20773,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G69" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>莲子（莲藕）
 【气味】味甘、涩，性平。
@@ -18979,7 +20797,7 @@
 诜曰︰诸鸟、猿猴取得不食，藏之石室内，人得三百年者，食之永不老也。又雁食之，粪于田野山岩之中，不逢阴雨，经久不坏。人得之，每旦空腹食十枚，身轻能登高涉远也。</t>
         </is>
       </c>
-      <c r="I69" s="24" t="inlineStr">
+      <c r="J69" s="24" t="inlineStr">
         <is>
           <t>果之六</t>
         </is>
@@ -19016,12 +20834,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G70" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>薏苡仁
 【气味】味甘、淡，性凉。
@@ -19037,7 +20858,7 @@
 颂曰︰薏苡仁，心肺之药多用之。故范汪治肺痈，张仲景治风湿、胸痹，并有方法。《济生方》治肺损咯血，以熟猪肺切，蘸薏苡仁末，空心食之。薏苡补肺，猪肺引经也。赵君猷言屡用有效。</t>
         </is>
       </c>
-      <c r="I70" s="24" t="inlineStr">
+      <c r="J70" s="24" t="inlineStr">
         <is>
           <t>谷之二</t>
         </is>
@@ -19074,12 +20895,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G71" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>砂仁
 【气味】味辛，性温。
@@ -19091,7 +20915,7 @@
 时珍曰︰按韩 《医通》云︰肾恶燥，以辛润之。缩砂仁之辛，以润肾燥。又云︰缩砂属土，主醒脾调胃，引诸药归宿丹田。香而能窜，和合五脏冲和之气，如天地以土 为冲和之气，故补肾药用同地黄丸蒸，取其达下之旨也。又化骨，食草木药及方士炼三黄皆用之，不知其性何以能制此物也？</t>
         </is>
       </c>
-      <c r="I71" s="24" t="inlineStr">
+      <c r="J71" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -19128,12 +20952,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G72" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>柴胡（茈胡）
 【气味】味苦、辛，性微寒。
@@ -19152,7 +20979,7 @@
 时珍曰：劳有五劳，病在五脏。若劳在肝、胆、心，及包络有热，或少阳经寒热者，则柴胡乃手足厥阴、少阳必用之药；劳在脾胃有热，或阳气下陷，则柴胡乃引清气、退热必用之药；惟劳在肺、肾者，不用可尔。然东垣李氏言诸有热者，宜加之；无热，则不加。又言诸经之疟，皆以柴胡为君。十二经疮疽，须用柴胡以散结聚。则是肺疟、肾疟，十二经之疮，有热者皆可用之矣。但要用者精思病原，加减佐使可也。寇氏不分脏腑经络、有热无热，乃谓柴胡不治劳乏，一概摈斥，殊非通论。如《和剂局方》治上下诸血，龙脑鸡苏丸，用银柴胡浸汁熬膏之法，则世人知此意者鲜矣。按：庞元英《谈薮》云：张知 久病疟，热时如火，年余骨立。医用茸、附诸药，热益甚。召医官孙琳诊之。琳投小柴胡汤一帖，热减十之九，三服脱然。琳曰：此名劳疟，热从髓出，加以刚剂，气血愈亏，安得不瘦？盖热有在皮肤、在脏腑、在骨髓，非柴胡不可。若得银柴胡，只须一服；南方者力减，故三服乃效也。观此，则得用药之妙的矣。寇氏之说，可尽凭乎？</t>
         </is>
       </c>
-      <c r="I72" s="24" t="inlineStr">
+      <c r="J72" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -19189,12 +21016,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G73" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>藿香
 【气味】味辛，性微温。
@@ -19208,7 +21038,7 @@
 好古曰︰手、足太阴之药。 故入顺气乌药散，则补肺；入黄 、四君子汤，则补脾也。</t>
         </is>
       </c>
-      <c r="I73" s="24" t="inlineStr">
+      <c r="J73" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -19245,12 +21075,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G74" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>白芷
 【气味】辛，温。
@@ -19269,7 +21102,7 @@
 宗奭曰︰《药性论》言白芷能蚀脓。今人用治带下，肠有败脓，淋露不已，腥秽殊甚，遂致脐腹冷痛，皆由败脓血所致，须此排脓。白芷一两，单叶红蜀葵根二两，白芍药、白枯 矾各半两。为末，以蜡化丸梧子大。每空心及饭前，米饮下十丸或十五丸。俟脓尽，乃以他药补之。</t>
         </is>
       </c>
-      <c r="I74" s="24" t="inlineStr">
+      <c r="J74" s="24" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -19306,12 +21139,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G75" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>大腹皮（槟榔）
 【气味】味辛，性微温。
@@ -19323,7 +21159,7 @@
 【发明】</t>
         </is>
       </c>
-      <c r="I75" s="24" t="inlineStr">
+      <c r="J75" s="24" t="inlineStr">
         <is>
           <t>果之三</t>
         </is>
@@ -19360,12 +21196,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G76" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>紫菀
 【气味】味辛、苦，性温。
@@ -19377,7 +21216,7 @@
 【发明】</t>
         </is>
       </c>
-      <c r="I76" s="24" t="inlineStr">
+      <c r="J76" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -19414,12 +21253,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G77" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>桑白皮（桑）
 【气味】味甘，性寒。
@@ -19434,7 +21276,7 @@
 颂曰︰桑白皮作线缝金疮肠出，更以热鸡血涂之。唐‧安金藏剖腹，用此法而愈。</t>
         </is>
       </c>
-      <c r="I77" s="24" t="inlineStr">
+      <c r="J77" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -19471,12 +21313,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G78" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>竹茹（竹）
 【气味】味甘，性微寒。
@@ -19487,7 +21332,7 @@
 【发明】</t>
         </is>
       </c>
-      <c r="I78" s="24" t="inlineStr">
+      <c r="J78" s="24" t="inlineStr">
         <is>
           <t>木之五</t>
         </is>
@@ -19524,12 +21369,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G79" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>枳实（枳）
 【气味】味苦、辛、酸，性微寒。
@@ -19547,7 +21395,7 @@
 好古曰：益气则佐之以人参、白术、干姜，破气则佐之以大黄、牵牛、芒硝，此《本经》所以言益气而复言消痞也。非白术不能去湿，非枳实不能除痞。故洁古制枳术丸方，以调胃脾；张仲景治心下坚大如盘，水饮所作，枳实白术汤，用枳实七枚，术三两，水一斗，煎三升，分三服，腹中软，即消也。余见枳壳下。</t>
         </is>
       </c>
-      <c r="I79" s="24" t="inlineStr">
+      <c r="J79" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -19584,12 +21432,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G80" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>羌活（独活羌活）
 【气味】味辛、苦，性温。
@@ -19604,7 +21455,7 @@
 刘完素曰：独活不摇风而治风，浮萍不沉水而利水，因其所胜而为制也。张元素曰：风能胜湿，故羌活能治水湿。独活与细辛同用，治少阴头痛，头运目眩，非此不能除；羌活与川芎同用，治太阳、少阴头痛，透关利节，治督脉为病，脊强而厥。好古曰：羌活乃足太阳、厥阴、少阴药，与独活不分二种。后人因羌活气雄，独活气细。故雄者，治足太阳风湿相搏，头痛、肢节痛、一身尽痛者，非此不能除，乃却乱反正之主君药也。细者，治足少阴伏风，头痛、两足湿痹、不能动止者，非此不能治，而不治太阳之证。时珍曰：羌活、独活皆能逐 风胜湿，透关利节，但气有刚、劣不同尔。《素问》云：从下上者，引而去之。二味苦辛而温，味之薄者，阴中之阳，故能引气上升，通达周身，而散风胜湿。按文系曰：唐刘师贞之兄病风，梦神人曰：但取胡王使者浸酒服，便愈。师贞访问，皆不晓。复梦其母曰：胡王使 者，即羌活也。求而用之，兄疾遂愈。嘉谟曰：羌活，本手足太阳表里引经之药，又入足少阴、厥阴。名列君部之中，非比柔懦之主。小无不入，大无不通。故能散肌表八风之邪，利周身百节之痛。</t>
         </is>
       </c>
-      <c r="I80" s="24" t="inlineStr">
+      <c r="J80" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -19641,12 +21492,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G81" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>独活（独活羌活）
 【气味】味辛、苦，性温。
@@ -19661,7 +21515,7 @@
 刘完素曰：独活不摇风而治风，浮萍不沉水而利水，因其所胜而为制也。张元素曰：风能胜湿，故羌活能治水湿。独活与细辛同用，治少阴头痛，头运目眩，非此不能除；羌活与川芎同用，治太阳、少阴头痛，透关利节，治督脉为病，脊强而厥。好古曰：羌活乃足太阳、厥阴、少阴药，与独活不分二种。后人因羌活气雄，独活气细。故雄者，治足太阳风湿相搏，头痛、肢节痛、一身尽痛者，非此不能除，乃却乱反正之主君药也。细者，治足少阴伏风，头痛、两足湿痹、不能动止者，非此不能治，而不治太阳之证。时珍曰：羌活、独活皆能逐 风胜湿，透关利节，但气有刚、劣不同尔。《素问》云：从下上者，引而去之。二味苦辛而温，味之薄者，阴中之阳，故能引气上升，通达周身，而散风胜湿。按文系曰：唐刘师贞之兄病风，梦神人曰：但取胡王使者浸酒服，便愈。师贞访问，皆不晓。复梦其母曰：胡王使 者，即羌活也。求而用之，兄疾遂愈。嘉谟曰：羌活，本手足太阳表里引经之药，又入足少阴、厥阴。名列君部之中，非比柔懦之主。小无不入，大无不通。故能散肌表八风之邪，利周身百节之痛。</t>
         </is>
       </c>
-      <c r="I81" s="24" t="inlineStr">
+      <c r="J81" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -19698,12 +21552,15 @@
           <t>有毒</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G82" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>胆南星（虎掌）
 【气味】味苦、微辛，性凉。
@@ -19719,7 +21576,7 @@
 杨士瀛《直指方》云︰诸风口噤，宜用南星，更以人参、石菖蒲佐之。</t>
         </is>
       </c>
-      <c r="I82" s="24" t="inlineStr">
+      <c r="J82" s="24" t="inlineStr">
         <is>
           <t>草之六</t>
         </is>
@@ -19756,12 +21613,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G83" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>石菖蒲（菖蒲）
 【气味】味辛、苦，性温。
@@ -19777,7 +21637,7 @@
 杨士瀛曰︰下痢噤口，虽是脾虚，亦热气闭隔心胸所致。俗用木香失之温，用山药失之闭。惟参苓白术散加石菖蒲，粳米饮调下。或用参、苓、石莲肉，少入菖蒲服。胸次一开，自然思食。</t>
         </is>
       </c>
-      <c r="I83" s="24" t="inlineStr">
+      <c r="J83" s="24" t="inlineStr">
         <is>
           <t>草之八</t>
         </is>
@@ -19814,12 +21674,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G84" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>香附（莎根，香附子）
 【气味】味辛、微苦、微甘，性平。
@@ -19833,7 +21696,7 @@
 时珍曰︰香附之气平而不寒，香而能窜。其味多辛能散，微苦能降，微甘能和。乃足厥 阴肝、手少阳三焦气分主药，而兼通十二经气分。生则上行胸膈，外达皮肤；熟则下走肝肾，外彻腰足。炒黑则止血，得童溲浸炒则入血分而补虚，盐水浸炒则入血分而润燥，青盐炒则补肾气，酒浸炒则行经络，醋浸炒则消积聚，姜汁炒则化痰饮。得参、术，则补气；得归、，则补血；得木香，则疏滞和中；得檀香则理气醒脾，得沉香则升降诸气，得芎 、苍术 则总解诸郁，得栀子、黄连则能降火热，得茯神则交济心肾，得茴香、破故纸则引气归元，得浓朴、半夏则决壅消胀，得紫苏、葱白则解散邪气，得三棱、莪术则消磨积块，得艾叶则治血气暖子宫，乃气病之总司，女科之主帅也。飞霞子韩 云︰香附能推陈致新，故诸书皆云益气。而俗有耗气之说，宜于女人不宜于男子者，非矣。盖妇人以血用事，气行则无疾。 老人精枯血闭，惟气是资。小儿气日充，则形乃日固。大凡病则气滞而馁，故香附于气分为君药，世所罕知。臣以参、 ，佐以甘草，治虚怯甚速也。 游方外时，悬壶轻赉，治百病黄鹤丹，治妇人青囊丸，随宜用引，辄有小效。人索不已，用者当思法外意可也。黄鹤丹乃铢衣翁在黄鹤楼所授之方，故名。其方用香附一斤，黄连半斤，洗晒为末，水糊丸梧子大。 假如外感，葱姜汤下；内伤，米饮下；气病，木香汤下；血病，酒下；痰病，姜汤下；火病，白汤下。余可类推。青囊丸乃邵应节真人祷母病，感方士所授者。方用香附（略炒）一斤，乌药（略炮）五两三钱，为末，水醋煮面糊为丸。随证用引，如头痛，茶下；痰气，姜汤下；多用酒下，为妙。</t>
         </is>
       </c>
-      <c r="I84" s="24" t="inlineStr">
+      <c r="J84" s="24" t="inlineStr">
         <is>
           <t>草之八</t>
         </is>
@@ -19870,12 +21733,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G85" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>肉桂（桂）
 【气味】味辛、甘，性大热。
@@ -19892,7 +21758,7 @@
 又桂性辛散，能通子宫而破血，故《别录》言其堕胎，庞安时乃云炒过则不损胎也。又丁香、官桂治痘疮灰塌，能温托化脓，详见丁香下。</t>
         </is>
       </c>
-      <c r="I85" s="24" t="inlineStr">
+      <c r="J85" s="24" t="inlineStr">
         <is>
           <t>木之一</t>
         </is>
@@ -19929,12 +21795,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G86" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>茴香
 【气味】味辛，性温。
@@ -19950,7 +21819,7 @@
 时珍曰：小茴香性平，理气开胃，夏月祛蝇辟臭，食料宜之。大茴香性热，多食伤目发疮，食料不宜过用。古方有去铃丸：用茴香二两，连皮生姜四两，同入坩器内腌一伏时，慢火炒之，入盐一两，为末，糊丸梧子大。每服三、五十丸，空心盐酒下。此方本治脾胃虚弱病。茴香得盐则引入肾经，发出邪气。肾不受邪，病自不生也。亦治小肠疝气有效。</t>
         </is>
       </c>
-      <c r="I86" s="24" t="inlineStr">
+      <c r="J86" s="24" t="inlineStr">
         <is>
           <t>菜之二</t>
         </is>
@@ -19987,12 +21856,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G87" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>枸杞子（枸杞地骨皮）
 【气味】味甘，性平。
@@ -20011,7 +21883,7 @@
 所集《保寿堂方》载地仙丹云︰昔有异人赤脚张，传此方于猗氏县一老人，服之寿百馀，行走如飞，发白反黑，齿落更生，阳事强健。此药性平，常服能除邪热，明目轻身。春采枸杞叶，名天精草；夏采花，名长生草；秋采子，名枸杞子；冬采根，名地骨皮。并阴干，用无灰酒浸一夜，晒露四十九昼夜，取日精月华气，待干为末，炼蜜丸如弹子大。每早晚各用一丸细嚼，以隔夜百沸汤下。此药采无刺味甜者，其有刺者服之无益。</t>
         </is>
       </c>
-      <c r="I87" s="24" t="inlineStr">
+      <c r="J87" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -20048,12 +21920,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G88" s="7" t="inlineStr">
+      <c r="G88" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>乌药
 【气味】味辛，性温。
@@ -20068,7 +21943,7 @@
 《朱氏集验方》治虚寒小便频数，缩泉丸，用同益智子等分为丸服者，取其通阳明、少阴经也，方见草部益智子下。</t>
         </is>
       </c>
-      <c r="I88" s="24" t="inlineStr">
+      <c r="J88" s="24" t="inlineStr">
         <is>
           <t>木之一</t>
         </is>
@@ -20105,12 +21980,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G89" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>沉香
 【气味】味辛、苦，性微温。
@@ -20123,7 +22001,7 @@
 【发明】</t>
         </is>
       </c>
-      <c r="I89" s="24" t="inlineStr">
+      <c r="J89" s="24" t="inlineStr">
         <is>
           <t>木之一</t>
         </is>
@@ -20160,12 +22038,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
+      <c r="G90" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>龟板胶（水龟）
 【气味】甘、咸，凉。
@@ -20180,7 +22061,7 @@
 乃物理之玄微，神工之能事。观龟甲所主诸病，皆属阴虚血弱，自可心解矣。又见鳖甲。</t>
         </is>
       </c>
-      <c r="I90" s="24" t="inlineStr">
+      <c r="J90" s="24" t="inlineStr">
         <is>
           <t>介之一</t>
         </is>
@@ -20217,12 +22098,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G91" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>鹿角胶
 【气味】甘、咸，温。
@@ -20237,7 +22121,7 @@
 时珍曰︰苏东坡《良方》云︰鹿阳兽，见阴而角解；麋阴兽，见阳而角解。故补阳以鹿角为胜，补阴以麋角为胜。其不同如此，但云鹿胜麋，麋胜鹿，疏矣。按此说与沈存中“鹿茸利补阴，麋茸利补阳”之说相反。以理与功推之，苏说为是。详见茸下。</t>
         </is>
       </c>
-      <c r="I91" s="24" t="inlineStr">
+      <c r="J91" s="24" t="inlineStr">
         <is>
           <t>兽之二</t>
         </is>
@@ -20274,12 +22158,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G92" s="7" t="inlineStr">
+      <c r="G92" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>菟丝子
 【气味】甘，温。
@@ -20296,7 +22183,7 @@
 颂曰︰《抱朴子》仙方单服法︰取实一斗，酒一斗浸，曝干再浸又曝，令酒尽乃止，捣筛。每酒服二钱，日二服。此药治腰膝去风，兼能明目。久服令人光泽，老变为少。十日外，饮啖如汤沃雪也。</t>
         </is>
       </c>
-      <c r="I92" s="24" t="inlineStr">
+      <c r="J92" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -20333,12 +22220,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G93" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>牛膝
 【气味】苦、甘、酸，平。
@@ -20354,7 +22244,7 @@
 时珍曰︰牛膝乃足厥阴、少阴之药。所主之病，大抵得酒则能补肝肾，生用则能去恶血，二者而已。其治腰膝骨痛、足痿阴消、失溺久疟、伤中少气诸病，非取其补肝肾之功欤？其症瘕心腹诸痛、按陈日华《经验方》云︰方夷吾书云︰老人久苦淋疾，百药不效。偶见临汀《集要方》中用牛膝者，服之而愈。又叶朝议亲人患血淋，流下小便在盆内凝如 ，膝根煎浓汁，日饮五服，名地髓汤。虽未即愈，而血色渐淡，久乃复旧。后十年病又作，服之又瘥。因检本草，见《肘后方》治小便不利，茎中痛欲死，用牛膝并叶，以酒煮服之。今再拈出，表其神功。又按杨士瀛《直指方》云︰小便淋痛，或尿血，或沙石胀痛。用川牛膝一两，水二盏，煎一盏，温服。一妇患此十年，服之得效。杜牛膝亦可，或入麝香、乳香尤良。</t>
         </is>
       </c>
-      <c r="I93" s="24" t="inlineStr">
+      <c r="J93" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -20391,12 +22281,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
+      <c r="G94" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>瓜蒌仁（栝蒌）
 【气味】味甘，性寒。
@@ -20412,7 +22305,7 @@
 时珍曰︰张仲景治胸痹痛引心背，咳唾喘息，及结胸满痛，皆用栝蒌实。乃取其甘寒不犯胃气，能降上焦之火，使痰气下降也。成无己不知此意，乃云苦寒以泻热。盖不尝其味原不苦，而随文傅会尔。</t>
         </is>
       </c>
-      <c r="I94" s="24" t="inlineStr">
+      <c r="J94" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -20449,12 +22342,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>钩藤（钓藤）
 【气味】味甘，性凉。
@@ -20467,7 +22363,7 @@
 时珍曰︰钓藤，手足厥阴药也。足厥阴主风，手厥阴主火。 惊痫眩晕，皆肝风相火之病。钓藤通心包于肝木，风静火息，则诸证自除。或云︰入数寸</t>
         </is>
       </c>
-      <c r="I95" s="24" t="inlineStr">
+      <c r="J95" s="24" t="inlineStr">
         <is>
           <t>草之七</t>
         </is>
@@ -20504,12 +22400,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="G96" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>菊花（菊）
 【气味】味甘、苦，性微寒。
@@ -20525,7 +22424,7 @@
 时珍曰︰菊春生夏茂，秋花冬实，备受四气，饱经露霜，叶枯不落，花槁不零，味兼甘苦，性禀平和。昔人谓其能除风热，益肝补阴，盖不知其得金水之精英尤多，能益金水二脏也。补水所以制火，益金所以平木，木平则风息，火降则热除，用治诸风头目，其旨深微。黄者入金水阴分；白者，入金水阳分；红者，行妇人血分。皆可入药，神而明之，存乎其人。其苗可蔬，叶可啜，花可饵，根实可药，囊之可枕，酿之可饮，自本至末，罔不有功。宜乎前贤比之君子，神农列之上品，隐士采入酒饵，骚人餐其落英。费长房言︰九日饮菊酒，可以辟不祥。《神仙传》言︰康风子、朱孺子皆以服菊花成仙。《荆州记》言︰胡广久病风羸，饮菊潭水多寿。菊之贵重如此，是岂群芳可伍哉？钟会《菊有五美赞》云︰圆花高悬，准天极也。纯黄不杂，后土色也。早植晚发，君子德也；冒霜吐颖，象贞质也；杯中体轻，神仙 食也。《西京杂记》言︰采菊花茎叶，杂秫米酿酒，至次年九月始熟，用之</t>
         </is>
       </c>
-      <c r="I96" s="24" t="inlineStr">
+      <c r="J96" s="24" t="inlineStr">
         <is>
           <t>草之四</t>
         </is>
@@ -20562,12 +22461,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G97" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>龙胆草（龙胆）
 【气味】味苦，性寒。
@@ -20581,7 +22483,7 @@
 时珍曰：相火寄在肝胆，有泻无补，故龙胆之益肝胆之气，正以其能泻肝胆之邪热也。但大苦大寒，过服恐伤胃中生发之气，反助火邪，亦久服黄连反从火化之义。《别录》久服轻身之说，恐不足信。</t>
         </is>
       </c>
-      <c r="I97" s="24" t="inlineStr">
+      <c r="J97" s="24" t="inlineStr">
         <is>
           <t>草之二</t>
         </is>
@@ -20618,12 +22520,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
+      <c r="G98" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>车前子（车前）
 【气味】味甘，性寒。
@@ -20639,7 +22544,7 @@
 时珍曰︰按《神仙服食经》云︰车前一名地衣，雷之精也，服之形化，八月采之。今车前五月子已老，而云七八月者，地气有不同尔。唐《张籍诗》云︰开州午月，皆道有神。惭愧文君怜病眼，三千里外寄闲人。观此亦以五月采开州者为良，又可见其治目之功。大抵入服食，须佐他药，如六味地黄丸之用泽泻可也。若单用则泄太过，恐非久服之物。欧阳公常得暴下病，国医不能治。夫人买市人药一帖，进之而愈。力叩其方，则车前子一味为末，米饮服二钱匕。云此药利水道而不动气，水道利则清浊分，而谷藏自止矣。</t>
         </is>
       </c>
-      <c r="I98" s="27" t="inlineStr">
+      <c r="J98" s="27" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -20676,12 +22581,15 @@
           <t>小毒</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G99" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>川楝子（楝）
 【气味】味苦，性寒。
@@ -20695,7 +22603,7 @@
 时珍曰︰楝实，导小肠、膀胱之热，因引心包相火下行，故心腹痛及疝气为要药。甄权乃言不入汤使，则《本经》何以有治热狂、利小便之文耶？近方治疝，有四治、五治、七治诸法，盖亦配合之巧耳。</t>
         </is>
       </c>
-      <c r="I99" s="24" t="inlineStr">
+      <c r="J99" s="24" t="inlineStr">
         <is>
           <t>木之二</t>
         </is>
@@ -20732,12 +22640,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G100" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>龙眼
 【气味】味甘，性温。
@@ -20752,7 +22663,7 @@
 时珍曰︰食品以荔枝为贵，而资益则龙眼为良。盖荔枝性热，而龙眼性和平也。严用和《济生方》，治思虑劳伤心脾有归脾汤，取甘味归脾、能益人智之义。</t>
         </is>
       </c>
-      <c r="I100" s="24" t="inlineStr">
+      <c r="J100" s="24" t="inlineStr">
         <is>
           <t>果之三</t>
         </is>
@@ -20789,12 +22700,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G101" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>茯神（茯苓）
 【气味】味甘、淡，性平。
@@ -20811,7 +22725,7 @@
 《圣济录》松节散︰用茯神心中木一两，乳香一钱，石器炒，研为末。每服二钱，木瓜酒下。治风寒冷湿搏于筋骨，足筋挛痛，行步艰难，但是诸筋挛缩疼痛并主之。</t>
         </is>
       </c>
-      <c r="I101" s="24" t="inlineStr">
+      <c r="J101" s="24" t="inlineStr">
         <is>
           <t>木之四</t>
         </is>
@@ -20848,12 +22762,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G102" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>木香
 【气味】味辛、苦，性温。
@@ -20874,7 +22791,7 @@
 颂曰︰《续传信方》著张仲景青木香丸，主阳衰诸不足。用昆仑青木香、六路诃子皮各二十两。捣筛，糖和丸梧桐子大。每空腹酒下三十丸，日再，其效尤速。郑驸马去沙糖用白蜜，加羚羊角十二两。用药不类古方，而云仲景，不知何从而得也？</t>
         </is>
       </c>
-      <c r="I102" s="24" t="inlineStr">
+      <c r="J102" s="24" t="inlineStr">
         <is>
           <t>木之三</t>
         </is>
@@ -20911,12 +22828,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G103" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>沙苑子 （白蒺藜）
 【气味】甘，温。
@@ -20933,7 +22853,7 @@
 时珍曰︰古方补肾治风，皆用刺蒺藜。后世补肾多用沙苑蒺藜，或以熬膏和药，恐其功亦不甚相远也。刺蒺藜炒黄去刺，磨面作饼，或蒸食，可以救荒。</t>
         </is>
       </c>
-      <c r="I103" s="24" t="inlineStr">
+      <c r="J103" s="24" t="inlineStr">
         <is>
           <t>草之五</t>
         </is>
@@ -20970,12 +22890,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
+      <c r="G104" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>芡实
 【气味】甘、涩，平。
@@ -20993,7 +22916,7 @@
 时珍曰︰案孙升《谈圃》云︰芡本不益人，而俗谓之水流黄何也？盖人之食芡，必咀之，终日嗫嗫。而芡味甘平，腴而不腻。食之者能使华液流通，转相灌溉，其功胜于乳石也。《淮南子》云︰狸头愈 ，鸡头已 。注者云︰即芡实也。</t>
         </is>
       </c>
-      <c r="I104" s="24" t="inlineStr">
+      <c r="J104" s="24" t="inlineStr">
         <is>
           <t>果之六</t>
         </is>
@@ -21030,12 +22953,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>龙骨
 【气味】甘、涩，平。
@@ -21048,7 +22974,7 @@
 时珍曰︰涩可去脱。故成氏云︰龙骨能收敛浮越之正气，固大肠而镇惊。又主带脉为病。</t>
         </is>
       </c>
-      <c r="I105" s="39" t="inlineStr">
+      <c r="J105" s="39" t="inlineStr">
         <is>
           <t>鳞之一</t>
         </is>
@@ -21085,12 +23011,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G106" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>牡蛎
 【气味】咸，微寒。
@@ -21109,7 +23038,7 @@
 元素曰︰壮水之主，以制阳光，则渴饮不思。故蛤蛎之类，能止渴也。</t>
         </is>
       </c>
-      <c r="I106" s="24" t="inlineStr">
+      <c r="J106" s="24" t="inlineStr">
         <is>
           <t>介之二</t>
         </is>
@@ -21146,12 +23075,15 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G107" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr">
         <is>
           <t>莲须（莲藕）
 【气味】甘、涩，平。
@@ -21166,7 +23098,7 @@
 时珍曰︰莲须本草不收，而《三因》诸方、固真丸、巨胜子丸各补益方中，往往用之。其功大抵与莲子同也。</t>
         </is>
       </c>
-      <c r="I107" s="24" t="inlineStr">
+      <c r="J107" s="24" t="inlineStr">
         <is>
           <t>果之六</t>
         </is>
@@ -21203,12 +23135,15 @@
           <t>小毒</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="G108" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>蛤蚧
 【气味】咸，平。
@@ -21222,7 +23157,7 @@
 时珍曰︰昔人言补可去弱，人参羊肉之属。蛤蚧补肺气，定喘止渴，功同人参。益阴血，助精扶羸，功同羊肉。近世治劳损痿弱，许叔微治消渴，皆用之，俱取其滋补也。刘纯云︰气液衰、阴血竭者，宜用之。何大英云︰定喘止嗽，莫佳于此。</t>
         </is>
       </c>
-      <c r="I108" s="39" t="inlineStr">
+      <c r="J108" s="39" t="inlineStr">
         <is>
           <t>鳞之一</t>
         </is>
@@ -21259,12 +23194,13 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G109" s="25" t="inlineStr">
+      <c r="G109" s="26" t="n"/>
+      <c r="H109" s="25" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="H109" s="25" t="inlineStr">
+      <c r="I109" s="25" t="inlineStr">
         <is>
           <t>赤芍（芍药）
 【气味】苦，微寒。
@@ -21285,7 +23221,7 @@
 时珍曰：白芍药益脾，能于土中泻木。赤芍药散邪，能行血中之滞。《日华子》言：赤补气，白治血，欠审矣。产后肝血已虚，不可更泻，故禁之。酸寒之药多矣，何独避芍药耶？以此杲曰：或言古人以酸涩为收，《本经》何以言利小便？曰：芍药能益阴滋湿而停津液，故小便自行，非因通利也。曰：又言缓中何也？曰：损其肝者缓其中，即调血也，故四物汤用芍药。大抵酸涩者为收敛停湿之剂，故主手足太阴经收敛之体，又能治血海而入于九地之下，后至厥阴经。白者色在西方，故补；赤者色在南方，故泻。</t>
         </is>
       </c>
-      <c r="I109" s="40" t="inlineStr">
+      <c r="J109" s="40" t="inlineStr">
         <is>
           <t>草之三</t>
         </is>
@@ -21682,7 +23618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22281,894 +24217,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
-  <cols>
-    <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>TheoryID</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>TheoryName</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>BookID</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>DetailText</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>ba_mai</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>把脉</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
-【寸关尺】
-寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
-【对应脏腑区域】
-浮脉：表
-左寸：心
-左关：肝
-左尺：肾阴
-右寸：肺
-右关：脾
-右尺：肾阳
-【脉象】
-游戏中脉象由波形图表示。
-波峰的高低反应气的强弱；
-波峰越高气滞程度越高，波峰越低气虚程度越高。
-波线的粗细反应血的状态；
-波线越粗血瘀程度越高，波线越细血虚程度越高。
-波宽的宽窄反应湿燥程度；
-波宽越宽越湿，波宽越窄越燥。
-波速的快慢反应寒热程度；
-波速越快越热，波速越慢越寒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>kai_fang</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>开方</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>点击选中君臣佐使区域，药材栏选取添加药材和药量，左键点击增加，右键减少。可以在搜索栏输入药材名或拼音，拼音首字母快速查找药材。
-【君臣佐使】
-方剂配伍的基本原则，指一个药方里不同药材扮演的不同角色，就像一只分工明确的团队。
-君药：针对主要病症的核心药材，力量最强，用量最大。
-臣药：辅助君药增强疗效，治疗兼带症状。
-佐药：制约君臣药的毒性或烈性，治疗次要症状。
-使药：调和诸药，引导药物直达病位，解毒缓解副作用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>xing_yi_ji_kao</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>行医记考</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>huang_di_nei_jing</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>李东壁在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材，方剂，疾病。
-在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
-  <cols>
-    <col width="20" bestFit="1" customWidth="1" style="49" min="1" max="1"/>
-    <col width="20" customWidth="1" style="43" min="2" max="2"/>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
-    <col width="10.265625" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
-    <col width="34" bestFit="1" customWidth="1" style="43" min="7" max="7"/>
-    <col width="11" customWidth="1" style="43" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="11"/>
-    <col width="9" customWidth="1" style="43" min="12" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="47" t="inlineStr">
-        <is>
-          <t>StoryID</t>
-        </is>
-      </c>
-      <c r="B1" s="42" t="inlineStr">
-        <is>
-          <t>StoryName</t>
-        </is>
-      </c>
-      <c r="C1" s="42" t="inlineStr">
-        <is>
-          <t>TriggerScene</t>
-        </is>
-      </c>
-      <c r="D1" s="42" t="inlineStr">
-        <is>
-          <t>TriggerDay</t>
-        </is>
-      </c>
-      <c r="E1" s="42" t="inlineStr">
-        <is>
-          <t>PlayOnce</t>
-        </is>
-      </c>
-      <c r="F1" s="42" t="inlineStr">
-        <is>
-          <t>ReturnScene</t>
-        </is>
-      </c>
-      <c r="G1" s="42" t="inlineStr">
-        <is>
-          <t>BackgroundPath</t>
-        </is>
-      </c>
-      <c r="H1" s="42" t="inlineStr">
-        <is>
-          <t>SortIndex</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="50" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B2" s="45" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C2" s="44" t="inlineStr">
-        <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="D2" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="44" t="inlineStr">
-        <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="G2" s="44" t="n"/>
-      <c r="H2" s="44" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="48" t="n"/>
-      <c r="B3" s="44" t="n"/>
-      <c r="C3" s="44" t="n"/>
-      <c r="D3" s="44" t="n"/>
-      <c r="E3" s="44" t="n"/>
-      <c r="F3" s="44" t="n"/>
-      <c r="G3" s="44" t="n"/>
-      <c r="H3" s="44" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="48" t="n"/>
-      <c r="B4" s="44" t="n"/>
-      <c r="C4" s="44" t="n"/>
-      <c r="D4" s="44" t="n"/>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="44" t="n"/>
-      <c r="G4" s="44" t="n"/>
-      <c r="H4" s="44" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="48" t="n"/>
-      <c r="B5" s="44" t="n"/>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="44" t="n"/>
-      <c r="G5" s="44" t="n"/>
-      <c r="H5" s="44" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="48" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="48" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="48" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="44" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="48" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="44" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="48" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="44" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="44" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="48" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="48" t="n"/>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="48" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="48" t="n"/>
-      <c r="B15" s="44" t="n"/>
-      <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="44" t="n"/>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="44" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="48" t="n"/>
-      <c r="B16" s="44" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="44" t="n"/>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="44" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="44" t="n"/>
-      <c r="C17" s="44" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="44" t="n"/>
-      <c r="F17" s="44" t="n"/>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="44" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="48" t="n"/>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="44" t="n"/>
-      <c r="F18" s="44" t="n"/>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="44" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="48" t="n"/>
-      <c r="B19" s="44" t="n"/>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="44" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="48" t="n"/>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
-  <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
-    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
-    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="10"/>
-    <col width="9" customWidth="1" style="43" min="11" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="42" t="inlineStr">
-        <is>
-          <t>StoryID</t>
-        </is>
-      </c>
-      <c r="B1" s="42" t="inlineStr">
-        <is>
-          <t>StoryName</t>
-        </is>
-      </c>
-      <c r="C1" s="42" t="inlineStr">
-        <is>
-          <t>LineIndex</t>
-        </is>
-      </c>
-      <c r="D1" s="42" t="inlineStr">
-        <is>
-          <t>LineType</t>
-        </is>
-      </c>
-      <c r="E1" s="42" t="inlineStr">
-        <is>
-          <t>Speaker</t>
-        </is>
-      </c>
-      <c r="F1" s="46" t="inlineStr">
-        <is>
-          <t>PortraitSide</t>
-        </is>
-      </c>
-      <c r="G1" s="46" t="inlineStr">
-        <is>
-          <t>PortraitPath</t>
-        </is>
-      </c>
-      <c r="H1" s="42" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>明嘉靖十一年，蕲州州衙放榜处</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>李东壁</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>res://Assets/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>…..........</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>李东壁</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>res://Assets/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>嘶...... 又没中......</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>res://Assets/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>你再仔细看看</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>李东壁</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>res://Assets/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>爹，我看了好几遍了，确实没有我的名字…...</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>李东壁</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>res://Assets/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>考了三次童试都没中，看来我不是读书的材料啊爹</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>res://Assets/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>这说的是什么话，你看隔壁村那个老范，考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>李东壁</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>res://Assets/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>我看我还是跟您学医吧，科举八股什么的，太难了</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>落榜</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>res://Assets/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
 </file>
--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="2" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Theory" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,7 +27,7 @@
   <numFmts count="0"/>
   <fonts count="12">
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -105,10 +105,10 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
       <family val="3"/>
-      <sz val="9"/>
+      <sz val="6"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -310,7 +310,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="163">
     <dxf>
@@ -2284,12 +2284,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="7.3984375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.59765625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.265625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="4.59765625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.25" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.625" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2331,13 +2331,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="6.86328125" customWidth="1" min="3" max="3"/>
+    <col width="6.875" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2555,14 +2555,14 @@
   <cols>
     <col width="20" bestFit="1" customWidth="1" style="49" min="1" max="1"/>
     <col width="20" customWidth="1" style="43" min="2" max="2"/>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
-    <col width="10.265625" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
+    <col width="10.25" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
     <col width="34" bestFit="1" customWidth="1" style="43" min="7" max="7"/>
     <col width="11" customWidth="1" style="43" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="13"/>
-    <col width="9" customWidth="1" style="43" min="14" max="16384"/>
+    <col width="9" customWidth="1" style="43" min="9" max="14"/>
+    <col width="9" customWidth="1" style="43" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2828,19 +2828,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
-    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
-    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="12"/>
-    <col width="9" customWidth="1" style="43" min="13" max="16384"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="12.375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="10.5" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
+    <col width="31.625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
+    <col width="41.625" customWidth="1" style="35" min="8" max="8"/>
+    <col width="9" customWidth="1" style="43" min="9" max="13"/>
+    <col width="9" customWidth="1" style="43" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18.75" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>001</t>
@@ -2909,11 +2909,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>明嘉靖十一年，蕲州州衙放榜处</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>明嘉靖十九年，武昌府放榜处</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>001</t>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>res://Assets/li_shi_zhen.png</t>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18.75" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>001</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>res://Assets/li_shi_zhen.png</t>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>001</t>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>res://Assets/li_yan_wen.png</t>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="18.75" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>001</t>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>res://Assets/li_shi_zhen.png</t>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18.75" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>001</t>
@@ -3104,16 +3104,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>res://Assets/li_shi_zhen.png</t>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>考了三次童试都没中，看来我不是读书的材料啊爹</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>考了三次都没中举，看来我不是读书的材料啊爹</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>001</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>res://Assets/li_yan_wen.png</t>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18.75" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>001</t>
@@ -3184,16 +3184,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>res://Assets/li_shi_zhen.png</t>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>我看我还是跟您学医吧，科举八股什么的，太难了</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>我看我还是跟您学医吧，科举八股什么的，孩儿实在是学不来…</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>001</t>
@@ -3224,12 +3224,120 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>res://Assets/li_yan_wen.png</t>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>可我真心喜欢研究那些药材方子，考证典籍。行医治病才是儿子此生志愿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢。东壁呀，你若真的想从医，今日起便随为父从《内经》，《本草》学起吧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>落榜</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>李东壁十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁便下定决心开始随父亲学医。</t>
         </is>
       </c>
     </row>
@@ -3246,14 +3354,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="37.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="37.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="19" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="26.59765625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="6.86328125" customWidth="1" style="7" min="4" max="4"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
+    <col width="26.625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="6.875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -3375,7 +3483,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
@@ -3410,7 +3518,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
@@ -3445,7 +3553,7 @@
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
@@ -3480,7 +3588,7 @@
         </is>
       </c>
       <c r="D7" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
@@ -3515,7 +3623,7 @@
         </is>
       </c>
       <c r="D8" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -3552,7 +3660,7 @@
         </is>
       </c>
       <c r="D9" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
@@ -3590,7 +3698,7 @@
         </is>
       </c>
       <c r="D10" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -3627,7 +3735,7 @@
         </is>
       </c>
       <c r="D11" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -3662,7 +3770,7 @@
         </is>
       </c>
       <c r="D12" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -3697,7 +3805,7 @@
         </is>
       </c>
       <c r="D13" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
@@ -3732,7 +3840,7 @@
         </is>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3767,7 +3875,7 @@
         </is>
       </c>
       <c r="D15" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
@@ -3802,7 +3910,7 @@
         </is>
       </c>
       <c r="D16" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3837,7 +3945,7 @@
         </is>
       </c>
       <c r="D17" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
@@ -3872,7 +3980,7 @@
         </is>
       </c>
       <c r="D18" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -3908,7 +4016,7 @@
         </is>
       </c>
       <c r="D19" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
@@ -3943,7 +4051,7 @@
         </is>
       </c>
       <c r="D20" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -3978,7 +4086,7 @@
         </is>
       </c>
       <c r="D21" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
@@ -4013,7 +4121,7 @@
         </is>
       </c>
       <c r="D22" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -4048,7 +4156,7 @@
         </is>
       </c>
       <c r="D23" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
@@ -4083,7 +4191,7 @@
         </is>
       </c>
       <c r="D24" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -4118,7 +4226,7 @@
         </is>
       </c>
       <c r="D25" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
@@ -4154,7 +4262,7 @@
         </is>
       </c>
       <c r="D26" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -4190,7 +4298,7 @@
         </is>
       </c>
       <c r="D27" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -4225,7 +4333,7 @@
         </is>
       </c>
       <c r="D28" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -4260,7 +4368,7 @@
         </is>
       </c>
       <c r="D29" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
@@ -4296,7 +4404,7 @@
         </is>
       </c>
       <c r="D30" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -4331,7 +4439,7 @@
         </is>
       </c>
       <c r="D31" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
@@ -4366,7 +4474,7 @@
         </is>
       </c>
       <c r="D32" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -4401,7 +4509,7 @@
         </is>
       </c>
       <c r="D33" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
@@ -4438,7 +4546,7 @@
         </is>
       </c>
       <c r="D34" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
@@ -4473,7 +4581,7 @@
         </is>
       </c>
       <c r="D35" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
@@ -4509,7 +4617,7 @@
         </is>
       </c>
       <c r="D36" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -4544,7 +4652,7 @@
         </is>
       </c>
       <c r="D37" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
@@ -4579,7 +4687,7 @@
         </is>
       </c>
       <c r="D38" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -4614,7 +4722,7 @@
         </is>
       </c>
       <c r="D39" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
@@ -4649,7 +4757,7 @@
         </is>
       </c>
       <c r="D40" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -4685,7 +4793,7 @@
         </is>
       </c>
       <c r="D41" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
@@ -4720,7 +4828,7 @@
         </is>
       </c>
       <c r="D42" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -4755,7 +4863,7 @@
         </is>
       </c>
       <c r="D43" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
@@ -4791,7 +4899,7 @@
         </is>
       </c>
       <c r="D44" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -5010,33 +5118,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="17" max="17"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="23" max="23"/>
-    <col width="4.86328125" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
+    <col width="4.875" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="46"/>
-    <col width="9" customWidth="1" style="9" min="47" max="16384"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="47"/>
+    <col width="9" customWidth="1" style="9" min="48" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -5785,13 +5893,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="6.86328125" customWidth="1" style="7" min="4" max="4"/>
-    <col width="45.73046875" customWidth="1" style="3" min="5" max="5"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="6.875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="45.75" customWidth="1" style="3" min="5" max="5"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5927,7 +6035,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -5970,7 +6078,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -6011,7 +6119,7 @@
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -6056,7 +6164,7 @@
         </is>
       </c>
       <c r="D7" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6099,7 +6207,7 @@
         </is>
       </c>
       <c r="D8" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6143,7 +6251,7 @@
         </is>
       </c>
       <c r="D9" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -6185,7 +6293,7 @@
         </is>
       </c>
       <c r="D10" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -6229,7 +6337,7 @@
         </is>
       </c>
       <c r="D11" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -6274,7 +6382,7 @@
         </is>
       </c>
       <c r="D12" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -6320,7 +6428,7 @@
         </is>
       </c>
       <c r="D13" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6473,7 @@
         </is>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -6409,7 +6517,7 @@
         </is>
       </c>
       <c r="D15" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -6453,7 +6561,7 @@
         </is>
       </c>
       <c r="D16" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -6496,7 +6604,7 @@
         </is>
       </c>
       <c r="D17" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -6542,7 +6650,7 @@
         </is>
       </c>
       <c r="D18" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -6584,7 +6692,7 @@
         </is>
       </c>
       <c r="D19" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -6630,7 +6738,7 @@
         </is>
       </c>
       <c r="D20" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -6673,7 +6781,7 @@
         </is>
       </c>
       <c r="D21" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -6716,7 +6824,7 @@
         </is>
       </c>
       <c r="D22" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -6759,7 +6867,7 @@
         </is>
       </c>
       <c r="D23" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -6802,7 +6910,7 @@
         </is>
       </c>
       <c r="D24" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -6846,7 +6954,7 @@
         </is>
       </c>
       <c r="D25" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -6891,7 +6999,7 @@
         </is>
       </c>
       <c r="D26" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -6936,7 +7044,7 @@
         </is>
       </c>
       <c r="D27" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -6979,7 +7087,7 @@
         </is>
       </c>
       <c r="D28" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -7027,7 +7135,7 @@
         </is>
       </c>
       <c r="D29" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -7071,7 +7179,7 @@
         </is>
       </c>
       <c r="D30" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -7117,7 +7225,7 @@
         </is>
       </c>
       <c r="D31" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -7161,7 +7269,7 @@
         </is>
       </c>
       <c r="D32" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -7207,7 +7315,7 @@
         </is>
       </c>
       <c r="D33" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -7251,7 +7359,7 @@
         </is>
       </c>
       <c r="D34" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -7294,7 +7402,7 @@
         </is>
       </c>
       <c r="D35" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -7339,7 +7447,7 @@
         </is>
       </c>
       <c r="D36" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -7385,7 +7493,7 @@
         </is>
       </c>
       <c r="D37" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -7431,7 +7539,7 @@
         </is>
       </c>
       <c r="D38" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -7476,7 +7584,7 @@
         </is>
       </c>
       <c r="D39" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -7520,7 +7628,7 @@
         </is>
       </c>
       <c r="D40" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -7566,7 +7674,7 @@
         </is>
       </c>
       <c r="D41" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -7612,7 +7720,7 @@
         </is>
       </c>
       <c r="D42" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
@@ -7654,7 +7762,7 @@
         </is>
       </c>
       <c r="D43" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -7698,7 +7806,7 @@
         </is>
       </c>
       <c r="D44" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
@@ -7932,14 +8040,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F306"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16527,18 +16635,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="6.59765625" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
+    <col width="6.625" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17057,7 +17165,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -17121,7 +17229,7 @@
         </is>
       </c>
       <c r="G10" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -17188,7 +17296,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -17252,7 +17360,7 @@
         </is>
       </c>
       <c r="G12" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -17311,7 +17419,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -17372,7 +17480,7 @@
         </is>
       </c>
       <c r="G14" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -17434,7 +17542,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -17494,7 +17602,7 @@
         </is>
       </c>
       <c r="G16" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -17556,7 +17664,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -17620,7 +17728,7 @@
         </is>
       </c>
       <c r="G18" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -17680,7 +17788,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -17742,7 +17850,7 @@
         </is>
       </c>
       <c r="G20" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -17812,7 +17920,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -17874,7 +17982,7 @@
         </is>
       </c>
       <c r="G22" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -17935,7 +18043,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -17995,7 +18103,7 @@
         </is>
       </c>
       <c r="G24" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -18054,7 +18162,7 @@
         </is>
       </c>
       <c r="G25" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -18117,7 +18225,7 @@
         </is>
       </c>
       <c r="G26" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -18176,7 +18284,7 @@
         </is>
       </c>
       <c r="G27" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -18241,7 +18349,7 @@
         </is>
       </c>
       <c r="G28" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -18304,7 +18412,7 @@
         </is>
       </c>
       <c r="G29" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -18363,7 +18471,7 @@
         </is>
       </c>
       <c r="G30" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -18424,7 +18532,7 @@
         </is>
       </c>
       <c r="G31" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -18482,7 +18590,7 @@
         </is>
       </c>
       <c r="G32" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -18543,7 +18651,7 @@
         </is>
       </c>
       <c r="G33" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -18604,7 +18712,7 @@
         </is>
       </c>
       <c r="G34" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -18664,7 +18772,7 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -18728,7 +18836,7 @@
         </is>
       </c>
       <c r="G36" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -18791,7 +18899,7 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -18852,7 +18960,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -18912,7 +19020,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -18976,7 +19084,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -19033,7 +19141,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -19095,7 +19203,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -19159,7 +19267,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -19220,7 +19328,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -19282,7 +19390,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -19344,7 +19452,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -19402,7 +19510,7 @@
         </is>
       </c>
       <c r="G47" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -19474,7 +19582,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -19545,7 +19653,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -19604,7 +19712,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -19667,7 +19775,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -19734,7 +19842,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -19793,7 +19901,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -19854,7 +19962,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
@@ -19913,7 +20021,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -19971,7 +20079,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -20030,7 +20138,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
@@ -20096,7 +20204,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -20160,7 +20268,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -20219,7 +20327,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -20282,7 +20390,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -20344,7 +20452,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -20404,7 +20512,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -20461,7 +20569,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -20520,7 +20628,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
@@ -20584,7 +20692,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -20647,7 +20755,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -20711,7 +20819,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -20774,7 +20882,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -20835,7 +20943,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -20896,7 +21004,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -20953,7 +21061,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -21017,7 +21125,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -21076,7 +21184,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -21140,7 +21248,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -21197,7 +21305,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -21254,7 +21362,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -21314,7 +21422,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -21370,7 +21478,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -21433,7 +21541,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -21493,7 +21601,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -21553,7 +21661,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -21614,7 +21722,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -21675,7 +21783,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -21734,7 +21842,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -21796,7 +21904,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -21857,7 +21965,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -21921,7 +22029,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -21981,7 +22089,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -22039,7 +22147,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -22099,7 +22207,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -22159,7 +22267,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -22221,7 +22329,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -22282,7 +22390,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
@@ -22343,7 +22451,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -22401,7 +22509,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -22462,7 +22570,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -22521,7 +22629,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -22582,7 +22690,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -22641,7 +22749,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -22701,7 +22809,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -22763,7 +22871,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -22829,7 +22937,7 @@
         </is>
       </c>
       <c r="G103" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
@@ -22891,7 +22999,7 @@
         </is>
       </c>
       <c r="G104" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -22954,7 +23062,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -23012,7 +23120,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -23076,7 +23184,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -23136,7 +23244,7 @@
         </is>
       </c>
       <c r="G108" s="28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -23194,7 +23302,9 @@
           <t>无毒</t>
         </is>
       </c>
-      <c r="G109" s="26" t="n"/>
+      <c r="G109" s="26" t="n">
+        <v>-1</v>
+      </c>
       <c r="H109" s="25" t="inlineStr">
         <is>
           <t>shen_nong_ben_cao_jing</t>
@@ -23625,14 +23735,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="45.59765625" customWidth="1" min="1" max="1"/>
-    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.73046875" customWidth="1" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.625" customWidth="1" min="1" max="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.75" customWidth="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="2" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Story" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="StoryLine" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Disease" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pulse" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Formula" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Formula" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pulse" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="FormulaIngredient" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Herb" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Book" sheetId="9" state="visible" r:id="rId9"/>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -280,9 +280,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -290,12 +287,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,6 +299,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2308,7 +2310,7 @@
           <t>Gender</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="48" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
@@ -2335,12 +2337,12 @@
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="6.875" customWidth="1" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TheoryID</t>
@@ -2351,9 +2353,9 @@
           <t>TheoryName</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
-        <is>
-          <t>unlock required experie</t>
+      <c r="C1" s="53" t="inlineStr">
+        <is>
+          <t>Experience</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2550,272 +2552,324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="49" min="1" max="1"/>
-    <col width="20" customWidth="1" style="43" min="2" max="2"/>
-    <col width="14.375" bestFit="1" customWidth="1" style="43" min="3" max="3"/>
-    <col width="12.125" bestFit="1" customWidth="1" style="43" min="4" max="4"/>
-    <col width="10.25" bestFit="1" customWidth="1" style="43" min="5" max="5"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="43" min="6" max="6"/>
-    <col width="34" bestFit="1" customWidth="1" style="43" min="7" max="7"/>
-    <col width="11" customWidth="1" style="43" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="14"/>
-    <col width="9" customWidth="1" style="43" min="15" max="16384"/>
+    <col width="10.875" customWidth="1" style="46" min="1" max="1"/>
+    <col width="20" customWidth="1" style="42" min="2" max="2"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="42" min="3" max="3"/>
+    <col width="11" customWidth="1" style="42" min="4" max="4"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
+    <col width="15.375" customWidth="1" style="42" min="6" max="6"/>
+    <col width="10.25" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="42" min="8" max="8"/>
+    <col width="34" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
+    <col width="11" customWidth="1" style="42" min="10" max="10"/>
+    <col width="9" customWidth="1" style="42" min="11" max="17"/>
+    <col width="9" customWidth="1" style="42" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="42" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>TriggerScene</t>
         </is>
       </c>
-      <c r="D1" s="42" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>TriggerDay</t>
         </is>
       </c>
-      <c r="E1" s="42" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
+        <is>
+          <t>Reputation</t>
+        </is>
+      </c>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>EntryId</t>
+        </is>
+      </c>
+      <c r="G1" s="50" t="inlineStr">
         <is>
           <t>PlayOnce</t>
         </is>
       </c>
-      <c r="F1" s="42" t="inlineStr">
+      <c r="H1" s="50" t="inlineStr">
         <is>
           <t>ReturnScene</t>
         </is>
       </c>
-      <c r="G1" s="42" t="inlineStr">
+      <c r="I1" s="50" t="inlineStr">
         <is>
           <t>BackgroundPath</t>
         </is>
       </c>
-      <c r="H1" s="42" t="inlineStr">
+      <c r="J1" s="50" t="inlineStr">
         <is>
           <t>SortIndex</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>落榜</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="43" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D2" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="D2" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="43" t="n"/>
+      <c r="G2" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="43" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="G2" s="44" t="n"/>
-      <c r="H2" s="44" t="n"/>
+      <c r="I2" s="43" t="n"/>
+      <c r="J2" s="43" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="n"/>
-      <c r="B3" s="44" t="n"/>
-      <c r="C3" s="44" t="n"/>
-      <c r="D3" s="44" t="n"/>
-      <c r="E3" s="44" t="n"/>
-      <c r="F3" s="44" t="n"/>
-      <c r="G3" s="44" t="n"/>
-      <c r="H3" s="44" t="n"/>
+      <c r="A3" s="45" t="n"/>
+      <c r="B3" s="43" t="n"/>
+      <c r="C3" s="43" t="n"/>
+      <c r="D3" s="43" t="n"/>
+      <c r="E3" s="43" t="n"/>
+      <c r="F3" s="43" t="n"/>
+      <c r="G3" s="43" t="n"/>
+      <c r="H3" s="43" t="n"/>
+      <c r="I3" s="43" t="n"/>
+      <c r="J3" s="43" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="n"/>
-      <c r="B4" s="44" t="n"/>
-      <c r="C4" s="44" t="n"/>
-      <c r="D4" s="44" t="n"/>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="44" t="n"/>
-      <c r="G4" s="44" t="n"/>
-      <c r="H4" s="44" t="n"/>
+      <c r="A4" s="45" t="n"/>
+      <c r="B4" s="43" t="n"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="I4" s="43" t="n"/>
+      <c r="J4" s="43" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="n"/>
-      <c r="B5" s="44" t="n"/>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="44" t="n"/>
-      <c r="G5" s="44" t="n"/>
-      <c r="H5" s="44" t="n"/>
+      <c r="A5" s="45" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
+      <c r="I5" s="43" t="n"/>
+      <c r="J5" s="43" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
+      <c r="A6" s="45" t="n"/>
+      <c r="B6" s="43" t="n"/>
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="43" t="n"/>
+      <c r="E6" s="43" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="43" t="n"/>
+      <c r="H6" s="43" t="n"/>
+      <c r="I6" s="43" t="n"/>
+      <c r="J6" s="43" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
+      <c r="A7" s="45" t="n"/>
+      <c r="B7" s="43" t="n"/>
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="43" t="n"/>
+      <c r="E7" s="43" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="43" t="n"/>
+      <c r="H7" s="43" t="n"/>
+      <c r="I7" s="43" t="n"/>
+      <c r="J7" s="43" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="44" t="n"/>
+      <c r="A8" s="45" t="n"/>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="43" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="43" t="n"/>
+      <c r="I8" s="43" t="n"/>
+      <c r="J8" s="43" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="44" t="n"/>
+      <c r="A9" s="45" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="43" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="43" t="n"/>
+      <c r="H9" s="43" t="n"/>
+      <c r="I9" s="43" t="n"/>
+      <c r="J9" s="43" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="n"/>
-      <c r="B10" s="44" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="44" t="n"/>
+      <c r="A10" s="45" t="n"/>
+      <c r="B10" s="43" t="n"/>
+      <c r="C10" s="43" t="n"/>
+      <c r="D10" s="43" t="n"/>
+      <c r="E10" s="43" t="n"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="43" t="n"/>
+      <c r="H10" s="43" t="n"/>
+      <c r="I10" s="43" t="n"/>
+      <c r="J10" s="43" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="44" t="n"/>
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="43" t="n"/>
+      <c r="C11" s="43" t="n"/>
+      <c r="D11" s="43" t="n"/>
+      <c r="E11" s="43" t="n"/>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="43" t="n"/>
+      <c r="H11" s="43" t="n"/>
+      <c r="I11" s="43" t="n"/>
+      <c r="J11" s="43" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
+      <c r="A12" s="45" t="n"/>
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="43" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="43" t="n"/>
+      <c r="H12" s="43" t="n"/>
+      <c r="I12" s="43" t="n"/>
+      <c r="J12" s="43" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="n"/>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
+      <c r="A13" s="45" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="43" t="n"/>
+      <c r="H13" s="43" t="n"/>
+      <c r="I13" s="43" t="n"/>
+      <c r="J13" s="43" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
+      <c r="A14" s="45" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="43" t="n"/>
+      <c r="H14" s="43" t="n"/>
+      <c r="I14" s="43" t="n"/>
+      <c r="J14" s="43" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="n"/>
-      <c r="B15" s="44" t="n"/>
-      <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="44" t="n"/>
-      <c r="G15" s="44" t="n"/>
-      <c r="H15" s="44" t="n"/>
+      <c r="A15" s="45" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="43" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="43" t="n"/>
+      <c r="H15" s="43" t="n"/>
+      <c r="I15" s="43" t="n"/>
+      <c r="J15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="n"/>
-      <c r="B16" s="44" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="44" t="n"/>
-      <c r="G16" s="44" t="n"/>
-      <c r="H16" s="44" t="n"/>
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="43" t="n"/>
+      <c r="E16" s="43" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="43" t="n"/>
+      <c r="H16" s="43" t="n"/>
+      <c r="I16" s="43" t="n"/>
+      <c r="J16" s="43" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="44" t="n"/>
-      <c r="C17" s="44" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="44" t="n"/>
-      <c r="F17" s="44" t="n"/>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="44" t="n"/>
+      <c r="A17" s="45" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="43" t="n"/>
+      <c r="D17" s="43" t="n"/>
+      <c r="E17" s="43" t="n"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="43" t="n"/>
+      <c r="I17" s="43" t="n"/>
+      <c r="J17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="n"/>
-      <c r="B18" s="44" t="n"/>
-      <c r="C18" s="44" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="44" t="n"/>
-      <c r="F18" s="44" t="n"/>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="44" t="n"/>
+      <c r="A18" s="45" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="n"/>
+      <c r="H18" s="43" t="n"/>
+      <c r="I18" s="43" t="n"/>
+      <c r="J18" s="43" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="n"/>
-      <c r="B19" s="44" t="n"/>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="44" t="n"/>
-      <c r="G19" s="44" t="n"/>
-      <c r="H19" s="44" t="n"/>
+      <c r="A19" s="45" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="43" t="n"/>
+      <c r="I19" s="43" t="n"/>
+      <c r="J19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="n"/>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="44" t="n"/>
-      <c r="G20" s="44" t="n"/>
-      <c r="H20" s="44" t="n"/>
+      <c r="A20" s="45" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="43" t="n"/>
+      <c r="E20" s="43" t="n"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="43" t="n"/>
+      <c r="H20" s="43" t="n"/>
+      <c r="I20" s="43" t="n"/>
+      <c r="J20" s="43" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2839,47 +2893,47 @@
     <col width="13.625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
     <col width="31.625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
     <col width="41.625" customWidth="1" style="35" min="8" max="8"/>
-    <col width="9" customWidth="1" style="43" min="9" max="13"/>
-    <col width="9" customWidth="1" style="43" min="14" max="16384"/>
+    <col width="9" customWidth="1" style="42" min="9" max="14"/>
+    <col width="9" customWidth="1" style="42" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="42" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>LineIndex</t>
         </is>
       </c>
-      <c r="D1" s="42" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>LineType</t>
         </is>
       </c>
-      <c r="E1" s="42" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Speaker</t>
         </is>
       </c>
-      <c r="F1" s="46" t="inlineStr">
+      <c r="F1" s="51" t="inlineStr">
         <is>
           <t>PortraitSide</t>
         </is>
       </c>
-      <c r="G1" s="46" t="inlineStr">
+      <c r="G1" s="51" t="inlineStr">
         <is>
           <t>PortraitPath</t>
         </is>
       </c>
-      <c r="H1" s="42" t="inlineStr">
+      <c r="H1" s="50" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -3233,7 +3287,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="18.75" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>001</t>
@@ -3273,7 +3327,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="18.75" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>001</t>
@@ -3313,7 +3367,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="18.75" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>001</t>
@@ -3356,10 +3410,10 @@
   <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="37.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="26.625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="6.875" customWidth="1" style="7" min="4" max="4"/>
+    <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
     <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
@@ -3375,14 +3429,14 @@
           <t>DiseaseName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>RecommendedFormulaID</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
-        <is>
-          <t>unlock required experie</t>
+      <c r="C1" s="53" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>RecommendedFormulaName</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -3407,13 +3461,13 @@
           <t>风寒表实证</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>ma_huang_tang</t>
-        </is>
-      </c>
-      <c r="D2" s="28" t="n">
+      <c r="C2" s="28" t="n">
         <v>0</v>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>麻黄汤</t>
+        </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
@@ -3442,13 +3496,13 @@
           <t>风寒表虚证</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>gui_zhi_tang</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="n">
+      <c r="C3" s="28" t="n">
         <v>0</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>桂枝汤</t>
+        </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
@@ -3477,13 +3531,13 @@
           <t>肺热壅盛</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>ma_xing_shi_gan_tang</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="n">
+      <c r="C4" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>麻杏石甘汤</t>
+        </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
@@ -3512,13 +3566,13 @@
           <t>心阳虚</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>gui_zhi_gan_cao_tang</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="n">
+      <c r="C5" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>桂枝甘草汤</t>
+        </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
@@ -3547,13 +3601,13 @@
           <t>寒凝心脉</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>dang_gui_si_ni_tang</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n">
+      <c r="C6" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>当归四逆汤</t>
+        </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
@@ -3582,13 +3636,13 @@
           <t>脾阳虚</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>li_zhong_wan</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="n">
+      <c r="C7" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>理中丸</t>
+        </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
@@ -3617,13 +3671,13 @@
           <t>肾虚水泛</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>zhen_wu_tang</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
+      <c r="C8" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>真武汤</t>
+        </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -3654,13 +3708,13 @@
           <t>气分热盛</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>bai_hu_tang</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="n">
+      <c r="C9" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>白虎汤</t>
+        </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
@@ -3692,13 +3746,13 @@
           <t>心肾不交</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>huang_lian_e_jiao_tang</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="n">
+      <c r="C10" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>黄连阿胶汤</t>
+        </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -3729,13 +3783,13 @@
           <t>风热表证</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>yin_qiao_san</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="n">
+      <c r="C11" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>银翘散</t>
+        </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -3764,13 +3818,13 @@
           <t>温燥证</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>sang_xing_tang</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="n">
+      <c r="C12" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>桑杏汤</t>
+        </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -3799,13 +3853,13 @@
           <t>凉燥证</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>xing_su_san</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="n">
+      <c r="C13" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>杏苏散</t>
+        </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
@@ -3834,13 +3888,13 @@
           <t>肺阴虚</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>sha_shen_mai_dong_tang</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="n">
+      <c r="C14" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>沙参麦冬汤</t>
+        </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3869,13 +3923,13 @@
           <t>痛痹</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>wu_tou_tang</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="n">
+      <c r="C15" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>乌头汤</t>
+        </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
@@ -3904,13 +3958,13 @@
           <t>热痹</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>bai_hu_gui_zhi_tang</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="n">
+      <c r="C16" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>白虎桂枝汤</t>
+        </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3939,13 +3993,13 @@
           <t>心阴虚</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>tian_wang_bu_xin_dan</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="n">
+      <c r="C17" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>天王补心丹</t>
+        </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
@@ -3974,13 +4028,13 @@
           <t>肾阳虚</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>jin_gui_shen_qi_wan</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="n">
+      <c r="C18" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>金匮肾气丸</t>
+        </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -4010,13 +4064,13 @@
           <t>行痹</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>fang_feng_tang</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="n">
+      <c r="C19" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>防风汤</t>
+        </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
@@ -4045,13 +4099,13 @@
           <t>痰湿阻肺</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>er_chen_tang</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="n">
+      <c r="C20" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>二陈汤</t>
+        </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -4080,13 +4134,13 @@
           <t>肝血虚</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>si_wu_tang</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="n">
+      <c r="C21" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>四物汤</t>
+        </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
@@ -4115,13 +4169,13 @@
           <t>脾气虚</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>si_jun_zi_tang</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="n">
+      <c r="C22" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>四君子汤</t>
+        </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -4150,13 +4204,13 @@
           <t>湿盛困脾</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>ping_wei_san</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="n">
+      <c r="C23" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>平胃散</t>
+        </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
@@ -4185,13 +4239,13 @@
           <t>脾虚湿盛</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>shen_ling_bai_zhu_san</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="n">
+      <c r="C24" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>参苓白术散</t>
+        </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -4220,13 +4274,13 @@
           <t>肝脾不和</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>xiao_yao_san</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="n">
+      <c r="C25" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>逍遥散</t>
+        </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
@@ -4256,13 +4310,13 @@
           <t>外感风寒，内伤湿滞</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>huo_xiang_zheng_qi_san</t>
-        </is>
-      </c>
-      <c r="D26" s="28" t="n">
+      <c r="C26" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>藿香正气散</t>
+        </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -4292,13 +4346,13 @@
           <t>肺气虚</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>bu_fei_tang</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="n">
+      <c r="C27" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>补肺汤</t>
+        </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
@@ -4327,13 +4381,13 @@
           <t>痰火扰心</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>huang_lian_wen_dan_tang</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="n">
+      <c r="C28" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>黄连温胆汤</t>
+        </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -4362,13 +4416,13 @@
           <t>着痹</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>yi_yi_ren_tang</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="n">
+      <c r="C29" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>薏苡仁汤</t>
+        </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
@@ -4398,13 +4452,13 @@
           <t>痰迷心窍</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>di_tan_tang</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="n">
+      <c r="C30" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>涤痰汤</t>
+        </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -4433,13 +4487,13 @@
           <t>肝气郁结</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>chai_hu_shu_gan_san</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="n">
+      <c r="C31" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>柴胡疏肝散</t>
+        </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
@@ -4468,13 +4522,13 @@
           <t>寒滞肝脉</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>nuan_gan_jian</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="n">
+      <c r="C32" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>暖肝煎</t>
+        </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -4503,13 +4557,13 @@
           <t>肾精不足</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>zuo_gui_wan</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="n">
+      <c r="C33" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>左归丸</t>
+        </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
@@ -4540,13 +4594,13 @@
           <t>心火亢盛</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>dao_chi_san</t>
-        </is>
-      </c>
-      <c r="D34" s="28" t="n">
+      <c r="C34" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>导赤散</t>
+        </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
@@ -4575,13 +4629,13 @@
           <t>肾阴虚</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>liu_wei_di_huang_wan</t>
-        </is>
-      </c>
-      <c r="D35" s="28" t="n">
+      <c r="C35" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>六味地黄丸</t>
+        </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
@@ -4611,13 +4665,13 @@
           <t>痰热壅肺</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>qing_qi_hua_tan_wan</t>
-        </is>
-      </c>
-      <c r="D36" s="28" t="n">
+      <c r="C36" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>清气化痰丸</t>
+        </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -4646,13 +4700,13 @@
           <t>肝阳上亢</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>gou_teng_san</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="n">
+      <c r="C37" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>钩藤散</t>
+        </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
@@ -4681,13 +4735,13 @@
           <t>肝火上炎</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>long_dan_xie_gan_tang</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="n">
+      <c r="C38" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>龙胆泻肝汤</t>
+        </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -4716,13 +4770,13 @@
           <t>肝阴虚</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>yi_guan_jian</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="n">
+      <c r="C39" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>一贯煎</t>
+        </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
@@ -4751,13 +4805,13 @@
           <t>心脾两虚</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>gui_pi_tang</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="n">
+      <c r="C40" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>归脾汤</t>
+        </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -4787,13 +4841,13 @@
           <t>心气虚</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>yang_xin_tang</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="n">
+      <c r="C41" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>养心汤</t>
+        </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
@@ -4822,13 +4876,13 @@
           <t>卫气虚</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>yu_ping_feng_san</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="n">
+      <c r="C42" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>玉屏风散</t>
+        </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -4857,13 +4911,13 @@
           <t>肾气不固</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>jin_suo_gu_jing_wan</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="n">
+      <c r="C43" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>金锁固精丸</t>
+        </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
@@ -4893,13 +4947,13 @@
           <t>肾不纳气</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>ren_shen_ge_jie_san</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="n">
+      <c r="C44" s="28" t="n">
         <v>-1</v>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>人参蛤蚧散</t>
+        </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -4919,191 +4973,191 @@
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="D45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="D46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
     </row>
     <row r="47"/>
     <row r="48" ht="15" customHeight="1">
-      <c r="D48" s="28" t="n"/>
+      <c r="C48" s="28" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="D49" s="28" t="n"/>
+      <c r="C49" s="28" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="D50" s="28" t="n"/>
+      <c r="C50" s="28" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="D51" s="28" t="n"/>
+      <c r="C51" s="28" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="D52" s="28" t="n"/>
+      <c r="C52" s="28" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="D53" s="28" t="n"/>
+      <c r="C53" s="28" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="D54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="D55" s="28" t="n"/>
+      <c r="C55" s="28" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="D56" s="28" t="n"/>
+      <c r="C56" s="28" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="D57" s="28" t="n"/>
+      <c r="C57" s="28" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="D58" s="28" t="n"/>
+      <c r="C58" s="28" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="D59" s="28" t="n"/>
+      <c r="C59" s="28" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="D60" s="28" t="n"/>
+      <c r="C60" s="28" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="D61" s="28" t="n"/>
+      <c r="C61" s="28" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="D62" s="28" t="n"/>
+      <c r="C62" s="28" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="D63" s="28" t="n"/>
+      <c r="C63" s="28" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="D64" s="28" t="n"/>
+      <c r="C64" s="28" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="D65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="D66" s="28" t="n"/>
+      <c r="C66" s="28" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="D67" s="28" t="n"/>
+      <c r="C67" s="28" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="D68" s="28" t="n"/>
+      <c r="C68" s="28" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="D69" s="28" t="n"/>
+      <c r="C69" s="28" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="D70" s="28" t="n"/>
+      <c r="C70" s="28" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="D71" s="28" t="n"/>
+      <c r="C71" s="28" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="D72" s="28" t="n"/>
+      <c r="C72" s="28" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="D73" s="28" t="n"/>
+      <c r="C73" s="28" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="D74" s="28" t="n"/>
+      <c r="C74" s="28" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="D75" s="28" t="n"/>
+      <c r="C75" s="28" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="D76" s="28" t="n"/>
+      <c r="C76" s="28" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="D77" s="28" t="n"/>
+      <c r="C77" s="28" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="D78" s="28" t="n"/>
+      <c r="C78" s="28" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="D79" s="28" t="n"/>
+      <c r="C79" s="28" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="D80" s="28" t="n"/>
+      <c r="C80" s="28" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="D81" s="28" t="n"/>
+      <c r="C81" s="28" t="n"/>
     </row>
     <row r="82"/>
     <row r="83" ht="15" customHeight="1">
-      <c r="D83" s="28" t="n"/>
+      <c r="C83" s="28" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="D84" s="28" t="n"/>
+      <c r="C84" s="28" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="D85" s="28" t="n"/>
+      <c r="C85" s="28" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="D86" s="28" t="n"/>
+      <c r="C86" s="28" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="D87" s="28" t="n"/>
+      <c r="C87" s="28" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="D88" s="28" t="n"/>
+      <c r="C88" s="28" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="D89" s="28" t="n"/>
+      <c r="C89" s="28" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="D90" s="28" t="n"/>
+      <c r="C90" s="28" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="D91" s="28" t="n"/>
+      <c r="C91" s="28" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="D92" s="28" t="n"/>
+      <c r="C92" s="28" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="D93" s="28" t="n"/>
+      <c r="C93" s="28" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1">
-      <c r="D94" s="28" t="n"/>
+      <c r="C94" s="28" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="D95" s="28" t="n"/>
+      <c r="C95" s="28" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="D96" s="28" t="n"/>
+      <c r="C96" s="28" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="D97" s="28" t="n"/>
+      <c r="C97" s="28" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="D98" s="28" t="n"/>
+      <c r="C98" s="28" t="n"/>
     </row>
     <row r="99"/>
     <row r="100" ht="15" customHeight="1">
-      <c r="D100" s="28" t="n"/>
+      <c r="C100" s="28" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1">
-      <c r="D101" s="28" t="n"/>
+      <c r="C101" s="28" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="D102" s="28" t="n"/>
+      <c r="C102" s="28" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1">
-      <c r="D103" s="28" t="n"/>
+      <c r="C103" s="28" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="D104" s="28" t="n"/>
+      <c r="C104" s="28" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="D105" s="28" t="n"/>
+      <c r="C105" s="28" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1">
-      <c r="D106" s="28" t="n"/>
+      <c r="C106" s="28" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="D107" s="28" t="n"/>
+      <c r="C107" s="28" t="n"/>
     </row>
     <row r="108"/>
     <row r="109" ht="15" customHeight="1">
-      <c r="D109" s="26" t="n"/>
+      <c r="C109" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5112,6 +5166,2153 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet2">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <cols>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="49.125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FormulaID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FormulaName</t>
+        </is>
+      </c>
+      <c r="C1" s="53" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>TargetDiseaseName</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>BookID</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>DetailText</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ma_huang_tang</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>麻黄汤</t>
+        </is>
+      </c>
+      <c r="C2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>风寒表实证</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>麻黄汤
+【出处】《伤寒论》
+【功效】发汗解表，宣肺平喘
+【主治】风寒表实证
+【组成】
+君：麻黄 三钱
+臣：桂枝 二钱
+佐：杏仁 二钱
+使：甘草 一钱
+【配伍】
+麻桂相须，增强发汗散寒之力，专治表实无汗。
+麻杏相使，宣降相配，专治寒邪闭肺之喘逆。
+甘草调和诸药</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>gui_zhi_tang</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>桂枝汤</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>风寒表虚证</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>桂枝汤
+【出处】《伤寒论》
+【功效】解肌发表，调和营卫
+【主治】风寒表虚证
+【组成】
+君：桂枝 三钱
+臣：白芍 三钱
+佐：生姜 三钱，大枣 二钱
+使：甘草 二钱
+【配伍】
+桂枝辛散卫邪，白芍酸敛营阴；一散一收，调和营卫，不伤正、不敛邪。
+姜枣相合，调和脾胃，化生气血，资营卫之源。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ma_xing_shi_gan_tang</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>麻杏石甘汤</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>肺热壅盛</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>麻杏石甘汤
+【出处】《伤寒论》
+【功效】辛凉疏表，清肺平喘
+【主治】肺热壅盛
+【组成】
+君：麻黄 三钱
+臣：石膏 八钱
+佐：杏仁 三钱
+使：甘草 二钱
+【配伍】
+麻黄：辛温，宣肺平喘、开泄肺气，散邪解表。
+石膏:辛甘大寒，清泻肺热、生津止渴，清里热以制麻黄之温。
+杏仁:苦降肺气，降利平喘，与麻黄一宣一降，恢复肺之宣肃。
+炙甘草:调和诸药，益气护中，缓急润肺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>gui_zhi_gan_cao_tang</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>桂枝甘草汤</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>心阳虚</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>桂枝甘草汤
+【出处】《伤寒论》
+【功效】温补心阳，益气定悸
+【主治】心阳虚
+【组成】
+君：桂枝 四钱
+臣：甘草 二钱
+佐：
+使：
+【配伍】
+桂枝：辛甘温，温通心阳、平冲降逆、温经通脉。
+炙甘草：益气补中、缓急养心，甘温益气。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>dang_gui_si_ni_tang</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>当归四逆汤</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>寒凝心脉</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>当归四逆汤
+【出处】《伤寒论》
+【功效】温经散寒，养血通脉
+【主治】寒凝心脉
+【组成】
+君：当归 四钱
+臣：桂枝 三钱，白芍 三钱
+佐：细辛 一钱，木通 二钱
+使：甘草 二钱，大枣 二钱
+【配伍】
+当归：养血和血、温补肝血，濡养经脉。
+桂枝：温通经脉、宣通阳气；
+白芍：养血敛阴，缓急止痛；
+细辛：直入三阴，温经散寒、破寒凝。
+通草：通利经脉，引寒邪外泄。
+大枣、炙甘草益气健脾、调和诸药，养血以助脉道充盈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>li_zhong_wan</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>理中丸</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>脾阳虚</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>理中丸
+【出处】《伤寒论》
+【功效】温中祛寒，补气健脾
+【主治】脾阳虚
+【组成】
+君：干姜 五钱
+臣：人参 五钱
+佐：白术 五钱
+使：甘草 五钱
+【配伍】
+干姜：大辛大热，温中祛寒、振奋脾阳。
+人参：益气健脾，补益脾胃气虚之本。
+白术：健脾燥湿，助运化、利水湿。
+炙甘草：益气和中、调和诸药，缓急止痛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>zhen_wu_tang</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>真武汤</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>肾虚水泛</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>真武汤
+【出处】《伤寒论》
+【功效】温阳利水
+【主治】肾虚水泛
+【组成】
+君：附子 三钱
+臣：茯苓 三钱，白术 三钱
+佐：生姜 二钱，白芍 三钱
+使：
+【配伍】
+附子：大辛大热，温补肾阳、散阴寒，助气化以行水。
+茯苓：健脾渗湿、利水消肿；
+白术：健脾燥湿、培土制水。
+生姜：温散水气、助附子温阳，兼和胃散饮。
+芍药：利小便、柔肝缓急止痛，防附子燥热伤阴，敛阴和营。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>bai_hu_tang</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>白虎汤</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>气分热盛</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>白虎汤
+【出处】《伤寒论》
+【功效】清热生津，辛寒清气
+【主治】气分热盛
+【组成】
+君：石膏 二两
+臣：知母 六钱
+佐：粳米 三钱
+使：甘草 二钱
+【配伍】
+生石膏：辛甘大寒，清泻阳明气分实热，除壮热、止大汗。
+知母：苦寒质润，清热泻火、滋阴生津，助石膏清润除烦止渴。
+粳米、炙甘草：益气养胃、缓和石膏知母寒凉之性，保护胃气；生津补液，防大寒伤中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>huang_lian_e_jiao_tang</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>黄连阿胶汤</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>心肾不交</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>shang_han_lun</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>黄连阿胶汤
+【出处】《伤寒论》
+【功效】滋阴降火，交通心肾
+【主治】心肾不交
+【组成】
+君：黄连 四钱
+臣：黄芩 三钱，白芍 三钱
+佐：阿胶 三钱
+使：鸡子黄 一两
+【配伍】
+黄连：苦寒直折，清泻心火、除烦安神。
+黄芩：助黄连清心泻火；
+阿胶：滋阴补肾、养血填阴，滋肾阴以济心火。
+白芍：敛阴和营、柔肝缓急；
+鸡子黄：滋阴润燥、养心安神，入少阴交通心肾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>yin_qiao_san</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>银翘散</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>风热表证</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>wen_bing_tiao_bian</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>银翘散
+【出处】《温病条辩》
+【功效】辛凉透表，清热解毒
+【主治】风热表证
+【组成】
+君：金银花 一两，连翘 一两
+臣：牛蒡子 六钱，荆芥四钱，薄荷 六钱，淡豆豉 五钱
+佐：桔梗 六钱，芦根 四钱，竹叶 四钱
+使：甘草 五钱
+【配伍】
+金银花、连翘：辛凉透表、疏散风热，清热解毒，轻清宣透上焦风热
+薄荷、牛蒡子：辛凉疏散风热，清利咽喉、宣肺止咳
+荆芥穗、淡豆豉：辛温透表，发汗透邪，防寒凉郁遏气机，助邪外达
+桔梗：宣肺利咽、开气止咳
+淡竹叶、芦根：清热生津、除烦止渴，缓解风热口渴
+生甘草：调和诸药，兼清热解毒、利咽止痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>sang_xing_tang</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>桑杏汤</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>温燥证</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>wen_bing_tiao_bian</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>桑杏汤
+【出处】《温病条辨》
+【功效】清宣温燥，润肺止咳
+【主治】温燥证
+【组成】
+君：桑叶 一钱五分，杏仁 二钱
+臣：沙参 一钱
+佐：贝母 一钱，淡豆豉 一钱，栀子 一钱，梨皮一钱
+使：
+【配伍】
+桑叶：轻清宣透、疏散上焦温燥
+杏仁：苦润降肺、润燥止咳
+淡豆豉：透表散邪
+贝母：清热化痰、润肺散结
+沙参：养阴生津、润肺
+栀皮：轻清泄上焦燥热
+梨皮：清热润燥、生津止渴</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>xing_su_san</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>杏苏散</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>温燥证</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>wen_bing_tiao_bian</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>杏苏散
+【出处】《温病条辨》
+【功效】轻宣凉燥，理肺化痰
+【主治】凉燥证
+【组成】
+君：杏仁 三钱，苏叶 三钱
+臣：半夏 三钱，前胡 三钱，陈皮 三钱
+佐：茯苓 二钱，桔梗 二钱，枳壳 二钱
+使：甘草 一钱
+【配伍】
+苏叶：辛温发散，轻宣凉燥、疏散风寒；
+杏仁：苦温润燥，降肺止咳。
+前胡：疏风降气、化痰；
+桔梗枳壳：一升一降，宣畅肺气。
+半夏、陈皮、茯苓：燥湿化痰、理气健脾，杜生痰之源。
+生甘草：调和诸药</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>sha_shen_mai_dong_tang</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>沙参麦冬汤</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>肺阴虚</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>wen_bing_tiao_bian</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>沙参麦冬汤
+【出处】《温病条辩》
+【功效】清养肺胃，生津润燥
+【主治】肺阴虚
+【组成】
+君：沙参 三钱，麦门冬 三钱
+臣：玉竹 二钱，天花粉 一钱五分
+佐：扁豆 一钱五分，桑叶 一钱五分
+使：甘草 一钱
+【配伍】
+沙参、麦冬：养阴润肺、生津止渴，直补肺阴。
+玉竹、天花粉：增强养阴生津、润燥止咳，清虚热、润肺燥。
+桑叶：轻清宣肺、疏散虚热；
+扁豆：健脾养胃，培土生金，助生津之源。
+甘草：调和诸药，益气和中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>wu_tou_tang</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>乌头汤</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>痛痹</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>jin_gui_yao_lue</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>乌头汤
+【出处】《金匮要略》
+【功效】温经散寒，除湿止痛
+【主治】痛痹（寒痹）
+【组成】
+君：乌头 二钱
+臣：麻黄 三钱
+佐：白芍 三钱，黄芪 三钱
+使：甘草 三钱，蜂蜜 一斤
+【配伍】
+乌头：大辛大热，温经散寒、逐寒湿、止剧痛，专治寒凝痹痛；
+麻黄：发汗散寒，宣通经络，助乌头透邪外出。
+黄芪：益气固表、扶正实卫，防辛散耗气；
+白芍：养血和营、缓急止痛，柔筋止拘挛；
+炙甘草、蜂蜜：缓乌头峻烈毒性，调和诸药，缓急止痛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>bai_hu_gui_zhi_tang</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>白虎桂枝汤</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>热痹</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>jin_gui_yao_lue</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>白虎桂枝汤
+【出处】《金匮要略》
+【功效】清热通络，和营祛风
+【主治】热痹
+【组成】
+君：石膏 二两
+臣：知母 六钱
+佐：桂枝 三钱，粳米 五钱
+使：甘草 三钱
+【配伍】
+生石膏：大寒大清，清气分实热，泻火除烦，专治关节红肿灼热。
+知母：苦寒清热、滋阴润燥，助石膏清泄里热。
+桂枝：辛温通络、祛风和营，引药直达经络关节，散经络风湿热邪；辛温反佐，防寒凉凝滞气血。
+炙甘草、粳米：益气养胃，缓和石膏、知母寒凉之性，保护胃气。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>tian_wang_bu_xin_dan</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>天王补心丹</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>心阴虚</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>jin_gui_yao_lue</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>天王补心丹
+【出处】《金匮要略》
+【功效】滋阴养血，补心安神
+【主治】心阴虚
+【组成】
+君：生地黄 四两
+臣：天门冬 一两，麦门冬 一两，酸枣仁 一两，柏子仁 一两，当归一两
+佐：人参五钱，茯苓 五钱，玄参 五钱，丹参 五钱，远志 五钱，五味子 五钱
+使：桔梗 五钱
+【配伍】
+生地黄：重用甘寒，滋阴养血、清心降火，直补心肾阴血。
+天冬、麦冬、玄参：滋阴清热、生津润燥，壮水制虚火；
+当归、丹参：养血和血、清心安神。
+人参、茯苓：益气宁心；
+酸枣仁、柏子仁、五味子：养心安神、敛汗宁心；
+远志：交通心肾、安神益智。
+桔梗：载药上行入心经，引药归经。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>jin_gui_shen_qi_wan</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>金匮肾气丸</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>肾阳虚</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>jin_gui_yao_lue</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>金匮肾气丸
+【出处】《金匮要略》
+【功效】温补肾阳，化气行水
+【主治】肾阳虚
+【组成】
+君：附子 二钱，桂枝 三钱
+臣：熟地黄 一钱，山茱萸 四钱，山药 五钱
+佐：泽泻 三钱，茯苓 三钱，丹皮 三钱
+使：
+【配伍】
+附子、桂枝：温补肾阳、温通命门，微微生火、鼓舞肾气。
+熟地、山萸肉、山药：即六味三补，滋补肾阴、阴中求阳。
+丹皮、茯苓、泽泻：即六味三泻，泻浊降火、渗湿利水，防滋腻壅滞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>fang_feng_tang</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>防风汤</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>行痹</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>防风汤
+【出处】《太平惠民和剂局方》
+【功效】祛风通络，散寒除湿
+【主治】行痹（风痹）
+【组成】
+君：防风 五钱
+臣：桂枝 三钱，秦艽 三钱
+佐：当归 二钱，川芎 二钱，葛根 三钱
+使：甘草 一钱
+【配伍】
+防风：祛风胜湿、走窜经络，专治游走痹痛。
+桂枝：温散风寒、通经活络；
+秦艽：祛风湿、通络止痛，善治游走痹。
+当归：养血和营、祛风通络；
+川芎：活血通络；
+葛根：解肌舒筋；
+甘草调和诸药，调和营卫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>er_chen_tang</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>二陈汤</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>痰湿阻肺</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>二陈汤
+【出处】《太平惠民和剂局方》
+【功效】燥湿化痰，理气和中
+【主治】痰湿阻肺
+【组成】
+君：半夏 五钱
+臣：陈皮 五钱
+佐：茯苓 三钱
+使：甘草 一钱五分
+【配伍】
+半夏：辛温燥烈，燥湿化痰、降逆止呕。
+陈皮：理气行滞、燥湿化痰，使气顺则痰消。
+茯苓：健脾渗湿，杜生痰之源。
+甘草：调和诸药，益气和中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>si_wu_tang</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>四物汤</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>肝血虚</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>四物汤
+【出处】《太平惠民和剂局方》
+【功效】补血调血
+【主治】肝血虚
+【组成】
+君：熟地黄 四钱
+臣：当归 三钱
+佐：白芍 三钱，川芎 二钱
+使：
+【配伍】
+熟地黄：甘温味厚，滋阴补血、填精益髓，为补血之本。
+当归：补血养肝、活血调经，既补又行，补而不滞。
+白芍：养血敛阴、柔肝缓急，濡养筋脉。
+川芎：行气活血、疏肝通络，使补而不壅、补血不滞气。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>si_jun_zi_tang</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>四君子汤</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>脾气虚</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>四君子汤
+【出处】《太平惠民和剂局方》
+【功效】益气健脾
+【主治】脾气虚
+【组成】
+君：人参 四钱
+臣：白术 三钱
+佐：茯苓 三钱
+使：甘草 二钱
+【配伍】
+人参：大补元气、益气健脾。
+白术：健脾燥湿，助人参运化。
+茯苓：健脾渗湿，宁心安神，使补而不滞。
+炙甘草：益气和中、调和诸药。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>ping_wei_san</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>平胃散</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>湿盛困脾</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>平胃散
+【出处】《太平惠民和剂局方》
+【功效】燥湿运脾，行气和胃
+【主治】湿盛困脾
+【组成】
+君：苍术 三钱
+臣：厚朴 二钱
+佐：陈皮 二钱
+使：甘草 一钱
+【配伍】
+苍术：苦温燥湿、健脾运脾，专治湿困脾胃。
+厚朴：行气除满、燥湿化浊，消脘腹胀痞。
+陈皮：理气和胃、燥湿醒脾，使气机条达。
+炙甘草：益气和中、调和诸药；姜枣调和脾胃。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>shen_ling_bai_zhu_san</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>参苓白术散</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>脾虚湿盛</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>参苓白术散
+【出处】《太平惠民和剂局方》
+【功效】益气健脾，渗湿止泻
+【主治】脾虚湿盛
+【组成】
+君：人参 五钱，茯苓 五钱，白术 五钱
+臣：山药 五钱，莲子 三钱，扁豆 三钱，薏苡仁 七钱
+佐：砂仁 二钱，桔梗 二钱
+使：甘草 二钱
+【配伍】
+人参、白术、茯苓、炙甘草：即四君子汤，益气健脾、补益脾虚之本。
+山药、莲子：健脾益气、固肠止泻；
+扁豆、薏仁：健脾渗湿、利水除浊；
+砂仁：芳香醒脾、行气和胃，防补药滋腻碍胃；
+桔梗：宣利肺气、载药上行，培土生金，兼治肺虚久咳。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>xiao_yao_san</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>逍遥散</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>肝脾不和</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>逍遥散
+【出处】《太平惠民和剂局方》
+【功效】疏肝解郁，养血健脾
+【主治】肝脾不和（肝郁脾虚）
+【组成】
+君：柴胡 三钱
+臣：当归 三钱，白芍 三钱
+佐：白术 三钱，茯苓 三钱，生姜 一钱，薄荷 一钱
+使：甘草 一钱五分
+【配伍】
+柴胡：疏肝解郁、条达肝气，疏散郁滞。
+当归、白芍：养血柔肝，补肝体、缓肝急；防肝郁化火伤阴。
+白术、茯苓：健脾祛湿、培土荣木；
+生姜：温胃和中、调和气血。
+薄荷：助柴胡疏肝透热、疏散郁遏；
+炙甘草：益气补中，调和诸药；合白芍缓急止痛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>huo_xiang_zheng_qi_san</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>藿香正气散</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>外感风寒，内伤湿滞</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>tai_ping_hui_min_he_ji_ju_fang</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>藿香正气散
+【出处】《太平惠民和剂局方》
+【功效】解表散寒，化湿和中，理气止呕
+【主治】外感风寒，内伤湿滞
+【组成】
+君：藿香 五钱
+臣：苏叶 三钱，白芷 三钱，半夏 四钱，厚朴 四钱
+佐：白术 四钱，苍术 四钱，陈皮 三钱，茯苓 五钱，大腹皮 五钱 ，桔梗 二钱
+使：甘草 二钱，生姜 二钱，大枣 二钱
+【配伍】
+藿香：芳香化湿、和中止呕，兼解表散寒，表里兼顾。
+紫苏、白芷：解表散寒、化湿辟秽，助藿香散外感风寒。
+陈皮、半夏、厚朴、大腹皮：理气燥湿、消胀除满、降逆止呕；
+白术、苍术、 茯苓：健脾祛湿、实脾止泻；
+桔梗：宣利肺气、载药上行。
+炙甘草、姜枣：调和脾胃，益气和中，调和诸药。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>bu_fei_tang</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>补肺汤</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>肺气虚</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>bei_ji_qian_jin_yao_fang</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>补肺汤
+【出处】《备急千金要方》
+【功效】补肺益气，止咳平喘
+【主治】肺气虚
+【组成】
+君：人参 三钱，黄芪 五钱
+臣：熟地黄 五钱
+佐：五味子 二钱，紫菀 三钱，桑白皮 三钱
+使：
+【配伍】
+人参、黄芪：大补肺气、固表益气，补益肺气虚之本。
+熟地黄：滋肾填精，金水相生，助肺气之源。
+五味子：收敛肺气、敛汗止喘，固表止自汗。
+紫菀、桑白皮：降肺气、化痰止咳，清润不燥，补虚不滞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>huang_lian_wen_dan_tang</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>黄连温胆汤</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>痰火扰心</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>bei_ji_qian_jin_yao_fang</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>黄连温胆汤
+【出处】《备急千金要方》
+【功效】清热化痰，和中安神
+【主治】痰火扰心
+【组成】
+君：黄连 三钱
+臣：半夏 四钱，竹茹 五钱
+佐：陈皮 四钱，枳实 四钱，茯苓 四钱
+使：甘草 二钱，生姜 一钱，大枣 一钱
+【配伍】
+黄连：苦寒直折，清心泻火、燥湿清热，专清痰火。
+半夏：燥湿化痰；
+竹茹：清热化痰、除烦安神。
+陈皮：理气化痰；
+枳实：破气消痞、导痰下行；
+茯苓：健脾渗湿，绝生痰之源。
+甘草:调和诸药，和中缓急。
+生姜：和胃止呕，制半夏之毒
+大枣：益气补中，调和脾胃</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>yi_yi_ren_tang</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>薏苡仁汤</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>着痹</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>薏苡仁汤
+【出处】《太医院经验奇效良方大全》
+【功效】除湿通络，祛风散寒
+【主治】着痹（湿痹）
+【组成】
+君：薏苡仁 一两
+臣：羌活 三钱，独活 三钱，麻黄 三钱，桂枝 三钱
+佐：当归 二钱，川芎 二钱
+使：甘草 三钱
+【配伍】
+薏苡仁：利水渗湿、健脾除痹、舒筋缓急，专治湿痹重着。
+羌活、独活：祛风胜湿、通络止痛，上下分治周身湿邪
+麻、桂：温经散寒、通阳通络，助祛湿
+当归、川芎：养血活血、通络止痛，治风先治血、血行风自灭
+甘草：调和诸药，温散助祛湿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>di_tan_tang</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>涤痰汤</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>痰迷心窍</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>涤痰汤
+【出处】《太医院经验奇效良方大全》
+【功效】涤痰开窍，益气扶正
+【主治】痰迷心窍
+【组成】
+君：半夏 二钱五分，胆南星 二钱五分
+臣：枳实 二钱，陈皮 一分五钱
+佐：竹茹 一钱，茯苓 二钱，石菖蒲 一钱，人参 一钱
+使：生姜 一钱，甘草 一钱
+【配伍】
+半夏、陈皮：燥湿化痰、理气和胃，直祛痰湿之本。
+胆南星：清气化痰，助半夏化痰之力
+枳实、竹茹：清热化痰、破气开郁，降逆涤痰。
+石菖蒲：豁痰开窍、交通心肾、醒神益智；
+茯苓：健脾渗湿，杜绝生痰之源；
+人参：益气扶正，扶助正气以运痰。
+甘草、生姜：调和诸药，益气和中，制胆南星、半夏之毒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>chai_hu_shu_gan_san</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>柴胡疏肝散</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>肝气郁结</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>jing_yue_quan_shu</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>柴胡疏肝散
+【出处】《景岳全书》
+【功效】疏肝解郁，行气止痛
+【主治】肝气郁结
+【组成】君：柴胡 二钱
+臣：香附 一钱五分钱，川芎 一钱五分
+佐：陈皮 二钱，枳壳 一钱五分，白芍 一钱五分
+使：甘草 五分
+【配伍】
+柴胡：疏肝解郁、调畅气机，直入肝胆疏泄郁滞。
+香附:理气疏肝、止痛；
+川芎:行气活血、通络止痛。
+枳壳、陈皮:理气行滞、宽胸除胀；
+白芍:柔肝缓急、养阴和营，防理气药耗伤肝阴。
+炙甘草:调和诸药，配白芍酸甘化阴、缓急止痛。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>nuan_gan_jian</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>暖肝煎</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>寒滞肝脉</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>jing_yue_quan_shu</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>暖肝煎
+【出处】《景岳全书》
+【功效】温补肝肾，行气散寒
+【主治】寒滞肝脉
+【组成】
+君：肉桂 一钱，茴香 二钱
+臣：当归 二钱，枸杞子 三钱
+佐：乌药 二钱，茯苓 二钱，沉香 一钱
+使：生姜 一钱
+【配伍】
+肉桂：温肾暖肝、散寒止痛；
+茴香：暖肝理气、专治寒疝睾丸冷痛。
+当归、枸杞：养血补肝、温补肝肾，扶正固本。
+乌药：行气散寒、疏肝止痛；
+沉香：降气暖肝、下气止痛；
+茯苓：健脾渗湿，助肝肾气化。
+生姜：散寒和胃，辅助中焦</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>zuo_gui_wan</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>左归丸</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>肾精不足</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>jing_yue_quan_shu</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>左归丸
+【出处】《景岳全书》
+【功效】滋阴补肾，填精益髓
+【主治】肾精不足
+【组成】
+君：熟地黄 八钱
+臣：龟板胶 四钱，鹿角胶 四钱，枸杞子 四钱，菟丝子 四钱
+佐：山茱萸 四钱，山药 四钱
+使：牛膝 三钱
+【配伍】
+熟地黄：大补真阴、填精补髓。
+山药、枸杞、山茱萸：滋补肝肾、养阴固精，助熟地滋补肾精。
+龟鹿二胶：峻补精血、阴阳双补、侧重填髓
+菟丝子：补肾益精
+川牛膝：补肝肾、强筋骨、引药下行</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>dao_chi_san</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>导赤散</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>心火亢盛</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>xiao_er_yao_zheng_zhi_jue</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>导赤散
+【出处】《小儿药证直决》
+【功效】清心利水养阴
+【主治】心火亢盛
+【组成】
+君：生地黄 二钱，木通 二钱
+臣：竹叶 二钱
+佐：甘草 二钱
+使：
+【配伍】
+生地黄：凉血滋阴、清心降火，养阴以制心火。
+木通：清心泻火、利水通淋，导心火从小便而出。
+竹叶：清心除烦、淡渗利水，助木通清心导赤。
+生甘草：梢清热解毒、直达茎中，缓尿痛、调和诸药。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>liu_wei_di_huang_wan</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>六味地黄丸</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>肾阴虚</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>xiao_er_yao_zheng_zhi_jue</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>六味地黄丸
+【出处】《金匮要略》
+【功效】滋阴补肾
+【主治】肾阴虚
+【组成】
+君：熟地黄 八钱
+臣：山茱萸 四钱，山药 四钱
+佐：泽泻 三钱，茯苓 三钱，丹皮 三钱
+使：
+【配伍】
+熟地黄：重用滋阴补肾、填精益髓。
+萸肉：补肝肾、敛精气；
+山药：补脾益肾、固涩下焦。
+泽泻：泻肾浊、防熟地滋腻；
+丹皮：清泻虚火、凉血除蒸；
+茯苓：健脾渗湿、助山药补脾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>qing_qi_hua_tan_wan</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>清气化痰丸</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>痰热壅肺</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>yi_fang_kao</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>清气化痰丸
+【出处】《医方考》
+【功效】清热化痰，理气止咳
+【主治】痰热壅肺
+【组成】
+君：胆南星 一两五钱
+臣：半夏 一两五钱，瓜蒌仁 一两，黄芩 一两
+佐：杏仁 一两，陈皮 一两，枳实 一两，茯苓 一两
+使：生姜 三两
+【配伍】
+胆南星：清热化痰，专治痰热壅肺。
+瓜蒌仁：清热化痰、润肺下气、宽胸散结；
+黄芩：清泻肺火，助南星清化痰热。
+杏仁、半夏：降利肺气、化痰止咳
+陈皮、枳实：理气破结，气顺痰自消
+茯苓：健脾渗湿，杜绝生痰之源
+生姜：制胆南星、半夏之毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>gou_teng_san</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>钩藤散</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>肝阳上亢</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>pu_ji_ben_shi_fang</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>钩藤散
+【出处】《普济本事方》
+【功效】平肝息风，清热化痰，益气养阴
+【主治】肝阳上亢
+【组成】
+君：钩藤 三钱，菊花 三钱
+臣：防风 三钱，石膏 三钱
+佐：茯苓 三钱，半夏 三钱，陈皮 三钱，人参 三钱
+使：甘草 三钱
+【配伍】
+钩藤、菊花：平肝息风、清利头目
+石膏：清热泻火、除烦止晕
+防风：祛风解痉、载药上行
+半夏、陈皮、茯苓：燥湿化痰、和胃降逆
+麦冬、人参：益气养阴、扶正固本
+茯神：宁心安神
+炙甘草、生姜+调和诸药、和胃止呕、制半夏之毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>long_dan_xie_gan_tang</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>龙胆泻肝汤</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>肝火上炎</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>lan_shi_mi_cang</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>龙胆泻肝汤
+【出处】《兰室秘藏》
+【功效】清泻肝胆实火，清利肝经湿热
+【主治】肝火上炎
+【组成】
+君：龙胆草 二钱
+臣：黄芩 三钱，栀子 三钱
+佐：泽泻四钱，木通三钱，车前子 三钱，当归 三钱，生地黄 六钱，柴胡 三钱
+使：甘草 二钱
+【配伍】
+龙胆草：大苦大寒，直泻肝胆实火、清利下焦湿热。
+黄芩、栀子：苦寒泻火，清热燥湿，助龙胆草清泻肝火。
+泽泻、木通、车前子：清热利湿，导湿热从小便而去；
+生地黄、当归：滋阴养血，防苦寒药燥烈伤阴；
+柴胡：疏肝引经，畅达肝胆气机。
+生甘草清热解毒、调和诸药，护胃安中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>yi_guan_jian</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>一贯煎</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>肝阴虚</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>liu_zhou_yi_hua</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>一贯煎
+【出处】《柳州医话》
+【功效】滋阴疏肝
+【主治】肝阴虚
+【组成】
+君：生地黄 一两
+臣：枸杞子 六钱，沙参 三钱，麦门冬 三钱，当归 三钱
+佐：川楝子 一钱五分
+使：
+【配伍】
+生地黄：重用滋阴养血、补益肝肾，直补肝阴之本。
+枸杞：滋补肝肾、填精养阴；
+当归：养血柔肝、濡养经脉。
+北沙参、麦冬：养阴生津、润肺养胃，滋水以涵木；
+川楝子：苦寒疏肝泄热、行气止痛，疏肝而不伤阴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>gui_pi_tang</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>归脾汤</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>心脾两虚</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>yan_shi_ji_sheng_fang</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>归脾汤
+【出处】《严氏济生方》
+【功效】益气补血，健脾养心
+【主治】心脾两虚
+【组成】
+君：黄芪 一两，人参 五钱
+臣：龙眼 五钱，白术 五钱，当归 五钱，酸枣仁 六钱
+佐：茯神 五钱，远志 三钱，木香 二钱
+使：甘草 二钱，生姜 一钱，大枣 一钱
+【配伍】
+黄芪、人参：大补脾气，益气生血。
+当归、龙眼：肉养血补心、安神。
+白术：助健脾；
+酸枣仁、茯神：宁心安神；
+远志：安神益智、交通心肾；
+木香：理气醒脾，防滋补壅滞碍胃。
+炙甘草、姜枣：益气和中、调和诸药，助脾胃生化气血。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>yang_xin_tang</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>养心汤</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>心气虚</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ren_zhai_zhi_zhi_fang_lun</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>养心汤
+【出处】《仁斋直指方论》
+【功效】益气补血，养心安神
+【主治】心气虚
+【组成】
+君：黄芪 五钱，人参 三钱
+臣：当归 五钱，茯神 五钱，茯苓 五钱
+佐：酸枣仁 三钱，柏子仁 三钱，远志 三钱，五味子 三钱，川芎 五钱，半夏 五钱，肉桂 三钱
+使：甘草 四钱，生姜 一钱，大枣 一钱
+【配伍】
+人参、黄芪：大补心气，固元益气，直补心气之本。
+当归、川芎：养血和营，气阴双补，气血互生。
+茯苓、茯神：健脾宁心、安神定悸
+枣仁、柏子仁、远志、五味子：养心安神、敛心止汗、交通心肾
+半夏：和胃化痰，防滋补壅滞
+肉桂：少佐温通，助心阳以鼓心气
+炙甘草、生姜、大枣：益气和中，调和诸药，制半夏之毒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>yu_ping_feng_san</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>玉屏风散</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>卫气虚</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>jiu_yuan_fang</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>玉屏风散
+【出处】《究原方》
+【功效】益气固表，止汗御风
+【主治】卫气虚
+【组成】
+君：黄芪  一两
+臣：白术 一两
+佐：防风 五钱
+使：
+【配伍】
+黄芪：大补肺脾之气，固表实卫、益气止汗。
+白术：健脾益气，助黄芪培补元气、固护肌表。
+防风：走肌表、疏散风邪，固表不留邪、祛风不伤正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>jin_suo_gu_jing_wan</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>金锁固精丸</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>肾气不固</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>yi_fang_ji_jie</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>金锁固精丸
+【出处】《医方集解》
+【功效】补肾涩精，固摄肾气
+【主治】肾气不固
+【组成】
+君：蒺藜 五钱
+臣：芡实 五钱
+佐：龙骨 五钱，牡蛎 五钱，莲须 三钱
+使：莲子 三两
+【配伍】
+沙苑蒺藜：补肾益精、平补肝肾，固本培元。
+芡实+健脾益肾、固涩精气。
+莲须：专涩精；
+龙骨、牡蛎：重镇收敛、固涩滑脱。
+莲子：养心安神，补肾涩精，制丸药赋型</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>ren_shen_ge_jie_san</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>人参蛤蚧散</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>肾不纳气</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>wang_shi_bo_ji_fang</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>人参蛤蚧散
+【出处】《博济方》
+【功效】补肺益肾，纳气定喘，止咳化痰
+【主治】肾不纳气
+【组成】
+君：蛤蚧 五钱，人参 四钱
+臣：知母 三钱，贝母 三钱，桑白皮 三钱
+佐：茯苓 四钱，杏仁 四钱
+使：甘草 三钱
+【配伍】
+蛤蚧：补肺益肾、温肾纳气、定喘止嗽，专治肾不纳气虚喘。
+人参：大补元气、补益肺气，助蛤蚧固本益气。
+杏仁、贝母：润肺化痰、降气止咳
+桑白皮、知母：清泻肺热、润燥止咳
+茯苓：健脾渗湿、杜绝生痰之源
+炙甘草：益气和中，调和诸药。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="7" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="15" customHeight="1">
+      <c r="C48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="C49" s="28" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="C50" s="28" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="C51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="C52" s="28" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="C53" s="28" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="C54" s="28" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="C55" s="28" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="C56" s="28" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="C57" s="28" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="C58" s="28" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="C59" s="28" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="C60" s="28" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="C61" s="28" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="C62" s="28" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="C63" s="28" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="C64" s="28" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="C65" s="28" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="C66" s="28" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="C67" s="28" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="C68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="C69" s="28" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="C70" s="28" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="C71" s="28" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="C72" s="28" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="C73" s="28" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="C74" s="28" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="C75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="C76" s="28" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="C77" s="28" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="C78" s="28" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="C79" s="28" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="C80" s="28" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="C81" s="28" t="n"/>
+    </row>
+    <row r="82"/>
+    <row r="83" ht="15" customHeight="1">
+      <c r="C83" s="28" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="C84" s="28" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="C85" s="28" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="C86" s="28" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="C87" s="28" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="C88" s="28" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="C89" s="28" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="C90" s="28" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="C91" s="28" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="C92" s="28" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="C93" s="28" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="C94" s="28" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="C95" s="28" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="C96" s="28" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="C97" s="28" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="C98" s="28" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100" ht="15" customHeight="1">
+      <c r="C100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="C101" s="28" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="C102" s="28" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="C103" s="28" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="C104" s="28" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="C105" s="28" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="C106" s="28" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="C107" s="28" t="n"/>
+    </row>
+    <row r="108"/>
+    <row r="109" ht="15" customHeight="1">
+      <c r="C109" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5143,8 +7344,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="47"/>
-    <col width="9" customWidth="1" style="9" min="48" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="48"/>
+    <col width="9" customWidth="1" style="9" min="49" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -5879,2153 +8080,6 @@
     </row>
     <row r="45">
       <c r="A45" s="10" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet2">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
-  <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="6.875" customWidth="1" style="7" min="4" max="4"/>
-    <col width="45.75" customWidth="1" style="3" min="5" max="5"/>
-    <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FormulaID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>FormulaName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>TargetDiseaseName</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
-        <is>
-          <t>unlock required experie</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>BookID</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>DetailText</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>ma_huang_tang</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>麻黄汤</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>风寒表实证</t>
-        </is>
-      </c>
-      <c r="D2" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>麻黄汤
-【出处】《伤寒论》
-【功效】发汗解表，宣肺平喘
-【主治】风寒表实证
-【组成】
-君：麻黄 三钱
-臣：桂枝 二钱
-佐：杏仁 二钱
-使：甘草 一钱
-【配伍】
-麻桂相须，增强发汗散寒之力，专治表实无汗。
-麻杏相使，宣降相配，专治寒邪闭肺之喘逆。
-甘草调和诸药</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>gui_zhi_tang</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>桂枝汤</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>风寒表虚证</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>桂枝汤
-【出处】《伤寒论》
-【功效】解肌发表，调和营卫
-【主治】风寒表虚证
-【组成】
-君：桂枝 三钱
-臣：白芍 三钱
-佐：生姜 三钱，大枣 二钱
-使：甘草 二钱
-【配伍】
-桂枝辛散卫邪，白芍酸敛营阴；一散一收，调和营卫，不伤正、不敛邪。
-姜枣相合，调和脾胃，化生气血，资营卫之源。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>ma_xing_shi_gan_tang</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>麻杏石甘汤</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>肺热壅盛</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>麻杏石甘汤
-【出处】《伤寒论》
-【功效】辛凉疏表，清肺平喘
-【主治】肺热壅盛
-【组成】
-君：麻黄 三钱
-臣：石膏 八钱
-佐：杏仁 三钱
-使：甘草 二钱
-【配伍】
-麻黄：辛温，宣肺平喘、开泄肺气，散邪解表。
-石膏:辛甘大寒，清泻肺热、生津止渴，清里热以制麻黄之温。
-杏仁:苦降肺气，降利平喘，与麻黄一宣一降，恢复肺之宣肃。
-炙甘草:调和诸药，益气护中，缓急润肺。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>gui_zhi_gan_cao_tang</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>桂枝甘草汤</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>心阳虚</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>桂枝甘草汤
-【出处】《伤寒论》
-【功效】温补心阳，益气定悸
-【主治】心阳虚
-【组成】
-君：桂枝 四钱
-臣：甘草 二钱
-佐：
-使：
-【配伍】
-桂枝：辛甘温，温通心阳、平冲降逆、温经通脉。
-炙甘草：益气补中、缓急养心，甘温益气。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>dang_gui_si_ni_tang</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>当归四逆汤</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>寒凝心脉</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>当归四逆汤
-【出处】《伤寒论》
-【功效】温经散寒，养血通脉
-【主治】寒凝心脉
-【组成】
-君：当归 四钱
-臣：桂枝 三钱，白芍 三钱
-佐：细辛 一钱，木通 二钱
-使：甘草 二钱，大枣 二钱
-【配伍】
-当归：养血和血、温补肝血，濡养经脉。
-桂枝：温通经脉、宣通阳气；
-白芍：养血敛阴，缓急止痛；
-细辛：直入三阴，温经散寒、破寒凝。
-通草：通利经脉，引寒邪外泄。
-大枣、炙甘草益气健脾、调和诸药，养血以助脉道充盈。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>li_zhong_wan</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>理中丸</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>脾阳虚</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>理中丸
-【出处】《伤寒论》
-【功效】温中祛寒，补气健脾
-【主治】脾阳虚
-【组成】
-君：干姜 五钱
-臣：人参 五钱
-佐：白术 五钱
-使：甘草 五钱
-【配伍】
-干姜：大辛大热，温中祛寒、振奋脾阳。
-人参：益气健脾，补益脾胃气虚之本。
-白术：健脾燥湿，助运化、利水湿。
-炙甘草：益气和中、调和诸药，缓急止痛。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>zhen_wu_tang</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>真武汤</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>肾虚水泛</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>真武汤
-【出处】《伤寒论》
-【功效】温阳利水
-【主治】肾虚水泛
-【组成】
-君：附子 三钱
-臣：茯苓 三钱，白术 三钱
-佐：生姜 二钱，白芍 三钱
-使：
-【配伍】
-附子：大辛大热，温补肾阳、散阴寒，助气化以行水。
-茯苓：健脾渗湿、利水消肿；
-白术：健脾燥湿、培土制水。
-生姜：温散水气、助附子温阳，兼和胃散饮。
-芍药：利小便、柔肝缓急止痛，防附子燥热伤阴，敛阴和营。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>bai_hu_tang</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>白虎汤</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>气分热盛</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>白虎汤
-【出处】《伤寒论》
-【功效】清热生津，辛寒清气
-【主治】气分热盛
-【组成】
-君：石膏 二两
-臣：知母 六钱
-佐：粳米 三钱
-使：甘草 二钱
-【配伍】
-生石膏：辛甘大寒，清泻阳明气分实热，除壮热、止大汗。
-知母：苦寒质润，清热泻火、滋阴生津，助石膏清润除烦止渴。
-粳米、炙甘草：益气养胃、缓和石膏知母寒凉之性，保护胃气；生津补液，防大寒伤中。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>huang_lian_e_jiao_tang</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>黄连阿胶汤</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>心肾不交</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>shang_han_lun</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>黄连阿胶汤
-【出处】《伤寒论》
-【功效】滋阴降火，交通心肾
-【主治】心肾不交
-【组成】
-君：黄连 四钱
-臣：黄芩 三钱，白芍 三钱
-佐：阿胶 三钱
-使：鸡子黄 一两
-【配伍】
-黄连：苦寒直折，清泻心火、除烦安神。
-黄芩：助黄连清心泻火；
-阿胶：滋阴补肾、养血填阴，滋肾阴以济心火。
-白芍：敛阴和营、柔肝缓急；
-鸡子黄：滋阴润燥、养心安神，入少阴交通心肾。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>yin_qiao_san</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>银翘散</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>风热表证</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>wen_bing_tiao_bian</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>银翘散
-【出处】《温病条辩》
-【功效】辛凉透表，清热解毒
-【主治】风热表证
-【组成】
-君：金银花 一两，连翘 一两
-臣：牛蒡子 六钱，荆芥四钱，薄荷 六钱，淡豆豉 五钱
-佐：桔梗 六钱，芦根 四钱，竹叶 四钱
-使：甘草 五钱
-【配伍】
-金银花、连翘：辛凉透表、疏散风热，清热解毒，轻清宣透上焦风热
-薄荷、牛蒡子：辛凉疏散风热，清利咽喉、宣肺止咳
-荆芥穗、淡豆豉：辛温透表，发汗透邪，防寒凉郁遏气机，助邪外达
-桔梗：宣肺利咽、开气止咳
-淡竹叶、芦根：清热生津、除烦止渴，缓解风热口渴
-生甘草：调和诸药，兼清热解毒、利咽止痛</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>sang_xing_tang</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>桑杏汤</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>温燥证</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>wen_bing_tiao_bian</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>桑杏汤
-【出处】《温病条辨》
-【功效】清宣温燥，润肺止咳
-【主治】温燥证
-【组成】
-君：桑叶 一钱五分，杏仁 二钱
-臣：沙参 一钱
-佐：贝母 一钱，淡豆豉 一钱，栀子 一钱，梨皮一钱
-使：
-【配伍】
-桑叶：轻清宣透、疏散上焦温燥
-杏仁：苦润降肺、润燥止咳
-淡豆豉：透表散邪
-贝母：清热化痰、润肺散结
-沙参：养阴生津、润肺
-栀皮：轻清泄上焦燥热
-梨皮：清热润燥、生津止渴</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>xing_su_san</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>杏苏散</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>温燥证</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>wen_bing_tiao_bian</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>杏苏散
-【出处】《温病条辨》
-【功效】轻宣凉燥，理肺化痰
-【主治】凉燥证
-【组成】
-君：杏仁 三钱，苏叶 三钱
-臣：半夏 三钱，前胡 三钱，陈皮 三钱
-佐：茯苓 二钱，桔梗 二钱，枳壳 二钱
-使：甘草 一钱
-【配伍】
-苏叶：辛温发散，轻宣凉燥、疏散风寒；
-杏仁：苦温润燥，降肺止咳。
-前胡：疏风降气、化痰；
-桔梗枳壳：一升一降，宣畅肺气。
-半夏、陈皮、茯苓：燥湿化痰、理气健脾，杜生痰之源。
-生甘草：调和诸药</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>sha_shen_mai_dong_tang</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>沙参麦冬汤</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>肺阴虚</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>wen_bing_tiao_bian</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>沙参麦冬汤
-【出处】《温病条辩》
-【功效】清养肺胃，生津润燥
-【主治】肺阴虚
-【组成】
-君：沙参 三钱，麦门冬 三钱
-臣：玉竹 二钱，天花粉 一钱五分
-佐：扁豆 一钱五分，桑叶 一钱五分
-使：甘草 一钱
-【配伍】
-沙参、麦冬：养阴润肺、生津止渴，直补肺阴。
-玉竹、天花粉：增强养阴生津、润燥止咳，清虚热、润肺燥。
-桑叶：轻清宣肺、疏散虚热；
-扁豆：健脾养胃，培土生金，助生津之源。
-甘草：调和诸药，益气和中。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>wu_tou_tang</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>乌头汤</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>痛痹</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>jin_gui_yao_lue</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>乌头汤
-【出处】《金匮要略》
-【功效】温经散寒，除湿止痛
-【主治】痛痹（寒痹）
-【组成】
-君：乌头 二钱
-臣：麻黄 三钱
-佐：白芍 三钱，黄芪 三钱
-使：甘草 三钱，蜂蜜 一斤
-【配伍】
-乌头：大辛大热，温经散寒、逐寒湿、止剧痛，专治寒凝痹痛；
-麻黄：发汗散寒，宣通经络，助乌头透邪外出。
-黄芪：益气固表、扶正实卫，防辛散耗气；
-白芍：养血和营、缓急止痛，柔筋止拘挛；
-炙甘草、蜂蜜：缓乌头峻烈毒性，调和诸药，缓急止痛。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>bai_hu_gui_zhi_tang</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>白虎桂枝汤</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>热痹</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>jin_gui_yao_lue</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>白虎桂枝汤
-【出处】《金匮要略》
-【功效】清热通络，和营祛风
-【主治】热痹
-【组成】
-君：石膏 二两
-臣：知母 六钱
-佐：桂枝 三钱，粳米 五钱
-使：甘草 三钱
-【配伍】
-生石膏：大寒大清，清气分实热，泻火除烦，专治关节红肿灼热。
-知母：苦寒清热、滋阴润燥，助石膏清泄里热。
-桂枝：辛温通络、祛风和营，引药直达经络关节，散经络风湿热邪；辛温反佐，防寒凉凝滞气血。
-炙甘草、粳米：益气养胃，缓和石膏、知母寒凉之性，保护胃气。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>tian_wang_bu_xin_dan</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>天王补心丹</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>心阴虚</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>jin_gui_yao_lue</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>天王补心丹
-【出处】《金匮要略》
-【功效】滋阴养血，补心安神
-【主治】心阴虚
-【组成】
-君：生地黄 四两
-臣：天门冬 一两，麦门冬 一两，酸枣仁 一两，柏子仁 一两，当归一两
-佐：人参五钱，茯苓 五钱，玄参 五钱，丹参 五钱，远志 五钱，五味子 五钱
-使：桔梗 五钱
-【配伍】
-生地黄：重用甘寒，滋阴养血、清心降火，直补心肾阴血。
-天冬、麦冬、玄参：滋阴清热、生津润燥，壮水制虚火；
-当归、丹参：养血和血、清心安神。
-人参、茯苓：益气宁心；
-酸枣仁、柏子仁、五味子：养心安神、敛汗宁心；
-远志：交通心肾、安神益智。
-桔梗：载药上行入心经，引药归经。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>jin_gui_shen_qi_wan</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>金匮肾气丸</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>肾阳虚</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>jin_gui_yao_lue</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>金匮肾气丸
-【出处】《金匮要略》
-【功效】温补肾阳，化气行水
-【主治】肾阳虚
-【组成】
-君：附子 二钱，桂枝 三钱
-臣：熟地黄 一钱，山茱萸 四钱，山药 五钱
-佐：泽泻 三钱，茯苓 三钱，丹皮 三钱
-使：
-【配伍】
-附子、桂枝：温补肾阳、温通命门，微微生火、鼓舞肾气。
-熟地、山萸肉、山药：即六味三补，滋补肾阴、阴中求阳。
-丹皮、茯苓、泽泻：即六味三泻，泻浊降火、渗湿利水，防滋腻壅滞。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>fang_feng_tang</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>防风汤</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>行痹</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>防风汤
-【出处】《太平惠民和剂局方》
-【功效】祛风通络，散寒除湿
-【主治】行痹（风痹）
-【组成】
-君：防风 五钱
-臣：桂枝 三钱，秦艽 三钱
-佐：当归 二钱，川芎 二钱，葛根 三钱
-使：甘草 一钱
-【配伍】
-防风：祛风胜湿、走窜经络，专治游走痹痛。
-桂枝：温散风寒、通经活络；
-秦艽：祛风湿、通络止痛，善治游走痹。
-当归：养血和营、祛风通络；
-川芎：活血通络；
-葛根：解肌舒筋；
-甘草调和诸药，调和营卫。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>er_chen_tang</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>二陈汤</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>痰湿阻肺</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>二陈汤
-【出处】《太平惠民和剂局方》
-【功效】燥湿化痰，理气和中
-【主治】痰湿阻肺
-【组成】
-君：半夏 五钱
-臣：陈皮 五钱
-佐：茯苓 三钱
-使：甘草 一钱五分
-【配伍】
-半夏：辛温燥烈，燥湿化痰、降逆止呕。
-陈皮：理气行滞、燥湿化痰，使气顺则痰消。
-茯苓：健脾渗湿，杜生痰之源。
-甘草：调和诸药，益气和中。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>si_wu_tang</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>四物汤</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>肝血虚</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>四物汤
-【出处】《太平惠民和剂局方》
-【功效】补血调血
-【主治】肝血虚
-【组成】
-君：熟地黄 四钱
-臣：当归 三钱
-佐：白芍 三钱，川芎 二钱
-使：
-【配伍】
-熟地黄：甘温味厚，滋阴补血、填精益髓，为补血之本。
-当归：补血养肝、活血调经，既补又行，补而不滞。
-白芍：养血敛阴、柔肝缓急，濡养筋脉。
-川芎：行气活血、疏肝通络，使补而不壅、补血不滞气。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>si_jun_zi_tang</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>四君子汤</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>脾气虚</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>四君子汤
-【出处】《太平惠民和剂局方》
-【功效】益气健脾
-【主治】脾气虚
-【组成】
-君：人参 四钱
-臣：白术 三钱
-佐：茯苓 三钱
-使：甘草 二钱
-【配伍】
-人参：大补元气、益气健脾。
-白术：健脾燥湿，助人参运化。
-茯苓：健脾渗湿，宁心安神，使补而不滞。
-炙甘草：益气和中、调和诸药。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>ping_wei_san</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>平胃散</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>湿盛困脾</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>平胃散
-【出处】《太平惠民和剂局方》
-【功效】燥湿运脾，行气和胃
-【主治】湿盛困脾
-【组成】
-君：苍术 三钱
-臣：厚朴 二钱
-佐：陈皮 二钱
-使：甘草 一钱
-【配伍】
-苍术：苦温燥湿、健脾运脾，专治湿困脾胃。
-厚朴：行气除满、燥湿化浊，消脘腹胀痞。
-陈皮：理气和胃、燥湿醒脾，使气机条达。
-炙甘草：益气和中、调和诸药；姜枣调和脾胃。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>shen_ling_bai_zhu_san</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>参苓白术散</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>脾虚湿盛</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>参苓白术散
-【出处】《太平惠民和剂局方》
-【功效】益气健脾，渗湿止泻
-【主治】脾虚湿盛
-【组成】
-君：人参 五钱，茯苓 五钱，白术 五钱
-臣：山药 五钱，莲子 三钱，扁豆 三钱，薏苡仁 七钱
-佐：砂仁 二钱，桔梗 二钱
-使：甘草 二钱
-【配伍】
-人参、白术、茯苓、炙甘草：即四君子汤，益气健脾、补益脾虚之本。
-山药、莲子：健脾益气、固肠止泻；
-扁豆、薏仁：健脾渗湿、利水除浊；
-砂仁：芳香醒脾、行气和胃，防补药滋腻碍胃；
-桔梗：宣利肺气、载药上行，培土生金，兼治肺虚久咳。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>xiao_yao_san</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>逍遥散</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>肝脾不和</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>逍遥散
-【出处】《太平惠民和剂局方》
-【功效】疏肝解郁，养血健脾
-【主治】肝脾不和（肝郁脾虚）
-【组成】
-君：柴胡 三钱
-臣：当归 三钱，白芍 三钱
-佐：白术 三钱，茯苓 三钱，生姜 一钱，薄荷 一钱
-使：甘草 一钱五分
-【配伍】
-柴胡：疏肝解郁、条达肝气，疏散郁滞。
-当归、白芍：养血柔肝，补肝体、缓肝急；防肝郁化火伤阴。
-白术、茯苓：健脾祛湿、培土荣木；
-生姜：温胃和中、调和气血。
-薄荷：助柴胡疏肝透热、疏散郁遏；
-炙甘草：益气补中，调和诸药；合白芍缓急止痛。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>huo_xiang_zheng_qi_san</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>藿香正气散</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>外感风寒，内伤湿滞</t>
-        </is>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>tai_ping_hui_min_he_ji_ju_fang</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>藿香正气散
-【出处】《太平惠民和剂局方》
-【功效】解表散寒，化湿和中，理气止呕
-【主治】外感风寒，内伤湿滞
-【组成】
-君：藿香 五钱
-臣：苏叶 三钱，白芷 三钱，半夏 四钱，厚朴 四钱
-佐：白术 四钱，苍术 四钱，陈皮 三钱，茯苓 五钱，大腹皮 五钱 ，桔梗 二钱
-使：甘草 二钱，生姜 二钱，大枣 二钱
-【配伍】
-藿香：芳香化湿、和中止呕，兼解表散寒，表里兼顾。
-紫苏、白芷：解表散寒、化湿辟秽，助藿香散外感风寒。
-陈皮、半夏、厚朴、大腹皮：理气燥湿、消胀除满、降逆止呕；
-白术、苍术、 茯苓：健脾祛湿、实脾止泻；
-桔梗：宣利肺气、载药上行。
-炙甘草、姜枣：调和脾胃，益气和中，调和诸药。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>bu_fei_tang</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>补肺汤</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>肺气虚</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>bei_ji_qian_jin_yao_fang</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>补肺汤
-【出处】《备急千金要方》
-【功效】补肺益气，止咳平喘
-【主治】肺气虚
-【组成】
-君：人参 三钱，黄芪 五钱
-臣：熟地黄 五钱
-佐：五味子 二钱，紫菀 三钱，桑白皮 三钱
-使：
-【配伍】
-人参、黄芪：大补肺气、固表益气，补益肺气虚之本。
-熟地黄：滋肾填精，金水相生，助肺气之源。
-五味子：收敛肺气、敛汗止喘，固表止自汗。
-紫菀、桑白皮：降肺气、化痰止咳，清润不燥，补虚不滞。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>huang_lian_wen_dan_tang</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>黄连温胆汤</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>痰火扰心</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>bei_ji_qian_jin_yao_fang</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>黄连温胆汤
-【出处】《备急千金要方》
-【功效】清热化痰，和中安神
-【主治】痰火扰心
-【组成】
-君：黄连 三钱
-臣：半夏 四钱，竹茹 五钱
-佐：陈皮 四钱，枳实 四钱，茯苓 四钱
-使：甘草 二钱，生姜 一钱，大枣 一钱
-【配伍】
-黄连：苦寒直折，清心泻火、燥湿清热，专清痰火。
-半夏：燥湿化痰；
-竹茹：清热化痰、除烦安神。
-陈皮：理气化痰；
-枳实：破气消痞、导痰下行；
-茯苓：健脾渗湿，绝生痰之源。
-甘草:调和诸药，和中缓急。
-生姜：和胃止呕，制半夏之毒
-大枣：益气补中，调和脾胃</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>yi_yi_ren_tang</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>薏苡仁汤</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>着痹</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>薏苡仁汤
-【出处】《太医院经验奇效良方大全》
-【功效】除湿通络，祛风散寒
-【主治】着痹（湿痹）
-【组成】
-君：薏苡仁 一两
-臣：羌活 三钱，独活 三钱，麻黄 三钱，桂枝 三钱
-佐：当归 二钱，川芎 二钱
-使：甘草 三钱
-【配伍】
-薏苡仁：利水渗湿、健脾除痹、舒筋缓急，专治湿痹重着。
-羌活、独活：祛风胜湿、通络止痛，上下分治周身湿邪
-麻、桂：温经散寒、通阳通络，助祛湿
-当归、川芎：养血活血、通络止痛，治风先治血、血行风自灭
-甘草：调和诸药，温散助祛湿。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>di_tan_tang</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>涤痰汤</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>痰迷心窍</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>涤痰汤
-【出处】《太医院经验奇效良方大全》
-【功效】涤痰开窍，益气扶正
-【主治】痰迷心窍
-【组成】
-君：半夏 二钱五分，胆南星 二钱五分
-臣：枳实 二钱，陈皮 一分五钱
-佐：竹茹 一钱，茯苓 二钱，石菖蒲 一钱，人参 一钱
-使：生姜 一钱，甘草 一钱
-【配伍】
-半夏、陈皮：燥湿化痰、理气和胃，直祛痰湿之本。
-胆南星：清气化痰，助半夏化痰之力
-枳实、竹茹：清热化痰、破气开郁，降逆涤痰。
-石菖蒲：豁痰开窍、交通心肾、醒神益智；
-茯苓：健脾渗湿，杜绝生痰之源；
-人参：益气扶正，扶助正气以运痰。
-甘草、生姜：调和诸药，益气和中，制胆南星、半夏之毒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>chai_hu_shu_gan_san</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>柴胡疏肝散</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>肝气郁结</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>jing_yue_quan_shu</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>柴胡疏肝散
-【出处】《景岳全书》
-【功效】疏肝解郁，行气止痛
-【主治】肝气郁结
-【组成】君：柴胡 二钱
-臣：香附 一钱五分钱，川芎 一钱五分
-佐：陈皮 二钱，枳壳 一钱五分，白芍 一钱五分
-使：甘草 五分
-【配伍】
-柴胡：疏肝解郁、调畅气机，直入肝胆疏泄郁滞。
-香附:理气疏肝、止痛；
-川芎:行气活血、通络止痛。
-枳壳、陈皮:理气行滞、宽胸除胀；
-白芍:柔肝缓急、养阴和营，防理气药耗伤肝阴。
-炙甘草:调和诸药，配白芍酸甘化阴、缓急止痛。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>nuan_gan_jian</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>暖肝煎</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>寒滞肝脉</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>jing_yue_quan_shu</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>暖肝煎
-【出处】《景岳全书》
-【功效】温补肝肾，行气散寒
-【主治】寒滞肝脉
-【组成】
-君：肉桂 一钱，茴香 二钱
-臣：当归 二钱，枸杞子 三钱
-佐：乌药 二钱，茯苓 二钱，沉香 一钱
-使：生姜 一钱
-【配伍】
-肉桂：温肾暖肝、散寒止痛；
-茴香：暖肝理气、专治寒疝睾丸冷痛。
-当归、枸杞：养血补肝、温补肝肾，扶正固本。
-乌药：行气散寒、疏肝止痛；
-沉香：降气暖肝、下气止痛；
-茯苓：健脾渗湿，助肝肾气化。
-生姜：散寒和胃，辅助中焦</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>zuo_gui_wan</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>左归丸</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>肾精不足</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>jing_yue_quan_shu</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>左归丸
-【出处】《景岳全书》
-【功效】滋阴补肾，填精益髓
-【主治】肾精不足
-【组成】
-君：熟地黄 八钱
-臣：龟板胶 四钱，鹿角胶 四钱，枸杞子 四钱，菟丝子 四钱
-佐：山茱萸 四钱，山药 四钱
-使：牛膝 三钱
-【配伍】
-熟地黄：大补真阴、填精补髓。
-山药、枸杞、山茱萸：滋补肝肾、养阴固精，助熟地滋补肾精。
-龟鹿二胶：峻补精血、阴阳双补、侧重填髓
-菟丝子：补肾益精
-川牛膝：补肝肾、强筋骨、引药下行</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>dao_chi_san</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>导赤散</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>心火亢盛</t>
-        </is>
-      </c>
-      <c r="D34" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>xiao_er_yao_zheng_zhi_jue</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>导赤散
-【出处】《小儿药证直决》
-【功效】清心利水养阴
-【主治】心火亢盛
-【组成】
-君：生地黄 二钱，木通 二钱
-臣：竹叶 二钱
-佐：甘草 二钱
-使：
-【配伍】
-生地黄：凉血滋阴、清心降火，养阴以制心火。
-木通：清心泻火、利水通淋，导心火从小便而出。
-竹叶：清心除烦、淡渗利水，助木通清心导赤。
-生甘草：梢清热解毒、直达茎中，缓尿痛、调和诸药。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>liu_wei_di_huang_wan</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>六味地黄丸</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>肾阴虚</t>
-        </is>
-      </c>
-      <c r="D35" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>xiao_er_yao_zheng_zhi_jue</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>六味地黄丸
-【出处】《金匮要略》
-【功效】滋阴补肾
-【主治】肾阴虚
-【组成】
-君：熟地黄 八钱
-臣：山茱萸 四钱，山药 四钱
-佐：泽泻 三钱，茯苓 三钱，丹皮 三钱
-使：
-【配伍】
-熟地黄：重用滋阴补肾、填精益髓。
-萸肉：补肝肾、敛精气；
-山药：补脾益肾、固涩下焦。
-泽泻：泻肾浊、防熟地滋腻；
-丹皮：清泻虚火、凉血除蒸；
-茯苓：健脾渗湿、助山药补脾。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>qing_qi_hua_tan_wan</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>清气化痰丸</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>痰热壅肺</t>
-        </is>
-      </c>
-      <c r="D36" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>yi_fang_kao</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>清气化痰丸
-【出处】《医方考》
-【功效】清热化痰，理气止咳
-【主治】痰热壅肺
-【组成】
-君：胆南星 一两五钱
-臣：半夏 一两五钱，瓜蒌仁 一两，黄芩 一两
-佐：杏仁 一两，陈皮 一两，枳实 一两，茯苓 一两
-使：生姜 三两
-【配伍】
-胆南星：清热化痰，专治痰热壅肺。
-瓜蒌仁：清热化痰、润肺下气、宽胸散结；
-黄芩：清泻肺火，助南星清化痰热。
-杏仁、半夏：降利肺气、化痰止咳
-陈皮、枳实：理气破结，气顺痰自消
-茯苓：健脾渗湿，杜绝生痰之源
-生姜：制胆南星、半夏之毒</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>gou_teng_san</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>钩藤散</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>肝阳上亢</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>pu_ji_ben_shi_fang</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>钩藤散
-【出处】《普济本事方》
-【功效】平肝息风，清热化痰，益气养阴
-【主治】肝阳上亢
-【组成】
-君：钩藤 三钱，菊花 三钱
-臣：防风 三钱，石膏 三钱
-佐：茯苓 三钱，半夏 三钱，陈皮 三钱，人参 三钱
-使：甘草 三钱
-【配伍】
-钩藤、菊花：平肝息风、清利头目
-石膏：清热泻火、除烦止晕
-防风：祛风解痉、载药上行
-半夏、陈皮、茯苓：燥湿化痰、和胃降逆
-麦冬、人参：益气养阴、扶正固本
-茯神：宁心安神
-炙甘草、生姜+调和诸药、和胃止呕、制半夏之毒</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>long_dan_xie_gan_tang</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>龙胆泻肝汤</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>肝火上炎</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>lan_shi_mi_cang</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>龙胆泻肝汤
-【出处】《兰室秘藏》
-【功效】清泻肝胆实火，清利肝经湿热
-【主治】肝火上炎
-【组成】
-君：龙胆草 二钱
-臣：黄芩 三钱，栀子 三钱
-佐：泽泻四钱，木通三钱，车前子 三钱，当归 三钱，生地黄 六钱，柴胡 三钱
-使：甘草 二钱
-【配伍】
-龙胆草：大苦大寒，直泻肝胆实火、清利下焦湿热。
-黄芩、栀子：苦寒泻火，清热燥湿，助龙胆草清泻肝火。
-泽泻、木通、车前子：清热利湿，导湿热从小便而去；
-生地黄、当归：滋阴养血，防苦寒药燥烈伤阴；
-柴胡：疏肝引经，畅达肝胆气机。
-生甘草清热解毒、调和诸药，护胃安中。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>yi_guan_jian</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>一贯煎</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>肝阴虚</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>liu_zhou_yi_hua</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>一贯煎
-【出处】《柳州医话》
-【功效】滋阴疏肝
-【主治】肝阴虚
-【组成】
-君：生地黄 一两
-臣：枸杞子 六钱，沙参 三钱，麦门冬 三钱，当归 三钱
-佐：川楝子 一钱五分
-使：
-【配伍】
-生地黄：重用滋阴养血、补益肝肾，直补肝阴之本。
-枸杞：滋补肝肾、填精养阴；
-当归：养血柔肝、濡养经脉。
-北沙参、麦冬：养阴生津、润肺养胃，滋水以涵木；
-川楝子：苦寒疏肝泄热、行气止痛，疏肝而不伤阴。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>gui_pi_tang</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>归脾汤</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>心脾两虚</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>yan_shi_ji_sheng_fang</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>归脾汤
-【出处】《严氏济生方》
-【功效】益气补血，健脾养心
-【主治】心脾两虚
-【组成】
-君：黄芪 一两，人参 五钱
-臣：龙眼 五钱，白术 五钱，当归 五钱，酸枣仁 六钱
-佐：茯神 五钱，远志 三钱，木香 二钱
-使：甘草 二钱，生姜 一钱，大枣 一钱
-【配伍】
-黄芪、人参：大补脾气，益气生血。
-当归、龙眼：肉养血补心、安神。
-白术：助健脾；
-酸枣仁、茯神：宁心安神；
-远志：安神益智、交通心肾；
-木香：理气醒脾，防滋补壅滞碍胃。
-炙甘草、姜枣：益气和中、调和诸药，助脾胃生化气血。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>yang_xin_tang</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>养心汤</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>心气虚</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>ren_zhai_zhi_zhi_fang_lun</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>养心汤
-【出处】《仁斋直指方论》
-【功效】益气补血，养心安神
-【主治】心气虚
-【组成】
-君：黄芪 五钱，人参 三钱
-臣：当归 五钱，茯神 五钱，茯苓 五钱
-佐：酸枣仁 三钱，柏子仁 三钱，远志 三钱，五味子 三钱，川芎 五钱，半夏 五钱，肉桂 三钱
-使：甘草 四钱，生姜 一钱，大枣 一钱
-【配伍】
-人参、黄芪：大补心气，固元益气，直补心气之本。
-当归、川芎：养血和营，气阴双补，气血互生。
-茯苓、茯神：健脾宁心、安神定悸
-枣仁、柏子仁、远志、五味子：养心安神、敛心止汗、交通心肾
-半夏：和胃化痰，防滋补壅滞
-肉桂：少佐温通，助心阳以鼓心气
-炙甘草、生姜、大枣：益气和中，调和诸药，制半夏之毒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>yu_ping_feng_san</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>玉屏风散</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>卫气虚</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>jiu_yuan_fang</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>玉屏风散
-【出处】《究原方》
-【功效】益气固表，止汗御风
-【主治】卫气虚
-【组成】
-君：黄芪  一两
-臣：白术 一两
-佐：防风 五钱
-使：
-【配伍】
-黄芪：大补肺脾之气，固表实卫、益气止汗。
-白术：健脾益气，助黄芪培补元气、固护肌表。
-防风：走肌表、疏散风邪，固表不留邪、祛风不伤正。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>jin_suo_gu_jing_wan</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>金锁固精丸</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>肾气不固</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>yi_fang_ji_jie</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>金锁固精丸
-【出处】《医方集解》
-【功效】补肾涩精，固摄肾气
-【主治】肾气不固
-【组成】
-君：蒺藜 五钱
-臣：芡实 五钱
-佐：龙骨 五钱，牡蛎 五钱，莲须 三钱
-使：莲子 三两
-【配伍】
-沙苑蒺藜：补肾益精、平补肝肾，固本培元。
-芡实+健脾益肾、固涩精气。
-莲须：专涩精；
-龙骨、牡蛎：重镇收敛、固涩滑脱。
-莲子：养心安神，补肾涩精，制丸药赋型</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>ren_shen_ge_jie_san</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>人参蛤蚧散</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>肾不纳气</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>wang_shi_bo_ji_fang</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>人参蛤蚧散
-【出处】《博济方》
-【功效】补肺益肾，纳气定喘，止咳化痰
-【主治】肾不纳气
-【组成】
-君：蛤蚧 五钱，人参 四钱
-臣：知母 三钱，贝母 三钱，桑白皮 三钱
-佐：茯苓 四钱，杏仁 四钱
-使：甘草 三钱
-【配伍】
-蛤蚧：补肺益肾、温肾纳气、定喘止嗽，专治肾不纳气虚喘。
-人参：大补元气、补益肺气，助蛤蚧固本益气。
-杏仁、贝母：润肺化痰、降气止咳
-桑白皮、知母：清泻肺热、润燥止咳
-茯苓：健脾渗湿、杜绝生痰之源
-炙甘草：益气和中，调和诸药。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="28" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="28" t="n"/>
-    </row>
-    <row r="47"/>
-    <row r="48" ht="15" customHeight="1">
-      <c r="D48" s="28" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="D49" s="28" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="D50" s="28" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="D51" s="28" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="D52" s="28" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="D53" s="28" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="D54" s="28" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="D55" s="28" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="D56" s="28" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="D57" s="28" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="D58" s="28" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="D59" s="28" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="D60" s="28" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="D61" s="28" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="D62" s="28" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="D63" s="28" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="D64" s="28" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="D65" s="28" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="D66" s="28" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="D67" s="28" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="D68" s="28" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="D69" s="28" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="D70" s="28" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="D71" s="28" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="D72" s="28" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="D73" s="28" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="D74" s="28" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="D75" s="28" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="D76" s="28" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="D77" s="28" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="D78" s="28" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="D79" s="28" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="D80" s="28" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="D81" s="28" t="n"/>
-    </row>
-    <row r="82"/>
-    <row r="83" ht="15" customHeight="1">
-      <c r="D83" s="28" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="D84" s="28" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="D85" s="28" t="n"/>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="D86" s="28" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="D87" s="28" t="n"/>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="D88" s="28" t="n"/>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="D89" s="28" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="D90" s="28" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="D91" s="28" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="D92" s="28" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="D93" s="28" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="D94" s="28" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="D95" s="28" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="D96" s="28" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="D97" s="28" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="D98" s="28" t="n"/>
-    </row>
-    <row r="99"/>
-    <row r="100" ht="15" customHeight="1">
-      <c r="D100" s="28" t="n"/>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="D101" s="28" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="D102" s="28" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="D103" s="28" t="n"/>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="D104" s="28" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="D105" s="28" t="n"/>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="D106" s="28" t="n"/>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="D107" s="28" t="n"/>
-    </row>
-    <row r="108"/>
-    <row r="109" ht="15" customHeight="1">
-      <c r="D109" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16643,7 +16697,7 @@
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
     <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
     <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="6.625" customWidth="1" style="7" min="7" max="7"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
     <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
     <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
     <col width="15.125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
@@ -16680,9 +16734,9 @@
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
-        <is>
-          <t>unlock required experie</t>
+      <c r="G1" s="53" t="inlineStr">
+        <is>
+          <t>Experience</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -23745,33 +23799,33 @@
     <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BookID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BookName</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>BookType</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SortIndex</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DetailText</t>
         </is>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,16 +18,16 @@
     <sheet name="Theory" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -91,13 +91,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="Noto Sans JP"/>
       <charset val="134"/>
       <family val="3"/>
@@ -105,10 +98,10 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <family val="3"/>
-      <sz val="6"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -195,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -286,20 +279,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -309,10 +295,13 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="163">
     <dxf>
@@ -2286,12 +2275,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="4.625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.3984375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.265625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2310,7 +2299,7 @@
           <t>Gender</t>
         </is>
       </c>
-      <c r="D1" s="48" t="inlineStr">
+      <c r="D1" s="46" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
@@ -2333,16 +2322,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TheoryID</t>
@@ -2353,7 +2342,7 @@
           <t>TheoryName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -2555,79 +2544,79 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="10.875" customWidth="1" style="46" min="1" max="1"/>
+    <col width="10.86328125" customWidth="1" style="45" min="1" max="1"/>
     <col width="20" customWidth="1" style="42" min="2" max="2"/>
-    <col width="14.375" bestFit="1" customWidth="1" style="42" min="3" max="3"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="42" min="3" max="3"/>
     <col width="11" customWidth="1" style="42" min="4" max="4"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
-    <col width="15.375" customWidth="1" style="42" min="6" max="6"/>
-    <col width="10.25" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="42" min="8" max="8"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
+    <col width="15.3984375" customWidth="1" style="42" min="6" max="6"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="42" min="8" max="8"/>
     <col width="34" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
     <col width="11" customWidth="1" style="42" min="10" max="10"/>
-    <col width="9" customWidth="1" style="42" min="11" max="17"/>
-    <col width="9" customWidth="1" style="42" min="18" max="16384"/>
+    <col width="9" customWidth="1" style="42" min="11" max="20"/>
+    <col width="9" customWidth="1" style="42" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>TriggerScene</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>TriggerDay</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Reputation</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>EntryId</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="47" t="inlineStr">
         <is>
           <t>PlayOnce</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="47" t="inlineStr">
         <is>
           <t>ReturnScene</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="I1" s="47" t="inlineStr">
         <is>
           <t>BackgroundPath</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="47" t="inlineStr">
         <is>
           <t>SortIndex</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t>落榜</t>
         </is>
@@ -2649,38 +2638,64 @@
       </c>
       <c r="H2" s="43" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>night</t>
         </is>
       </c>
       <c r="I2" s="43" t="n"/>
-      <c r="J2" s="43" t="n"/>
+      <c r="J2" s="43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="n"/>
-      <c r="B3" s="43" t="n"/>
-      <c r="C3" s="43" t="n"/>
-      <c r="D3" s="43" t="n"/>
-      <c r="E3" s="43" t="n"/>
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="43" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" s="43" t="n"/>
-      <c r="G3" s="43" t="n"/>
-      <c r="H3" s="43" t="n"/>
+      <c r="G3" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="43" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
       <c r="I3" s="43" t="n"/>
-      <c r="J3" s="43" t="n"/>
+      <c r="J3" s="43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="n"/>
+      <c r="A4" s="44" t="n"/>
       <c r="B4" s="43" t="n"/>
       <c r="C4" s="43" t="n"/>
       <c r="D4" s="43" t="n"/>
       <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
+      <c r="F4" s="51" t="n"/>
       <c r="G4" s="43" t="n"/>
       <c r="H4" s="43" t="n"/>
       <c r="I4" s="43" t="n"/>
       <c r="J4" s="43" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="n"/>
+      <c r="A5" s="44" t="n"/>
       <c r="B5" s="43" t="n"/>
       <c r="C5" s="43" t="n"/>
       <c r="D5" s="43" t="n"/>
@@ -2692,7 +2707,7 @@
       <c r="J5" s="43" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="n"/>
+      <c r="A6" s="44" t="n"/>
       <c r="B6" s="43" t="n"/>
       <c r="C6" s="43" t="n"/>
       <c r="D6" s="43" t="n"/>
@@ -2704,7 +2719,7 @@
       <c r="J6" s="43" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="n"/>
+      <c r="A7" s="44" t="n"/>
       <c r="B7" s="43" t="n"/>
       <c r="C7" s="43" t="n"/>
       <c r="D7" s="43" t="n"/>
@@ -2716,7 +2731,7 @@
       <c r="J7" s="43" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="n"/>
+      <c r="A8" s="44" t="n"/>
       <c r="B8" s="43" t="n"/>
       <c r="C8" s="43" t="n"/>
       <c r="D8" s="43" t="n"/>
@@ -2728,7 +2743,7 @@
       <c r="J8" s="43" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="n"/>
+      <c r="A9" s="44" t="n"/>
       <c r="B9" s="43" t="n"/>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
@@ -2740,7 +2755,7 @@
       <c r="J9" s="43" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="n"/>
+      <c r="A10" s="44" t="n"/>
       <c r="B10" s="43" t="n"/>
       <c r="C10" s="43" t="n"/>
       <c r="D10" s="43" t="n"/>
@@ -2752,7 +2767,7 @@
       <c r="J10" s="43" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="n"/>
+      <c r="A11" s="44" t="n"/>
       <c r="B11" s="43" t="n"/>
       <c r="C11" s="43" t="n"/>
       <c r="D11" s="43" t="n"/>
@@ -2764,7 +2779,7 @@
       <c r="J11" s="43" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="n"/>
+      <c r="A12" s="44" t="n"/>
       <c r="B12" s="43" t="n"/>
       <c r="C12" s="43" t="n"/>
       <c r="D12" s="43" t="n"/>
@@ -2776,7 +2791,7 @@
       <c r="J12" s="43" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="n"/>
+      <c r="A13" s="44" t="n"/>
       <c r="B13" s="43" t="n"/>
       <c r="C13" s="43" t="n"/>
       <c r="D13" s="43" t="n"/>
@@ -2788,7 +2803,7 @@
       <c r="J13" s="43" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="n"/>
+      <c r="A14" s="44" t="n"/>
       <c r="B14" s="43" t="n"/>
       <c r="C14" s="43" t="n"/>
       <c r="D14" s="43" t="n"/>
@@ -2800,7 +2815,7 @@
       <c r="J14" s="43" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="n"/>
+      <c r="A15" s="44" t="n"/>
       <c r="B15" s="43" t="n"/>
       <c r="C15" s="43" t="n"/>
       <c r="D15" s="43" t="n"/>
@@ -2812,7 +2827,7 @@
       <c r="J15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
+      <c r="A16" s="44" t="n"/>
       <c r="B16" s="43" t="n"/>
       <c r="C16" s="43" t="n"/>
       <c r="D16" s="43" t="n"/>
@@ -2824,7 +2839,7 @@
       <c r="J16" s="43" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="n"/>
+      <c r="A17" s="44" t="n"/>
       <c r="B17" s="43" t="n"/>
       <c r="C17" s="43" t="n"/>
       <c r="D17" s="43" t="n"/>
@@ -2836,7 +2851,7 @@
       <c r="J17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="n"/>
+      <c r="A18" s="44" t="n"/>
       <c r="B18" s="43" t="n"/>
       <c r="C18" s="43" t="n"/>
       <c r="D18" s="43" t="n"/>
@@ -2848,7 +2863,7 @@
       <c r="J18" s="43" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="n"/>
+      <c r="A19" s="44" t="n"/>
       <c r="B19" s="43" t="n"/>
       <c r="C19" s="43" t="n"/>
       <c r="D19" s="43" t="n"/>
@@ -2860,7 +2875,7 @@
       <c r="J19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="n"/>
+      <c r="A20" s="44" t="n"/>
       <c r="B20" s="43" t="n"/>
       <c r="C20" s="43" t="n"/>
       <c r="D20" s="43" t="n"/>
@@ -2882,58 +2897,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="12.375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
-    <col width="41.625" customWidth="1" style="35" min="8" max="8"/>
-    <col width="9" customWidth="1" style="42" min="9" max="14"/>
-    <col width="9" customWidth="1" style="42" min="15" max="16384"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
+    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
+    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
+    <col width="9" customWidth="1" style="42" min="9" max="17"/>
+    <col width="9" customWidth="1" style="42" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>LineIndex</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="47" t="inlineStr">
         <is>
           <t>LineType</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="47" t="inlineStr">
         <is>
           <t>Speaker</t>
         </is>
       </c>
-      <c r="F1" s="51" t="inlineStr">
+      <c r="F1" s="48" t="inlineStr">
         <is>
           <t>PortraitSide</t>
         </is>
       </c>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="G1" s="48" t="inlineStr">
         <is>
           <t>PortraitPath</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="47" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -3392,6 +3407,166 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>李东壁十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁便下定决心开始随父亲学医。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>东壁啊，白天教你的都听明白了吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>平常日子里看您治病，其实已经窥探得些门道了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>学医最要紧的是积累，吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>哇，太好了！</t>
         </is>
       </c>
     </row>
@@ -3408,14 +3583,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -3429,7 +3604,7 @@
           <t>DiseaseName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -5172,13 +5347,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5193,7 +5368,7 @@
           <t>FormulaName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -7319,33 +7494,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="48"/>
-    <col width="9" customWidth="1" style="9" min="49" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="51"/>
+    <col width="9" customWidth="1" style="9" min="52" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -8094,14 +8269,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F306"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16689,18 +16864,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16734,7 +16909,7 @@
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G1" s="53" t="inlineStr">
+      <c r="G1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -23789,17 +23964,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BookID</t>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,7 +29,7 @@
   <numFmts count="0"/>
   <fonts count="12">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -100,19 +100,19 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Noto Sans JP"/>
       <charset val="134"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -320,10 +320,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -337,7 +337,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2300,19 +2300,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
+  <dimension ref="A1:I71"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
-    <col width="9.75" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
-    <col width="8.25" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
-    <col width="4.625" bestFit="1" customWidth="1" style="24" min="5" max="5"/>
-    <col width="23.125" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
-    <col width="25.125" bestFit="1" customWidth="1" style="24" min="7" max="7"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="24" min="8" max="8"/>
-    <col width="33.375" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="24" min="10" max="16384"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="9.73046875" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="8.265625" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" style="24" min="5" max="5"/>
+    <col width="23.1328125" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
+    <col width="25.1328125" bestFit="1" customWidth="1" style="24" min="7" max="7"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="24" min="8" max="8"/>
+    <col width="33.3984375" bestFit="1" customWidth="1" style="24" min="9" max="9"/>
+    <col width="9.1328125" customWidth="1" style="24" min="10" max="13"/>
+    <col width="9.1328125" customWidth="1" style="24" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -2365,17 +2366,17 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>wang_wu</t>
+          <t>shen_xiu_wen</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>沈修文</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -2384,88 +2385,56 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>大夫，我这两天</t>
-        </is>
-      </c>
-      <c r="G2" s="49" t="inlineStr">
-        <is>
-          <t>给我看看吧。</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>多谢大夫，感觉好多了。</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>还是好难受啊…</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>wang_da_sao</t>
+          <t>lei_wan_jun</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>王大嫂</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>先生，俺这两天</t>
-        </is>
-      </c>
-      <c r="G3" s="49" t="inlineStr">
-        <is>
-          <t>您帮俺瞧瞧吧。</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>麻烦先生了，我感觉好多了</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>哎哟...哎哟…</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>wang_chao_feng</t>
+          <t>chen_pi</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>王朝奉</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -2474,43 +2443,27 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>咳咳，我最近</t>
-        </is>
-      </c>
-      <c r="G4" s="49" t="inlineStr">
-        <is>
-          <t>您帮老夫瞧瞧吧。</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>好多了，多谢大夫。</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>你给我开的什么药啊…</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>wang_lao_an_ren</t>
+          <t>ban_xia</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>王老安人</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2519,43 +2472,27 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>先生，老妇这两天</t>
-        </is>
-      </c>
-      <c r="G5" s="49" t="inlineStr">
-        <is>
-          <t>劳烦您给我看看。</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>真是多谢先生了，好多了</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>咳咳咳，哎哟...</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>huang_niu_er</t>
+          <t>yang_shan_quan</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>黄牛儿</t>
+          <t>杨善泉</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2564,43 +2501,27 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>哎哟大夫，我</t>
-        </is>
-      </c>
-      <c r="G6" s="49" t="inlineStr">
-        <is>
-          <t>快给我看看吧。</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>真是太谢谢大夫了。</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>感觉不太对啊…</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>huang_qiu_ju</t>
+          <t>yang_su_niang</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>黄秋菊</t>
+          <t>杨素娘</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2609,43 +2530,27 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>我这两天</t>
-        </is>
-      </c>
-      <c r="G7" s="49" t="inlineStr">
-        <is>
-          <t>请您给小女看看吧。</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>多谢先生，我好多了。</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>还是好难受啊…</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>he_zhang_shao</t>
+          <t>jia_quan</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>何掌勺</t>
+          <t>贾荃</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2654,43 +2559,27 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>先生，我最近</t>
-        </is>
-      </c>
-      <c r="G8" s="49" t="inlineStr">
-        <is>
-          <t>大夫快给我看看吧。</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>多谢先生了。</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>还是好难受啊…</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>hua_yun</t>
+          <t>wu_shi_liang</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>花芸</t>
+          <t>吴世良</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2699,43 +2588,27 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>先生，小可这几日</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="inlineStr">
-        <is>
-          <t>劳烦您给看看。</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>有劳先生了，感觉好多了。</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>哎哟…感觉更难受了…</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>zhou_lu_an</t>
+          <t>cao_wang</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>周炉安</t>
+          <t>曹旺</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2744,43 +2617,27 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>先生，我这几天</t>
-        </is>
-      </c>
-      <c r="G10" s="49" t="inlineStr">
-        <is>
-          <t>麻烦您给我看看。</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>多谢先生了。</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>先生，我这病怎么还不见好？</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>jiang_chuan_er</t>
+          <t>chu_gong_wang</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>蒋船儿</t>
+          <t>楚恭王</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2789,88 +2646,56 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>大夫，我这几天</t>
-        </is>
-      </c>
-      <c r="G11" s="49" t="inlineStr">
-        <is>
-          <t>给我看看吧。</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>多谢先生，我好多了。</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>嗯…哎哟…</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>qin_san_niang</t>
+          <t>gu_ri_yan</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>秦三娘</t>
+          <t>顾日岩</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>咳咳，大夫，我这几日</t>
-        </is>
-      </c>
-      <c r="G12" s="49" t="inlineStr">
-        <is>
-          <t>劳烦您给我看看。</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>多谢先生，感觉好多了。</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>哎哟...哎哟…</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>shi_gan</t>
+          <t>li_shi_zhen</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>石敢</t>
+          <t>李时珍</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2879,43 +2704,27 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>咳咳，先生我这两天</t>
-        </is>
-      </c>
-      <c r="G13" s="49" t="inlineStr">
-        <is>
-          <t>您快帮我看看吧。</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>哎呀，真是太感谢了，好多了。</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>哎…奇怪…</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>cha_bo_shi</t>
+          <t>li_yan_wen</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>茶博士</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2924,38 +2733,22 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>我最近几日</t>
-        </is>
-      </c>
-      <c r="G14" s="49" t="inlineStr">
-        <is>
-          <t>劳烦先生给小可看看。</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>哎呀，真是多谢先生了。</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>感觉更不舒服了…</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>shen_xiu_wen</t>
+          <t>wu_zhi_lan</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>沈修文</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2965,42 +2758,26 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>小可这几日</t>
-        </is>
-      </c>
-      <c r="G15" s="49" t="inlineStr">
-        <is>
-          <t>劳烦先生给我看看。</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>有劳先生了，感觉好多了。</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>您给我开的这是什么药啊…</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>shen_gui</t>
+          <t>wang_wu</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>沈贵</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -3014,83 +2791,83 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>哎哟哟，我</t>
+          <t>大夫，我这两天</t>
         </is>
       </c>
       <c r="G16" s="49" t="inlineStr">
         <is>
-          <t>快给我看看吧。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>多谢多谢。</t>
+          <t>多谢大夫，感觉好多了。</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>你会不会看病啊？</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>lei_wan_jun</t>
+          <t>wang_da_sao</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>王大嫂</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>random</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，我这几日</t>
+          <t>先生，俺这两天</t>
         </is>
       </c>
       <c r="G17" s="49" t="inlineStr">
         <is>
-          <t>请您给我看看吧。</t>
+          <t>您帮俺瞧瞧吧。</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>感觉好多了，多谢先生。</t>
+          <t>麻烦先生了，我感觉好多了</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>你给我吃的是什么药…</t>
+          <t>哎哟...哎哟…</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>li_gou_dan</t>
+          <t>wang_chao_feng</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>李狗蛋</t>
+          <t>王朝奉</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3104,38 +2881,38 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>先生，俺这两天</t>
+          <t>咳咳，我最近</t>
         </is>
       </c>
       <c r="G18" s="49" t="inlineStr">
         <is>
-          <t>请您给俺看看吧。</t>
+          <t>您帮老夫瞧瞧吧。</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>真是太谢谢大夫了。</t>
+          <t>好多了，多谢大夫。</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>你给我开的什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>li_si</t>
+          <t>wang_lao_an_ren</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>王老安人</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -3145,42 +2922,42 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几天</t>
+          <t>先生，老妇这两天</t>
         </is>
       </c>
       <c r="G19" s="49" t="inlineStr">
         <is>
-          <t>麻烦您帮我看看吧。</t>
+          <t>劳烦您给我看看。</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我感觉好多了。</t>
+          <t>真是多谢先生了，好多了</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这病怎么还不见好？</t>
+          <t>咳咳咳，哎哟...</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>li_jiang_shi</t>
+          <t>huang_niu_er</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>李姜氏</t>
+          <t>黄牛儿</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3190,42 +2967,42 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>哎哟大夫，我</t>
         </is>
       </c>
       <c r="G20" s="49" t="inlineStr">
         <is>
-          <t>劳烦先生给我看看。</t>
+          <t>快给我看看吧。</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>先生医术真是高明，多谢了</t>
+          <t>真是太谢谢大夫了。</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>嗯？感觉好奇怪啊…</t>
+          <t>感觉不太对啊…</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>li_yuan_wai</t>
+          <t>huang_qiu_ju</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>李员外</t>
+          <t>黄秋菊</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -3235,42 +3012,42 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>小郎中啊，老夫这几日</t>
+          <t>我这两天</t>
         </is>
       </c>
       <c r="G21" s="49" t="inlineStr">
         <is>
-          <t>你给老夫瞧瞧。</t>
+          <t>请您给小女看看吧。</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>嗯，不错不错，医术高明啊。</t>
+          <t>多谢先生，我好多了。</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>你这庸医，招摇撞骗！</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>yan_po</t>
+          <t>he_zhang_shao</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>严婆</t>
+          <t>何掌勺</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -3280,42 +3057,42 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>先生，老妇这两天</t>
+          <t>先生，我最近</t>
         </is>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>大夫快给我看看吧。</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>感觉好多了，多谢先生。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，哎哟...</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>feng_jun_bao</t>
+          <t>hua_yun</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>冯军保</t>
+          <t>花芸</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -3329,38 +3106,38 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>先生，小可这几日</t>
         </is>
       </c>
       <c r="G23" s="49" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>劳烦您给看看。</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>有劳先生了，感觉好多了。</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>哎哟…感觉更难受了…</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>liu_tai_gong</t>
+          <t>zhou_lu_an</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>刘太公</t>
+          <t>周炉安</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -3374,11 +3151,11 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>先生啊，老朽这几日</t>
+          <t>先生，我这几天</t>
         </is>
       </c>
       <c r="G24" s="49" t="inlineStr">
@@ -3388,24 +3165,24 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>麻烦大夫啦，好多了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，哎哟…</t>
+          <t>先生，我这病怎么还不见好？</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>liu_da</t>
+          <t>jiang_chuan_er</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>刘大</t>
+          <t>蒋船儿</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -3419,38 +3196,38 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>大夫，俺这两天</t>
+          <t>大夫，我这几天</t>
         </is>
       </c>
       <c r="G25" s="49" t="inlineStr">
         <is>
-          <t>麻烦您帮俺看看吧。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>多谢大夫，感觉好多了。</t>
+          <t>多谢先生，我好多了。</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>感觉不太对啊…</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>liu_wen_po</t>
+          <t>qin_san_niang</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>刘稳婆</t>
+          <t>秦三娘</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -3464,38 +3241,38 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>先生啊，俺这几天</t>
+          <t>咳咳，大夫，我这几日</t>
         </is>
       </c>
       <c r="G26" s="49" t="inlineStr">
         <is>
-          <t>请您给俺看看把。</t>
+          <t>劳烦您给我看看。</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>哎哟，谢谢先生，您真是神医啊！</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>哎，不对啊…</t>
+          <t>哎哟...哎哟…</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>hua_jin_niang</t>
+          <t>shi_gan</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>华锦娘</t>
+          <t>石敢</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3505,42 +3282,42 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>咳咳，先生我这两天</t>
         </is>
       </c>
       <c r="G27" s="49" t="inlineStr">
         <is>
-          <t>劳烦先生您给小妇看看吧。</t>
+          <t>您快帮我看看吧。</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>哎呀，真是太感谢了，好多了。</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>lv_tai_jun</t>
+          <t>cha_bo_shi</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>吕太君</t>
+          <t>茶博士</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -3550,42 +3327,42 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>小先生啊，老婆子我最近</t>
+          <t>我最近几日</t>
         </is>
       </c>
       <c r="G28" s="49" t="inlineStr">
         <is>
-          <t>您给我瞧瞧。</t>
+          <t>劳烦先生给小可看看。</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>多谢小先生，老婆子我好多啦。</t>
+          <t>哎呀，真是多谢先生了。</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，你这开的是什么药啊？</t>
+          <t>感觉更不舒服了…</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>wu_ban_tou</t>
+          <t>shen_gui</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>吴班头</t>
+          <t>沈贵</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -3599,38 +3376,38 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>哎哟哟，我</t>
         </is>
       </c>
       <c r="G29" s="49" t="inlineStr">
         <is>
-          <t>您快帮我看看吧。</t>
+          <t>快给我看看吧。</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>有劳先生了，感觉好多了。</t>
+          <t>多谢多谢。</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>他娘的，你给我吃的是什么？</t>
+          <t>你会不会看病啊？</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>sun_jiang_er</t>
+          <t>li_gou_dan</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>孙匠儿</t>
+          <t>李狗蛋</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -3644,38 +3421,38 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>先生，俺这两天</t>
         </is>
       </c>
       <c r="G30" s="49" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>请您给俺看看吧。</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>真是太谢谢大夫了。</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>呃…不对啊</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>sun_xiao_mei</t>
+          <t>li_si</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>孙小妹</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3685,11 +3462,11 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -3698,29 +3475,29 @@
       </c>
       <c r="G31" s="49" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>麻烦您帮我看看吧。</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>多谢先生，我感觉好多了。</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，好难受啊</t>
+          <t>大夫，我这病怎么还不见好？</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>zhang_san</t>
+          <t>li_jiang_shi</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>李姜氏</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3730,42 +3507,42 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这几天</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G32" s="49" t="inlineStr">
         <is>
-          <t>帮我看看吧。</t>
+          <t>劳烦先生给我看看。</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>多谢大夫，我好多了。</t>
+          <t>先生医术真是高明，多谢了</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>嗯？感觉好奇怪啊…</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>zhang_tu</t>
+          <t>li_yuan_wai</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>张屠</t>
+          <t>李员外</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -3779,38 +3556,38 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>哎哟大夫，俺</t>
+          <t>小郎中啊，老夫这几日</t>
         </is>
       </c>
       <c r="G33" s="49" t="inlineStr">
         <is>
-          <t>快给俺看看吧。</t>
+          <t>你给老夫瞧瞧。</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>哈哈哈，太谢谢了。</t>
+          <t>嗯，不错不错，医术高明啊。</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>他娘的怎么感觉怪怪的</t>
+          <t>你这庸医，招摇撞骗！</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>zhang_you_shi</t>
+          <t>yan_po</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>张尤氏</t>
+          <t>严婆</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3824,38 +3601,38 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>我最近几天</t>
+          <t>先生，老妇这两天</t>
         </is>
       </c>
       <c r="G34" s="49" t="inlineStr">
         <is>
-          <t>请先生给我看看吧</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>感觉好多了，多谢先生。</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>咳咳咳，哎哟...</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>yang_xiu_cai</t>
+          <t>feng_jun_bao</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>杨秀才</t>
+          <t>冯军保</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -3869,38 +3646,38 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>大夫，学生这几日</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G35" s="49" t="inlineStr">
         <is>
-          <t>请您给看看吧。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>有劳大夫了，我好多了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>su_xiu_he</t>
-        </is>
-      </c>
-      <c r="B36" s="52" t="inlineStr">
-        <is>
-          <t>苏绣荷</t>
+          <t>liu_tai_gong</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>刘太公</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -3910,42 +3687,42 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>先生啊，老朽这几日</t>
         </is>
       </c>
       <c r="G36" s="49" t="inlineStr">
         <is>
-          <t>麻烦您给小女子看看吧。</t>
+          <t>麻烦您给我看看。</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>好多了，真是太谢谢先生了。</t>
+          <t>麻烦大夫啦，好多了。</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，好难受啊</t>
+          <t>咳咳咳，哎哟…</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>xu_xiang_jun</t>
+          <t>liu_da</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>许香君</t>
+          <t>刘大</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -3955,42 +3732,42 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>大夫，俺这两天</t>
         </is>
       </c>
       <c r="G37" s="49" t="inlineStr">
         <is>
-          <t>烦请先生给奴家看看。</t>
+          <t>麻烦您帮俺看看吧。</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了，我好多了。</t>
+          <t>多谢大夫，感觉好多了。</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>感觉不太对啊…</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>xie_fei_yan</t>
+          <t>liu_wen_po</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>刘稳婆</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -4004,38 +3781,38 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>先生，我这两天</t>
+          <t>先生啊，俺这几天</t>
         </is>
       </c>
       <c r="G38" s="49" t="inlineStr">
         <is>
-          <t>劳烦先生给妾身看看。</t>
+          <t>请您给俺看看把。</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>感觉好多了，真是太谢谢先生了。</t>
+          <t>哎哟，谢谢先生，您真是神医啊！</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>哎哟…感觉更难受了…</t>
+          <t>哎，不对啊…</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>zhao_ya_po</t>
+          <t>liu_fu</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>赵牙婆</t>
+          <t>刘福</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -4045,42 +3822,42 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>大夫，老婆子我这几日</t>
+          <t>大夫，我最近</t>
         </is>
       </c>
       <c r="G39" s="49" t="inlineStr">
         <is>
-          <t>劳烦您给我看看。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>哎哟，谢谢先生，您真是神医啊！</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>哎，不对啊…</t>
+          <t>呃...不对啊。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>zhao_liu</t>
+          <t>hua_jin_niang</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>华锦娘</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -4090,42 +3867,42 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G40" s="49" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>劳烦先生您给小妇看看吧。</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>还是好难受啊…</t>
+          <t>您给我开的这是什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>zheng_er_jie</t>
+          <t>lv_tai_jun</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>郑二姐</t>
+          <t>吕太君</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -4139,38 +3916,38 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>小先生啊，老婆子我最近</t>
         </is>
       </c>
       <c r="G41" s="49" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>您给我瞧瞧。</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>有劳先生了，感觉好多了。</t>
+          <t>多谢小先生，老婆子我好多啦。</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>咳咳咳，你这开的是什么药啊？</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>qian_bu_lou</t>
+          <t>wu_ban_tou</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>钱不漏</t>
+          <t>吴班头</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -4184,38 +3961,38 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>我最近</t>
+          <t>先生，我最近</t>
         </is>
       </c>
       <c r="G42" s="49" t="inlineStr">
         <is>
-          <t>快快，快给我看看。</t>
+          <t>您快帮我看看吧。</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>谢啦。</t>
+          <t>有劳先生了，感觉好多了。</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>这开的是什么药，我要到官府告你！</t>
+          <t>他娘的，你给我吃的是什么？</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>chen_shan_zhang</t>
-        </is>
-      </c>
-      <c r="B43" s="52" t="inlineStr">
-        <is>
-          <t>陈山长</t>
+          <t>sun_jiang_er</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>孙匠儿</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -4229,38 +4006,38 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这几日</t>
+          <t>先生，我这几日</t>
         </is>
       </c>
       <c r="G43" s="49" t="inlineStr">
         <is>
-          <t>劳烦您给我看看。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>大夫真是妙手回春啊。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>医术不精，还敢自称郎中！</t>
+          <t>呃…不对啊</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>chen_er</t>
+          <t>sun_xiao_mei</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>陈二</t>
+          <t>孙小妹</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -4270,42 +4047,42 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>先生，我这几天</t>
         </is>
       </c>
       <c r="G44" s="49" t="inlineStr">
         <is>
-          <t>帮我看看吧。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>咳咳咳，好难受啊</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>chen_puo</t>
+          <t>zhang_san</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>陈婆</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -4315,42 +4092,42 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>先生，老婆子我这几日</t>
+          <t>大夫，我这几天</t>
         </is>
       </c>
       <c r="G45" s="49" t="inlineStr">
         <is>
-          <t>您快帮我看看吧。</t>
+          <t>帮我看看吧。</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>真是太谢谢先生了。</t>
+          <t>多谢大夫，我好多了。</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>感觉不太对啊…</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>chen_fu</t>
+          <t>zhang_tu</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>陈福</t>
+          <t>张屠</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -4364,205 +4141,613 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>大夫，我最近</t>
+          <t>哎哟大夫，俺</t>
         </is>
       </c>
       <c r="G46" s="49" t="inlineStr">
         <is>
-          <t>给我看看吧。</t>
+          <t>快给俺看看吧。</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>哈哈哈，太谢谢了。</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>呃...不对啊。</t>
+          <t>他娘的怎么感觉怪怪的</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>zhang_you_shi</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>张尤氏</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>我最近几天</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="inlineStr">
+        <is>
+          <t>请先生给我看看吧</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>多谢先生，感觉好多了。</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>嗯…哎哟…</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>yang_xiu_cai</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>杨秀才</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>大夫，学生这几日</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="inlineStr">
+        <is>
+          <t>请您给看看吧。</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>有劳大夫了，我好多了。</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>您给我开的这是什么药啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>su_xiu_he</t>
+        </is>
+      </c>
+      <c r="B49" s="52" t="inlineStr">
+        <is>
+          <t>苏绣荷</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>先生，我这几日</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>麻烦您给小女子看看吧。</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>好多了，真是太谢谢先生了。</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>咳咳咳，好难受啊</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>xu_xiang_jun</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>许香君</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>先生，我这几日</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>烦请先生给奴家看看。</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>多谢先生了，我好多了。</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>您给我开的这是什么药啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>xie_fei_yan</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>先生，我这两天</t>
+        </is>
+      </c>
+      <c r="G51" s="49" t="inlineStr">
+        <is>
+          <t>劳烦先生给妾身看看。</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>感觉好多了，真是太谢谢先生了。</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>哎哟…感觉更难受了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>zhao_ya_po</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>赵牙婆</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>大夫，老婆子我这几日</t>
+        </is>
+      </c>
+      <c r="G52" s="49" t="inlineStr">
+        <is>
+          <t>劳烦您给我看看。</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>哎哟，谢谢先生，您真是神医啊！</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>哎，不对啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>zhao_liu</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>先生，我最近</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>麻烦您给我看看。</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>多谢先生，我好多了。</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>还是好难受啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>zheng_er_jie</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>郑二姐</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>先生，我最近</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="inlineStr">
+        <is>
+          <t>麻烦您给我看看。</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>有劳先生了，感觉好多了。</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>哎…奇怪…</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>qian_bu_lou</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>钱不漏</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>我最近</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="inlineStr">
+        <is>
+          <t>快快，快给我看看。</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>谢啦。</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>这开的是什么药，我要到官府告你！</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>chen_shan_zhang</t>
+        </is>
+      </c>
+      <c r="B56" s="52" t="inlineStr">
+        <is>
+          <t>陈山长</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>大夫，我这几日</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="inlineStr">
+        <is>
+          <t>劳烦您给我看看。</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>大夫真是妙手回春啊。</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>医术不精，还敢自称郎中！</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>chen_er</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>陈二</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>先生，我最近</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
+          <t>帮我看看吧。</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>多谢先生，我好多了。</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>嗯…哎哟…</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>chen_puo</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>陈婆</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>先生，老婆子我这几日</t>
+        </is>
+      </c>
+      <c r="G58" s="49" t="inlineStr">
+        <is>
+          <t>您快帮我看看吧。</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>真是太谢谢先生了。</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>感觉不太对啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
           <t>han_zhang_gui</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>韩掌柜</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E59" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>大夫，我这两天</t>
         </is>
       </c>
-      <c r="G47" s="49" t="inlineStr">
+      <c r="G59" s="49" t="inlineStr">
         <is>
           <t>劳烦您给我看看。</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>多谢大夫啦。</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>大夫，我这病怎么还不见好？</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="49" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="49" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="49" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="49" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="49" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="7" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
-      <c r="G53" s="49" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="49" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="49" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="49" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="49" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="7" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="49" t="n"/>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="7" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="49" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="7" t="n"/>
@@ -4575,10 +4760,131 @@
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
     </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="49" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="49" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="49" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="49" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="49" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="49" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="49" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="49" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="49" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="49" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="49" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1">
-    <sortState ref="A2:I47">
-      <sortCondition ref="B1"/>
+    <sortState ref="A2:I54">
+      <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4593,13 +4899,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -4812,22 +5118,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="43" min="1" max="1"/>
-    <col width="12.375" bestFit="1" customWidth="1" style="40" min="2" max="2"/>
-    <col width="14.375" bestFit="1" customWidth="1" style="40" min="3" max="3"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="43" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="40" min="2" max="2"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="40" min="3" max="3"/>
     <col width="11" customWidth="1" style="40" min="4" max="4"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="40" min="5" max="5"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="40" min="6" max="6"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="40" min="5" max="5"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="40" min="6" max="6"/>
     <col width="11" customWidth="1" style="40" min="7" max="7"/>
-    <col width="10.25" bestFit="1" customWidth="1" style="40" min="8" max="8"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="40" min="9" max="9"/>
-    <col width="34" bestFit="1" customWidth="1" style="40" min="10" max="10"/>
-    <col width="11" customWidth="1" style="40" min="11" max="11"/>
-    <col width="9" customWidth="1" style="40" min="12" max="26"/>
-    <col width="9" customWidth="1" style="40" min="27" max="16384"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="40" min="8" max="8"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="40" min="9" max="9"/>
+    <col width="11" customWidth="1" style="40" min="10" max="10"/>
+    <col width="9" customWidth="1" style="40" min="11" max="29"/>
+    <col width="9" customWidth="1" style="40" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4878,11 +5183,6 @@
       </c>
       <c r="J1" s="44" t="inlineStr">
         <is>
-          <t>BackgroundPath</t>
-        </is>
-      </c>
-      <c r="K1" s="44" t="inlineStr">
-        <is>
           <t>SortIndex</t>
         </is>
       </c>
@@ -4919,8 +5219,7 @@
           <t>night</t>
         </is>
       </c>
-      <c r="J2" s="41" t="n"/>
-      <c r="K2" s="41" t="n">
+      <c r="J2" s="41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4956,8 +5255,7 @@
           <t>night</t>
         </is>
       </c>
-      <c r="J3" s="41" t="n"/>
-      <c r="K3" s="41" t="n">
+      <c r="J3" s="41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4993,8 +5291,7 @@
           <t>clinic</t>
         </is>
       </c>
-      <c r="J4" s="41" t="n"/>
-      <c r="K4" s="41" t="n">
+      <c r="J4" s="41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5009,7 +5306,6 @@
       <c r="H5" s="41" t="n"/>
       <c r="I5" s="41" t="n"/>
       <c r="J5" s="41" t="n"/>
-      <c r="K5" s="41" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="42" t="n"/>
@@ -5022,7 +5318,6 @@
       <c r="H6" s="41" t="n"/>
       <c r="I6" s="41" t="n"/>
       <c r="J6" s="41" t="n"/>
-      <c r="K6" s="41" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="42" t="n"/>
@@ -5035,7 +5330,6 @@
       <c r="H7" s="41" t="n"/>
       <c r="I7" s="41" t="n"/>
       <c r="J7" s="41" t="n"/>
-      <c r="K7" s="41" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="42" t="n"/>
@@ -5048,7 +5342,6 @@
       <c r="H8" s="41" t="n"/>
       <c r="I8" s="41" t="n"/>
       <c r="J8" s="41" t="n"/>
-      <c r="K8" s="41" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="42" t="n"/>
@@ -5061,7 +5354,6 @@
       <c r="H9" s="41" t="n"/>
       <c r="I9" s="41" t="n"/>
       <c r="J9" s="41" t="n"/>
-      <c r="K9" s="41" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="42" t="n"/>
@@ -5074,7 +5366,6 @@
       <c r="H10" s="41" t="n"/>
       <c r="I10" s="41" t="n"/>
       <c r="J10" s="41" t="n"/>
-      <c r="K10" s="41" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="42" t="n"/>
@@ -5087,7 +5378,6 @@
       <c r="H11" s="41" t="n"/>
       <c r="I11" s="41" t="n"/>
       <c r="J11" s="41" t="n"/>
-      <c r="K11" s="41" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="42" t="n"/>
@@ -5100,7 +5390,6 @@
       <c r="H12" s="41" t="n"/>
       <c r="I12" s="41" t="n"/>
       <c r="J12" s="41" t="n"/>
-      <c r="K12" s="41" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="42" t="n"/>
@@ -5113,7 +5402,6 @@
       <c r="H13" s="41" t="n"/>
       <c r="I13" s="41" t="n"/>
       <c r="J13" s="41" t="n"/>
-      <c r="K13" s="41" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="42" t="n"/>
@@ -5126,7 +5414,6 @@
       <c r="H14" s="41" t="n"/>
       <c r="I14" s="41" t="n"/>
       <c r="J14" s="41" t="n"/>
-      <c r="K14" s="41" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="42" t="n"/>
@@ -5139,7 +5426,6 @@
       <c r="H15" s="41" t="n"/>
       <c r="I15" s="41" t="n"/>
       <c r="J15" s="41" t="n"/>
-      <c r="K15" s="41" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="42" t="n"/>
@@ -5152,7 +5438,6 @@
       <c r="H16" s="41" t="n"/>
       <c r="I16" s="41" t="n"/>
       <c r="J16" s="41" t="n"/>
-      <c r="K16" s="41" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="42" t="n"/>
@@ -5165,7 +5450,6 @@
       <c r="H17" s="41" t="n"/>
       <c r="I17" s="41" t="n"/>
       <c r="J17" s="41" t="n"/>
-      <c r="K17" s="41" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="42" t="n"/>
@@ -5178,7 +5462,6 @@
       <c r="H18" s="41" t="n"/>
       <c r="I18" s="41" t="n"/>
       <c r="J18" s="41" t="n"/>
-      <c r="K18" s="41" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="42" t="n"/>
@@ -5191,7 +5474,6 @@
       <c r="H19" s="41" t="n"/>
       <c r="I19" s="41" t="n"/>
       <c r="J19" s="41" t="n"/>
-      <c r="K19" s="41" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="42" t="n"/>
@@ -5204,7 +5486,6 @@
       <c r="H20" s="41" t="n"/>
       <c r="I20" s="41" t="n"/>
       <c r="J20" s="41" t="n"/>
-      <c r="K20" s="41" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5218,19 +5499,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="34" min="1" max="1"/>
-    <col width="12.375" bestFit="1" customWidth="1" style="34" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="34" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="34" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="34" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="34" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" style="34" min="7" max="7"/>
-    <col width="41.625" customWidth="1" style="34" min="8" max="8"/>
-    <col width="9" customWidth="1" style="40" min="9" max="22"/>
-    <col width="9" customWidth="1" style="40" min="23" max="16384"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="34" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="34" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="34" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="34" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="34" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="34" min="6" max="6"/>
+    <col width="13.3984375" bestFit="1" customWidth="1" style="34" min="7" max="7"/>
+    <col width="43.9296875" bestFit="1" customWidth="1" style="34" min="8" max="8"/>
+    <col width="41.59765625" customWidth="1" style="34" min="9" max="9"/>
+    <col width="9" customWidth="1" style="40" min="10" max="27"/>
+    <col width="9" customWidth="1" style="40" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5271,6 +5553,11 @@
       </c>
       <c r="H1" s="44" t="inlineStr">
         <is>
+          <t>BackgroundPath</t>
+        </is>
+      </c>
+      <c r="I1" s="44" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
@@ -5299,6 +5586,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>res://Assets/Background/clinic/autumn.png</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>明嘉靖十九年，武昌府放榜处</t>
         </is>
       </c>
@@ -5324,22 +5616,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>李东壁</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>…..........</t>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>老爷，少爷，榜上没找到少爷的名字。</t>
         </is>
       </c>
     </row>
@@ -5372,12 +5661,9 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>嘶...... 又没中......</t>
         </is>
@@ -5412,12 +5698,9 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>你再仔细看看</t>
         </is>
@@ -5444,22 +5727,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>李东壁</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>爹，我看了好几遍了，确实没有我的名字…...</t>
+          <t>res://Assets/Background/clinic/autumn_night.png</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>老爷，我看了好几遍了，确实没有少爷的名字…...</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5776,9 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>考了三次都没中举，看来我不是读书的材料啊爹</t>
         </is>
@@ -5532,12 +5813,9 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>这说的是什么话，你看隔壁村那个老范，考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
         </is>
@@ -5572,12 +5850,9 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>我看我还是跟您学医吧，科举八股什么的，孩儿实在是学不来…</t>
         </is>
@@ -5612,12 +5887,9 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
         </is>
@@ -5652,12 +5924,9 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>可我真心喜欢研究那些药材方子，考证典籍。行医治病才是儿子此生志愿。</t>
         </is>
@@ -5692,12 +5961,9 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢。东壁呀，你若真的想从医，今日起便随为父从《内经》，《本草》学起吧。</t>
         </is>
@@ -5725,9 +5991,10 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>李东壁十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁便下定决心开始随父亲学医。</t>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>李东壁十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁决定开始随父亲学医。</t>
         </is>
       </c>
     </row>
@@ -5760,12 +6027,13 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/clinic/autumn.png</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>东壁啊，白天教你的都听明白了吗？</t>
         </is>
@@ -5800,12 +6068,9 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>嗯，都明白了，平常日子里看您治病，其实已经窥探得些门道了。</t>
         </is>
@@ -5840,12 +6105,9 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>学医最要紧的是积累，吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊。</t>
         </is>
@@ -5880,18 +6142,15 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>哇，太好了！</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>003</t>
@@ -5920,12 +6179,13 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/clinic/autumn.png</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>从今天起，你就正式开始给病患诊断开药。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。好了，病人已经在等着你了，快去吧。</t>
         </is>
@@ -5944,17 +6204,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F111"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DiseaseID</t>
@@ -7670,191 +7930,191 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15" customHeight="1">
       <c r="C47" s="27" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15" customHeight="1">
       <c r="C48" s="27" t="n"/>
     </row>
     <row r="49"/>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="C50" s="27" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15" customHeight="1">
       <c r="C51" s="27" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15" customHeight="1">
       <c r="C52" s="27" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15" customHeight="1">
       <c r="C53" s="27" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15" customHeight="1">
       <c r="C54" s="27" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15" customHeight="1">
       <c r="C55" s="27" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15" customHeight="1">
       <c r="C56" s="27" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15" customHeight="1">
       <c r="C57" s="27" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15" customHeight="1">
       <c r="C58" s="27" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15" customHeight="1">
       <c r="C59" s="27" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15" customHeight="1">
       <c r="C60" s="27" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15" customHeight="1">
       <c r="C61" s="27" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15" customHeight="1">
       <c r="C62" s="27" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15" customHeight="1">
       <c r="C63" s="27" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15" customHeight="1">
       <c r="C64" s="27" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15" customHeight="1">
       <c r="C65" s="27" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15" customHeight="1">
       <c r="C66" s="27" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15" customHeight="1">
       <c r="C67" s="27" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15" customHeight="1">
       <c r="C68" s="27" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15" customHeight="1">
       <c r="C69" s="27" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15" customHeight="1">
       <c r="C70" s="27" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15" customHeight="1">
       <c r="C71" s="27" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15" customHeight="1">
       <c r="C72" s="27" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15" customHeight="1">
       <c r="C73" s="27" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15" customHeight="1">
       <c r="C74" s="27" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15" customHeight="1">
       <c r="C75" s="27" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15" customHeight="1">
       <c r="C76" s="27" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15" customHeight="1">
       <c r="C77" s="27" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15" customHeight="1">
       <c r="C78" s="27" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15" customHeight="1">
       <c r="C79" s="27" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15" customHeight="1">
       <c r="C80" s="27" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15" customHeight="1">
       <c r="C81" s="27" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15" customHeight="1">
       <c r="C82" s="27" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15" customHeight="1">
       <c r="C83" s="27" t="n"/>
     </row>
     <row r="84"/>
-    <row r="85">
+    <row r="85" ht="15" customHeight="1">
       <c r="C85" s="27" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15" customHeight="1">
       <c r="C86" s="27" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15" customHeight="1">
       <c r="C87" s="27" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15" customHeight="1">
       <c r="C88" s="27" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15" customHeight="1">
       <c r="C89" s="27" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15" customHeight="1">
       <c r="C90" s="27" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15" customHeight="1">
       <c r="C91" s="27" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15" customHeight="1">
       <c r="C92" s="27" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15" customHeight="1">
       <c r="C93" s="27" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15" customHeight="1">
       <c r="C94" s="27" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15" customHeight="1">
       <c r="C95" s="27" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15" customHeight="1">
       <c r="C96" s="27" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15" customHeight="1">
       <c r="C97" s="27" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15" customHeight="1">
       <c r="C98" s="27" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15" customHeight="1">
       <c r="C99" s="27" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15" customHeight="1">
       <c r="C100" s="27" t="n"/>
     </row>
     <row r="101"/>
-    <row r="102">
+    <row r="102" ht="15" customHeight="1">
       <c r="C102" s="27" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15" customHeight="1">
       <c r="C103" s="27" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15" customHeight="1">
       <c r="C104" s="27" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15" customHeight="1">
       <c r="C105" s="27" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15" customHeight="1">
       <c r="C106" s="27" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15" customHeight="1">
       <c r="C107" s="27" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15" customHeight="1">
       <c r="C108" s="27" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15" customHeight="1">
       <c r="C109" s="27" t="n"/>
     </row>
     <row r="110"/>
-    <row r="111">
+    <row r="111" ht="15" customHeight="1">
       <c r="C111" s="26" t="n"/>
     </row>
   </sheetData>
@@ -7870,12 +8130,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -9843,33 +10103,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC47"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="34" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="34" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="34" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="29" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="35" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="34" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="34" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="29" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="35" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="36" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="34" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="34" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="34" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="37" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="34" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="34" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="37" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="37" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="37" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="37" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="37" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="37" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="37" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="37" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="37" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="37" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="37" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="37" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="56"/>
-    <col width="9" customWidth="1" style="9" min="57" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="37" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="60"/>
+    <col width="9" customWidth="1" style="9" min="61" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -10647,14 +10907,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F321"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19662,18 +19922,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26405,6 +26665,49 @@
       <c r="A123" s="10" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A97 A110:A1048576">
+    <cfRule type="duplicateValues" priority="2013" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A8 A110:A1048576">
+    <cfRule type="duplicateValues" priority="398" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A20 A27 A30 A34:A36 A40 A44 A55 A57:A58 A67 A79 A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="2024" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A30 A32:A36 A40 A44 A46 A49:A52 A55 A57:A58 A67:A68 A72:A74 A76:A79 A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="2051" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A30 A32:A36 A40 A44 A49:A52 A55 A57:A58 A67 A79 A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="2038" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A36 A40:A46 A49:A52 A55 A57:A58 A61 A67:A68 A72:A74 A76:A79 A83 A95:A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="2123" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A37 A40:A46 A49:A52 A55 A57:A63 A67:A68 A72:A74 A76:A79 A83 A95:A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1962" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A37 A40:A52 A55 A57:A69 A72:A74 A76:A79 A83 A85 A95:A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1704" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A52 A55:A69 A72:A74 A76:A79 A83 A85 A95:A97 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1694" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A53 A55:A70 A72:A79 A83 A85:A90 A95:A99 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1724" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A53 A55:A70 A72:A79 A83 A85:A90 A95:A101 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1742" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A70 A72:A79 A82:A93 A95:A101 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1797" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A70 A72:A79 A83 A85:A90 A92:A93 A95:A101 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1789" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A93 A95:A101 A107:A108 A110:A1048576">
+    <cfRule type="duplicateValues" priority="1804" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="1803" dxfId="0"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
   </conditionalFormatting>
@@ -26426,8 +26729,8 @@
     <cfRule type="duplicateValues" priority="128" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" priority="125" dxfId="0"/>
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="125" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
     <cfRule type="duplicateValues" priority="124" dxfId="0"/>
@@ -26438,8 +26741,8 @@
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
     <cfRule type="duplicateValues" priority="118" dxfId="0"/>
@@ -26465,45 +26768,45 @@
     <cfRule type="duplicateValues" priority="108" dxfId="0"/>
     <cfRule type="duplicateValues" priority="109" dxfId="0"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A29 A32:A33">
+    <cfRule type="duplicateValues" priority="526" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="527" dxfId="0"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" priority="144" dxfId="0"/>
     <cfRule type="duplicateValues" priority="145" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="144" dxfId="0"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29 A32:A33">
-    <cfRule type="duplicateValues" priority="527" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="526" dxfId="0"/>
+  <conditionalFormatting sqref="A31 A42">
+    <cfRule type="duplicateValues" priority="476" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="477" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
     <cfRule type="duplicateValues" priority="156" dxfId="0"/>
     <cfRule type="duplicateValues" priority="157" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35:A36">
+    <cfRule type="duplicateValues" priority="583" dxfId="0"/>
     <cfRule type="duplicateValues" priority="584" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="583" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
+    <cfRule type="duplicateValues" priority="67" dxfId="0"/>
     <cfRule type="duplicateValues" priority="68" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="67" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:A39">
+    <cfRule type="duplicateValues" priority="631" dxfId="0"/>
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="631" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
     <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
+    <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="78" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31 A42">
-    <cfRule type="duplicateValues" priority="477" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="476" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
     <cfRule type="duplicateValues" priority="147" dxfId="0"/>
@@ -26526,16 +26829,16 @@
     <cfRule type="duplicateValues" priority="107" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="44" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
@@ -26550,12 +26853,12 @@
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -26566,80 +26869,80 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="61" dxfId="0"/>
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65">
+    <cfRule type="duplicateValues" priority="58" dxfId="0"/>
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="58" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
     <cfRule type="duplicateValues" priority="57" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
+    <cfRule type="duplicateValues" priority="151" dxfId="0"/>
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="151" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68 A76">
+    <cfRule type="duplicateValues" priority="865" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
     <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
+    <cfRule type="duplicateValues" priority="42" dxfId="0"/>
     <cfRule type="duplicateValues" priority="43" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="42" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A71">
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
     <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
     <cfRule type="duplicateValues" priority="100" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A68 A76">
-    <cfRule type="duplicateValues" priority="866" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="865" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:A78">
+    <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="982" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
     <cfRule type="duplicateValues" priority="14" dxfId="0"/>
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A81">
+    <cfRule type="duplicateValues" priority="12" dxfId="0"/>
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="12" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82">
     <cfRule type="duplicateValues" priority="22" dxfId="0"/>
     <cfRule type="duplicateValues" priority="21" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83">
+    <cfRule type="duplicateValues" priority="82" dxfId="0"/>
     <cfRule type="duplicateValues" priority="83" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="82" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="19" dxfId="0"/>
     <cfRule type="duplicateValues" priority="20" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="19" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="63" dxfId="0"/>
@@ -26650,8 +26953,8 @@
     <cfRule type="duplicateValues" priority="1376" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A90">
+    <cfRule type="duplicateValues" priority="41" dxfId="0"/>
     <cfRule type="duplicateValues" priority="40" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A91">
     <cfRule type="duplicateValues" priority="17" dxfId="0"/>
@@ -26666,16 +26969,16 @@
     <cfRule type="duplicateValues" priority="24" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94">
+    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A95">
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
     <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A97">
     <cfRule type="duplicateValues" priority="143" dxfId="0"/>
@@ -26694,55 +26997,12 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107:A108">
+    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
     <cfRule type="duplicateValues" priority="132" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A8 A110:A1048576">
-    <cfRule type="duplicateValues" priority="398" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A36 A40:A46 A49:A52 A55 A57:A58 A61 A67:A68 A72:A74 A76:A79 A83 A95:A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="2123" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A37 A40:A46 A49:A52 A55 A57:A63 A67:A68 A72:A74 A76:A79 A83 A95:A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1962" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A37 A40:A52 A55 A57:A69 A72:A74 A76:A79 A83 A85 A95:A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1704" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A70 A72:A79 A82:A93 A95:A101 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1797" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A70 A72:A79 A83 A85:A90 A92:A93 A95:A101 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1789" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A93 A95:A101 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1803" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1804" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A97 A110:A1048576">
-    <cfRule type="duplicateValues" priority="2013" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A20 A27 A30 A34:A36 A40 A44 A55 A57:A58 A67 A79 A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="2024" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A30 A32:A36 A40 A44 A49:A52 A55 A57:A58 A67 A79 A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="2038" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A30 A32:A36 A40 A44 A46 A49:A52 A55 A57:A58 A67:A68 A72:A74 A76:A79 A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="2051" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A52 A55:A69 A72:A74 A76:A79 A83 A85 A95:A97 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1694" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A53 A55:A70 A72:A79 A83 A85:A90 A95:A99 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1724" dxfId="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A53 A55:A70 A72:A79 A83 A85:A90 A95:A101 A107:A108 A110:A1048576">
-    <cfRule type="duplicateValues" priority="1742" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -26759,14 +27019,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -5565,7 +5565,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>res://Assets/Background/001/001</t>
+          <t>res://Assets/Background/001/001.png</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2355" yWindow="2475" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2297,8 +2297,8 @@
     <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="19"/>
-    <col width="9.125" customWidth="1" style="23" min="20" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="20"/>
+    <col width="9.125" customWidth="1" style="23" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5110,8 +5110,8 @@
     <col width="10.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
     <col width="13.875" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
     <col width="11" customWidth="1" style="36" min="10" max="10"/>
-    <col width="9" customWidth="1" style="36" min="11" max="35"/>
-    <col width="9" customWidth="1" style="36" min="36" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="11" max="36"/>
+    <col width="9" customWidth="1" style="36" min="37" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5502,7 +5502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
@@ -5512,10 +5512,11 @@
     <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
     <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
     <col width="13.375" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="43.875" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
-    <col width="41.625" customWidth="1" style="32" min="9" max="9"/>
-    <col width="9" customWidth="1" style="36" min="10" max="33"/>
-    <col width="9" customWidth="1" style="36" min="34" max="16384"/>
+    <col width="6.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="43.875" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
+    <col width="41.625" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="36" min="11" max="35"/>
+    <col width="9" customWidth="1" style="36" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5554,12 +5555,17 @@
           <t>PortraitPath</t>
         </is>
       </c>
-      <c r="H1" s="40" t="inlineStr">
+      <c r="H1" s="41" t="inlineStr">
+        <is>
+          <t>Hide</t>
+        </is>
+      </c>
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>BackgroundPath</t>
         </is>
       </c>
-      <c r="I1" s="40" t="inlineStr">
+      <c r="J1" s="40" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -5587,12 +5593,13 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>res://Assets/Background/001/001.png</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>明嘉靖十九年，武昌府放榜处</t>
         </is>
@@ -5628,8 +5635,13 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>老爷，少爷，榜上没找到少爷的名字。</t>
         </is>
@@ -5666,7 +5678,8 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>嘶...... 又没中......</t>
         </is>
@@ -5703,7 +5716,8 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>你再仔细看看</t>
         </is>
@@ -5740,7 +5754,8 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>老爷，我看了好几遍了，确实没有少爷的名字…...</t>
         </is>
@@ -5777,7 +5792,8 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>考了三次都没中举，看来我不是读书的材料啊爹</t>
         </is>
@@ -5814,7 +5830,8 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>这说的是什么话，你看隔壁村那个老范，考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
         </is>
@@ -5851,7 +5868,8 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>我看我还是跟您学医吧，科举八股什么的，孩儿实在是学不来…</t>
         </is>
@@ -5888,7 +5906,8 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
         </is>
@@ -5925,7 +5944,8 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>可我真心喜欢研究那些药材方子，考证典籍。行医治病才是儿子此生志愿。</t>
         </is>
@@ -5962,7 +5982,8 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢。东壁呀，你若真的想从医，今日起便随为父从《内经》，《本草》学起吧。</t>
         </is>
@@ -5991,7 +6012,8 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>李东璧十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁决定开始随父亲学医。</t>
         </is>
@@ -6027,12 +6049,13 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
         </is>
@@ -6069,7 +6092,8 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>相公，晚饭做好了，该吃饭了。</t>
         </is>
@@ -6106,7 +6130,8 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>来了来了。</t>
         </is>
@@ -6143,7 +6168,8 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>东壁啊，白天教你的都听明白了吗？</t>
         </is>
@@ -6180,7 +6206,8 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>都明白了，平常日子里看您治病，其实已经窥得些门道了。</t>
         </is>
@@ -6217,7 +6244,8 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>学医最要紧的是积累，吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊。</t>
         </is>
@@ -6254,7 +6282,8 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>哇，太好了！</t>
         </is>
@@ -6290,12 +6319,13 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring.png</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>从今天起，你就正式开始给病患诊断开药。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。好了，病人已经在等着你了，快去吧。</t>
         </is>
@@ -6331,12 +6361,13 @@
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring.png</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>言闻兄别来无恙啊。</t>
         </is>
@@ -6373,7 +6404,8 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>哎哟，是日岩兄啊，失迎失迎。</t>
         </is>
@@ -6410,7 +6442,8 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>东壁近来如何啊？</t>
         </is>
@@ -6447,7 +6480,8 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>和我学了一年多医术，现在啊已经能自己出诊了。你还别说，这小子还真是块学医的材料。</t>
         </is>
@@ -6484,7 +6518,8 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>顾先生，学生有礼了。</t>
         </is>
@@ -6521,7 +6556,8 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>世人皆以为考取功名方为正途，你能认清本心承袭家学，济世安民，难得啊。</t>
         </is>
@@ -6558,7 +6594,8 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>学生愚钝，辜负了老师的教导…</t>
         </is>
@@ -6595,7 +6632,8 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>你是我最中意的门生，以前是，现在也是。</t>
         </is>
@@ -6632,7 +6670,8 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>人生在世不止考取科举一条路，你能找到一条适合自己的路，为师很欣慰。</t>
         </is>
@@ -6669,7 +6708,8 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
         </is>
@@ -8752,8 +8792,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="66"/>
-    <col width="9" customWidth="1" style="9" min="67" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="67"/>
+    <col width="9" customWidth="1" style="9" min="68" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -28806,8 +28846,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -28834,32 +28874,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
     <cfRule type="duplicateValues" priority="124" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
     <cfRule type="duplicateValues" priority="120" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
     <cfRule type="duplicateValues" priority="118" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
     <cfRule type="duplicateValues" priority="116" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
     <cfRule type="duplicateValues" priority="111" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -28898,20 +28938,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
     <cfRule type="duplicateValues" priority="155" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
     <cfRule type="duplicateValues" priority="77" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
     <cfRule type="duplicateValues" priority="147" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -28922,8 +28962,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
     <cfRule type="duplicateValues" priority="55" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -28934,32 +28974,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
     <cfRule type="duplicateValues" priority="29" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
     <cfRule type="duplicateValues" priority="134" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
     <cfRule type="duplicateValues" priority="50" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
     <cfRule type="duplicateValues" priority="149" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
     <cfRule type="duplicateValues" priority="74" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
     <cfRule type="duplicateValues" priority="72" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -28970,8 +29010,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
     <cfRule type="duplicateValues" priority="66" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -28982,8 +29022,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
     <cfRule type="duplicateValues" priority="57" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -28994,8 +29034,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
     <cfRule type="duplicateValues" priority="53" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -29006,36 +29046,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
     <cfRule type="duplicateValues" priority="100" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
     <cfRule type="duplicateValues" priority="39" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
     <cfRule type="duplicateValues" priority="63" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
     <cfRule type="duplicateValues" priority="136" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -29066,12 +29106,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
     <cfRule type="duplicateValues" priority="85" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
     <cfRule type="duplicateValues" priority="17" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -29086,12 +29126,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
     <cfRule type="duplicateValues" priority="89" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
     <cfRule type="duplicateValues" priority="143" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -29102,8 +29142,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
     <cfRule type="duplicateValues" priority="132" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,16 +20,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$J$1</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -129,17 +129,24 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -233,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -381,9 +388,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2347,20 +2355,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J71"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="10.86328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
-    <col width="9.1328125" customWidth="1" style="23" min="11" max="34"/>
-    <col width="9.1328125" customWidth="1" style="23" min="35" max="16384"/>
+    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="10.875" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="23.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="25.125" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="33.375" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="9.125" customWidth="1" style="23" min="11" max="35"/>
+    <col width="9.125" customWidth="1" style="23" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5077,13 +5085,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5299,21 +5307,21 @@
   <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.46484375" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
-    <col width="15.1328125" customWidth="1" style="36" min="2" max="2"/>
-    <col width="27.3984375" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.1328125" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="11.86328125" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="19.73046875" customWidth="1" style="36" min="7" max="7"/>
-    <col width="12.3984375" customWidth="1" style="36" min="8" max="8"/>
-    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="15.125" customWidth="1" style="36" min="2" max="2"/>
+    <col width="27.375" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
+    <col width="14.125" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="19.75" customWidth="1" style="36" min="7" max="7"/>
+    <col width="12.375" customWidth="1" style="36" min="8" max="8"/>
+    <col width="14.25" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
     <col width="23" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="10.265625" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="10.25" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
     <col width="11" customWidth="1" style="36" min="13" max="13"/>
-    <col width="9" customWidth="1" style="36" min="14" max="52"/>
-    <col width="9" customWidth="1" style="36" min="53" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="14" max="53"/>
+    <col width="9" customWidth="1" style="36" min="54" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5582,7 +5590,11 @@
       <c r="F6" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="37" t="inlineStr"/>
+      <c r="G6" s="59" t="inlineStr">
+        <is>
+          <t>脾虚湿盛</t>
+        </is>
+      </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
           <t>shi_zi</t>
@@ -5895,18 +5907,18 @@
   <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
-    <col width="12.3984375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.3984375" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="6.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
-    <col width="43.86328125" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="89.73046875" customWidth="1" style="32" min="10" max="10"/>
-    <col width="9" customWidth="1" style="36" min="11" max="48"/>
-    <col width="9" customWidth="1" style="36" min="49" max="16384"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="12.375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.375" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="43.875" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
+    <col width="89.75" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="36" min="11" max="49"/>
+    <col width="9" customWidth="1" style="36" min="50" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6480,7 +6492,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I14" s="64" t="inlineStr">
+      <c r="I14" s="65" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -7321,7 +7333,7 @@
       <c r="G34" s="51" t="inlineStr"/>
       <c r="H34" s="53" t="inlineStr">
         <is>
-          <t>dim</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="I34" s="51" t="inlineStr">
@@ -7493,7 +7505,7 @@
       <c r="G38" s="32" t="inlineStr"/>
       <c r="H38" s="53" t="inlineStr">
         <is>
-          <t>dim</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="I38" s="32" t="inlineStr"/>
@@ -7880,7 +7892,7 @@
       </c>
       <c r="I47" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/clinic/spring.png</t>
+          <t>res://Assets/Background/003/003_04.png</t>
         </is>
       </c>
       <c r="J47" s="52" t="inlineStr">
@@ -8014,7 +8026,7 @@
       </c>
       <c r="I50" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/clinic/spring.png</t>
+          <t>res://Assets/Background/003/003_04.png</t>
         </is>
       </c>
       <c r="J50" s="52" t="inlineStr">
@@ -8204,14 +8216,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -10243,33 +10255,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="80"/>
-    <col width="9" customWidth="1" style="9" min="81" max="16384"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="81"/>
+    <col width="9" customWidth="1" style="9" min="82" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -11083,12 +11095,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -13188,15 +13200,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24968,18 +24980,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32417,14 +32429,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="45.59765625" customWidth="1" min="1" max="1"/>
-    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.73046875" customWidth="1" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.625" customWidth="1" min="1" max="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.75" customWidth="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$J$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,7 +29,7 @@
   <numFmts count="0"/>
   <fonts count="17">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -129,17 +129,17 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <family val="3"/>
-      <sz val="6"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,7 +238,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -391,7 +391,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2355,20 +2355,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J71"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="10.875" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="23.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="25.125" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="33.375" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
-    <col width="9.125" customWidth="1" style="23" min="11" max="36"/>
-    <col width="9.125" customWidth="1" style="23" min="37" max="16384"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="10.86328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="9.1328125" customWidth="1" style="23" min="11" max="37"/>
+    <col width="9.1328125" customWidth="1" style="23" min="38" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5085,13 +5085,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5307,21 +5307,21 @@
   <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.5" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
-    <col width="15.125" customWidth="1" style="36" min="2" max="2"/>
-    <col width="27.375" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.125" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.125" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="19.75" customWidth="1" style="36" min="7" max="7"/>
-    <col width="12.375" customWidth="1" style="36" min="8" max="8"/>
-    <col width="14.25" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="8.46484375" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="15.1328125" customWidth="1" style="36" min="2" max="2"/>
+    <col width="27.3984375" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
+    <col width="14.1328125" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="19.73046875" customWidth="1" style="36" min="7" max="7"/>
+    <col width="12.3984375" customWidth="1" style="36" min="8" max="8"/>
+    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
     <col width="23" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="10.25" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
     <col width="11" customWidth="1" style="36" min="13" max="13"/>
-    <col width="9" customWidth="1" style="36" min="14" max="54"/>
-    <col width="9" customWidth="1" style="36" min="55" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="14" max="55"/>
+    <col width="9" customWidth="1" style="36" min="56" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5907,18 +5907,18 @@
   <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
-    <col width="12.375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.375" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="6.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
-    <col width="43.875" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="89.75" customWidth="1" style="32" min="10" max="10"/>
-    <col width="9" customWidth="1" style="36" min="11" max="50"/>
-    <col width="9" customWidth="1" style="36" min="51" max="16384"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.3984375" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="43.86328125" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
+    <col width="89.73046875" customWidth="1" style="32" min="10" max="10"/>
+    <col width="9" customWidth="1" style="36" min="11" max="51"/>
+    <col width="9" customWidth="1" style="36" min="52" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8220,14 +8220,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -10259,33 +10259,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="82"/>
-    <col width="9" customWidth="1" style="9" min="83" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="83"/>
+    <col width="9" customWidth="1" style="9" min="84" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -11099,12 +11099,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -13204,15 +13204,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24984,18 +24984,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32433,14 +32433,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C370D4-9286-4A6B-B998-CFD0B7D3C0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F20E188-C818-40CF-B08F-653569362F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -10303,20 +10303,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="36" customWidth="1"/>
-    <col min="3" max="3" width="27.375" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" style="36" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="36" customWidth="1"/>
-    <col min="9" max="9" width="12.375" style="36" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="36" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="57" width="9" style="36" customWidth="1"/>
     <col min="58" max="16384" width="9" style="36"/>
   </cols>
@@ -10815,20 +10814,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.25" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="32" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.125" style="32" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="89.75" style="32" customWidth="1"/>
-    <col min="11" max="52" width="9" style="36" customWidth="1"/>
-    <col min="53" max="16384" width="9" style="36"/>
+    <col min="7" max="7" width="13.875" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9753ED-D728-48EC-B2E7-0A3DB33AD628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801FDE57-C045-4254-BD2E-7651E932AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4482" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4481" uniqueCount="1249">
   <si>
     <t>NpcID</t>
   </si>
@@ -6061,10 +6061,6 @@
   <si>
     <t>李东璧在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材，方剂，疾病。
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="14"/>
   </si>
   <si>
     <t>TriggerNpcID</t>
@@ -10359,7 +10355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="38" bestFit="1" customWidth="1"/>
@@ -10373,17 +10369,16 @@
     <col min="9" max="9" width="15.625" style="36" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.375" style="36" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.75" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.75" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="65" width="9" style="36" customWidth="1"/>
-    <col min="66" max="16384" width="9" style="36"/>
+    <col min="12" max="12" width="27.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="64" width="9" style="36" customWidth="1"/>
+    <col min="65" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="41" t="s">
         <v>248</v>
       </c>
@@ -10415,28 +10410,25 @@
         <v>0</v>
       </c>
       <c r="K1" s="61" t="s">
-        <v>1249</v>
-      </c>
-      <c r="L1" s="61" t="s">
         <v>1248</v>
       </c>
+      <c r="L1" s="64" t="s">
+        <v>257</v>
+      </c>
       <c r="M1" s="64" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N1" s="64" t="s">
-        <v>258</v>
-      </c>
-      <c r="O1" s="64" t="s">
         <v>259</v>
       </c>
+      <c r="O1" s="65" t="s">
+        <v>260</v>
+      </c>
       <c r="P1" s="65" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q1" s="65" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="37" t="s">
         <v>262</v>
       </c>
@@ -10465,15 +10457,14 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
       <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="37">
+      <c r="O2" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16">
       <c r="A3" s="37" t="s">
         <v>267</v>
       </c>
@@ -10502,15 +10493,14 @@
       <c r="L3" s="37"/>
       <c r="M3" s="37"/>
       <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
         <v>269</v>
       </c>
@@ -10539,15 +10529,14 @@
       <c r="L4" s="37"/>
       <c r="M4" s="37"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="37">
+      <c r="O4" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="36" customHeight="1">
+    <row r="5" spans="1:16" ht="36" customHeight="1">
       <c r="A5" s="37" t="s">
         <v>271</v>
       </c>
@@ -10575,20 +10564,19 @@
         <v>36</v>
       </c>
       <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37" t="s">
+      <c r="L5" s="37" t="s">
         <v>273</v>
       </c>
+      <c r="M5" s="37"/>
       <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="O5" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="37" t="s">
         <v>274</v>
       </c>
@@ -10612,22 +10600,19 @@
       <c r="K6" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="37">
-        <v>1</v>
-      </c>
+      <c r="L6" s="37"/>
       <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37">
+      <c r="N6" s="37">
         <v>5</v>
       </c>
-      <c r="P6" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="59">
+      <c r="O6" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="59">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16">
       <c r="A7" s="37" t="s">
         <v>277</v>
       </c>
@@ -10654,15 +10639,14 @@
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
       <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37" t="b">
+      <c r="O7" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" s="59">
+      <c r="P7" s="59">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="36" customHeight="1">
+    <row r="8" spans="1:16" ht="36" customHeight="1">
       <c r="A8" s="37" t="s">
         <v>280</v>
       </c>
@@ -10692,20 +10676,19 @@
         <v>33</v>
       </c>
       <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37" t="s">
+      <c r="L8" s="37" t="s">
         <v>282</v>
       </c>
+      <c r="M8" s="37"/>
       <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="37">
+      <c r="O8" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16">
       <c r="A9" s="37" t="s">
         <v>283</v>
       </c>
@@ -10733,24 +10716,21 @@
       <c r="K9" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="37">
-        <v>1</v>
-      </c>
-      <c r="M9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37">
+        <v>1000</v>
+      </c>
       <c r="N9" s="37">
-        <v>1000</v>
-      </c>
-      <c r="O9" s="37">
         <v>5</v>
       </c>
-      <c r="P9" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="37">
+      <c r="O9" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16">
       <c r="A10" s="37" t="s">
         <v>285</v>
       </c>
@@ -10778,20 +10758,17 @@
       <c r="K10" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="37">
-        <v>1</v>
-      </c>
+      <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="37">
+      <c r="O10" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16">
       <c r="A11" s="37"/>
       <c r="B11" s="37"/>
       <c r="C11" s="37"/>
@@ -10808,9 +10785,8 @@
       <c r="N11" s="37"/>
       <c r="O11" s="37"/>
       <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-    </row>
-    <row r="12" spans="1:17">
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="37"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
@@ -10827,9 +10803,8 @@
       <c r="N12" s="37"/>
       <c r="O12" s="37"/>
       <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-    </row>
-    <row r="13" spans="1:17">
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="37"/>
       <c r="B13" s="37"/>
       <c r="C13" s="37"/>
@@ -10846,9 +10821,8 @@
       <c r="N13" s="37"/>
       <c r="O13" s="37"/>
       <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-    </row>
-    <row r="14" spans="1:17">
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="37"/>
       <c r="B14" s="37"/>
       <c r="C14" s="37"/>
@@ -10865,9 +10839,8 @@
       <c r="N14" s="37"/>
       <c r="O14" s="37"/>
       <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-    </row>
-    <row r="15" spans="1:17">
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="37"/>
       <c r="B15" s="37"/>
       <c r="C15" s="37"/>
@@ -10884,9 +10857,8 @@
       <c r="N15" s="37"/>
       <c r="O15" s="37"/>
       <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-    </row>
-    <row r="16" spans="1:17">
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="37"/>
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
@@ -10903,9 +10875,8 @@
       <c r="N16" s="37"/>
       <c r="O16" s="37"/>
       <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-    </row>
-    <row r="17" spans="1:17">
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="37"/>
       <c r="B17" s="37"/>
       <c r="C17" s="37"/>
@@ -10922,9 +10893,8 @@
       <c r="N17" s="37"/>
       <c r="O17" s="37"/>
       <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-    </row>
-    <row r="18" spans="1:17">
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="37"/>
       <c r="B18" s="37"/>
       <c r="C18" s="37"/>
@@ -10941,9 +10911,8 @@
       <c r="N18" s="37"/>
       <c r="O18" s="37"/>
       <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-    </row>
-    <row r="19" spans="1:17">
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="37"/>
       <c r="B19" s="37"/>
       <c r="C19" s="37"/>
@@ -10960,7 +10929,6 @@
       <c r="N19" s="37"/>
       <c r="O19" s="37"/>
       <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14"/>
@@ -27497,8 +27465,8 @@
     <cfRule type="duplicateValues" dxfId="149" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="2332"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="2331"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="2331"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="2332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="146" priority="162"/>
@@ -27525,32 +27493,32 @@
     <cfRule type="duplicateValues" dxfId="137" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="136" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="134" priority="121"/>
     <cfRule type="duplicateValues" dxfId="133" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="130" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
-    <cfRule type="duplicateValues" dxfId="128" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="126" priority="112"/>
     <cfRule type="duplicateValues" dxfId="125" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
-    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="122" priority="140"/>
@@ -27589,20 +27557,20 @@
     <cfRule type="duplicateValues" dxfId="105" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" dxfId="102" priority="78"/>
     <cfRule type="duplicateValues" dxfId="101" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="98" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="96" priority="90"/>
@@ -27613,8 +27581,8 @@
     <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" dxfId="90" priority="106"/>
@@ -27625,32 +27593,32 @@
     <cfRule type="duplicateValues" dxfId="87" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="82" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="78" priority="152"/>
     <cfRule type="duplicateValues" dxfId="77" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="72" priority="86"/>
@@ -27661,8 +27629,8 @@
     <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="66" priority="60"/>
@@ -27673,8 +27641,8 @@
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="60" priority="150"/>
@@ -27685,8 +27653,8 @@
     <cfRule type="duplicateValues" dxfId="57" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="54" priority="42"/>
@@ -27697,36 +27665,36 @@
     <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
-    <cfRule type="duplicateValues" dxfId="50" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" dxfId="48" priority="95"/>
     <cfRule type="duplicateValues" dxfId="47" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" dxfId="42" priority="1727"/>
     <cfRule type="duplicateValues" dxfId="41" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" dxfId="38" priority="982"/>
     <cfRule type="duplicateValues" dxfId="37" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="36" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" dxfId="34" priority="13"/>
@@ -27757,12 +27725,12 @@
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" dxfId="20" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" dxfId="16" priority="26"/>
@@ -27777,12 +27745,12 @@
     <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="10" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="8" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" dxfId="6" priority="1709"/>
@@ -27793,8 +27761,8 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
-    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="395"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -5705,12 +5705,8 @@
           <t>night</t>
         </is>
       </c>
-      <c r="F9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="37" t="n">
-        <v>0</v>
-      </c>
+      <c r="F9" s="37" t="inlineStr"/>
+      <c r="G9" s="37" t="inlineStr"/>
       <c r="H9" s="37" t="inlineStr">
         <is>
           <t>005_01</t>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,9 +27,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="18">
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -129,10 +129,24 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,9 +245,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -387,9 +401,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2353,19 +2369,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I71"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.1328125" customWidth="1" style="23" min="10" max="41"/>
-    <col width="9.1328125" customWidth="1" style="23" min="42" max="16384"/>
+    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="42"/>
+    <col width="9.125" customWidth="1" style="23" min="43" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5003,13 +5019,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5225,24 +5241,24 @@
   <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.59765625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.46484375" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="18.3984375" customWidth="1" style="36" min="7" max="7"/>
-    <col width="16.265625" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
-    <col width="15.59765625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
-    <col width="7.3984375" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="8.46484375" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="27.73046875" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="14.625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="14.25" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.5" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="18.375" customWidth="1" style="36" min="7" max="7"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
+    <col width="15.625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="7.375" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="27.75" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="10.73046875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="10.86328125" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="64"/>
-    <col width="9" customWidth="1" style="36" min="65" max="16384"/>
+    <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="9" customWidth="1" style="36" min="17" max="65"/>
+    <col width="9" customWidth="1" style="36" min="66" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5776,22 +5792,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="n"/>
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="37" t="n"/>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="37" t="n"/>
-      <c r="L11" s="37" t="n"/>
-      <c r="M11" s="37" t="n"/>
-      <c r="N11" s="37" t="n"/>
-      <c r="O11" s="37" t="n"/>
-      <c r="P11" s="37" t="n"/>
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>要上来访</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="37" t="inlineStr"/>
+      <c r="H11" s="37" t="inlineStr"/>
+      <c r="I11" s="37" t="inlineStr">
+        <is>
+          <t>人参</t>
+        </is>
+      </c>
+      <c r="J11" s="37" t="inlineStr"/>
+      <c r="K11" s="37" t="inlineStr"/>
+      <c r="L11" s="37" t="inlineStr"/>
+      <c r="M11" s="37" t="inlineStr"/>
+      <c r="N11" s="37" t="inlineStr"/>
+      <c r="O11" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="37" t="n"/>
@@ -5949,21 +5995,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.86328125" defaultRowHeight="18"/>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="8.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="150.46484375" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.86328125" customWidth="1" style="36" min="11" max="15"/>
-    <col width="8.86328125" customWidth="1" style="36" min="16" max="16384"/>
+    <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="16"/>
+    <col width="8.875" customWidth="1" style="36" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6537,7 +6583,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I14" s="66" t="inlineStr">
+      <c r="I14" s="68" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -6667,7 +6713,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I17" s="66" t="inlineStr">
+      <c r="I17" s="68" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -7405,7 +7451,7 @@
       <c r="H35" s="51" t="inlineStr"/>
       <c r="I35" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_01.png</t>
+          <t>res://Assets/Background/005/005_01.png</t>
         </is>
       </c>
       <c r="J35" s="56" t="inlineStr">
@@ -7493,7 +7539,7 @@
       </c>
       <c r="I37" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_02.png</t>
+          <t>res://Assets/Background/005/005_02.png</t>
         </is>
       </c>
       <c r="J37" s="50" t="inlineStr">
@@ -7779,7 +7825,7 @@
       </c>
       <c r="I44" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_03.png</t>
+          <t>res://Assets/Background/005/005_03.png</t>
         </is>
       </c>
       <c r="J44" s="32" t="inlineStr">
@@ -7867,7 +7913,7 @@
       </c>
       <c r="I46" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_04.png</t>
+          <t>res://Assets/Background/005/005_04.png</t>
         </is>
       </c>
       <c r="J46" s="32" t="inlineStr">
@@ -7957,7 +8003,7 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="I48" s="66" t="inlineStr"/>
+      <c r="I48" s="67" t="inlineStr"/>
       <c r="J48" s="58" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -8047,7 +8093,7 @@
       </c>
       <c r="I50" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_04.png</t>
+          <t>res://Assets/Background/005/005_04.png</t>
         </is>
       </c>
       <c r="J50" s="52" t="inlineStr">
@@ -8425,7 +8471,7 @@
       </c>
       <c r="I59" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/003/003_04.png</t>
+          <t>res://Assets/Background/005/005_04.png</t>
         </is>
       </c>
       <c r="J59" s="52" t="inlineStr">
@@ -8601,6 +8647,130 @@
           <t>不好！啊啊啊啊！！！</t>
         </is>
       </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="50" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B64" s="50" t="inlineStr">
+        <is>
+          <t>要上来访</t>
+        </is>
+      </c>
+      <c r="C64" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E64" s="50" t="inlineStr"/>
+      <c r="F64" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G64" s="51" t="inlineStr"/>
+      <c r="H64" s="53" t="inlineStr"/>
+      <c r="I64" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/</t>
+        </is>
+      </c>
+      <c r="J64" s="50" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B65" s="50" t="inlineStr">
+        <is>
+          <t>要上来访</t>
+        </is>
+      </c>
+      <c r="C65" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E65" s="50" t="inlineStr"/>
+      <c r="F65" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G65" s="51" t="inlineStr"/>
+      <c r="H65" s="53" t="inlineStr"/>
+      <c r="I65" s="51" t="inlineStr"/>
+      <c r="J65" s="50" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="50" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B66" s="50" t="inlineStr">
+        <is>
+          <t>要上来访</t>
+        </is>
+      </c>
+      <c r="C66" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E66" s="50" t="inlineStr"/>
+      <c r="F66" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G66" s="51" t="inlineStr"/>
+      <c r="H66" s="53" t="inlineStr"/>
+      <c r="I66" s="51" t="inlineStr"/>
+      <c r="J66" s="50" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="50" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B67" s="50" t="inlineStr">
+        <is>
+          <t>要上来访</t>
+        </is>
+      </c>
+      <c r="C67" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E67" s="50" t="inlineStr"/>
+      <c r="F67" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G67" s="51" t="inlineStr"/>
+      <c r="H67" s="51" t="inlineStr"/>
+      <c r="I67" s="51" t="inlineStr"/>
+      <c r="J67" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8615,14 +8785,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -10339,7 +10509,7 @@
     <row r="47">
       <c r="A47" s="47" t="inlineStr">
         <is>
-          <t>ren_shen</t>
+          <t>ren_shen_disease</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -10654,33 +10824,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="89"/>
-    <col width="9" customWidth="1" style="9" min="90" max="16384"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="90"/>
+    <col width="9" customWidth="1" style="9" min="91" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -11494,12 +11664,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -13599,15 +13769,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25379,18 +25549,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="41.73046875" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="41.75" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32514,8 +32684,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -32542,32 +32712,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -32606,20 +32776,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -32630,8 +32800,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -32642,32 +32812,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -32678,8 +32848,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -32690,8 +32860,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -32702,8 +32872,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -32714,36 +32884,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -32774,12 +32944,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -32794,12 +32964,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -32810,8 +32980,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -32828,14 +32998,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="45.59765625" customWidth="1" min="1" max="1"/>
-    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.73046875" customWidth="1" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.625" customWidth="1" min="1" max="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.75" customWidth="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2380,8 +2380,8 @@
     <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="42"/>
-    <col width="9.125" customWidth="1" style="23" min="43" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="43"/>
+    <col width="9.125" customWidth="1" style="23" min="44" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5257,8 +5257,8 @@
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
     <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
     <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="65"/>
-    <col width="9" customWidth="1" style="36" min="66" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="17" max="66"/>
+    <col width="9" customWidth="1" style="36" min="67" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6008,8 +6008,8 @@
     <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
     <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="16"/>
-    <col width="8.875" customWidth="1" style="36" min="17" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="17"/>
+    <col width="8.875" customWidth="1" style="36" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10509,7 +10509,7 @@
     <row r="47">
       <c r="A47" s="47" t="inlineStr">
         <is>
-          <t>ren_shen_disease</t>
+          <t>ren_shen</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -10849,8 +10849,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="90"/>
-    <col width="9" customWidth="1" style="9" min="91" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="91"/>
+    <col width="9" customWidth="1" style="9" min="92" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -2380,8 +2380,8 @@
     <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="43"/>
-    <col width="9.125" customWidth="1" style="23" min="44" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="44"/>
+    <col width="9.125" customWidth="1" style="23" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5257,8 +5257,8 @@
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
     <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
     <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="66"/>
-    <col width="9" customWidth="1" style="36" min="67" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="17" max="67"/>
+    <col width="9" customWidth="1" style="36" min="68" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6008,8 +6008,8 @@
     <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
     <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="17"/>
-    <col width="8.875" customWidth="1" style="36" min="18" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="18"/>
+    <col width="8.875" customWidth="1" style="36" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10509,7 +10509,7 @@
     <row r="47">
       <c r="A47" s="47" t="inlineStr">
         <is>
-          <t>ren_shen</t>
+          <t>ren_shen_disease</t>
         </is>
       </c>
       <c r="B47" s="47" t="inlineStr">
@@ -10849,8 +10849,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="91"/>
-    <col width="9" customWidth="1" style="9" min="92" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="92"/>
+    <col width="9" customWidth="1" style="9" min="93" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,16 +20,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -129,21 +129,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -151,9 +137,9 @@
     </font>
     <font>
       <name val="等线"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -245,9 +231,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -406,12 +392,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2375,19 +2359,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I74"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="23.125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="50"/>
-    <col width="9.125" customWidth="1" style="23" min="51" max="16384"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="9.1328125" customWidth="1" style="23" min="10" max="51"/>
+    <col width="9.1328125" customWidth="1" style="23" min="52" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5112,13 +5096,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5334,24 +5318,24 @@
   <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="14.25" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.5" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="18.375" customWidth="1" style="36" min="7" max="7"/>
-    <col width="16.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
-    <col width="15.625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
-    <col width="7.375" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="27.75" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="12.125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="14.59765625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.46484375" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="18.3984375" customWidth="1" style="36" min="7" max="7"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="12.19921875" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
+    <col width="8.46484375" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="29.73046875" customWidth="1" style="36" min="12" max="12"/>
+    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="73"/>
-    <col width="9" customWidth="1" style="36" min="74" max="16384"/>
+    <col width="10.73046875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="10.86328125" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="9" customWidth="1" style="36" min="17" max="74"/>
+    <col width="9" customWidth="1" style="36" min="75" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6122,7 +6106,7 @@
       </c>
       <c r="L15" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/xing_kong/xing_kong_sick.png</t>
+          <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
         </is>
       </c>
       <c r="M15" s="37" t="inlineStr"/>
@@ -6226,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="37" t="inlineStr">
         <is>
           <t>009_01</t>
@@ -6297,20 +6281,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J110"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.86328125" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="8.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="24"/>
-    <col width="8.875" customWidth="1" style="36" min="25" max="16384"/>
+    <col width="150.46484375" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.86328125" customWidth="1" style="36" min="11" max="25"/>
+    <col width="8.86328125" customWidth="1" style="36" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6884,7 +6868,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I14" s="70" t="inlineStr">
+      <c r="I14" s="68" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -7014,7 +6998,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I17" s="70" t="inlineStr">
+      <c r="I17" s="68" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -8304,7 +8288,7 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="I48" s="70" t="inlineStr"/>
+      <c r="I48" s="68" t="inlineStr"/>
       <c r="J48" s="58" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -9253,7 +9237,7 @@
       <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="58" t="inlineStr">
         <is>
-          <t>而是小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
+          <t>小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
         </is>
       </c>
     </row>
@@ -10800,14 +10784,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -12839,33 +12823,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="98"/>
-    <col width="9" customWidth="1" style="9" min="99" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="99"/>
+    <col width="9" customWidth="1" style="9" min="100" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -13679,12 +13663,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -15784,15 +15768,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27564,18 +27548,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="41.75" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="41.73046875" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34699,8 +34683,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -34727,32 +34711,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -34791,20 +34775,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -34815,8 +34799,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -34827,32 +34811,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -34863,8 +34847,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -34875,8 +34859,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -34887,8 +34871,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -34899,36 +34883,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -34959,12 +34943,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -34979,12 +34963,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -34995,8 +34979,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -35013,14 +34997,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,16 +20,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -129,17 +129,24 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -233,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -393,9 +400,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2359,19 +2367,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I74"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.1328125" customWidth="1" style="23" min="10" max="51"/>
-    <col width="9.1328125" customWidth="1" style="23" min="52" max="16384"/>
+    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="52"/>
+    <col width="9.125" customWidth="1" style="23" min="53" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5096,13 +5104,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5315,27 +5323,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.59765625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.46484375" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="18.3984375" customWidth="1" style="36" min="7" max="7"/>
-    <col width="16.265625" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
-    <col width="12.19921875" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="8.46484375" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="29.73046875" customWidth="1" style="36" min="12" max="12"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="14.625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="14.25" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.5" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="18.375" customWidth="1" style="36" min="7" max="7"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
+    <col width="15.625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="12.25" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="29.75" customWidth="1" style="36" min="12" max="12"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="10.73046875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="10.86328125" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="74"/>
-    <col width="9" customWidth="1" style="36" min="75" max="16384"/>
+    <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="9" customWidth="1" style="36" min="17" max="75"/>
+    <col width="9" customWidth="1" style="36" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6256,7 +6264,7 @@
       </c>
       <c r="L18" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/jia_quan/jia_quan.png</t>
+          <t>res://Assets/Portrait/StoryNpc/jia_quan/jia_quan_sick.png</t>
         </is>
       </c>
       <c r="M18" s="37" t="inlineStr"/>
@@ -6265,6 +6273,146 @@
         <v>1</v>
       </c>
       <c r="P18" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>story_npc_cured</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>009_01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>009_03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>009治疗失败</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>009_01</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>009_01</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6280,21 +6428,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.86328125" defaultRowHeight="18"/>
+  <dimension ref="A1:J134"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="8.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="150.46484375" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.86328125" customWidth="1" style="36" min="11" max="25"/>
-    <col width="8.86328125" customWidth="1" style="36" min="26" max="16384"/>
+    <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="26"/>
+    <col width="8.875" customWidth="1" style="36" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6868,7 +7016,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I14" s="68" t="inlineStr">
+      <c r="I14" s="69" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -6998,7 +7146,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I17" s="68" t="inlineStr">
+      <c r="I17" s="69" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -8066,7 +8214,11 @@
       <c r="F43" s="51" t="inlineStr"/>
       <c r="G43" s="32" t="inlineStr"/>
       <c r="H43" s="32" t="inlineStr"/>
-      <c r="I43" s="32" t="inlineStr"/>
+      <c r="I43" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/005/005_03.png</t>
+        </is>
+      </c>
       <c r="J43" s="32" t="inlineStr">
         <is>
           <t>一夜舟车劳顿，李东璧到了楚恭王府。</t>
@@ -8108,11 +8260,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I44" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/005/005_03.png</t>
-        </is>
-      </c>
+      <c r="I44" s="51" t="inlineStr"/>
       <c r="J44" s="32" t="inlineStr">
         <is>
           <t>您就是李神医啊，比我想得要年轻许多。请先生来，是小王有事相求。</t>
@@ -10728,18 +10876,22 @@
       </c>
       <c r="E109" s="50" t="inlineStr">
         <is>
-          <t>贾荃</t>
+          <t>陆忠</t>
         </is>
       </c>
       <c r="F109" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G109" s="51" t="inlineStr"/>
       <c r="H109" s="53" t="inlineStr"/>
       <c r="I109" s="51" t="inlineStr"/>
-      <c r="J109" s="50" t="inlineStr"/>
+      <c r="J109" s="52" t="inlineStr">
+        <is>
+          <t>我家老爷刚才在醉仙楼喝酒，突然就开始胡言乱语，神志不清了。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="50" t="inlineStr">
@@ -10760,16 +10912,996 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E110" s="50" t="inlineStr"/>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>贾荃</t>
+        </is>
+      </c>
       <c r="F110" s="51" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G110" s="51" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G110" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H110" s="51" t="inlineStr"/>
       <c r="I110" s="51" t="inlineStr"/>
-      <c r="J110" s="50" t="inlineStr"/>
+      <c r="J110" s="52" t="inlineStr">
+        <is>
+          <t>我是湖广首富！哈哈哈哈，我看谁再敢小看我！</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="50" t="inlineStr">
+        <is>
+          <t>009_01</t>
+        </is>
+      </c>
+      <c r="B111" s="50" t="inlineStr">
+        <is>
+          <t>贾荃痰火扰心</t>
+        </is>
+      </c>
+      <c r="C111" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E111" s="56" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F111" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G111" s="51" t="inlineStr"/>
+      <c r="H111" s="51" t="inlineStr"/>
+      <c r="I111" s="51" t="inlineStr"/>
+      <c r="J111" s="52" t="inlineStr">
+        <is>
+          <t>这不是贾老板吗，快把他抬过来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="50" t="inlineStr">
+        <is>
+          <t>009_01</t>
+        </is>
+      </c>
+      <c r="B112" s="50" t="inlineStr">
+        <is>
+          <t>贾荃痰火扰心</t>
+        </is>
+      </c>
+      <c r="C112" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D112" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E112" s="52" t="inlineStr">
+        <is>
+          <t>贾荃</t>
+        </is>
+      </c>
+      <c r="F112" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G112" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H112" s="32" t="inlineStr"/>
+      <c r="I112" s="32" t="inlineStr"/>
+      <c r="J112" s="52" t="inlineStr">
+        <is>
+          <t>我有一单大买卖，天大的买卖！呕~</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="50" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B113" s="50" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C113" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E113" s="52" t="inlineStr">
+        <is>
+          <t>贾荃</t>
+        </is>
+      </c>
+      <c r="F113" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G113" s="51" t="inlineStr"/>
+      <c r="H113" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I113" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J113" s="52" t="inlineStr">
+        <is>
+          <t>哎哟，我的头好晕啊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="50" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B114" s="50" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C114" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E114" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F114" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G114" s="51" t="inlineStr"/>
+      <c r="H114" s="53" t="inlineStr"/>
+      <c r="I114" s="51" t="inlineStr"/>
+      <c r="J114" s="52" t="inlineStr">
+        <is>
+          <t>贾老板的神志不清是由痰火扰心所致，心情大起大落再加上饮酒过度，使病情加剧。需要戒酒静养，按时服药。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="50" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B115" s="50" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C115" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E115" s="52" t="inlineStr">
+        <is>
+          <t>陆忠</t>
+        </is>
+      </c>
+      <c r="F115" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G115" s="51" t="inlineStr"/>
+      <c r="H115" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I115" s="51" t="inlineStr"/>
+      <c r="J115" s="52" t="inlineStr">
+        <is>
+          <t>真是太谢谢先生了，老爷我们走吧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="50" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B116" s="50" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C116" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E116" s="52" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F116" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G116" s="51" t="inlineStr"/>
+      <c r="H116" s="51" t="inlineStr"/>
+      <c r="I116" s="51" t="inlineStr"/>
+      <c r="J116" s="52" t="inlineStr">
+        <is>
+          <t>这贾老板怎么突然犯病了呀？我看是这个奸商干坏事儿遭报应了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="50" t="inlineStr">
+        <is>
+          <t>009_02</t>
+        </is>
+      </c>
+      <c r="B117" s="50" t="inlineStr">
+        <is>
+          <t>009治疗成功</t>
+        </is>
+      </c>
+      <c r="C117" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D117" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E117" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F117" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G117" s="51" t="inlineStr"/>
+      <c r="H117" s="53" t="inlineStr"/>
+      <c r="I117" s="51" t="inlineStr"/>
+      <c r="J117" s="52" t="inlineStr">
+        <is>
+          <t>别乱说，快去吧他吐的收拾收拾，还有病患要看病呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="50" t="inlineStr">
+        <is>
+          <t>009_03</t>
+        </is>
+      </c>
+      <c r="B118" s="50" t="inlineStr">
+        <is>
+          <t>009治疗失败</t>
+        </is>
+      </c>
+      <c r="C118" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E118" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F118" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G118" s="51" t="inlineStr"/>
+      <c r="H118" s="53" t="inlineStr"/>
+      <c r="I118" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J118" s="52" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B119" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C119" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E119" s="50" t="inlineStr">
+        <is>
+          <t>衙役</t>
+        </is>
+      </c>
+      <c r="F119" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G119" s="51" t="inlineStr"/>
+      <c r="H119" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I119" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J119" s="50" t="inlineStr">
+        <is>
+          <t>李大夫，知州大人请您去州衙有事商议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B120" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C120" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E120" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F120" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G120" s="51" t="inlineStr"/>
+      <c r="H120" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I120" s="51" t="inlineStr"/>
+      <c r="J120" s="50" t="inlineStr">
+        <is>
+          <t>我知道了，我这就去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B121" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C121" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E121" s="50" t="inlineStr">
+        <is>
+          <t>吴世良</t>
+        </is>
+      </c>
+      <c r="F121" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G121" s="51" t="inlineStr"/>
+      <c r="H121" s="53" t="inlineStr"/>
+      <c r="I121" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/010/010_01.png</t>
+        </is>
+      </c>
+      <c r="J121" s="50" t="inlineStr">
+        <is>
+          <t>今日召诸位来，是朝廷有旨意下达。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B122" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C122" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E122" s="50" t="inlineStr">
+        <is>
+          <t>吴世良</t>
+        </is>
+      </c>
+      <c r="F122" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G122" s="51" t="inlineStr"/>
+      <c r="H122" s="51" t="inlineStr"/>
+      <c r="I122" s="51" t="inlineStr"/>
+      <c r="J122" s="50" t="inlineStr">
+        <is>
+          <t>浙江省淳安建德两县突发水灾，周边各地已有瘟疫出现，朝廷为防止疫情扩散，特调拨赈灾药材发放沿途州府。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B123" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C123" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D123" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E123" s="50" t="inlineStr">
+        <is>
+          <t>吴世良</t>
+        </is>
+      </c>
+      <c r="F123" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G123" s="51" t="inlineStr"/>
+      <c r="H123" s="51" t="inlineStr"/>
+      <c r="I123" s="51" t="inlineStr"/>
+      <c r="J123" s="50" t="inlineStr">
+        <is>
+          <t>昨日赈灾药材已到了咱们蕲州，这次除了惠民药局，还要各医馆药铺配合发放药材。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B124" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C124" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E124" s="50" t="inlineStr">
+        <is>
+          <t>吴世良</t>
+        </is>
+      </c>
+      <c r="F124" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G124" s="32" t="inlineStr"/>
+      <c r="H124" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I124" s="32" t="inlineStr"/>
+      <c r="J124" s="32" t="inlineStr">
+        <is>
+          <t>一会儿诸位就去库房画押取药，明日起官府会发放榜文通知百姓就近领取药材。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B125" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C125" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D125" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E125" s="32" t="inlineStr">
+        <is>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F125" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G125" s="32" t="inlineStr"/>
+      <c r="H125" s="32" t="inlineStr"/>
+      <c r="I125" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/010/010_02.png</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>诸位到我这画押，排好队一个一个来，写好收货地址，我们会专门派人运送。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B126" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C126" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E126" s="32" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F126" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G126" s="32" t="inlineStr"/>
+      <c r="H126" s="32" t="inlineStr"/>
+      <c r="I126" s="32" t="inlineStr"/>
+      <c r="J126" s="32" t="inlineStr">
+        <is>
+          <t>可是还没辨验药材就直接装车了吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B127" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C127" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D127" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E127" s="32" t="inlineStr">
+        <is>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F127" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G127" s="32" t="inlineStr"/>
+      <c r="H127" s="32" t="inlineStr"/>
+      <c r="I127" s="32" t="inlineStr"/>
+      <c r="J127" s="32" t="inlineStr">
+        <is>
+          <t>箱子上都贴着封条，都是太医院直接调拨过来的，难道你还信不过朝廷吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B128" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C128" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D128" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E128" s="32" t="inlineStr">
+        <is>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G128" s="32" t="inlineStr"/>
+      <c r="H128" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I128" s="32" t="inlineStr"/>
+      <c r="J128" s="32" t="inlineStr">
+        <is>
+          <t>快画押吧李大夫，上面催得紧，我们还赶着出货呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B129" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C129" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D129" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E129" s="32" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G129" s="32" t="inlineStr"/>
+      <c r="H129" s="53" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I129" s="32" t="inlineStr"/>
+      <c r="J129" s="32" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B130" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C130" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D130" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E130" s="32" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G130" s="32" t="inlineStr"/>
+      <c r="H130" s="32" t="inlineStr"/>
+      <c r="I130" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J130" s="32" t="inlineStr">
+        <is>
+          <t>东璧啊回来了啦，什么事儿啊一大早就被叫去了？</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B131" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C131" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="D131" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E131" s="32" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F131" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G131" s="32" t="inlineStr"/>
+      <c r="H131" s="32" t="inlineStr"/>
+      <c r="I131" s="32" t="inlineStr"/>
+      <c r="J131" s="32" t="inlineStr">
+        <is>
+          <t>朝廷调拨了赈灾药材，这次不光惠民药局，咱们这些医馆药铺也要一起帮忙发放药材。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B132" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C132" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D132" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E132" s="32" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F132" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G132" s="32" t="inlineStr"/>
+      <c r="H132" s="32" t="inlineStr"/>
+      <c r="I132" s="32" t="inlineStr"/>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>这几日我去菜市街买菜得时候，看到不少流民在城东，大灾之后必有大疫，朝廷这次赈灾太及时了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B133" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C133" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D133" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E133" s="32" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F133" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G133" s="32" t="inlineStr"/>
+      <c r="H133" s="32" t="inlineStr"/>
+      <c r="I133" s="32" t="inlineStr"/>
+      <c r="J133" s="32" t="inlineStr">
+        <is>
+          <t>陈皮，跟我去后院收拾收拾库房，一会儿药材就要送来了，得赶紧腾出地方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="50" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B134" s="50" t="inlineStr">
+        <is>
+          <t>知州有请</t>
+        </is>
+      </c>
+      <c r="C134" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="D134" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E134" s="32" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F134" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G134" s="32" t="inlineStr"/>
+      <c r="H134" s="32" t="inlineStr"/>
+      <c r="I134" s="32" t="inlineStr"/>
+      <c r="J134" s="32" t="inlineStr">
+        <is>
+          <t>好嘞。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10784,14 +11916,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -12823,33 +13955,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="99"/>
-    <col width="9" customWidth="1" style="9" min="100" max="16384"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="100"/>
+    <col width="9" customWidth="1" style="9" min="101" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -13663,12 +14795,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -15768,15 +16900,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27548,18 +28680,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="41.73046875" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="41.75" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34997,14 +36129,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="45.59765625" customWidth="1" min="1" max="1"/>
-    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.73046875" customWidth="1" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.625" customWidth="1" min="1" max="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.75" customWidth="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -407,10 +407,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2389,8 +2389,8 @@
     <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="54"/>
-    <col width="9.125" customWidth="1" style="23" min="55" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="55"/>
+    <col width="9.125" customWidth="1" style="23" min="56" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5382,8 +5382,8 @@
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
     <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
     <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="77"/>
-    <col width="9" customWidth="1" style="36" min="78" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="17" max="78"/>
+    <col width="9" customWidth="1" style="36" min="79" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6751,22 +6751,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="n"/>
-      <c r="B28" s="37" t="n"/>
-      <c r="C28" s="37" t="n"/>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
-      <c r="H28" s="37" t="n"/>
-      <c r="I28" s="37" t="n"/>
-      <c r="J28" s="37" t="n"/>
-      <c r="K28" s="37" t="n"/>
-      <c r="L28" s="37" t="n"/>
-      <c r="M28" s="37" t="n"/>
-      <c r="N28" s="37" t="n"/>
-      <c r="O28" s="37" t="n"/>
-      <c r="P28" s="37" t="n"/>
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>015_03</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>015治疗失败</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F28" s="37" t="inlineStr"/>
+      <c r="G28" s="37" t="inlineStr"/>
+      <c r="H28" s="37" t="inlineStr">
+        <is>
+          <t>015_01</t>
+        </is>
+      </c>
+      <c r="I28" s="37" t="inlineStr"/>
+      <c r="J28" s="37" t="inlineStr"/>
+      <c r="K28" s="37" t="inlineStr"/>
+      <c r="L28" s="37" t="inlineStr"/>
+      <c r="M28" s="37" t="inlineStr"/>
+      <c r="N28" s="37" t="inlineStr"/>
+      <c r="O28" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="n"/>
@@ -7230,7 +7258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
@@ -7243,8 +7271,8 @@
     <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
     <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="28"/>
-    <col width="8.875" customWidth="1" style="36" min="29" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="29"/>
+    <col width="8.875" customWidth="1" style="36" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8905,7 +8933,7 @@
       <c r="I40" s="51" t="inlineStr"/>
       <c r="J40" s="50" t="inlineStr">
         <is>
-          <t>奉楚恭王敕令，请先生去王府走一趟。</t>
+          <t>奉楚王敕令，请先生去王府走一趟。</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9266,7 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="I48" s="69" t="inlineStr"/>
+      <c r="I48" s="70" t="inlineStr"/>
       <c r="J48" s="58" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -12263,7 +12291,7 @@
       <c r="I123" s="51" t="inlineStr"/>
       <c r="J123" s="50" t="inlineStr">
         <is>
-          <t>昨日衙门采购的赈灾药材已到了咱们蕲州，这次除了惠民药局，还要各医馆药铺配合诊治发放。</t>
+          <t>昨日，赈灾药材已采办完备，这次除了惠民药局，还要各医馆药铺配合诊治发放。</t>
         </is>
       </c>
     </row>
@@ -12707,7 +12735,7 @@
         </is>
       </c>
       <c r="I134" s="51" t="inlineStr"/>
-      <c r="J134" s="70" t="inlineStr">
+      <c r="J134" s="69" t="inlineStr">
         <is>
           <t>还有公务在身，就不劳烦李太医啦，兄弟们，走了！</t>
         </is>
@@ -13555,9 +13583,9 @@
       <c r="G156" s="51" t="inlineStr"/>
       <c r="H156" s="53" t="inlineStr"/>
       <c r="I156" s="51" t="inlineStr"/>
-      <c r="J156" s="70" t="inlineStr">
-        <is>
-          <t>这次省内各州县的赈灾药材都要从咱们蕲州调拨，我们负责护送，全省各处跑，路上染了点风寒。</t>
+      <c r="J156" s="69" t="inlineStr">
+        <is>
+          <t>这次省内各州县的赈灾药材都要从咱们蕲州调拨，我奉命押送，全省各处跑，路上染了点风寒。</t>
         </is>
       </c>
     </row>
@@ -13785,7 +13813,7 @@
       <c r="I162" s="32" t="inlineStr"/>
       <c r="J162" s="58" t="inlineStr">
         <is>
-          <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我去一趟武昌府布政司，把这事报上去。</t>
+          <t>他娘的，没有王法了！这州府衙门肯定是不能去了，我到武昌府布政司，把这事报上去。</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14201,163 @@
       <c r="I172" s="32" t="inlineStr"/>
       <c r="J172" s="58" t="inlineStr">
         <is>
-          <t>无妨，您和令尊医术高明</t>
+          <t>无妨，您和令尊医术高明，赈灾药材用的是什么方子想必心里有数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="50" t="inlineStr">
+        <is>
+          <t>015_02</t>
+        </is>
+      </c>
+      <c r="B173" s="50" t="inlineStr">
+        <is>
+          <t>015治疗成功</t>
+        </is>
+      </c>
+      <c r="C173" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D173" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E173" s="50" t="inlineStr">
+        <is>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F173" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G173" s="32" t="inlineStr"/>
+      <c r="H173" s="32" t="inlineStr"/>
+      <c r="I173" s="32" t="inlineStr"/>
+      <c r="J173" s="32" t="inlineStr">
+        <is>
+          <t>但我得提醒您一句，赈灾药材朝廷很重视，不只是一两个州府的事，更不是你我能管的事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="50" t="inlineStr">
+        <is>
+          <t>015_02</t>
+        </is>
+      </c>
+      <c r="B174" s="50" t="inlineStr">
+        <is>
+          <t>015治疗成功</t>
+        </is>
+      </c>
+      <c r="C174" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D174" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E174" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F174" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G174" s="32" t="inlineStr"/>
+      <c r="H174" s="32" t="inlineStr"/>
+      <c r="I174" s="32" t="inlineStr"/>
+      <c r="J174" s="32" t="inlineStr">
+        <is>
+          <t>......</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="50" t="inlineStr">
+        <is>
+          <t>015_02</t>
+        </is>
+      </c>
+      <c r="B175" s="50" t="inlineStr">
+        <is>
+          <t>015治疗成功</t>
+        </is>
+      </c>
+      <c r="C175" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D175" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E175" s="50" t="inlineStr">
+        <is>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F175" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G175" s="32" t="inlineStr"/>
+      <c r="H175" s="32" t="inlineStr"/>
+      <c r="I175" s="32" t="inlineStr"/>
+      <c r="J175" s="32" t="inlineStr">
+        <is>
+          <t>先生医术闻名全省，在下十分钦佩，不要浪费了老天给您的才华。在下告辞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="50" t="inlineStr">
+        <is>
+          <t>015_03</t>
+        </is>
+      </c>
+      <c r="B176" s="50" t="inlineStr">
+        <is>
+          <t>015治疗失败</t>
+        </is>
+      </c>
+      <c r="C176" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E176" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F176" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G176" s="51" t="inlineStr"/>
+      <c r="H176" s="53" t="inlineStr"/>
+      <c r="I176" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J176" s="50" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
     </row>
@@ -16254,8 +16438,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="102"/>
-    <col width="9" customWidth="1" style="9" min="103" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="103"/>
+    <col width="9" customWidth="1" style="9" min="104" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -38089,8 +38273,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -38117,32 +38301,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -38181,20 +38365,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -38205,8 +38389,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -38217,32 +38401,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -38253,8 +38437,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -38265,8 +38449,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -38277,8 +38461,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -38289,36 +38473,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -38349,12 +38533,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -38369,12 +38553,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -38385,8 +38569,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -2386,8 +2386,8 @@
     <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="60"/>
-    <col width="9.125" customWidth="1" style="23" min="61" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="61"/>
+    <col width="9.125" customWidth="1" style="23" min="62" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5408,8 +5408,8 @@
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
     <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
     <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="83"/>
-    <col width="9" customWidth="1" style="36" min="84" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="17" max="84"/>
+    <col width="9" customWidth="1" style="36" min="85" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7271,58 +7271,154 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="n"/>
-      <c r="B38" s="37" t="n"/>
-      <c r="C38" s="37" t="n"/>
-      <c r="D38" s="37" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="37" t="n"/>
-      <c r="H38" s="37" t="n"/>
-      <c r="I38" s="37" t="n"/>
-      <c r="J38" s="37" t="n"/>
-      <c r="K38" s="37" t="n"/>
-      <c r="L38" s="37" t="n"/>
-      <c r="M38" s="37" t="n"/>
-      <c r="N38" s="37" t="n"/>
-      <c r="O38" s="37" t="n"/>
-      <c r="P38" s="37" t="n"/>
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D38" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F38" s="37" t="inlineStr"/>
+      <c r="G38" s="37" t="inlineStr"/>
+      <c r="H38" s="37" t="inlineStr"/>
+      <c r="I38" s="37" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="J38" s="37" t="inlineStr">
+        <is>
+          <t>wu_zhi_lan</t>
+        </is>
+      </c>
+      <c r="K38" s="37" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="L38" s="37" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
+        </is>
+      </c>
+      <c r="M38" s="37" t="inlineStr"/>
+      <c r="N38" s="37" t="inlineStr"/>
+      <c r="O38" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="n"/>
-      <c r="B39" s="37" t="n"/>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="37" t="n"/>
-      <c r="F39" s="37" t="n"/>
-      <c r="G39" s="37" t="n"/>
-      <c r="H39" s="37" t="n"/>
-      <c r="I39" s="37" t="n"/>
-      <c r="J39" s="37" t="n"/>
-      <c r="K39" s="37" t="n"/>
-      <c r="L39" s="37" t="n"/>
-      <c r="M39" s="37" t="n"/>
-      <c r="N39" s="37" t="n"/>
-      <c r="O39" s="37" t="n"/>
-      <c r="P39" s="37" t="n"/>
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_cured</t>
+        </is>
+      </c>
+      <c r="D39" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr"/>
+      <c r="G39" s="37" t="inlineStr"/>
+      <c r="H39" s="37" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="I39" s="37" t="inlineStr"/>
+      <c r="J39" s="37" t="inlineStr"/>
+      <c r="K39" s="37" t="inlineStr"/>
+      <c r="L39" s="37" t="inlineStr"/>
+      <c r="M39" s="37" t="inlineStr"/>
+      <c r="N39" s="37" t="inlineStr"/>
+      <c r="O39" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="n"/>
-      <c r="B40" s="37" t="n"/>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
-      <c r="H40" s="37" t="n"/>
-      <c r="I40" s="37" t="n"/>
-      <c r="J40" s="37" t="n"/>
-      <c r="K40" s="37" t="n"/>
-      <c r="L40" s="37" t="n"/>
-      <c r="M40" s="37" t="n"/>
-      <c r="N40" s="37" t="n"/>
-      <c r="O40" s="37" t="n"/>
-      <c r="P40" s="37" t="n"/>
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>023_03</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>023治疗失败</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D40" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F40" s="37" t="inlineStr"/>
+      <c r="G40" s="37" t="inlineStr"/>
+      <c r="H40" s="37" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="I40" s="37" t="inlineStr"/>
+      <c r="J40" s="37" t="inlineStr"/>
+      <c r="K40" s="37" t="inlineStr"/>
+      <c r="L40" s="37" t="inlineStr"/>
+      <c r="M40" s="37" t="inlineStr"/>
+      <c r="N40" s="37" t="inlineStr"/>
+      <c r="O40" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="37" t="n"/>
@@ -7444,7 +7540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J258"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
@@ -7457,8 +7553,8 @@
     <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
     <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="34"/>
-    <col width="8.875" customWidth="1" style="36" min="35" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="35"/>
+    <col width="8.875" customWidth="1" style="36" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9841,7 +9937,7 @@
       <c r="I59" s="51" t="inlineStr"/>
       <c r="J59" s="53" t="inlineStr">
         <is>
-          <t>名声+1000</t>
+          <t>名望+1000</t>
         </is>
       </c>
     </row>
@@ -17580,6 +17676,448 @@
       <c r="J258" s="50" t="inlineStr">
         <is>
           <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B259" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C259" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E259" s="52" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F259" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G259" s="51" t="inlineStr"/>
+      <c r="H259" s="53" t="inlineStr"/>
+      <c r="I259" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J259" s="52" t="inlineStr">
+        <is>
+          <t>少掌柜的，夫人在屋里晕倒了，您快来看看啊！</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B260" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C260" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D260" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E260" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F260" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G260" s="51" t="inlineStr"/>
+      <c r="H260" s="53" t="inlineStr"/>
+      <c r="I260" s="51" t="inlineStr"/>
+      <c r="J260" s="52" t="inlineStr">
+        <is>
+          <t>芷兰！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B261" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C261" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D261" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E261" s="52" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F261" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G261" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H261" s="53" t="inlineStr"/>
+      <c r="I261" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/023/023.png</t>
+        </is>
+      </c>
+      <c r="J261" s="52" t="inlineStr">
+        <is>
+          <t>…...</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B262" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C262" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D262" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E262" s="52" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F262" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G262" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H262" s="53" t="inlineStr"/>
+      <c r="I262" s="51" t="inlineStr"/>
+      <c r="J262" s="52" t="inlineStr">
+        <is>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B263" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C263" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D263" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E263" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F263" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G263" s="51" t="inlineStr"/>
+      <c r="H263" s="51" t="inlineStr"/>
+      <c r="I263" s="51" t="inlineStr"/>
+      <c r="J263" s="52" t="inlineStr">
+        <is>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B264" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C264" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E264" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F264" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G264" s="51" t="inlineStr"/>
+      <c r="H264" s="53" t="inlineStr"/>
+      <c r="I264" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/023/023.png</t>
+        </is>
+      </c>
+      <c r="J264" s="50" t="inlineStr">
+        <is>
+          <t>呜呜呜，夫人到底是得了什么病啊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B265" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C265" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E265" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F265" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G265" s="51" t="inlineStr"/>
+      <c r="H265" s="53" t="inlineStr"/>
+      <c r="I265" s="51" t="inlineStr"/>
+      <c r="J265" s="50" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B266" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C266" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D266" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E266" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F266" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G266" s="51" t="inlineStr"/>
+      <c r="H266" s="53" t="inlineStr"/>
+      <c r="I266" s="51" t="inlineStr"/>
+      <c r="J266" s="50" t="inlineStr">
+        <is>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B267" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C267" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D267" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E267" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F267" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G267" s="51" t="inlineStr"/>
+      <c r="H267" s="51" t="inlineStr"/>
+      <c r="I267" s="51" t="inlineStr"/>
+      <c r="J267" s="54" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B268" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C268" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D268" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E268" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F268" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G268" s="51" t="inlineStr"/>
+      <c r="H268" s="51" t="inlineStr"/>
+      <c r="I268" s="51" t="inlineStr"/>
+      <c r="J268" s="50" t="inlineStr">
+        <is>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="50" t="inlineStr">
+        <is>
+          <t>023_03</t>
+        </is>
+      </c>
+      <c r="B269" s="50" t="inlineStr">
+        <is>
+          <t>023治疗失败</t>
+        </is>
+      </c>
+      <c r="C269" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E269" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F269" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G269" s="51" t="inlineStr"/>
+      <c r="H269" s="53" t="inlineStr"/>
+      <c r="I269" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/023/023.png</t>
+        </is>
+      </c>
+      <c r="J269" s="50" t="inlineStr">
+        <is>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
         </is>
       </c>
     </row>
@@ -19660,8 +20198,8 @@
     <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="108"/>
-    <col width="9" customWidth="1" style="9" min="109" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="109"/>
+    <col width="9" customWidth="1" style="9" min="110" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,9 +27,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -136,10 +136,17 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -409,9 +416,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2374,20 +2382,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.1328125" customWidth="1" style="23" min="10" max="62"/>
-    <col width="9.1328125" customWidth="1" style="23" min="63" max="16384"/>
+    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="63"/>
+    <col width="9.125" customWidth="1" style="23" min="64" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -3020,17 +3028,17 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>wang_wu</t>
+          <t>liu_jing_ting</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -3039,43 +3047,27 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>大夫，我这两天</t>
-        </is>
-      </c>
-      <c r="G22" s="43" t="inlineStr">
-        <is>
-          <t>给我看看吧。</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>多谢大夫，感觉好多了。</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>还是好难受啊…</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="43" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>wang_da_sao</t>
+          <t>xie_fei_yan</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>王大嫂</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3084,43 +3076,27 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>先生，俺这两天</t>
-        </is>
-      </c>
-      <c r="G23" s="43" t="inlineStr">
-        <is>
-          <t>您帮俺瞧瞧吧。</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>麻烦先生了，我感觉好多了</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>哎哟...哎哟…</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>wang_chao_feng</t>
+          <t>wang_bai_tang</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>王朝奉</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3129,43 +3105,27 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>咳咳，我最近</t>
-        </is>
-      </c>
-      <c r="G24" s="43" t="inlineStr">
-        <is>
-          <t>您帮老夫瞧瞧吧。</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>好多了，多谢大夫。</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>你给我开的什么药啊…</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="43" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>wang_lao_an_ren</t>
+          <t>jin_yi_ma</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>王老安人</t>
+          <t>金姨妈</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>story</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -3174,38 +3134,22 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>先生，老妇这两天</t>
-        </is>
-      </c>
-      <c r="G25" s="43" t="inlineStr">
-        <is>
-          <t>劳烦您给我看看。</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>真是多谢先生了，好多了</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>咳咳咳，哎哟...</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="43" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>huang_niu_er</t>
+          <t>wang_wu</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>黄牛儿</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -3219,38 +3163,38 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>哎哟大夫，我</t>
+          <t>大夫，我这两天</t>
         </is>
       </c>
       <c r="G26" s="43" t="inlineStr">
         <is>
-          <t>快给我看看吧。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>真是太谢谢大夫了。</t>
+          <t>多谢大夫，感觉好多了。</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>感觉不太对啊…</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>huang_qiu_ju</t>
+          <t>wang_da_sao</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>黄秋菊</t>
+          <t>王大嫂</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3264,38 +3208,38 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>我这两天</t>
+          <t>先生，俺这两天</t>
         </is>
       </c>
       <c r="G27" s="43" t="inlineStr">
         <is>
-          <t>请您给小女看看吧。</t>
+          <t>您帮俺瞧瞧吧。</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>麻烦先生了，我感觉好多了</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>还是好难受啊…</t>
+          <t>哎哟...哎哟…</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>he_zhang_shao</t>
+          <t>wang_chao_feng</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>何掌勺</t>
+          <t>王朝奉</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -3309,38 +3253,38 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>咳咳，我最近</t>
         </is>
       </c>
       <c r="G28" s="43" t="inlineStr">
         <is>
-          <t>大夫快给我看看吧。</t>
+          <t>您帮老夫瞧瞧吧。</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>好多了，多谢大夫。</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>还是好难受啊…</t>
+          <t>你给我开的什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>zhou_lu_an</t>
+          <t>wang_lao_an_ren</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>周炉安</t>
+          <t>王老安人</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -3350,42 +3294,42 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几天</t>
+          <t>先生，老妇这两天</t>
         </is>
       </c>
       <c r="G29" s="43" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>劳烦您给我看看。</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>真是多谢先生了，好多了</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>先生，我这病怎么还不见好？</t>
+          <t>咳咳咳，哎哟...</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>jiang_chuan_er</t>
+          <t>huang_niu_er</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>蒋船儿</t>
+          <t>黄牛儿</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -3399,38 +3343,38 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这几天</t>
+          <t>哎哟大夫，我</t>
         </is>
       </c>
       <c r="G30" s="43" t="inlineStr">
         <is>
-          <t>给我看看吧。</t>
+          <t>快给我看看吧。</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>真是太谢谢大夫了。</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>感觉不太对啊…</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>qin_san_niang</t>
+          <t>huang_qiu_ju</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>秦三娘</t>
+          <t>黄秋菊</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3444,38 +3388,38 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>咳咳，大夫，我这几日</t>
+          <t>我这两天</t>
         </is>
       </c>
       <c r="G31" s="43" t="inlineStr">
         <is>
-          <t>劳烦您给我看看。</t>
+          <t>请您给小女看看吧。</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>多谢先生，我好多了。</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>哎哟...哎哟…</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>shi_gan</t>
+          <t>he_zhang_shao</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>石敢</t>
+          <t>何掌勺</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3489,38 +3433,38 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>咳咳，先生我这两天</t>
+          <t>先生，我最近</t>
         </is>
       </c>
       <c r="G32" s="43" t="inlineStr">
         <is>
-          <t>您快帮我看看吧。</t>
+          <t>大夫快给我看看吧。</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>哎呀，真是太感谢了，好多了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>cha_bo_shi</t>
+          <t>zhou_lu_an</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>茶博士</t>
+          <t>周炉安</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -3534,38 +3478,38 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>我最近几日</t>
+          <t>先生，我这几天</t>
         </is>
       </c>
       <c r="G33" s="43" t="inlineStr">
         <is>
-          <t>劳烦先生给小可看看。</t>
+          <t>麻烦您给我看看。</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>哎呀，真是多谢先生了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>感觉更不舒服了…</t>
+          <t>先生，我这病怎么还不见好？</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>shen_gui</t>
+          <t>jiang_chuan_er</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>沈贵</t>
+          <t>蒋船儿</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3579,38 +3523,38 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>哎哟哟，我</t>
+          <t>大夫，我这几天</t>
         </is>
       </c>
       <c r="G34" s="43" t="inlineStr">
         <is>
-          <t>快给我看看吧。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>多谢多谢。</t>
+          <t>多谢先生，我好多了。</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>你会不会看病啊？</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>li_gou_dan</t>
+          <t>qin_san_niang</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>李狗蛋</t>
+          <t>秦三娘</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -3620,42 +3564,42 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>先生，俺这两天</t>
+          <t>咳咳，大夫，我这几日</t>
         </is>
       </c>
       <c r="G35" s="43" t="inlineStr">
         <is>
-          <t>请您给俺看看吧。</t>
+          <t>劳烦您给我看看。</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>真是太谢谢大夫了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>哎哟...哎哟…</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>li_si</t>
+          <t>shi_gan</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>石敢</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -3669,38 +3613,38 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几天</t>
+          <t>咳咳，先生我这两天</t>
         </is>
       </c>
       <c r="G36" s="43" t="inlineStr">
         <is>
-          <t>麻烦您帮我看看吧。</t>
+          <t>您快帮我看看吧。</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我感觉好多了。</t>
+          <t>哎呀，真是太感谢了，好多了。</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这病怎么还不见好？</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>li_jiang_shi</t>
+          <t>cha_bo_shi</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>李姜氏</t>
+          <t>茶博士</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -3710,42 +3654,42 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>我最近几日</t>
         </is>
       </c>
       <c r="G37" s="43" t="inlineStr">
         <is>
-          <t>劳烦先生给我看看。</t>
+          <t>劳烦先生给小可看看。</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>先生医术真是高明，多谢了</t>
+          <t>哎呀，真是多谢先生了。</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>嗯？感觉好奇怪啊…</t>
+          <t>感觉更不舒服了…</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>li_yuan_wai</t>
+          <t>shen_gui</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>李员外</t>
+          <t>沈贵</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -3759,38 +3703,38 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>小郎中啊，老夫这几日</t>
+          <t>哎哟哟，我</t>
         </is>
       </c>
       <c r="G38" s="43" t="inlineStr">
         <is>
-          <t>你给老夫瞧瞧。</t>
+          <t>快给我看看吧。</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>嗯，不错不错，医术高明啊。</t>
+          <t>多谢多谢。</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>你这庸医，招摇撞骗！</t>
+          <t>你会不会看病啊？</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>yan_po</t>
+          <t>li_gou_dan</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>严婆</t>
+          <t>李狗蛋</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -3800,42 +3744,42 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>先生，老妇这两天</t>
+          <t>先生，俺这两天</t>
         </is>
       </c>
       <c r="G39" s="43" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>请您给俺看看吧。</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>感觉好多了，多谢先生。</t>
+          <t>真是太谢谢大夫了。</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，哎哟...</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>yan_bu_tou</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>严捕头</t>
+          <t>li_si</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>李四</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -3849,38 +3793,38 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>先生，我这几天</t>
         </is>
       </c>
       <c r="G40" s="43" t="inlineStr">
         <is>
-          <t>烦请先生给看看。</t>
+          <t>麻烦您帮我看看吧。</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>好多了，多谢先生。</t>
+          <t>多谢先生，我感觉好多了。</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>大夫，我这病怎么还不见好？</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>feng_jun_bao</t>
+          <t>li_jiang_shi</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>冯军保</t>
+          <t>李姜氏</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -3890,11 +3834,11 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -3903,29 +3847,29 @@
       </c>
       <c r="G41" s="43" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>劳烦先生给我看看。</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>先生医术真是高明，多谢了</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>嗯？感觉好奇怪啊…</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>liu_tai_gong</t>
+          <t>li_yuan_wai</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>刘太公</t>
+          <t>李员外</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -3939,38 +3883,38 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>先生啊，老朽这几日</t>
+          <t>小郎中啊，老夫这几日</t>
         </is>
       </c>
       <c r="G42" s="43" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>你给老夫瞧瞧。</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>麻烦大夫啦，好多了。</t>
+          <t>嗯，不错不错，医术高明啊。</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，哎哟…</t>
+          <t>你这庸医，招摇撞骗！</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>liu_da</t>
+          <t>yan_po</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>刘大</t>
+          <t>严婆</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -3980,42 +3924,42 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>大夫，俺这两天</t>
+          <t>先生，老妇这两天</t>
         </is>
       </c>
       <c r="G43" s="43" t="inlineStr">
         <is>
-          <t>麻烦您帮俺看看吧。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>多谢大夫，感觉好多了。</t>
+          <t>感觉好多了，多谢先生。</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>感觉不太对啊…</t>
+          <t>咳咳咳，哎哟...</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>liu_wen_po</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>刘稳婆</t>
+          <t>yan_bu_tou</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>严捕头</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -4025,42 +3969,42 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>先生啊，俺这几天</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G44" s="43" t="inlineStr">
         <is>
-          <t>请您给俺看看吧。</t>
+          <t>烦请先生给看看。</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>哎哟，谢谢先生，您真是神医啊！</t>
+          <t>好多了，多谢先生。</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>哎，不对啊…</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>liu_fu</t>
+          <t>feng_jun_bao</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>刘福</t>
+          <t>冯军保</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -4074,38 +4018,38 @@
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>大夫，我最近</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G45" s="43" t="inlineStr">
         <is>
-          <t>给我看看吧。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>呃...不对啊。</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>hua_jin_niang</t>
+          <t>liu_tai_gong</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>华锦娘</t>
+          <t>刘太公</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -4115,42 +4059,42 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>我这几日</t>
+          <t>先生啊，老朽这几日</t>
         </is>
       </c>
       <c r="G46" s="43" t="inlineStr">
         <is>
-          <t>劳烦先生您给小妇看看吧。</t>
+          <t>麻烦您给我看看。</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>麻烦大夫啦，好多了。</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>咳咳咳，哎哟…</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>lv_tai_jun</t>
+          <t>liu_da</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>吕太君</t>
+          <t>刘大</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -4160,42 +4104,42 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>小先生啊，老婆子我最近</t>
+          <t>大夫，俺这两天</t>
         </is>
       </c>
       <c r="G47" s="43" t="inlineStr">
         <is>
-          <t>您给我瞧瞧。</t>
+          <t>麻烦您帮俺看看吧。</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>多谢小先生，老婆子我好多啦。</t>
+          <t>多谢大夫，感觉好多了。</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，你这开的是什么药啊？</t>
+          <t>感觉不太对啊…</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>wu_ban_tou</t>
+          <t>liu_wen_po</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>吴班头</t>
+          <t>刘稳婆</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -4205,42 +4149,42 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>先生啊，俺这几天</t>
         </is>
       </c>
       <c r="G48" s="43" t="inlineStr">
         <is>
-          <t>您快帮我看看吧。</t>
+          <t>请您给俺看看吧。</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>有劳先生了，感觉好多了。</t>
+          <t>哎哟，谢谢先生，您真是神医啊！</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>他娘的，你给我吃的是什么？</t>
+          <t>哎，不对啊…</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>sun_jiang_er</t>
+          <t>liu_fu</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>孙匠儿</t>
+          <t>刘福</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -4254,16 +4198,16 @@
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>大夫，我最近</t>
         </is>
       </c>
       <c r="G49" s="43" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>给我看看吧。</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -4273,19 +4217,19 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>呃…不对啊</t>
+          <t>呃...不对啊。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>sun_xiao_mei</t>
+          <t>hua_jin_niang</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>孙小妹</t>
+          <t>华锦娘</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -4299,38 +4243,38 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几天</t>
+          <t>我这几日</t>
         </is>
       </c>
       <c r="G50" s="43" t="inlineStr">
         <is>
-          <t>请您帮我看看吧。</t>
+          <t>劳烦先生您给小妇看看吧。</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，好难受啊</t>
+          <t>您给我开的这是什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>zhang_san</t>
+          <t>lv_tai_jun</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>吕太君</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -4340,42 +4284,42 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这几天</t>
+          <t>小先生啊，老婆子我最近</t>
         </is>
       </c>
       <c r="G51" s="43" t="inlineStr">
         <is>
-          <t>帮我看看吧。</t>
+          <t>您给我瞧瞧。</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>多谢大夫，我好多了。</t>
+          <t>多谢小先生，老婆子我好多啦。</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>咳咳咳，你这开的是什么药啊？</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>zhang_tu</t>
+          <t>wu_ban_tou</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>张屠</t>
+          <t>吴班头</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -4389,38 +4333,38 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>哎哟大夫，俺</t>
+          <t>先生，我最近</t>
         </is>
       </c>
       <c r="G52" s="43" t="inlineStr">
         <is>
-          <t>快给俺看看吧。</t>
+          <t>您快帮我看看吧。</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>哈哈哈，太谢谢了。</t>
+          <t>有劳先生了，感觉好多了。</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>他娘的怎么感觉怪怪的</t>
+          <t>他娘的，你给我吃的是什么？</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>zhang_you_shi</t>
+          <t>sun_jiang_er</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>张尤氏</t>
+          <t>孙匠儿</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -4430,42 +4374,42 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>我最近几天</t>
+          <t>先生，我这几日</t>
         </is>
       </c>
       <c r="G53" s="43" t="inlineStr">
         <is>
-          <t>请先生给我看看吧</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，感觉好多了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>呃…不对啊</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>yang_xiu_cai</t>
+          <t>sun_xiao_mei</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>杨秀才</t>
+          <t>孙小妹</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -4475,42 +4419,42 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>大夫，学生这几日</t>
+          <t>先生，我这几天</t>
         </is>
       </c>
       <c r="G54" s="43" t="inlineStr">
         <is>
-          <t>请您给看看吧。</t>
+          <t>请您帮我看看吧。</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>有劳大夫了，我好多了。</t>
+          <t>多谢先生了。</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>咳咳咳，好难受啊</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>su_xiu_he</t>
-        </is>
-      </c>
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>苏绣荷</t>
+          <t>zhang_san</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>张三</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -4520,42 +4464,42 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>大夫，我这几天</t>
         </is>
       </c>
       <c r="G55" s="43" t="inlineStr">
         <is>
-          <t>麻烦您给小女子看看吧。</t>
+          <t>帮我看看吧。</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>好多了，真是太谢谢先生了。</t>
+          <t>多谢大夫，我好多了。</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>咳咳咳，好难受啊</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>xu_xiang_jun</t>
+          <t>zhang_tu</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>许香君</t>
+          <t>张屠</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -4565,42 +4509,42 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>先生，我这几日</t>
+          <t>哎哟大夫，俺</t>
         </is>
       </c>
       <c r="G56" s="43" t="inlineStr">
         <is>
-          <t>烦请先生给奴家看看。</t>
+          <t>快给俺看看吧。</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>多谢先生了，我好多了。</t>
+          <t>哈哈哈，太谢谢了。</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>您给我开的这是什么药啊…</t>
+          <t>他娘的怎么感觉怪怪的</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>xie_fei_yan</t>
+          <t>zhang_you_shi</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>张尤氏</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -4614,38 +4558,38 @@
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>先生，我这两天</t>
+          <t>我最近几天</t>
         </is>
       </c>
       <c r="G57" s="43" t="inlineStr">
         <is>
-          <t>劳烦先生给妾身看看。</t>
+          <t>请先生给我看看吧</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>感觉好多了，真是太谢谢先生了。</t>
+          <t>多谢先生，感觉好多了。</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>哎哟…感觉更难受了…</t>
+          <t>嗯…哎哟…</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>zhao_ya_po</t>
+          <t>yang_xiu_cai</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>赵牙婆</t>
+          <t>杨秀才</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -4655,42 +4599,42 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>大夫，老婆子我这几日</t>
+          <t>大夫，学生这几日</t>
         </is>
       </c>
       <c r="G58" s="43" t="inlineStr">
         <is>
-          <t>劳烦您给我看看。</t>
+          <t>请您给看看吧。</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>哎哟，谢谢先生，您真是神医啊！</t>
+          <t>有劳大夫了，我好多了。</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>哎，不对啊…</t>
+          <t>您给我开的这是什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>zhao_liu</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>赵六</t>
+          <t>su_xiu_he</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>苏绣荷</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -4700,7 +4644,7 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
@@ -4708,34 +4652,34 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>先生，我这几日</t>
         </is>
       </c>
       <c r="G59" s="43" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>麻烦您给小女子看看吧。</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>好多了，真是太谢谢先生了。</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>还是好难受啊…</t>
+          <t>咳咳咳，好难受啊</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>zheng_er_jie</t>
+          <t>xu_xiang_jun</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>郑二姐</t>
+          <t>许香君</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -4749,38 +4693,38 @@
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>先生，我最近</t>
+          <t>先生，我这几日</t>
         </is>
       </c>
       <c r="G60" s="43" t="inlineStr">
         <is>
-          <t>麻烦您给我看看。</t>
+          <t>烦请先生给奴家看看。</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>有劳先生了，感觉好多了。</t>
+          <t>多谢先生了，我好多了。</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>哎…奇怪…</t>
+          <t>您给我开的这是什么药啊…</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>qian_bu_lou</t>
+          <t>zhao_ya_po</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>钱不漏</t>
+          <t>赵牙婆</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -4790,42 +4734,42 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>我最近</t>
+          <t>大夫，老婆子我这几日</t>
         </is>
       </c>
       <c r="G61" s="43" t="inlineStr">
         <is>
-          <t>快快，快给我看看。</t>
+          <t>劳烦您给我看看。</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>谢啦。</t>
+          <t>哎哟，谢谢先生，您真是神医啊！</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>这开的是什么药，我要到官府告你！</t>
+          <t>哎，不对啊…</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>chen_shan_zhang</t>
-        </is>
-      </c>
-      <c r="B62" s="46" t="inlineStr">
-        <is>
-          <t>陈山长</t>
+          <t>zhao_liu</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -4839,38 +4783,38 @@
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>大夫，我这几日</t>
+          <t>先生，我最近</t>
         </is>
       </c>
       <c r="G62" s="43" t="inlineStr">
         <is>
-          <t>劳烦您给我看看。</t>
+          <t>麻烦您给我看看。</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>大夫真是妙手回春啊。</t>
+          <t>多谢先生，我好多了。</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>医术不精，还敢自称郎中！</t>
+          <t>还是好难受啊…</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>chen_er</t>
+          <t>zheng_er_jie</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>陈二</t>
+          <t>郑二姐</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -4880,11 +4824,11 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -4893,29 +4837,29 @@
       </c>
       <c r="G63" s="43" t="inlineStr">
         <is>
-          <t>帮我看看吧。</t>
+          <t>麻烦您给我看看。</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>多谢先生，我好多了。</t>
+          <t>有劳先生了，感觉好多了。</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>嗯…哎哟…</t>
+          <t>哎…奇怪…</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>chen_po</t>
+          <t>qian_bu_lou</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>陈婆</t>
+          <t>钱不漏</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -4925,155 +4869,257 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>先生，老婆子我这几日</t>
+          <t>我最近</t>
         </is>
       </c>
       <c r="G64" s="43" t="inlineStr">
         <is>
-          <t>您快帮我看看吧。</t>
+          <t>快快，快给我看看。</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>真是太谢谢先生了。</t>
+          <t>谢啦。</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>感觉不太对啊…</t>
+          <t>这开的是什么药，我要到官府告你！</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
+          <t>chen_shan_zhang</t>
+        </is>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>陈山长</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>大夫，我这几日</t>
+        </is>
+      </c>
+      <c r="G65" s="43" t="inlineStr">
+        <is>
+          <t>劳烦您给我看看。</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>大夫真是妙手回春啊。</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>医术不精，还敢自称郎中！</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>chen_er</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>陈二</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>先生，我最近</t>
+        </is>
+      </c>
+      <c r="G66" s="43" t="inlineStr">
+        <is>
+          <t>帮我看看吧。</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>多谢先生，我好多了。</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>嗯…哎哟…</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>chen_po</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>陈婆</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>先生，老婆子我这几日</t>
+        </is>
+      </c>
+      <c r="G67" s="43" t="inlineStr">
+        <is>
+          <t>您快帮我看看吧。</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>真是太谢谢先生了。</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>感觉不太对啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
           <t>han_zhang_gui</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>韩掌柜</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E68" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>大夫，我这两天</t>
         </is>
       </c>
-      <c r="G65" s="43" t="inlineStr">
+      <c r="G68" s="43" t="inlineStr">
         <is>
           <t>劳烦您给我看看。</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>多谢大夫啦。</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>大夫，我这病怎么还不见好？</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>yao_zhang_gui</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>姚掌柜</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E69" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>先生，我这两天</t>
         </is>
       </c>
-      <c r="G66" s="43" t="inlineStr">
+      <c r="G69" s="43" t="inlineStr">
         <is>
           <t>请您给看看。</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>多谢先生，我好多了。</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>大夫，我这病怎么还不见好？</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="7" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="43" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="7" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
-      <c r="G68" s="43" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="43" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="7" t="n"/>
@@ -5151,6 +5197,39 @@
       <c r="G76" s="43" t="n"/>
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="43" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="7" t="n"/>
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="43" t="n"/>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="43" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1">
@@ -5170,13 +5249,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5389,27 +5468,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.59765625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.46484375" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="18.3984375" customWidth="1" style="36" min="7" max="7"/>
-    <col width="16.265625" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
-    <col width="15.59765625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
-    <col width="12.265625" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="8.46484375" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="29.73046875" customWidth="1" style="36" min="12" max="12"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="14.625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="14.25" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.5" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="18.375" customWidth="1" style="36" min="7" max="7"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
+    <col width="15.625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="12.25" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="29.75" customWidth="1" style="36" min="12" max="12"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="10.73046875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="10.86328125" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="85"/>
-    <col width="9" customWidth="1" style="36" min="86" max="16384"/>
+    <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="9" customWidth="1" style="36" min="17" max="86"/>
+    <col width="9" customWidth="1" style="36" min="87" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7128,7 +7207,7 @@
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>柳敬亭温燥证</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
@@ -7151,22 +7230,22 @@
       <c r="H35" s="37" t="inlineStr"/>
       <c r="I35" s="37" t="inlineStr">
         <is>
-          <t>肾精不足</t>
+          <t>温燥证</t>
         </is>
       </c>
       <c r="J35" s="37" t="inlineStr">
         <is>
-          <t>xing_kong</t>
+          <t>liu_jing_ting</t>
         </is>
       </c>
       <c r="K35" s="37" t="inlineStr">
         <is>
-          <t>肾精不足</t>
+          <t>温燥证</t>
         </is>
       </c>
       <c r="L35" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
+          <t>res://Assets/Portrait/StoryNpc/liu_jing_ting/liu_jing_ting.png</t>
         </is>
       </c>
       <c r="M35" s="37" t="inlineStr"/>
@@ -7208,7 +7287,7 @@
       <c r="G36" s="37" t="inlineStr"/>
       <c r="H36" s="37" t="inlineStr">
         <is>
-          <t>008_01</t>
+          <t>022_01</t>
         </is>
       </c>
       <c r="I36" s="37" t="inlineStr"/>
@@ -7254,7 +7333,7 @@
       <c r="G37" s="37" t="inlineStr"/>
       <c r="H37" s="37" t="inlineStr">
         <is>
-          <t>008_01</t>
+          <t>022_01</t>
         </is>
       </c>
       <c r="I37" s="37" t="inlineStr"/>
@@ -7278,7 +7357,7 @@
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>谢飞燕肺气虚</t>
         </is>
       </c>
       <c r="C38" s="37" t="inlineStr">
@@ -7301,22 +7380,22 @@
       <c r="H38" s="37" t="inlineStr"/>
       <c r="I38" s="37" t="inlineStr">
         <is>
-          <t>妊娠</t>
+          <t>肺气虚</t>
         </is>
       </c>
       <c r="J38" s="37" t="inlineStr">
         <is>
-          <t>wu_zhi_lan</t>
+          <t>xie_fei_yan</t>
         </is>
       </c>
       <c r="K38" s="37" t="inlineStr">
         <is>
-          <t>妊娠</t>
+          <t>肺气虚</t>
         </is>
       </c>
       <c r="L38" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
+          <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
         </is>
       </c>
       <c r="M38" s="37" t="inlineStr"/>
@@ -7414,119 +7493,461 @@
       <c r="M40" s="37" t="inlineStr"/>
       <c r="N40" s="37" t="inlineStr"/>
       <c r="O40" s="37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="n"/>
-      <c r="B41" s="37" t="n"/>
-      <c r="C41" s="37" t="n"/>
-      <c r="D41" s="37" t="n"/>
-      <c r="E41" s="37" t="n"/>
-      <c r="F41" s="37" t="n"/>
-      <c r="G41" s="37" t="n"/>
-      <c r="H41" s="37" t="n"/>
-      <c r="I41" s="37" t="n"/>
-      <c r="J41" s="37" t="n"/>
-      <c r="K41" s="37" t="n"/>
-      <c r="L41" s="37" t="n"/>
-      <c r="M41" s="37" t="n"/>
-      <c r="N41" s="37" t="n"/>
-      <c r="O41" s="37" t="n"/>
-      <c r="P41" s="37" t="n"/>
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>谢飞燕肺阴虚</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D41" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="inlineStr"/>
+      <c r="G41" s="37" t="inlineStr"/>
+      <c r="H41" s="37" t="inlineStr"/>
+      <c r="I41" s="37" t="inlineStr">
+        <is>
+          <t>肺阴虚</t>
+        </is>
+      </c>
+      <c r="J41" s="37" t="inlineStr">
+        <is>
+          <t>xie_fei_yan</t>
+        </is>
+      </c>
+      <c r="K41" s="37" t="inlineStr">
+        <is>
+          <t>肺阴虚</t>
+        </is>
+      </c>
+      <c r="L41" s="37" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
+        </is>
+      </c>
+      <c r="M41" s="37" t="inlineStr"/>
+      <c r="N41" s="37" t="inlineStr"/>
+      <c r="O41" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="37" t="n"/>
-      <c r="B42" s="37" t="n"/>
-      <c r="C42" s="37" t="n"/>
-      <c r="D42" s="37" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="37" t="n"/>
-      <c r="G42" s="37" t="n"/>
-      <c r="H42" s="37" t="n"/>
-      <c r="I42" s="37" t="n"/>
-      <c r="J42" s="37" t="n"/>
-      <c r="K42" s="37" t="n"/>
-      <c r="L42" s="37" t="n"/>
-      <c r="M42" s="37" t="n"/>
-      <c r="N42" s="37" t="n"/>
-      <c r="O42" s="37" t="n"/>
-      <c r="P42" s="37" t="n"/>
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_cured</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr"/>
+      <c r="G42" s="37" t="inlineStr"/>
+      <c r="H42" s="37" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="I42" s="37" t="inlineStr"/>
+      <c r="J42" s="37" t="inlineStr"/>
+      <c r="K42" s="37" t="inlineStr"/>
+      <c r="L42" s="37" t="inlineStr"/>
+      <c r="M42" s="37" t="inlineStr"/>
+      <c r="N42" s="37" t="inlineStr"/>
+      <c r="O42" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="n"/>
-      <c r="B43" s="37" t="n"/>
-      <c r="C43" s="37" t="n"/>
-      <c r="D43" s="37" t="n"/>
-      <c r="E43" s="37" t="n"/>
-      <c r="F43" s="37" t="n"/>
-      <c r="G43" s="37" t="n"/>
-      <c r="H43" s="37" t="n"/>
-      <c r="I43" s="37" t="n"/>
-      <c r="J43" s="37" t="n"/>
-      <c r="K43" s="37" t="n"/>
-      <c r="L43" s="37" t="n"/>
-      <c r="M43" s="37" t="n"/>
-      <c r="N43" s="37" t="n"/>
-      <c r="O43" s="37" t="n"/>
-      <c r="P43" s="37" t="n"/>
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>024_03</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>024治疗失败</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D43" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr"/>
+      <c r="G43" s="37" t="inlineStr"/>
+      <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="I43" s="37" t="inlineStr"/>
+      <c r="J43" s="37" t="inlineStr"/>
+      <c r="K43" s="37" t="inlineStr"/>
+      <c r="L43" s="37" t="inlineStr"/>
+      <c r="M43" s="37" t="inlineStr"/>
+      <c r="N43" s="37" t="inlineStr"/>
+      <c r="O43" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="37" t="n"/>
-      <c r="B44" s="37" t="n"/>
-      <c r="C44" s="37" t="n"/>
-      <c r="D44" s="37" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="37" t="n"/>
-      <c r="G44" s="37" t="n"/>
-      <c r="H44" s="37" t="n"/>
-      <c r="I44" s="37" t="n"/>
-      <c r="J44" s="37" t="n"/>
-      <c r="K44" s="37" t="n"/>
-      <c r="L44" s="37" t="n"/>
-      <c r="M44" s="37" t="n"/>
-      <c r="N44" s="37" t="n"/>
-      <c r="O44" s="37" t="n"/>
-      <c r="P44" s="37" t="n"/>
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>和尚肾精不足</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr"/>
+      <c r="G44" s="37" t="inlineStr"/>
+      <c r="H44" s="37" t="inlineStr"/>
+      <c r="I44" s="37" t="inlineStr">
+        <is>
+          <t>肾精不足</t>
+        </is>
+      </c>
+      <c r="J44" s="37" t="inlineStr">
+        <is>
+          <t>xing_kong</t>
+        </is>
+      </c>
+      <c r="K44" s="37" t="inlineStr">
+        <is>
+          <t>肾精不足</t>
+        </is>
+      </c>
+      <c r="L44" s="37" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
+        </is>
+      </c>
+      <c r="M44" s="37" t="inlineStr"/>
+      <c r="N44" s="37" t="inlineStr"/>
+      <c r="O44" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="37" t="n"/>
-      <c r="B45" s="37" t="n"/>
-      <c r="C45" s="37" t="n"/>
-      <c r="D45" s="37" t="n"/>
-      <c r="E45" s="37" t="n"/>
-      <c r="F45" s="37" t="n"/>
-      <c r="G45" s="37" t="n"/>
-      <c r="H45" s="37" t="n"/>
-      <c r="I45" s="37" t="n"/>
-      <c r="J45" s="37" t="n"/>
-      <c r="K45" s="37" t="n"/>
-      <c r="L45" s="37" t="n"/>
-      <c r="M45" s="37" t="n"/>
-      <c r="N45" s="37" t="n"/>
-      <c r="O45" s="37" t="n"/>
-      <c r="P45" s="37" t="n"/>
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_cured</t>
+        </is>
+      </c>
+      <c r="D45" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr"/>
+      <c r="G45" s="37" t="inlineStr"/>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="I45" s="37" t="inlineStr"/>
+      <c r="J45" s="37" t="inlineStr"/>
+      <c r="K45" s="37" t="inlineStr"/>
+      <c r="L45" s="37" t="inlineStr"/>
+      <c r="M45" s="37" t="inlineStr"/>
+      <c r="N45" s="37" t="inlineStr"/>
+      <c r="O45" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="37" t="n"/>
-      <c r="B46" s="37" t="n"/>
-      <c r="C46" s="37" t="n"/>
-      <c r="D46" s="37" t="n"/>
-      <c r="E46" s="37" t="n"/>
-      <c r="F46" s="37" t="n"/>
-      <c r="G46" s="37" t="n"/>
-      <c r="H46" s="37" t="n"/>
-      <c r="I46" s="37" t="n"/>
-      <c r="J46" s="37" t="n"/>
-      <c r="K46" s="37" t="n"/>
-      <c r="L46" s="37" t="n"/>
-      <c r="M46" s="37" t="n"/>
-      <c r="N46" s="37" t="n"/>
-      <c r="O46" s="37" t="n"/>
-      <c r="P46" s="37" t="n"/>
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>025_03</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>022治疗失败</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D46" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E46" s="37" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F46" s="37" t="inlineStr"/>
+      <c r="G46" s="37" t="inlineStr"/>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="I46" s="37" t="inlineStr"/>
+      <c r="J46" s="37" t="inlineStr"/>
+      <c r="K46" s="37" t="inlineStr"/>
+      <c r="L46" s="37" t="inlineStr"/>
+      <c r="M46" s="37" t="inlineStr"/>
+      <c r="N46" s="37" t="inlineStr"/>
+      <c r="O46" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>scene_enter</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>wu_zhi_lan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>妊娠</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>story_npc_cured</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>026_03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>023治疗失败</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>story_npc_failed_retry</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7540,21 +7961,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J269"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.86328125" defaultRowHeight="18"/>
+  <dimension ref="A1:J336"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
-    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.86328125" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="8.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="150.46484375" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.86328125" customWidth="1" style="36" min="11" max="36"/>
-    <col width="8.86328125" customWidth="1" style="36" min="37" max="16384"/>
+    <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.875" customWidth="1" style="36" min="11" max="37"/>
+    <col width="8.875" customWidth="1" style="36" min="38" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8084,7 +8505,7 @@
       </c>
       <c r="G14" s="51" t="inlineStr"/>
       <c r="H14" s="53" t="inlineStr"/>
-      <c r="I14" s="70" t="inlineStr">
+      <c r="I14" s="72" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -8202,7 +8623,7 @@
       </c>
       <c r="G17" s="51" t="inlineStr"/>
       <c r="H17" s="53" t="inlineStr"/>
-      <c r="I17" s="70" t="inlineStr">
+      <c r="I17" s="72" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -9442,7 +9863,7 @@
         </is>
       </c>
       <c r="H49" s="53" t="inlineStr"/>
-      <c r="I49" s="70" t="inlineStr"/>
+      <c r="I49" s="72" t="inlineStr"/>
       <c r="J49" s="57" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -16955,7 +17376,7 @@
       </c>
       <c r="B245" s="50" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>柳敬亭温燥证</t>
         </is>
       </c>
       <c r="C245" s="50" t="n">
@@ -16968,7 +17389,7 @@
       </c>
       <c r="E245" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F245" s="51" t="inlineStr">
@@ -16976,20 +17397,16 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G245" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+      <c r="G245" s="51" t="inlineStr"/>
       <c r="H245" s="53" t="inlineStr"/>
       <c r="I245" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J245" s="54" t="inlineStr">
-        <is>
-          <t>贫僧法号性空，《中论》曰："众因缘生发，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+      <c r="J245" s="50" t="inlineStr">
+        <is>
+          <t>咳咳咳，咳咳，大夫，我这嗓子不知怎得，又疼又痒，咳得多，都哑了。</t>
         </is>
       </c>
     </row>
@@ -17001,7 +17418,7 @@
       </c>
       <c r="B246" s="50" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>柳敬亭温燥证</t>
         </is>
       </c>
       <c r="C246" s="50" t="n">
@@ -17025,9 +17442,9 @@
       <c r="G246" s="51" t="inlineStr"/>
       <c r="H246" s="53" t="inlineStr"/>
       <c r="I246" s="51" t="inlineStr"/>
-      <c r="J246" s="54" t="inlineStr">
-        <is>
-          <t>师傅请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
+      <c r="J246" s="50" t="inlineStr">
+        <is>
+          <t>是柳先生啊，快请坐。</t>
         </is>
       </c>
     </row>
@@ -17052,12 +17469,12 @@
       </c>
       <c r="E247" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F247" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G247" s="51" t="inlineStr"/>
@@ -17067,9 +17484,9 @@
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J247" s="54" t="inlineStr">
-        <is>
-          <t>师傅所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+      <c r="J247" s="50" t="inlineStr">
+        <is>
+          <t>哎呀，舒服多了。</t>
         </is>
       </c>
     </row>
@@ -17094,24 +17511,20 @@
       </c>
       <c r="E248" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F248" s="51" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G248" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G248" s="51" t="inlineStr"/>
       <c r="H248" s="53" t="inlineStr"/>
       <c r="I248" s="51" t="inlineStr"/>
       <c r="J248" s="50" t="inlineStr">
         <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+          <t>您这是温燥证，整日说书久坐少动，伤津耗气，易生内热。</t>
         </is>
       </c>
     </row>
@@ -17147,9 +17560,9 @@
       <c r="G249" s="51" t="inlineStr"/>
       <c r="H249" s="53" t="inlineStr"/>
       <c r="I249" s="51" t="inlineStr"/>
-      <c r="J249" s="50" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="J249" s="54" t="inlineStr">
+        <is>
+          <t>给您开一副桑杏汤，一天三服，也记得多喝水。</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17587,7 @@
       </c>
       <c r="E250" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F250" s="51" t="inlineStr">
@@ -17182,16 +17595,12 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G250" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
+      <c r="G250" s="51" t="inlineStr"/>
       <c r="H250" s="51" t="inlineStr"/>
       <c r="I250" s="51" t="inlineStr"/>
       <c r="J250" s="50" t="inlineStr">
         <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>柳先生，我最喜欢听您说书啦，您真是啥都知道啥都会，讲什么像什么。</t>
         </is>
       </c>
     </row>
@@ -17216,20 +17625,20 @@
       </c>
       <c r="E251" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F251" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G251" s="51" t="inlineStr"/>
       <c r="H251" s="51" t="inlineStr"/>
       <c r="I251" s="51" t="inlineStr"/>
-      <c r="J251" s="50" t="inlineStr">
-        <is>
-          <t>是是是，师傅说的对，也不是没有这个可能。</t>
+      <c r="J251" s="54" t="inlineStr">
+        <is>
+          <t>诶嘿嘿，小兄弟过奖了，我只是说些王侯将相，才子佳人，来听书的客官喜欢什么，我就讲什么。</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17663,7 @@
       </c>
       <c r="E252" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F252" s="51" t="inlineStr">
@@ -17262,20 +17671,12 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G252" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H252" s="32" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="G252" s="32" t="inlineStr"/>
+      <c r="H252" s="32" t="inlineStr"/>
       <c r="I252" s="32" t="inlineStr"/>
-      <c r="J252" s="71" t="inlineStr">
-        <is>
-          <t>嗯，以后可别乱说啊，这小郎中真是…</t>
+      <c r="J252" s="32" t="inlineStr">
+        <is>
+          <t>先生您现在就在这讲一段吧。</t>
         </is>
       </c>
     </row>
@@ -17298,22 +17699,22 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E253" s="32" t="inlineStr">
+      <c r="E253" s="50" t="inlineStr">
         <is>
           <t>半夏</t>
         </is>
       </c>
       <c r="F253" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G253" s="32" t="inlineStr"/>
       <c r="H253" s="32" t="inlineStr"/>
       <c r="I253" s="32" t="inlineStr"/>
-      <c r="J253" s="32" t="inlineStr">
-        <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
+      <c r="J253" s="36" t="inlineStr">
+        <is>
+          <t>是啊是啊，讲一段吧。</t>
         </is>
       </c>
     </row>
@@ -17351,7 +17752,7 @@
       <c r="I254" s="32" t="inlineStr"/>
       <c r="J254" s="32" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>人家柳先生还病着呢，你们别在这胡闹。</t>
         </is>
       </c>
     </row>
@@ -17374,14 +17775,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E255" s="32" t="inlineStr">
-        <is>
-          <t>陈皮</t>
+      <c r="E255" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F255" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G255" s="32" t="inlineStr"/>
@@ -17389,7 +17790,7 @@
       <c r="I255" s="32" t="inlineStr"/>
       <c r="J255" s="32" t="inlineStr">
         <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+          <t>无妨，呵呵，那就说一个王道士胡诌妒妇方。</t>
         </is>
       </c>
     </row>
@@ -17412,9 +17813,9 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E256" s="32" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E256" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F256" s="51" t="inlineStr">
@@ -17427,7 +17828,7 @@
       <c r="I256" s="32" t="inlineStr"/>
       <c r="J256" s="32" t="inlineStr">
         <is>
-          <t>找打！</t>
+          <t>说京城有一富商，娶了位善妒的夫人，家中鸡飞狗跳无一日安宁。他的朋友觉得这是病，得找人医治。</t>
         </is>
       </c>
     </row>
@@ -17450,14 +17851,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E257" s="32" t="inlineStr">
-        <is>
-          <t>陈皮</t>
+      <c r="E257" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F257" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G257" s="32" t="inlineStr"/>
@@ -17465,23 +17866,23 @@
       <c r="I257" s="32" t="inlineStr"/>
       <c r="J257" s="32" t="inlineStr">
         <is>
-          <t>哎哟！</t>
+          <t>正巧天齐庙有位摆摊卖膏药的王道士，因膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="50" t="inlineStr">
         <is>
-          <t>022_03</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B258" s="50" t="inlineStr">
         <is>
-          <t>022治疗失败</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C258" s="50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D258" s="50" t="inlineStr">
         <is>
@@ -17490,246 +17891,226 @@
       </c>
       <c r="E258" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F258" s="51" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G258" s="51" t="inlineStr"/>
-      <c r="H258" s="53" t="inlineStr"/>
-      <c r="I258" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J258" s="50" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G258" s="32" t="inlineStr"/>
+      <c r="H258" s="32" t="inlineStr"/>
+      <c r="I258" s="32" t="inlineStr"/>
+      <c r="J258" s="32" t="inlineStr">
+        <is>
+          <t>王一贴道：“这贴妒的膏药倒没经过。有一种汤药，或者可医，只是慢些儿，不能立刻见效的。”</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B259" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C259" s="50" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D259" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E259" s="52" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F259" s="53" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G259" s="51" t="inlineStr"/>
-      <c r="H259" s="53" t="inlineStr"/>
-      <c r="I259" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J259" s="52" t="inlineStr">
-        <is>
-          <t>少掌柜的，夫人在屋里晕倒了，您快来看看啊！</t>
+      <c r="E259" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
+        </is>
+      </c>
+      <c r="F259" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G259" s="32" t="inlineStr"/>
+      <c r="H259" s="32" t="inlineStr"/>
+      <c r="I259" s="32" t="inlineStr"/>
+      <c r="J259" s="32" t="inlineStr">
+        <is>
+          <t>朋友问：“什么汤？怎么吃法？”</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B260" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C260" s="50" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D260" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E260" s="52" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E260" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F260" s="51" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G260" s="51" t="inlineStr"/>
-      <c r="H260" s="53" t="inlineStr"/>
-      <c r="I260" s="51" t="inlineStr"/>
-      <c r="J260" s="52" t="inlineStr">
-        <is>
-          <t>芷兰！！！</t>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G260" s="32" t="inlineStr"/>
+      <c r="H260" s="32" t="inlineStr"/>
+      <c r="I260" s="32" t="inlineStr"/>
+      <c r="J260" s="32" t="inlineStr">
+        <is>
+          <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B261" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C261" s="50" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D261" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E261" s="52" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F261" s="53" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G261" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H261" s="53" t="inlineStr"/>
-      <c r="I261" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/023/023.png</t>
-        </is>
-      </c>
-      <c r="J261" s="52" t="inlineStr">
-        <is>
-          <t>…...</t>
+      <c r="E261" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
+        </is>
+      </c>
+      <c r="F261" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G261" s="32" t="inlineStr"/>
+      <c r="H261" s="32" t="inlineStr"/>
+      <c r="I261" s="32" t="inlineStr"/>
+      <c r="J261" s="32" t="inlineStr">
+        <is>
+          <t>朋友道：“这也不值什么。只怕未必见效。”</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B262" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C262" s="50" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D262" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E262" s="52" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F262" s="53" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G262" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H262" s="53" t="inlineStr"/>
-      <c r="I262" s="51" t="inlineStr"/>
-      <c r="J262" s="52" t="inlineStr">
-        <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+      <c r="E262" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
+        </is>
+      </c>
+      <c r="F262" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G262" s="32" t="inlineStr"/>
+      <c r="H262" s="32" t="inlineStr"/>
+      <c r="I262" s="32" t="inlineStr"/>
+      <c r="J262" s="32" t="inlineStr">
+        <is>
+          <t>王一贴道：“一剂不效，吃十剂；今日不效，明日再吃；今年不效，明年再吃。”</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B263" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C263" s="50" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D263" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E263" s="52" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F263" s="53" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G263" s="51" t="inlineStr"/>
-      <c r="H263" s="51" t="inlineStr"/>
-      <c r="I263" s="51" t="inlineStr"/>
-      <c r="J263" s="52" t="inlineStr">
-        <is>
-          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+      <c r="E263" s="50" t="inlineStr">
+        <is>
+          <t>柳敬亭</t>
+        </is>
+      </c>
+      <c r="F263" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G263" s="32" t="inlineStr"/>
+      <c r="H263" s="32" t="inlineStr"/>
+      <c r="I263" s="32" t="inlineStr"/>
+      <c r="J263" s="32" t="inlineStr">
+        <is>
+          <t>“横竖这三味药都是润肺开胃不伤人的，甜丝丝的，又止咳嗽，又好吃。吃过一百岁，人横竖是要死的，死了还妒什么？那时就见效了。”</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="50" t="inlineStr">
         <is>
-          <t>023_02</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B264" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C264" s="50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D264" s="50" t="inlineStr">
         <is>
@@ -17738,40 +18119,36 @@
       </c>
       <c r="E264" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F264" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G264" s="51" t="inlineStr"/>
-      <c r="H264" s="53" t="inlineStr"/>
-      <c r="I264" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/023/023.png</t>
-        </is>
-      </c>
-      <c r="J264" s="50" t="inlineStr">
-        <is>
-          <t>呜呜呜，夫人到底是得了什么病啊。</t>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G264" s="32" t="inlineStr"/>
+      <c r="H264" s="32" t="inlineStr"/>
+      <c r="I264" s="32" t="inlineStr"/>
+      <c r="J264" s="32" t="inlineStr">
+        <is>
+          <t>哈哈哈，还有这种方子。</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="50" t="inlineStr">
         <is>
-          <t>023_02</t>
+          <t>022_03</t>
         </is>
       </c>
       <c r="B265" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>022治疗失败</t>
         </is>
       </c>
       <c r="C265" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" s="50" t="inlineStr">
         <is>
@@ -17785,31 +18162,35 @@
       </c>
       <c r="F265" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G265" s="51" t="inlineStr"/>
       <c r="H265" s="53" t="inlineStr"/>
-      <c r="I265" s="51" t="inlineStr"/>
-      <c r="J265" s="50" t="inlineStr">
-        <is>
-          <t>芷兰…我们有孩子了…</t>
+      <c r="I265" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J265" s="52" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="50" t="inlineStr">
         <is>
-          <t>023_02</t>
+          <t>023_01</t>
         </is>
       </c>
       <c r="B266" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>谢飞燕肺气虚</t>
         </is>
       </c>
       <c r="C266" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D266" s="50" t="inlineStr">
         <is>
@@ -17818,36 +18199,40 @@
       </c>
       <c r="E266" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F266" s="53" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F266" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G266" s="51" t="inlineStr"/>
       <c r="H266" s="53" t="inlineStr"/>
-      <c r="I266" s="51" t="inlineStr"/>
+      <c r="I266" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J266" s="50" t="inlineStr">
         <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+          <t>李大夫，您快给我女儿瞧瞧吧，这孩子整日茶饭不进，愁眉苦脸咳个不停。</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="50" t="inlineStr">
         <is>
-          <t>023_02</t>
+          <t>023_01</t>
         </is>
       </c>
       <c r="B267" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>谢飞燕肺气虚</t>
         </is>
       </c>
       <c r="C267" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D267" s="50" t="inlineStr">
         <is>
@@ -17856,36 +18241,40 @@
       </c>
       <c r="E267" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F267" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G267" s="51" t="inlineStr"/>
-      <c r="H267" s="51" t="inlineStr"/>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F267" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G267" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H267" s="53" t="inlineStr"/>
       <c r="I267" s="51" t="inlineStr"/>
-      <c r="J267" s="54" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="J267" s="50" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="50" t="inlineStr">
         <is>
-          <t>023_02</t>
+          <t>023_01</t>
         </is>
       </c>
       <c r="B268" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>谢飞燕肺气虚</t>
         </is>
       </c>
       <c r="C268" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D268" s="50" t="inlineStr">
         <is>
@@ -17894,60 +18283,2710 @@
       </c>
       <c r="E268" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F268" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G268" s="51" t="inlineStr"/>
-      <c r="H268" s="51" t="inlineStr"/>
+      <c r="H268" s="53" t="inlineStr"/>
       <c r="I268" s="51" t="inlineStr"/>
       <c r="J268" s="50" t="inlineStr">
         <is>
-          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+          <t>这是您女儿？</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="50" t="inlineStr">
         <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B269" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C269" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D269" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E269" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F269" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G269" s="51" t="inlineStr"/>
+      <c r="H269" s="51" t="inlineStr"/>
+      <c r="I269" s="51" t="inlineStr"/>
+      <c r="J269" s="50" t="inlineStr">
+        <is>
+          <t>哎呀，可不是嘛，这孩子随我学艺两年又半载，犹善歌舞，是咱柳月坊的花魁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B270" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C270" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D270" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E270" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F270" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G270" s="51" t="inlineStr"/>
+      <c r="H270" s="51" t="inlineStr"/>
+      <c r="I270" s="51" t="inlineStr"/>
+      <c r="J270" s="50" t="inlineStr">
+        <is>
+          <t>可你看她现在这个样子，还怎么接待客人啊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="32" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B271" s="32" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C271" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D271" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E271" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F271" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G271" s="32" t="inlineStr"/>
+      <c r="H271" s="32" t="inlineStr"/>
+      <c r="I271" s="32" t="inlineStr"/>
+      <c r="J271" s="32" t="inlineStr">
+        <is>
+          <t>姑娘你坐下，我给你把把脉。哎，半夏你在这干什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="32" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B272" s="32" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C272" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D272" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E272" s="52" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F272" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G272" s="32" t="inlineStr"/>
+      <c r="H272" s="32" t="inlineStr"/>
+      <c r="I272" s="32" t="inlineStr"/>
+      <c r="J272" s="57" t="inlineStr">
+        <is>
+          <t>我替夫人来看着你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="32" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B273" s="32" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C273" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D273" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E273" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F273" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G273" s="32" t="inlineStr"/>
+      <c r="H273" s="32" t="inlineStr"/>
+      <c r="I273" s="32" t="inlineStr"/>
+      <c r="J273" s="57" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B274" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C274" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E274" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F274" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G274" s="51" t="inlineStr"/>
+      <c r="H274" s="53" t="inlineStr"/>
+      <c r="I274" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J274" s="50" t="inlineStr">
+        <is>
+          <t>姑娘这病是肺气虚，平日注意避风避寒，开副补肺汤调养调养。早上练练六字诀中的呬字决，舒畅胸中气机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B275" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C275" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D275" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E275" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F275" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G275" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H275" s="53" t="inlineStr"/>
+      <c r="I275" s="51" t="inlineStr"/>
+      <c r="J275" s="50" t="inlineStr">
+        <is>
+          <t>…多谢先生。</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B276" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C276" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D276" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E276" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F276" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G276" s="51" t="inlineStr"/>
+      <c r="H276" s="53" t="inlineStr"/>
+      <c r="I276" s="51" t="inlineStr"/>
+      <c r="J276" s="50" t="inlineStr">
+        <is>
+          <t>姑娘可是有什么心事？</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B277" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C277" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D277" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E277" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F277" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G277" s="51" t="inlineStr"/>
+      <c r="H277" s="51" t="inlineStr"/>
+      <c r="I277" s="51" t="inlineStr"/>
+      <c r="J277" s="50" t="inlineStr">
+        <is>
+          <t>成天好吃好喝的伺候着，她能有什么心事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B278" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C278" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D278" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E278" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F278" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G278" s="51" t="inlineStr"/>
+      <c r="H278" s="51" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I278" s="51" t="inlineStr"/>
+      <c r="J278" s="50" t="inlineStr">
+        <is>
+          <t>那就多谢大夫了，走吧女儿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B279" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C279" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D279" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E279" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F279" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G279" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H279" s="32" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I279" s="32" t="inlineStr"/>
+      <c r="J279" s="50" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B280" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C280" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D280" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E280" s="32" t="inlineStr">
+        <is>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F280" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G280" s="32" t="inlineStr"/>
+      <c r="H280" s="32" t="inlineStr"/>
+      <c r="I280" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J280" s="32" t="inlineStr">
+        <is>
+          <t>先生，刚才那姑娘是得了什么病啊？</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B281" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C281" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D281" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E281" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F281" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G281" s="32" t="inlineStr"/>
+      <c r="H281" s="32" t="inlineStr"/>
+      <c r="I281" s="32" t="inlineStr"/>
+      <c r="J281" s="32" t="inlineStr">
+        <is>
+          <t>您是？</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B282" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C282" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D282" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E282" s="32" t="inlineStr">
+        <is>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F282" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G282" s="32" t="inlineStr"/>
+      <c r="H282" s="32" t="inlineStr"/>
+      <c r="I282" s="32" t="inlineStr"/>
+      <c r="J282" s="32" t="inlineStr">
+        <is>
+          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B283" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C283" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D283" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E283" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F283" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G283" s="32" t="inlineStr"/>
+      <c r="H283" s="32" t="inlineStr"/>
+      <c r="I283" s="32" t="inlineStr"/>
+      <c r="J283" s="32" t="inlineStr">
+        <is>
+          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B284" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C284" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D284" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E284" s="32" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F284" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G284" s="32" t="inlineStr"/>
+      <c r="H284" s="32" t="inlineStr"/>
+      <c r="I284" s="32" t="inlineStr"/>
+      <c r="J284" s="32" t="inlineStr">
+        <is>
+          <t>哎哟？这里面有事儿，快说来听听。</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B285" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C285" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D285" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E285" s="32" t="inlineStr">
+        <is>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F285" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G285" s="32" t="inlineStr"/>
+      <c r="H285" s="32" t="inlineStr"/>
+      <c r="I285" s="32" t="inlineStr"/>
+      <c r="J285" s="10" t="inlineStr">
+        <is>
+          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B286" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C286" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="D286" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E286" s="32" t="inlineStr">
+        <is>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F286" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G286" s="32" t="inlineStr"/>
+      <c r="H286" s="32" t="inlineStr"/>
+      <c r="I286" s="32" t="inlineStr"/>
+      <c r="J286" s="32" t="inlineStr">
+        <is>
+          <t>原想着凑够五百两白银，给她赎身。可她那老鸨坐地起价一千两，这让我们上哪去凑这么多银子啊…</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B287" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C287" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D287" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E287" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F287" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G287" s="32" t="inlineStr"/>
+      <c r="H287" s="32" t="inlineStr"/>
+      <c r="I287" s="32" t="inlineStr"/>
+      <c r="J287" s="32" t="inlineStr">
+        <is>
+          <t>想必姑娘是因为这事急坏了身子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B288" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C288" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D288" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E288" s="32" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F288" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G288" s="32" t="inlineStr"/>
+      <c r="H288" s="32" t="inlineStr"/>
+      <c r="I288" s="32" t="inlineStr"/>
+      <c r="J288" s="32" t="inlineStr">
+        <is>
+          <t>唉，又是一对儿苦命的鸳鸯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B289" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C289" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="D289" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E289" s="32" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F289" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G289" s="32" t="inlineStr"/>
+      <c r="H289" s="32" t="inlineStr"/>
+      <c r="I289" s="32" t="inlineStr"/>
+      <c r="J289" s="32" t="inlineStr">
+        <is>
+          <t>你在这儿干啥呢，夫人找你呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="50" t="inlineStr">
+        <is>
           <t>023_03</t>
         </is>
       </c>
-      <c r="B269" s="50" t="inlineStr">
+      <c r="B290" s="50" t="inlineStr">
         <is>
           <t>023治疗失败</t>
         </is>
       </c>
-      <c r="C269" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="50" t="inlineStr">
+      <c r="C290" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E269" s="50" t="inlineStr">
+      <c r="E290" s="50" t="inlineStr"/>
+      <c r="F290" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G290" s="51" t="inlineStr"/>
+      <c r="H290" s="53" t="inlineStr"/>
+      <c r="I290" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J290" s="52" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="50" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="B291" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺阴虚</t>
+        </is>
+      </c>
+      <c r="C291" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D291" s="50" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E291" s="52" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F269" s="51" t="inlineStr">
+      <c r="F291" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G291" s="51" t="inlineStr"/>
+      <c r="H291" s="53" t="inlineStr"/>
+      <c r="I291" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J291" s="52" t="inlineStr">
+        <is>
+          <t>姑娘你来啦，病好点了吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="50" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="B292" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺阴虚</t>
+        </is>
+      </c>
+      <c r="C292" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D292" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E292" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F292" s="53" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G269" s="51" t="inlineStr"/>
-      <c r="H269" s="53" t="inlineStr"/>
-      <c r="I269" s="51" t="inlineStr">
+      <c r="G292" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H292" s="53" t="inlineStr"/>
+      <c r="I292" s="51" t="inlineStr"/>
+      <c r="J292" s="52" t="inlineStr">
+        <is>
+          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="50" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="B293" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺阴虚</t>
+        </is>
+      </c>
+      <c r="C293" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D293" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E293" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F293" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G293" s="51" t="inlineStr"/>
+      <c r="H293" s="53" t="inlineStr"/>
+      <c r="I293" s="51" t="inlineStr"/>
+      <c r="J293" s="52" t="inlineStr">
+        <is>
+          <t>请坐，我再给你看看。</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B294" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C294" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D294" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E294" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F294" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G294" s="51" t="inlineStr"/>
+      <c r="H294" s="53" t="inlineStr"/>
+      <c r="I294" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J294" s="52" t="inlineStr">
+        <is>
+          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B295" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C295" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D295" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E295" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F295" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G295" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H295" s="53" t="inlineStr"/>
+      <c r="I295" s="51" t="inlineStr"/>
+      <c r="J295" s="52" t="inlineStr">
+        <is>
+          <t>多谢先生…</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B296" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C296" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D296" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E296" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F296" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G296" s="51" t="inlineStr"/>
+      <c r="H296" s="53" t="inlineStr"/>
+      <c r="I296" s="51" t="inlineStr"/>
+      <c r="J296" s="52" t="inlineStr">
+        <is>
+          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B297" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C297" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D297" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E297" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F297" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G297" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H297" s="51" t="inlineStr"/>
+      <c r="I297" s="51" t="inlineStr"/>
+      <c r="J297" s="52" t="inlineStr">
+        <is>
+          <t>先生这是何意味？</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B298" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C298" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D298" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E298" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F298" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G298" s="51" t="inlineStr"/>
+      <c r="H298" s="51" t="inlineStr"/>
+      <c r="I298" s="51" t="inlineStr"/>
+      <c r="J298" s="52" t="inlineStr">
+        <is>
+          <t>前些天你来看病，你前脚刚走，李公子就来我这问你的病情，很是担心你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B299" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C299" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D299" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E299" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F299" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G299" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H299" s="32" t="inlineStr"/>
+      <c r="I299" s="32" t="inlineStr"/>
+      <c r="J299" s="57" t="inlineStr">
+        <is>
+          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B300" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C300" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D300" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E300" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F300" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G300" s="53" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H300" s="32" t="inlineStr"/>
+      <c r="I300" s="32" t="inlineStr"/>
+      <c r="J300" s="57" t="inlineStr">
+        <is>
+          <t>李郎待我是真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B301" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C301" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D301" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E301" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F301" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G301" s="32" t="inlineStr"/>
+      <c r="H301" s="32" t="inlineStr"/>
+      <c r="I301" s="32" t="inlineStr"/>
+      <c r="J301" s="57" t="inlineStr">
+        <is>
+          <t>我有一计，可让你二人有情人终成眷属。</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B302" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C302" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D302" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E302" s="52" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F302" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G302" s="32" t="inlineStr"/>
+      <c r="H302" s="32" t="inlineStr"/>
+      <c r="I302" s="32" t="inlineStr"/>
+      <c r="J302" s="57" t="inlineStr">
+        <is>
+          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B303" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C303" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D303" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E303" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F303" s="53" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G303" s="32" t="inlineStr"/>
+      <c r="H303" s="32" t="inlineStr"/>
+      <c r="I303" s="32" t="inlineStr"/>
+      <c r="J303" s="57" t="inlineStr">
+        <is>
+          <t>少掌柜的你有什么注意呀？快说快说！</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B304" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C304" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D304" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E304" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F304" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G304" s="32" t="inlineStr"/>
+      <c r="H304" s="32" t="inlineStr"/>
+      <c r="I304" s="32" t="inlineStr"/>
+      <c r="J304" s="57" t="inlineStr">
+        <is>
+          <t>明日你带金姨妈来我这，如此这般….</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B305" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C305" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D305" s="50" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E305" s="32" t="inlineStr"/>
+      <c r="F305" s="51" t="inlineStr"/>
+      <c r="G305" s="32" t="inlineStr"/>
+      <c r="H305" s="32" t="inlineStr"/>
+      <c r="I305" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J305" s="57" t="inlineStr">
+        <is>
+          <t>次日</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B306" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C306" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="D306" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E306" s="57" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F306" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G306" s="32" t="inlineStr"/>
+      <c r="H306" s="32" t="inlineStr"/>
+      <c r="I306" s="32" t="inlineStr"/>
+      <c r="J306" s="57" t="inlineStr">
+        <is>
+          <t>李大夫，你叫我来是什么事儿啊？</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B307" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C307" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D307" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E307" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F307" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G307" s="32" t="inlineStr"/>
+      <c r="H307" s="32" t="inlineStr"/>
+      <c r="I307" s="32" t="inlineStr"/>
+      <c r="J307" s="57" t="inlineStr">
+        <is>
+          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B308" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C308" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D308" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E308" s="57" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F308" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G308" s="32" t="inlineStr"/>
+      <c r="H308" s="32" t="inlineStr"/>
+      <c r="I308" s="32" t="inlineStr"/>
+      <c r="J308" s="57" t="inlineStr">
+        <is>
+          <t>啊？这可如何是好？</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B309" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C309" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="D309" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E309" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F309" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G309" s="32" t="inlineStr"/>
+      <c r="H309" s="32" t="inlineStr"/>
+      <c r="I309" s="32" t="inlineStr"/>
+      <c r="J309" s="57" t="inlineStr">
+        <is>
+          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B310" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C310" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="D310" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E310" s="57" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F310" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G310" s="32" t="inlineStr"/>
+      <c r="H310" s="32" t="inlineStr"/>
+      <c r="I310" s="32" t="inlineStr"/>
+      <c r="J310" s="57" t="inlineStr">
+        <is>
+          <t>若是这样，不如趁那小子不知情，便宜与了那小子….</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="50" t="inlineStr">
+        <is>
+          <t>024_03</t>
+        </is>
+      </c>
+      <c r="B311" s="50" t="inlineStr">
+        <is>
+          <t>024治疗失败</t>
+        </is>
+      </c>
+      <c r="C311" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E311" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F311" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G311" s="51" t="inlineStr"/>
+      <c r="H311" s="53" t="inlineStr"/>
+      <c r="I311" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J311" s="50" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="50" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="B312" s="50" t="inlineStr">
+        <is>
+          <t>和尚肾精不足</t>
+        </is>
+      </c>
+      <c r="C312" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E312" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F312" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G312" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H312" s="53" t="inlineStr"/>
+      <c r="I312" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J312" s="54" t="inlineStr">
+        <is>
+          <t>贫僧法号性空，《中论》曰："众因缘生发，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="50" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="B313" s="50" t="inlineStr">
+        <is>
+          <t>和尚肾精不足</t>
+        </is>
+      </c>
+      <c r="C313" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D313" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E313" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F313" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G313" s="51" t="inlineStr"/>
+      <c r="H313" s="53" t="inlineStr"/>
+      <c r="I313" s="51" t="inlineStr"/>
+      <c r="J313" s="54" t="inlineStr">
+        <is>
+          <t>师傅请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B314" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C314" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E314" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F314" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G314" s="51" t="inlineStr"/>
+      <c r="H314" s="53" t="inlineStr"/>
+      <c r="I314" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J314" s="54" t="inlineStr">
+        <is>
+          <t>师傅所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B315" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C315" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D315" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E315" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F315" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G315" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H315" s="53" t="inlineStr"/>
+      <c r="I315" s="51" t="inlineStr"/>
+      <c r="J315" s="50" t="inlineStr">
+        <is>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B316" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C316" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D316" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E316" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F316" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G316" s="51" t="inlineStr"/>
+      <c r="H316" s="53" t="inlineStr"/>
+      <c r="I316" s="51" t="inlineStr"/>
+      <c r="J316" s="50" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B317" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C317" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D317" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E317" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F317" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G317" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H317" s="51" t="inlineStr"/>
+      <c r="I317" s="51" t="inlineStr"/>
+      <c r="J317" s="50" t="inlineStr">
+        <is>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B318" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C318" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D318" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E318" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F318" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G318" s="51" t="inlineStr"/>
+      <c r="H318" s="51" t="inlineStr"/>
+      <c r="I318" s="51" t="inlineStr"/>
+      <c r="J318" s="50" t="inlineStr">
+        <is>
+          <t>是是是，师傅说的对，也不是没有这个可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B319" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C319" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D319" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E319" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F319" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G319" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H319" s="32" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I319" s="32" t="inlineStr"/>
+      <c r="J319" s="71" t="inlineStr">
+        <is>
+          <t>嗯，以后可别乱说啊，这小郎中真是…</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B320" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C320" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D320" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E320" s="32" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F320" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G320" s="32" t="inlineStr"/>
+      <c r="H320" s="32" t="inlineStr"/>
+      <c r="I320" s="32" t="inlineStr"/>
+      <c r="J320" s="32" t="inlineStr">
+        <is>
+          <t>哇，这就是传说中的花和尚吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B321" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C321" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D321" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E321" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F321" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G321" s="32" t="inlineStr"/>
+      <c r="H321" s="32" t="inlineStr"/>
+      <c r="I321" s="32" t="inlineStr"/>
+      <c r="J321" s="32" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B322" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C322" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D322" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E322" s="32" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F322" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G322" s="32" t="inlineStr"/>
+      <c r="H322" s="32" t="inlineStr"/>
+      <c r="I322" s="32" t="inlineStr"/>
+      <c r="J322" s="32" t="inlineStr">
+        <is>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B323" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C323" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D323" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E323" s="32" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F323" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G323" s="32" t="inlineStr"/>
+      <c r="H323" s="32" t="inlineStr"/>
+      <c r="I323" s="32" t="inlineStr"/>
+      <c r="J323" s="32" t="inlineStr">
+        <is>
+          <t>找打！</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B324" s="50" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C324" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D324" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E324" s="32" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F324" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G324" s="32" t="inlineStr"/>
+      <c r="H324" s="32" t="inlineStr"/>
+      <c r="I324" s="32" t="inlineStr"/>
+      <c r="J324" s="32" t="inlineStr">
+        <is>
+          <t>哎哟！</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="50" t="inlineStr">
+        <is>
+          <t>025_03</t>
+        </is>
+      </c>
+      <c r="B325" s="50" t="inlineStr">
+        <is>
+          <t>022治疗失败</t>
+        </is>
+      </c>
+      <c r="C325" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E325" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F325" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G325" s="51" t="inlineStr"/>
+      <c r="H325" s="53" t="inlineStr"/>
+      <c r="I325" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J325" s="50" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B326" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C326" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D326" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E326" s="52" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F326" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G326" s="51" t="inlineStr"/>
+      <c r="H326" s="53" t="inlineStr"/>
+      <c r="I326" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J326" s="52" t="inlineStr">
+        <is>
+          <t>少掌柜的，夫人在屋里晕倒了，您快来看看啊！</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B327" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C327" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D327" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E327" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F327" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G327" s="51" t="inlineStr"/>
+      <c r="H327" s="53" t="inlineStr"/>
+      <c r="I327" s="51" t="inlineStr"/>
+      <c r="J327" s="52" t="inlineStr">
+        <is>
+          <t>芷兰！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B328" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C328" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D328" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E328" s="52" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F328" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G328" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H328" s="53" t="inlineStr"/>
+      <c r="I328" s="51" t="inlineStr">
         <is>
           <t>res://Assets/Background/023/023.png</t>
         </is>
       </c>
-      <c r="J269" s="50" t="inlineStr">
+      <c r="J328" s="52" t="inlineStr">
+        <is>
+          <t>…...</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B329" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C329" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D329" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E329" s="52" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F329" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G329" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H329" s="53" t="inlineStr"/>
+      <c r="I329" s="51" t="inlineStr"/>
+      <c r="J329" s="52" t="inlineStr">
+        <is>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B330" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C330" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D330" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E330" s="52" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F330" s="53" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G330" s="51" t="inlineStr"/>
+      <c r="H330" s="51" t="inlineStr"/>
+      <c r="I330" s="51" t="inlineStr"/>
+      <c r="J330" s="52" t="inlineStr">
+        <is>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B331" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C331" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D331" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E331" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F331" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G331" s="51" t="inlineStr"/>
+      <c r="H331" s="53" t="inlineStr"/>
+      <c r="I331" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/023/023.png</t>
+        </is>
+      </c>
+      <c r="J331" s="50" t="inlineStr">
+        <is>
+          <t>呜呜呜，夫人到底是得了什么病啊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B332" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C332" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D332" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E332" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F332" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G332" s="51" t="inlineStr"/>
+      <c r="H332" s="53" t="inlineStr"/>
+      <c r="I332" s="51" t="inlineStr"/>
+      <c r="J332" s="50" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B333" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C333" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D333" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E333" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F333" s="53" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G333" s="51" t="inlineStr"/>
+      <c r="H333" s="53" t="inlineStr"/>
+      <c r="I333" s="51" t="inlineStr"/>
+      <c r="J333" s="50" t="inlineStr">
+        <is>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B334" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C334" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D334" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E334" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F334" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G334" s="51" t="inlineStr"/>
+      <c r="H334" s="51" t="inlineStr"/>
+      <c r="I334" s="51" t="inlineStr"/>
+      <c r="J334" s="54" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B335" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C335" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D335" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E335" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F335" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G335" s="51" t="inlineStr"/>
+      <c r="H335" s="51" t="inlineStr"/>
+      <c r="I335" s="51" t="inlineStr"/>
+      <c r="J335" s="50" t="inlineStr">
+        <is>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="50" t="inlineStr">
+        <is>
+          <t>026_03</t>
+        </is>
+      </c>
+      <c r="B336" s="50" t="inlineStr">
+        <is>
+          <t>023治疗失败</t>
+        </is>
+      </c>
+      <c r="C336" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D336" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E336" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F336" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G336" s="51" t="inlineStr"/>
+      <c r="H336" s="53" t="inlineStr"/>
+      <c r="I336" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/023/023.png</t>
+        </is>
+      </c>
+      <c r="J336" s="50" t="inlineStr">
         <is>
           <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
         </is>
@@ -17966,14 +21005,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -20005,33 +23044,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="110"/>
-    <col width="9" customWidth="1" style="9" min="111" max="16384"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="111"/>
+    <col width="9" customWidth="1" style="9" min="112" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -20842,12 +23881,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -22947,15 +25986,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34727,18 +37766,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="41.73046875" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="41.75" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41862,8 +44901,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -41890,32 +44929,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
     <cfRule type="duplicateValues" priority="124" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="123" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
     <cfRule type="duplicateValues" priority="120" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="119" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
     <cfRule type="duplicateValues" priority="118" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="117" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
     <cfRule type="duplicateValues" priority="116" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="115" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
     <cfRule type="duplicateValues" priority="111" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="110" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -41954,20 +44993,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
     <cfRule type="duplicateValues" priority="155" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="154" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
     <cfRule type="duplicateValues" priority="77" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="76" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
     <cfRule type="duplicateValues" priority="147" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="146" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -41978,8 +45017,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
     <cfRule type="duplicateValues" priority="55" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="54" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -41990,32 +45029,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
     <cfRule type="duplicateValues" priority="29" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="28" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
     <cfRule type="duplicateValues" priority="134" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="133" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
     <cfRule type="duplicateValues" priority="50" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="49" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
     <cfRule type="duplicateValues" priority="149" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="148" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
     <cfRule type="duplicateValues" priority="74" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="73" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
     <cfRule type="duplicateValues" priority="72" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="71" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -42026,8 +45065,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
     <cfRule type="duplicateValues" priority="66" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="65" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -42038,8 +45077,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
     <cfRule type="duplicateValues" priority="57" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="56" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -42050,8 +45089,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
     <cfRule type="duplicateValues" priority="53" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="52" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -42062,36 +45101,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
     <cfRule type="duplicateValues" priority="100" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="99" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
     <cfRule type="duplicateValues" priority="39" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="38" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
     <cfRule type="duplicateValues" priority="63" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="62" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
     <cfRule type="duplicateValues" priority="136" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="135" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -42122,12 +45161,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
     <cfRule type="duplicateValues" priority="85" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="84" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
     <cfRule type="duplicateValues" priority="17" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="16" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -42142,12 +45181,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
     <cfRule type="duplicateValues" priority="89" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="88" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
     <cfRule type="duplicateValues" priority="143" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="142" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -42158,8 +45197,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
     <cfRule type="duplicateValues" priority="132" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="131" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -42176,14 +45215,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col width="45.59765625" customWidth="1" min="1" max="1"/>
-    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.73046875" customWidth="1" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.625" customWidth="1" min="1" max="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.75" customWidth="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,16 +20,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Npc'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -136,14 +136,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -151,9 +144,9 @@
     </font>
     <font>
       <name val="等线"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -245,7 +238,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -412,14 +405,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2383,19 +2378,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.125" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.1328125" defaultRowHeight="18"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
-    <col width="9.75" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
-    <col width="8.25" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
-    <col width="4.625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
-    <col width="23.125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
-    <col width="25.125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
-    <col width="33.375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="63"/>
-    <col width="9.125" customWidth="1" style="23" min="64" max="16384"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" style="23" min="2" max="2"/>
+    <col width="9.73046875" bestFit="1" customWidth="1" style="23" min="3" max="3"/>
+    <col width="8.265625" bestFit="1" customWidth="1" style="23" min="4" max="4"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" style="23" min="5" max="5"/>
+    <col width="23.1328125" bestFit="1" customWidth="1" style="23" min="6" max="6"/>
+    <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
+    <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
+    <col width="9.1328125" customWidth="1" style="23" min="10" max="64"/>
+    <col width="9.1328125" customWidth="1" style="23" min="65" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5249,13 +5244,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -5468,27 +5463,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
-    <col width="14.625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
-    <col width="14.25" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
-    <col width="12.5" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
-    <col width="18.375" customWidth="1" style="36" min="7" max="7"/>
-    <col width="16.25" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
-    <col width="15.625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
-    <col width="12.25" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
-    <col width="29.75" customWidth="1" style="36" min="12" max="12"/>
-    <col width="12.125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="14.59765625" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
+    <col width="14.265625" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
+    <col width="12.46484375" bestFit="1" customWidth="1" style="36" min="6" max="6"/>
+    <col width="18.3984375" customWidth="1" style="36" min="7" max="7"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="36" min="8" max="8"/>
+    <col width="15.59765625" bestFit="1" customWidth="1" style="36" min="9" max="9"/>
+    <col width="12.265625" bestFit="1" customWidth="1" style="36" min="10" max="10"/>
+    <col width="8.46484375" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
+    <col width="29.73046875" customWidth="1" style="36" min="12" max="12"/>
+    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="12" bestFit="1" customWidth="1" style="36" min="14" max="14"/>
-    <col width="10.75" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
-    <col width="10.875" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
-    <col width="9" customWidth="1" style="36" min="17" max="86"/>
-    <col width="9" customWidth="1" style="36" min="87" max="16384"/>
+    <col width="10.73046875" bestFit="1" customWidth="1" style="36" min="15" max="15"/>
+    <col width="10.86328125" bestFit="1" customWidth="1" style="36" min="16" max="16"/>
+    <col width="9" customWidth="1" style="36" min="17" max="87"/>
+    <col width="9" customWidth="1" style="36" min="88" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7499,7 +7494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="36" customHeight="1">
       <c r="A41" s="37" t="inlineStr">
         <is>
           <t>024_01</t>
@@ -7649,7 +7644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="36" customHeight="1">
       <c r="A44" s="37" t="inlineStr">
         <is>
           <t>025_01</t>
@@ -7715,7 +7710,7 @@
       </c>
       <c r="B45" s="37" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C45" s="37" t="inlineStr">
@@ -7761,7 +7756,7 @@
       </c>
       <c r="B46" s="37" t="inlineStr">
         <is>
-          <t>022治疗失败</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C46" s="37" t="inlineStr">
@@ -7800,154 +7795,514 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>吴芷兰妊娠</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>scene_enter</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr"/>
+      <c r="G47" s="37" t="inlineStr"/>
+      <c r="H47" s="37" t="inlineStr"/>
+      <c r="I47" s="37" t="inlineStr">
         <is>
           <t>妊娠</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="37" t="inlineStr">
         <is>
           <t>wu_zhi_lan</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="37" t="inlineStr">
         <is>
           <t>妊娠</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="72" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="b">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="M47" s="37" t="inlineStr"/>
+      <c r="N47" s="37" t="inlineStr"/>
+      <c r="O47" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>026_02</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>023治疗成功</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>026治疗成功</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>story_npc_cured</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr"/>
+      <c r="G48" s="37" t="inlineStr"/>
+      <c r="H48" s="37" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="b">
-        <v>1</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="I48" s="37" t="inlineStr"/>
+      <c r="J48" s="37" t="inlineStr"/>
+      <c r="K48" s="37" t="inlineStr"/>
+      <c r="L48" s="37" t="inlineStr"/>
+      <c r="M48" s="37" t="inlineStr"/>
+      <c r="N48" s="37" t="inlineStr"/>
+      <c r="O48" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" s="37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>026_03</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>023治疗失败</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>026治疗失败</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>story_npc_failed_retry</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="37" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr"/>
+      <c r="G49" s="37" t="inlineStr"/>
+      <c r="H49" s="37" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="b">
+      <c r="I49" s="37" t="inlineStr"/>
+      <c r="J49" s="37" t="inlineStr"/>
+      <c r="K49" s="37" t="inlineStr"/>
+      <c r="L49" s="37" t="inlineStr"/>
+      <c r="M49" s="37" t="inlineStr"/>
+      <c r="N49" s="37" t="inlineStr"/>
+      <c r="O49" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P49" s="37" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="n"/>
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="37" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="37" t="n"/>
+      <c r="G50" s="37" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="37" t="n"/>
+      <c r="J50" s="37" t="n"/>
+      <c r="K50" s="37" t="n"/>
+      <c r="L50" s="37" t="n"/>
+      <c r="M50" s="37" t="n"/>
+      <c r="N50" s="37" t="n"/>
+      <c r="O50" s="37" t="n"/>
+      <c r="P50" s="37" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="n"/>
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="37" t="n"/>
+      <c r="E51" s="37" t="n"/>
+      <c r="F51" s="37" t="n"/>
+      <c r="G51" s="37" t="n"/>
+      <c r="H51" s="37" t="n"/>
+      <c r="I51" s="37" t="n"/>
+      <c r="J51" s="37" t="n"/>
+      <c r="K51" s="37" t="n"/>
+      <c r="L51" s="37" t="n"/>
+      <c r="M51" s="37" t="n"/>
+      <c r="N51" s="37" t="n"/>
+      <c r="O51" s="37" t="n"/>
+      <c r="P51" s="37" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="37" t="n"/>
+      <c r="G52" s="37" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="37" t="n"/>
+      <c r="J52" s="37" t="n"/>
+      <c r="K52" s="37" t="n"/>
+      <c r="L52" s="37" t="n"/>
+      <c r="M52" s="37" t="n"/>
+      <c r="N52" s="37" t="n"/>
+      <c r="O52" s="37" t="n"/>
+      <c r="P52" s="37" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="n"/>
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="37" t="n"/>
+      <c r="E53" s="37" t="n"/>
+      <c r="F53" s="37" t="n"/>
+      <c r="G53" s="37" t="n"/>
+      <c r="H53" s="37" t="n"/>
+      <c r="I53" s="37" t="n"/>
+      <c r="J53" s="37" t="n"/>
+      <c r="K53" s="37" t="n"/>
+      <c r="L53" s="37" t="n"/>
+      <c r="M53" s="37" t="n"/>
+      <c r="N53" s="37" t="n"/>
+      <c r="O53" s="37" t="n"/>
+      <c r="P53" s="37" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="n"/>
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="37" t="n"/>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="37" t="n"/>
+      <c r="F54" s="37" t="n"/>
+      <c r="G54" s="37" t="n"/>
+      <c r="H54" s="37" t="n"/>
+      <c r="I54" s="37" t="n"/>
+      <c r="J54" s="37" t="n"/>
+      <c r="K54" s="37" t="n"/>
+      <c r="L54" s="37" t="n"/>
+      <c r="M54" s="37" t="n"/>
+      <c r="N54" s="37" t="n"/>
+      <c r="O54" s="37" t="n"/>
+      <c r="P54" s="37" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="n"/>
+      <c r="B55" s="37" t="n"/>
+      <c r="C55" s="37" t="n"/>
+      <c r="D55" s="37" t="n"/>
+      <c r="E55" s="37" t="n"/>
+      <c r="F55" s="37" t="n"/>
+      <c r="G55" s="37" t="n"/>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="37" t="n"/>
+      <c r="J55" s="37" t="n"/>
+      <c r="K55" s="37" t="n"/>
+      <c r="L55" s="37" t="n"/>
+      <c r="M55" s="37" t="n"/>
+      <c r="N55" s="37" t="n"/>
+      <c r="O55" s="37" t="n"/>
+      <c r="P55" s="37" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="n"/>
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="37" t="n"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="37" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="37" t="n"/>
+      <c r="J56" s="37" t="n"/>
+      <c r="K56" s="37" t="n"/>
+      <c r="L56" s="37" t="n"/>
+      <c r="M56" s="37" t="n"/>
+      <c r="N56" s="37" t="n"/>
+      <c r="O56" s="37" t="n"/>
+      <c r="P56" s="37" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="37" t="n"/>
+      <c r="B57" s="37" t="n"/>
+      <c r="C57" s="37" t="n"/>
+      <c r="D57" s="37" t="n"/>
+      <c r="E57" s="37" t="n"/>
+      <c r="F57" s="37" t="n"/>
+      <c r="G57" s="37" t="n"/>
+      <c r="H57" s="37" t="n"/>
+      <c r="I57" s="37" t="n"/>
+      <c r="J57" s="37" t="n"/>
+      <c r="K57" s="37" t="n"/>
+      <c r="L57" s="37" t="n"/>
+      <c r="M57" s="37" t="n"/>
+      <c r="N57" s="37" t="n"/>
+      <c r="O57" s="37" t="n"/>
+      <c r="P57" s="37" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="37" t="n"/>
+      <c r="B58" s="37" t="n"/>
+      <c r="C58" s="37" t="n"/>
+      <c r="D58" s="37" t="n"/>
+      <c r="E58" s="37" t="n"/>
+      <c r="F58" s="37" t="n"/>
+      <c r="G58" s="37" t="n"/>
+      <c r="H58" s="37" t="n"/>
+      <c r="I58" s="37" t="n"/>
+      <c r="J58" s="37" t="n"/>
+      <c r="K58" s="37" t="n"/>
+      <c r="L58" s="37" t="n"/>
+      <c r="M58" s="37" t="n"/>
+      <c r="N58" s="37" t="n"/>
+      <c r="O58" s="37" t="n"/>
+      <c r="P58" s="37" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="37" t="n"/>
+      <c r="B59" s="37" t="n"/>
+      <c r="C59" s="37" t="n"/>
+      <c r="D59" s="37" t="n"/>
+      <c r="E59" s="37" t="n"/>
+      <c r="F59" s="37" t="n"/>
+      <c r="G59" s="37" t="n"/>
+      <c r="H59" s="37" t="n"/>
+      <c r="I59" s="37" t="n"/>
+      <c r="J59" s="37" t="n"/>
+      <c r="K59" s="37" t="n"/>
+      <c r="L59" s="37" t="n"/>
+      <c r="M59" s="37" t="n"/>
+      <c r="N59" s="37" t="n"/>
+      <c r="O59" s="37" t="n"/>
+      <c r="P59" s="37" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="37" t="n"/>
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="37" t="n"/>
+      <c r="D60" s="37" t="n"/>
+      <c r="E60" s="37" t="n"/>
+      <c r="F60" s="37" t="n"/>
+      <c r="G60" s="37" t="n"/>
+      <c r="H60" s="37" t="n"/>
+      <c r="I60" s="37" t="n"/>
+      <c r="J60" s="37" t="n"/>
+      <c r="K60" s="37" t="n"/>
+      <c r="L60" s="37" t="n"/>
+      <c r="M60" s="37" t="n"/>
+      <c r="N60" s="37" t="n"/>
+      <c r="O60" s="37" t="n"/>
+      <c r="P60" s="37" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="37" t="n"/>
+      <c r="B61" s="37" t="n"/>
+      <c r="C61" s="37" t="n"/>
+      <c r="D61" s="37" t="n"/>
+      <c r="E61" s="37" t="n"/>
+      <c r="F61" s="37" t="n"/>
+      <c r="G61" s="37" t="n"/>
+      <c r="H61" s="37" t="n"/>
+      <c r="I61" s="37" t="n"/>
+      <c r="J61" s="37" t="n"/>
+      <c r="K61" s="37" t="n"/>
+      <c r="L61" s="37" t="n"/>
+      <c r="M61" s="37" t="n"/>
+      <c r="N61" s="37" t="n"/>
+      <c r="O61" s="37" t="n"/>
+      <c r="P61" s="37" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="37" t="n"/>
+      <c r="B62" s="37" t="n"/>
+      <c r="C62" s="37" t="n"/>
+      <c r="D62" s="37" t="n"/>
+      <c r="E62" s="37" t="n"/>
+      <c r="F62" s="37" t="n"/>
+      <c r="G62" s="37" t="n"/>
+      <c r="H62" s="37" t="n"/>
+      <c r="I62" s="37" t="n"/>
+      <c r="J62" s="37" t="n"/>
+      <c r="K62" s="37" t="n"/>
+      <c r="L62" s="37" t="n"/>
+      <c r="M62" s="37" t="n"/>
+      <c r="N62" s="37" t="n"/>
+      <c r="O62" s="37" t="n"/>
+      <c r="P62" s="37" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="37" t="n"/>
+      <c r="B63" s="37" t="n"/>
+      <c r="C63" s="37" t="n"/>
+      <c r="D63" s="37" t="n"/>
+      <c r="E63" s="37" t="n"/>
+      <c r="F63" s="37" t="n"/>
+      <c r="G63" s="37" t="n"/>
+      <c r="H63" s="37" t="n"/>
+      <c r="I63" s="37" t="n"/>
+      <c r="J63" s="37" t="n"/>
+      <c r="K63" s="37" t="n"/>
+      <c r="L63" s="37" t="n"/>
+      <c r="M63" s="37" t="n"/>
+      <c r="N63" s="37" t="n"/>
+      <c r="O63" s="37" t="n"/>
+      <c r="P63" s="37" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="37" t="n"/>
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="37" t="n"/>
+      <c r="D64" s="37" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="37" t="n"/>
+      <c r="G64" s="37" t="n"/>
+      <c r="H64" s="37" t="n"/>
+      <c r="I64" s="37" t="n"/>
+      <c r="J64" s="37" t="n"/>
+      <c r="K64" s="37" t="n"/>
+      <c r="L64" s="37" t="n"/>
+      <c r="M64" s="37" t="n"/>
+      <c r="N64" s="37" t="n"/>
+      <c r="O64" s="37" t="n"/>
+      <c r="P64" s="37" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="37" t="n"/>
+      <c r="B65" s="37" t="n"/>
+      <c r="C65" s="37" t="n"/>
+      <c r="D65" s="37" t="n"/>
+      <c r="E65" s="37" t="n"/>
+      <c r="F65" s="37" t="n"/>
+      <c r="G65" s="37" t="n"/>
+      <c r="H65" s="37" t="n"/>
+      <c r="I65" s="37" t="n"/>
+      <c r="J65" s="37" t="n"/>
+      <c r="K65" s="37" t="n"/>
+      <c r="L65" s="37" t="n"/>
+      <c r="M65" s="37" t="n"/>
+      <c r="N65" s="37" t="n"/>
+      <c r="O65" s="37" t="n"/>
+      <c r="P65" s="37" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="37" t="n"/>
+      <c r="B66" s="37" t="n"/>
+      <c r="C66" s="37" t="n"/>
+      <c r="D66" s="37" t="n"/>
+      <c r="E66" s="37" t="n"/>
+      <c r="F66" s="37" t="n"/>
+      <c r="G66" s="37" t="n"/>
+      <c r="H66" s="37" t="n"/>
+      <c r="I66" s="37" t="n"/>
+      <c r="J66" s="37" t="n"/>
+      <c r="K66" s="37" t="n"/>
+      <c r="L66" s="37" t="n"/>
+      <c r="M66" s="37" t="n"/>
+      <c r="N66" s="37" t="n"/>
+      <c r="O66" s="37" t="n"/>
+      <c r="P66" s="37" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="37" t="n"/>
+      <c r="B67" s="37" t="n"/>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="37" t="n"/>
+      <c r="E67" s="37" t="n"/>
+      <c r="F67" s="37" t="n"/>
+      <c r="G67" s="37" t="n"/>
+      <c r="H67" s="37" t="n"/>
+      <c r="I67" s="37" t="n"/>
+      <c r="J67" s="37" t="n"/>
+      <c r="K67" s="37" t="n"/>
+      <c r="L67" s="37" t="n"/>
+      <c r="M67" s="37" t="n"/>
+      <c r="N67" s="37" t="n"/>
+      <c r="O67" s="37" t="n"/>
+      <c r="P67" s="37" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="37" t="n"/>
+      <c r="B68" s="37" t="n"/>
+      <c r="C68" s="37" t="n"/>
+      <c r="D68" s="37" t="n"/>
+      <c r="E68" s="37" t="n"/>
+      <c r="F68" s="37" t="n"/>
+      <c r="G68" s="37" t="n"/>
+      <c r="H68" s="37" t="n"/>
+      <c r="I68" s="37" t="n"/>
+      <c r="J68" s="37" t="n"/>
+      <c r="K68" s="37" t="n"/>
+      <c r="L68" s="37" t="n"/>
+      <c r="M68" s="37" t="n"/>
+      <c r="N68" s="37" t="n"/>
+      <c r="O68" s="37" t="n"/>
+      <c r="P68" s="37" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="37" t="n"/>
+      <c r="B69" s="37" t="n"/>
+      <c r="C69" s="37" t="n"/>
+      <c r="D69" s="37" t="n"/>
+      <c r="E69" s="37" t="n"/>
+      <c r="F69" s="37" t="n"/>
+      <c r="G69" s="37" t="n"/>
+      <c r="H69" s="37" t="n"/>
+      <c r="I69" s="37" t="n"/>
+      <c r="J69" s="37" t="n"/>
+      <c r="K69" s="37" t="n"/>
+      <c r="L69" s="37" t="n"/>
+      <c r="M69" s="37" t="n"/>
+      <c r="N69" s="37" t="n"/>
+      <c r="O69" s="37" t="n"/>
+      <c r="P69" s="37" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7962,20 +8317,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J336"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.86328125" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="32" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
-    <col width="8.125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="32" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="32" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="32" min="7" max="7"/>
+    <col width="8.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="48" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
-    <col width="150.5" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
-    <col width="8.875" customWidth="1" style="36" min="11" max="37"/>
-    <col width="8.875" customWidth="1" style="36" min="38" max="16384"/>
+    <col width="150.46484375" bestFit="1" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.86328125" customWidth="1" style="36" min="11" max="38"/>
+    <col width="8.86328125" customWidth="1" style="36" min="39" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8505,7 +8860,7 @@
       </c>
       <c r="G14" s="51" t="inlineStr"/>
       <c r="H14" s="53" t="inlineStr"/>
-      <c r="I14" s="72" t="inlineStr">
+      <c r="I14" s="71" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -8623,7 +8978,7 @@
       </c>
       <c r="G17" s="51" t="inlineStr"/>
       <c r="H17" s="53" t="inlineStr"/>
-      <c r="I17" s="72" t="inlineStr">
+      <c r="I17" s="71" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -9863,7 +10218,7 @@
         </is>
       </c>
       <c r="H49" s="53" t="inlineStr"/>
-      <c r="I49" s="72" t="inlineStr"/>
+      <c r="I49" s="71" t="inlineStr"/>
       <c r="J49" s="57" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -20078,7 +20433,7 @@
       </c>
       <c r="B314" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C314" s="50" t="n">
@@ -20120,7 +20475,7 @@
       </c>
       <c r="B315" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C315" s="50" t="n">
@@ -20162,7 +20517,7 @@
       </c>
       <c r="B316" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C316" s="50" t="n">
@@ -20200,7 +20555,7 @@
       </c>
       <c r="B317" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C317" s="50" t="n">
@@ -20242,7 +20597,7 @@
       </c>
       <c r="B318" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C318" s="50" t="n">
@@ -20280,7 +20635,7 @@
       </c>
       <c r="B319" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C319" s="50" t="n">
@@ -20312,7 +20667,7 @@
         </is>
       </c>
       <c r="I319" s="32" t="inlineStr"/>
-      <c r="J319" s="71" t="inlineStr">
+      <c r="J319" s="70" t="inlineStr">
         <is>
           <t>嗯，以后可别乱说啊，这小郎中真是…</t>
         </is>
@@ -20326,7 +20681,7 @@
       </c>
       <c r="B320" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C320" s="50" t="n">
@@ -20364,7 +20719,7 @@
       </c>
       <c r="B321" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C321" s="50" t="n">
@@ -20402,7 +20757,7 @@
       </c>
       <c r="B322" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C322" s="50" t="n">
@@ -20440,7 +20795,7 @@
       </c>
       <c r="B323" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C323" s="50" t="n">
@@ -20478,7 +20833,7 @@
       </c>
       <c r="B324" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C324" s="50" t="n">
@@ -20516,7 +20871,7 @@
       </c>
       <c r="B325" s="50" t="inlineStr">
         <is>
-          <t>022治疗失败</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C325" s="50" t="n">
@@ -20764,7 +21119,7 @@
       </c>
       <c r="B331" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C331" s="50" t="n">
@@ -20806,7 +21161,7 @@
       </c>
       <c r="B332" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C332" s="50" t="n">
@@ -20844,7 +21199,7 @@
       </c>
       <c r="B333" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C333" s="50" t="n">
@@ -20882,7 +21237,7 @@
       </c>
       <c r="B334" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C334" s="50" t="n">
@@ -20920,7 +21275,7 @@
       </c>
       <c r="B335" s="50" t="inlineStr">
         <is>
-          <t>023治疗成功</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C335" s="50" t="n">
@@ -20958,7 +21313,7 @@
       </c>
       <c r="B336" s="50" t="inlineStr">
         <is>
-          <t>023治疗失败</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C336" s="50" t="n">
@@ -21005,14 +21360,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="29.5" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="29.46484375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -23044,33 +23399,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="27" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="33" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="33" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="33" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="34" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="34" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="34" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="32" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="32" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="35" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="111"/>
-    <col width="9" customWidth="1" style="9" min="112" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="112"/>
+    <col width="9" customWidth="1" style="9" min="113" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -23881,12 +24236,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -25986,15 +26341,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="9.125" customWidth="1" style="6" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9.1328125" customWidth="1" style="6" min="6" max="6"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37766,18 +38121,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="41.75" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="41.73046875" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="23" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44901,8 +45256,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -44929,32 +45284,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -44993,20 +45348,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -45017,8 +45372,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -45029,32 +45384,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -45065,8 +45420,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -45077,8 +45432,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -45089,8 +45444,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -45101,36 +45456,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -45161,12 +45516,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -45181,12 +45536,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -45197,8 +45552,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -45215,14 +45570,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -1,48 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5330921D-CF6F-4BAB-809B-7A6E6E3FA415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA78CCA3-D944-4110-9EB8-FD9C5904C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
-    <sheet name="Story" sheetId="2" r:id="rId2"/>
-    <sheet name="StoryLine" sheetId="3" r:id="rId3"/>
-    <sheet name="Disease" sheetId="4" r:id="rId4"/>
-    <sheet name="Pulse" sheetId="5" r:id="rId5"/>
-    <sheet name="Formula" sheetId="6" r:id="rId6"/>
-    <sheet name="FormulaIngredient" sheetId="7" r:id="rId7"/>
-    <sheet name="Herb" sheetId="8" r:id="rId8"/>
-    <sheet name="Book" sheetId="9" r:id="rId9"/>
-    <sheet name="Theory" sheetId="10" r:id="rId10"/>
+    <sheet name="123" sheetId="2" r:id="rId2"/>
+    <sheet name="Story" sheetId="11" r:id="rId3"/>
+    <sheet name="StoryLine" sheetId="3" r:id="rId4"/>
+    <sheet name="Disease" sheetId="4" r:id="rId5"/>
+    <sheet name="Pulse" sheetId="5" r:id="rId6"/>
+    <sheet name="Formula" sheetId="6" r:id="rId7"/>
+    <sheet name="FormulaIngredient" sheetId="7" r:id="rId8"/>
+    <sheet name="Herb" sheetId="8" r:id="rId9"/>
+    <sheet name="Book" sheetId="9" r:id="rId10"/>
+    <sheet name="Theory" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6531" uniqueCount="1640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6219" uniqueCount="1631">
   <si>
     <t>NpcID</t>
   </si>
@@ -7149,98 +7137,103 @@
     <t>现在你可以预制方剂，开方时搜索并选取方剂名可以填写该方剂的所有药材。</t>
   </si>
   <si>
-    <t>ConditionScene</t>
-  </si>
-  <si>
-    <t>ConditionDay</t>
-  </si>
-  <si>
-    <t>ConditionMoneyOp</t>
-  </si>
-  <si>
-    <t>ConditionMoney</t>
-  </si>
-  <si>
-    <t>ConditionReputationOp</t>
-  </si>
-  <si>
-    <t>ConditionReputation</t>
-  </si>
-  <si>
-    <t>ConditionEntryId</t>
-  </si>
-  <si>
-    <t>ConditionStoryID</t>
-  </si>
-  <si>
-    <t>ConditionTreatmentResult</t>
-  </si>
-  <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
-    <t>EndGame</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>Money</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>clinic</t>
-  </si>
-  <si>
-    <t>night</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
-  </si>
-  <si>
-    <t>cured</t>
-  </si>
-  <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_sick.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/lei_wan_jun/lei_wan_jun.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/jia_quan/jia_quan_sick.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/shen_xiu_wen/shen_xiu_wen.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/yang_shan_quan/yang_shan_quan_sick.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/liu_jing_ting/liu_jing_ting.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
+    <t>剧情ID</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>金钱判定</t>
+    <phoneticPr fontId="16"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7354,10 +7347,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Noto Sans JP"/>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -7365,7 +7356,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -7373,15 +7364,29 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <family val="3"/>
-      <charset val="128"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="13">
@@ -7502,7 +7507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7656,45 +7661,42 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -11461,15 +11463,450 @@
       <c r="I79" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <cols>
+    <col min="1" max="1" width="45.625" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="11.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" ht="18" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E5" s="7">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E6" s="7">
+        <v>4</v>
+      </c>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E8" s="7">
+        <v>6</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7">
+        <v>7</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E10" s="7">
+        <v>8</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7">
+        <v>9</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E14" s="7">
+        <v>11</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E15" s="7">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E16" s="7">
+        <v>14</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" ht="18" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E17" s="7">
+        <v>15</v>
+      </c>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" ht="18" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E18" s="7">
+        <v>16</v>
+      </c>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E19" s="7">
+        <v>17</v>
+      </c>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E20" s="7">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" ht="18" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E21" s="7">
+        <v>19</v>
+      </c>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E22" s="7">
+        <v>20</v>
+      </c>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E23" s="7">
+        <v>21</v>
+      </c>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -11627,1942 +12064,1173 @@
       <c r="E14" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <dimension ref="A1:T69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="36" customWidth="1"/>
-    <col min="4" max="4" width="14" style="36" customWidth="1"/>
-    <col min="5" max="5" width="20" style="36" customWidth="1"/>
-    <col min="6" max="6" width="18" style="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.375" style="36" customWidth="1"/>
-    <col min="8" max="8" width="20.875" style="36" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="36" customWidth="1"/>
-    <col min="10" max="10" width="18" style="36" customWidth="1"/>
-    <col min="11" max="11" width="26" style="36" customWidth="1"/>
-    <col min="12" max="12" width="13.75" style="36" customWidth="1"/>
-    <col min="13" max="13" width="10.5" style="36" customWidth="1"/>
-    <col min="14" max="14" width="11.875" style="36" customWidth="1"/>
-    <col min="15" max="15" width="9" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34" style="36" customWidth="1"/>
-    <col min="17" max="17" width="8" style="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5" style="36" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="95" width="9" style="36" customWidth="1"/>
-    <col min="96" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="6.6875" style="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5625" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="8.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5625" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6875" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="94" width="9" style="36" customWidth="1"/>
+    <col min="95" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18">
-      <c r="A1" s="65" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>259</v>
-      </c>
-      <c r="C1" s="67" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" s="68" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L1" s="72" t="s">
+        <v>1623</v>
+      </c>
+      <c r="M1" s="73" t="s">
+        <v>1624</v>
+      </c>
+      <c r="N1" s="73" t="s">
+        <v>1625</v>
+      </c>
+      <c r="O1" s="73" t="s">
+        <v>1626</v>
+      </c>
+      <c r="P1" s="73" t="s">
+        <v>1627</v>
+      </c>
+      <c r="Q1" s="73" t="s">
+        <v>1628</v>
+      </c>
+      <c r="R1" s="73" t="s">
+        <v>1629</v>
+      </c>
+      <c r="S1" s="74" t="s">
         <v>1611</v>
       </c>
-      <c r="D1" s="67" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F1" s="68" t="s">
-        <v>1614</v>
-      </c>
-      <c r="G1" s="68" t="s">
-        <v>1615</v>
-      </c>
-      <c r="H1" s="68" t="s">
-        <v>1616</v>
-      </c>
-      <c r="I1" s="68" t="s">
-        <v>1617</v>
-      </c>
-      <c r="J1" s="68" t="s">
-        <v>1618</v>
-      </c>
-      <c r="K1" s="68" t="s">
-        <v>1619</v>
-      </c>
-      <c r="L1" s="71" t="s">
-        <v>1620</v>
-      </c>
-      <c r="M1" s="69" t="s">
-        <v>1621</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" s="69" t="s">
-        <v>1563</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>1622</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>1623</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>1624</v>
-      </c>
-      <c r="S1" s="74" t="s">
-        <v>1345</v>
-      </c>
-      <c r="T1" s="75" t="s">
-        <v>1625</v>
-      </c>
-      <c r="U1" s="75" t="s">
+      <c r="T1" s="74" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D2" s="72">
-        <v>1</v>
-      </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="72" t="s">
-        <v>288</v>
-      </c>
-      <c r="B3" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D3" s="72">
-        <v>1</v>
-      </c>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>301</v>
-      </c>
-      <c r="C4" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D4" s="72">
-        <v>2</v>
-      </c>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-    </row>
-    <row r="5" spans="1:21" ht="36" customHeight="1">
-      <c r="A5" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="B5" s="72" t="s">
-        <v>306</v>
-      </c>
-      <c r="C5" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D5" s="72">
-        <v>3</v>
-      </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="72" t="s">
-        <v>866</v>
-      </c>
-      <c r="P5" s="72" t="s">
-        <v>1628</v>
-      </c>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="K6" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L6" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="76">
-        <v>5</v>
-      </c>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-    </row>
-    <row r="7" spans="1:21" ht="36">
-      <c r="A7" s="72" t="s">
-        <v>322</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="K7" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L7" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="72" t="s">
-        <v>866</v>
-      </c>
-      <c r="P7" s="72" t="s">
-        <v>1628</v>
-      </c>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="76"/>
-      <c r="T7" s="76"/>
-      <c r="U7" s="76"/>
-    </row>
-    <row r="8" spans="1:21" ht="36" customHeight="1">
-      <c r="A8" s="72" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D8" s="72">
-        <v>10</v>
-      </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="76"/>
-      <c r="T8" s="76"/>
-      <c r="U8" s="76"/>
-    </row>
-    <row r="9" spans="1:21" ht="36" customHeight="1">
-      <c r="A9" s="72" t="s">
-        <v>338</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>339</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72" t="s">
-        <v>829</v>
-      </c>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="72" t="s">
-        <v>829</v>
-      </c>
-      <c r="P9" s="72" t="s">
-        <v>1631</v>
-      </c>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="76"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="72" t="s">
-        <v>360</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>361</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72" t="s">
-        <v>338</v>
-      </c>
-      <c r="K10" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L10" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72">
-        <v>1000</v>
-      </c>
-      <c r="S10" s="76">
-        <v>5</v>
-      </c>
-      <c r="T10" s="76"/>
-      <c r="U10" s="76"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="72" t="s">
-        <v>372</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>373</v>
-      </c>
-      <c r="C11" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72" t="s">
-        <v>338</v>
-      </c>
-      <c r="K11" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L11" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="76"/>
-      <c r="U11" s="76"/>
-    </row>
-    <row r="12" spans="1:21" ht="36" customHeight="1">
-      <c r="A12" s="72" t="s">
-        <v>379</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72" t="s">
-        <v>1196</v>
-      </c>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="76"/>
-      <c r="U12" s="76"/>
-    </row>
-    <row r="13" spans="1:21" ht="36" customHeight="1">
-      <c r="A13" s="72" t="s">
-        <v>395</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>396</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72" t="s">
-        <v>907</v>
-      </c>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="72" t="s">
-        <v>907</v>
-      </c>
-      <c r="P13" s="72" t="s">
-        <v>1632</v>
-      </c>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="76"/>
-      <c r="T13" s="76"/>
-      <c r="U13" s="76"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="72" t="s">
-        <v>401</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>402</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72" t="s">
-        <v>395</v>
-      </c>
-      <c r="K14" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L14" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="76"/>
-      <c r="T14" s="76"/>
-      <c r="U14" s="76"/>
-    </row>
-    <row r="15" spans="1:21" ht="36" customHeight="1">
-      <c r="A15" s="72" t="s">
-        <v>413</v>
-      </c>
-      <c r="B15" s="72" t="s">
-        <v>414</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72" t="s">
-        <v>395</v>
-      </c>
-      <c r="K15" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L15" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72" t="s">
-        <v>13</v>
-      </c>
-      <c r="O15" s="72" t="s">
-        <v>907</v>
-      </c>
-      <c r="P15" s="72" t="s">
-        <v>1632</v>
-      </c>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="76"/>
-      <c r="T15" s="76"/>
-      <c r="U15" s="76"/>
-    </row>
-    <row r="16" spans="1:21" ht="36" customHeight="1">
-      <c r="A16" s="72" t="s">
-        <v>415</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>416</v>
-      </c>
-      <c r="C16" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72" t="s">
-        <v>870</v>
-      </c>
-      <c r="J16" s="72" t="s">
-        <v>379</v>
-      </c>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="O16" s="72" t="s">
-        <v>870</v>
-      </c>
-      <c r="P16" s="72" t="s">
-        <v>1633</v>
-      </c>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="76"/>
-      <c r="T16" s="76"/>
-      <c r="U16" s="76"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="72" t="s">
-        <v>423</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>424</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72" t="s">
-        <v>415</v>
-      </c>
-      <c r="K17" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L17" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="76"/>
-      <c r="T17" s="76"/>
-      <c r="U17" s="76"/>
-    </row>
-    <row r="18" spans="1:21" ht="36" customHeight="1">
-      <c r="A18" s="72" t="s">
-        <v>431</v>
-      </c>
-      <c r="B18" s="72" t="s">
-        <v>432</v>
-      </c>
-      <c r="C18" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72" t="s">
-        <v>415</v>
-      </c>
-      <c r="K18" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L18" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" s="72" t="s">
-        <v>870</v>
-      </c>
-      <c r="P18" s="72" t="s">
-        <v>1633</v>
-      </c>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="76"/>
-      <c r="T18" s="76"/>
-      <c r="U18" s="76"/>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" s="72" t="s">
-        <v>433</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>434</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D19" s="72">
-        <v>5</v>
-      </c>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72" t="s">
-        <v>1339</v>
-      </c>
-      <c r="J19" s="72" t="s">
-        <v>423</v>
-      </c>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="76"/>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" s="72" t="s">
-        <v>451</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>452</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D20" s="72">
-        <v>1</v>
-      </c>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72" t="s">
-        <v>433</v>
-      </c>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="76"/>
-      <c r="T20" s="76"/>
-      <c r="U20" s="76"/>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" s="72" t="s">
-        <v>460</v>
-      </c>
-      <c r="B21" s="72" t="s">
-        <v>461</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D21" s="72">
-        <v>1</v>
-      </c>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72" t="s">
-        <v>451</v>
-      </c>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="76"/>
-      <c r="T21" s="76"/>
-      <c r="U21" s="76"/>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="72" t="s">
-        <v>471</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>472</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D22" s="72">
-        <v>1</v>
-      </c>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72" t="s">
-        <v>460</v>
-      </c>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="76"/>
-      <c r="T22" s="76"/>
-      <c r="U22" s="76"/>
-    </row>
-    <row r="23" spans="1:21" ht="36" customHeight="1">
-      <c r="A23" s="72" t="s">
-        <v>479</v>
-      </c>
-      <c r="B23" s="72" t="s">
-        <v>480</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D23" s="72">
-        <v>1</v>
-      </c>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72" t="s">
-        <v>471</v>
-      </c>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="76"/>
-      <c r="T23" s="76"/>
-      <c r="U23" s="76"/>
-    </row>
-    <row r="24" spans="1:21" ht="54" customHeight="1">
-      <c r="A24" s="72" t="s">
-        <v>491</v>
-      </c>
-      <c r="B24" s="72" t="s">
-        <v>492</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D24" s="72">
-        <v>1</v>
-      </c>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72" t="s">
-        <v>874</v>
-      </c>
-      <c r="J24" s="72" t="s">
-        <v>479</v>
-      </c>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="O24" s="72" t="s">
-        <v>874</v>
-      </c>
-      <c r="P24" s="72" t="s">
-        <v>1634</v>
-      </c>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="76"/>
-      <c r="U24" s="76"/>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" s="72" t="s">
-        <v>496</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>497</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72" t="s">
-        <v>491</v>
-      </c>
-      <c r="K25" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L25" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="76"/>
-      <c r="T25" s="76"/>
-      <c r="U25" s="76"/>
-    </row>
-    <row r="26" spans="1:21" ht="36">
-      <c r="A26" s="72" t="s">
-        <v>507</v>
-      </c>
-      <c r="B26" s="72" t="s">
-        <v>508</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72" t="s">
-        <v>491</v>
-      </c>
-      <c r="K26" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L26" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="O26" s="72" t="s">
-        <v>874</v>
-      </c>
-      <c r="P26" s="72" t="s">
-        <v>1634</v>
-      </c>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="76"/>
-      <c r="T26" s="76"/>
-      <c r="U26" s="76"/>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="72" t="s">
-        <v>509</v>
-      </c>
-      <c r="B27" s="72" t="s">
-        <v>510</v>
-      </c>
-      <c r="C27" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D27" s="72">
-        <v>1</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72" t="s">
-        <v>496</v>
-      </c>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="76"/>
-      <c r="T27" s="76"/>
-      <c r="U27" s="76"/>
-    </row>
-    <row r="28" spans="1:21" ht="54" customHeight="1">
-      <c r="A28" s="72" t="s">
-        <v>536</v>
-      </c>
-      <c r="B28" s="72" t="s">
-        <v>537</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D28" s="72">
-        <v>3</v>
-      </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72" t="s">
-        <v>509</v>
-      </c>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="76"/>
-      <c r="T28" s="76"/>
-      <c r="U28" s="76"/>
-    </row>
-    <row r="29" spans="1:21" ht="54" customHeight="1">
-      <c r="A29" s="72" t="s">
-        <v>547</v>
-      </c>
-      <c r="B29" s="72" t="s">
-        <v>548</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D29" s="72">
-        <v>1</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72" t="s">
-        <v>940</v>
-      </c>
-      <c r="J29" s="72" t="s">
-        <v>536</v>
-      </c>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="O29" s="72" t="s">
-        <v>940</v>
-      </c>
-      <c r="P29" s="72" t="s">
-        <v>1635</v>
-      </c>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="76"/>
-      <c r="T29" s="76"/>
-      <c r="U29" s="76"/>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" s="72" t="s">
-        <v>551</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>552</v>
-      </c>
-      <c r="C30" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72" t="s">
-        <v>547</v>
-      </c>
-      <c r="K30" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L30" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="76"/>
-      <c r="T30" s="76"/>
-      <c r="U30" s="76"/>
-    </row>
-    <row r="31" spans="1:21" ht="36">
-      <c r="A31" s="72" t="s">
-        <v>560</v>
-      </c>
-      <c r="B31" s="72" t="s">
-        <v>561</v>
-      </c>
-      <c r="C31" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72" t="s">
-        <v>547</v>
-      </c>
-      <c r="K31" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L31" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="O31" s="72" t="s">
-        <v>940</v>
-      </c>
-      <c r="P31" s="72" t="s">
-        <v>1635</v>
-      </c>
-      <c r="Q31" s="72"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="76"/>
-      <c r="T31" s="76"/>
-      <c r="U31" s="76"/>
-    </row>
-    <row r="32" spans="1:21">
-      <c r="A32" s="72" t="s">
-        <v>562</v>
-      </c>
-      <c r="B32" s="72" t="s">
-        <v>563</v>
-      </c>
-      <c r="C32" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D32" s="72">
-        <v>1</v>
-      </c>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72" t="s">
-        <v>551</v>
-      </c>
-      <c r="K32" s="72"/>
-      <c r="L32" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="72"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="76"/>
-      <c r="T32" s="76"/>
-      <c r="U32" s="76"/>
-    </row>
-    <row r="33" spans="1:21">
-      <c r="A33" s="72" t="s">
-        <v>571</v>
-      </c>
-      <c r="B33" s="72" t="s">
-        <v>572</v>
-      </c>
-      <c r="C33" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D33" s="72">
-        <v>1</v>
-      </c>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72" t="s">
-        <v>562</v>
-      </c>
-      <c r="K33" s="72"/>
-      <c r="L33" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
-      <c r="Q33" s="72"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="76"/>
-      <c r="T33" s="76"/>
-      <c r="U33" s="76"/>
-    </row>
-    <row r="34" spans="1:21">
-      <c r="A34" s="72" t="s">
-        <v>578</v>
-      </c>
-      <c r="B34" s="72" t="s">
-        <v>579</v>
-      </c>
-      <c r="C34" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D34" s="72">
-        <v>1</v>
-      </c>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72" t="s">
-        <v>571</v>
-      </c>
-      <c r="K34" s="72"/>
-      <c r="L34" s="72" t="s">
-        <v>1627</v>
-      </c>
-      <c r="M34" s="72"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="72"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="76"/>
-      <c r="T34" s="76"/>
-      <c r="U34" s="76"/>
-    </row>
-    <row r="35" spans="1:21" ht="36" customHeight="1">
-      <c r="A35" s="72" t="s">
-        <v>599</v>
-      </c>
-      <c r="B35" s="72" t="s">
-        <v>600</v>
-      </c>
-      <c r="C35" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D35" s="72">
-        <v>2</v>
-      </c>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72" t="s">
-        <v>578</v>
-      </c>
-      <c r="K35" s="72"/>
-      <c r="L35" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M35" s="72"/>
-      <c r="N35" s="72"/>
-      <c r="O35" s="72"/>
-      <c r="P35" s="72"/>
-      <c r="Q35" s="72"/>
-      <c r="R35" s="72">
-        <v>1000</v>
-      </c>
-      <c r="S35" s="76"/>
-      <c r="T35" s="76"/>
-      <c r="U35" s="76"/>
-    </row>
-    <row r="36" spans="1:21" ht="36" customHeight="1">
-      <c r="A36" s="72" t="s">
-        <v>612</v>
-      </c>
-      <c r="B36" s="72" t="s">
-        <v>613</v>
-      </c>
-      <c r="C36" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72" t="s">
-        <v>752</v>
-      </c>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="O36" s="72" t="s">
-        <v>752</v>
-      </c>
-      <c r="P36" s="72" t="s">
-        <v>1636</v>
-      </c>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="76"/>
-      <c r="T36" s="76"/>
-      <c r="U36" s="76"/>
-    </row>
-    <row r="37" spans="1:21">
-      <c r="A37" s="72" t="s">
-        <v>616</v>
-      </c>
-      <c r="B37" s="72" t="s">
-        <v>617</v>
-      </c>
-      <c r="C37" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72" t="s">
-        <v>612</v>
-      </c>
-      <c r="K37" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L37" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M37" s="72"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="72"/>
-      <c r="P37" s="72"/>
-      <c r="Q37" s="72"/>
-      <c r="R37" s="72"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="76"/>
-      <c r="U37" s="76"/>
-    </row>
-    <row r="38" spans="1:21" ht="54" customHeight="1">
-      <c r="A38" s="72" t="s">
-        <v>637</v>
-      </c>
-      <c r="B38" s="72" t="s">
-        <v>638</v>
-      </c>
-      <c r="C38" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72" t="s">
-        <v>612</v>
-      </c>
-      <c r="K38" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L38" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M38" s="72"/>
-      <c r="N38" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="O38" s="72" t="s">
-        <v>752</v>
-      </c>
-      <c r="P38" s="72" t="s">
-        <v>1636</v>
-      </c>
-      <c r="Q38" s="72"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="76"/>
-      <c r="T38" s="76"/>
-      <c r="U38" s="76"/>
-    </row>
-    <row r="39" spans="1:21" ht="36" customHeight="1">
-      <c r="A39" s="72" t="s">
-        <v>639</v>
-      </c>
-      <c r="B39" s="72" t="s">
-        <v>640</v>
-      </c>
-      <c r="C39" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72" t="s">
-        <v>786</v>
-      </c>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M39" s="72"/>
-      <c r="N39" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O39" s="72" t="s">
-        <v>786</v>
-      </c>
-      <c r="P39" s="72" t="s">
-        <v>1637</v>
-      </c>
-      <c r="Q39" s="72"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="76"/>
-      <c r="T39" s="76"/>
-      <c r="U39" s="76"/>
-    </row>
-    <row r="40" spans="1:21">
-      <c r="A40" s="72" t="s">
-        <v>648</v>
-      </c>
-      <c r="B40" s="72" t="s">
-        <v>649</v>
-      </c>
-      <c r="C40" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72" t="s">
-        <v>639</v>
-      </c>
-      <c r="K40" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L40" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M40" s="72"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="72"/>
-      <c r="P40" s="72"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="72"/>
-      <c r="S40" s="76"/>
-      <c r="T40" s="76"/>
-      <c r="U40" s="76"/>
-    </row>
-    <row r="41" spans="1:21" ht="36" customHeight="1">
-      <c r="A41" s="72" t="s">
-        <v>666</v>
-      </c>
-      <c r="B41" s="72" t="s">
-        <v>667</v>
-      </c>
-      <c r="C41" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72" t="s">
-        <v>639</v>
-      </c>
-      <c r="K41" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L41" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M41" s="72"/>
-      <c r="N41" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O41" s="72" t="s">
-        <v>786</v>
-      </c>
-      <c r="P41" s="72" t="s">
-        <v>1637</v>
-      </c>
-      <c r="Q41" s="72"/>
-      <c r="R41" s="72"/>
-      <c r="S41" s="76"/>
-      <c r="T41" s="76"/>
-      <c r="U41" s="76"/>
-    </row>
-    <row r="42" spans="1:21" ht="36" customHeight="1">
-      <c r="A42" s="72" t="s">
-        <v>668</v>
-      </c>
-      <c r="B42" s="72" t="s">
-        <v>669</v>
-      </c>
-      <c r="C42" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D42" s="72">
-        <v>1</v>
-      </c>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72" t="s">
-        <v>796</v>
-      </c>
-      <c r="J42" s="72" t="s">
-        <v>648</v>
-      </c>
-      <c r="K42" s="72"/>
-      <c r="L42" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M42" s="72"/>
-      <c r="N42" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O42" s="72" t="s">
-        <v>796</v>
-      </c>
-      <c r="P42" s="72" t="s">
-        <v>1637</v>
-      </c>
-      <c r="Q42" s="72"/>
-      <c r="R42" s="72"/>
-      <c r="S42" s="76"/>
-      <c r="T42" s="76"/>
-      <c r="U42" s="76"/>
-    </row>
-    <row r="43" spans="1:21">
-      <c r="A43" s="72" t="s">
-        <v>673</v>
-      </c>
-      <c r="B43" s="72" t="s">
-        <v>674</v>
-      </c>
-      <c r="C43" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D43" s="72"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="72"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="72" t="s">
-        <v>668</v>
-      </c>
-      <c r="K43" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L43" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="72"/>
-      <c r="P43" s="72"/>
-      <c r="Q43" s="72"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="76"/>
-      <c r="T43" s="76"/>
-      <c r="U43" s="76"/>
-    </row>
-    <row r="44" spans="1:21" ht="36" customHeight="1">
-      <c r="A44" s="72" t="s">
-        <v>693</v>
-      </c>
-      <c r="B44" s="72" t="s">
-        <v>694</v>
-      </c>
-      <c r="C44" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72" t="s">
-        <v>668</v>
-      </c>
-      <c r="K44" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L44" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O44" s="72" t="s">
-        <v>796</v>
-      </c>
-      <c r="P44" s="72" t="s">
-        <v>1637</v>
-      </c>
-      <c r="Q44" s="72"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="76"/>
-      <c r="T44" s="76"/>
-      <c r="U44" s="76"/>
-    </row>
-    <row r="45" spans="1:21" ht="36" customHeight="1">
-      <c r="A45" s="72" t="s">
-        <v>695</v>
-      </c>
-      <c r="B45" s="72" t="s">
-        <v>696</v>
-      </c>
-      <c r="C45" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="72"/>
-      <c r="I45" s="72" t="s">
-        <v>936</v>
-      </c>
-      <c r="J45" s="72"/>
-      <c r="K45" s="72"/>
-      <c r="L45" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M45" s="72"/>
-      <c r="N45" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="O45" s="72" t="s">
-        <v>936</v>
-      </c>
-      <c r="P45" s="72" t="s">
-        <v>1638</v>
-      </c>
-      <c r="Q45" s="72"/>
-      <c r="R45" s="72"/>
-      <c r="S45" s="76"/>
-      <c r="T45" s="76"/>
-      <c r="U45" s="76"/>
-    </row>
-    <row r="46" spans="1:21">
-      <c r="A46" s="72" t="s">
-        <v>700</v>
-      </c>
-      <c r="B46" s="72" t="s">
-        <v>701</v>
-      </c>
-      <c r="C46" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72" t="s">
-        <v>695</v>
-      </c>
-      <c r="K46" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L46" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M46" s="72"/>
-      <c r="N46" s="72"/>
-      <c r="O46" s="72"/>
-      <c r="P46" s="72"/>
-      <c r="Q46" s="72"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="76"/>
-      <c r="T46" s="76"/>
-      <c r="U46" s="76"/>
-    </row>
-    <row r="47" spans="1:21" ht="36">
-      <c r="A47" s="72" t="s">
-        <v>711</v>
-      </c>
-      <c r="B47" s="72" t="s">
-        <v>712</v>
-      </c>
-      <c r="C47" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="72"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72" t="s">
-        <v>695</v>
-      </c>
-      <c r="K47" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L47" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M47" s="72"/>
-      <c r="N47" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="O47" s="72" t="s">
-        <v>936</v>
-      </c>
-      <c r="P47" s="72" t="s">
-        <v>1638</v>
-      </c>
-      <c r="Q47" s="72"/>
-      <c r="R47" s="72"/>
-      <c r="S47" s="76"/>
-      <c r="T47" s="76"/>
-      <c r="U47" s="76"/>
-    </row>
-    <row r="48" spans="1:21" ht="54" customHeight="1">
-      <c r="A48" s="72" t="s">
-        <v>714</v>
-      </c>
-      <c r="B48" s="72" t="s">
-        <v>715</v>
-      </c>
-      <c r="C48" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="72" t="s">
-        <v>944</v>
-      </c>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M48" s="72"/>
-      <c r="N48" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="O48" s="72" t="s">
-        <v>944</v>
-      </c>
-      <c r="P48" s="72" t="s">
-        <v>1639</v>
-      </c>
-      <c r="Q48" s="72"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="76"/>
-      <c r="T48" s="76"/>
-      <c r="U48" s="76"/>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="A49" s="72" t="s">
-        <v>721</v>
-      </c>
-      <c r="B49" s="72" t="s">
-        <v>722</v>
-      </c>
-      <c r="C49" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="72" t="s">
-        <v>714</v>
-      </c>
-      <c r="K49" s="72" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L49" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M49" s="72"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="76"/>
-      <c r="U49" s="76"/>
-    </row>
-    <row r="50" spans="1:21" ht="36">
-      <c r="A50" s="72" t="s">
-        <v>728</v>
-      </c>
-      <c r="B50" s="72" t="s">
-        <v>729</v>
-      </c>
-      <c r="C50" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D50" s="72"/>
-      <c r="E50" s="72"/>
-      <c r="F50" s="72"/>
-      <c r="G50" s="72"/>
-      <c r="H50" s="72"/>
-      <c r="I50" s="72"/>
-      <c r="J50" s="72" t="s">
-        <v>714</v>
-      </c>
-      <c r="K50" s="72" t="s">
-        <v>1630</v>
-      </c>
-      <c r="L50" s="72" t="s">
-        <v>1626</v>
-      </c>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="O50" s="72" t="s">
-        <v>944</v>
-      </c>
-      <c r="P50" s="72" t="s">
-        <v>1639</v>
-      </c>
-      <c r="Q50" s="72"/>
-      <c r="R50" s="72"/>
-      <c r="S50" s="76"/>
-      <c r="T50" s="76"/>
-      <c r="U50" s="76"/>
-    </row>
-    <row r="51" spans="1:21">
+    <row r="2" spans="1:20">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+    </row>
+    <row r="5" spans="1:20" ht="36" customHeight="1">
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+    </row>
+    <row r="8" spans="1:20" ht="36" customHeight="1">
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+    </row>
+    <row r="9" spans="1:20" ht="36" customHeight="1">
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+    </row>
+    <row r="12" spans="1:20" ht="36" customHeight="1">
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+    </row>
+    <row r="13" spans="1:20" ht="36" customHeight="1">
+      <c r="A13" s="65"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+    </row>
+    <row r="15" spans="1:20" ht="36" customHeight="1">
+      <c r="A15" s="65"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+    </row>
+    <row r="16" spans="1:20" ht="36" customHeight="1">
+      <c r="A16" s="65"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="65"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+    </row>
+    <row r="18" spans="1:20" ht="36" customHeight="1">
+      <c r="A18" s="65"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="65"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="65"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+    </row>
+    <row r="23" spans="1:20" ht="36" customHeight="1">
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+    </row>
+    <row r="24" spans="1:20" ht="54" customHeight="1">
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" s="65"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+    </row>
+    <row r="28" spans="1:20" ht="54" customHeight="1">
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+    </row>
+    <row r="29" spans="1:20" ht="54" customHeight="1">
+      <c r="A29" s="65"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="65"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="65"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="65"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="65"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" s="65"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="65"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="65"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="65"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+    </row>
+    <row r="35" spans="1:20" ht="36" customHeight="1">
+      <c r="A35" s="65"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+    </row>
+    <row r="36" spans="1:20" ht="36" customHeight="1">
+      <c r="A36" s="65"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="67"/>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="67"/>
+      <c r="T37" s="67"/>
+    </row>
+    <row r="38" spans="1:20" ht="54" customHeight="1">
+      <c r="A38" s="65"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="67"/>
+      <c r="T38" s="67"/>
+    </row>
+    <row r="39" spans="1:20" ht="36" customHeight="1">
+      <c r="A39" s="65"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
+      <c r="N39" s="65"/>
+      <c r="O39" s="65"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="67"/>
+      <c r="T39" s="67"/>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="65"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65"/>
+      <c r="L40" s="65"/>
+      <c r="M40" s="65"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="65"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="67"/>
+      <c r="T40" s="67"/>
+    </row>
+    <row r="41" spans="1:20" ht="36" customHeight="1">
+      <c r="A41" s="65"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="67"/>
+      <c r="T41" s="67"/>
+    </row>
+    <row r="42" spans="1:20" ht="36" customHeight="1">
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" s="65"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="67"/>
+    </row>
+    <row r="44" spans="1:20" ht="36" customHeight="1">
+      <c r="A44" s="65"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="67"/>
+      <c r="T44" s="67"/>
+    </row>
+    <row r="45" spans="1:20" ht="36" customHeight="1">
+      <c r="A45" s="65"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="65"/>
+      <c r="R45" s="65"/>
+      <c r="S45" s="67"/>
+      <c r="T45" s="67"/>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" s="65"/>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="65"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="65"/>
+      <c r="R46" s="65"/>
+      <c r="S46" s="67"/>
+      <c r="T46" s="67"/>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" s="65"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
+      <c r="R47" s="65"/>
+      <c r="S47" s="67"/>
+      <c r="T47" s="67"/>
+    </row>
+    <row r="48" spans="1:20" ht="54" customHeight="1">
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="67"/>
+      <c r="T48" s="67"/>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" s="65"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="67"/>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" s="65"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="65"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="65"/>
+      <c r="R50" s="65"/>
+      <c r="S50" s="67"/>
+      <c r="T50" s="67"/>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51" s="37"/>
       <c r="B51" s="37"/>
       <c r="C51" s="37"/>
@@ -13583,9 +13251,8 @@
       <c r="R51" s="37"/>
       <c r="S51" s="64"/>
       <c r="T51" s="64"/>
-      <c r="U51" s="64"/>
-    </row>
-    <row r="52" spans="1:21">
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52" s="37"/>
       <c r="B52" s="37"/>
       <c r="C52" s="37"/>
@@ -13606,9 +13273,8 @@
       <c r="R52" s="37"/>
       <c r="S52" s="64"/>
       <c r="T52" s="64"/>
-      <c r="U52" s="64"/>
-    </row>
-    <row r="53" spans="1:21">
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53" s="37"/>
       <c r="B53" s="37"/>
       <c r="C53" s="37"/>
@@ -13629,9 +13295,8 @@
       <c r="R53" s="37"/>
       <c r="S53" s="64"/>
       <c r="T53" s="64"/>
-      <c r="U53" s="64"/>
-    </row>
-    <row r="54" spans="1:21">
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54" s="37"/>
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
@@ -13652,9 +13317,8 @@
       <c r="R54" s="37"/>
       <c r="S54" s="64"/>
       <c r="T54" s="64"/>
-      <c r="U54" s="64"/>
-    </row>
-    <row r="55" spans="1:21">
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55" s="37"/>
       <c r="B55" s="37"/>
       <c r="C55" s="37"/>
@@ -13675,9 +13339,8 @@
       <c r="R55" s="37"/>
       <c r="S55" s="64"/>
       <c r="T55" s="64"/>
-      <c r="U55" s="64"/>
-    </row>
-    <row r="56" spans="1:21">
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56" s="37"/>
       <c r="B56" s="37"/>
       <c r="C56" s="37"/>
@@ -13698,9 +13361,8 @@
       <c r="R56" s="37"/>
       <c r="S56" s="64"/>
       <c r="T56" s="64"/>
-      <c r="U56" s="64"/>
-    </row>
-    <row r="57" spans="1:21">
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57" s="37"/>
       <c r="B57" s="37"/>
       <c r="C57" s="37"/>
@@ -13721,9 +13383,8 @@
       <c r="R57" s="37"/>
       <c r="S57" s="64"/>
       <c r="T57" s="64"/>
-      <c r="U57" s="64"/>
-    </row>
-    <row r="58" spans="1:21">
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58" s="37"/>
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
@@ -13744,9 +13405,8 @@
       <c r="R58" s="37"/>
       <c r="S58" s="64"/>
       <c r="T58" s="64"/>
-      <c r="U58" s="64"/>
-    </row>
-    <row r="59" spans="1:21">
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59" s="37"/>
       <c r="B59" s="37"/>
       <c r="C59" s="37"/>
@@ -13767,9 +13427,8 @@
       <c r="R59" s="37"/>
       <c r="S59" s="64"/>
       <c r="T59" s="64"/>
-      <c r="U59" s="64"/>
-    </row>
-    <row r="60" spans="1:21">
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60" s="37"/>
       <c r="B60" s="37"/>
       <c r="C60" s="37"/>
@@ -13790,9 +13449,8 @@
       <c r="R60" s="37"/>
       <c r="S60" s="64"/>
       <c r="T60" s="64"/>
-      <c r="U60" s="64"/>
-    </row>
-    <row r="61" spans="1:21">
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61" s="37"/>
       <c r="B61" s="37"/>
       <c r="C61" s="37"/>
@@ -13813,9 +13471,8 @@
       <c r="R61" s="37"/>
       <c r="S61" s="64"/>
       <c r="T61" s="64"/>
-      <c r="U61" s="64"/>
-    </row>
-    <row r="62" spans="1:21">
+    </row>
+    <row r="62" spans="1:20">
       <c r="A62" s="37"/>
       <c r="B62" s="37"/>
       <c r="C62" s="37"/>
@@ -13836,9 +13493,8 @@
       <c r="R62" s="37"/>
       <c r="S62" s="64"/>
       <c r="T62" s="64"/>
-      <c r="U62" s="64"/>
-    </row>
-    <row r="63" spans="1:21">
+    </row>
+    <row r="63" spans="1:20">
       <c r="A63" s="37"/>
       <c r="B63" s="37"/>
       <c r="C63" s="37"/>
@@ -13859,9 +13515,8 @@
       <c r="R63" s="37"/>
       <c r="S63" s="64"/>
       <c r="T63" s="64"/>
-      <c r="U63" s="64"/>
-    </row>
-    <row r="64" spans="1:21">
+    </row>
+    <row r="64" spans="1:20">
       <c r="A64" s="37"/>
       <c r="B64" s="37"/>
       <c r="C64" s="37"/>
@@ -13882,9 +13537,8 @@
       <c r="R64" s="37"/>
       <c r="S64" s="64"/>
       <c r="T64" s="64"/>
-      <c r="U64" s="64"/>
-    </row>
-    <row r="65" spans="1:21">
+    </row>
+    <row r="65" spans="1:20">
       <c r="A65" s="37"/>
       <c r="B65" s="37"/>
       <c r="C65" s="37"/>
@@ -13905,9 +13559,8 @@
       <c r="R65" s="37"/>
       <c r="S65" s="64"/>
       <c r="T65" s="64"/>
-      <c r="U65" s="64"/>
-    </row>
-    <row r="66" spans="1:21">
+    </row>
+    <row r="66" spans="1:20">
       <c r="A66" s="37"/>
       <c r="B66" s="37"/>
       <c r="C66" s="37"/>
@@ -13928,9 +13581,8 @@
       <c r="R66" s="37"/>
       <c r="S66" s="64"/>
       <c r="T66" s="64"/>
-      <c r="U66" s="64"/>
-    </row>
-    <row r="67" spans="1:21">
+    </row>
+    <row r="67" spans="1:20">
       <c r="A67" s="37"/>
       <c r="B67" s="37"/>
       <c r="C67" s="37"/>
@@ -13951,9 +13603,8 @@
       <c r="R67" s="37"/>
       <c r="S67" s="64"/>
       <c r="T67" s="64"/>
-      <c r="U67" s="64"/>
-    </row>
-    <row r="68" spans="1:21">
+    </row>
+    <row r="68" spans="1:20">
       <c r="A68" s="37"/>
       <c r="B68" s="37"/>
       <c r="C68" s="37"/>
@@ -13974,9 +13625,8 @@
       <c r="R68" s="37"/>
       <c r="S68" s="64"/>
       <c r="T68" s="64"/>
-      <c r="U68" s="64"/>
-    </row>
-    <row r="69" spans="1:21">
+    </row>
+    <row r="69" spans="1:20">
       <c r="A69" s="37"/>
       <c r="B69" s="37"/>
       <c r="C69" s="37"/>
@@ -13997,10 +13647,9 @@
       <c r="R69" s="37"/>
       <c r="S69" s="64"/>
       <c r="T69" s="64"/>
-      <c r="U69" s="64"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <dataValidations count="4">
     <dataValidation type="list" sqref="C2:C50 L2:L50" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"clinic,night,map"</formula1>
@@ -14020,6 +13669,94 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C48339D4-4E33-43CF-BB53-AE7D6F1B1B90}">
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="6.6875" style="77" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5625" style="77" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="8.375" style="77" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="77" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="77" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5625" style="77" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6875" style="77" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.75" style="77" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" style="77" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.375" style="77" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.5625" style="77" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" style="77" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="76"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" s="75" customFormat="1">
+      <c r="A1" s="68" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G1" s="71" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I1" s="71" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L1" s="72" t="s">
+        <v>1623</v>
+      </c>
+      <c r="M1" s="73" t="s">
+        <v>1624</v>
+      </c>
+      <c r="N1" s="73" t="s">
+        <v>1625</v>
+      </c>
+      <c r="O1" s="73" t="s">
+        <v>1626</v>
+      </c>
+      <c r="P1" s="73" t="s">
+        <v>1627</v>
+      </c>
+      <c r="Q1" s="73" t="s">
+        <v>1628</v>
+      </c>
+      <c r="R1" s="73" t="s">
+        <v>1629</v>
+      </c>
+      <c r="S1" s="74" t="s">
+        <v>1611</v>
+      </c>
+      <c r="T1" s="74" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J352"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18"/>
@@ -15540,7 +15277,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="18.75">
+    <row r="60" spans="1:10">
       <c r="A60" s="47" t="s">
         <v>338</v>
       </c>
@@ -22899,15 +22636,15 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="37" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.25" style="3" customWidth="1"/>
@@ -24081,15 +23818,15 @@
       <c r="C114" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.5" style="32" customWidth="1"/>
@@ -24760,15 +24497,15 @@
       <c r="A50" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E114"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="1" width="25.5" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.125" style="3" customWidth="1"/>
@@ -25680,15 +25417,15 @@
     <row r="112" ht="15" customHeight="1"/>
     <row r="114" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G357"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14.375" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="4" customWidth="1"/>
@@ -33892,15 +33629,15 @@
       <c r="F357" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L129"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="7" customWidth="1"/>
@@ -38323,7 +38060,7 @@
       <c r="A129" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19"/>
+  <phoneticPr fontId="16"/>
   <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A103 A116:A1048576">
     <cfRule type="duplicateValues" dxfId="161" priority="2013"/>
   </conditionalFormatting>
@@ -38668,439 +38405,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="45.625" customWidth="1"/>
-    <col min="2" max="2" width="23.5" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="11.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1551</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>1554</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>1557</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" ht="18" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>1352</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1561</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>1562</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E5" s="7">
-        <v>3</v>
-      </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>990</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1565</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1567</v>
-      </c>
-      <c r="E6" s="7">
-        <v>4</v>
-      </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>1568</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1569</v>
-      </c>
-      <c r="E7" s="7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1567</v>
-      </c>
-      <c r="E8" s="7">
-        <v>6</v>
-      </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>1571</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7">
-        <v>7</v>
-      </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>1573</v>
-      </c>
-      <c r="E10" s="7">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7">
-        <v>9</v>
-      </c>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E12" s="7">
-        <v>10</v>
-      </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>1578</v>
-      </c>
-      <c r="E13" s="7">
-        <v>12</v>
-      </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>1580</v>
-      </c>
-      <c r="E14" s="7">
-        <v>11</v>
-      </c>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>1582</v>
-      </c>
-      <c r="E15" s="7">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>1583</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>1584</v>
-      </c>
-      <c r="E16" s="7">
-        <v>14</v>
-      </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1">
-      <c r="A17" s="7" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E17" s="7">
-        <v>15</v>
-      </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E18" s="7">
-        <v>16</v>
-      </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1">
-      <c r="A19" s="7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E19" s="7">
-        <v>17</v>
-      </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="7" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>1591</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E20" s="7">
-        <v>18</v>
-      </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E21" s="7">
-        <v>19</v>
-      </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>1596</v>
-      </c>
-      <c r="E22" s="7">
-        <v>20</v>
-      </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>1597</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E23" s="7">
-        <v>21</v>
-      </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="19"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -5907,7 +5907,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>end_game</t>
+          <t>endgame</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5953,7 +5953,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>end_game</t>
+          <t>endgame</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>end_game</t>
+          <t>endgame</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>end_game</t>
+          <t>endgame</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF6CF33-772E-4476-8F28-60447208E21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D646C5-C41E-46C2-AE11-BEFB5B616A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,25 @@
     <sheet name="Book" sheetId="9" r:id="rId9"/>
     <sheet name="Theory" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6814" uniqueCount="1713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6815" uniqueCount="1714">
   <si>
     <t>NpcID</t>
   </si>
@@ -7440,6 +7453,10 @@
   </si>
   <si>
     <t>现在你可以预制方剂，开方时搜索并选取方剂名可以填写该方剂的所有药材。</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7713,7 +7730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7851,9 +7868,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7863,25 +7877,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7896,13 +7895,70 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -11719,7 +11775,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -14075,7 +14131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J394"/>
+  <dimension ref="A1:K394"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="10" customWidth="1"/>
@@ -14087,12 +14143,13 @@
     <col min="7" max="7" width="13.875" style="10" customWidth="1"/>
     <col min="8" max="8" width="8.125" style="10" customWidth="1"/>
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
-    <col min="10" max="10" width="150.5" style="10" customWidth="1"/>
-    <col min="11" max="47" width="8.875" style="36" customWidth="1"/>
+    <col min="10" max="10" width="150.5" style="88" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="90" customWidth="1"/>
+    <col min="12" max="47" width="8.875" style="36" customWidth="1"/>
     <col min="48" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="37" t="s">
         <v>426</v>
       </c>
@@ -14120,11 +14177,14 @@
       <c r="I1" s="37" t="s">
         <v>434</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="71" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+      <c r="K1" s="89" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="33" customHeight="1">
       <c r="A2" s="57" t="s">
         <v>282</v>
       </c>
@@ -14144,11 +14204,11 @@
       <c r="I2" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="72" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="57" t="s">
         <v>282</v>
       </c>
@@ -14172,11 +14232,11 @@
       </c>
       <c r="H3" s="59"/>
       <c r="I3" s="58"/>
-      <c r="J3" s="61" t="s">
+      <c r="J3" s="73" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="57" t="s">
         <v>282</v>
       </c>
@@ -14200,11 +14260,11 @@
       </c>
       <c r="H4" s="59"/>
       <c r="I4" s="58"/>
-      <c r="J4" s="57" t="s">
+      <c r="J4" s="74" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="57" t="s">
         <v>282</v>
       </c>
@@ -14226,11 +14286,11 @@
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
       <c r="I5" s="58"/>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="74" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="57" t="s">
         <v>282</v>
       </c>
@@ -14252,11 +14312,11 @@
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
       <c r="I6" s="58"/>
-      <c r="J6" s="60" t="s">
+      <c r="J6" s="72" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="57" t="s">
         <v>287</v>
       </c>
@@ -14276,15 +14336,15 @@
         <v>445</v>
       </c>
       <c r="G7" s="58"/>
-      <c r="H7" s="62"/>
+      <c r="H7" s="61"/>
       <c r="I7" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J7" s="60" t="s">
+      <c r="J7" s="72" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="57" t="s">
         <v>287</v>
       </c>
@@ -14306,13 +14366,13 @@
       <c r="G8" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H8" s="62"/>
+      <c r="H8" s="61"/>
       <c r="I8" s="58"/>
-      <c r="J8" s="60" t="s">
+      <c r="J8" s="72" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="57" t="s">
         <v>287</v>
       </c>
@@ -14326,15 +14386,15 @@
         <v>436</v>
       </c>
       <c r="E9" s="60"/>
-      <c r="F9" s="62"/>
+      <c r="F9" s="61"/>
       <c r="G9" s="58"/>
-      <c r="H9" s="62"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="58"/>
-      <c r="J9" s="60" t="s">
+      <c r="J9" s="72" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="57" t="s">
         <v>287</v>
       </c>
@@ -14356,11 +14416,11 @@
       <c r="G10" s="58"/>
       <c r="H10" s="58"/>
       <c r="I10" s="58"/>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="72" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" s="57" t="s">
         <v>287</v>
       </c>
@@ -14384,11 +14444,11 @@
       </c>
       <c r="H11" s="58"/>
       <c r="I11" s="58"/>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="72" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" s="57" t="s">
         <v>287</v>
       </c>
@@ -14407,14 +14467,14 @@
       <c r="F12" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="64" t="s">
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="75" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" s="57" t="s">
         <v>287</v>
       </c>
@@ -14433,14 +14493,14 @@
       <c r="F13" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="64" t="s">
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="75" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" s="57" t="s">
         <v>287</v>
       </c>
@@ -14459,14 +14519,14 @@
       <c r="F14" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64" t="s">
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="75" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" s="57" t="s">
         <v>287</v>
       </c>
@@ -14485,14 +14545,14 @@
       <c r="F15" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64" t="s">
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="75" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" s="57" t="s">
         <v>287</v>
       </c>
@@ -14511,10 +14571,10 @@
       <c r="F16" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="64" t="s">
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="75" t="s">
         <v>457</v>
       </c>
     </row>
@@ -14537,10 +14597,10 @@
       <c r="F17" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="64" t="s">
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="75" t="s">
         <v>458</v>
       </c>
     </row>
@@ -14566,9 +14626,9 @@
       <c r="G18" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="64" t="s">
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="75" t="s">
         <v>459</v>
       </c>
     </row>
@@ -14591,10 +14651,10 @@
       <c r="F19" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="64" t="s">
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="75" t="s">
         <v>460</v>
       </c>
     </row>
@@ -14618,11 +14678,11 @@
         <v>445</v>
       </c>
       <c r="G20" s="58"/>
-      <c r="H20" s="62"/>
+      <c r="H20" s="61"/>
       <c r="I20" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J20" s="60" t="s">
+      <c r="J20" s="72" t="s">
         <v>461</v>
       </c>
     </row>
@@ -14642,15 +14702,15 @@
       <c r="E21" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G21" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H21" s="62"/>
+      <c r="H21" s="61"/>
       <c r="I21" s="58"/>
-      <c r="J21" s="60" t="s">
+      <c r="J21" s="72" t="s">
         <v>462</v>
       </c>
     </row>
@@ -14674,9 +14734,9 @@
         <v>445</v>
       </c>
       <c r="G22" s="58"/>
-      <c r="H22" s="62"/>
+      <c r="H22" s="61"/>
       <c r="I22" s="58"/>
-      <c r="J22" s="60" t="s">
+      <c r="J22" s="72" t="s">
         <v>463</v>
       </c>
     </row>
@@ -14696,7 +14756,7 @@
       <c r="E23" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G23" s="59" t="s">
@@ -14704,7 +14764,7 @@
       </c>
       <c r="H23" s="58"/>
       <c r="I23" s="58"/>
-      <c r="J23" s="60" t="s">
+      <c r="J23" s="72" t="s">
         <v>464</v>
       </c>
     </row>
@@ -14730,7 +14790,7 @@
       <c r="G24" s="58"/>
       <c r="H24" s="58"/>
       <c r="I24" s="58"/>
-      <c r="J24" s="57" t="s">
+      <c r="J24" s="74" t="s">
         <v>465</v>
       </c>
     </row>
@@ -14750,15 +14810,15 @@
       <c r="E25" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G25" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H25" s="63"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="64" t="s">
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="75" t="s">
         <v>466</v>
       </c>
     </row>
@@ -14778,15 +14838,15 @@
       <c r="E26" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G26" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="64" t="s">
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="75" t="s">
         <v>467</v>
       </c>
     </row>
@@ -14803,7 +14863,7 @@
       <c r="D27" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E27" s="64" t="s">
+      <c r="E27" s="63" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="59" t="s">
@@ -14812,9 +14872,9 @@
       <c r="G27" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="64" t="s">
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="75" t="s">
         <v>468</v>
       </c>
     </row>
@@ -14834,15 +14894,15 @@
       <c r="E28" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="62" t="s">
+      <c r="F28" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G28" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="64" t="s">
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="75" t="s">
         <v>469</v>
       </c>
     </row>
@@ -14865,10 +14925,10 @@
       <c r="F29" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="64" t="s">
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="75" t="s">
         <v>470</v>
       </c>
     </row>
@@ -14892,11 +14952,11 @@
         <v>445</v>
       </c>
       <c r="G30" s="58"/>
-      <c r="H30" s="62"/>
+      <c r="H30" s="61"/>
       <c r="I30" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J30" s="60" t="s">
+      <c r="J30" s="72" t="s">
         <v>471</v>
       </c>
     </row>
@@ -14916,9 +14976,9 @@
       <c r="E31" s="57"/>
       <c r="F31" s="58"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="62"/>
+      <c r="H31" s="61"/>
       <c r="I31" s="58"/>
-      <c r="J31" s="60" t="s">
+      <c r="J31" s="72" t="s">
         <v>472</v>
       </c>
     </row>
@@ -14938,15 +14998,15 @@
       <c r="E32" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G32" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="H32" s="62"/>
+      <c r="H32" s="61"/>
       <c r="I32" s="58"/>
-      <c r="J32" s="60" t="s">
+      <c r="J32" s="72" t="s">
         <v>473</v>
       </c>
     </row>
@@ -14972,7 +15032,7 @@
       <c r="G33" s="58"/>
       <c r="H33" s="58"/>
       <c r="I33" s="58"/>
-      <c r="J33" s="60" t="s">
+      <c r="J33" s="72" t="s">
         <v>474</v>
       </c>
     </row>
@@ -14992,7 +15052,7 @@
       <c r="E34" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="62" t="s">
+      <c r="F34" s="61" t="s">
         <v>440</v>
       </c>
       <c r="G34" s="59" t="s">
@@ -15000,7 +15060,7 @@
       </c>
       <c r="H34" s="58"/>
       <c r="I34" s="58"/>
-      <c r="J34" s="60" t="s">
+      <c r="J34" s="72" t="s">
         <v>475</v>
       </c>
     </row>
@@ -15017,14 +15077,14 @@
       <c r="D35" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E35" s="63"/>
+      <c r="E35" s="62"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
       <c r="I35" s="58" t="s">
         <v>476</v>
       </c>
-      <c r="J35" s="65" t="s">
+      <c r="J35" s="76" t="s">
         <v>477</v>
       </c>
     </row>
@@ -15041,12 +15101,12 @@
       <c r="D36" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E36" s="63"/>
+      <c r="E36" s="62"/>
       <c r="F36" s="58"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="63" t="s">
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="77" t="s">
         <v>478</v>
       </c>
     </row>
@@ -15063,12 +15123,12 @@
       <c r="D37" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E37" s="63"/>
+      <c r="E37" s="62"/>
       <c r="F37" s="58"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="66" t="s">
+      <c r="G37" s="62"/>
+      <c r="H37" s="62"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="78" t="s">
         <v>479</v>
       </c>
     </row>
@@ -15092,11 +15152,11 @@
         <v>440</v>
       </c>
       <c r="G38" s="58"/>
-      <c r="H38" s="62"/>
+      <c r="H38" s="61"/>
       <c r="I38" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J38" s="60" t="s">
+      <c r="J38" s="72" t="s">
         <v>480</v>
       </c>
     </row>
@@ -15116,11 +15176,11 @@
       <c r="E39" s="57"/>
       <c r="F39" s="58"/>
       <c r="G39" s="58"/>
-      <c r="H39" s="62"/>
+      <c r="H39" s="61"/>
       <c r="I39" s="58" t="s">
         <v>481</v>
       </c>
-      <c r="J39" s="60" t="s">
+      <c r="J39" s="72" t="s">
         <v>482</v>
       </c>
     </row>
@@ -15148,7 +15208,7 @@
       <c r="I40" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J40" s="60" t="s">
+      <c r="J40" s="72" t="s">
         <v>483</v>
       </c>
     </row>
@@ -15174,7 +15234,7 @@
       <c r="G41" s="58"/>
       <c r="H41" s="59"/>
       <c r="I41" s="58"/>
-      <c r="J41" s="60" t="s">
+      <c r="J41" s="72" t="s">
         <v>484</v>
       </c>
     </row>
@@ -15200,7 +15260,7 @@
       <c r="G42" s="58"/>
       <c r="H42" s="59"/>
       <c r="I42" s="58"/>
-      <c r="J42" s="60" t="s">
+      <c r="J42" s="72" t="s">
         <v>485</v>
       </c>
     </row>
@@ -15221,10 +15281,10 @@
       <c r="F43" s="58"/>
       <c r="G43" s="58"/>
       <c r="H43" s="58"/>
-      <c r="I43" s="77" t="s">
+      <c r="I43" s="70" t="s">
         <v>486</v>
       </c>
-      <c r="J43" s="60" t="s">
+      <c r="J43" s="72" t="s">
         <v>487</v>
       </c>
     </row>
@@ -15248,7 +15308,7 @@
       <c r="I44" s="58" t="s">
         <v>488</v>
       </c>
-      <c r="J44" s="61" t="s">
+      <c r="J44" s="73" t="s">
         <v>489</v>
       </c>
     </row>
@@ -15274,7 +15334,7 @@
       <c r="G45" s="58"/>
       <c r="H45" s="59"/>
       <c r="I45" s="58"/>
-      <c r="J45" s="61" t="s">
+      <c r="J45" s="73" t="s">
         <v>490</v>
       </c>
     </row>
@@ -15300,7 +15360,7 @@
       <c r="G46" s="58"/>
       <c r="H46" s="59"/>
       <c r="I46" s="58"/>
-      <c r="J46" s="61" t="s">
+      <c r="J46" s="73" t="s">
         <v>491</v>
       </c>
     </row>
@@ -15326,7 +15386,7 @@
       <c r="G47" s="58"/>
       <c r="H47" s="59"/>
       <c r="I47" s="58"/>
-      <c r="J47" s="61" t="s">
+      <c r="J47" s="73" t="s">
         <v>492</v>
       </c>
     </row>
@@ -15352,7 +15412,7 @@
       <c r="G48" s="58"/>
       <c r="H48" s="59"/>
       <c r="I48" s="58"/>
-      <c r="J48" s="61" t="s">
+      <c r="J48" s="73" t="s">
         <v>493</v>
       </c>
     </row>
@@ -15378,7 +15438,7 @@
       <c r="G49" s="58"/>
       <c r="H49" s="59"/>
       <c r="I49" s="58"/>
-      <c r="J49" s="61" t="s">
+      <c r="J49" s="73" t="s">
         <v>494</v>
       </c>
     </row>
@@ -15404,7 +15464,7 @@
       <c r="G50" s="58"/>
       <c r="H50" s="59"/>
       <c r="I50" s="58"/>
-      <c r="J50" s="61" t="s">
+      <c r="J50" s="73" t="s">
         <v>495</v>
       </c>
     </row>
@@ -15430,7 +15490,7 @@
       <c r="G51" s="58"/>
       <c r="H51" s="59"/>
       <c r="I51" s="58"/>
-      <c r="J51" s="61" t="s">
+      <c r="J51" s="73" t="s">
         <v>496</v>
       </c>
     </row>
@@ -15456,7 +15516,7 @@
       <c r="G52" s="58"/>
       <c r="H52" s="59"/>
       <c r="I52" s="58"/>
-      <c r="J52" s="61" t="s">
+      <c r="J52" s="73" t="s">
         <v>497</v>
       </c>
     </row>
@@ -15482,7 +15542,7 @@
       <c r="G53" s="58"/>
       <c r="H53" s="59"/>
       <c r="I53" s="58"/>
-      <c r="J53" s="61" t="s">
+      <c r="J53" s="73" t="s">
         <v>498</v>
       </c>
     </row>
@@ -15508,29 +15568,29 @@
       <c r="G54" s="58"/>
       <c r="H54" s="59"/>
       <c r="I54" s="58"/>
-      <c r="J54" s="61" t="s">
+      <c r="J54" s="73" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="62" t="s">
         <v>304</v>
       </c>
-      <c r="C55" s="63">
+      <c r="C55" s="62">
         <v>12</v>
       </c>
       <c r="D55" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E55" s="63"/>
+      <c r="E55" s="62"/>
       <c r="F55" s="58"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
-      <c r="I55" s="63"/>
-      <c r="J55" s="61" t="s">
+      <c r="G55" s="62"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="62"/>
+      <c r="J55" s="73" t="s">
         <v>500</v>
       </c>
     </row>
@@ -15551,10 +15611,10 @@
       <c r="F56" s="59"/>
       <c r="G56" s="58"/>
       <c r="H56" s="59"/>
-      <c r="I56" s="77" t="s">
+      <c r="I56" s="70" t="s">
         <v>501</v>
       </c>
-      <c r="J56" s="67" t="s">
+      <c r="J56" s="79" t="s">
         <v>502</v>
       </c>
     </row>
@@ -15579,8 +15639,8 @@
       </c>
       <c r="G57" s="58"/>
       <c r="H57" s="59"/>
-      <c r="I57" s="77"/>
-      <c r="J57" s="67" t="s">
+      <c r="I57" s="70"/>
+      <c r="J57" s="79" t="s">
         <v>503</v>
       </c>
     </row>
@@ -15606,7 +15666,7 @@
       <c r="G58" s="58"/>
       <c r="H58" s="59"/>
       <c r="I58" s="58"/>
-      <c r="J58" s="67" t="s">
+      <c r="J58" s="79" t="s">
         <v>504</v>
       </c>
     </row>
@@ -15632,7 +15692,7 @@
       <c r="G59" s="58"/>
       <c r="H59" s="59"/>
       <c r="I59" s="58"/>
-      <c r="J59" s="60" t="s">
+      <c r="J59" s="72" t="s">
         <v>505</v>
       </c>
     </row>
@@ -15657,10 +15717,10 @@
       </c>
       <c r="G60" s="58"/>
       <c r="H60" s="59"/>
-      <c r="I60" s="77" t="s">
+      <c r="I60" s="70" t="s">
         <v>506</v>
       </c>
-      <c r="J60" s="61" t="s">
+      <c r="J60" s="73" t="s">
         <v>507</v>
       </c>
     </row>
@@ -15686,7 +15746,7 @@
       <c r="G61" s="58"/>
       <c r="H61" s="59"/>
       <c r="I61" s="58"/>
-      <c r="J61" s="68" t="s">
+      <c r="J61" s="80" t="s">
         <v>508</v>
       </c>
     </row>
@@ -15709,10 +15769,10 @@
       <c r="F62" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G62" s="63"/>
+      <c r="G62" s="62"/>
       <c r="H62" s="59"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="57" t="s">
+      <c r="I62" s="62"/>
+      <c r="J62" s="74" t="s">
         <v>509</v>
       </c>
     </row>
@@ -15735,10 +15795,10 @@
       <c r="F63" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G63" s="63"/>
+      <c r="G63" s="62"/>
       <c r="H63" s="59"/>
-      <c r="I63" s="63"/>
-      <c r="J63" s="57" t="s">
+      <c r="I63" s="62"/>
+      <c r="J63" s="74" t="s">
         <v>510</v>
       </c>
     </row>
@@ -15766,7 +15826,7 @@
       <c r="I64" s="58" t="s">
         <v>511</v>
       </c>
-      <c r="J64" s="60" t="s">
+      <c r="J64" s="72" t="s">
         <v>512</v>
       </c>
     </row>
@@ -15792,7 +15852,7 @@
       <c r="G65" s="58"/>
       <c r="H65" s="59"/>
       <c r="I65" s="58"/>
-      <c r="J65" s="60" t="s">
+      <c r="J65" s="72" t="s">
         <v>513</v>
       </c>
     </row>
@@ -15820,7 +15880,7 @@
       <c r="I66" s="58" t="s">
         <v>514</v>
       </c>
-      <c r="J66" s="57" t="s">
+      <c r="J66" s="74" t="s">
         <v>515</v>
       </c>
     </row>
@@ -15846,7 +15906,7 @@
       <c r="G67" s="58"/>
       <c r="H67" s="59"/>
       <c r="I67" s="58"/>
-      <c r="J67" s="57" t="s">
+      <c r="J67" s="74" t="s">
         <v>516</v>
       </c>
     </row>
@@ -15872,7 +15932,7 @@
       <c r="G68" s="58"/>
       <c r="H68" s="59"/>
       <c r="I68" s="58"/>
-      <c r="J68" s="61" t="s">
+      <c r="J68" s="73" t="s">
         <v>517</v>
       </c>
     </row>
@@ -15898,7 +15958,7 @@
       <c r="G69" s="58"/>
       <c r="H69" s="59"/>
       <c r="I69" s="58"/>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="74" t="s">
         <v>518</v>
       </c>
     </row>
@@ -15924,18 +15984,18 @@
       <c r="G70" s="58"/>
       <c r="H70" s="59"/>
       <c r="I70" s="58"/>
-      <c r="J70" s="57" t="s">
+      <c r="J70" s="74" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="63" t="s">
+      <c r="A71" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="62" t="s">
         <v>310</v>
       </c>
-      <c r="C71" s="63">
+      <c r="C71" s="62">
         <v>6</v>
       </c>
       <c r="D71" s="57" t="s">
@@ -15947,10 +16007,10 @@
       <c r="F71" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G71" s="63"/>
+      <c r="G71" s="62"/>
       <c r="H71" s="59"/>
-      <c r="I71" s="63"/>
-      <c r="J71" s="64" t="s">
+      <c r="I71" s="62"/>
+      <c r="J71" s="75" t="s">
         <v>520</v>
       </c>
     </row>
@@ -15978,7 +16038,7 @@
       <c r="I72" s="58" t="s">
         <v>514</v>
       </c>
-      <c r="J72" s="60" t="s">
+      <c r="J72" s="72" t="s">
         <v>521</v>
       </c>
     </row>
@@ -16004,7 +16064,7 @@
       <c r="G73" s="58"/>
       <c r="H73" s="59"/>
       <c r="I73" s="58"/>
-      <c r="J73" s="63" t="s">
+      <c r="J73" s="77" t="s">
         <v>522</v>
       </c>
     </row>
@@ -16030,7 +16090,7 @@
       <c r="G74" s="58"/>
       <c r="H74" s="59"/>
       <c r="I74" s="58"/>
-      <c r="J74" s="63" t="s">
+      <c r="J74" s="77" t="s">
         <v>523</v>
       </c>
     </row>
@@ -16056,7 +16116,7 @@
       <c r="G75" s="58"/>
       <c r="H75" s="58"/>
       <c r="I75" s="58"/>
-      <c r="J75" s="63" t="s">
+      <c r="J75" s="77" t="s">
         <v>524</v>
       </c>
     </row>
@@ -16082,18 +16142,18 @@
       <c r="G76" s="58"/>
       <c r="H76" s="58"/>
       <c r="I76" s="58"/>
-      <c r="J76" s="64" t="s">
+      <c r="J76" s="75" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="62" t="s">
         <v>313</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="62" t="s">
         <v>314</v>
       </c>
-      <c r="C77" s="63">
+      <c r="C77" s="62">
         <v>6</v>
       </c>
       <c r="D77" s="57" t="s">
@@ -16105,10 +16165,10 @@
       <c r="F77" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G77" s="63"/>
-      <c r="H77" s="63"/>
-      <c r="I77" s="63"/>
-      <c r="J77" s="64" t="s">
+      <c r="G77" s="62"/>
+      <c r="H77" s="62"/>
+      <c r="I77" s="62"/>
+      <c r="J77" s="75" t="s">
         <v>526</v>
       </c>
     </row>
@@ -16136,7 +16196,7 @@
       <c r="I78" s="58" t="s">
         <v>514</v>
       </c>
-      <c r="J78" s="60" t="s">
+      <c r="J78" s="72" t="s">
         <v>527</v>
       </c>
     </row>
@@ -16164,7 +16224,7 @@
       <c r="I79" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J79" s="60" t="s">
+      <c r="J79" s="72" t="s">
         <v>528</v>
       </c>
     </row>
@@ -16190,7 +16250,7 @@
       <c r="G80" s="58"/>
       <c r="H80" s="59"/>
       <c r="I80" s="58"/>
-      <c r="J80" s="60" t="s">
+      <c r="J80" s="72" t="s">
         <v>529</v>
       </c>
     </row>
@@ -16216,7 +16276,7 @@
       <c r="G81" s="58"/>
       <c r="H81" s="59"/>
       <c r="I81" s="58"/>
-      <c r="J81" s="60" t="s">
+      <c r="J81" s="72" t="s">
         <v>530</v>
       </c>
     </row>
@@ -16242,7 +16302,7 @@
       <c r="G82" s="58"/>
       <c r="H82" s="58"/>
       <c r="I82" s="58"/>
-      <c r="J82" s="60" t="s">
+      <c r="J82" s="72" t="s">
         <v>531</v>
       </c>
     </row>
@@ -16268,7 +16328,7 @@
       <c r="G83" s="58"/>
       <c r="H83" s="58"/>
       <c r="I83" s="58"/>
-      <c r="J83" s="60" t="s">
+      <c r="J83" s="72" t="s">
         <v>532</v>
       </c>
     </row>
@@ -16291,10 +16351,10 @@
       <c r="F84" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G84" s="63"/>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63"/>
-      <c r="J84" s="64" t="s">
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
+      <c r="I84" s="62"/>
+      <c r="J84" s="75" t="s">
         <v>533</v>
       </c>
     </row>
@@ -16317,10 +16377,10 @@
       <c r="F85" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G85" s="63"/>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="64" t="s">
+      <c r="G85" s="62"/>
+      <c r="H85" s="62"/>
+      <c r="I85" s="62"/>
+      <c r="J85" s="75" t="s">
         <v>534</v>
       </c>
     </row>
@@ -16343,10 +16403,10 @@
       <c r="F86" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="64" t="s">
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
+      <c r="I86" s="62"/>
+      <c r="J86" s="75" t="s">
         <v>535</v>
       </c>
     </row>
@@ -16369,10 +16429,10 @@
       <c r="F87" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G87" s="63"/>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="64" t="s">
+      <c r="G87" s="62"/>
+      <c r="H87" s="62"/>
+      <c r="I87" s="62"/>
+      <c r="J87" s="75" t="s">
         <v>536</v>
       </c>
     </row>
@@ -16395,10 +16455,10 @@
       <c r="F88" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
-      <c r="J88" s="64" t="s">
+      <c r="G88" s="62"/>
+      <c r="H88" s="62"/>
+      <c r="I88" s="62"/>
+      <c r="J88" s="75" t="s">
         <v>537</v>
       </c>
     </row>
@@ -16422,7 +16482,7 @@
       <c r="I89" s="58" t="s">
         <v>538</v>
       </c>
-      <c r="J89" s="67" t="s">
+      <c r="J89" s="79" t="s">
         <v>539</v>
       </c>
     </row>
@@ -16448,7 +16508,7 @@
       <c r="G90" s="58"/>
       <c r="H90" s="59"/>
       <c r="I90" s="58"/>
-      <c r="J90" s="57" t="s">
+      <c r="J90" s="74" t="s">
         <v>540</v>
       </c>
     </row>
@@ -16476,7 +16536,7 @@
       <c r="I91" s="58" t="s">
         <v>541</v>
       </c>
-      <c r="J91" s="57" t="s">
+      <c r="J91" s="74" t="s">
         <v>542</v>
       </c>
     </row>
@@ -16502,7 +16562,7 @@
       <c r="G92" s="58"/>
       <c r="H92" s="59"/>
       <c r="I92" s="58"/>
-      <c r="J92" s="58" t="s">
+      <c r="J92" s="81" t="s">
         <v>543</v>
       </c>
     </row>
@@ -16525,10 +16585,10 @@
       <c r="F93" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G93" s="63"/>
+      <c r="G93" s="62"/>
       <c r="H93" s="59"/>
-      <c r="I93" s="63"/>
-      <c r="J93" s="63" t="s">
+      <c r="I93" s="62"/>
+      <c r="J93" s="77" t="s">
         <v>544</v>
       </c>
     </row>
@@ -16554,7 +16614,7 @@
       <c r="G94" s="58"/>
       <c r="H94" s="59"/>
       <c r="I94" s="58"/>
-      <c r="J94" s="57" t="s">
+      <c r="J94" s="74" t="s">
         <v>545</v>
       </c>
     </row>
@@ -16577,10 +16637,10 @@
       <c r="F95" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G95" s="63"/>
+      <c r="G95" s="62"/>
       <c r="H95" s="59"/>
-      <c r="I95" s="63"/>
-      <c r="J95" s="63" t="s">
+      <c r="I95" s="62"/>
+      <c r="J95" s="77" t="s">
         <v>546</v>
       </c>
     </row>
@@ -16603,10 +16663,10 @@
       <c r="F96" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G96" s="63"/>
+      <c r="G96" s="62"/>
       <c r="H96" s="59"/>
-      <c r="I96" s="63"/>
-      <c r="J96" s="63" t="s">
+      <c r="I96" s="62"/>
+      <c r="J96" s="77" t="s">
         <v>547</v>
       </c>
     </row>
@@ -16625,12 +16685,12 @@
       </c>
       <c r="E97" s="57"/>
       <c r="F97" s="58"/>
-      <c r="G97" s="63"/>
-      <c r="H97" s="63"/>
+      <c r="G97" s="62"/>
+      <c r="H97" s="62"/>
       <c r="I97" s="58" t="s">
         <v>548</v>
       </c>
-      <c r="J97" s="63" t="s">
+      <c r="J97" s="77" t="s">
         <v>549</v>
       </c>
     </row>
@@ -16653,10 +16713,10 @@
       <c r="F98" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G98" s="63"/>
+      <c r="G98" s="62"/>
       <c r="H98" s="59"/>
       <c r="I98" s="58"/>
-      <c r="J98" s="63" t="s">
+      <c r="J98" s="77" t="s">
         <v>550</v>
       </c>
     </row>
@@ -16679,10 +16739,10 @@
       <c r="F99" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G99" s="63"/>
+      <c r="G99" s="62"/>
       <c r="H99" s="59"/>
-      <c r="I99" s="63"/>
-      <c r="J99" s="63" t="s">
+      <c r="I99" s="62"/>
+      <c r="J99" s="77" t="s">
         <v>551</v>
       </c>
     </row>
@@ -16705,12 +16765,12 @@
       <c r="F100" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G100" s="63"/>
+      <c r="G100" s="62"/>
       <c r="H100" s="59"/>
       <c r="I100" s="58" t="s">
         <v>552</v>
       </c>
-      <c r="J100" s="63" t="s">
+      <c r="J100" s="77" t="s">
         <v>553</v>
       </c>
     </row>
@@ -16733,10 +16793,10 @@
       <c r="F101" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G101" s="63"/>
+      <c r="G101" s="62"/>
       <c r="H101" s="59"/>
-      <c r="I101" s="63"/>
-      <c r="J101" s="63" t="s">
+      <c r="I101" s="62"/>
+      <c r="J101" s="77" t="s">
         <v>554</v>
       </c>
     </row>
@@ -16759,12 +16819,12 @@
       <c r="F102" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G102" s="64" t="s">
+      <c r="G102" s="63" t="s">
         <v>555</v>
       </c>
       <c r="H102" s="59"/>
-      <c r="I102" s="77"/>
-      <c r="J102" s="64" t="s">
+      <c r="I102" s="70"/>
+      <c r="J102" s="75" t="s">
         <v>556</v>
       </c>
     </row>
@@ -16787,10 +16847,10 @@
       <c r="F103" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G103" s="63"/>
+      <c r="G103" s="62"/>
       <c r="H103" s="59"/>
-      <c r="I103" s="63"/>
-      <c r="J103" s="64" t="s">
+      <c r="I103" s="62"/>
+      <c r="J103" s="75" t="s">
         <v>557</v>
       </c>
     </row>
@@ -16820,7 +16880,7 @@
       <c r="I104" s="58" t="s">
         <v>552</v>
       </c>
-      <c r="J104" s="60" t="s">
+      <c r="J104" s="72" t="s">
         <v>559</v>
       </c>
     </row>
@@ -16846,7 +16906,7 @@
       <c r="G105" s="58"/>
       <c r="H105" s="59"/>
       <c r="I105" s="58"/>
-      <c r="J105" s="57" t="s">
+      <c r="J105" s="74" t="s">
         <v>560</v>
       </c>
     </row>
@@ -16872,7 +16932,7 @@
       <c r="G106" s="58"/>
       <c r="H106" s="59"/>
       <c r="I106" s="58"/>
-      <c r="J106" s="57" t="s">
+      <c r="J106" s="74" t="s">
         <v>561</v>
       </c>
     </row>
@@ -16898,7 +16958,7 @@
       <c r="G107" s="58"/>
       <c r="H107" s="59"/>
       <c r="I107" s="58"/>
-      <c r="J107" s="60" t="s">
+      <c r="J107" s="72" t="s">
         <v>562</v>
       </c>
     </row>
@@ -16921,10 +16981,10 @@
       <c r="F108" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G108" s="63"/>
+      <c r="G108" s="62"/>
       <c r="H108" s="59"/>
-      <c r="I108" s="63"/>
-      <c r="J108" s="64" t="s">
+      <c r="I108" s="62"/>
+      <c r="J108" s="75" t="s">
         <v>563</v>
       </c>
     </row>
@@ -16950,7 +17010,7 @@
       <c r="G109" s="58"/>
       <c r="H109" s="59"/>
       <c r="I109" s="58"/>
-      <c r="J109" s="59" t="s">
+      <c r="J109" s="82" t="s">
         <v>564</v>
       </c>
     </row>
@@ -16975,8 +17035,8 @@
       </c>
       <c r="G110" s="58"/>
       <c r="H110" s="59"/>
-      <c r="I110" s="63"/>
-      <c r="J110" s="64" t="s">
+      <c r="I110" s="62"/>
+      <c r="J110" s="75" t="s">
         <v>565</v>
       </c>
     </row>
@@ -17001,8 +17061,8 @@
       </c>
       <c r="G111" s="58"/>
       <c r="H111" s="59"/>
-      <c r="I111" s="63"/>
-      <c r="J111" s="64" t="s">
+      <c r="I111" s="62"/>
+      <c r="J111" s="75" t="s">
         <v>566</v>
       </c>
     </row>
@@ -17024,7 +17084,7 @@
       <c r="G112" s="58"/>
       <c r="H112" s="59"/>
       <c r="I112" s="58"/>
-      <c r="J112" s="59" t="s">
+      <c r="J112" s="82" t="s">
         <v>567</v>
       </c>
     </row>
@@ -17041,20 +17101,20 @@
       <c r="D113" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E113" s="69" t="s">
+      <c r="E113" s="65" t="s">
         <v>33</v>
       </c>
       <c r="F113" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G113" s="64" t="s">
+      <c r="G113" s="63" t="s">
         <v>555</v>
       </c>
       <c r="H113" s="59"/>
       <c r="I113" s="58" t="s">
         <v>552</v>
       </c>
-      <c r="J113" s="60" t="s">
+      <c r="J113" s="72" t="s">
         <v>568</v>
       </c>
     </row>
@@ -17071,7 +17131,7 @@
       <c r="D114" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E114" s="69" t="s">
+      <c r="E114" s="65" t="s">
         <v>31</v>
       </c>
       <c r="F114" s="59" t="s">
@@ -17080,7 +17140,7 @@
       <c r="G114" s="58"/>
       <c r="H114" s="59"/>
       <c r="I114" s="58"/>
-      <c r="J114" s="60" t="s">
+      <c r="J114" s="72" t="s">
         <v>569</v>
       </c>
     </row>
@@ -17106,7 +17166,7 @@
       <c r="G115" s="58"/>
       <c r="H115" s="59"/>
       <c r="I115" s="58"/>
-      <c r="J115" s="60" t="s">
+      <c r="J115" s="72" t="s">
         <v>570</v>
       </c>
     </row>
@@ -17123,7 +17183,7 @@
       <c r="D116" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E116" s="69" t="s">
+      <c r="E116" s="65" t="s">
         <v>31</v>
       </c>
       <c r="F116" s="59" t="s">
@@ -17132,7 +17192,7 @@
       <c r="G116" s="58"/>
       <c r="H116" s="59"/>
       <c r="I116" s="58"/>
-      <c r="J116" s="60" t="s">
+      <c r="J116" s="72" t="s">
         <v>571</v>
       </c>
     </row>
@@ -17158,7 +17218,7 @@
       <c r="G117" s="58"/>
       <c r="H117" s="59"/>
       <c r="I117" s="58"/>
-      <c r="J117" s="59" t="s">
+      <c r="J117" s="82" t="s">
         <v>572</v>
       </c>
     </row>
@@ -17186,7 +17246,7 @@
       <c r="I118" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J118" s="60" t="s">
+      <c r="J118" s="72" t="s">
         <v>573</v>
       </c>
     </row>
@@ -17212,7 +17272,7 @@
       <c r="G119" s="58"/>
       <c r="H119" s="59"/>
       <c r="I119" s="58"/>
-      <c r="J119" s="60" t="s">
+      <c r="J119" s="72" t="s">
         <v>574</v>
       </c>
     </row>
@@ -17238,7 +17298,7 @@
       <c r="G120" s="58"/>
       <c r="H120" s="59"/>
       <c r="I120" s="58"/>
-      <c r="J120" s="60" t="s">
+      <c r="J120" s="72" t="s">
         <v>575</v>
       </c>
     </row>
@@ -17264,7 +17324,7 @@
       <c r="G121" s="58"/>
       <c r="H121" s="58"/>
       <c r="I121" s="58"/>
-      <c r="J121" s="60" t="s">
+      <c r="J121" s="72" t="s">
         <v>576</v>
       </c>
     </row>
@@ -17290,18 +17350,18 @@
       <c r="G122" s="58"/>
       <c r="H122" s="58"/>
       <c r="I122" s="58"/>
-      <c r="J122" s="60" t="s">
+      <c r="J122" s="72" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="63" t="s">
+      <c r="A123" s="62" t="s">
         <v>330</v>
       </c>
-      <c r="B123" s="63" t="s">
+      <c r="B123" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="C123" s="63">
+      <c r="C123" s="62">
         <v>6</v>
       </c>
       <c r="D123" s="57" t="s">
@@ -17313,10 +17373,10 @@
       <c r="F123" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G123" s="63"/>
-      <c r="H123" s="63"/>
-      <c r="I123" s="63"/>
-      <c r="J123" s="64" t="s">
+      <c r="G123" s="62"/>
+      <c r="H123" s="62"/>
+      <c r="I123" s="62"/>
+      <c r="J123" s="75" t="s">
         <v>578</v>
       </c>
     </row>
@@ -17339,10 +17399,10 @@
       <c r="F124" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G124" s="63"/>
-      <c r="H124" s="63"/>
-      <c r="I124" s="63"/>
-      <c r="J124" s="64" t="s">
+      <c r="G124" s="62"/>
+      <c r="H124" s="62"/>
+      <c r="I124" s="62"/>
+      <c r="J124" s="75" t="s">
         <v>579</v>
       </c>
     </row>
@@ -17365,10 +17425,10 @@
       <c r="F125" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G125" s="63"/>
-      <c r="H125" s="63"/>
-      <c r="I125" s="63"/>
-      <c r="J125" s="64" t="s">
+      <c r="G125" s="62"/>
+      <c r="H125" s="62"/>
+      <c r="I125" s="62"/>
+      <c r="J125" s="75" t="s">
         <v>580</v>
       </c>
     </row>
@@ -17391,10 +17451,10 @@
       <c r="F126" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G126" s="63"/>
-      <c r="H126" s="63"/>
-      <c r="I126" s="63"/>
-      <c r="J126" s="63" t="s">
+      <c r="G126" s="62"/>
+      <c r="H126" s="62"/>
+      <c r="I126" s="62"/>
+      <c r="J126" s="77" t="s">
         <v>581</v>
       </c>
     </row>
@@ -17417,10 +17477,10 @@
       <c r="F127" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G127" s="63"/>
-      <c r="H127" s="63"/>
-      <c r="I127" s="63"/>
-      <c r="J127" s="63" t="s">
+      <c r="G127" s="62"/>
+      <c r="H127" s="62"/>
+      <c r="I127" s="62"/>
+      <c r="J127" s="77" t="s">
         <v>582</v>
       </c>
     </row>
@@ -17443,21 +17503,21 @@
       <c r="F128" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G128" s="63"/>
-      <c r="H128" s="63"/>
-      <c r="I128" s="63"/>
-      <c r="J128" s="64" t="s">
+      <c r="G128" s="62"/>
+      <c r="H128" s="62"/>
+      <c r="I128" s="62"/>
+      <c r="J128" s="75" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="63" t="s">
+      <c r="A129" s="62" t="s">
         <v>330</v>
       </c>
-      <c r="B129" s="63" t="s">
+      <c r="B129" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="C129" s="63">
+      <c r="C129" s="62">
         <v>12</v>
       </c>
       <c r="D129" s="57" t="s">
@@ -17469,47 +17529,47 @@
       <c r="F129" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G129" s="63"/>
-      <c r="H129" s="63"/>
-      <c r="I129" s="63"/>
-      <c r="J129" s="64" t="s">
+      <c r="G129" s="62"/>
+      <c r="H129" s="62"/>
+      <c r="I129" s="62"/>
+      <c r="J129" s="75" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="63" t="s">
+      <c r="A130" s="62" t="s">
         <v>330</v>
       </c>
-      <c r="B130" s="63" t="s">
+      <c r="B130" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="C130" s="63">
+      <c r="C130" s="62">
         <v>13</v>
       </c>
       <c r="D130" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E130" s="64" t="s">
+      <c r="E130" s="63" t="s">
         <v>25</v>
       </c>
       <c r="F130" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G130" s="63"/>
-      <c r="H130" s="63"/>
-      <c r="I130" s="63"/>
-      <c r="J130" s="64" t="s">
+      <c r="G130" s="62"/>
+      <c r="H130" s="62"/>
+      <c r="I130" s="62"/>
+      <c r="J130" s="75" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="63" t="s">
+      <c r="A131" s="62" t="s">
         <v>330</v>
       </c>
-      <c r="B131" s="63" t="s">
+      <c r="B131" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="C131" s="63">
+      <c r="C131" s="62">
         <v>14</v>
       </c>
       <c r="D131" s="57" t="s">
@@ -17521,10 +17581,10 @@
       <c r="F131" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G131" s="63"/>
-      <c r="H131" s="63"/>
-      <c r="I131" s="63"/>
-      <c r="J131" s="64" t="s">
+      <c r="G131" s="62"/>
+      <c r="H131" s="62"/>
+      <c r="I131" s="62"/>
+      <c r="J131" s="75" t="s">
         <v>586</v>
       </c>
     </row>
@@ -17552,7 +17612,7 @@
       <c r="I132" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J132" s="60" t="s">
+      <c r="J132" s="72" t="s">
         <v>587</v>
       </c>
     </row>
@@ -17578,7 +17638,7 @@
       <c r="G133" s="58"/>
       <c r="H133" s="59"/>
       <c r="I133" s="58"/>
-      <c r="J133" s="60" t="s">
+      <c r="J133" s="72" t="s">
         <v>588</v>
       </c>
     </row>
@@ -17604,7 +17664,7 @@
       <c r="G134" s="58"/>
       <c r="H134" s="59"/>
       <c r="I134" s="58"/>
-      <c r="J134" s="60" t="s">
+      <c r="J134" s="72" t="s">
         <v>589</v>
       </c>
     </row>
@@ -17630,7 +17690,7 @@
       <c r="G135" s="58"/>
       <c r="H135" s="59"/>
       <c r="I135" s="58"/>
-      <c r="J135" s="60" t="s">
+      <c r="J135" s="72" t="s">
         <v>590</v>
       </c>
     </row>
@@ -17658,7 +17718,7 @@
       <c r="I136" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J136" s="60" t="s">
+      <c r="J136" s="72" t="s">
         <v>591</v>
       </c>
     </row>
@@ -17684,7 +17744,7 @@
       <c r="G137" s="58"/>
       <c r="H137" s="59"/>
       <c r="I137" s="58"/>
-      <c r="J137" s="60" t="s">
+      <c r="J137" s="72" t="s">
         <v>592</v>
       </c>
     </row>
@@ -17710,7 +17770,7 @@
       <c r="G138" s="58"/>
       <c r="H138" s="59"/>
       <c r="I138" s="58"/>
-      <c r="J138" s="60" t="s">
+      <c r="J138" s="72" t="s">
         <v>593</v>
       </c>
     </row>
@@ -17736,7 +17796,7 @@
       <c r="G139" s="58"/>
       <c r="H139" s="58"/>
       <c r="I139" s="58"/>
-      <c r="J139" s="60" t="s">
+      <c r="J139" s="72" t="s">
         <v>594</v>
       </c>
     </row>
@@ -17762,7 +17822,7 @@
       <c r="G140" s="58"/>
       <c r="H140" s="58"/>
       <c r="I140" s="58"/>
-      <c r="J140" s="60" t="s">
+      <c r="J140" s="72" t="s">
         <v>595</v>
       </c>
     </row>
@@ -17785,10 +17845,10 @@
       <c r="F141" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G141" s="63"/>
-      <c r="H141" s="63"/>
-      <c r="I141" s="63"/>
-      <c r="J141" s="70" t="s">
+      <c r="G141" s="62"/>
+      <c r="H141" s="62"/>
+      <c r="I141" s="62"/>
+      <c r="J141" s="83" t="s">
         <v>596</v>
       </c>
     </row>
@@ -17811,10 +17871,10 @@
       <c r="F142" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G142" s="63"/>
-      <c r="H142" s="63"/>
-      <c r="I142" s="63"/>
-      <c r="J142" s="64" t="s">
+      <c r="G142" s="62"/>
+      <c r="H142" s="62"/>
+      <c r="I142" s="62"/>
+      <c r="J142" s="75" t="s">
         <v>597</v>
       </c>
     </row>
@@ -17837,10 +17897,10 @@
       <c r="F143" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G143" s="63"/>
-      <c r="H143" s="63"/>
-      <c r="I143" s="63"/>
-      <c r="J143" s="64" t="s">
+      <c r="G143" s="62"/>
+      <c r="H143" s="62"/>
+      <c r="I143" s="62"/>
+      <c r="J143" s="75" t="s">
         <v>598</v>
       </c>
     </row>
@@ -17863,10 +17923,10 @@
       <c r="F144" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G144" s="63"/>
-      <c r="H144" s="63"/>
-      <c r="I144" s="63"/>
-      <c r="J144" s="64" t="s">
+      <c r="G144" s="62"/>
+      <c r="H144" s="62"/>
+      <c r="I144" s="62"/>
+      <c r="J144" s="75" t="s">
         <v>599</v>
       </c>
     </row>
@@ -17889,10 +17949,10 @@
       <c r="F145" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G145" s="63"/>
-      <c r="H145" s="63"/>
-      <c r="I145" s="63"/>
-      <c r="J145" s="64" t="s">
+      <c r="G145" s="62"/>
+      <c r="H145" s="62"/>
+      <c r="I145" s="62"/>
+      <c r="J145" s="75" t="s">
         <v>600</v>
       </c>
     </row>
@@ -17920,7 +17980,7 @@
       <c r="I146" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J146" s="57" t="s">
+      <c r="J146" s="74" t="s">
         <v>527</v>
       </c>
     </row>
@@ -17948,7 +18008,7 @@
       <c r="I147" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J147" s="57" t="s">
+      <c r="J147" s="74" t="s">
         <v>601</v>
       </c>
     </row>
@@ -17965,7 +18025,7 @@
       <c r="D148" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E148" s="67" t="s">
+      <c r="E148" s="64" t="s">
         <v>16</v>
       </c>
       <c r="F148" s="58" t="s">
@@ -17974,7 +18034,7 @@
       <c r="G148" s="58"/>
       <c r="H148" s="59"/>
       <c r="I148" s="58"/>
-      <c r="J148" s="57" t="s">
+      <c r="J148" s="74" t="s">
         <v>602</v>
       </c>
     </row>
@@ -18000,7 +18060,7 @@
       <c r="G149" s="58"/>
       <c r="H149" s="59"/>
       <c r="I149" s="58"/>
-      <c r="J149" s="60" t="s">
+      <c r="J149" s="72" t="s">
         <v>603</v>
       </c>
     </row>
@@ -18028,7 +18088,7 @@
       </c>
       <c r="H150" s="58"/>
       <c r="I150" s="58"/>
-      <c r="J150" s="60" t="s">
+      <c r="J150" s="72" t="s">
         <v>604</v>
       </c>
     </row>
@@ -18045,7 +18105,7 @@
       <c r="D151" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E151" s="67" t="s">
+      <c r="E151" s="64" t="s">
         <v>16</v>
       </c>
       <c r="F151" s="58" t="s">
@@ -18054,7 +18114,7 @@
       <c r="G151" s="58"/>
       <c r="H151" s="58"/>
       <c r="I151" s="58"/>
-      <c r="J151" s="60" t="s">
+      <c r="J151" s="72" t="s">
         <v>605</v>
       </c>
     </row>
@@ -18080,9 +18140,9 @@
       <c r="G152" s="59" t="s">
         <v>555</v>
       </c>
-      <c r="H152" s="63"/>
-      <c r="I152" s="63"/>
-      <c r="J152" s="60" t="s">
+      <c r="H152" s="62"/>
+      <c r="I152" s="62"/>
+      <c r="J152" s="72" t="s">
         <v>606</v>
       </c>
     </row>
@@ -18110,7 +18170,7 @@
       <c r="I153" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J153" s="60" t="s">
+      <c r="J153" s="72" t="s">
         <v>607</v>
       </c>
     </row>
@@ -18136,7 +18196,7 @@
       <c r="G154" s="58"/>
       <c r="H154" s="59"/>
       <c r="I154" s="58"/>
-      <c r="J154" s="60" t="s">
+      <c r="J154" s="72" t="s">
         <v>608</v>
       </c>
     </row>
@@ -18164,7 +18224,7 @@
         <v>609</v>
       </c>
       <c r="I155" s="58"/>
-      <c r="J155" s="60" t="s">
+      <c r="J155" s="72" t="s">
         <v>610</v>
       </c>
     </row>
@@ -18190,7 +18250,7 @@
       <c r="G156" s="58"/>
       <c r="H156" s="58"/>
       <c r="I156" s="58"/>
-      <c r="J156" s="60" t="s">
+      <c r="J156" s="72" t="s">
         <v>611</v>
       </c>
     </row>
@@ -18216,7 +18276,7 @@
       <c r="G157" s="58"/>
       <c r="H157" s="59"/>
       <c r="I157" s="58"/>
-      <c r="J157" s="60" t="s">
+      <c r="J157" s="72" t="s">
         <v>612</v>
       </c>
     </row>
@@ -18244,7 +18304,7 @@
       <c r="I158" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J158" s="60" t="s">
+      <c r="J158" s="72" t="s">
         <v>527</v>
       </c>
     </row>
@@ -18272,7 +18332,7 @@
       <c r="I159" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J159" s="57" t="s">
+      <c r="J159" s="74" t="s">
         <v>613</v>
       </c>
     </row>
@@ -18298,7 +18358,7 @@
       <c r="G160" s="58"/>
       <c r="H160" s="59"/>
       <c r="I160" s="58"/>
-      <c r="J160" s="57" t="s">
+      <c r="J160" s="74" t="s">
         <v>614</v>
       </c>
     </row>
@@ -18326,7 +18386,7 @@
       <c r="I161" s="58" t="s">
         <v>615</v>
       </c>
-      <c r="J161" s="57" t="s">
+      <c r="J161" s="74" t="s">
         <v>616</v>
       </c>
     </row>
@@ -18352,7 +18412,7 @@
       <c r="G162" s="58"/>
       <c r="H162" s="58"/>
       <c r="I162" s="58"/>
-      <c r="J162" s="57" t="s">
+      <c r="J162" s="74" t="s">
         <v>617</v>
       </c>
     </row>
@@ -18378,7 +18438,7 @@
       <c r="G163" s="58"/>
       <c r="H163" s="58"/>
       <c r="I163" s="58"/>
-      <c r="J163" s="57" t="s">
+      <c r="J163" s="74" t="s">
         <v>618</v>
       </c>
     </row>
@@ -18401,10 +18461,10 @@
       <c r="F164" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G164" s="63"/>
+      <c r="G164" s="62"/>
       <c r="H164" s="59"/>
-      <c r="I164" s="63"/>
-      <c r="J164" s="63" t="s">
+      <c r="I164" s="62"/>
+      <c r="J164" s="77" t="s">
         <v>619</v>
       </c>
     </row>
@@ -18421,18 +18481,18 @@
       <c r="D165" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E165" s="63" t="s">
+      <c r="E165" s="62" t="s">
         <v>45</v>
       </c>
       <c r="F165" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G165" s="63"/>
-      <c r="H165" s="63"/>
+      <c r="G165" s="62"/>
+      <c r="H165" s="62"/>
       <c r="I165" s="58" t="s">
         <v>620</v>
       </c>
-      <c r="J165" s="65" t="s">
+      <c r="J165" s="76" t="s">
         <v>621</v>
       </c>
     </row>
@@ -18449,16 +18509,16 @@
       <c r="D166" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E166" s="63" t="s">
+      <c r="E166" s="62" t="s">
         <v>45</v>
       </c>
       <c r="F166" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G166" s="63"/>
+      <c r="G166" s="62"/>
       <c r="H166" s="59"/>
-      <c r="I166" s="63"/>
-      <c r="J166" s="64" t="s">
+      <c r="I166" s="62"/>
+      <c r="J166" s="75" t="s">
         <v>622</v>
       </c>
     </row>
@@ -18475,16 +18535,16 @@
       <c r="D167" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E167" s="63" t="s">
+      <c r="E167" s="62" t="s">
         <v>16</v>
       </c>
       <c r="F167" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G167" s="63"/>
+      <c r="G167" s="62"/>
       <c r="H167" s="59"/>
-      <c r="I167" s="63"/>
-      <c r="J167" s="63" t="s">
+      <c r="I167" s="62"/>
+      <c r="J167" s="77" t="s">
         <v>623</v>
       </c>
     </row>
@@ -18501,18 +18561,18 @@
       <c r="D168" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E168" s="63" t="s">
+      <c r="E168" s="62" t="s">
         <v>18</v>
       </c>
       <c r="F168" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G168" s="63"/>
-      <c r="H168" s="63"/>
+      <c r="G168" s="62"/>
+      <c r="H168" s="62"/>
       <c r="I168" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J168" s="65" t="s">
+      <c r="J168" s="76" t="s">
         <v>624</v>
       </c>
     </row>
@@ -18529,16 +18589,16 @@
       <c r="D169" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E169" s="63" t="s">
+      <c r="E169" s="62" t="s">
         <v>16</v>
       </c>
       <c r="F169" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G169" s="63"/>
-      <c r="H169" s="63"/>
-      <c r="I169" s="63"/>
-      <c r="J169" s="63" t="s">
+      <c r="G169" s="62"/>
+      <c r="H169" s="62"/>
+      <c r="I169" s="62"/>
+      <c r="J169" s="77" t="s">
         <v>625</v>
       </c>
     </row>
@@ -18555,16 +18615,16 @@
       <c r="D170" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E170" s="63" t="s">
+      <c r="E170" s="62" t="s">
         <v>20</v>
       </c>
       <c r="F170" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G170" s="63"/>
-      <c r="H170" s="63"/>
-      <c r="I170" s="63"/>
-      <c r="J170" s="65" t="s">
+      <c r="G170" s="62"/>
+      <c r="H170" s="62"/>
+      <c r="I170" s="62"/>
+      <c r="J170" s="76" t="s">
         <v>626</v>
       </c>
     </row>
@@ -18581,16 +18641,16 @@
       <c r="D171" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E171" s="63" t="s">
+      <c r="E171" s="62" t="s">
         <v>16</v>
       </c>
       <c r="F171" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G171" s="63"/>
-      <c r="H171" s="63"/>
-      <c r="I171" s="63"/>
-      <c r="J171" s="63" t="s">
+      <c r="G171" s="62"/>
+      <c r="H171" s="62"/>
+      <c r="I171" s="62"/>
+      <c r="J171" s="77" t="s">
         <v>627</v>
       </c>
     </row>
@@ -18607,16 +18667,16 @@
       <c r="D172" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E172" s="63" t="s">
+      <c r="E172" s="62" t="s">
         <v>25</v>
       </c>
       <c r="F172" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G172" s="63"/>
-      <c r="H172" s="63"/>
-      <c r="I172" s="63"/>
-      <c r="J172" s="63" t="s">
+      <c r="G172" s="62"/>
+      <c r="H172" s="62"/>
+      <c r="I172" s="62"/>
+      <c r="J172" s="77" t="s">
         <v>628</v>
       </c>
     </row>
@@ -18644,7 +18704,7 @@
       <c r="I173" s="58" t="s">
         <v>629</v>
       </c>
-      <c r="J173" s="67" t="s">
+      <c r="J173" s="79" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18672,7 +18732,7 @@
         <v>609</v>
       </c>
       <c r="I174" s="58"/>
-      <c r="J174" s="71" t="s">
+      <c r="J174" s="84" t="s">
         <v>631</v>
       </c>
     </row>
@@ -18698,7 +18758,7 @@
       <c r="G175" s="58"/>
       <c r="H175" s="59"/>
       <c r="I175" s="58"/>
-      <c r="J175" s="60" t="s">
+      <c r="J175" s="72" t="s">
         <v>632</v>
       </c>
     </row>
@@ -18724,7 +18784,7 @@
       <c r="G176" s="58"/>
       <c r="H176" s="58"/>
       <c r="I176" s="58"/>
-      <c r="J176" s="59" t="s">
+      <c r="J176" s="82" t="s">
         <v>633</v>
       </c>
     </row>
@@ -18750,7 +18810,7 @@
       <c r="G177" s="58"/>
       <c r="H177" s="58"/>
       <c r="I177" s="58"/>
-      <c r="J177" s="60" t="s">
+      <c r="J177" s="72" t="s">
         <v>634</v>
       </c>
     </row>
@@ -18773,10 +18833,10 @@
       <c r="F178" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G178" s="63"/>
-      <c r="H178" s="63"/>
-      <c r="I178" s="63"/>
-      <c r="J178" s="63" t="s">
+      <c r="G178" s="62"/>
+      <c r="H178" s="62"/>
+      <c r="I178" s="62"/>
+      <c r="J178" s="77" t="s">
         <v>635</v>
       </c>
     </row>
@@ -18804,7 +18864,7 @@
       <c r="I179" s="58" t="s">
         <v>636</v>
       </c>
-      <c r="J179" s="60" t="s">
+      <c r="J179" s="72" t="s">
         <v>637</v>
       </c>
     </row>
@@ -18830,7 +18890,7 @@
       <c r="G180" s="58"/>
       <c r="H180" s="59"/>
       <c r="I180" s="58"/>
-      <c r="J180" s="60" t="s">
+      <c r="J180" s="72" t="s">
         <v>638</v>
       </c>
     </row>
@@ -18856,7 +18916,7 @@
       <c r="G181" s="58"/>
       <c r="H181" s="59"/>
       <c r="I181" s="58"/>
-      <c r="J181" s="60" t="s">
+      <c r="J181" s="72" t="s">
         <v>639</v>
       </c>
     </row>
@@ -18882,7 +18942,7 @@
       <c r="G182" s="58"/>
       <c r="H182" s="58"/>
       <c r="I182" s="58"/>
-      <c r="J182" s="60" t="s">
+      <c r="J182" s="72" t="s">
         <v>640</v>
       </c>
     </row>
@@ -18908,7 +18968,7 @@
       <c r="G183" s="58"/>
       <c r="H183" s="58"/>
       <c r="I183" s="58"/>
-      <c r="J183" s="60" t="s">
+      <c r="J183" s="72" t="s">
         <v>641</v>
       </c>
     </row>
@@ -18931,10 +18991,10 @@
       <c r="F184" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G184" s="63"/>
-      <c r="H184" s="63"/>
-      <c r="I184" s="63"/>
-      <c r="J184" s="64" t="s">
+      <c r="G184" s="62"/>
+      <c r="H184" s="62"/>
+      <c r="I184" s="62"/>
+      <c r="J184" s="75" t="s">
         <v>642</v>
       </c>
     </row>
@@ -18957,10 +19017,10 @@
       <c r="F185" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G185" s="63"/>
-      <c r="H185" s="63"/>
-      <c r="I185" s="63"/>
-      <c r="J185" s="64" t="s">
+      <c r="G185" s="62"/>
+      <c r="H185" s="62"/>
+      <c r="I185" s="62"/>
+      <c r="J185" s="75" t="s">
         <v>643</v>
       </c>
     </row>
@@ -18983,10 +19043,10 @@
       <c r="F186" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G186" s="63"/>
-      <c r="H186" s="63"/>
-      <c r="I186" s="63"/>
-      <c r="J186" s="64" t="s">
+      <c r="G186" s="62"/>
+      <c r="H186" s="62"/>
+      <c r="I186" s="62"/>
+      <c r="J186" s="75" t="s">
         <v>644</v>
       </c>
     </row>
@@ -19014,7 +19074,7 @@
       <c r="I187" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J187" s="60" t="s">
+      <c r="J187" s="72" t="s">
         <v>645</v>
       </c>
     </row>
@@ -19040,7 +19100,7 @@
       <c r="G188" s="58"/>
       <c r="H188" s="59"/>
       <c r="I188" s="58"/>
-      <c r="J188" s="60" t="s">
+      <c r="J188" s="72" t="s">
         <v>602</v>
       </c>
     </row>
@@ -19066,7 +19126,7 @@
       <c r="G189" s="58"/>
       <c r="H189" s="59"/>
       <c r="I189" s="58"/>
-      <c r="J189" s="60" t="s">
+      <c r="J189" s="72" t="s">
         <v>646</v>
       </c>
     </row>
@@ -19092,7 +19152,7 @@
       <c r="G190" s="58"/>
       <c r="H190" s="58"/>
       <c r="I190" s="58"/>
-      <c r="J190" s="60" t="s">
+      <c r="J190" s="72" t="s">
         <v>647</v>
       </c>
     </row>
@@ -19118,7 +19178,7 @@
       <c r="G191" s="58"/>
       <c r="H191" s="58"/>
       <c r="I191" s="58"/>
-      <c r="J191" s="60" t="s">
+      <c r="J191" s="72" t="s">
         <v>648</v>
       </c>
     </row>
@@ -19141,10 +19201,10 @@
       <c r="F192" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G192" s="63"/>
-      <c r="H192" s="63"/>
-      <c r="I192" s="63"/>
-      <c r="J192" s="64" t="s">
+      <c r="G192" s="62"/>
+      <c r="H192" s="62"/>
+      <c r="I192" s="62"/>
+      <c r="J192" s="75" t="s">
         <v>649</v>
       </c>
     </row>
@@ -19167,10 +19227,10 @@
       <c r="F193" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G193" s="63"/>
-      <c r="H193" s="63"/>
-      <c r="I193" s="63"/>
-      <c r="J193" s="64" t="s">
+      <c r="G193" s="62"/>
+      <c r="H193" s="62"/>
+      <c r="I193" s="62"/>
+      <c r="J193" s="75" t="s">
         <v>650</v>
       </c>
     </row>
@@ -19198,7 +19258,7 @@
       <c r="I194" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J194" s="60" t="s">
+      <c r="J194" s="72" t="s">
         <v>651</v>
       </c>
     </row>
@@ -19224,7 +19284,7 @@
       <c r="G195" s="58"/>
       <c r="H195" s="59"/>
       <c r="I195" s="58"/>
-      <c r="J195" s="60" t="s">
+      <c r="J195" s="72" t="s">
         <v>652</v>
       </c>
     </row>
@@ -19250,7 +19310,7 @@
       <c r="G196" s="58"/>
       <c r="H196" s="59"/>
       <c r="I196" s="58"/>
-      <c r="J196" s="71" t="s">
+      <c r="J196" s="84" t="s">
         <v>653</v>
       </c>
     </row>
@@ -19276,7 +19336,7 @@
       <c r="G197" s="58"/>
       <c r="H197" s="58"/>
       <c r="I197" s="58"/>
-      <c r="J197" s="60" t="s">
+      <c r="J197" s="72" t="s">
         <v>654</v>
       </c>
     </row>
@@ -19302,7 +19362,7 @@
       <c r="G198" s="58"/>
       <c r="H198" s="58"/>
       <c r="I198" s="58"/>
-      <c r="J198" s="60" t="s">
+      <c r="J198" s="72" t="s">
         <v>655</v>
       </c>
     </row>
@@ -19325,10 +19385,10 @@
       <c r="F199" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G199" s="63"/>
-      <c r="H199" s="63"/>
-      <c r="I199" s="63"/>
-      <c r="J199" s="64" t="s">
+      <c r="G199" s="62"/>
+      <c r="H199" s="62"/>
+      <c r="I199" s="62"/>
+      <c r="J199" s="75" t="s">
         <v>656</v>
       </c>
     </row>
@@ -19351,10 +19411,10 @@
       <c r="F200" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G200" s="63"/>
-      <c r="H200" s="63"/>
-      <c r="I200" s="63"/>
-      <c r="J200" s="64" t="s">
+      <c r="G200" s="62"/>
+      <c r="H200" s="62"/>
+      <c r="I200" s="62"/>
+      <c r="J200" s="75" t="s">
         <v>657</v>
       </c>
     </row>
@@ -19377,10 +19437,10 @@
       <c r="F201" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G201" s="63"/>
-      <c r="H201" s="63"/>
-      <c r="I201" s="63"/>
-      <c r="J201" s="64" t="s">
+      <c r="G201" s="62"/>
+      <c r="H201" s="62"/>
+      <c r="I201" s="62"/>
+      <c r="J201" s="75" t="s">
         <v>658</v>
       </c>
     </row>
@@ -19403,10 +19463,10 @@
       <c r="F202" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G202" s="63"/>
-      <c r="H202" s="63"/>
-      <c r="I202" s="63"/>
-      <c r="J202" s="64" t="s">
+      <c r="G202" s="62"/>
+      <c r="H202" s="62"/>
+      <c r="I202" s="62"/>
+      <c r="J202" s="75" t="s">
         <v>659</v>
       </c>
     </row>
@@ -19429,10 +19489,10 @@
       <c r="F203" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G203" s="63"/>
-      <c r="H203" s="63"/>
-      <c r="I203" s="63"/>
-      <c r="J203" s="64" t="s">
+      <c r="G203" s="62"/>
+      <c r="H203" s="62"/>
+      <c r="I203" s="62"/>
+      <c r="J203" s="75" t="s">
         <v>660</v>
       </c>
     </row>
@@ -19460,7 +19520,7 @@
       <c r="I204" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J204" s="60" t="s">
+      <c r="J204" s="72" t="s">
         <v>661</v>
       </c>
     </row>
@@ -19486,7 +19546,7 @@
       <c r="G205" s="58"/>
       <c r="H205" s="59"/>
       <c r="I205" s="58"/>
-      <c r="J205" s="60" t="s">
+      <c r="J205" s="72" t="s">
         <v>662</v>
       </c>
     </row>
@@ -19512,7 +19572,7 @@
       <c r="G206" s="58"/>
       <c r="H206" s="59"/>
       <c r="I206" s="58"/>
-      <c r="J206" s="60" t="s">
+      <c r="J206" s="72" t="s">
         <v>663</v>
       </c>
     </row>
@@ -19540,7 +19600,7 @@
       <c r="I207" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J207" s="59" t="s">
+      <c r="J207" s="82" t="s">
         <v>664</v>
       </c>
     </row>
@@ -19566,7 +19626,7 @@
       <c r="G208" s="58"/>
       <c r="H208" s="59"/>
       <c r="I208" s="58"/>
-      <c r="J208" s="60" t="s">
+      <c r="J208" s="72" t="s">
         <v>665</v>
       </c>
     </row>
@@ -19592,7 +19652,7 @@
       <c r="G209" s="58"/>
       <c r="H209" s="59"/>
       <c r="I209" s="58"/>
-      <c r="J209" s="60" t="s">
+      <c r="J209" s="72" t="s">
         <v>666</v>
       </c>
     </row>
@@ -19618,7 +19678,7 @@
       <c r="G210" s="58"/>
       <c r="H210" s="58"/>
       <c r="I210" s="58"/>
-      <c r="J210" s="60" t="s">
+      <c r="J210" s="72" t="s">
         <v>667</v>
       </c>
     </row>
@@ -19644,7 +19704,7 @@
       <c r="G211" s="58"/>
       <c r="H211" s="58"/>
       <c r="I211" s="58"/>
-      <c r="J211" s="60" t="s">
+      <c r="J211" s="72" t="s">
         <v>668</v>
       </c>
     </row>
@@ -19667,10 +19727,10 @@
       <c r="F212" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G212" s="63"/>
-      <c r="H212" s="63"/>
-      <c r="I212" s="63"/>
-      <c r="J212" s="64" t="s">
+      <c r="G212" s="62"/>
+      <c r="H212" s="62"/>
+      <c r="I212" s="62"/>
+      <c r="J212" s="75" t="s">
         <v>669</v>
       </c>
     </row>
@@ -19693,10 +19753,10 @@
       <c r="F213" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G213" s="63"/>
-      <c r="H213" s="63"/>
-      <c r="I213" s="63"/>
-      <c r="J213" s="63" t="s">
+      <c r="G213" s="62"/>
+      <c r="H213" s="62"/>
+      <c r="I213" s="62"/>
+      <c r="J213" s="77" t="s">
         <v>670</v>
       </c>
     </row>
@@ -19719,10 +19779,10 @@
       <c r="F214" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G214" s="63"/>
-      <c r="H214" s="63"/>
-      <c r="I214" s="63"/>
-      <c r="J214" s="63" t="s">
+      <c r="G214" s="62"/>
+      <c r="H214" s="62"/>
+      <c r="I214" s="62"/>
+      <c r="J214" s="77" t="s">
         <v>671</v>
       </c>
     </row>
@@ -19745,10 +19805,10 @@
       <c r="F215" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G215" s="63"/>
-      <c r="H215" s="63"/>
-      <c r="I215" s="63"/>
-      <c r="J215" s="63" t="s">
+      <c r="G215" s="62"/>
+      <c r="H215" s="62"/>
+      <c r="I215" s="62"/>
+      <c r="J215" s="77" t="s">
         <v>672</v>
       </c>
     </row>
@@ -19776,7 +19836,7 @@
       <c r="I216" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J216" s="57" t="s">
+      <c r="J216" s="74" t="s">
         <v>527</v>
       </c>
     </row>
@@ -19800,7 +19860,7 @@
       <c r="I217" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J217" s="60" t="s">
+      <c r="J217" s="72" t="s">
         <v>673</v>
       </c>
     </row>
@@ -19826,7 +19886,7 @@
       <c r="G218" s="58"/>
       <c r="H218" s="59"/>
       <c r="I218" s="58"/>
-      <c r="J218" s="60" t="s">
+      <c r="J218" s="72" t="s">
         <v>674</v>
       </c>
     </row>
@@ -19852,7 +19912,7 @@
       <c r="G219" s="58"/>
       <c r="H219" s="59"/>
       <c r="I219" s="58"/>
-      <c r="J219" s="71" t="s">
+      <c r="J219" s="84" t="s">
         <v>675</v>
       </c>
     </row>
@@ -19878,7 +19938,7 @@
       <c r="G220" s="58"/>
       <c r="H220" s="58"/>
       <c r="I220" s="58"/>
-      <c r="J220" s="60" t="s">
+      <c r="J220" s="72" t="s">
         <v>676</v>
       </c>
     </row>
@@ -19904,7 +19964,7 @@
       <c r="G221" s="58"/>
       <c r="H221" s="58"/>
       <c r="I221" s="58"/>
-      <c r="J221" s="58" t="s">
+      <c r="J221" s="81" t="s">
         <v>677</v>
       </c>
     </row>
@@ -19927,10 +19987,10 @@
       <c r="F222" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G222" s="63"/>
-      <c r="H222" s="63"/>
-      <c r="I222" s="63"/>
-      <c r="J222" s="64" t="s">
+      <c r="G222" s="62"/>
+      <c r="H222" s="62"/>
+      <c r="I222" s="62"/>
+      <c r="J222" s="75" t="s">
         <v>678</v>
       </c>
     </row>
@@ -19953,10 +20013,10 @@
       <c r="F223" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G223" s="63"/>
-      <c r="H223" s="63"/>
-      <c r="I223" s="63"/>
-      <c r="J223" s="63" t="s">
+      <c r="G223" s="62"/>
+      <c r="H223" s="62"/>
+      <c r="I223" s="62"/>
+      <c r="J223" s="77" t="s">
         <v>679</v>
       </c>
     </row>
@@ -19979,10 +20039,10 @@
       <c r="F224" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G224" s="63"/>
-      <c r="H224" s="63"/>
-      <c r="I224" s="63"/>
-      <c r="J224" s="63" t="s">
+      <c r="G224" s="62"/>
+      <c r="H224" s="62"/>
+      <c r="I224" s="62"/>
+      <c r="J224" s="77" t="s">
         <v>680</v>
       </c>
     </row>
@@ -20005,10 +20065,10 @@
       <c r="F225" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G225" s="63"/>
-      <c r="H225" s="63"/>
-      <c r="I225" s="63"/>
-      <c r="J225" s="63" t="s">
+      <c r="G225" s="62"/>
+      <c r="H225" s="62"/>
+      <c r="I225" s="62"/>
+      <c r="J225" s="77" t="s">
         <v>681</v>
       </c>
     </row>
@@ -20031,10 +20091,10 @@
       <c r="F226" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G226" s="63"/>
-      <c r="H226" s="63"/>
-      <c r="I226" s="63"/>
-      <c r="J226" s="63" t="s">
+      <c r="G226" s="62"/>
+      <c r="H226" s="62"/>
+      <c r="I226" s="62"/>
+      <c r="J226" s="77" t="s">
         <v>682</v>
       </c>
     </row>
@@ -20057,10 +20117,10 @@
       <c r="F227" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G227" s="63"/>
-      <c r="H227" s="63"/>
-      <c r="I227" s="63"/>
-      <c r="J227" s="65" t="s">
+      <c r="G227" s="62"/>
+      <c r="H227" s="62"/>
+      <c r="I227" s="62"/>
+      <c r="J227" s="76" t="s">
         <v>683</v>
       </c>
     </row>
@@ -20083,10 +20143,10 @@
       <c r="F228" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G228" s="63"/>
-      <c r="H228" s="63"/>
-      <c r="I228" s="63"/>
-      <c r="J228" s="63" t="s">
+      <c r="G228" s="62"/>
+      <c r="H228" s="62"/>
+      <c r="I228" s="62"/>
+      <c r="J228" s="77" t="s">
         <v>684</v>
       </c>
     </row>
@@ -20109,10 +20169,10 @@
       <c r="F229" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G229" s="63"/>
-      <c r="H229" s="63"/>
-      <c r="I229" s="63"/>
-      <c r="J229" s="63" t="s">
+      <c r="G229" s="62"/>
+      <c r="H229" s="62"/>
+      <c r="I229" s="62"/>
+      <c r="J229" s="77" t="s">
         <v>685</v>
       </c>
     </row>
@@ -20129,14 +20189,14 @@
       <c r="D230" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E230" s="63"/>
+      <c r="E230" s="62"/>
       <c r="F230" s="58"/>
-      <c r="G230" s="63"/>
-      <c r="H230" s="63"/>
+      <c r="G230" s="62"/>
+      <c r="H230" s="62"/>
       <c r="I230" s="58" t="s">
         <v>686</v>
       </c>
-      <c r="J230" s="63" t="s">
+      <c r="J230" s="77" t="s">
         <v>687</v>
       </c>
     </row>
@@ -20153,18 +20213,18 @@
       <c r="D231" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E231" s="63" t="s">
+      <c r="E231" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F231" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G231" s="63"/>
-      <c r="H231" s="63"/>
+      <c r="G231" s="62"/>
+      <c r="H231" s="62"/>
       <c r="I231" s="58" t="s">
         <v>688</v>
       </c>
-      <c r="J231" s="63" t="s">
+      <c r="J231" s="77" t="s">
         <v>689</v>
       </c>
     </row>
@@ -20187,10 +20247,10 @@
       <c r="F232" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G232" s="63"/>
-      <c r="H232" s="63"/>
-      <c r="I232" s="63"/>
-      <c r="J232" s="63" t="s">
+      <c r="G232" s="62"/>
+      <c r="H232" s="62"/>
+      <c r="I232" s="62"/>
+      <c r="J232" s="77" t="s">
         <v>690</v>
       </c>
     </row>
@@ -20207,16 +20267,16 @@
       <c r="D233" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E233" s="63" t="s">
+      <c r="E233" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F233" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G233" s="63"/>
-      <c r="H233" s="63"/>
-      <c r="I233" s="63"/>
-      <c r="J233" s="63" t="s">
+      <c r="G233" s="62"/>
+      <c r="H233" s="62"/>
+      <c r="I233" s="62"/>
+      <c r="J233" s="77" t="s">
         <v>691</v>
       </c>
     </row>
@@ -20235,10 +20295,10 @@
       </c>
       <c r="E234" s="60"/>
       <c r="F234" s="59"/>
-      <c r="G234" s="63"/>
-      <c r="H234" s="63"/>
-      <c r="I234" s="63"/>
-      <c r="J234" s="63" t="s">
+      <c r="G234" s="62"/>
+      <c r="H234" s="62"/>
+      <c r="I234" s="62"/>
+      <c r="J234" s="77" t="s">
         <v>692</v>
       </c>
     </row>
@@ -20255,16 +20315,16 @@
       <c r="D235" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E235" s="63" t="s">
+      <c r="E235" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F235" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G235" s="63"/>
-      <c r="H235" s="63"/>
-      <c r="I235" s="63"/>
-      <c r="J235" s="64" t="s">
+      <c r="G235" s="62"/>
+      <c r="H235" s="62"/>
+      <c r="I235" s="62"/>
+      <c r="J235" s="75" t="s">
         <v>693</v>
       </c>
     </row>
@@ -20287,10 +20347,10 @@
       <c r="F236" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G236" s="63"/>
-      <c r="H236" s="63"/>
-      <c r="I236" s="63"/>
-      <c r="J236" s="64" t="s">
+      <c r="G236" s="62"/>
+      <c r="H236" s="62"/>
+      <c r="I236" s="62"/>
+      <c r="J236" s="75" t="s">
         <v>694</v>
       </c>
     </row>
@@ -20307,16 +20367,16 @@
       <c r="D237" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E237" s="63" t="s">
+      <c r="E237" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F237" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G237" s="63"/>
-      <c r="H237" s="63"/>
-      <c r="I237" s="63"/>
-      <c r="J237" s="64" t="s">
+      <c r="G237" s="62"/>
+      <c r="H237" s="62"/>
+      <c r="I237" s="62"/>
+      <c r="J237" s="75" t="s">
         <v>695</v>
       </c>
     </row>
@@ -20339,10 +20399,10 @@
       <c r="F238" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G238" s="63"/>
-      <c r="H238" s="63"/>
-      <c r="I238" s="63"/>
-      <c r="J238" s="63" t="s">
+      <c r="G238" s="62"/>
+      <c r="H238" s="62"/>
+      <c r="I238" s="62"/>
+      <c r="J238" s="77" t="s">
         <v>696</v>
       </c>
     </row>
@@ -20359,16 +20419,16 @@
       <c r="D239" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E239" s="63" t="s">
+      <c r="E239" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F239" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G239" s="63"/>
-      <c r="H239" s="63"/>
-      <c r="I239" s="63"/>
-      <c r="J239" s="64" t="s">
+      <c r="G239" s="62"/>
+      <c r="H239" s="62"/>
+      <c r="I239" s="62"/>
+      <c r="J239" s="75" t="s">
         <v>697</v>
       </c>
     </row>
@@ -20396,7 +20456,7 @@
       <c r="I240" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J240" s="60" t="s">
+      <c r="J240" s="72" t="s">
         <v>698</v>
       </c>
     </row>
@@ -20422,7 +20482,7 @@
       <c r="G241" s="58"/>
       <c r="H241" s="59"/>
       <c r="I241" s="58"/>
-      <c r="J241" s="60" t="s">
+      <c r="J241" s="72" t="s">
         <v>699</v>
       </c>
     </row>
@@ -20448,7 +20508,7 @@
       <c r="G242" s="58"/>
       <c r="H242" s="59"/>
       <c r="I242" s="58"/>
-      <c r="J242" s="60" t="s">
+      <c r="J242" s="72" t="s">
         <v>700</v>
       </c>
     </row>
@@ -20474,7 +20534,7 @@
       <c r="G243" s="58"/>
       <c r="H243" s="58"/>
       <c r="I243" s="58"/>
-      <c r="J243" s="57" t="s">
+      <c r="J243" s="74" t="s">
         <v>701</v>
       </c>
     </row>
@@ -20500,7 +20560,7 @@
       <c r="G244" s="58"/>
       <c r="H244" s="58"/>
       <c r="I244" s="58"/>
-      <c r="J244" s="64" t="s">
+      <c r="J244" s="75" t="s">
         <v>702</v>
       </c>
     </row>
@@ -20523,10 +20583,10 @@
       <c r="F245" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G245" s="63"/>
-      <c r="H245" s="63"/>
-      <c r="I245" s="63"/>
-      <c r="J245" s="64" t="s">
+      <c r="G245" s="62"/>
+      <c r="H245" s="62"/>
+      <c r="I245" s="62"/>
+      <c r="J245" s="75" t="s">
         <v>703</v>
       </c>
     </row>
@@ -20549,10 +20609,10 @@
       <c r="F246" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G246" s="63"/>
-      <c r="H246" s="63"/>
-      <c r="I246" s="63"/>
-      <c r="J246" s="64" t="s">
+      <c r="G246" s="62"/>
+      <c r="H246" s="62"/>
+      <c r="I246" s="62"/>
+      <c r="J246" s="75" t="s">
         <v>704</v>
       </c>
     </row>
@@ -20575,10 +20635,10 @@
       <c r="F247" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G247" s="63"/>
-      <c r="H247" s="63"/>
-      <c r="I247" s="63"/>
-      <c r="J247" s="64" t="s">
+      <c r="G247" s="62"/>
+      <c r="H247" s="62"/>
+      <c r="I247" s="62"/>
+      <c r="J247" s="75" t="s">
         <v>705</v>
       </c>
     </row>
@@ -20601,10 +20661,10 @@
       <c r="F248" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G248" s="63"/>
-      <c r="H248" s="63"/>
-      <c r="I248" s="63"/>
-      <c r="J248" s="64" t="s">
+      <c r="G248" s="62"/>
+      <c r="H248" s="62"/>
+      <c r="I248" s="62"/>
+      <c r="J248" s="75" t="s">
         <v>706</v>
       </c>
     </row>
@@ -20634,7 +20694,7 @@
       <c r="I249" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J249" s="57" t="s">
+      <c r="J249" s="74" t="s">
         <v>707</v>
       </c>
     </row>
@@ -20660,7 +20720,7 @@
       <c r="G250" s="58"/>
       <c r="H250" s="59"/>
       <c r="I250" s="58"/>
-      <c r="J250" s="61" t="s">
+      <c r="J250" s="73" t="s">
         <v>708</v>
       </c>
     </row>
@@ -20688,7 +20748,7 @@
       <c r="I251" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J251" s="61" t="s">
+      <c r="J251" s="73" t="s">
         <v>709</v>
       </c>
     </row>
@@ -20716,7 +20776,7 @@
       </c>
       <c r="H252" s="59"/>
       <c r="I252" s="58"/>
-      <c r="J252" s="57" t="s">
+      <c r="J252" s="74" t="s">
         <v>710</v>
       </c>
     </row>
@@ -20742,7 +20802,7 @@
       <c r="G253" s="58"/>
       <c r="H253" s="59"/>
       <c r="I253" s="58"/>
-      <c r="J253" s="57" t="s">
+      <c r="J253" s="74" t="s">
         <v>711</v>
       </c>
     </row>
@@ -20770,7 +20830,7 @@
       </c>
       <c r="H254" s="58"/>
       <c r="I254" s="58"/>
-      <c r="J254" s="57" t="s">
+      <c r="J254" s="74" t="s">
         <v>712</v>
       </c>
     </row>
@@ -20796,7 +20856,7 @@
       <c r="G255" s="58"/>
       <c r="H255" s="58"/>
       <c r="I255" s="58"/>
-      <c r="J255" s="57" t="s">
+      <c r="J255" s="74" t="s">
         <v>713</v>
       </c>
     </row>
@@ -20822,9 +20882,9 @@
       <c r="G256" s="58" t="s">
         <v>555</v>
       </c>
-      <c r="H256" s="63"/>
-      <c r="I256" s="63"/>
-      <c r="J256" s="63" t="s">
+      <c r="H256" s="62"/>
+      <c r="I256" s="62"/>
+      <c r="J256" s="77" t="s">
         <v>714</v>
       </c>
     </row>
@@ -20850,9 +20910,9 @@
       <c r="G257" s="58" t="s">
         <v>555</v>
       </c>
-      <c r="H257" s="63"/>
-      <c r="I257" s="63"/>
-      <c r="J257" s="64" t="s">
+      <c r="H257" s="62"/>
+      <c r="I257" s="62"/>
+      <c r="J257" s="75" t="s">
         <v>715</v>
       </c>
     </row>
@@ -20875,10 +20935,10 @@
       <c r="F258" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G258" s="63"/>
-      <c r="H258" s="63"/>
-      <c r="I258" s="63"/>
-      <c r="J258" s="63" t="s">
+      <c r="G258" s="62"/>
+      <c r="H258" s="62"/>
+      <c r="I258" s="62"/>
+      <c r="J258" s="77" t="s">
         <v>671</v>
       </c>
     </row>
@@ -20895,7 +20955,7 @@
       <c r="D259" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E259" s="72" t="s">
+      <c r="E259" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F259" s="59" t="s">
@@ -20906,7 +20966,7 @@
       <c r="I259" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J259" s="57" t="s">
+      <c r="J259" s="74" t="s">
         <v>527</v>
       </c>
     </row>
@@ -20930,7 +20990,7 @@
       <c r="I260" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J260" s="57" t="s">
+      <c r="J260" s="74" t="s">
         <v>716</v>
       </c>
     </row>
@@ -20947,16 +21007,16 @@
       <c r="D261" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E261" s="72" t="s">
+      <c r="E261" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="F261" s="73" t="s">
+      <c r="F261" s="67" t="s">
         <v>445</v>
       </c>
       <c r="G261" s="58"/>
       <c r="H261" s="59"/>
       <c r="I261" s="58"/>
-      <c r="J261" s="72" t="s">
+      <c r="J261" s="85" t="s">
         <v>717</v>
       </c>
     </row>
@@ -20973,7 +21033,7 @@
       <c r="D262" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E262" s="72" t="s">
+      <c r="E262" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F262" s="59" t="s">
@@ -20982,7 +21042,7 @@
       <c r="G262" s="58"/>
       <c r="H262" s="59"/>
       <c r="I262" s="58"/>
-      <c r="J262" s="72" t="s">
+      <c r="J262" s="85" t="s">
         <v>718</v>
       </c>
     </row>
@@ -20999,7 +21059,7 @@
       <c r="D263" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E263" s="72" t="s">
+      <c r="E263" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F263" s="59" t="s">
@@ -21010,7 +21070,7 @@
       <c r="I263" s="58" t="s">
         <v>719</v>
       </c>
-      <c r="J263" s="72" t="s">
+      <c r="J263" s="85" t="s">
         <v>720</v>
       </c>
     </row>
@@ -21027,16 +21087,16 @@
       <c r="D264" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E264" s="72" t="s">
+      <c r="E264" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="F264" s="73" t="s">
+      <c r="F264" s="67" t="s">
         <v>445</v>
       </c>
       <c r="G264" s="58"/>
       <c r="H264" s="58"/>
       <c r="I264" s="58"/>
-      <c r="J264" s="72" t="s">
+      <c r="J264" s="85" t="s">
         <v>721</v>
       </c>
     </row>
@@ -21053,16 +21113,16 @@
       <c r="D265" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E265" s="72" t="s">
+      <c r="E265" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F265" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G265" s="63"/>
-      <c r="H265" s="63"/>
-      <c r="I265" s="63"/>
-      <c r="J265" s="74" t="s">
+      <c r="G265" s="62"/>
+      <c r="H265" s="62"/>
+      <c r="I265" s="62"/>
+      <c r="J265" s="86" t="s">
         <v>722</v>
       </c>
     </row>
@@ -21090,7 +21150,7 @@
       <c r="I266" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J266" s="60" t="s">
+      <c r="J266" s="72" t="s">
         <v>723</v>
       </c>
     </row>
@@ -21116,7 +21176,7 @@
       <c r="G267" s="58"/>
       <c r="H267" s="59"/>
       <c r="I267" s="58"/>
-      <c r="J267" s="60" t="s">
+      <c r="J267" s="72" t="s">
         <v>724</v>
       </c>
     </row>
@@ -21142,7 +21202,7 @@
       <c r="G268" s="58"/>
       <c r="H268" s="59"/>
       <c r="I268" s="58"/>
-      <c r="J268" s="60" t="s">
+      <c r="J268" s="72" t="s">
         <v>725</v>
       </c>
     </row>
@@ -21168,7 +21228,7 @@
       <c r="G269" s="58"/>
       <c r="H269" s="58"/>
       <c r="I269" s="58"/>
-      <c r="J269" s="60" t="s">
+      <c r="J269" s="72" t="s">
         <v>726</v>
       </c>
     </row>
@@ -21194,7 +21254,7 @@
       <c r="G270" s="58"/>
       <c r="H270" s="58"/>
       <c r="I270" s="58"/>
-      <c r="J270" s="60" t="s">
+      <c r="J270" s="72" t="s">
         <v>727</v>
       </c>
     </row>
@@ -21211,14 +21271,14 @@
       <c r="D271" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E271" s="72"/>
+      <c r="E271" s="66"/>
       <c r="F271" s="58"/>
       <c r="G271" s="58"/>
       <c r="H271" s="59"/>
       <c r="I271" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J271" s="72" t="s">
+      <c r="J271" s="85" t="s">
         <v>728</v>
       </c>
     </row>
@@ -21235,7 +21295,7 @@
       <c r="D272" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E272" s="72" t="s">
+      <c r="E272" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F272" s="58" t="s">
@@ -21244,7 +21304,7 @@
       <c r="G272" s="58"/>
       <c r="H272" s="59"/>
       <c r="I272" s="58"/>
-      <c r="J272" s="72" t="s">
+      <c r="J272" s="85" t="s">
         <v>729</v>
       </c>
     </row>
@@ -21261,7 +21321,7 @@
       <c r="D273" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E273" s="72" t="s">
+      <c r="E273" s="66" t="s">
         <v>49</v>
       </c>
       <c r="F273" s="58" t="s">
@@ -21272,7 +21332,7 @@
       <c r="I273" s="58" t="s">
         <v>730</v>
       </c>
-      <c r="J273" s="72" t="s">
+      <c r="J273" s="85" t="s">
         <v>731</v>
       </c>
     </row>
@@ -21289,7 +21349,7 @@
       <c r="D274" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E274" s="72" t="s">
+      <c r="E274" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F274" s="58" t="s">
@@ -21300,7 +21360,7 @@
       <c r="I274" s="58" t="s">
         <v>732</v>
       </c>
-      <c r="J274" s="72" t="s">
+      <c r="J274" s="85" t="s">
         <v>713</v>
       </c>
     </row>
@@ -21324,7 +21384,7 @@
       <c r="I275" s="58" t="s">
         <v>733</v>
       </c>
-      <c r="J275" s="72" t="s">
+      <c r="J275" s="85" t="s">
         <v>734</v>
       </c>
     </row>
@@ -21341,16 +21401,16 @@
       <c r="D276" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E276" s="72" t="s">
+      <c r="E276" s="66" t="s">
         <v>49</v>
       </c>
       <c r="F276" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G276" s="63"/>
-      <c r="H276" s="63"/>
-      <c r="I276" s="63"/>
-      <c r="J276" s="74" t="s">
+      <c r="G276" s="62"/>
+      <c r="H276" s="62"/>
+      <c r="I276" s="62"/>
+      <c r="J276" s="86" t="s">
         <v>735</v>
       </c>
     </row>
@@ -21367,18 +21427,18 @@
       <c r="D277" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E277" s="72" t="s">
+      <c r="E277" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F277" s="58" t="s">
         <v>443</v>
       </c>
       <c r="G277" s="58"/>
-      <c r="H277" s="64" t="s">
+      <c r="H277" s="63" t="s">
         <v>609</v>
       </c>
       <c r="I277" s="58"/>
-      <c r="J277" s="72" t="s">
+      <c r="J277" s="85" t="s">
         <v>713</v>
       </c>
     </row>
@@ -21395,20 +21455,20 @@
       <c r="D278" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E278" s="74" t="s">
+      <c r="E278" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="F278" s="73" t="s">
+      <c r="F278" s="67" t="s">
         <v>440</v>
       </c>
-      <c r="G278" s="63"/>
-      <c r="H278" s="64" t="s">
+      <c r="G278" s="62"/>
+      <c r="H278" s="63" t="s">
         <v>609</v>
       </c>
       <c r="I278" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J278" s="74" t="s">
+      <c r="J278" s="86" t="s">
         <v>736</v>
       </c>
     </row>
@@ -21425,16 +21485,16 @@
       <c r="D279" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E279" s="74" t="s">
+      <c r="E279" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="F279" s="73" t="s">
+      <c r="F279" s="67" t="s">
         <v>445</v>
       </c>
-      <c r="G279" s="63"/>
-      <c r="H279" s="63"/>
-      <c r="I279" s="63"/>
-      <c r="J279" s="74" t="s">
+      <c r="G279" s="62"/>
+      <c r="H279" s="62"/>
+      <c r="I279" s="62"/>
+      <c r="J279" s="86" t="s">
         <v>737</v>
       </c>
     </row>
@@ -21451,20 +21511,20 @@
       <c r="D280" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E280" s="74" t="s">
+      <c r="E280" s="68" t="s">
         <v>47</v>
       </c>
       <c r="F280" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G280" s="74" t="s">
+      <c r="G280" s="68" t="s">
         <v>738</v>
       </c>
-      <c r="H280" s="64" t="s">
+      <c r="H280" s="63" t="s">
         <v>609</v>
       </c>
-      <c r="I280" s="63"/>
-      <c r="J280" s="74" t="s">
+      <c r="I280" s="62"/>
+      <c r="J280" s="86" t="s">
         <v>739</v>
       </c>
     </row>
@@ -21481,14 +21541,14 @@
       <c r="D281" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E281" s="63"/>
+      <c r="E281" s="62"/>
       <c r="F281" s="58"/>
-      <c r="G281" s="63"/>
-      <c r="H281" s="63"/>
+      <c r="G281" s="62"/>
+      <c r="H281" s="62"/>
       <c r="I281" s="58" t="s">
         <v>740</v>
       </c>
-      <c r="J281" s="64" t="s">
+      <c r="J281" s="75" t="s">
         <v>741</v>
       </c>
     </row>
@@ -21505,16 +21565,16 @@
       <c r="D282" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E282" s="74" t="s">
+      <c r="E282" s="68" t="s">
         <v>35</v>
       </c>
       <c r="F282" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G282" s="63"/>
-      <c r="H282" s="63"/>
-      <c r="I282" s="63"/>
-      <c r="J282" s="64" t="s">
+      <c r="G282" s="62"/>
+      <c r="H282" s="62"/>
+      <c r="I282" s="62"/>
+      <c r="J282" s="75" t="s">
         <v>742</v>
       </c>
     </row>
@@ -21531,16 +21591,16 @@
       <c r="D283" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E283" s="64" t="s">
+      <c r="E283" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="F283" s="73" t="s">
+      <c r="F283" s="67" t="s">
         <v>440</v>
       </c>
-      <c r="G283" s="63"/>
-      <c r="H283" s="63"/>
-      <c r="I283" s="63"/>
-      <c r="J283" s="64" t="s">
+      <c r="G283" s="62"/>
+      <c r="H283" s="62"/>
+      <c r="I283" s="62"/>
+      <c r="J283" s="75" t="s">
         <v>743</v>
       </c>
     </row>
@@ -21557,16 +21617,16 @@
       <c r="D284" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E284" s="64" t="s">
+      <c r="E284" s="63" t="s">
         <v>51</v>
       </c>
       <c r="F284" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G284" s="63"/>
-      <c r="H284" s="63"/>
-      <c r="I284" s="63"/>
-      <c r="J284" s="64" t="s">
+      <c r="G284" s="62"/>
+      <c r="H284" s="62"/>
+      <c r="I284" s="62"/>
+      <c r="J284" s="75" t="s">
         <v>744</v>
       </c>
     </row>
@@ -21583,16 +21643,16 @@
       <c r="D285" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E285" s="72" t="s">
+      <c r="E285" s="66" t="s">
         <v>16</v>
       </c>
       <c r="F285" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G285" s="63"/>
-      <c r="H285" s="63"/>
-      <c r="I285" s="63"/>
-      <c r="J285" s="64" t="s">
+      <c r="G285" s="62"/>
+      <c r="H285" s="62"/>
+      <c r="I285" s="62"/>
+      <c r="J285" s="75" t="s">
         <v>745</v>
       </c>
     </row>
@@ -21609,12 +21669,12 @@
       <c r="D286" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E286" s="63"/>
+      <c r="E286" s="62"/>
       <c r="F286" s="58"/>
-      <c r="G286" s="63"/>
-      <c r="H286" s="63"/>
-      <c r="I286" s="63"/>
-      <c r="J286" s="64" t="s">
+      <c r="G286" s="62"/>
+      <c r="H286" s="62"/>
+      <c r="I286" s="62"/>
+      <c r="J286" s="75" t="s">
         <v>746</v>
       </c>
     </row>
@@ -21638,7 +21698,7 @@
       <c r="I287" s="58" t="s">
         <v>747</v>
       </c>
-      <c r="J287" s="60" t="s">
+      <c r="J287" s="72" t="s">
         <v>748</v>
       </c>
     </row>
@@ -21660,7 +21720,7 @@
       <c r="G288" s="58"/>
       <c r="H288" s="59"/>
       <c r="I288" s="58"/>
-      <c r="J288" s="60" t="s">
+      <c r="J288" s="72" t="s">
         <v>749</v>
       </c>
     </row>
@@ -21682,7 +21742,7 @@
       <c r="G289" s="58"/>
       <c r="H289" s="59"/>
       <c r="I289" s="58"/>
-      <c r="J289" s="60" t="s">
+      <c r="J289" s="72" t="s">
         <v>750</v>
       </c>
     </row>
@@ -21708,7 +21768,7 @@
       <c r="G290" s="58"/>
       <c r="H290" s="58"/>
       <c r="I290" s="58"/>
-      <c r="J290" s="60" t="s">
+      <c r="J290" s="72" t="s">
         <v>751</v>
       </c>
     </row>
@@ -21734,7 +21794,7 @@
       <c r="G291" s="58"/>
       <c r="H291" s="58"/>
       <c r="I291" s="58"/>
-      <c r="J291" s="60" t="s">
+      <c r="J291" s="72" t="s">
         <v>752</v>
       </c>
     </row>
@@ -21751,16 +21811,16 @@
       <c r="D292" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E292" s="64" t="s">
+      <c r="E292" s="63" t="s">
         <v>31</v>
       </c>
       <c r="F292" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G292" s="63"/>
-      <c r="H292" s="63"/>
-      <c r="I292" s="63"/>
-      <c r="J292" s="63" t="s">
+      <c r="G292" s="62"/>
+      <c r="H292" s="62"/>
+      <c r="I292" s="62"/>
+      <c r="J292" s="77" t="s">
         <v>753</v>
       </c>
     </row>
@@ -21783,10 +21843,10 @@
       <c r="F293" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G293" s="63"/>
-      <c r="H293" s="63"/>
-      <c r="I293" s="63"/>
-      <c r="J293" s="64" t="s">
+      <c r="G293" s="62"/>
+      <c r="H293" s="62"/>
+      <c r="I293" s="62"/>
+      <c r="J293" s="75" t="s">
         <v>754</v>
       </c>
     </row>
@@ -21803,16 +21863,16 @@
       <c r="D294" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E294" s="64" t="s">
+      <c r="E294" s="63" t="s">
         <v>31</v>
       </c>
       <c r="F294" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G294" s="63"/>
-      <c r="H294" s="63"/>
-      <c r="I294" s="63"/>
-      <c r="J294" s="64" t="s">
+      <c r="G294" s="62"/>
+      <c r="H294" s="62"/>
+      <c r="I294" s="62"/>
+      <c r="J294" s="75" t="s">
         <v>755</v>
       </c>
     </row>
@@ -21835,10 +21895,10 @@
       <c r="F295" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G295" s="63"/>
-      <c r="H295" s="63"/>
-      <c r="I295" s="63"/>
-      <c r="J295" s="64" t="s">
+      <c r="G295" s="62"/>
+      <c r="H295" s="62"/>
+      <c r="I295" s="62"/>
+      <c r="J295" s="75" t="s">
         <v>756</v>
       </c>
     </row>
@@ -21855,16 +21915,16 @@
       <c r="D296" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E296" s="64" t="s">
+      <c r="E296" s="63" t="s">
         <v>31</v>
       </c>
       <c r="F296" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G296" s="63"/>
-      <c r="H296" s="63"/>
-      <c r="I296" s="63"/>
-      <c r="J296" s="64" t="s">
+      <c r="G296" s="62"/>
+      <c r="H296" s="62"/>
+      <c r="I296" s="62"/>
+      <c r="J296" s="75" t="s">
         <v>757</v>
       </c>
     </row>
@@ -21881,12 +21941,12 @@
       <c r="D297" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E297" s="63"/>
+      <c r="E297" s="62"/>
       <c r="F297" s="58"/>
-      <c r="G297" s="63"/>
-      <c r="H297" s="63"/>
-      <c r="I297" s="63"/>
-      <c r="J297" s="64" t="s">
+      <c r="G297" s="62"/>
+      <c r="H297" s="62"/>
+      <c r="I297" s="62"/>
+      <c r="J297" s="75" t="s">
         <v>567</v>
       </c>
     </row>
@@ -21914,7 +21974,7 @@
       <c r="I298" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J298" s="57" t="s">
+      <c r="J298" s="74" t="s">
         <v>758</v>
       </c>
     </row>
@@ -21940,7 +22000,7 @@
       <c r="G299" s="58"/>
       <c r="H299" s="59"/>
       <c r="I299" s="58"/>
-      <c r="J299" s="57" t="s">
+      <c r="J299" s="74" t="s">
         <v>759</v>
       </c>
     </row>
@@ -21968,7 +22028,7 @@
       <c r="I300" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J300" s="57" t="s">
+      <c r="J300" s="74" t="s">
         <v>760</v>
       </c>
     </row>
@@ -21994,7 +22054,7 @@
       <c r="G301" s="58"/>
       <c r="H301" s="59"/>
       <c r="I301" s="58"/>
-      <c r="J301" s="57" t="s">
+      <c r="J301" s="74" t="s">
         <v>761</v>
       </c>
     </row>
@@ -22020,7 +22080,7 @@
       <c r="G302" s="58"/>
       <c r="H302" s="59"/>
       <c r="I302" s="58"/>
-      <c r="J302" s="61" t="s">
+      <c r="J302" s="73" t="s">
         <v>762</v>
       </c>
     </row>
@@ -22046,7 +22106,7 @@
       <c r="G303" s="58"/>
       <c r="H303" s="58"/>
       <c r="I303" s="58"/>
-      <c r="J303" s="57" t="s">
+      <c r="J303" s="74" t="s">
         <v>763</v>
       </c>
     </row>
@@ -22072,7 +22132,7 @@
       <c r="G304" s="58"/>
       <c r="H304" s="58"/>
       <c r="I304" s="58"/>
-      <c r="J304" s="61" t="s">
+      <c r="J304" s="73" t="s">
         <v>764</v>
       </c>
     </row>
@@ -22095,10 +22155,10 @@
       <c r="F305" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G305" s="63"/>
-      <c r="H305" s="63"/>
-      <c r="I305" s="63"/>
-      <c r="J305" s="63" t="s">
+      <c r="G305" s="62"/>
+      <c r="H305" s="62"/>
+      <c r="I305" s="62"/>
+      <c r="J305" s="77" t="s">
         <v>765</v>
       </c>
     </row>
@@ -22121,10 +22181,10 @@
       <c r="F306" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G306" s="63"/>
-      <c r="H306" s="63"/>
-      <c r="I306" s="63"/>
-      <c r="J306" s="75" t="s">
+      <c r="G306" s="62"/>
+      <c r="H306" s="62"/>
+      <c r="I306" s="62"/>
+      <c r="J306" s="69" t="s">
         <v>766</v>
       </c>
     </row>
@@ -22147,10 +22207,10 @@
       <c r="F307" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G307" s="63"/>
-      <c r="H307" s="63"/>
-      <c r="I307" s="63"/>
-      <c r="J307" s="63" t="s">
+      <c r="G307" s="62"/>
+      <c r="H307" s="62"/>
+      <c r="I307" s="62"/>
+      <c r="J307" s="77" t="s">
         <v>767</v>
       </c>
     </row>
@@ -22173,10 +22233,10 @@
       <c r="F308" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G308" s="63"/>
-      <c r="H308" s="63"/>
-      <c r="I308" s="63"/>
-      <c r="J308" s="63" t="s">
+      <c r="G308" s="62"/>
+      <c r="H308" s="62"/>
+      <c r="I308" s="62"/>
+      <c r="J308" s="77" t="s">
         <v>768</v>
       </c>
     </row>
@@ -22199,10 +22259,10 @@
       <c r="F309" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G309" s="63"/>
-      <c r="H309" s="63"/>
-      <c r="I309" s="63"/>
-      <c r="J309" s="63" t="s">
+      <c r="G309" s="62"/>
+      <c r="H309" s="62"/>
+      <c r="I309" s="62"/>
+      <c r="J309" s="77" t="s">
         <v>769</v>
       </c>
     </row>
@@ -22225,10 +22285,10 @@
       <c r="F310" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G310" s="63"/>
-      <c r="H310" s="63"/>
-      <c r="I310" s="63"/>
-      <c r="J310" s="63" t="s">
+      <c r="G310" s="62"/>
+      <c r="H310" s="62"/>
+      <c r="I310" s="62"/>
+      <c r="J310" s="77" t="s">
         <v>770</v>
       </c>
     </row>
@@ -22251,10 +22311,10 @@
       <c r="F311" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G311" s="63"/>
-      <c r="H311" s="63"/>
-      <c r="I311" s="63"/>
-      <c r="J311" s="63" t="s">
+      <c r="G311" s="62"/>
+      <c r="H311" s="62"/>
+      <c r="I311" s="62"/>
+      <c r="J311" s="77" t="s">
         <v>771</v>
       </c>
     </row>
@@ -22277,10 +22337,10 @@
       <c r="F312" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G312" s="63"/>
-      <c r="H312" s="63"/>
-      <c r="I312" s="63"/>
-      <c r="J312" s="63" t="s">
+      <c r="G312" s="62"/>
+      <c r="H312" s="62"/>
+      <c r="I312" s="62"/>
+      <c r="J312" s="77" t="s">
         <v>772</v>
       </c>
     </row>
@@ -22303,10 +22363,10 @@
       <c r="F313" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G313" s="63"/>
-      <c r="H313" s="63"/>
-      <c r="I313" s="63"/>
-      <c r="J313" s="63" t="s">
+      <c r="G313" s="62"/>
+      <c r="H313" s="62"/>
+      <c r="I313" s="62"/>
+      <c r="J313" s="77" t="s">
         <v>773</v>
       </c>
     </row>
@@ -22329,10 +22389,10 @@
       <c r="F314" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G314" s="63"/>
-      <c r="H314" s="63"/>
-      <c r="I314" s="63"/>
-      <c r="J314" s="63" t="s">
+      <c r="G314" s="62"/>
+      <c r="H314" s="62"/>
+      <c r="I314" s="62"/>
+      <c r="J314" s="77" t="s">
         <v>774</v>
       </c>
     </row>
@@ -22355,10 +22415,10 @@
       <c r="F315" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G315" s="63"/>
-      <c r="H315" s="63"/>
-      <c r="I315" s="63"/>
-      <c r="J315" s="63" t="s">
+      <c r="G315" s="62"/>
+      <c r="H315" s="62"/>
+      <c r="I315" s="62"/>
+      <c r="J315" s="77" t="s">
         <v>775</v>
       </c>
     </row>
@@ -22381,10 +22441,10 @@
       <c r="F316" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G316" s="63"/>
-      <c r="H316" s="63"/>
-      <c r="I316" s="63"/>
-      <c r="J316" s="63" t="s">
+      <c r="G316" s="62"/>
+      <c r="H316" s="62"/>
+      <c r="I316" s="62"/>
+      <c r="J316" s="77" t="s">
         <v>776</v>
       </c>
     </row>
@@ -22407,21 +22467,21 @@
       <c r="F317" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G317" s="63"/>
-      <c r="H317" s="63"/>
-      <c r="I317" s="63"/>
-      <c r="J317" s="63" t="s">
+      <c r="G317" s="62"/>
+      <c r="H317" s="62"/>
+      <c r="I317" s="62"/>
+      <c r="J317" s="77" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="318" spans="1:10">
-      <c r="A318" s="63" t="s">
+      <c r="A318" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="B318" s="63" t="s">
+      <c r="B318" s="62" t="s">
         <v>392</v>
       </c>
-      <c r="C318" s="63">
+      <c r="C318" s="62">
         <v>19</v>
       </c>
       <c r="D318" s="57" t="s">
@@ -22433,10 +22493,10 @@
       <c r="F318" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G318" s="63"/>
-      <c r="H318" s="63"/>
-      <c r="I318" s="63"/>
-      <c r="J318" s="63" t="s">
+      <c r="G318" s="62"/>
+      <c r="H318" s="62"/>
+      <c r="I318" s="62"/>
+      <c r="J318" s="77" t="s">
         <v>778</v>
       </c>
     </row>
@@ -22464,7 +22524,7 @@
       <c r="I319" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J319" s="60" t="s">
+      <c r="J319" s="72" t="s">
         <v>527</v>
       </c>
     </row>
@@ -22492,7 +22552,7 @@
       <c r="I320" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J320" s="57" t="s">
+      <c r="J320" s="74" t="s">
         <v>779</v>
       </c>
     </row>
@@ -22520,7 +22580,7 @@
       </c>
       <c r="H321" s="59"/>
       <c r="I321" s="58"/>
-      <c r="J321" s="57" t="s">
+      <c r="J321" s="74" t="s">
         <v>780</v>
       </c>
     </row>
@@ -22546,7 +22606,7 @@
       <c r="G322" s="58"/>
       <c r="H322" s="59"/>
       <c r="I322" s="58"/>
-      <c r="J322" s="57" t="s">
+      <c r="J322" s="74" t="s">
         <v>781</v>
       </c>
     </row>
@@ -22572,7 +22632,7 @@
       <c r="G323" s="58"/>
       <c r="H323" s="58"/>
       <c r="I323" s="58"/>
-      <c r="J323" s="57" t="s">
+      <c r="J323" s="74" t="s">
         <v>782</v>
       </c>
     </row>
@@ -22598,18 +22658,18 @@
       <c r="G324" s="58"/>
       <c r="H324" s="58"/>
       <c r="I324" s="58"/>
-      <c r="J324" s="57" t="s">
+      <c r="J324" s="74" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="325" spans="1:10">
-      <c r="A325" s="63" t="s">
+      <c r="A325" s="62" t="s">
         <v>395</v>
       </c>
-      <c r="B325" s="63" t="s">
+      <c r="B325" s="62" t="s">
         <v>396</v>
       </c>
-      <c r="C325" s="63">
+      <c r="C325" s="62">
         <v>6</v>
       </c>
       <c r="D325" s="57" t="s">
@@ -22621,21 +22681,21 @@
       <c r="F325" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G325" s="63"/>
-      <c r="H325" s="63"/>
-      <c r="I325" s="63"/>
-      <c r="J325" s="63" t="s">
+      <c r="G325" s="62"/>
+      <c r="H325" s="62"/>
+      <c r="I325" s="62"/>
+      <c r="J325" s="77" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="326" spans="1:10">
-      <c r="A326" s="63" t="s">
+      <c r="A326" s="62" t="s">
         <v>395</v>
       </c>
-      <c r="B326" s="63" t="s">
+      <c r="B326" s="62" t="s">
         <v>396</v>
       </c>
-      <c r="C326" s="63">
+      <c r="C326" s="62">
         <v>7</v>
       </c>
       <c r="D326" s="57" t="s">
@@ -22647,21 +22707,21 @@
       <c r="F326" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G326" s="63"/>
-      <c r="H326" s="63"/>
-      <c r="I326" s="63"/>
-      <c r="J326" s="64" t="s">
+      <c r="G326" s="62"/>
+      <c r="H326" s="62"/>
+      <c r="I326" s="62"/>
+      <c r="J326" s="75" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="327" spans="1:10">
-      <c r="A327" s="63" t="s">
+      <c r="A327" s="62" t="s">
         <v>395</v>
       </c>
-      <c r="B327" s="63" t="s">
+      <c r="B327" s="62" t="s">
         <v>396</v>
       </c>
-      <c r="C327" s="63">
+      <c r="C327" s="62">
         <v>8</v>
       </c>
       <c r="D327" s="57" t="s">
@@ -22673,10 +22733,10 @@
       <c r="F327" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G327" s="63"/>
-      <c r="H327" s="63"/>
-      <c r="I327" s="63"/>
-      <c r="J327" s="64" t="s">
+      <c r="G327" s="62"/>
+      <c r="H327" s="62"/>
+      <c r="I327" s="62"/>
+      <c r="J327" s="75" t="s">
         <v>780</v>
       </c>
     </row>
@@ -22704,7 +22764,7 @@
       <c r="I328" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J328" s="57" t="s">
+      <c r="J328" s="74" t="s">
         <v>786</v>
       </c>
     </row>
@@ -22732,7 +22792,7 @@
       </c>
       <c r="H329" s="59"/>
       <c r="I329" s="58"/>
-      <c r="J329" s="57" t="s">
+      <c r="J329" s="74" t="s">
         <v>787</v>
       </c>
     </row>
@@ -22758,7 +22818,7 @@
       <c r="G330" s="58"/>
       <c r="H330" s="59"/>
       <c r="I330" s="58"/>
-      <c r="J330" s="57" t="s">
+      <c r="J330" s="74" t="s">
         <v>788</v>
       </c>
     </row>
@@ -22784,7 +22844,7 @@
       <c r="G331" s="58"/>
       <c r="H331" s="58"/>
       <c r="I331" s="58"/>
-      <c r="J331" s="57" t="s">
+      <c r="J331" s="74" t="s">
         <v>789</v>
       </c>
     </row>
@@ -22812,7 +22872,7 @@
         <v>609</v>
       </c>
       <c r="I332" s="58"/>
-      <c r="J332" s="57" t="s">
+      <c r="J332" s="74" t="s">
         <v>790</v>
       </c>
     </row>
@@ -22838,11 +22898,11 @@
       <c r="G333" s="59" t="s">
         <v>555</v>
       </c>
-      <c r="H333" s="63" t="s">
+      <c r="H333" s="62" t="s">
         <v>609</v>
       </c>
-      <c r="I333" s="63"/>
-      <c r="J333" s="57" t="s">
+      <c r="I333" s="62"/>
+      <c r="J333" s="74" t="s">
         <v>780</v>
       </c>
     </row>
@@ -22859,18 +22919,18 @@
       <c r="D334" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E334" s="63" t="s">
+      <c r="E334" s="62" t="s">
         <v>59</v>
       </c>
       <c r="F334" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G334" s="63"/>
-      <c r="H334" s="63"/>
+      <c r="G334" s="62"/>
+      <c r="H334" s="62"/>
       <c r="I334" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J334" s="63" t="s">
+      <c r="J334" s="77" t="s">
         <v>791</v>
       </c>
     </row>
@@ -22893,10 +22953,10 @@
       <c r="F335" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G335" s="63"/>
-      <c r="H335" s="63"/>
-      <c r="I335" s="63"/>
-      <c r="J335" s="63" t="s">
+      <c r="G335" s="62"/>
+      <c r="H335" s="62"/>
+      <c r="I335" s="62"/>
+      <c r="J335" s="77" t="s">
         <v>792</v>
       </c>
     </row>
@@ -22913,16 +22973,16 @@
       <c r="D336" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E336" s="63" t="s">
+      <c r="E336" s="62" t="s">
         <v>59</v>
       </c>
       <c r="F336" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G336" s="63"/>
-      <c r="H336" s="63"/>
-      <c r="I336" s="63"/>
-      <c r="J336" s="63" t="s">
+      <c r="G336" s="62"/>
+      <c r="H336" s="62"/>
+      <c r="I336" s="62"/>
+      <c r="J336" s="77" t="s">
         <v>793</v>
       </c>
     </row>
@@ -22945,10 +23005,10 @@
       <c r="F337" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G337" s="63"/>
-      <c r="H337" s="63"/>
-      <c r="I337" s="63"/>
-      <c r="J337" s="63" t="s">
+      <c r="G337" s="62"/>
+      <c r="H337" s="62"/>
+      <c r="I337" s="62"/>
+      <c r="J337" s="77" t="s">
         <v>794</v>
       </c>
     </row>
@@ -22965,16 +23025,16 @@
       <c r="D338" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E338" s="63" t="s">
+      <c r="E338" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F338" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G338" s="63"/>
-      <c r="H338" s="63"/>
-      <c r="I338" s="63"/>
-      <c r="J338" s="63" t="s">
+      <c r="G338" s="62"/>
+      <c r="H338" s="62"/>
+      <c r="I338" s="62"/>
+      <c r="J338" s="77" t="s">
         <v>795</v>
       </c>
     </row>
@@ -22991,16 +23051,16 @@
       <c r="D339" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E339" s="63" t="s">
+      <c r="E339" s="62" t="s">
         <v>59</v>
       </c>
       <c r="F339" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G339" s="63"/>
-      <c r="H339" s="63"/>
-      <c r="I339" s="63"/>
-      <c r="J339" s="65" t="s">
+      <c r="G339" s="62"/>
+      <c r="H339" s="62"/>
+      <c r="I339" s="62"/>
+      <c r="J339" s="76" t="s">
         <v>796</v>
       </c>
     </row>
@@ -23017,16 +23077,16 @@
       <c r="D340" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E340" s="63" t="s">
+      <c r="E340" s="62" t="s">
         <v>59</v>
       </c>
       <c r="F340" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G340" s="63"/>
-      <c r="H340" s="63"/>
-      <c r="I340" s="63"/>
-      <c r="J340" s="63" t="s">
+      <c r="G340" s="62"/>
+      <c r="H340" s="62"/>
+      <c r="I340" s="62"/>
+      <c r="J340" s="77" t="s">
         <v>797</v>
       </c>
     </row>
@@ -23049,10 +23109,10 @@
       <c r="F341" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G341" s="63"/>
-      <c r="H341" s="63"/>
-      <c r="I341" s="63"/>
-      <c r="J341" s="63" t="s">
+      <c r="G341" s="62"/>
+      <c r="H341" s="62"/>
+      <c r="I341" s="62"/>
+      <c r="J341" s="77" t="s">
         <v>798</v>
       </c>
     </row>
@@ -23069,16 +23129,16 @@
       <c r="D342" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E342" s="63" t="s">
+      <c r="E342" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F342" s="58" t="s">
         <v>440</v>
       </c>
-      <c r="G342" s="63"/>
-      <c r="H342" s="63"/>
-      <c r="I342" s="63"/>
-      <c r="J342" s="63" t="s">
+      <c r="G342" s="62"/>
+      <c r="H342" s="62"/>
+      <c r="I342" s="62"/>
+      <c r="J342" s="77" t="s">
         <v>799</v>
       </c>
     </row>
@@ -23095,16 +23155,16 @@
       <c r="D343" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E343" s="64" t="s">
+      <c r="E343" s="63" t="s">
         <v>20</v>
       </c>
       <c r="F343" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G343" s="63"/>
-      <c r="H343" s="63"/>
-      <c r="I343" s="63"/>
-      <c r="J343" s="64" t="s">
+      <c r="G343" s="62"/>
+      <c r="H343" s="62"/>
+      <c r="I343" s="62"/>
+      <c r="J343" s="75" t="s">
         <v>800</v>
       </c>
     </row>
@@ -23127,10 +23187,10 @@
       <c r="F344" s="58" t="s">
         <v>443</v>
       </c>
-      <c r="G344" s="63"/>
-      <c r="H344" s="63"/>
-      <c r="I344" s="63"/>
-      <c r="J344" s="63" t="s">
+      <c r="G344" s="62"/>
+      <c r="H344" s="62"/>
+      <c r="I344" s="62"/>
+      <c r="J344" s="77" t="s">
         <v>801</v>
       </c>
     </row>
@@ -23158,7 +23218,7 @@
       <c r="I345" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J345" s="60" t="s">
+      <c r="J345" s="72" t="s">
         <v>527</v>
       </c>
     </row>
@@ -23186,7 +23246,7 @@
       <c r="I346" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J346" s="60" t="s">
+      <c r="J346" s="72" t="s">
         <v>802</v>
       </c>
     </row>
@@ -23214,7 +23274,7 @@
       </c>
       <c r="H347" s="59"/>
       <c r="I347" s="58"/>
-      <c r="J347" s="60" t="s">
+      <c r="J347" s="72" t="s">
         <v>803</v>
       </c>
     </row>
@@ -23240,7 +23300,7 @@
       <c r="G348" s="58"/>
       <c r="H348" s="59"/>
       <c r="I348" s="58"/>
-      <c r="J348" s="60" t="s">
+      <c r="J348" s="72" t="s">
         <v>804</v>
       </c>
     </row>
@@ -23268,7 +23328,7 @@
       <c r="I349" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J349" s="60" t="s">
+      <c r="J349" s="72" t="s">
         <v>805</v>
       </c>
     </row>
@@ -23296,7 +23356,7 @@
       </c>
       <c r="H350" s="59"/>
       <c r="I350" s="58"/>
-      <c r="J350" s="60" t="s">
+      <c r="J350" s="72" t="s">
         <v>806</v>
       </c>
     </row>
@@ -23322,7 +23382,7 @@
       <c r="G351" s="58"/>
       <c r="H351" s="59"/>
       <c r="I351" s="58"/>
-      <c r="J351" s="60" t="s">
+      <c r="J351" s="72" t="s">
         <v>807</v>
       </c>
     </row>
@@ -23350,7 +23410,7 @@
       </c>
       <c r="H352" s="58"/>
       <c r="I352" s="58"/>
-      <c r="J352" s="60" t="s">
+      <c r="J352" s="72" t="s">
         <v>808</v>
       </c>
     </row>
@@ -23376,7 +23436,7 @@
       <c r="G353" s="58"/>
       <c r="H353" s="58"/>
       <c r="I353" s="58"/>
-      <c r="J353" s="60" t="s">
+      <c r="J353" s="72" t="s">
         <v>809</v>
       </c>
     </row>
@@ -23402,9 +23462,9 @@
       <c r="G354" s="59" t="s">
         <v>555</v>
       </c>
-      <c r="H354" s="63"/>
-      <c r="I354" s="63"/>
-      <c r="J354" s="64" t="s">
+      <c r="H354" s="62"/>
+      <c r="I354" s="62"/>
+      <c r="J354" s="75" t="s">
         <v>810</v>
       </c>
     </row>
@@ -23430,9 +23490,9 @@
       <c r="G355" s="59" t="s">
         <v>555</v>
       </c>
-      <c r="H355" s="63"/>
-      <c r="I355" s="63"/>
-      <c r="J355" s="64" t="s">
+      <c r="H355" s="62"/>
+      <c r="I355" s="62"/>
+      <c r="J355" s="75" t="s">
         <v>811</v>
       </c>
     </row>
@@ -23455,10 +23515,10 @@
       <c r="F356" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G356" s="63"/>
-      <c r="H356" s="63"/>
-      <c r="I356" s="63"/>
-      <c r="J356" s="64" t="s">
+      <c r="G356" s="62"/>
+      <c r="H356" s="62"/>
+      <c r="I356" s="62"/>
+      <c r="J356" s="75" t="s">
         <v>812</v>
       </c>
     </row>
@@ -23475,18 +23535,18 @@
       <c r="D357" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E357" s="64" t="s">
+      <c r="E357" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F357" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G357" s="63"/>
-      <c r="H357" s="63" t="s">
+      <c r="G357" s="62"/>
+      <c r="H357" s="62" t="s">
         <v>609</v>
       </c>
-      <c r="I357" s="63"/>
-      <c r="J357" s="64" t="s">
+      <c r="I357" s="62"/>
+      <c r="J357" s="75" t="s">
         <v>813</v>
       </c>
     </row>
@@ -23509,10 +23569,10 @@
       <c r="F358" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G358" s="63"/>
-      <c r="H358" s="63"/>
-      <c r="I358" s="63"/>
-      <c r="J358" s="64" t="s">
+      <c r="G358" s="62"/>
+      <c r="H358" s="62"/>
+      <c r="I358" s="62"/>
+      <c r="J358" s="75" t="s">
         <v>814</v>
       </c>
     </row>
@@ -23531,10 +23591,10 @@
       </c>
       <c r="E359" s="60"/>
       <c r="F359" s="59"/>
-      <c r="G359" s="63"/>
-      <c r="H359" s="63"/>
-      <c r="I359" s="63"/>
-      <c r="J359" s="64" t="s">
+      <c r="G359" s="62"/>
+      <c r="H359" s="62"/>
+      <c r="I359" s="62"/>
+      <c r="J359" s="75" t="s">
         <v>815</v>
       </c>
     </row>
@@ -23557,10 +23617,10 @@
       <c r="F360" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G360" s="63"/>
-      <c r="H360" s="63"/>
-      <c r="I360" s="63"/>
-      <c r="J360" s="64" t="s">
+      <c r="G360" s="62"/>
+      <c r="H360" s="62"/>
+      <c r="I360" s="62"/>
+      <c r="J360" s="75" t="s">
         <v>816</v>
       </c>
     </row>
@@ -23577,14 +23637,14 @@
       <c r="D361" s="57" t="s">
         <v>436</v>
       </c>
-      <c r="E361" s="63"/>
+      <c r="E361" s="62"/>
       <c r="F361" s="58"/>
-      <c r="G361" s="63"/>
-      <c r="H361" s="63"/>
+      <c r="G361" s="62"/>
+      <c r="H361" s="62"/>
       <c r="I361" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J361" s="64" t="s">
+      <c r="J361" s="75" t="s">
         <v>817</v>
       </c>
     </row>
@@ -23601,16 +23661,16 @@
       <c r="D362" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E362" s="64" t="s">
+      <c r="E362" s="63" t="s">
         <v>61</v>
       </c>
       <c r="F362" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G362" s="63"/>
-      <c r="H362" s="63"/>
-      <c r="I362" s="63"/>
-      <c r="J362" s="64" t="s">
+      <c r="G362" s="62"/>
+      <c r="H362" s="62"/>
+      <c r="I362" s="62"/>
+      <c r="J362" s="75" t="s">
         <v>818</v>
       </c>
     </row>
@@ -23633,10 +23693,10 @@
       <c r="F363" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G363" s="63"/>
-      <c r="H363" s="63"/>
-      <c r="I363" s="63"/>
-      <c r="J363" s="64" t="s">
+      <c r="G363" s="62"/>
+      <c r="H363" s="62"/>
+      <c r="I363" s="62"/>
+      <c r="J363" s="75" t="s">
         <v>819</v>
       </c>
     </row>
@@ -23653,16 +23713,16 @@
       <c r="D364" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E364" s="64" t="s">
+      <c r="E364" s="63" t="s">
         <v>61</v>
       </c>
       <c r="F364" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G364" s="63"/>
-      <c r="H364" s="63"/>
-      <c r="I364" s="63"/>
-      <c r="J364" s="64" t="s">
+      <c r="G364" s="62"/>
+      <c r="H364" s="62"/>
+      <c r="I364" s="62"/>
+      <c r="J364" s="75" t="s">
         <v>820</v>
       </c>
     </row>
@@ -23685,10 +23745,10 @@
       <c r="F365" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G365" s="63"/>
-      <c r="H365" s="63"/>
-      <c r="I365" s="63"/>
-      <c r="J365" s="64" t="s">
+      <c r="G365" s="62"/>
+      <c r="H365" s="62"/>
+      <c r="I365" s="62"/>
+      <c r="J365" s="75" t="s">
         <v>821</v>
       </c>
     </row>
@@ -23705,16 +23765,16 @@
       <c r="D366" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E366" s="64" t="s">
+      <c r="E366" s="63" t="s">
         <v>61</v>
       </c>
       <c r="F366" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="G366" s="63"/>
-      <c r="H366" s="63"/>
-      <c r="I366" s="63"/>
-      <c r="J366" s="64" t="s">
+      <c r="G366" s="62"/>
+      <c r="H366" s="62"/>
+      <c r="I366" s="62"/>
+      <c r="J366" s="75" t="s">
         <v>822</v>
       </c>
     </row>
@@ -23742,7 +23802,7 @@
       <c r="I367" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J367" s="57" t="s">
+      <c r="J367" s="74" t="s">
         <v>527</v>
       </c>
     </row>
@@ -23772,7 +23832,7 @@
       <c r="I368" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J368" s="61" t="s">
+      <c r="J368" s="73" t="s">
         <v>823</v>
       </c>
     </row>
@@ -23798,7 +23858,7 @@
       <c r="G369" s="58"/>
       <c r="H369" s="59"/>
       <c r="I369" s="58"/>
-      <c r="J369" s="61" t="s">
+      <c r="J369" s="73" t="s">
         <v>824</v>
       </c>
     </row>
@@ -23826,7 +23886,7 @@
       </c>
       <c r="H370" s="59"/>
       <c r="I370" s="58"/>
-      <c r="J370" s="57" t="s">
+      <c r="J370" s="74" t="s">
         <v>825</v>
       </c>
     </row>
@@ -23854,7 +23914,7 @@
       <c r="I371" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J371" s="61" t="s">
+      <c r="J371" s="73" t="s">
         <v>826</v>
       </c>
     </row>
@@ -23882,7 +23942,7 @@
       </c>
       <c r="H372" s="59"/>
       <c r="I372" s="58"/>
-      <c r="J372" s="57" t="s">
+      <c r="J372" s="74" t="s">
         <v>827</v>
       </c>
     </row>
@@ -23908,7 +23968,7 @@
       <c r="G373" s="58"/>
       <c r="H373" s="59"/>
       <c r="I373" s="58"/>
-      <c r="J373" s="57" t="s">
+      <c r="J373" s="74" t="s">
         <v>780</v>
       </c>
     </row>
@@ -23936,7 +23996,7 @@
       </c>
       <c r="H374" s="58"/>
       <c r="I374" s="58"/>
-      <c r="J374" s="57" t="s">
+      <c r="J374" s="74" t="s">
         <v>828</v>
       </c>
     </row>
@@ -23962,7 +24022,7 @@
       <c r="G375" s="58"/>
       <c r="H375" s="58"/>
       <c r="I375" s="58"/>
-      <c r="J375" s="57" t="s">
+      <c r="J375" s="74" t="s">
         <v>829</v>
       </c>
     </row>
@@ -23988,11 +24048,11 @@
       <c r="G376" s="58" t="s">
         <v>558</v>
       </c>
-      <c r="H376" s="63" t="s">
+      <c r="H376" s="62" t="s">
         <v>609</v>
       </c>
-      <c r="I376" s="63"/>
-      <c r="J376" s="76" t="s">
+      <c r="I376" s="62"/>
+      <c r="J376" s="87" t="s">
         <v>830</v>
       </c>
     </row>
@@ -24012,9 +24072,9 @@
       <c r="E377" s="57"/>
       <c r="F377" s="58"/>
       <c r="G377" s="58"/>
-      <c r="H377" s="63"/>
-      <c r="I377" s="63"/>
-      <c r="J377" s="64" t="s">
+      <c r="H377" s="62"/>
+      <c r="I377" s="62"/>
+      <c r="J377" s="75" t="s">
         <v>831</v>
       </c>
     </row>
@@ -24031,16 +24091,16 @@
       <c r="D378" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E378" s="63" t="s">
+      <c r="E378" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F378" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G378" s="63"/>
-      <c r="H378" s="63"/>
-      <c r="I378" s="63"/>
-      <c r="J378" s="63" t="s">
+      <c r="G378" s="62"/>
+      <c r="H378" s="62"/>
+      <c r="I378" s="62"/>
+      <c r="J378" s="77" t="s">
         <v>832</v>
       </c>
     </row>
@@ -24063,10 +24123,10 @@
       <c r="F379" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="G379" s="63"/>
-      <c r="H379" s="63"/>
-      <c r="I379" s="63"/>
-      <c r="J379" s="63" t="s">
+      <c r="G379" s="62"/>
+      <c r="H379" s="62"/>
+      <c r="I379" s="62"/>
+      <c r="J379" s="77" t="s">
         <v>780</v>
       </c>
     </row>
@@ -24083,16 +24143,16 @@
       <c r="D380" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E380" s="63" t="s">
+      <c r="E380" s="62" t="s">
         <v>25</v>
       </c>
       <c r="F380" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G380" s="63"/>
-      <c r="H380" s="63"/>
-      <c r="I380" s="63"/>
-      <c r="J380" s="63" t="s">
+      <c r="G380" s="62"/>
+      <c r="H380" s="62"/>
+      <c r="I380" s="62"/>
+      <c r="J380" s="77" t="s">
         <v>833</v>
       </c>
     </row>
@@ -24109,16 +24169,16 @@
       <c r="D381" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E381" s="63" t="s">
+      <c r="E381" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F381" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="G381" s="63"/>
-      <c r="H381" s="63"/>
-      <c r="I381" s="63"/>
-      <c r="J381" s="63" t="s">
+      <c r="G381" s="62"/>
+      <c r="H381" s="62"/>
+      <c r="I381" s="62"/>
+      <c r="J381" s="77" t="s">
         <v>834</v>
       </c>
     </row>
@@ -24135,16 +24195,16 @@
       <c r="D382" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="E382" s="63" t="s">
+      <c r="E382" s="62" t="s">
         <v>25</v>
       </c>
       <c r="F382" s="58" t="s">
         <v>445</v>
       </c>
-      <c r="G382" s="63"/>
-      <c r="H382" s="63"/>
-      <c r="I382" s="63"/>
-      <c r="J382" s="63" t="s">
+      <c r="G382" s="62"/>
+      <c r="H382" s="62"/>
+      <c r="I382" s="62"/>
+      <c r="J382" s="77" t="s">
         <v>735</v>
       </c>
     </row>
@@ -24172,7 +24232,7 @@
       <c r="I383" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J383" s="57" t="s">
+      <c r="J383" s="74" t="s">
         <v>835</v>
       </c>
     </row>
@@ -24200,7 +24260,7 @@
       <c r="I384" s="58" t="s">
         <v>437</v>
       </c>
-      <c r="J384" s="60" t="s">
+      <c r="J384" s="72" t="s">
         <v>836</v>
       </c>
     </row>
@@ -24226,7 +24286,7 @@
       <c r="G385" s="58"/>
       <c r="H385" s="59"/>
       <c r="I385" s="58"/>
-      <c r="J385" s="60" t="s">
+      <c r="J385" s="72" t="s">
         <v>837</v>
       </c>
     </row>
@@ -24256,7 +24316,7 @@
       <c r="I386" s="58" t="s">
         <v>838</v>
       </c>
-      <c r="J386" s="60" t="s">
+      <c r="J386" s="72" t="s">
         <v>650</v>
       </c>
     </row>
@@ -24284,7 +24344,7 @@
       </c>
       <c r="H387" s="59"/>
       <c r="I387" s="58"/>
-      <c r="J387" s="60" t="s">
+      <c r="J387" s="72" t="s">
         <v>839</v>
       </c>
     </row>
@@ -24310,7 +24370,7 @@
       <c r="G388" s="58"/>
       <c r="H388" s="58"/>
       <c r="I388" s="58"/>
-      <c r="J388" s="60" t="s">
+      <c r="J388" s="72" t="s">
         <v>840</v>
       </c>
     </row>
@@ -24338,7 +24398,7 @@
       <c r="I389" s="58" t="s">
         <v>838</v>
       </c>
-      <c r="J389" s="61" t="s">
+      <c r="J389" s="73" t="s">
         <v>841</v>
       </c>
     </row>
@@ -24364,7 +24424,7 @@
       <c r="G390" s="58"/>
       <c r="H390" s="59"/>
       <c r="I390" s="58"/>
-      <c r="J390" s="57" t="s">
+      <c r="J390" s="74" t="s">
         <v>842</v>
       </c>
     </row>
@@ -24390,7 +24450,7 @@
       <c r="G391" s="58"/>
       <c r="H391" s="59"/>
       <c r="I391" s="58"/>
-      <c r="J391" s="57" t="s">
+      <c r="J391" s="74" t="s">
         <v>843</v>
       </c>
     </row>
@@ -24416,7 +24476,7 @@
       <c r="G392" s="58"/>
       <c r="H392" s="58"/>
       <c r="I392" s="58"/>
-      <c r="J392" s="61" t="s">
+      <c r="J392" s="73" t="s">
         <v>844</v>
       </c>
     </row>
@@ -24442,7 +24502,7 @@
       <c r="G393" s="58"/>
       <c r="H393" s="58"/>
       <c r="I393" s="58"/>
-      <c r="J393" s="57" t="s">
+      <c r="J393" s="74" t="s">
         <v>845</v>
       </c>
     </row>
@@ -24470,7 +24530,7 @@
       <c r="I394" s="58" t="s">
         <v>838</v>
       </c>
-      <c r="J394" s="57" t="s">
+      <c r="J394" s="74" t="s">
         <v>846</v>
       </c>
     </row>
@@ -24483,7 +24543,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="37" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.25" style="3" customWidth="1"/>
@@ -25665,7 +25725,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.5" style="32" customWidth="1"/>
@@ -26344,7 +26404,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E114"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="25.5" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.125" style="3" customWidth="1"/>
@@ -27264,7 +27324,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G357"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="14.375" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="4" customWidth="1"/>
@@ -35476,7 +35536,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L129"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="16.25" style="7" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="7" customWidth="1"/>
@@ -40249,7 +40309,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="45.625" customWidth="1"/>
     <col min="2" max="2" width="23.5" customWidth="1"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -161,17 +161,17 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="BIZ UDGothic"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="BIZ UDGothic"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -485,7 +485,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -498,6 +497,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2408,8 +2408,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="74"/>
-    <col width="9.125" customWidth="1" style="23" min="75" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="75"/>
+    <col width="9.125" customWidth="1" style="23" min="76" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5552,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T59"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="7.5" bestFit="1" customWidth="1" style="53" min="1" max="1"/>
@@ -5569,8 +5569,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="53" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="53" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="53" min="20" max="20"/>
-    <col width="9" customWidth="1" style="54" min="21" max="24"/>
-    <col width="9" customWidth="1" style="54" min="25" max="16384"/>
+    <col width="9" customWidth="1" style="54" min="21" max="25"/>
+    <col width="9" customWidth="1" style="54" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="53">
@@ -5676,2892 +5676,2938 @@
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>000_01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>完书</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr"/>
+      <c r="F2" s="55" t="inlineStr"/>
+      <c r="G2" s="55" t="inlineStr">
         <is>
           <t>gte</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="55" t="n">
         <v>107</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="55" t="inlineStr"/>
+      <c r="J2" s="55" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="K2" s="55" t="inlineStr"/>
+      <c r="L2" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="b">
+      <c r="M2" s="55" t="inlineStr"/>
+      <c r="N2" s="55" t="inlineStr"/>
+      <c r="O2" s="55" t="inlineStr"/>
+      <c r="P2" s="55" t="inlineStr"/>
+      <c r="Q2" s="55" t="inlineStr"/>
+      <c r="R2" s="55" t="inlineStr"/>
+      <c r="S2" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="55" t="inlineStr">
         <is>
           <t>000_02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="55" t="inlineStr">
         <is>
           <t>书商来访</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="D3" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="55" t="inlineStr"/>
+      <c r="F3" s="55" t="inlineStr"/>
+      <c r="G3" s="55" t="inlineStr"/>
+      <c r="H3" s="55" t="inlineStr"/>
+      <c r="I3" s="55" t="inlineStr"/>
+      <c r="J3" s="55" t="inlineStr">
         <is>
           <t>000_01</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K3" s="55" t="inlineStr"/>
+      <c r="L3" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="b">
+      <c r="M3" s="55" t="inlineStr"/>
+      <c r="N3" s="55" t="inlineStr"/>
+      <c r="O3" s="55" t="inlineStr"/>
+      <c r="P3" s="55" t="inlineStr"/>
+      <c r="Q3" s="55" t="inlineStr"/>
+      <c r="R3" s="55" t="inlineStr"/>
+      <c r="S3" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>000_03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>如何出书</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="D4" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="55" t="inlineStr"/>
+      <c r="F4" s="55" t="inlineStr"/>
+      <c r="G4" s="55" t="inlineStr"/>
+      <c r="H4" s="55" t="inlineStr"/>
+      <c r="I4" s="55" t="inlineStr"/>
+      <c r="J4" s="55" t="inlineStr">
         <is>
           <t>000_02</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" s="55" t="inlineStr"/>
+      <c r="L4" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="b">
+      <c r="M4" s="55" t="inlineStr"/>
+      <c r="N4" s="55" t="inlineStr"/>
+      <c r="O4" s="55" t="inlineStr"/>
+      <c r="P4" s="55" t="inlineStr"/>
+      <c r="Q4" s="55" t="inlineStr"/>
+      <c r="R4" s="55" t="inlineStr"/>
+      <c r="S4" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>000_04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>好消息</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="D5" s="55" t="inlineStr"/>
+      <c r="E5" s="55" t="inlineStr"/>
+      <c r="F5" s="55" t="inlineStr"/>
+      <c r="G5" s="55" t="inlineStr"/>
+      <c r="H5" s="55" t="inlineStr"/>
+      <c r="I5" s="55" t="inlineStr"/>
+      <c r="J5" s="55" t="inlineStr">
         <is>
           <t>000_03</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="55" t="inlineStr"/>
+      <c r="L5" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="b">
+      <c r="M5" s="55" t="inlineStr"/>
+      <c r="N5" s="55" t="inlineStr"/>
+      <c r="O5" s="55" t="inlineStr"/>
+      <c r="P5" s="55" t="inlineStr"/>
+      <c r="Q5" s="55" t="inlineStr"/>
+      <c r="R5" s="55" t="inlineStr"/>
+      <c r="S5" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T5" t="inlineStr"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>000_05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>结局</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr"/>
+      <c r="E6" s="55" t="inlineStr">
         <is>
           <t>gte</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="G6" s="55" t="inlineStr"/>
+      <c r="H6" s="55" t="inlineStr"/>
+      <c r="I6" s="55" t="inlineStr"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>000_04</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" s="55" t="inlineStr"/>
+      <c r="L6" s="55" t="inlineStr">
         <is>
           <t>endgame</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="b">
+      <c r="M6" s="55" t="inlineStr"/>
+      <c r="N6" s="55" t="inlineStr"/>
+      <c r="O6" s="55" t="inlineStr"/>
+      <c r="P6" s="55" t="inlineStr"/>
+      <c r="Q6" s="55" t="inlineStr"/>
+      <c r="R6" s="55" t="inlineStr"/>
+      <c r="S6" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>000_06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>金钱过低</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr"/>
+      <c r="E7" s="55" t="inlineStr">
         <is>
           <t>lte</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="G7" s="55" t="inlineStr"/>
+      <c r="H7" s="55" t="inlineStr"/>
+      <c r="I7" s="55" t="inlineStr"/>
+      <c r="J7" s="55" t="inlineStr"/>
+      <c r="K7" s="55" t="inlineStr"/>
+      <c r="L7" s="55" t="inlineStr">
         <is>
           <t>gameover</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="b">
+      <c r="M7" s="55" t="inlineStr"/>
+      <c r="N7" s="55" t="inlineStr"/>
+      <c r="O7" s="55" t="inlineStr"/>
+      <c r="P7" s="55" t="inlineStr"/>
+      <c r="Q7" s="55" t="inlineStr"/>
+      <c r="R7" s="55" t="inlineStr"/>
+      <c r="S7" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>000_07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>名望过低</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr"/>
+      <c r="E8" s="55" t="inlineStr"/>
+      <c r="F8" s="55" t="inlineStr"/>
+      <c r="G8" s="55" t="inlineStr">
         <is>
           <t>lte</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="55" t="n">
         <v>-200</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="I8" s="55" t="inlineStr"/>
+      <c r="J8" s="55" t="inlineStr"/>
+      <c r="K8" s="55" t="inlineStr"/>
+      <c r="L8" s="55" t="inlineStr">
         <is>
           <t>gameover</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="b">
+      <c r="M8" s="55" t="inlineStr"/>
+      <c r="N8" s="55" t="inlineStr"/>
+      <c r="O8" s="55" t="inlineStr"/>
+      <c r="P8" s="55" t="inlineStr"/>
+      <c r="Q8" s="55" t="inlineStr"/>
+      <c r="R8" s="55" t="inlineStr"/>
+      <c r="S8" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>000_08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>时间过长</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="55" t="n">
         <v>240</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="E9" s="55" t="inlineStr"/>
+      <c r="F9" s="55" t="inlineStr"/>
+      <c r="G9" s="55" t="inlineStr"/>
+      <c r="H9" s="55" t="inlineStr"/>
+      <c r="I9" s="55" t="inlineStr"/>
+      <c r="J9" s="55" t="inlineStr"/>
+      <c r="K9" s="55" t="inlineStr"/>
+      <c r="L9" s="55" t="inlineStr">
         <is>
           <t>gameover</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="b">
+      <c r="M9" s="55" t="inlineStr"/>
+      <c r="N9" s="55" t="inlineStr"/>
+      <c r="O9" s="55" t="inlineStr"/>
+      <c r="P9" s="55" t="inlineStr"/>
+      <c r="Q9" s="55" t="inlineStr"/>
+      <c r="R9" s="55" t="inlineStr"/>
+      <c r="S9" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T9" t="inlineStr"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>落榜</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="D10" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="55" t="inlineStr"/>
+      <c r="F10" s="55" t="inlineStr"/>
+      <c r="G10" s="55" t="inlineStr"/>
+      <c r="H10" s="55" t="inlineStr"/>
+      <c r="I10" s="55" t="inlineStr"/>
+      <c r="J10" s="55" t="inlineStr"/>
+      <c r="K10" s="55" t="inlineStr"/>
+      <c r="L10" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="b">
+      <c r="M10" s="55" t="inlineStr"/>
+      <c r="N10" s="55" t="inlineStr"/>
+      <c r="O10" s="55" t="inlineStr"/>
+      <c r="P10" s="55" t="inlineStr"/>
+      <c r="Q10" s="55" t="inlineStr"/>
+      <c r="R10" s="55" t="inlineStr"/>
+      <c r="S10" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T10" t="inlineStr"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>初学医术</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="D11" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="55" t="inlineStr"/>
+      <c r="F11" s="55" t="inlineStr"/>
+      <c r="G11" s="55" t="inlineStr"/>
+      <c r="H11" s="55" t="inlineStr"/>
+      <c r="I11" s="55" t="inlineStr"/>
+      <c r="J11" s="55" t="inlineStr"/>
+      <c r="K11" s="55" t="inlineStr"/>
+      <c r="L11" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="b">
+      <c r="M11" s="55" t="inlineStr"/>
+      <c r="N11" s="55" t="inlineStr"/>
+      <c r="O11" s="55" t="inlineStr"/>
+      <c r="P11" s="55" t="inlineStr"/>
+      <c r="Q11" s="55" t="inlineStr"/>
+      <c r="R11" s="55" t="inlineStr"/>
+      <c r="S11" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T11" t="inlineStr"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>第一次行医</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="E12" s="55" t="inlineStr"/>
+      <c r="F12" s="55" t="inlineStr"/>
+      <c r="G12" s="55" t="inlineStr"/>
+      <c r="H12" s="55" t="inlineStr"/>
+      <c r="I12" s="55" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="b">
+      <c r="M12" s="55" t="inlineStr"/>
+      <c r="N12" s="55" t="inlineStr"/>
+      <c r="O12" s="55" t="inlineStr"/>
+      <c r="P12" s="55" t="inlineStr"/>
+      <c r="Q12" s="55" t="inlineStr"/>
+      <c r="R12" s="55" t="inlineStr"/>
+      <c r="S12" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T12" t="inlineStr"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>004_01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>老师心阳虚</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="E13" s="55" t="inlineStr"/>
+      <c r="F13" s="55" t="inlineStr"/>
+      <c r="G13" s="55" t="inlineStr"/>
+      <c r="H13" s="55" t="inlineStr"/>
+      <c r="I13" s="55" t="inlineStr"/>
+      <c r="J13" s="55" t="inlineStr"/>
+      <c r="K13" s="55" t="inlineStr"/>
+      <c r="L13" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="55" t="inlineStr">
         <is>
           <t>gu_wen</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="55" t="inlineStr">
         <is>
           <t>心阳虚</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="b">
+      <c r="P13" s="55" t="inlineStr"/>
+      <c r="Q13" s="55" t="inlineStr"/>
+      <c r="R13" s="55" t="inlineStr"/>
+      <c r="S13" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T13" t="inlineStr"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>004_02</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>004治疗成功</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr"/>
+      <c r="E14" s="55" t="inlineStr"/>
+      <c r="F14" s="55" t="inlineStr"/>
+      <c r="G14" s="55" t="inlineStr"/>
+      <c r="H14" s="55" t="inlineStr"/>
+      <c r="I14" s="55" t="inlineStr"/>
+      <c r="J14" s="55" t="inlineStr">
         <is>
           <t>004_01</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
+      <c r="M14" s="55" t="inlineStr"/>
+      <c r="N14" s="55" t="inlineStr"/>
+      <c r="O14" s="55" t="inlineStr"/>
+      <c r="P14" s="55" t="inlineStr"/>
+      <c r="Q14" s="55" t="inlineStr"/>
+      <c r="R14" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="S14" t="b">
+      <c r="S14" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>004_03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>004治疗失败</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="D15" s="55" t="inlineStr"/>
+      <c r="E15" s="55" t="inlineStr"/>
+      <c r="F15" s="55" t="inlineStr"/>
+      <c r="G15" s="55" t="inlineStr"/>
+      <c r="H15" s="55" t="inlineStr"/>
+      <c r="I15" s="55" t="inlineStr"/>
+      <c r="J15" s="55" t="inlineStr">
         <is>
           <t>004_01</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="55" t="inlineStr">
         <is>
           <t>gu_wen</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="55" t="inlineStr">
         <is>
           <t>心阳虚</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="b">
+      <c r="P15" s="55" t="inlineStr"/>
+      <c r="Q15" s="55" t="inlineStr"/>
+      <c r="R15" s="55" t="inlineStr"/>
+      <c r="S15" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>004_04</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>辞别老师</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="E16" s="55" t="inlineStr"/>
+      <c r="F16" s="55" t="inlineStr"/>
+      <c r="G16" s="55" t="inlineStr"/>
+      <c r="H16" s="55" t="inlineStr"/>
+      <c r="I16" s="55" t="inlineStr"/>
+      <c r="J16" s="55" t="inlineStr">
         <is>
           <t>022_02</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" s="55" t="inlineStr"/>
+      <c r="L16" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="M16" s="55" t="inlineStr"/>
+      <c r="N16" s="55" t="inlineStr"/>
+      <c r="O16" s="55" t="inlineStr"/>
+      <c r="P16" s="55" t="inlineStr"/>
+      <c r="Q16" s="55" t="inlineStr"/>
+      <c r="R16" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="S16" t="b">
+      <c r="S16" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="55" t="inlineStr">
         <is>
           <t>005_01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>世子脾虚湿盛</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>night_end</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="D17" s="55" t="inlineStr"/>
+      <c r="E17" s="55" t="inlineStr"/>
+      <c r="F17" s="55" t="inlineStr"/>
+      <c r="G17" s="55" t="inlineStr"/>
+      <c r="H17" s="55" t="inlineStr"/>
+      <c r="I17" s="55" t="inlineStr">
         <is>
           <t>脾虚湿盛</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="J17" s="55" t="inlineStr"/>
+      <c r="K17" s="55" t="inlineStr"/>
+      <c r="L17" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="55" t="inlineStr">
         <is>
           <t>shi_zi</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="55" t="inlineStr">
         <is>
           <t>脾虚湿盛</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_sick.png</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="b">
+      <c r="P17" s="55" t="inlineStr"/>
+      <c r="Q17" s="55" t="inlineStr"/>
+      <c r="R17" s="55" t="inlineStr"/>
+      <c r="S17" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>005_02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>005治疗成功</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr"/>
+      <c r="D18" s="55" t="inlineStr"/>
+      <c r="E18" s="55" t="inlineStr"/>
+      <c r="F18" s="55" t="inlineStr"/>
+      <c r="G18" s="55" t="inlineStr"/>
+      <c r="H18" s="55" t="inlineStr"/>
+      <c r="I18" s="55" t="inlineStr"/>
+      <c r="J18" s="55" t="inlineStr">
         <is>
           <t>005_01</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="M18" s="55" t="inlineStr"/>
+      <c r="N18" s="55" t="inlineStr"/>
+      <c r="O18" s="55" t="inlineStr"/>
+      <c r="P18" s="55" t="inlineStr"/>
+      <c r="Q18" s="55" t="n">
         <v>1000</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="S18" t="b">
+      <c r="S18" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>005_03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>005治疗失败</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr"/>
+      <c r="D19" s="55" t="inlineStr"/>
+      <c r="E19" s="55" t="inlineStr"/>
+      <c r="F19" s="55" t="inlineStr"/>
+      <c r="G19" s="55" t="inlineStr"/>
+      <c r="H19" s="55" t="inlineStr"/>
+      <c r="I19" s="55" t="inlineStr"/>
+      <c r="J19" s="55" t="inlineStr">
         <is>
           <t>005_01</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="55" t="inlineStr">
         <is>
           <t>gameover</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="b">
+      <c r="M19" s="55" t="inlineStr"/>
+      <c r="N19" s="55" t="inlineStr"/>
+      <c r="O19" s="55" t="inlineStr"/>
+      <c r="P19" s="55" t="inlineStr"/>
+      <c r="Q19" s="55" t="inlineStr"/>
+      <c r="R19" s="55" t="inlineStr"/>
+      <c r="S19" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T19" t="inlineStr"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>药商来访</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="D20" s="55" t="inlineStr"/>
+      <c r="E20" s="55" t="inlineStr"/>
+      <c r="F20" s="55" t="inlineStr"/>
+      <c r="G20" s="55" t="inlineStr"/>
+      <c r="H20" s="55" t="inlineStr"/>
+      <c r="I20" s="55" t="inlineStr">
         <is>
           <t>人参</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="J20" s="55" t="inlineStr"/>
+      <c r="K20" s="55" t="inlineStr"/>
+      <c r="L20" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="b">
+      <c r="M20" s="55" t="inlineStr"/>
+      <c r="N20" s="55" t="inlineStr"/>
+      <c r="O20" s="55" t="inlineStr"/>
+      <c r="P20" s="55" t="inlineStr"/>
+      <c r="Q20" s="55" t="inlineStr"/>
+      <c r="R20" s="55" t="inlineStr"/>
+      <c r="S20" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T20" t="inlineStr"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t>007_01</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>雷万钧肝阳上亢</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="D21" s="55" t="inlineStr"/>
+      <c r="E21" s="55" t="inlineStr"/>
+      <c r="F21" s="55" t="inlineStr"/>
+      <c r="G21" s="55" t="inlineStr"/>
+      <c r="H21" s="55" t="inlineStr"/>
+      <c r="I21" s="55" t="inlineStr">
         <is>
           <t>肝阳上亢</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="J21" s="55" t="inlineStr"/>
+      <c r="K21" s="55" t="inlineStr"/>
+      <c r="L21" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="55" t="inlineStr">
         <is>
           <t>lei_wan_jun</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="55" t="inlineStr">
         <is>
           <t>肝阳上亢</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/lei_wan_jun/lei_wan_jun.png</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="b">
+      <c r="P21" s="55" t="inlineStr"/>
+      <c r="Q21" s="55" t="inlineStr"/>
+      <c r="R21" s="55" t="inlineStr"/>
+      <c r="S21" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T21" t="inlineStr"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t>007_02</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>007治疗成功</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="C22" s="55" t="inlineStr"/>
+      <c r="D22" s="55" t="inlineStr"/>
+      <c r="E22" s="55" t="inlineStr"/>
+      <c r="F22" s="55" t="inlineStr"/>
+      <c r="G22" s="55" t="inlineStr"/>
+      <c r="H22" s="55" t="inlineStr"/>
+      <c r="I22" s="55" t="inlineStr"/>
+      <c r="J22" s="55" t="inlineStr">
         <is>
           <t>007_01</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="b">
+      <c r="M22" s="55" t="inlineStr"/>
+      <c r="N22" s="55" t="inlineStr"/>
+      <c r="O22" s="55" t="inlineStr"/>
+      <c r="P22" s="55" t="inlineStr"/>
+      <c r="Q22" s="55" t="inlineStr"/>
+      <c r="R22" s="55" t="inlineStr"/>
+      <c r="S22" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>007_03</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>007治疗失败</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr"/>
+      <c r="D23" s="55" t="inlineStr"/>
+      <c r="E23" s="55" t="inlineStr"/>
+      <c r="F23" s="55" t="inlineStr"/>
+      <c r="G23" s="55" t="inlineStr"/>
+      <c r="H23" s="55" t="inlineStr"/>
+      <c r="I23" s="55" t="inlineStr"/>
+      <c r="J23" s="55" t="inlineStr">
         <is>
           <t>007_01</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="55" t="inlineStr">
         <is>
           <t>lei_wan_jun</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="55" t="inlineStr">
         <is>
           <t>肝阳上亢</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/lei_wan_jun/lei_wan_jun.png</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="b">
+      <c r="P23" s="55" t="inlineStr"/>
+      <c r="Q23" s="55" t="inlineStr"/>
+      <c r="R23" s="55" t="inlineStr"/>
+      <c r="S23" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>008_01</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>贾荃痰火扰心</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr"/>
+      <c r="E24" s="55" t="inlineStr"/>
+      <c r="F24" s="55" t="inlineStr"/>
+      <c r="G24" s="55" t="inlineStr"/>
+      <c r="H24" s="55" t="inlineStr"/>
+      <c r="I24" s="55" t="inlineStr">
         <is>
           <t>痰火扰心</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="55" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K24" s="55" t="inlineStr"/>
+      <c r="L24" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="55" t="inlineStr">
         <is>
           <t>jia_quan</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="55" t="inlineStr">
         <is>
           <t>痰火扰心</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/jia_quan/jia_quan_sick.png</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="b">
+      <c r="P24" s="55" t="inlineStr"/>
+      <c r="Q24" s="55" t="inlineStr"/>
+      <c r="R24" s="55" t="inlineStr"/>
+      <c r="S24" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T24" t="inlineStr"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>008_02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="55" t="inlineStr">
         <is>
           <t>008治疗成功</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="C25" s="55" t="inlineStr"/>
+      <c r="D25" s="55" t="inlineStr"/>
+      <c r="E25" s="55" t="inlineStr"/>
+      <c r="F25" s="55" t="inlineStr"/>
+      <c r="G25" s="55" t="inlineStr"/>
+      <c r="H25" s="55" t="inlineStr"/>
+      <c r="I25" s="55" t="inlineStr"/>
+      <c r="J25" s="55" t="inlineStr">
         <is>
           <t>008_01</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="b">
+      <c r="M25" s="55" t="inlineStr"/>
+      <c r="N25" s="55" t="inlineStr"/>
+      <c r="O25" s="55" t="inlineStr"/>
+      <c r="P25" s="55" t="inlineStr"/>
+      <c r="Q25" s="55" t="inlineStr"/>
+      <c r="R25" s="55" t="inlineStr"/>
+      <c r="S25" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T25" t="inlineStr"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>008_03</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t>008治疗失败</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="C26" s="55" t="inlineStr"/>
+      <c r="D26" s="55" t="inlineStr"/>
+      <c r="E26" s="55" t="inlineStr"/>
+      <c r="F26" s="55" t="inlineStr"/>
+      <c r="G26" s="55" t="inlineStr"/>
+      <c r="H26" s="55" t="inlineStr"/>
+      <c r="I26" s="55" t="inlineStr"/>
+      <c r="J26" s="55" t="inlineStr">
         <is>
           <t>008_01</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="55" t="inlineStr">
         <is>
           <t>jia_quan</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="55" t="inlineStr">
         <is>
           <t>痰火扰心</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/jia_quan/jia_quan_sick.png</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="b">
+      <c r="P26" s="55" t="inlineStr"/>
+      <c r="Q26" s="55" t="inlineStr"/>
+      <c r="R26" s="55" t="inlineStr"/>
+      <c r="S26" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="55" t="inlineStr">
         <is>
           <t>知州有请</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="55" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="E27" s="55" t="inlineStr"/>
+      <c r="F27" s="55" t="inlineStr"/>
+      <c r="G27" s="55" t="inlineStr"/>
+      <c r="H27" s="55" t="inlineStr"/>
+      <c r="I27" s="55" t="inlineStr">
         <is>
           <t>鸡子黄</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="55" t="inlineStr">
         <is>
           <t>008_02</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K27" s="55" t="inlineStr"/>
+      <c r="L27" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="b">
+      <c r="M27" s="55" t="inlineStr"/>
+      <c r="N27" s="55" t="inlineStr"/>
+      <c r="O27" s="55" t="inlineStr"/>
+      <c r="P27" s="55" t="inlineStr"/>
+      <c r="Q27" s="55" t="inlineStr"/>
+      <c r="R27" s="55" t="inlineStr"/>
+      <c r="S27" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T27" t="inlineStr"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>药材到货</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="D28" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="55" t="inlineStr"/>
+      <c r="F28" s="55" t="inlineStr"/>
+      <c r="G28" s="55" t="inlineStr"/>
+      <c r="H28" s="55" t="inlineStr"/>
+      <c r="I28" s="55" t="inlineStr"/>
+      <c r="J28" s="55" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K28" s="55" t="inlineStr"/>
+      <c r="L28" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="b">
+      <c r="M28" s="55" t="inlineStr"/>
+      <c r="N28" s="55" t="inlineStr"/>
+      <c r="O28" s="55" t="inlineStr"/>
+      <c r="P28" s="55" t="inlineStr"/>
+      <c r="Q28" s="55" t="inlineStr"/>
+      <c r="R28" s="55" t="inlineStr"/>
+      <c r="S28" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T28" t="inlineStr"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="55" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>药材有假</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="D29" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="55" t="inlineStr"/>
+      <c r="F29" s="55" t="inlineStr"/>
+      <c r="G29" s="55" t="inlineStr"/>
+      <c r="H29" s="55" t="inlineStr"/>
+      <c r="I29" s="55" t="inlineStr"/>
+      <c r="J29" s="55" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K29" s="55" t="inlineStr"/>
+      <c r="L29" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="b">
+      <c r="M29" s="55" t="inlineStr"/>
+      <c r="N29" s="55" t="inlineStr"/>
+      <c r="O29" s="55" t="inlineStr"/>
+      <c r="P29" s="55" t="inlineStr"/>
+      <c r="Q29" s="55" t="inlineStr"/>
+      <c r="R29" s="55" t="inlineStr"/>
+      <c r="S29" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T29" t="inlineStr"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="55" t="inlineStr">
         <is>
           <t>012</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>孙大夫被抓</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="D30" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="55" t="inlineStr"/>
+      <c r="F30" s="55" t="inlineStr"/>
+      <c r="G30" s="55" t="inlineStr"/>
+      <c r="H30" s="55" t="inlineStr"/>
+      <c r="I30" s="55" t="inlineStr"/>
+      <c r="J30" s="55" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="K30" s="55" t="inlineStr"/>
+      <c r="L30" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="b">
+      <c r="M30" s="55" t="inlineStr"/>
+      <c r="N30" s="55" t="inlineStr"/>
+      <c r="O30" s="55" t="inlineStr"/>
+      <c r="P30" s="55" t="inlineStr"/>
+      <c r="Q30" s="55" t="inlineStr"/>
+      <c r="R30" s="55" t="inlineStr"/>
+      <c r="S30" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T30" t="inlineStr"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="55" t="inlineStr">
         <is>
           <t>013</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>雷万钧来访</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="D31" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="55" t="inlineStr"/>
+      <c r="F31" s="55" t="inlineStr"/>
+      <c r="G31" s="55" t="inlineStr"/>
+      <c r="H31" s="55" t="inlineStr"/>
+      <c r="I31" s="55" t="inlineStr"/>
+      <c r="J31" s="55" t="inlineStr">
         <is>
           <t>012</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="K31" s="55" t="inlineStr"/>
+      <c r="L31" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="b">
+      <c r="M31" s="55" t="inlineStr"/>
+      <c r="N31" s="55" t="inlineStr"/>
+      <c r="O31" s="55" t="inlineStr"/>
+      <c r="P31" s="55" t="inlineStr"/>
+      <c r="Q31" s="55" t="inlineStr"/>
+      <c r="R31" s="55" t="inlineStr"/>
+      <c r="S31" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T31" t="inlineStr"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>014_01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>沈修文心脾两虚</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="D32" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="55" t="inlineStr"/>
+      <c r="F32" s="55" t="inlineStr"/>
+      <c r="G32" s="55" t="inlineStr"/>
+      <c r="H32" s="55" t="inlineStr"/>
+      <c r="I32" s="55" t="inlineStr">
         <is>
           <t>心脾两虚</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="55" t="inlineStr">
         <is>
           <t>013</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K32" s="55" t="inlineStr"/>
+      <c r="L32" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="55" t="inlineStr">
         <is>
           <t>shen_xiu_wen</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="55" t="inlineStr">
         <is>
           <t>心脾两虚</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/shen_xiu_wen/shen_xiu_wen.png</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="b">
+      <c r="P32" s="55" t="inlineStr"/>
+      <c r="Q32" s="55" t="inlineStr"/>
+      <c r="R32" s="55" t="inlineStr"/>
+      <c r="S32" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T32" t="inlineStr"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="55" t="inlineStr">
         <is>
           <t>014_02</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>015治疗成功</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="C33" s="55" t="inlineStr"/>
+      <c r="D33" s="55" t="inlineStr"/>
+      <c r="E33" s="55" t="inlineStr"/>
+      <c r="F33" s="55" t="inlineStr"/>
+      <c r="G33" s="55" t="inlineStr"/>
+      <c r="H33" s="55" t="inlineStr"/>
+      <c r="I33" s="55" t="inlineStr"/>
+      <c r="J33" s="55" t="inlineStr">
         <is>
           <t>014_01</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="b">
+      <c r="M33" s="55" t="inlineStr"/>
+      <c r="N33" s="55" t="inlineStr"/>
+      <c r="O33" s="55" t="inlineStr"/>
+      <c r="P33" s="55" t="inlineStr"/>
+      <c r="Q33" s="55" t="inlineStr"/>
+      <c r="R33" s="55" t="inlineStr"/>
+      <c r="S33" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T33" t="inlineStr"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="55" t="inlineStr">
         <is>
           <t>014_03</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t>015治疗失败</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="C34" s="55" t="inlineStr"/>
+      <c r="D34" s="55" t="inlineStr"/>
+      <c r="E34" s="55" t="inlineStr"/>
+      <c r="F34" s="55" t="inlineStr"/>
+      <c r="G34" s="55" t="inlineStr"/>
+      <c r="H34" s="55" t="inlineStr"/>
+      <c r="I34" s="55" t="inlineStr"/>
+      <c r="J34" s="55" t="inlineStr">
         <is>
           <t>014_01</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="55" t="inlineStr">
         <is>
           <t>shen_xiu_wen</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="55" t="inlineStr">
         <is>
           <t>心脾两虚</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/shen_xiu_wen/shen_xiu_wen.png</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="b">
+      <c r="P34" s="55" t="inlineStr"/>
+      <c r="Q34" s="55" t="inlineStr"/>
+      <c r="R34" s="55" t="inlineStr"/>
+      <c r="S34" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>雷万钧归来</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="D35" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="55" t="inlineStr"/>
+      <c r="F35" s="55" t="inlineStr"/>
+      <c r="G35" s="55" t="inlineStr"/>
+      <c r="H35" s="55" t="inlineStr"/>
+      <c r="I35" s="55" t="inlineStr"/>
+      <c r="J35" s="55" t="inlineStr">
         <is>
           <t>014_02</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K35" s="55" t="inlineStr"/>
+      <c r="L35" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="b">
+      <c r="M35" s="55" t="inlineStr"/>
+      <c r="N35" s="55" t="inlineStr"/>
+      <c r="O35" s="55" t="inlineStr"/>
+      <c r="P35" s="55" t="inlineStr"/>
+      <c r="Q35" s="55" t="inlineStr"/>
+      <c r="R35" s="55" t="inlineStr"/>
+      <c r="S35" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T35" t="inlineStr"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="55" t="inlineStr">
         <is>
           <t>016</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="55" t="inlineStr">
         <is>
           <t>沈修文来访</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="E36" s="55" t="inlineStr"/>
+      <c r="F36" s="55" t="inlineStr"/>
+      <c r="G36" s="55" t="inlineStr"/>
+      <c r="H36" s="55" t="inlineStr"/>
+      <c r="I36" s="55" t="inlineStr"/>
+      <c r="J36" s="55" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K36" s="55" t="inlineStr"/>
+      <c r="L36" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="b">
+      <c r="M36" s="55" t="inlineStr"/>
+      <c r="N36" s="55" t="inlineStr"/>
+      <c r="O36" s="55" t="inlineStr"/>
+      <c r="P36" s="55" t="inlineStr"/>
+      <c r="Q36" s="55" t="inlineStr"/>
+      <c r="R36" s="55" t="inlineStr"/>
+      <c r="S36" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T36" t="inlineStr"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>017_01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>杨善泉肾气不固</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="D37" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="55" t="inlineStr"/>
+      <c r="F37" s="55" t="inlineStr"/>
+      <c r="G37" s="55" t="inlineStr"/>
+      <c r="H37" s="55" t="inlineStr"/>
+      <c r="I37" s="55" t="inlineStr">
         <is>
           <t>肾气不固</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="55" t="inlineStr">
         <is>
           <t>016</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K37" s="55" t="inlineStr"/>
+      <c r="L37" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="55" t="inlineStr">
         <is>
           <t>yang_shan_quan</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="55" t="inlineStr">
         <is>
           <t>肾气不固</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/yang_shan_quan/yang_shan_quan_sick.png</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="b">
+      <c r="P37" s="55" t="inlineStr"/>
+      <c r="Q37" s="55" t="inlineStr"/>
+      <c r="R37" s="55" t="inlineStr"/>
+      <c r="S37" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T37" t="inlineStr"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="55" t="inlineStr">
         <is>
           <t>017_02</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="55" t="inlineStr">
         <is>
           <t>018治疗成功</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="C38" s="55" t="inlineStr"/>
+      <c r="D38" s="55" t="inlineStr"/>
+      <c r="E38" s="55" t="inlineStr"/>
+      <c r="F38" s="55" t="inlineStr"/>
+      <c r="G38" s="55" t="inlineStr"/>
+      <c r="H38" s="55" t="inlineStr"/>
+      <c r="I38" s="55" t="inlineStr"/>
+      <c r="J38" s="55" t="inlineStr">
         <is>
           <t>017_01</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="b">
+      <c r="M38" s="55" t="inlineStr"/>
+      <c r="N38" s="55" t="inlineStr"/>
+      <c r="O38" s="55" t="inlineStr"/>
+      <c r="P38" s="55" t="inlineStr"/>
+      <c r="Q38" s="55" t="inlineStr"/>
+      <c r="R38" s="55" t="inlineStr"/>
+      <c r="S38" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T38" t="inlineStr"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t>017_03</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>018治疗失败</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="C39" s="55" t="inlineStr"/>
+      <c r="D39" s="55" t="inlineStr"/>
+      <c r="E39" s="55" t="inlineStr"/>
+      <c r="F39" s="55" t="inlineStr"/>
+      <c r="G39" s="55" t="inlineStr"/>
+      <c r="H39" s="55" t="inlineStr"/>
+      <c r="I39" s="55" t="inlineStr"/>
+      <c r="J39" s="55" t="inlineStr">
         <is>
           <t>017_01</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="55" t="inlineStr">
         <is>
           <t>yang_shan_quan</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="55" t="inlineStr">
         <is>
           <t>肾气不固</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/yang_shan_quan/yang_shan_quan_sick.png</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="b">
+      <c r="P39" s="55" t="inlineStr"/>
+      <c r="Q39" s="55" t="inlineStr"/>
+      <c r="R39" s="55" t="inlineStr"/>
+      <c r="S39" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T39" t="inlineStr"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="55" t="inlineStr">
         <is>
           <t>018</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>库房失火</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
+      <c r="D40" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="55" t="inlineStr"/>
+      <c r="F40" s="55" t="inlineStr"/>
+      <c r="G40" s="55" t="inlineStr"/>
+      <c r="H40" s="55" t="inlineStr"/>
+      <c r="I40" s="55" t="inlineStr"/>
+      <c r="J40" s="55" t="inlineStr">
         <is>
           <t>017_02</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="K40" s="55" t="inlineStr"/>
+      <c r="L40" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="b">
+      <c r="M40" s="55" t="inlineStr"/>
+      <c r="N40" s="55" t="inlineStr"/>
+      <c r="O40" s="55" t="inlineStr"/>
+      <c r="P40" s="55" t="inlineStr"/>
+      <c r="Q40" s="55" t="inlineStr"/>
+      <c r="R40" s="55" t="inlineStr"/>
+      <c r="S40" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T40" t="inlineStr"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>赵顺来访</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="D41" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="55" t="inlineStr"/>
+      <c r="F41" s="55" t="inlineStr"/>
+      <c r="G41" s="55" t="inlineStr"/>
+      <c r="H41" s="55" t="inlineStr"/>
+      <c r="I41" s="55" t="inlineStr"/>
+      <c r="J41" s="55" t="inlineStr">
         <is>
           <t>018</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="K41" s="55" t="inlineStr"/>
+      <c r="L41" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="b">
+      <c r="M41" s="55" t="inlineStr"/>
+      <c r="N41" s="55" t="inlineStr"/>
+      <c r="O41" s="55" t="inlineStr"/>
+      <c r="P41" s="55" t="inlineStr"/>
+      <c r="Q41" s="55" t="inlineStr"/>
+      <c r="R41" s="55" t="inlineStr"/>
+      <c r="S41" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T41" t="inlineStr"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="55" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>夜晚遇刺</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="55" t="inlineStr">
         <is>
           <t>night_end</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="D42" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="55" t="inlineStr"/>
+      <c r="F42" s="55" t="inlineStr"/>
+      <c r="G42" s="55" t="inlineStr"/>
+      <c r="H42" s="55" t="inlineStr"/>
+      <c r="I42" s="55" t="inlineStr"/>
+      <c r="J42" s="55" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="K42" s="55" t="inlineStr"/>
+      <c r="L42" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="b">
+      <c r="M42" s="55" t="inlineStr"/>
+      <c r="N42" s="55" t="inlineStr"/>
+      <c r="O42" s="55" t="inlineStr"/>
+      <c r="P42" s="55" t="inlineStr"/>
+      <c r="Q42" s="55" t="inlineStr"/>
+      <c r="R42" s="55" t="inlineStr"/>
+      <c r="S42" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T42" t="inlineStr"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="55" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="55" t="inlineStr">
         <is>
           <t>结案</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="E43" s="55" t="inlineStr"/>
+      <c r="F43" s="55" t="inlineStr"/>
+      <c r="G43" s="55" t="inlineStr"/>
+      <c r="H43" s="55" t="inlineStr"/>
+      <c r="I43" s="55" t="inlineStr"/>
+      <c r="J43" s="55" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="K43" s="55" t="inlineStr"/>
+      <c r="L43" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="b">
+      <c r="M43" s="55" t="inlineStr"/>
+      <c r="N43" s="55" t="inlineStr"/>
+      <c r="O43" s="55" t="inlineStr"/>
+      <c r="P43" s="55" t="inlineStr"/>
+      <c r="Q43" s="55" t="inlineStr"/>
+      <c r="R43" s="55" t="inlineStr"/>
+      <c r="S43" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T43" t="inlineStr"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="55" t="inlineStr">
         <is>
           <t>022_01</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="55" t="inlineStr">
         <is>
           <t>柳敬亭温燥证</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
+      <c r="D44" s="55" t="inlineStr"/>
+      <c r="E44" s="55" t="inlineStr"/>
+      <c r="F44" s="55" t="inlineStr"/>
+      <c r="G44" s="55" t="inlineStr"/>
+      <c r="H44" s="55" t="inlineStr"/>
+      <c r="I44" s="55" t="inlineStr">
         <is>
           <t>温燥证</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="J44" s="55" t="inlineStr"/>
+      <c r="K44" s="55" t="inlineStr"/>
+      <c r="L44" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="55" t="inlineStr">
         <is>
           <t>liu_jing_ting</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="55" t="inlineStr">
         <is>
           <t>温燥证</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/liu_jing_ting/liu_jing_ting.png</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="b">
+      <c r="P44" s="55" t="inlineStr"/>
+      <c r="Q44" s="55" t="inlineStr"/>
+      <c r="R44" s="55" t="inlineStr"/>
+      <c r="S44" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T44" t="inlineStr"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>022_02</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>022治疗成功</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr"/>
+      <c r="D45" s="55" t="inlineStr"/>
+      <c r="E45" s="55" t="inlineStr"/>
+      <c r="F45" s="55" t="inlineStr"/>
+      <c r="G45" s="55" t="inlineStr"/>
+      <c r="H45" s="55" t="inlineStr"/>
+      <c r="I45" s="55" t="inlineStr"/>
+      <c r="J45" s="55" t="inlineStr">
         <is>
           <t>022_01</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="b">
+      <c r="M45" s="55" t="inlineStr"/>
+      <c r="N45" s="55" t="inlineStr"/>
+      <c r="O45" s="55" t="inlineStr"/>
+      <c r="P45" s="55" t="inlineStr"/>
+      <c r="Q45" s="55" t="inlineStr"/>
+      <c r="R45" s="55" t="inlineStr"/>
+      <c r="S45" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T45" t="inlineStr"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t>022_03</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="55" t="inlineStr">
         <is>
           <t>022治疗失败</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="C46" s="55" t="inlineStr"/>
+      <c r="D46" s="55" t="inlineStr"/>
+      <c r="E46" s="55" t="inlineStr"/>
+      <c r="F46" s="55" t="inlineStr"/>
+      <c r="G46" s="55" t="inlineStr"/>
+      <c r="H46" s="55" t="inlineStr"/>
+      <c r="I46" s="55" t="inlineStr"/>
+      <c r="J46" s="55" t="inlineStr">
         <is>
           <t>022_01</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="55" t="inlineStr">
         <is>
           <t>liu_jing_ting</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="55" t="inlineStr">
         <is>
           <t>温燥证</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/liu_jing_ting/liu_jing_ting.png</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="b">
+      <c r="P46" s="55" t="inlineStr"/>
+      <c r="Q46" s="55" t="inlineStr"/>
+      <c r="R46" s="55" t="inlineStr"/>
+      <c r="S46" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T46" t="inlineStr"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>谢飞燕肺气虚</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="D47" s="55" t="inlineStr"/>
+      <c r="E47" s="55" t="inlineStr"/>
+      <c r="F47" s="55" t="inlineStr"/>
+      <c r="G47" s="55" t="inlineStr"/>
+      <c r="H47" s="55" t="inlineStr"/>
+      <c r="I47" s="55" t="inlineStr">
         <is>
           <t>肺气虚</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="J47" s="55" t="inlineStr"/>
+      <c r="K47" s="55" t="inlineStr"/>
+      <c r="L47" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="55" t="inlineStr">
         <is>
           <t>xie_fei_yan</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="55" t="inlineStr">
         <is>
           <t>肺气虚</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="b">
+      <c r="P47" s="55" t="inlineStr"/>
+      <c r="Q47" s="55" t="inlineStr"/>
+      <c r="R47" s="55" t="inlineStr"/>
+      <c r="S47" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T47" t="inlineStr"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="55" t="inlineStr">
         <is>
           <t>023_02</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="55" t="inlineStr">
         <is>
           <t>023治疗成功</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="D48" s="55" t="inlineStr"/>
+      <c r="E48" s="55" t="inlineStr"/>
+      <c r="F48" s="55" t="inlineStr"/>
+      <c r="G48" s="55" t="inlineStr"/>
+      <c r="H48" s="55" t="inlineStr"/>
+      <c r="I48" s="55" t="inlineStr"/>
+      <c r="J48" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="b">
+      <c r="M48" s="55" t="inlineStr"/>
+      <c r="N48" s="55" t="inlineStr"/>
+      <c r="O48" s="55" t="inlineStr"/>
+      <c r="P48" s="55" t="inlineStr"/>
+      <c r="Q48" s="55" t="inlineStr"/>
+      <c r="R48" s="55" t="inlineStr"/>
+      <c r="S48" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T48" t="inlineStr"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="55" t="inlineStr">
         <is>
           <t>023_03</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="55" t="inlineStr">
         <is>
           <t>023治疗失败</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
+      <c r="C49" s="55" t="inlineStr"/>
+      <c r="D49" s="55" t="inlineStr"/>
+      <c r="E49" s="55" t="inlineStr"/>
+      <c r="F49" s="55" t="inlineStr"/>
+      <c r="G49" s="55" t="inlineStr"/>
+      <c r="H49" s="55" t="inlineStr"/>
+      <c r="I49" s="55" t="inlineStr"/>
+      <c r="J49" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="55" t="inlineStr">
         <is>
           <t>xie_fei_yan</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="55" t="inlineStr">
         <is>
           <t>肺气虚</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="b">
+      <c r="P49" s="55" t="inlineStr"/>
+      <c r="Q49" s="55" t="inlineStr"/>
+      <c r="R49" s="55" t="inlineStr"/>
+      <c r="S49" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T49" t="inlineStr"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="55" t="inlineStr">
         <is>
           <t>024_01</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>谢飞燕肺阴虚</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="D50" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="55" t="inlineStr"/>
+      <c r="F50" s="55" t="inlineStr"/>
+      <c r="G50" s="55" t="inlineStr"/>
+      <c r="H50" s="55" t="inlineStr"/>
+      <c r="I50" s="55" t="inlineStr">
         <is>
           <t>肺阴虚</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="55" t="inlineStr">
         <is>
           <t>023_02</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="K50" s="55" t="inlineStr"/>
+      <c r="L50" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="55" t="inlineStr">
         <is>
           <t>xie_fei_yan</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="55" t="inlineStr">
         <is>
           <t>肺阴虚</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="b">
+      <c r="P50" s="55" t="inlineStr"/>
+      <c r="Q50" s="55" t="inlineStr"/>
+      <c r="R50" s="55" t="inlineStr"/>
+      <c r="S50" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T50" t="inlineStr"/>
     </row>
     <row r="51" ht="17.65" customHeight="1">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="55" t="inlineStr">
         <is>
           <t>024_02</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t>024治疗成功</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
+      <c r="C51" s="55" t="inlineStr"/>
+      <c r="D51" s="55" t="inlineStr"/>
+      <c r="E51" s="55" t="inlineStr"/>
+      <c r="F51" s="55" t="inlineStr"/>
+      <c r="G51" s="55" t="inlineStr"/>
+      <c r="H51" s="55" t="inlineStr"/>
+      <c r="I51" s="55" t="inlineStr"/>
+      <c r="J51" s="55" t="inlineStr">
         <is>
           <t>024_01</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="b">
+      <c r="M51" s="55" t="inlineStr"/>
+      <c r="N51" s="55" t="inlineStr"/>
+      <c r="O51" s="55" t="inlineStr"/>
+      <c r="P51" s="55" t="inlineStr"/>
+      <c r="Q51" s="55" t="inlineStr"/>
+      <c r="R51" s="55" t="inlineStr"/>
+      <c r="S51" s="55" t="b">
         <v>1</v>
       </c>
       <c r="T51" t="inlineStr"/>
     </row>
     <row r="52" ht="17.65" customHeight="1">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="55" t="inlineStr">
         <is>
           <t>024_03</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t>024治疗失败</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
+      <c r="C52" s="55" t="inlineStr"/>
+      <c r="D52" s="55" t="inlineStr"/>
+      <c r="E52" s="55" t="inlineStr"/>
+      <c r="F52" s="55" t="inlineStr"/>
+      <c r="G52" s="55" t="inlineStr"/>
+      <c r="H52" s="55" t="inlineStr"/>
+      <c r="I52" s="55" t="inlineStr"/>
+      <c r="J52" s="55" t="inlineStr">
         <is>
           <t>024_01</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="55" t="inlineStr">
         <is>
           <t>xie_fei_yan</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="55" t="inlineStr">
         <is>
           <t>肺阴虚</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xie_fei_yan/xie_fei_yan_sick.png</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="b">
+      <c r="P52" s="55" t="inlineStr"/>
+      <c r="Q52" s="55" t="inlineStr"/>
+      <c r="R52" s="55" t="inlineStr"/>
+      <c r="S52" s="55" t="b">
         <v>0</v>
       </c>
       <c r="T52" t="inlineStr"/>
     </row>
     <row r="53" ht="17.65" customHeight="1">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="55" t="inlineStr">
+        <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B53" s="55" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C53" s="55" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="D53" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="55" t="inlineStr"/>
+      <c r="F53" s="55" t="inlineStr"/>
+      <c r="G53" s="55" t="inlineStr"/>
+      <c r="H53" s="55" t="inlineStr"/>
+      <c r="I53" s="55" t="inlineStr"/>
+      <c r="J53" s="55" t="inlineStr">
+        <is>
+          <t>008_02</t>
+        </is>
+      </c>
+      <c r="K53" s="55" t="inlineStr"/>
+      <c r="L53" s="55" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="M53" s="55" t="inlineStr"/>
+      <c r="N53" s="55" t="inlineStr"/>
+      <c r="O53" s="55" t="inlineStr"/>
+      <c r="P53" s="55" t="inlineStr"/>
+      <c r="Q53" s="55" t="inlineStr"/>
+      <c r="R53" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="S53" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17.65" customHeight="1">
+      <c r="A54" s="55" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" s="55" t="inlineStr">
         <is>
           <t>和尚肾精不足</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
+      <c r="D54" s="55" t="inlineStr"/>
+      <c r="E54" s="55" t="inlineStr"/>
+      <c r="F54" s="55" t="inlineStr"/>
+      <c r="G54" s="55" t="inlineStr"/>
+      <c r="H54" s="55" t="inlineStr"/>
+      <c r="I54" s="55" t="inlineStr">
         <is>
           <t>肾精不足</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="J54" s="55" t="inlineStr"/>
+      <c r="K54" s="55" t="inlineStr"/>
+      <c r="L54" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" s="55" t="inlineStr">
         <is>
           <t>xing_kong</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N54" s="55" t="inlineStr">
         <is>
           <t>肾精不足</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="b">
-        <v>1</v>
-      </c>
-      <c r="T53" t="inlineStr"/>
-    </row>
-    <row r="54" ht="17.65" customHeight="1">
-      <c r="A54" t="inlineStr">
+      <c r="P54" s="55" t="inlineStr"/>
+      <c r="Q54" s="55" t="inlineStr"/>
+      <c r="R54" s="55" t="inlineStr"/>
+      <c r="S54" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+    </row>
+    <row r="55" ht="17.65" customHeight="1">
+      <c r="A55" s="55" t="inlineStr">
         <is>
           <t>025_02</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" s="55" t="inlineStr">
         <is>
           <t>025治疗成功</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="C55" s="55" t="inlineStr"/>
+      <c r="D55" s="55" t="inlineStr"/>
+      <c r="E55" s="55" t="inlineStr"/>
+      <c r="F55" s="55" t="inlineStr"/>
+      <c r="G55" s="55" t="inlineStr"/>
+      <c r="H55" s="55" t="inlineStr"/>
+      <c r="I55" s="55" t="inlineStr"/>
+      <c r="J55" s="55" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K55" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L55" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="b">
-        <v>1</v>
-      </c>
-      <c r="T54" t="inlineStr"/>
-    </row>
-    <row r="55" ht="17.65" customHeight="1">
-      <c r="A55" t="inlineStr">
+      <c r="M55" s="55" t="inlineStr"/>
+      <c r="N55" s="55" t="inlineStr"/>
+      <c r="O55" s="55" t="inlineStr"/>
+      <c r="P55" s="55" t="inlineStr"/>
+      <c r="Q55" s="55" t="inlineStr"/>
+      <c r="R55" s="55" t="inlineStr"/>
+      <c r="S55" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+    </row>
+    <row r="56" ht="17.65" customHeight="1">
+      <c r="A56" s="55" t="inlineStr">
         <is>
           <t>025_03</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" s="55" t="inlineStr">
         <is>
           <t>025治疗失败</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
+      <c r="C56" s="55" t="inlineStr"/>
+      <c r="D56" s="55" t="inlineStr"/>
+      <c r="E56" s="55" t="inlineStr"/>
+      <c r="F56" s="55" t="inlineStr"/>
+      <c r="G56" s="55" t="inlineStr"/>
+      <c r="H56" s="55" t="inlineStr"/>
+      <c r="I56" s="55" t="inlineStr"/>
+      <c r="J56" s="55" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" s="55" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M56" s="55" t="inlineStr">
         <is>
           <t>xing_kong</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N56" s="55" t="inlineStr">
         <is>
           <t>肾精不足</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O56" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="b">
+      <c r="P56" s="55" t="inlineStr"/>
+      <c r="Q56" s="55" t="inlineStr"/>
+      <c r="R56" s="55" t="inlineStr"/>
+      <c r="S56" s="55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" t="inlineStr"/>
-    </row>
-    <row r="56" ht="17.65" customHeight="1">
-      <c r="A56" t="inlineStr">
+      <c r="T56" t="inlineStr"/>
+    </row>
+    <row r="57" ht="17.65" customHeight="1">
+      <c r="A57" s="55" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" s="55" t="inlineStr">
         <is>
           <t>吴芷兰妊娠</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
+      <c r="D57" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="55" t="inlineStr"/>
+      <c r="F57" s="55" t="inlineStr"/>
+      <c r="G57" s="55" t="inlineStr"/>
+      <c r="H57" s="55" t="inlineStr"/>
+      <c r="I57" s="55" t="inlineStr">
         <is>
           <t>妊娠</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" s="55" t="inlineStr">
         <is>
           <t>027</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
+      <c r="K57" s="55" t="inlineStr"/>
+      <c r="L57" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M57" s="55" t="inlineStr">
         <is>
           <t>wu_zhi_lan</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N57" s="55" t="inlineStr">
         <is>
           <t>妊娠</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O57" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="b">
-        <v>1</v>
-      </c>
-      <c r="T56" t="inlineStr"/>
-    </row>
-    <row r="57" ht="17.65" customHeight="1">
-      <c r="A57" t="inlineStr">
+      <c r="P57" s="55" t="inlineStr"/>
+      <c r="Q57" s="55" t="inlineStr"/>
+      <c r="R57" s="55" t="inlineStr"/>
+      <c r="S57" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18.75" customHeight="1">
+      <c r="A58" s="55" t="inlineStr">
         <is>
           <t>026_02</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" s="55" t="inlineStr">
         <is>
           <t>026治疗成功</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
+      <c r="C58" s="55" t="inlineStr"/>
+      <c r="D58" s="55" t="inlineStr"/>
+      <c r="E58" s="55" t="inlineStr"/>
+      <c r="F58" s="55" t="inlineStr"/>
+      <c r="G58" s="55" t="inlineStr"/>
+      <c r="H58" s="55" t="inlineStr"/>
+      <c r="I58" s="55" t="inlineStr"/>
+      <c r="J58" s="55" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K58" s="55" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="b">
-        <v>1</v>
-      </c>
-      <c r="T57" t="inlineStr"/>
-    </row>
-    <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" t="inlineStr">
+      <c r="M58" s="55" t="inlineStr"/>
+      <c r="N58" s="55" t="inlineStr"/>
+      <c r="O58" s="55" t="inlineStr"/>
+      <c r="P58" s="55" t="inlineStr"/>
+      <c r="Q58" s="55" t="inlineStr"/>
+      <c r="R58" s="55" t="inlineStr"/>
+      <c r="S58" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18.75" customHeight="1">
+      <c r="A59" s="55" t="inlineStr">
         <is>
           <t>026_03</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" s="55" t="inlineStr">
         <is>
           <t>026治疗失败</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="C59" s="55" t="inlineStr"/>
+      <c r="D59" s="55" t="inlineStr"/>
+      <c r="E59" s="55" t="inlineStr"/>
+      <c r="F59" s="55" t="inlineStr"/>
+      <c r="G59" s="55" t="inlineStr"/>
+      <c r="H59" s="55" t="inlineStr"/>
+      <c r="I59" s="55" t="inlineStr"/>
+      <c r="J59" s="55" t="inlineStr">
         <is>
           <t>026_01</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K59" s="55" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M59" s="55" t="inlineStr">
         <is>
           <t>wu_zhi_lan</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N59" s="55" t="inlineStr">
         <is>
           <t>妊娠</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O59" s="55" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/wu_zhi_lan/wu_zhi_lan_sick.png</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="b">
+      <c r="P59" s="55" t="inlineStr"/>
+      <c r="Q59" s="55" t="inlineStr"/>
+      <c r="R59" s="55" t="inlineStr"/>
+      <c r="S59" s="55" t="b">
         <v>0</v>
       </c>
-      <c r="T58" t="inlineStr"/>
-    </row>
-    <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" t="inlineStr">
+      <c r="T59" t="inlineStr"/>
+    </row>
+    <row r="60" ht="18.75" customHeight="1">
+      <c r="A60" s="55" t="inlineStr">
         <is>
           <t>027</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" s="55" t="inlineStr">
         <is>
           <t>上元灯节</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="n">
+      <c r="C60" s="55" t="inlineStr"/>
+      <c r="D60" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="E60" s="55" t="inlineStr"/>
+      <c r="F60" s="55" t="inlineStr"/>
+      <c r="G60" s="55" t="inlineStr"/>
+      <c r="H60" s="55" t="inlineStr"/>
+      <c r="I60" s="55" t="inlineStr"/>
+      <c r="J60" s="55" t="inlineStr"/>
+      <c r="K60" s="55" t="inlineStr"/>
+      <c r="L60" s="55" t="inlineStr">
         <is>
           <t>night</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="b">
-        <v>1</v>
-      </c>
-      <c r="T59" t="inlineStr"/>
+      <c r="M60" s="55" t="inlineStr"/>
+      <c r="N60" s="55" t="inlineStr"/>
+      <c r="O60" s="55" t="inlineStr"/>
+      <c r="P60" s="55" t="inlineStr"/>
+      <c r="Q60" s="55" t="inlineStr"/>
+      <c r="R60" s="55" t="inlineStr"/>
+      <c r="S60" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8574,7 +8620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K424"/>
+  <dimension ref="A1:K430"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -8588,8 +8634,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="71" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="73" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="48"/>
-    <col width="8.875" customWidth="1" style="36" min="49" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="49"/>
+    <col width="8.875" customWidth="1" style="36" min="50" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11060,7 +11106,7 @@
       <c r="G63" s="58" t="inlineStr"/>
       <c r="H63" s="59" t="inlineStr"/>
       <c r="I63" s="58" t="inlineStr"/>
-      <c r="J63" s="78" t="inlineStr">
+      <c r="J63" s="77" t="inlineStr">
         <is>
           <t>都明白了，平常日子里看您治病，其实已经窥得些门道了。</t>
         </is>
@@ -14224,7 +14270,7 @@
       <c r="G143" s="62" t="inlineStr"/>
       <c r="H143" s="62" t="inlineStr"/>
       <c r="I143" s="62" t="inlineStr"/>
-      <c r="J143" s="79" t="inlineStr">
+      <c r="J143" s="78" t="inlineStr">
         <is>
           <t>官吏再踢一脚斛，那些被震落、洒在斛外的粮食，不算入百姓缴纳的赋税，直接入了这帮狗腿子的口袋。</t>
         </is>
@@ -15563,7 +15609,7 @@
         </is>
       </c>
       <c r="I176" s="58" t="inlineStr"/>
-      <c r="J176" s="80" t="inlineStr">
+      <c r="J176" s="79" t="inlineStr">
         <is>
           <t>还有公务在身，就不劳烦李太医啦，兄弟们，走了！</t>
         </is>
@@ -16433,7 +16479,7 @@
       <c r="G198" s="58" t="inlineStr"/>
       <c r="H198" s="59" t="inlineStr"/>
       <c r="I198" s="58" t="inlineStr"/>
-      <c r="J198" s="80" t="inlineStr">
+      <c r="J198" s="79" t="inlineStr">
         <is>
           <t>这次省内各州县的赈灾药材都要从咱们蕲州调拨，我奉命押送，全省各处跑，路上染了点风寒。</t>
         </is>
@@ -17338,7 +17384,7 @@
       <c r="G221" s="58" t="inlineStr"/>
       <c r="H221" s="59" t="inlineStr"/>
       <c r="I221" s="58" t="inlineStr"/>
-      <c r="J221" s="80" t="inlineStr">
+      <c r="J221" s="79" t="inlineStr">
         <is>
           <t>贤弟，是我。</t>
         </is>
@@ -23201,15 +23247,15 @@
       </c>
       <c r="K369" s="57" t="inlineStr"/>
     </row>
-    <row r="370" ht="34.5" customHeight="1">
+    <row r="370">
       <c r="A370" s="57" t="inlineStr">
         <is>
-          <t>025_01</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B370" s="57" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C370" s="57" t="n">
@@ -23222,7 +23268,7 @@
       </c>
       <c r="E370" s="57" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F370" s="58" t="inlineStr">
@@ -23230,20 +23276,16 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G370" s="58" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H370" s="59" t="inlineStr"/>
+      <c r="G370" s="58" t="inlineStr"/>
+      <c r="H370" s="61" t="inlineStr"/>
       <c r="I370" s="58" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J370" s="74" t="inlineStr">
-        <is>
-          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+      <c r="J370" s="57" t="inlineStr">
+        <is>
+          <t>恩公！小生拜见恩公。</t>
         </is>
       </c>
       <c r="K370" s="57" t="inlineStr"/>
@@ -23251,12 +23293,12 @@
     <row r="371">
       <c r="A371" s="57" t="inlineStr">
         <is>
-          <t>025_01</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B371" s="57" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C371" s="57" t="n">
@@ -23272,17 +23314,17 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F371" s="59" t="inlineStr">
+      <c r="F371" s="61" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G371" s="58" t="inlineStr"/>
-      <c r="H371" s="59" t="inlineStr"/>
+      <c r="H371" s="61" t="inlineStr"/>
       <c r="I371" s="58" t="inlineStr"/>
-      <c r="J371" s="74" t="inlineStr">
-        <is>
-          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
+      <c r="J371" s="57" t="inlineStr">
+        <is>
+          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
         </is>
       </c>
       <c r="K371" s="57" t="inlineStr"/>
@@ -23290,12 +23332,12 @@
     <row r="372">
       <c r="A372" s="57" t="inlineStr">
         <is>
-          <t>025_01</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B372" s="57" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C372" s="57" t="n">
@@ -23308,7 +23350,7 @@
       </c>
       <c r="E372" s="57" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F372" s="58" t="inlineStr">
@@ -23316,16 +23358,12 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G372" s="58" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H372" s="59" t="inlineStr"/>
+      <c r="G372" s="58" t="inlineStr"/>
+      <c r="H372" s="61" t="inlineStr"/>
       <c r="I372" s="58" t="inlineStr"/>
       <c r="J372" s="57" t="inlineStr">
         <is>
-          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
+          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
         </is>
       </c>
       <c r="K372" s="57" t="inlineStr"/>
@@ -23333,16 +23371,16 @@
     <row r="373">
       <c r="A373" s="57" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B373" s="57" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C373" s="57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D373" s="57" t="inlineStr">
         <is>
@@ -23351,24 +23389,20 @@
       </c>
       <c r="E373" s="57" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F373" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F373" s="58" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G373" s="58" t="inlineStr"/>
-      <c r="H373" s="59" t="inlineStr"/>
-      <c r="I373" s="58" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J373" s="74" t="inlineStr">
-        <is>
-          <t>师傅所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+      <c r="H373" s="58" t="inlineStr"/>
+      <c r="I373" s="58" t="inlineStr"/>
+      <c r="J373" s="57" t="inlineStr">
+        <is>
+          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
         </is>
       </c>
       <c r="K373" s="57" t="inlineStr"/>
@@ -23376,16 +23410,16 @@
     <row r="374">
       <c r="A374" s="57" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B374" s="57" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C374" s="57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D374" s="57" t="inlineStr">
         <is>
@@ -23394,86 +23428,74 @@
       </c>
       <c r="E374" s="57" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F374" s="58" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G374" s="58" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H374" s="59" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F374" s="61" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G374" s="58" t="inlineStr"/>
+      <c r="H374" s="58" t="inlineStr"/>
       <c r="I374" s="58" t="inlineStr"/>
       <c r="J374" s="57" t="inlineStr">
         <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+          <t>哎呀，这可太好了，真是求之不得啊。</t>
         </is>
       </c>
       <c r="K374" s="57" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="57" t="inlineStr">
-        <is>
-          <t>025_02</t>
-        </is>
-      </c>
-      <c r="B375" s="57" t="inlineStr">
-        <is>
-          <t>025治疗成功</t>
-        </is>
-      </c>
-      <c r="C375" s="57" t="n">
-        <v>3</v>
+      <c r="A375" s="62" t="inlineStr">
+        <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B375" s="62" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C375" s="62" t="n">
+        <v>6</v>
       </c>
       <c r="D375" s="57" t="inlineStr">
         <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E375" s="62" t="inlineStr"/>
+      <c r="F375" s="58" t="inlineStr"/>
+      <c r="G375" s="62" t="inlineStr"/>
+      <c r="H375" s="62" t="inlineStr"/>
+      <c r="I375" s="62" t="inlineStr"/>
+      <c r="J375" s="62" t="inlineStr">
+        <is>
+          <t>心得+5</t>
+        </is>
+      </c>
+      <c r="K375" s="62" t="inlineStr"/>
+    </row>
+    <row r="376" ht="34.5" customHeight="1">
+      <c r="A376" s="57" t="inlineStr">
+        <is>
+          <t>025_01</t>
+        </is>
+      </c>
+      <c r="B376" s="57" t="inlineStr">
+        <is>
+          <t>和尚肾精不足</t>
+        </is>
+      </c>
+      <c r="C376" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" s="57" t="inlineStr">
+        <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E375" s="57" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F375" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G375" s="58" t="inlineStr"/>
-      <c r="H375" s="59" t="inlineStr"/>
-      <c r="I375" s="58" t="inlineStr"/>
-      <c r="J375" s="57" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K375" s="57" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="57" t="inlineStr">
-        <is>
-          <t>025_02</t>
-        </is>
-      </c>
-      <c r="B376" s="57" t="inlineStr">
-        <is>
-          <t>025治疗成功</t>
-        </is>
-      </c>
-      <c r="C376" s="57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D376" s="57" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E376" s="57" t="inlineStr">
         <is>
           <t>性空</t>
@@ -23486,14 +23508,18 @@
       </c>
       <c r="G376" s="58" t="inlineStr">
         <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H376" s="58" t="inlineStr"/>
-      <c r="I376" s="58" t="inlineStr"/>
-      <c r="J376" s="57" t="inlineStr">
-        <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H376" s="59" t="inlineStr"/>
+      <c r="I376" s="58" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J376" s="74" t="inlineStr">
+        <is>
+          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
         </is>
       </c>
       <c r="K376" s="57" t="inlineStr"/>
@@ -23501,16 +23527,16 @@
     <row r="377">
       <c r="A377" s="57" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B377" s="57" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C377" s="57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D377" s="57" t="inlineStr">
         <is>
@@ -23528,11 +23554,11 @@
         </is>
       </c>
       <c r="G377" s="58" t="inlineStr"/>
-      <c r="H377" s="58" t="inlineStr"/>
+      <c r="H377" s="59" t="inlineStr"/>
       <c r="I377" s="58" t="inlineStr"/>
-      <c r="J377" s="57" t="inlineStr">
-        <is>
-          <t>是是是，师父说的对，也不是没有这个可能。</t>
+      <c r="J377" s="74" t="inlineStr">
+        <is>
+          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K377" s="57" t="inlineStr"/>
@@ -23540,16 +23566,16 @@
     <row r="378">
       <c r="A378" s="57" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B378" s="57" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C378" s="57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D378" s="57" t="inlineStr">
         <is>
@@ -23568,18 +23594,14 @@
       </c>
       <c r="G378" s="58" t="inlineStr">
         <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H378" s="62" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I378" s="62" t="inlineStr"/>
-      <c r="J378" s="81" t="inlineStr">
-        <is>
-          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H378" s="59" t="inlineStr"/>
+      <c r="I378" s="58" t="inlineStr"/>
+      <c r="J378" s="57" t="inlineStr">
+        <is>
+          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
         </is>
       </c>
       <c r="K378" s="57" t="inlineStr"/>
@@ -23596,21 +23618,33 @@
         </is>
       </c>
       <c r="C379" s="57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D379" s="57" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E379" s="57" t="inlineStr"/>
-      <c r="F379" s="58" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E379" s="57" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F379" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G379" s="58" t="inlineStr"/>
-      <c r="H379" s="62" t="inlineStr"/>
-      <c r="I379" s="62" t="inlineStr"/>
-      <c r="J379" s="63" t="inlineStr">
-        <is>
-          <t>金钱+2两</t>
+      <c r="H379" s="59" t="inlineStr"/>
+      <c r="I379" s="58" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J379" s="74" t="inlineStr">
+        <is>
+          <t>师傅所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
         </is>
       </c>
       <c r="K379" s="57" t="inlineStr"/>
@@ -23627,29 +23661,33 @@
         </is>
       </c>
       <c r="C380" s="57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D380" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E380" s="62" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F380" s="59" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G380" s="62" t="inlineStr"/>
-      <c r="H380" s="62" t="inlineStr"/>
-      <c r="I380" s="62" t="inlineStr"/>
-      <c r="J380" s="62" t="inlineStr">
-        <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
+      <c r="E380" s="57" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F380" s="58" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G380" s="58" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H380" s="59" t="inlineStr"/>
+      <c r="I380" s="58" t="inlineStr"/>
+      <c r="J380" s="57" t="inlineStr">
+        <is>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
         </is>
       </c>
       <c r="K380" s="57" t="inlineStr"/>
@@ -23666,7 +23704,7 @@
         </is>
       </c>
       <c r="C381" s="57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D381" s="57" t="inlineStr">
         <is>
@@ -23683,10 +23721,10 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G381" s="62" t="inlineStr"/>
-      <c r="H381" s="62" t="inlineStr"/>
-      <c r="I381" s="62" t="inlineStr"/>
-      <c r="J381" s="62" t="inlineStr">
+      <c r="G381" s="58" t="inlineStr"/>
+      <c r="H381" s="59" t="inlineStr"/>
+      <c r="I381" s="58" t="inlineStr"/>
+      <c r="J381" s="57" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -23705,16 +23743,16 @@
         </is>
       </c>
       <c r="C382" s="57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D382" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E382" s="62" t="inlineStr">
-        <is>
-          <t>陈皮</t>
+      <c r="E382" s="57" t="inlineStr">
+        <is>
+          <t>性空</t>
         </is>
       </c>
       <c r="F382" s="58" t="inlineStr">
@@ -23722,12 +23760,16 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G382" s="62" t="inlineStr"/>
-      <c r="H382" s="62" t="inlineStr"/>
-      <c r="I382" s="62" t="inlineStr"/>
-      <c r="J382" s="62" t="inlineStr">
-        <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+      <c r="G382" s="58" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H382" s="58" t="inlineStr"/>
+      <c r="I382" s="58" t="inlineStr"/>
+      <c r="J382" s="57" t="inlineStr">
+        <is>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
         </is>
       </c>
       <c r="K382" s="57" t="inlineStr"/>
@@ -23744,29 +23786,29 @@
         </is>
       </c>
       <c r="C383" s="57" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D383" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E383" s="62" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E383" s="57" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F383" s="59" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G383" s="62" t="inlineStr"/>
-      <c r="H383" s="62" t="inlineStr"/>
-      <c r="I383" s="62" t="inlineStr"/>
-      <c r="J383" s="62" t="inlineStr">
-        <is>
-          <t>找打！</t>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G383" s="58" t="inlineStr"/>
+      <c r="H383" s="58" t="inlineStr"/>
+      <c r="I383" s="58" t="inlineStr"/>
+      <c r="J383" s="57" t="inlineStr">
+        <is>
+          <t>是是是，师父说的对，也不是没有这个可能。</t>
         </is>
       </c>
       <c r="K383" s="57" t="inlineStr"/>
@@ -23783,16 +23825,16 @@
         </is>
       </c>
       <c r="C384" s="57" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D384" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E384" s="62" t="inlineStr">
-        <is>
-          <t>陈皮</t>
+      <c r="E384" s="57" t="inlineStr">
+        <is>
+          <t>性空</t>
         </is>
       </c>
       <c r="F384" s="58" t="inlineStr">
@@ -23800,12 +23842,20 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G384" s="62" t="inlineStr"/>
-      <c r="H384" s="62" t="inlineStr"/>
+      <c r="G384" s="58" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H384" s="62" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I384" s="62" t="inlineStr"/>
-      <c r="J384" s="62" t="inlineStr">
-        <is>
-          <t>哎哟！</t>
+      <c r="J384" s="80" t="inlineStr">
+        <is>
+          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
         </is>
       </c>
       <c r="K384" s="57" t="inlineStr"/>
@@ -23813,42 +23863,30 @@
     <row r="385">
       <c r="A385" s="57" t="inlineStr">
         <is>
-          <t>025_03</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B385" s="57" t="inlineStr">
         <is>
-          <t>025治疗失败</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C385" s="57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D385" s="57" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E385" s="57" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F385" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E385" s="57" t="inlineStr"/>
+      <c r="F385" s="58" t="inlineStr"/>
       <c r="G385" s="58" t="inlineStr"/>
-      <c r="H385" s="59" t="inlineStr"/>
-      <c r="I385" s="58" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J385" s="57" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+      <c r="H385" s="62" t="inlineStr"/>
+      <c r="I385" s="62" t="inlineStr"/>
+      <c r="J385" s="63" t="inlineStr">
+        <is>
+          <t>金钱+2两</t>
         </is>
       </c>
       <c r="K385" s="57" t="inlineStr"/>
@@ -23856,23 +23894,23 @@
     <row r="386">
       <c r="A386" s="57" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B386" s="57" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C386" s="57" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D386" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E386" s="60" t="inlineStr">
+      <c r="E386" s="62" t="inlineStr">
         <is>
           <t>半夏</t>
         </is>
@@ -23882,16 +23920,12 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G386" s="58" t="inlineStr"/>
-      <c r="H386" s="59" t="inlineStr"/>
-      <c r="I386" s="58" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J386" s="60" t="inlineStr">
-        <is>
-          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
+      <c r="G386" s="62" t="inlineStr"/>
+      <c r="H386" s="62" t="inlineStr"/>
+      <c r="I386" s="62" t="inlineStr"/>
+      <c r="J386" s="62" t="inlineStr">
+        <is>
+          <t>哇，这就是传说中的花和尚吗？</t>
         </is>
       </c>
       <c r="K386" s="57" t="inlineStr"/>
@@ -23899,23 +23933,23 @@
     <row r="387">
       <c r="A387" s="57" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B387" s="57" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C387" s="57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D387" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E387" s="60" t="inlineStr">
+      <c r="E387" s="57" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -23925,12 +23959,12 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G387" s="58" t="inlineStr"/>
-      <c r="H387" s="59" t="inlineStr"/>
-      <c r="I387" s="58" t="inlineStr"/>
-      <c r="J387" s="60" t="inlineStr">
-        <is>
-          <t>芷兰！！！</t>
+      <c r="G387" s="62" t="inlineStr"/>
+      <c r="H387" s="62" t="inlineStr"/>
+      <c r="I387" s="62" t="inlineStr"/>
+      <c r="J387" s="62" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="K387" s="57" t="inlineStr"/>
@@ -23938,46 +23972,38 @@
     <row r="388">
       <c r="A388" s="57" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B388" s="57" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C388" s="57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D388" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E388" s="60" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F388" s="59" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G388" s="58" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H388" s="59" t="inlineStr"/>
-      <c r="I388" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J388" s="60" t="inlineStr">
-        <is>
-          <t>…...</t>
+      <c r="E388" s="62" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F388" s="58" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G388" s="62" t="inlineStr"/>
+      <c r="H388" s="62" t="inlineStr"/>
+      <c r="I388" s="62" t="inlineStr"/>
+      <c r="J388" s="62" t="inlineStr">
+        <is>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
         </is>
       </c>
       <c r="K388" s="57" t="inlineStr"/>
@@ -23985,25 +24011,25 @@
     <row r="389">
       <c r="A389" s="57" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B389" s="57" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C389" s="57" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D389" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E389" s="60" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E389" s="62" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F389" s="59" t="inlineStr">
@@ -24011,16 +24037,12 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G389" s="58" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H389" s="59" t="inlineStr"/>
-      <c r="I389" s="58" t="inlineStr"/>
-      <c r="J389" s="60" t="inlineStr">
-        <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+      <c r="G389" s="62" t="inlineStr"/>
+      <c r="H389" s="62" t="inlineStr"/>
+      <c r="I389" s="62" t="inlineStr"/>
+      <c r="J389" s="62" t="inlineStr">
+        <is>
+          <t>找打！</t>
         </is>
       </c>
       <c r="K389" s="57" t="inlineStr"/>
@@ -24028,38 +24050,38 @@
     <row r="390">
       <c r="A390" s="57" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B390" s="57" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C390" s="57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D390" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E390" s="60" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F390" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G390" s="58" t="inlineStr"/>
-      <c r="H390" s="58" t="inlineStr"/>
-      <c r="I390" s="58" t="inlineStr"/>
-      <c r="J390" s="60" t="inlineStr">
-        <is>
-          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+      <c r="E390" s="62" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F390" s="58" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G390" s="62" t="inlineStr"/>
+      <c r="H390" s="62" t="inlineStr"/>
+      <c r="I390" s="62" t="inlineStr"/>
+      <c r="J390" s="62" t="inlineStr">
+        <is>
+          <t>哎哟！</t>
         </is>
       </c>
       <c r="K390" s="57" t="inlineStr"/>
@@ -24067,12 +24089,12 @@
     <row r="391">
       <c r="A391" s="57" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>025_03</t>
         </is>
       </c>
       <c r="B391" s="57" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C391" s="57" t="n">
@@ -24085,24 +24107,24 @@
       </c>
       <c r="E391" s="57" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F391" s="59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G391" s="58" t="inlineStr"/>
       <c r="H391" s="59" t="inlineStr"/>
       <c r="I391" s="58" t="inlineStr">
         <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J391" s="74" t="inlineStr">
-        <is>
-          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J391" s="57" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
         </is>
       </c>
       <c r="K391" s="57" t="inlineStr"/>
@@ -24110,38 +24132,42 @@
     <row r="392">
       <c r="A392" s="57" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B392" s="57" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C392" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D392" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E392" s="57" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F392" s="58" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E392" s="60" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F392" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G392" s="58" t="inlineStr"/>
       <c r="H392" s="59" t="inlineStr"/>
-      <c r="I392" s="58" t="inlineStr"/>
-      <c r="J392" s="57" t="inlineStr">
-        <is>
-          <t>芷兰…我们有孩子了…</t>
+      <c r="I392" s="58" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J392" s="60" t="inlineStr">
+        <is>
+          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K392" s="57" t="inlineStr"/>
@@ -24149,38 +24175,38 @@
     <row r="393">
       <c r="A393" s="57" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B393" s="57" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C393" s="57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D393" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E393" s="57" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E393" s="60" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F393" s="59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G393" s="58" t="inlineStr"/>
       <c r="H393" s="59" t="inlineStr"/>
       <c r="I393" s="58" t="inlineStr"/>
-      <c r="J393" s="57" t="inlineStr">
-        <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+      <c r="J393" s="60" t="inlineStr">
+        <is>
+          <t>芷兰！！！</t>
         </is>
       </c>
       <c r="K393" s="57" t="inlineStr"/>
@@ -24188,38 +24214,46 @@
     <row r="394">
       <c r="A394" s="57" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B394" s="57" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C394" s="57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D394" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E394" s="57" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F394" s="58" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G394" s="58" t="inlineStr"/>
-      <c r="H394" s="58" t="inlineStr"/>
-      <c r="I394" s="58" t="inlineStr"/>
-      <c r="J394" s="74" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="E394" s="60" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F394" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G394" s="58" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H394" s="59" t="inlineStr"/>
+      <c r="I394" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J394" s="60" t="inlineStr">
+        <is>
+          <t>…...</t>
         </is>
       </c>
       <c r="K394" s="57" t="inlineStr"/>
@@ -24227,38 +24261,42 @@
     <row r="395">
       <c r="A395" s="57" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B395" s="57" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C395" s="57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D395" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E395" s="57" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E395" s="60" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F395" s="59" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G395" s="58" t="inlineStr"/>
-      <c r="H395" s="58" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G395" s="58" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H395" s="59" t="inlineStr"/>
       <c r="I395" s="58" t="inlineStr"/>
-      <c r="J395" s="57" t="inlineStr">
-        <is>
-          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+      <c r="J395" s="60" t="inlineStr">
+        <is>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
         </is>
       </c>
       <c r="K395" s="57" t="inlineStr"/>
@@ -24266,23 +24304,23 @@
     <row r="396">
       <c r="A396" s="57" t="inlineStr">
         <is>
-          <t>026_03</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B396" s="57" t="inlineStr">
         <is>
-          <t>026治疗失败</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C396" s="57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D396" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E396" s="57" t="inlineStr">
+      <c r="E396" s="60" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -24293,15 +24331,11 @@
         </is>
       </c>
       <c r="G396" s="58" t="inlineStr"/>
-      <c r="H396" s="59" t="inlineStr"/>
-      <c r="I396" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J396" s="57" t="inlineStr">
-        <is>
-          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
+      <c r="H396" s="58" t="inlineStr"/>
+      <c r="I396" s="58" t="inlineStr"/>
+      <c r="J396" s="60" t="inlineStr">
+        <is>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
         </is>
       </c>
       <c r="K396" s="57" t="inlineStr"/>
@@ -24309,12 +24343,12 @@
     <row r="397">
       <c r="A397" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B397" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C397" s="57" t="n">
@@ -24325,26 +24359,26 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E397" s="60" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E397" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F397" s="59" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G397" s="58" t="inlineStr"/>
-      <c r="H397" s="61" t="inlineStr"/>
+      <c r="H397" s="59" t="inlineStr"/>
       <c r="I397" s="58" t="inlineStr">
         <is>
-          <t>res://Assets/Background/004/004.png</t>
-        </is>
-      </c>
-      <c r="J397" s="60" t="inlineStr">
-        <is>
-          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J397" s="74" t="inlineStr">
+        <is>
+          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
         </is>
       </c>
       <c r="K397" s="57" t="inlineStr"/>
@@ -24352,12 +24386,12 @@
     <row r="398">
       <c r="A398" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B398" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C398" s="57" t="n">
@@ -24368,22 +24402,22 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E398" s="60" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E398" s="57" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F398" s="58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G398" s="58" t="inlineStr"/>
-      <c r="H398" s="61" t="inlineStr"/>
+      <c r="H398" s="59" t="inlineStr"/>
       <c r="I398" s="58" t="inlineStr"/>
-      <c r="J398" s="60" t="inlineStr">
-        <is>
-          <t>太好了，咱们快出发吧。</t>
+      <c r="J398" s="57" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K398" s="57" t="inlineStr"/>
@@ -24391,12 +24425,12 @@
     <row r="399">
       <c r="A399" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B399" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C399" s="57" t="n">
@@ -24407,22 +24441,22 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E399" s="60" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F399" s="61" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E399" s="57" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F399" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G399" s="58" t="inlineStr"/>
-      <c r="H399" s="61" t="inlineStr"/>
+      <c r="H399" s="59" t="inlineStr"/>
       <c r="I399" s="58" t="inlineStr"/>
-      <c r="J399" s="60" t="inlineStr">
-        <is>
-          <t>走。</t>
+      <c r="J399" s="57" t="inlineStr">
+        <is>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
         </is>
       </c>
       <c r="K399" s="57" t="inlineStr"/>
@@ -24430,12 +24464,12 @@
     <row r="400">
       <c r="A400" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B400" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C400" s="57" t="n">
@@ -24448,24 +24482,20 @@
       </c>
       <c r="E400" s="57" t="inlineStr">
         <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F400" s="59" t="inlineStr">
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F400" s="58" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G400" s="58" t="inlineStr"/>
-      <c r="H400" s="59" t="inlineStr"/>
-      <c r="I400" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_01.png</t>
-        </is>
-      </c>
-      <c r="J400" s="60" t="inlineStr">
-        <is>
-          <t>哇，好多人啊！好热闹啊！</t>
+      <c r="H400" s="58" t="inlineStr"/>
+      <c r="I400" s="58" t="inlineStr"/>
+      <c r="J400" s="74" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
         </is>
       </c>
       <c r="K400" s="57" t="inlineStr"/>
@@ -24473,12 +24503,12 @@
     <row r="401">
       <c r="A401" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B401" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C401" s="57" t="n">
@@ -24489,26 +24519,22 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E401" s="60" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F401" s="61" t="inlineStr">
+      <c r="E401" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F401" s="59" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
       <c r="G401" s="58" t="inlineStr"/>
-      <c r="H401" s="59" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H401" s="58" t="inlineStr"/>
       <c r="I401" s="58" t="inlineStr"/>
-      <c r="J401" s="60" t="inlineStr">
-        <is>
-          <t>看你那没见过世面的样子。</t>
+      <c r="J401" s="57" t="inlineStr">
+        <is>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
         </is>
       </c>
       <c r="K401" s="57" t="inlineStr"/>
@@ -24516,16 +24542,16 @@
     <row r="402">
       <c r="A402" s="57" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_03</t>
         </is>
       </c>
       <c r="B402" s="57" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C402" s="57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D402" s="57" t="inlineStr">
         <is>
@@ -24534,7 +24560,7 @@
       </c>
       <c r="E402" s="57" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F402" s="59" t="inlineStr">
@@ -24542,19 +24568,19 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G402" s="62" t="inlineStr"/>
-      <c r="H402" s="59" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I402" s="62" t="inlineStr"/>
-      <c r="J402" s="63" t="inlineStr">
-        <is>
-          <t>找打，你别跑！</t>
-        </is>
-      </c>
-      <c r="K402" s="62" t="inlineStr"/>
+      <c r="G402" s="58" t="inlineStr"/>
+      <c r="H402" s="59" t="inlineStr"/>
+      <c r="I402" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J402" s="57" t="inlineStr">
+        <is>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
+        </is>
+      </c>
+      <c r="K402" s="57" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="57" t="inlineStr">
@@ -24568,7 +24594,7 @@
         </is>
       </c>
       <c r="C403" s="57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D403" s="57" t="inlineStr">
         <is>
@@ -24585,15 +24611,19 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G403" s="62" t="inlineStr"/>
-      <c r="H403" s="62" t="inlineStr"/>
-      <c r="I403" s="62" t="inlineStr"/>
-      <c r="J403" s="63" t="inlineStr">
-        <is>
-          <t>那边好像有唱戏的，咱们去那边看看。</t>
-        </is>
-      </c>
-      <c r="K403" s="62" t="inlineStr"/>
+      <c r="G403" s="58" t="inlineStr"/>
+      <c r="H403" s="61" t="inlineStr"/>
+      <c r="I403" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/004/004.png</t>
+        </is>
+      </c>
+      <c r="J403" s="60" t="inlineStr">
+        <is>
+          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+        </is>
+      </c>
+      <c r="K403" s="57" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="57" t="inlineStr">
@@ -24607,40 +24637,32 @@
         </is>
       </c>
       <c r="C404" s="57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D404" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E404" s="57" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F404" s="59" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G404" s="62" t="inlineStr"/>
-      <c r="H404" s="59" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I404" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_02.png</t>
-        </is>
-      </c>
-      <c r="J404" s="63" t="inlineStr">
-        <is>
-          <t>夫人，那边有座桥，咱们去走百病！</t>
-        </is>
-      </c>
-      <c r="K404" s="62" t="inlineStr"/>
+      <c r="E404" s="60" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F404" s="58" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G404" s="58" t="inlineStr"/>
+      <c r="H404" s="61" t="inlineStr"/>
+      <c r="I404" s="58" t="inlineStr"/>
+      <c r="J404" s="60" t="inlineStr">
+        <is>
+          <t>太好了，咱们快出发吧。</t>
+        </is>
+      </c>
+      <c r="K404" s="57" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="57" t="inlineStr">
@@ -24654,7 +24676,7 @@
         </is>
       </c>
       <c r="C405" s="57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D405" s="57" t="inlineStr">
         <is>
@@ -24663,27 +24685,23 @@
       </c>
       <c r="E405" s="60" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F405" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G405" s="62" t="inlineStr"/>
-      <c r="H405" s="59" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I405" s="62" t="inlineStr"/>
-      <c r="J405" s="63" t="inlineStr">
-        <is>
-          <t>走，今夜走三桥，一年无灾病。</t>
-        </is>
-      </c>
-      <c r="K405" s="62" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F405" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G405" s="58" t="inlineStr"/>
+      <c r="H405" s="61" t="inlineStr"/>
+      <c r="I405" s="58" t="inlineStr"/>
+      <c r="J405" s="60" t="inlineStr">
+        <is>
+          <t>走。</t>
+        </is>
+      </c>
+      <c r="K405" s="57" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="57" t="inlineStr">
@@ -24697,16 +24715,16 @@
         </is>
       </c>
       <c r="C406" s="57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D406" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E406" s="60" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E406" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F406" s="59" t="inlineStr">
@@ -24714,15 +24732,19 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G406" s="62" t="inlineStr"/>
-      <c r="H406" s="62" t="inlineStr"/>
-      <c r="I406" s="62" t="inlineStr"/>
-      <c r="J406" s="63" t="inlineStr">
-        <is>
-          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
-        </is>
-      </c>
-      <c r="K406" s="62" t="inlineStr"/>
+      <c r="G406" s="58" t="inlineStr"/>
+      <c r="H406" s="59" t="inlineStr"/>
+      <c r="I406" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_01.png</t>
+        </is>
+      </c>
+      <c r="J406" s="60" t="inlineStr">
+        <is>
+          <t>哇，好多人啊！好热闹啊！</t>
+        </is>
+      </c>
+      <c r="K406" s="57" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="57" t="inlineStr">
@@ -24736,7 +24758,7 @@
         </is>
       </c>
       <c r="C407" s="57" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D407" s="57" t="inlineStr">
         <is>
@@ -24745,7 +24767,7 @@
       </c>
       <c r="E407" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F407" s="61" t="inlineStr">
@@ -24753,15 +24775,19 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G407" s="62" t="inlineStr"/>
-      <c r="H407" s="62" t="inlineStr"/>
-      <c r="I407" s="62" t="inlineStr"/>
-      <c r="J407" s="63" t="inlineStr">
-        <is>
-          <t>哎哟，爹，您就别操心了。</t>
-        </is>
-      </c>
-      <c r="K407" s="62" t="inlineStr"/>
+      <c r="G407" s="58" t="inlineStr"/>
+      <c r="H407" s="59" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I407" s="58" t="inlineStr"/>
+      <c r="J407" s="60" t="inlineStr">
+        <is>
+          <t>看你那没见过世面的样子。</t>
+        </is>
+      </c>
+      <c r="K407" s="57" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="57" t="inlineStr">
@@ -24775,16 +24801,16 @@
         </is>
       </c>
       <c r="C408" s="57" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D408" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E408" s="60" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E408" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F408" s="59" t="inlineStr">
@@ -24793,11 +24819,15 @@
         </is>
       </c>
       <c r="G408" s="62" t="inlineStr"/>
-      <c r="H408" s="62" t="inlineStr"/>
+      <c r="H408" s="59" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I408" s="62" t="inlineStr"/>
       <c r="J408" s="63" t="inlineStr">
         <is>
-          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
+          <t>找打，你别跑！</t>
         </is>
       </c>
       <c r="K408" s="62" t="inlineStr"/>
@@ -24814,7 +24844,7 @@
         </is>
       </c>
       <c r="C409" s="57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D409" s="57" t="inlineStr">
         <is>
@@ -24823,12 +24853,12 @@
       </c>
       <c r="E409" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F409" s="61" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F409" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G409" s="62" t="inlineStr"/>
@@ -24836,7 +24866,7 @@
       <c r="I409" s="62" t="inlineStr"/>
       <c r="J409" s="63" t="inlineStr">
         <is>
-          <t>别说了爹，咱们看戏去吧。</t>
+          <t>那边好像有唱戏的，咱们去那边看看。</t>
         </is>
       </c>
       <c r="K409" s="62" t="inlineStr"/>
@@ -24853,29 +24883,37 @@
         </is>
       </c>
       <c r="C410" s="57" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D410" s="57" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E410" s="60" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F410" s="61" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="E410" s="57" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F410" s="59" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G410" s="62" t="inlineStr"/>
-      <c r="H410" s="62" t="inlineStr"/>
-      <c r="I410" s="58" t="inlineStr"/>
+      <c r="H410" s="59" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I410" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_02.png</t>
+        </is>
+      </c>
       <c r="J410" s="63" t="inlineStr">
         <is>
-          <t>老爷，那边儿在唱紫钗记呢。</t>
+          <t>夫人，那边有座桥，咱们去走百病！</t>
         </is>
       </c>
       <c r="K410" s="62" t="inlineStr"/>
@@ -24892,25 +24930,33 @@
         </is>
       </c>
       <c r="C411" s="57" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D411" s="57" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E411" s="62" t="inlineStr"/>
-      <c r="F411" s="57" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E411" s="60" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F411" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G411" s="62" t="inlineStr"/>
-      <c r="H411" s="62" t="inlineStr"/>
-      <c r="I411" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_03.png</t>
-        </is>
-      </c>
+      <c r="H411" s="59" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I411" s="62" t="inlineStr"/>
       <c r="J411" s="63" t="inlineStr">
         <is>
-          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
+          <t>走，今夜走三桥，一年无灾病。</t>
         </is>
       </c>
       <c r="K411" s="62" t="inlineStr"/>
@@ -24927,7 +24973,7 @@
         </is>
       </c>
       <c r="C412" s="57" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D412" s="57" t="inlineStr">
         <is>
@@ -24936,20 +24982,20 @@
       </c>
       <c r="E412" s="60" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F412" s="59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G412" s="62" t="inlineStr"/>
       <c r="H412" s="62" t="inlineStr"/>
       <c r="I412" s="62" t="inlineStr"/>
-      <c r="J412" s="62" t="inlineStr">
-        <is>
-          <t>相公，咱们去猜灯谜吧！</t>
+      <c r="J412" s="63" t="inlineStr">
+        <is>
+          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
         </is>
       </c>
       <c r="K412" s="62" t="inlineStr"/>
@@ -24966,7 +25012,7 @@
         </is>
       </c>
       <c r="C413" s="57" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D413" s="57" t="inlineStr">
         <is>
@@ -24986,9 +25032,9 @@
       <c r="G413" s="62" t="inlineStr"/>
       <c r="H413" s="62" t="inlineStr"/>
       <c r="I413" s="62" t="inlineStr"/>
-      <c r="J413" s="62" t="inlineStr">
-        <is>
-          <t>走！</t>
+      <c r="J413" s="63" t="inlineStr">
+        <is>
+          <t>哎哟，爹，您就别操心了。</t>
         </is>
       </c>
       <c r="K413" s="62" t="inlineStr"/>
@@ -25005,7 +25051,7 @@
         </is>
       </c>
       <c r="C414" s="57" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D414" s="57" t="inlineStr">
         <is>
@@ -25014,24 +25060,20 @@
       </c>
       <c r="E414" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F414" s="61" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F414" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G414" s="62" t="inlineStr"/>
       <c r="H414" s="62" t="inlineStr"/>
-      <c r="I414" s="58" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_04.png</t>
-        </is>
-      </c>
-      <c r="J414" s="75" t="inlineStr">
-        <is>
-          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
+      <c r="I414" s="62" t="inlineStr"/>
+      <c r="J414" s="63" t="inlineStr">
+        <is>
+          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
         </is>
       </c>
       <c r="K414" s="62" t="inlineStr"/>
@@ -25048,7 +25090,7 @@
         </is>
       </c>
       <c r="C415" s="57" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D415" s="57" t="inlineStr">
         <is>
@@ -25057,20 +25099,20 @@
       </c>
       <c r="E415" s="60" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F415" s="59" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F415" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G415" s="62" t="inlineStr"/>
       <c r="H415" s="62" t="inlineStr"/>
       <c r="I415" s="62" t="inlineStr"/>
-      <c r="J415" s="62" t="inlineStr">
-        <is>
-          <t>我知道，这是个"府"字。</t>
+      <c r="J415" s="63" t="inlineStr">
+        <is>
+          <t>别说了爹，咱们看戏去吧。</t>
         </is>
       </c>
       <c r="K415" s="62" t="inlineStr"/>
@@ -25087,7 +25129,7 @@
         </is>
       </c>
       <c r="C416" s="57" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D416" s="57" t="inlineStr">
         <is>
@@ -25096,20 +25138,20 @@
       </c>
       <c r="E416" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F416" s="61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G416" s="62" t="inlineStr"/>
       <c r="H416" s="62" t="inlineStr"/>
-      <c r="I416" s="62" t="inlineStr"/>
-      <c r="J416" s="62" t="inlineStr">
-        <is>
-          <t>还是娘子聪慧啊，哈哈。</t>
+      <c r="I416" s="58" t="inlineStr"/>
+      <c r="J416" s="63" t="inlineStr">
+        <is>
+          <t>老爷，那边儿在唱紫钗记呢。</t>
         </is>
       </c>
       <c r="K416" s="62" t="inlineStr"/>
@@ -25126,29 +25168,25 @@
         </is>
       </c>
       <c r="C417" s="57" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D417" s="57" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E417" s="60" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F417" s="59" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E417" s="62" t="inlineStr"/>
+      <c r="F417" s="57" t="inlineStr"/>
       <c r="G417" s="62" t="inlineStr"/>
       <c r="H417" s="62" t="inlineStr"/>
-      <c r="I417" s="62" t="inlineStr"/>
-      <c r="J417" s="62" t="inlineStr">
-        <is>
-          <t>你看这个，"大雪压青松"，打一味药材。</t>
+      <c r="I417" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_03.png</t>
+        </is>
+      </c>
+      <c r="J417" s="63" t="inlineStr">
+        <is>
+          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
         </is>
       </c>
       <c r="K417" s="62" t="inlineStr"/>
@@ -25165,7 +25203,7 @@
         </is>
       </c>
       <c r="C418" s="57" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D418" s="57" t="inlineStr">
         <is>
@@ -25174,20 +25212,20 @@
       </c>
       <c r="E418" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F418" s="61" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F418" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G418" s="62" t="inlineStr"/>
       <c r="H418" s="62" t="inlineStr"/>
       <c r="I418" s="62" t="inlineStr"/>
-      <c r="J418" s="75" t="inlineStr">
-        <is>
-          <t>这个我会，是"忍冬。</t>
+      <c r="J418" s="62" t="inlineStr">
+        <is>
+          <t>相公，咱们去猜灯谜吧！</t>
         </is>
       </c>
       <c r="K418" s="62" t="inlineStr"/>
@@ -25204,7 +25242,7 @@
         </is>
       </c>
       <c r="C419" s="57" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D419" s="57" t="inlineStr">
         <is>
@@ -25213,20 +25251,20 @@
       </c>
       <c r="E419" s="60" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F419" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F419" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G419" s="62" t="inlineStr"/>
       <c r="H419" s="62" t="inlineStr"/>
       <c r="I419" s="62" t="inlineStr"/>
-      <c r="J419" s="75" t="inlineStr">
-        <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+      <c r="J419" s="62" t="inlineStr">
+        <is>
+          <t>走！</t>
         </is>
       </c>
       <c r="K419" s="62" t="inlineStr"/>
@@ -25243,7 +25281,7 @@
         </is>
       </c>
       <c r="C420" s="57" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D420" s="57" t="inlineStr">
         <is>
@@ -25252,24 +25290,24 @@
       </c>
       <c r="E420" s="60" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F420" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F420" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G420" s="62" t="inlineStr"/>
       <c r="H420" s="62" t="inlineStr"/>
       <c r="I420" s="58" t="inlineStr">
         <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J420" s="62" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+          <t>res://Assets/Background/027/027_04.png</t>
+        </is>
+      </c>
+      <c r="J420" s="75" t="inlineStr">
+        <is>
+          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
         </is>
       </c>
       <c r="K420" s="62" t="inlineStr"/>
@@ -25286,7 +25324,7 @@
         </is>
       </c>
       <c r="C421" s="57" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D421" s="57" t="inlineStr">
         <is>
@@ -25295,12 +25333,12 @@
       </c>
       <c r="E421" s="60" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F421" s="61" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F421" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G421" s="62" t="inlineStr"/>
@@ -25308,7 +25346,7 @@
       <c r="I421" s="62" t="inlineStr"/>
       <c r="J421" s="62" t="inlineStr">
         <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+          <t>我知道，这是个"府"字。</t>
         </is>
       </c>
       <c r="K421" s="62" t="inlineStr"/>
@@ -25325,7 +25363,7 @@
         </is>
       </c>
       <c r="C422" s="57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D422" s="57" t="inlineStr">
         <is>
@@ -25334,12 +25372,12 @@
       </c>
       <c r="E422" s="60" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F422" s="59" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F422" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G422" s="62" t="inlineStr"/>
@@ -25347,7 +25385,7 @@
       <c r="I422" s="62" t="inlineStr"/>
       <c r="J422" s="62" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>还是娘子聪慧啊，哈哈。</t>
         </is>
       </c>
       <c r="K422" s="62" t="inlineStr"/>
@@ -25364,7 +25402,7 @@
         </is>
       </c>
       <c r="C423" s="57" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D423" s="57" t="inlineStr">
         <is>
@@ -25373,12 +25411,12 @@
       </c>
       <c r="E423" s="60" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F423" s="59" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G423" s="62" t="inlineStr"/>
@@ -25386,7 +25424,7 @@
       <c r="I423" s="62" t="inlineStr"/>
       <c r="J423" s="62" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>你看这个，"大雪压青松"，打一味药材。</t>
         </is>
       </c>
       <c r="K423" s="62" t="inlineStr"/>
@@ -25403,7 +25441,7 @@
         </is>
       </c>
       <c r="C424" s="57" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D424" s="57" t="inlineStr">
         <is>
@@ -25412,23 +25450,261 @@
       </c>
       <c r="E424" s="60" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F424" s="59" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F424" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G424" s="62" t="inlineStr"/>
       <c r="H424" s="62" t="inlineStr"/>
       <c r="I424" s="62" t="inlineStr"/>
-      <c r="J424" s="62" t="inlineStr">
+      <c r="J424" s="75" t="inlineStr">
+        <is>
+          <t>这个我会，是"忍冬。</t>
+        </is>
+      </c>
+      <c r="K424" s="62" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B425" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C425" s="57" t="n">
+        <v>23</v>
+      </c>
+      <c r="D425" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E425" s="60" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F425" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G425" s="62" t="inlineStr"/>
+      <c r="H425" s="62" t="inlineStr"/>
+      <c r="I425" s="62" t="inlineStr"/>
+      <c r="J425" s="75" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+        </is>
+      </c>
+      <c r="K425" s="62" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B426" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C426" s="57" t="n">
+        <v>24</v>
+      </c>
+      <c r="D426" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E426" s="60" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F426" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G426" s="62" t="inlineStr"/>
+      <c r="H426" s="62" t="inlineStr"/>
+      <c r="I426" s="58" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
+      <c r="J426" s="62" t="inlineStr">
+        <is>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+        </is>
+      </c>
+      <c r="K426" s="62" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B427" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C427" s="57" t="n">
+        <v>25</v>
+      </c>
+      <c r="D427" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E427" s="60" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F427" s="61" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G427" s="62" t="inlineStr"/>
+      <c r="H427" s="62" t="inlineStr"/>
+      <c r="I427" s="62" t="inlineStr"/>
+      <c r="J427" s="62" t="inlineStr">
+        <is>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+        </is>
+      </c>
+      <c r="K427" s="62" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B428" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C428" s="57" t="n">
+        <v>26</v>
+      </c>
+      <c r="D428" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E428" s="60" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F428" s="59" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G428" s="62" t="inlineStr"/>
+      <c r="H428" s="62" t="inlineStr"/>
+      <c r="I428" s="62" t="inlineStr"/>
+      <c r="J428" s="62" t="inlineStr">
+        <is>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+        </is>
+      </c>
+      <c r="K428" s="62" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B429" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C429" s="57" t="n">
+        <v>27</v>
+      </c>
+      <c r="D429" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E429" s="60" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F429" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G429" s="62" t="inlineStr"/>
+      <c r="H429" s="62" t="inlineStr"/>
+      <c r="I429" s="62" t="inlineStr"/>
+      <c r="J429" s="62" t="inlineStr">
+        <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K429" s="62" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="57" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B430" s="57" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C430" s="57" t="n">
+        <v>28</v>
+      </c>
+      <c r="D430" s="57" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E430" s="60" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F430" s="59" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G430" s="62" t="inlineStr"/>
+      <c r="H430" s="62" t="inlineStr"/>
+      <c r="I430" s="62" t="inlineStr"/>
+      <c r="J430" s="62" t="inlineStr">
         <is>
           <t>好了，不早了，咱们该回家了。</t>
         </is>
       </c>
-      <c r="K424" s="62" t="inlineStr"/>
+      <c r="K430" s="62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27505,8 +27781,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="122"/>
-    <col width="9" customWidth="1" style="9" min="123" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="123"/>
+    <col width="9" customWidth="1" style="9" min="124" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story'!$A$1:$AA$60</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -170,10 +170,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="BIZ UDGothic"/>
-      <charset val="128"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <family val="3"/>
-      <sz val="6"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -501,12 +501,12 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2413,8 +2413,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="78"/>
-    <col width="9.125" customWidth="1" style="23" min="79" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="79"/>
+    <col width="9.125" customWidth="1" style="23" min="80" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5558,7 +5558,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -5815,8 +5815,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="28"/>
-    <col width="9" customWidth="1" style="47" min="29" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="29"/>
+    <col width="9" customWidth="1" style="47" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -5971,7 +5971,7 @@
       <c r="S2" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T2" s="84" t="inlineStr"/>
+      <c r="T2" s="83" t="inlineStr"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="48" t="inlineStr">
@@ -6017,7 +6017,7 @@
       <c r="S3" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T3" s="84" t="inlineStr"/>
+      <c r="T3" s="83" t="inlineStr"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="48" t="inlineStr">
@@ -6063,7 +6063,7 @@
       <c r="S4" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T4" s="84" t="inlineStr"/>
+      <c r="T4" s="83" t="inlineStr"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="48" t="inlineStr">
@@ -6107,7 +6107,7 @@
       <c r="S5" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T5" s="84" t="inlineStr"/>
+      <c r="T5" s="83" t="inlineStr"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="48" t="inlineStr">
@@ -6157,7 +6157,7 @@
       <c r="S6" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T6" s="84" t="inlineStr"/>
+      <c r="T6" s="83" t="inlineStr"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="48" t="inlineStr">
@@ -6203,7 +6203,7 @@
       <c r="S7" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="84" t="inlineStr"/>
+      <c r="T7" s="83" t="inlineStr"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="48" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="S8" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="84" t="inlineStr"/>
+      <c r="T8" s="83" t="inlineStr"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="48" t="inlineStr">
@@ -6291,7 +6291,7 @@
       <c r="S9" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="84" t="inlineStr"/>
+      <c r="T9" s="83" t="inlineStr"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="48" t="inlineStr">
@@ -6333,7 +6333,7 @@
       <c r="S10" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T10" s="84" t="inlineStr"/>
+      <c r="T10" s="83" t="inlineStr"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="48" t="inlineStr">
@@ -6375,7 +6375,7 @@
       <c r="S11" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T11" s="84" t="inlineStr"/>
+      <c r="T11" s="83" t="inlineStr"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="S12" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T12" s="84" t="inlineStr"/>
+      <c r="T12" s="83" t="inlineStr"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="48" t="inlineStr">
@@ -6471,7 +6471,7 @@
       <c r="S13" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T13" s="84" t="inlineStr"/>
+      <c r="T13" s="83" t="inlineStr"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
@@ -6521,7 +6521,7 @@
       <c r="S14" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T14" s="84" t="inlineStr"/>
+      <c r="T14" s="83" t="inlineStr"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="48" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="S15" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="84" t="inlineStr"/>
+      <c r="T15" s="83" t="inlineStr"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="48" t="inlineStr">
@@ -6629,7 +6629,7 @@
       <c r="S16" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T16" s="84" t="inlineStr"/>
+      <c r="T16" s="83" t="inlineStr"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="48" t="inlineStr">
@@ -6685,7 +6685,7 @@
       <c r="S17" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T17" s="84" t="inlineStr"/>
+      <c r="T17" s="83" t="inlineStr"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
@@ -6733,7 +6733,7 @@
       <c r="S18" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T18" s="84" t="inlineStr"/>
+      <c r="T18" s="83" t="inlineStr"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="48" t="inlineStr">
@@ -6777,7 +6777,7 @@
       <c r="S19" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="84" t="inlineStr"/>
+      <c r="T19" s="83" t="inlineStr"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
@@ -6821,7 +6821,7 @@
       <c r="S20" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T20" s="84" t="inlineStr"/>
+      <c r="T20" s="83" t="inlineStr"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="48" t="inlineStr">
@@ -6877,7 +6877,7 @@
       <c r="S21" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T21" s="84" t="inlineStr"/>
+      <c r="T21" s="83" t="inlineStr"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
@@ -6921,7 +6921,7 @@
       <c r="S22" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T22" s="84" t="inlineStr"/>
+      <c r="T22" s="83" t="inlineStr"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="48" t="inlineStr">
@@ -6977,7 +6977,7 @@
       <c r="S23" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="84" t="inlineStr"/>
+      <c r="T23" s="83" t="inlineStr"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="48" t="inlineStr">
@@ -7037,7 +7037,7 @@
       <c r="S24" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="84" t="inlineStr"/>
+      <c r="T24" s="83" t="inlineStr"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="48" t="inlineStr">
@@ -7081,7 +7081,7 @@
       <c r="S25" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T25" s="84" t="inlineStr"/>
+      <c r="T25" s="83" t="inlineStr"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="48" t="inlineStr">
@@ -7137,7 +7137,7 @@
       <c r="S26" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="84" t="inlineStr"/>
+      <c r="T26" s="83" t="inlineStr"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="48" t="inlineStr">
@@ -7187,7 +7187,7 @@
       <c r="S27" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T27" s="84" t="inlineStr"/>
+      <c r="T27" s="83" t="inlineStr"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
@@ -7233,7 +7233,7 @@
       <c r="S28" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T28" s="84" t="inlineStr"/>
+      <c r="T28" s="83" t="inlineStr"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="48" t="inlineStr">
@@ -7279,7 +7279,7 @@
       <c r="S29" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T29" s="84" t="inlineStr"/>
+      <c r="T29" s="83" t="inlineStr"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="48" t="inlineStr">
@@ -7325,7 +7325,7 @@
       <c r="S30" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T30" s="84" t="inlineStr"/>
+      <c r="T30" s="83" t="inlineStr"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="48" t="inlineStr">
@@ -7371,7 +7371,7 @@
       <c r="S31" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T31" s="84" t="inlineStr"/>
+      <c r="T31" s="83" t="inlineStr"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="48" t="inlineStr">
@@ -7433,7 +7433,7 @@
       <c r="S32" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T32" s="84" t="inlineStr"/>
+      <c r="T32" s="83" t="inlineStr"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="48" t="inlineStr">
@@ -7477,7 +7477,7 @@
       <c r="S33" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T33" s="84" t="inlineStr"/>
+      <c r="T33" s="83" t="inlineStr"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
@@ -7533,7 +7533,7 @@
       <c r="S34" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="84" t="inlineStr"/>
+      <c r="T34" s="83" t="inlineStr"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="48" t="inlineStr">
@@ -7579,7 +7579,7 @@
       <c r="S35" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T35" s="84" t="inlineStr"/>
+      <c r="T35" s="83" t="inlineStr"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
@@ -7625,7 +7625,7 @@
       <c r="S36" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T36" s="84" t="inlineStr"/>
+      <c r="T36" s="83" t="inlineStr"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="48" t="inlineStr">
@@ -7687,7 +7687,7 @@
       <c r="S37" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T37" s="84" t="inlineStr"/>
+      <c r="T37" s="83" t="inlineStr"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="48" t="inlineStr">
@@ -7731,7 +7731,7 @@
       <c r="S38" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T38" s="84" t="inlineStr"/>
+      <c r="T38" s="83" t="inlineStr"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="48" t="inlineStr">
@@ -7787,7 +7787,7 @@
       <c r="S39" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="84" t="inlineStr"/>
+      <c r="T39" s="83" t="inlineStr"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
@@ -7833,7 +7833,7 @@
       <c r="S40" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T40" s="84" t="inlineStr"/>
+      <c r="T40" s="83" t="inlineStr"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="48" t="inlineStr">
@@ -7879,7 +7879,7 @@
       <c r="S41" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T41" s="84" t="inlineStr"/>
+      <c r="T41" s="83" t="inlineStr"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
@@ -7925,7 +7925,7 @@
       <c r="S42" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T42" s="84" t="inlineStr"/>
+      <c r="T42" s="83" t="inlineStr"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="48" t="inlineStr">
@@ -7971,7 +7971,7 @@
       <c r="S43" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T43" s="84" t="inlineStr"/>
+      <c r="T43" s="83" t="inlineStr"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="48" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="S44" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T44" s="84" t="inlineStr"/>
+      <c r="T44" s="83" t="inlineStr"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="48" t="inlineStr">
@@ -8071,7 +8071,7 @@
       <c r="S45" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T45" s="84" t="inlineStr"/>
+      <c r="T45" s="83" t="inlineStr"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="48" t="inlineStr">
@@ -8127,7 +8127,7 @@
       <c r="S46" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="84" t="inlineStr"/>
+      <c r="T46" s="83" t="inlineStr"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
@@ -8183,7 +8183,7 @@
       <c r="S47" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T47" s="84" t="inlineStr"/>
+      <c r="T47" s="83" t="inlineStr"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="48" t="inlineStr">
@@ -8231,7 +8231,7 @@
       <c r="S48" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T48" s="84" t="inlineStr"/>
+      <c r="T48" s="83" t="inlineStr"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
@@ -8287,7 +8287,7 @@
       <c r="S49" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="84" t="inlineStr"/>
+      <c r="T49" s="83" t="inlineStr"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
@@ -8349,7 +8349,7 @@
       <c r="S50" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T50" s="84" t="inlineStr"/>
+      <c r="T50" s="83" t="inlineStr"/>
     </row>
     <row r="51" ht="17.65" customHeight="1">
       <c r="A51" s="48" t="inlineStr">
@@ -8393,7 +8393,7 @@
       <c r="S51" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T51" s="84" t="inlineStr"/>
+      <c r="T51" s="83" t="inlineStr"/>
     </row>
     <row r="52" ht="17.65" customHeight="1">
       <c r="A52" s="48" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="S52" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="84" t="inlineStr"/>
+      <c r="T52" s="83" t="inlineStr"/>
     </row>
     <row r="53" ht="17.65" customHeight="1">
       <c r="A53" s="48" t="inlineStr">
@@ -8497,7 +8497,7 @@
       <c r="S53" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T53" s="84" t="inlineStr"/>
+      <c r="T53" s="83" t="inlineStr"/>
     </row>
     <row r="54" ht="17.65" customHeight="1">
       <c r="A54" s="48" t="inlineStr">
@@ -8553,7 +8553,7 @@
       <c r="S54" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T54" s="84" t="inlineStr"/>
+      <c r="T54" s="83" t="inlineStr"/>
     </row>
     <row r="55" ht="17.65" customHeight="1">
       <c r="A55" s="48" t="inlineStr">
@@ -8599,7 +8599,7 @@
       <c r="S55" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T55" s="84" t="inlineStr"/>
+      <c r="T55" s="83" t="inlineStr"/>
     </row>
     <row r="56" ht="17.65" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
@@ -8655,7 +8655,7 @@
       <c r="S56" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="84" t="inlineStr"/>
+      <c r="T56" s="83" t="inlineStr"/>
     </row>
     <row r="57" ht="17.65" customHeight="1">
       <c r="A57" s="48" t="inlineStr">
@@ -8717,7 +8717,7 @@
       <c r="S57" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T57" s="84" t="inlineStr"/>
+      <c r="T57" s="83" t="inlineStr"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
@@ -8761,7 +8761,7 @@
       <c r="S58" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T58" s="84" t="inlineStr"/>
+      <c r="T58" s="83" t="inlineStr"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="48" t="inlineStr">
@@ -8817,7 +8817,7 @@
       <c r="S59" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="84" t="inlineStr"/>
+      <c r="T59" s="83" t="inlineStr"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
@@ -8855,7 +8855,7 @@
       <c r="S60" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T60" s="84" t="inlineStr"/>
+      <c r="T60" s="83" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA60"/>
@@ -8883,8 +8883,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="52"/>
-    <col width="8.875" customWidth="1" style="36" min="53" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="53"/>
+    <col width="8.875" customWidth="1" style="36" min="54" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20096,7 +20096,7 @@
       <c r="H283" s="55" t="inlineStr"/>
       <c r="I283" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/020/020.png</t>
+          <t>res://Assets/Background/020/020_04.png</t>
         </is>
       </c>
       <c r="J283" s="56" t="inlineStr">
@@ -25949,7 +25949,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" customWidth="1" style="3" min="1" max="1"/>
     <col width="19.25" customWidth="1" style="3" min="2" max="2"/>
@@ -27987,7 +27987,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="1" max="1"/>
     <col width="4.5" customWidth="1" style="32" min="2" max="2"/>
@@ -28012,8 +28012,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="126"/>
-    <col width="9" customWidth="1" style="9" min="127" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="127"/>
+    <col width="9" customWidth="1" style="9" min="128" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -28823,7 +28823,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="25.5" customWidth="1" style="3" min="1" max="1"/>
     <col width="15.125" customWidth="1" style="3" min="2" max="2"/>
@@ -30927,7 +30927,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="14.375" customWidth="1" style="4" min="1" max="1"/>
     <col width="11.875" customWidth="1" style="4" min="2" max="2"/>
@@ -42706,7 +42706,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16.25" customWidth="1" style="7" min="1" max="1"/>
     <col width="11.625" customWidth="1" style="7" min="2" max="2"/>
@@ -50850,7 +50850,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="45.625" customWidth="1" min="1" max="1"/>
     <col width="23.5" customWidth="1" min="2" max="2"/>

--- a/DataTables/Data.xlsx
+++ b/DataTables/Data.xlsx
@@ -19694,7 +19694,11 @@
           <t>咯噔</t>
         </is>
       </c>
-      <c r="K273" s="50" t="inlineStr"/>
+      <c r="K273" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/020/圍剿夜襲.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="50" t="inlineStr">
@@ -20326,9 +20330,13 @@
           <t>蕲州赈灾药材贪污案惊动朝廷，锦衣卫奉旨查办，地方涉案官员数十人，贪污银钱近万两。</t>
         </is>
       </c>
-      <c r="K289" s="50" t="inlineStr"/>
-    </row>
-    <row r="290" ht="18.75" customHeight="1">
+      <c r="K289" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/021/问斩.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
       <c r="A290" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -24841,7 +24849,11 @@
           <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
         </is>
       </c>
-      <c r="K402" s="50" t="inlineStr"/>
+      <c r="K402" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="50" t="inlineStr">
